--- a/Vite-Vercel開発.xlsx
+++ b/Vite-Vercel開発.xlsx
@@ -1,26 +1,46 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="110" windowWidth="14810" windowHeight="8010"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="よく使うこまんど" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="122211" fullCalcOnLoad="1"/>
+  <calcPr calcId="122211" refMode="R1C1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+  <si>
+    <t>npm install -g vercel</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>git config --global user.name umezawakanta</t>
+    <phoneticPr fontId="1"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -48,15 +68,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -98,7 +126,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -133,7 +161,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -341,10 +369,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="D4:D5"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="4" max="4" width="40.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Vite-Vercel開発.xlsx
+++ b/Vite-Vercel開発.xlsx
@@ -1,20 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4FC54BC-D0AD-4C2B-8E96-C8795F9999B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="110" windowWidth="14810" windowHeight="8010"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="よく使うこまんど" sheetId="1" r:id="rId1"/>
+    <sheet name="ToDo" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="122211" refMode="R1C1"/>
+  <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>npm install -g vercel</t>
     <phoneticPr fontId="1"/>
@@ -23,11 +25,19 @@
     <t>git config --global user.name umezawakanta</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>Vercelにデプロイ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>できた</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -64,8 +74,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -84,9 +95,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -124,9 +135,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -161,7 +172,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -196,7 +207,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -369,19 +380,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="D4:D5"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="4" max="4" width="40.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="40.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="4:4" x14ac:dyDescent="0.15">
       <c r="D4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="4:4" x14ac:dyDescent="0.15">
       <c r="D5" t="s">
         <v>1</v>
       </c>
@@ -391,4 +402,30 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29E011BA-FF28-4838-A033-18A49EB7C30B}">
+  <dimension ref="C4:E4"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="3" max="3" width="15.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="3:5" x14ac:dyDescent="0.15">
+      <c r="C4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="1">
+        <v>45729</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Vite-Vercel開発.xlsx
+++ b/Vite-Vercel開発.xlsx
@@ -3,20 +3,34 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4FC54BC-D0AD-4C2B-8E96-C8795F9999B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B67E8B45-1756-42DB-B2CC-D12B5DB9E471}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="よく使うこまんど" sheetId="1" r:id="rId1"/>
     <sheet name="ToDo" sheetId="2" r:id="rId2"/>
+    <sheet name="開発環境" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="122211"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
   <si>
     <t>npm install -g vercel</t>
     <phoneticPr fontId="1"/>
@@ -31,6 +45,58 @@
   </si>
   <si>
     <t>できた</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://cloud.mongodb.com/v2/66f1bfd0e7dc010c6f671901#/security/network/accessList</t>
+  </si>
+  <si>
+    <t>MongoDB Atlas</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://vercel.com/umezawakantas-projects/work-time-tracker-5d9q/logs?live=true</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Vercel</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://work-time-tracker-5d9q.vercel.app/</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デプロイ先</t>
+    <rPh sb="4" eb="5">
+      <t>サキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Home改善</t>
+    <rPh sb="4" eb="6">
+      <t>カイゼン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>やった</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Home.tsx</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>資産/負債レポート改善</t>
+    <rPh sb="9" eb="11">
+      <t>カイゼン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AssetLiabilityReportPage.tsx</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -38,7 +104,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -51,6 +117,14 @@
       <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
       <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -71,14 +145,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -406,26 +483,101 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29E011BA-FF28-4838-A033-18A49EB7C30B}">
-  <dimension ref="C4:E4"/>
+  <dimension ref="C4:F6"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="3" max="3" width="15.25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="3:5" x14ac:dyDescent="0.15">
+    <row r="4" spans="3:6" x14ac:dyDescent="0.15">
       <c r="C4" t="s">
         <v>2</v>
       </c>
       <c r="D4" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="1">
+      <c r="F4" s="1">
+        <v>45729</v>
+      </c>
+    </row>
+    <row r="5" spans="3:6" x14ac:dyDescent="0.15">
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="1">
+        <v>45729</v>
+      </c>
+    </row>
+    <row r="6" spans="3:6" x14ac:dyDescent="0.15">
+      <c r="C6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="1">
         <v>45729</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="E5" r:id="rId1" xr:uid="{710BA6B0-B0F6-4236-8BB2-74C40F796674}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C954C604-59FA-4E71-B562-0C51EBE0CA48}">
+  <dimension ref="C3:D5"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="3" max="3" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="82" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="3:4" x14ac:dyDescent="0.15">
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="3:4" x14ac:dyDescent="0.15">
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="3:4" x14ac:dyDescent="0.15">
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="D4" r:id="rId1" xr:uid="{ABD404D3-B385-4979-8E15-E31861E65E28}"/>
+    <hyperlink ref="D5" r:id="rId2" xr:uid="{5796EFDF-5CB9-4253-80FF-8BF4337CB0B6}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Vite-Vercel開発.xlsx
+++ b/Vite-Vercel開発.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B67E8B45-1756-42DB-B2CC-D12B5DB9E471}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46C636D9-B298-49DD-A214-6DCF313EA4CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-135" yWindow="-135" windowWidth="29070" windowHeight="15750" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="よく使うこまんど" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
   <si>
     <t>npm install -g vercel</t>
     <phoneticPr fontId="1"/>
@@ -97,6 +97,31 @@
   </si>
   <si>
     <t>AssetLiabilityReportPage.tsx</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>npx shadcn-ui@latest add skeleton</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>npx shadcn@latest add skeleton</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>vercel</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>資産増減カレンダー改善</t>
+    <rPh sb="9" eb="11">
+      <t>カイゼン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AssetCalendarPage.tsx
+AssetCalendar.tsx
+AssetCalendar.css</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -149,10 +174,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
@@ -458,7 +486,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="D4:D5"/>
+  <dimension ref="D4:D8"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="4" max="4" width="40.125" bestFit="1" customWidth="1"/>
@@ -472,6 +500,21 @@
     <row r="5" spans="4:4" x14ac:dyDescent="0.15">
       <c r="D5" t="s">
         <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="4:4" x14ac:dyDescent="0.15">
+      <c r="D6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="4:4" x14ac:dyDescent="0.15">
+      <c r="D7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="4:4" x14ac:dyDescent="0.15">
+      <c r="D8" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -483,7 +526,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29E011BA-FF28-4838-A033-18A49EB7C30B}">
-  <dimension ref="C4:F6"/>
+  <dimension ref="C4:F7"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="3" max="3" width="21.25" bestFit="1" customWidth="1"/>
@@ -527,6 +570,20 @@
         <v>14</v>
       </c>
       <c r="F6" s="1">
+        <v>45729</v>
+      </c>
+    </row>
+    <row r="7" spans="3:6" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="C7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="1">
         <v>45729</v>
       </c>
     </row>

--- a/Vite-Vercel開発.xlsx
+++ b/Vite-Vercel開発.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46C636D9-B298-49DD-A214-6DCF313EA4CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64D821E1-B79C-428E-B875-D69B23A1A623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-135" yWindow="-135" windowWidth="29070" windowHeight="15750" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
   <si>
     <t>npm install -g vercel</t>
     <phoneticPr fontId="1"/>
@@ -122,6 +122,16 @@
     <t>AssetCalendarPage.tsx
 AssetCalendar.tsx
 AssetCalendar.css</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>各社平均タブのグラフがおかしい</t>
+    <rPh sb="0" eb="2">
+      <t>カクシャ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ヘイキン</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -526,7 +536,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29E011BA-FF28-4838-A033-18A49EB7C30B}">
-  <dimension ref="C4:F7"/>
+  <dimension ref="C4:F8"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="3" max="3" width="21.25" bestFit="1" customWidth="1"/>
@@ -585,6 +595,11 @@
       </c>
       <c r="F7" s="1">
         <v>45729</v>
+      </c>
+    </row>
+    <row r="8" spans="3:6" ht="27" x14ac:dyDescent="0.15">
+      <c r="C8" s="3" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/Vite-Vercel開発.xlsx
+++ b/Vite-Vercel開発.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64D821E1-B79C-428E-B875-D69B23A1A623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E40B36CD-86E1-4441-8FB6-6E9D25A32E48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-135" yWindow="-135" windowWidth="29070" windowHeight="15750" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="22">
   <si>
     <t>npm install -g vercel</t>
     <phoneticPr fontId="1"/>
@@ -132,6 +132,10 @@
     <rPh sb="2" eb="4">
       <t>ヘイキン</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PoliticalChart.tsx</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -601,6 +605,15 @@
       <c r="C8" s="3" t="s">
         <v>20</v>
       </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="1">
+        <v>45731</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/Vite-Vercel開発.xlsx
+++ b/Vite-Vercel開発.xlsx
@@ -3,14 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E40B36CD-86E1-4441-8FB6-6E9D25A32E48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EC1FDA3-B9C9-4832-8D99-1ECECE9D600F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-135" yWindow="-135" windowWidth="29070" windowHeight="15750" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="よく使うこまんど" sheetId="1" r:id="rId1"/>
     <sheet name="ToDo" sheetId="2" r:id="rId2"/>
     <sheet name="開発環境" sheetId="3" r:id="rId3"/>
+    <sheet name="コンポーネント分割案" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="56">
   <si>
     <t>npm install -g vercel</t>
     <phoneticPr fontId="1"/>
@@ -136,6 +137,231 @@
   </si>
   <si>
     <t>PoliticalChart.tsx</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2024年9月以降で、調査結果が登録されていない調査社と調査月が分かるように画面表示したいです。</t>
+    <rPh sb="4" eb="5">
+      <t>ネン</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ガツ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>イコウ</t>
+    </rPh>
+    <rPh sb="11" eb="15">
+      <t>チョウサケッカ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>チョウサ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>シャ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>チョウサ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ツキ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PoliticalChartのコンポーネント分割案</t>
+  </si>
+  <si>
+    <t>コンポーネント分割の構造</t>
+  </si>
+  <si>
+    <t>/components/chart/</t>
+  </si>
+  <si>
+    <t>├── PoliticalChart.tsx (メインコンポーネント)</t>
+  </si>
+  <si>
+    <t>├── hooks/</t>
+  </si>
+  <si>
+    <t>│   └── useSurveyData.ts (データ取得ロジック)</t>
+  </si>
+  <si>
+    <t>└── components/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ├── CustomTooltip.tsx (ツールチップコンポーネント)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ├── MissingDataAlert.tsx (欠落データ表示コンポーネント)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ├── ChartControls.tsx (タブ操作部分)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    └── PoliticalLineChart.tsx (実際のグラフ描画部分)</t>
+  </si>
+  <si>
+    <t>各コンポーネントの責任</t>
+  </si>
+  <si>
+    <r>
+      <t>1. useSurveyData.ts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - データ取得と加工のロジック</t>
+    </r>
+  </si>
+  <si>
+    <t>API呼び出し</t>
+  </si>
+  <si>
+    <t>データの整形と計算</t>
+  </si>
+  <si>
+    <t>状態管理</t>
+  </si>
+  <si>
+    <r>
+      <t>2. CustomTooltip.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - ツールチップの表示</t>
+    </r>
+  </si>
+  <si>
+    <t>ホバー時のデータ表示</t>
+  </si>
+  <si>
+    <r>
+      <t>3. MissingDataAlert.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - 欠落データの警告表示</t>
+    </r>
+  </si>
+  <si>
+    <t>欠落しているデータの情報表示</t>
+  </si>
+  <si>
+    <r>
+      <t>4. ChartControls.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - タブとメディア選択インターフェース</t>
+    </r>
+  </si>
+  <si>
+    <t>メディア切り替えタブのレンダリング</t>
+  </si>
+  <si>
+    <t>アクティブなメディアの管理</t>
+  </si>
+  <si>
+    <r>
+      <t>5. PoliticalLineChart.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - 実際のグラフコンポーネント</t>
+    </r>
+  </si>
+  <si>
+    <t>LineChartの描画</t>
+  </si>
+  <si>
+    <t>線の生成ロジック</t>
+  </si>
+  <si>
+    <r>
+      <t>6. PoliticalChart.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - これらをまとめる親コンポーネント</t>
+    </r>
+  </si>
+  <si>
+    <t>各コンポーネントの組み合わせ</t>
+  </si>
+  <si>
+    <t>全体のレイアウト管理</t>
+  </si>
+  <si>
+    <t>pnpm add file-saver html2canvas</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>pnpm add -D @types/file-saver</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>政党支持率グラフ改善</t>
+    <rPh sb="0" eb="2">
+      <t>セイトウ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>シジリツ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カイゼン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PoliticalChart.tsx
+TimeRangeSelector.tsx</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -143,7 +369,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -164,6 +390,39 @@
       <color theme="10"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.5"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -188,12 +447,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -500,35 +777,45 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="D4:D8"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <dimension ref="D4:D10"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="4" max="4" width="40.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="4:4" x14ac:dyDescent="0.15">
+    <row r="4" spans="4:4">
       <c r="D4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="4:4" x14ac:dyDescent="0.15">
+    <row r="5" spans="4:4">
       <c r="D5" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="4:4" x14ac:dyDescent="0.15">
+    <row r="6" spans="4:4">
       <c r="D6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="4:4" x14ac:dyDescent="0.15">
+    <row r="7" spans="4:4">
       <c r="D7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="4:4" x14ac:dyDescent="0.15">
+    <row r="8" spans="4:4">
       <c r="D8" t="s">
         <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="4:4">
+      <c r="D9" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="4:4">
+      <c r="D10" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -540,15 +827,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29E011BA-FF28-4838-A033-18A49EB7C30B}">
-  <dimension ref="C4:F8"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <dimension ref="B4:F10"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
+    <col min="2" max="2" width="2.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21.25" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="25.125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="3:6" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:6">
+      <c r="B4">
+        <v>1</v>
+      </c>
       <c r="C4" t="s">
         <v>2</v>
       </c>
@@ -559,7 +850,11 @@
         <v>45729</v>
       </c>
     </row>
-    <row r="5" spans="3:6" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:6">
+      <c r="B5">
+        <f>B4+1</f>
+        <v>2</v>
+      </c>
       <c r="C5" t="s">
         <v>10</v>
       </c>
@@ -573,7 +868,11 @@
         <v>45729</v>
       </c>
     </row>
-    <row r="6" spans="3:6" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:6">
+      <c r="B6">
+        <f t="shared" ref="B6:B9" si="0">B5+1</f>
+        <v>3</v>
+      </c>
       <c r="C6" t="s">
         <v>13</v>
       </c>
@@ -587,7 +886,11 @@
         <v>45729</v>
       </c>
     </row>
-    <row r="7" spans="3:6" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:6" ht="40.5">
+      <c r="B7">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
       <c r="C7" t="s">
         <v>18</v>
       </c>
@@ -601,7 +904,11 @@
         <v>45729</v>
       </c>
     </row>
-    <row r="8" spans="3:6" ht="27" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:6" ht="27">
+      <c r="B8">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
       <c r="C8" s="3" t="s">
         <v>20</v>
       </c>
@@ -613,6 +920,39 @@
       </c>
       <c r="F8" s="1">
         <v>45731</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" ht="67.5">
+      <c r="B9">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="1">
+        <v>45735</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" ht="27">
+      <c r="B10">
+        <f>B9+1</f>
+        <v>7</v>
+      </c>
+      <c r="C10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" s="1">
+        <v>45735</v>
       </c>
     </row>
   </sheetData>
@@ -627,13 +967,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C954C604-59FA-4E71-B562-0C51EBE0CA48}">
   <dimension ref="C3:D5"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="3" max="3" width="14.125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="82" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:4" x14ac:dyDescent="0.15">
+    <row r="3" spans="3:4">
       <c r="C3" t="s">
         <v>5</v>
       </c>
@@ -641,7 +981,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="3:4" x14ac:dyDescent="0.15">
+    <row r="4" spans="3:4">
       <c r="C4" t="s">
         <v>7</v>
       </c>
@@ -649,7 +989,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="3:4" x14ac:dyDescent="0.15">
+    <row r="5" spans="3:4">
       <c r="C5" t="s">
         <v>9</v>
       </c>
@@ -665,4 +1005,214 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57B697DF-EBFB-495C-BA65-6BC1E0B5AF25}">
+  <dimension ref="B3:B52"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetData>
+    <row r="3" spans="2:2" ht="21">
+      <c r="B3" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2" ht="16.5">
+      <c r="B5" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2">
+      <c r="B7" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2">
+      <c r="B8" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2">
+      <c r="B9" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2">
+      <c r="B10" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2">
+      <c r="B11" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2">
+      <c r="B12" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2">
+      <c r="B13" s="6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2">
+      <c r="B14" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="2:2">
+      <c r="B15" s="6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" ht="16.5">
+      <c r="B17" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2">
+      <c r="B18" s="7"/>
+    </row>
+    <row r="19" spans="2:2">
+      <c r="B19" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2">
+      <c r="B20" s="7"/>
+    </row>
+    <row r="21" spans="2:2">
+      <c r="B21" s="7"/>
+    </row>
+    <row r="22" spans="2:2">
+      <c r="B22" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2">
+      <c r="B23" s="9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2">
+      <c r="B24" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2">
+      <c r="B25" s="7"/>
+    </row>
+    <row r="26" spans="2:2">
+      <c r="B26" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2">
+      <c r="B27" s="7"/>
+    </row>
+    <row r="28" spans="2:2">
+      <c r="B28" s="7"/>
+    </row>
+    <row r="29" spans="2:2">
+      <c r="B29" s="9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2">
+      <c r="B30" s="7"/>
+    </row>
+    <row r="31" spans="2:2">
+      <c r="B31" s="8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2">
+      <c r="B32" s="7"/>
+    </row>
+    <row r="33" spans="2:2">
+      <c r="B33" s="7"/>
+    </row>
+    <row r="34" spans="2:2">
+      <c r="B34" s="9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2">
+      <c r="B35" s="7"/>
+    </row>
+    <row r="36" spans="2:2">
+      <c r="B36" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2">
+      <c r="B37" s="7"/>
+    </row>
+    <row r="38" spans="2:2">
+      <c r="B38" s="7"/>
+    </row>
+    <row r="39" spans="2:2">
+      <c r="B39" s="9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2">
+      <c r="B40" s="9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="41" spans="2:2">
+      <c r="B41" s="7"/>
+    </row>
+    <row r="42" spans="2:2">
+      <c r="B42" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="43" spans="2:2">
+      <c r="B43" s="7"/>
+    </row>
+    <row r="44" spans="2:2">
+      <c r="B44" s="7"/>
+    </row>
+    <row r="45" spans="2:2">
+      <c r="B45" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="46" spans="2:2">
+      <c r="B46" s="9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2">
+      <c r="B47" s="7"/>
+    </row>
+    <row r="48" spans="2:2">
+      <c r="B48" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2">
+      <c r="B49" s="7"/>
+    </row>
+    <row r="50" spans="2:2">
+      <c r="B50" s="7"/>
+    </row>
+    <row r="51" spans="2:2">
+      <c r="B51" s="9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2">
+      <c r="B52" s="9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Vite-Vercel開発.xlsx
+++ b/Vite-Vercel開発.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EC1FDA3-B9C9-4832-8D99-1ECECE9D600F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C754C0A-8E3A-4175-97AC-408449CF5FA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="57">
   <si>
     <t>npm install -g vercel</t>
     <phoneticPr fontId="1"/>
@@ -362,6 +362,13 @@
   <si>
     <t>PoliticalChart.tsx
 TimeRangeSelector.tsx</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コンポーネントの最新化</t>
+    <rPh sb="8" eb="11">
+      <t>サイシンカ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -827,7 +834,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29E011BA-FF28-4838-A033-18A49EB7C30B}">
-  <dimension ref="B4:F10"/>
+  <dimension ref="B4:F11"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="2.5" bestFit="1" customWidth="1"/>
@@ -953,6 +960,15 @@
       </c>
       <c r="F10" s="1">
         <v>45735</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6">
+      <c r="B11">
+        <f>B10+1</f>
+        <v>8</v>
+      </c>
+      <c r="C11" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/Vite-Vercel開発.xlsx
+++ b/Vite-Vercel開発.xlsx
@@ -3,15 +3,16 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C754C0A-8E3A-4175-97AC-408449CF5FA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F90ED236-7B14-4B1C-8FF3-66B63DF9E0D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="よく使うこまんど" sheetId="1" r:id="rId1"/>
     <sheet name="ToDo" sheetId="2" r:id="rId2"/>
-    <sheet name="開発環境" sheetId="3" r:id="rId3"/>
-    <sheet name="コンポーネント分割案" sheetId="4" r:id="rId4"/>
+    <sheet name="プロンプト" sheetId="5" r:id="rId3"/>
+    <sheet name="開発環境" sheetId="3" r:id="rId4"/>
+    <sheet name="コンポーネント分割案" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="59">
   <si>
     <t>npm install -g vercel</t>
     <phoneticPr fontId="1"/>
@@ -368,6 +369,17 @@
     <t>コンポーネントの最新化</t>
     <rPh sb="8" eb="11">
       <t>サイシンカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>このコンポーネントを改善してください。このToDoリストに登録したことしかやってはいけないというルールで運用したいです。将来的にはこのサイトを世界最高のサイトに改善し、優良でサブスクしたユーザーだけが使用できるサービスとしてリリースしたいです。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ToDoリスト改善</t>
+    <rPh sb="7" eb="9">
+      <t>カイゼン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -834,10 +846,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29E011BA-FF28-4838-A033-18A49EB7C30B}">
-  <dimension ref="B4:F11"/>
+  <dimension ref="B4:F13"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="2.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21.25" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="25.125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
@@ -969,6 +981,33 @@
       </c>
       <c r="C11" t="s">
         <v>56</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="1">
+        <v>45735</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6">
+      <c r="B12">
+        <f>B11+1</f>
+        <v>9</v>
+      </c>
+      <c r="C12" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="1">
+        <v>45738</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6">
+      <c r="B13">
+        <f>B12+1</f>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -981,6 +1020,25 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6313D91D-4E4E-4302-B673-A8C3F21575BA}">
+  <dimension ref="C3"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="3" max="3" width="83.75" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="3:3" ht="40.5">
+      <c r="C3" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C954C604-59FA-4E71-B562-0C51EBE0CA48}">
   <dimension ref="C3:D5"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -1023,7 +1081,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57B697DF-EBFB-495C-BA65-6BC1E0B5AF25}">
   <dimension ref="B3:B52"/>
   <sheetFormatPr defaultRowHeight="13.5"/>

--- a/Vite-Vercel開発.xlsx
+++ b/Vite-Vercel開発.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F90ED236-7B14-4B1C-8FF3-66B63DF9E0D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EF2D497-31DA-4B73-8D84-FF5372ADE95D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="70">
   <si>
     <t>npm install -g vercel</t>
     <phoneticPr fontId="1"/>
@@ -379,6 +379,187 @@
   <si>
     <t>ToDoリスト改善</t>
     <rPh sb="7" eb="9">
+      <t>カイゼン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>未登録一覧</t>
+    <rPh sb="0" eb="3">
+      <t>ミトウロク</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>イチラン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>選挙ウォッチのリンクを表示</t>
+    <rPh sb="0" eb="2">
+      <t>センキョ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>このページで未登録の選挙区の一覧を表示したいです。どの選挙区の候補者が未登録かみながら候補者登録をしたいです。。将来的にはこのサイトを世界最高のサイトに改善し、優良でサブスクしたユーザーだけが使用できるサービスとしてリリースしたいです。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>このページに選挙ウォッチのリンクを表示したいです。選挙ウォッチを情報源として候補者を登録するためです。
+https://senkyo.watch/shu/senkyoku
+将来的にはこのサイトを世界最高のサイトに改善し、優良でサブスクしたユーザーだけが使用できるサービスとしてリリースしたいです。</t>
+    <rPh sb="6" eb="8">
+      <t>センキョ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>センキョ</t>
+    </rPh>
+    <rPh sb="32" eb="35">
+      <t>ジョウホウゲン</t>
+    </rPh>
+    <rPh sb="38" eb="41">
+      <t>コウホシャ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>このページで「今すぐ始める」ボタンをクリックした際の機能を実装したいです。将来的にはこのサイトを世界最高のサイトに改善し、有料でサブスクしたユーザーだけが使用できるサービスとしてリリースしたいです。</t>
+    <rPh sb="7" eb="8">
+      <t>イマ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ハジ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="61" eb="63">
+      <t>ユウリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>今すぐ始める機能実装</t>
+    <rPh sb="0" eb="1">
+      <t>イマ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ハジ</t>
+    </rPh>
+    <rPh sb="6" eb="10">
+      <t>キノウジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サブスク管理の運用手順表示</t>
+    <rPh sb="4" eb="6">
+      <t>カンリ</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>ウンヨウテジュン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>このページでサブスク管理の運用手順を画面表示したいです。具多的には過去のカード利用履歴を確認してサブスクの引き落とし額を一件ずつ登録していきます。登録した月と登録していない月が分かるようにしたいです。将来的にはこのサイトを世界最高のサイトに改善し、有料でサブスクしたユーザーだけが使用できるサービスとしてリリースしたいです。</t>
+    <rPh sb="10" eb="12">
+      <t>カンリ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ウンヨウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>テジュン</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="28" eb="31">
+      <t>グタテキ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>カコ</t>
+    </rPh>
+    <rPh sb="39" eb="43">
+      <t>リヨウリレキ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="53" eb="54">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="55" eb="56">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="58" eb="59">
+      <t>ガク</t>
+    </rPh>
+    <rPh sb="60" eb="62">
+      <t>イッケン</t>
+    </rPh>
+    <rPh sb="64" eb="66">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="73" eb="75">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="77" eb="78">
+      <t>ツキ</t>
+    </rPh>
+    <rPh sb="79" eb="81">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="86" eb="87">
+      <t>ツキ</t>
+    </rPh>
+    <rPh sb="88" eb="89">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="124" eb="126">
+      <t>ユウリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>本棚改善</t>
+    <rPh sb="0" eb="2">
+      <t>ホンダナ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カイゼン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>このコンポーネントを改善してください。本を読むモチベーションを高めるページにしたいです。。将来的にはこのサイトを世界最高のサイトに改善し、有料でサブスクしたユーザーだけが使用できるサービスとしてリリースしたいです。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サブスクリプション管理の改善</t>
+    <rPh sb="12" eb="14">
       <t>カイゼン</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -846,11 +1027,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29E011BA-FF28-4838-A033-18A49EB7C30B}">
-  <dimension ref="B4:F13"/>
+  <dimension ref="B4:F18"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="3.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="25.125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
   </cols>
@@ -1008,6 +1189,84 @@
       <c r="B13">
         <f>B12+1</f>
         <v>10</v>
+      </c>
+      <c r="C13" t="s">
+        <v>59</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="1">
+        <v>45739</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6">
+      <c r="B14">
+        <f>B13+1</f>
+        <v>11</v>
+      </c>
+      <c r="C14" t="s">
+        <v>60</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="1">
+        <v>45739</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6">
+      <c r="B15">
+        <f>B14+1</f>
+        <v>12</v>
+      </c>
+      <c r="C15" t="s">
+        <v>64</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="1">
+        <v>45739</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6">
+      <c r="B16">
+        <f>B15+1</f>
+        <v>13</v>
+      </c>
+      <c r="C16" t="s">
+        <v>65</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="1">
+        <v>45739</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6">
+      <c r="B17">
+        <f>B16+1</f>
+        <v>14</v>
+      </c>
+      <c r="C17" t="s">
+        <v>67</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="1">
+        <v>45739</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6">
+      <c r="B18">
+        <f>B17+1</f>
+        <v>15</v>
+      </c>
+      <c r="C18" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -1021,7 +1280,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6313D91D-4E4E-4302-B673-A8C3F21575BA}">
-  <dimension ref="C3"/>
+  <dimension ref="C3:C8"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="3" max="3" width="83.75" bestFit="1" customWidth="1"/>
@@ -1030,6 +1289,31 @@
     <row r="3" spans="3:3" ht="40.5">
       <c r="C3" s="3" t="s">
         <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="3:3" ht="40.5">
+      <c r="C4" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="3:3" ht="94.5">
+      <c r="C5" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" spans="3:3" ht="27">
+      <c r="C6" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="3:3" ht="54">
+      <c r="C7" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" spans="3:3" ht="40.5">
+      <c r="C8" s="3" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/Vite-Vercel開発.xlsx
+++ b/Vite-Vercel開発.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EF2D497-31DA-4B73-8D84-FF5372ADE95D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A060EE3-4F6C-4DFD-8122-0675EA226BE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="72">
   <si>
     <t>npm install -g vercel</t>
     <phoneticPr fontId="1"/>
@@ -562,6 +562,14 @@
     <rPh sb="12" eb="14">
       <t>カイゼン</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>このページではカード利用履歴だけでなく銀行口座のを確認してサブスクの引き落とし額を一件ずつ登録していきます。登録した月と登録していない月が分かるようにしたいです。将来的にはこのサイトを世界最高のサイトに改善し、有料でサブスクしたユーザーだけが使用できるサービスとしてリリースしたいです。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>途中で切れてしまいました。下記の部分から再出力してください。</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1268,6 +1276,12 @@
       <c r="C18" t="s">
         <v>69</v>
       </c>
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" s="1">
+        <v>45739</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -1280,7 +1294,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6313D91D-4E4E-4302-B673-A8C3F21575BA}">
-  <dimension ref="C3:C8"/>
+  <dimension ref="C3:C10"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="3" max="3" width="83.75" bestFit="1" customWidth="1"/>
@@ -1314,6 +1328,16 @@
     <row r="8" spans="3:3" ht="40.5">
       <c r="C8" s="3" t="s">
         <v>68</v>
+      </c>
+    </row>
+    <row r="9" spans="3:3" ht="40.5">
+      <c r="C9" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10" spans="3:3">
+      <c r="C10" s="3" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/Vite-Vercel開発.xlsx
+++ b/Vite-Vercel開発.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A060EE3-4F6C-4DFD-8122-0675EA226BE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F657E0F6-CC35-421A-9A78-C7C2F838E305}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="78">
   <si>
     <t>npm install -g vercel</t>
     <phoneticPr fontId="1"/>
@@ -570,6 +570,48 @@
   </si>
   <si>
     <t>途中で切れてしまいました。下記の部分から再出力してください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>本棚のダミーデータ修正</t>
+    <rPh sb="0" eb="2">
+      <t>ホンダナ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>シュウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ダミーデータが入っている部分を実際に登録されているデータから取得するようにしてください。まずは総読書冊数部分についてお願いします。将来的にはこのサイトを世界最高のサイトに改善し、有料でサブスクしたユーザーだけが使用できるサービスとしてリリースしたいです。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ギターの練習を記録するページ</t>
+    <rPh sb="4" eb="6">
+      <t>レンシュウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>キロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>上記のサイトにギターの練習を記録するページを追加してください。いつどのような練習をやったかを記録して、それを可視化することでギター練習のモチベーションを保つことができたらよいと思います。将来的にはこのサイトを世界最高のサイトに改善し、優良でサブスクしたユーザーだけが使用できるサービスとしてリリースしたいです。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ADHD日記改善</t>
+    <rPh sb="4" eb="6">
+      <t>ニッキ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カイゼン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>このコンポーネントを改善してください。日々達成したことを記録することによって自己肯定感を高めることが狙いです。将来的にはこのサイトを世界最高のサイトに改善し、優良でサブスクしたユーザーだけが使用できるサービスとしてリリースしたいです。</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1035,7 +1077,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29E011BA-FF28-4838-A033-18A49EB7C30B}">
-  <dimension ref="B4:F18"/>
+  <dimension ref="B4:F21"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="3.5" bestFit="1" customWidth="1"/>
@@ -1283,6 +1325,51 @@
         <v>45739</v>
       </c>
     </row>
+    <row r="19" spans="2:6">
+      <c r="B19">
+        <f>B18+1</f>
+        <v>16</v>
+      </c>
+      <c r="C19" t="s">
+        <v>72</v>
+      </c>
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" s="1">
+        <v>45739</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6">
+      <c r="B20">
+        <f>B19+1</f>
+        <v>17</v>
+      </c>
+      <c r="C20" t="s">
+        <v>74</v>
+      </c>
+      <c r="D20" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" s="1">
+        <v>45739</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6">
+      <c r="B21">
+        <f>B20+1</f>
+        <v>18</v>
+      </c>
+      <c r="C21" t="s">
+        <v>76</v>
+      </c>
+      <c r="D21" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21" s="1">
+        <v>45739</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <hyperlinks>
@@ -1294,7 +1381,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6313D91D-4E4E-4302-B673-A8C3F21575BA}">
-  <dimension ref="C3:C10"/>
+  <dimension ref="C3:C13"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="3" max="3" width="83.75" bestFit="1" customWidth="1"/>
@@ -1338,6 +1425,21 @@
     <row r="10" spans="3:3">
       <c r="C10" s="3" t="s">
         <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="3:3" ht="40.5">
+      <c r="C11" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="3:3" ht="54">
+      <c r="C12" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="13" spans="3:3" ht="40.5">
+      <c r="C13" s="3" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/Vite-Vercel開発.xlsx
+++ b/Vite-Vercel開発.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F657E0F6-CC35-421A-9A78-C7C2F838E305}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81C9F148-5B3F-4F35-9EE2-5008DB2B744F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="85">
   <si>
     <t>npm install -g vercel</t>
     <phoneticPr fontId="1"/>
@@ -612,6 +612,61 @@
   </si>
   <si>
     <t>このコンポーネントを改善してください。日々達成したことを記録することによって自己肯定感を高めることが狙いです。将来的にはこのサイトを世界最高のサイトに改善し、優良でサブスクしたユーザーだけが使用できるサービスとしてリリースしたいです。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>このコンポーネントを改善してください。未実装の部分を一つづつでいいので実装してください。将来的にはこのサイトを世界最高のサイトに改善し、優良でサブスクしたユーザーだけが使用できるサービスとしてリリースしたいです。</t>
+    <rPh sb="19" eb="22">
+      <t>ミジッソウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ブブン</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>資産／負債改善</t>
+    <rPh sb="0" eb="2">
+      <t>シサン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>フサイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カイゼン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>このコンポーネントを改善してください。できる限り手間をかけずに作業時間を記録し、後でどのくらい作業に時間を費やしたのかを俯瞰できるようにしたいです。将来的にはこのサイトを世界最高のサイトに改善し、有料でサブスクしたユーザーだけが使用できるサービスとしてリリースしたいです。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作業時間の記録改善</t>
+    <rPh sb="7" eb="9">
+      <t>カイゼン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>このコンポーネントを改善してください。できる限り手間をかけずに政党支持率データを記録し、後で各社の政党支持率調査の結果を長期トレンドでグラフで確認できるようにしたいです。将来的にはこのサイトを世界最高のサイトに改善し、有料でサブスクしたユーザーだけが使用できるサービスとしてリリースしたいです。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>政党支持率トレンド改善</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>睡眠トラッカー改善</t>
+    <rPh sb="7" eb="9">
+      <t>カイゼン</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1077,7 +1132,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29E011BA-FF28-4838-A033-18A49EB7C30B}">
-  <dimension ref="B4:F21"/>
+  <dimension ref="B4:F25"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="3.5" bestFit="1" customWidth="1"/>
@@ -1370,6 +1425,60 @@
         <v>45739</v>
       </c>
     </row>
+    <row r="22" spans="2:6">
+      <c r="B22">
+        <f>B21+1</f>
+        <v>19</v>
+      </c>
+      <c r="C22" t="s">
+        <v>79</v>
+      </c>
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="1">
+        <v>45739</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6">
+      <c r="B23">
+        <f>B22+1</f>
+        <v>20</v>
+      </c>
+      <c r="C23" t="s">
+        <v>81</v>
+      </c>
+      <c r="D23" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" s="1">
+        <v>45739</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6">
+      <c r="B24">
+        <f>B23+1</f>
+        <v>21</v>
+      </c>
+      <c r="C24" t="s">
+        <v>83</v>
+      </c>
+      <c r="D24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" s="1">
+        <v>45739</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6">
+      <c r="B25">
+        <f>B24+1</f>
+        <v>22</v>
+      </c>
+      <c r="C25" t="s">
+        <v>84</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <hyperlinks>
@@ -1381,7 +1490,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6313D91D-4E4E-4302-B673-A8C3F21575BA}">
-  <dimension ref="C3:C13"/>
+  <dimension ref="C3:C16"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="3" max="3" width="83.75" bestFit="1" customWidth="1"/>
@@ -1440,6 +1549,21 @@
     <row r="13" spans="3:3" ht="40.5">
       <c r="C13" s="3" t="s">
         <v>77</v>
+      </c>
+    </row>
+    <row r="14" spans="3:3" ht="40.5">
+      <c r="C14" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="15" spans="3:3" ht="40.5">
+      <c r="C15" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" spans="3:3" ht="54">
+      <c r="C16" s="3" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/Vite-Vercel開発.xlsx
+++ b/Vite-Vercel開発.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81C9F148-5B3F-4F35-9EE2-5008DB2B744F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16CE715F-D948-4CEE-A12C-18276AB23C31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="91">
   <si>
     <t>npm install -g vercel</t>
     <phoneticPr fontId="1"/>
@@ -667,6 +667,42 @@
     <rPh sb="7" eb="9">
       <t>カイゼン</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>このコンポーネントを改善してください。できる限り手間をかけずに起床時間、就寝時間を記録し、後でどのくらい睡眠に時間を費やしたのかを俯瞰できるようにしたいです。将来的にはこのサイトを世界最高のサイトに改善し、有料でサブスクしたユーザーだけが使用できるサービスとしてリリースしたいです。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>このコンポーネントを改善してください。できる限り手間をかけずに政党支持率データを記録し、後で各社の政党支持率調査の結果を長期トレンドでグラフで確認できるようにしたいです。未実装機能があればひとつずつでいいので実装してください。将来的にはこのサイトを世界最高のサイトに改善し、有料でサブスクしたユーザーだけが使用できるサービスとしてリリースしたいです。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>このコンポーネントを改善してください。できる限り手間をかけずに資産/負債データを記録し、後で財務状況をを長期トレンドでグラフで確認できるようにしたいです。未実装機能があればひとつずつでいいので実装してください。将来的にはこのサイトを世界最高のサイトに改善し、有料でサブスクしたユーザーだけが使用できるサービスとしてリリースしたいです。日本語でお願いします。</t>
+    <rPh sb="167" eb="170">
+      <t>ニホンゴ</t>
+    </rPh>
+    <rPh sb="172" eb="173">
+      <t>ネガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>このコンポーネントを改善してください。できる限り手間をかけずに資産/負債データを記録し、後で財務状況をを長期トレンドでグラフで確認できるようにしたいです。日ごと、週ごと、2W毎、1月ごと、3ヶ月毎、半年ごと、1年ごと、2年ごと、3年ごと、5年ごと、10年ごとに目標を設定して、その目標の達成度が可視化できるとよいです。将来的にはこのサイトを世界最高のサイトに改善し、有料でサブスクしたユーザーだけが使用できるサービスとしてリリースしたいです。日本語でお願いします。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ToDoリストのリセットボタンの挙動改善</t>
+    <rPh sb="16" eb="18">
+      <t>キョドウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>カイゼン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ADHD改善</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1132,7 +1168,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29E011BA-FF28-4838-A033-18A49EB7C30B}">
-  <dimension ref="B4:F25"/>
+  <dimension ref="B4:F29"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="3.5" bestFit="1" customWidth="1"/>
@@ -1478,6 +1514,66 @@
       <c r="C25" t="s">
         <v>84</v>
       </c>
+      <c r="D25" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" s="1">
+        <v>45739</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6">
+      <c r="B26">
+        <f>B25+1</f>
+        <v>23</v>
+      </c>
+      <c r="C26" t="s">
+        <v>83</v>
+      </c>
+      <c r="D26" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" s="1">
+        <v>45739</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
+      <c r="B27">
+        <f>B26+1</f>
+        <v>24</v>
+      </c>
+      <c r="C27" t="s">
+        <v>13</v>
+      </c>
+      <c r="D27" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" s="1">
+        <v>45739</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6" ht="27">
+      <c r="B28">
+        <f>B27+1</f>
+        <v>25</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D28" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" s="1">
+        <v>45739</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6">
+      <c r="B29">
+        <f>B28+1</f>
+        <v>26</v>
+      </c>
+      <c r="C29" t="s">
+        <v>90</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -1490,9 +1586,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6313D91D-4E4E-4302-B673-A8C3F21575BA}">
-  <dimension ref="C3:C16"/>
+  <dimension ref="B3:C21"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
+    <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="83.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1564,6 +1661,34 @@
     <row r="16" spans="3:3" ht="54">
       <c r="C16" s="3" t="s">
         <v>82</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" ht="40.5">
+      <c r="C17" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" ht="54">
+      <c r="B18" s="1">
+        <v>45739</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3">
+      <c r="C19" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" ht="54">
+      <c r="C20" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" ht="67.5">
+      <c r="C21" s="3" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/Vite-Vercel開発.xlsx
+++ b/Vite-Vercel開発.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16CE715F-D948-4CEE-A12C-18276AB23C31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17F332A2-6698-4CBA-9FE3-A825928C5CE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="95">
   <si>
     <t>npm install -g vercel</t>
     <phoneticPr fontId="1"/>
@@ -615,22 +615,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>このコンポーネントを改善してください。未実装の部分を一つづつでいいので実装してください。将来的にはこのサイトを世界最高のサイトに改善し、優良でサブスクしたユーザーだけが使用できるサービスとしてリリースしたいです。</t>
-    <rPh sb="19" eb="22">
-      <t>ミジッソウ</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>ブブン</t>
-    </rPh>
-    <rPh sb="26" eb="27">
-      <t>ヒト</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>ジッソウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>資産／負債改善</t>
     <rPh sb="0" eb="2">
       <t>シサン</t>
@@ -703,6 +687,62 @@
   </si>
   <si>
     <t>ADHD改善</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>このコンポーネントを改善してください。未実装の部分を一つづつでいいので実装してください。将来的にはこのサイトを世界最高のサイトに改善し、有料でサブスクしたユーザーだけが使用できるサービスとしてリリースしたいです。日本語でお願いします。</t>
+    <rPh sb="19" eb="22">
+      <t>ミジッソウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ブブン</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="68" eb="70">
+      <t>ユウリョウ</t>
+    </rPh>
+    <rPh sb="106" eb="109">
+      <t>ニホンゴ</t>
+    </rPh>
+    <rPh sb="111" eb="112">
+      <t>ネガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>このコンポーネントを改善してください。未実装の部分を一つづつでいいので実装してください。将来的にはこのサイトを世界最高のサイトに改善し、有料でサブスクしたユーザーだけが使用できるサービスとしてリリースしたいです。日本語でお願いします。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>このコンポーネントを改善してください。未実装の部分やモックデータを使用している部分を一つづつでいいので本番用に実装してください。将来的にはこのサイトを世界最高のサイトに改善し、有料でサブスクしたユーザーだけが使用できるサービスとしてリリースしたいです。日本語でお願いします。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>型定義は一か所にまとめる</t>
+    <rPh sb="0" eb="3">
+      <t>カタテイギ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>イッ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作業時間トラッカーの改善</t>
+    <rPh sb="0" eb="4">
+      <t>サギョウジカン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カイゼン</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1168,7 +1208,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29E011BA-FF28-4838-A033-18A49EB7C30B}">
-  <dimension ref="B4:F29"/>
+  <dimension ref="B4:F31"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="3.5" bestFit="1" customWidth="1"/>
@@ -1467,7 +1507,7 @@
         <v>19</v>
       </c>
       <c r="C22" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D22" t="s">
         <v>11</v>
@@ -1482,7 +1522,7 @@
         <v>20</v>
       </c>
       <c r="C23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D23" t="s">
         <v>11</v>
@@ -1497,7 +1537,7 @@
         <v>21</v>
       </c>
       <c r="C24" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D24" t="s">
         <v>11</v>
@@ -1512,7 +1552,7 @@
         <v>22</v>
       </c>
       <c r="C25" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D25" t="s">
         <v>11</v>
@@ -1527,7 +1567,7 @@
         <v>23</v>
       </c>
       <c r="C26" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D26" t="s">
         <v>11</v>
@@ -1557,7 +1597,7 @@
         <v>25</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D28" t="s">
         <v>11</v>
@@ -1572,7 +1612,25 @@
         <v>26</v>
       </c>
       <c r="C29" t="s">
-        <v>90</v>
+        <v>89</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
+      <c r="B30">
+        <f>B29+1</f>
+        <v>27</v>
+      </c>
+      <c r="C30" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6">
+      <c r="B31">
+        <f>B30+1</f>
+        <v>28</v>
+      </c>
+      <c r="C31" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -1586,7 +1644,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6313D91D-4E4E-4302-B673-A8C3F21575BA}">
-  <dimension ref="B3:C21"/>
+  <dimension ref="B3:C25"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
@@ -1650,22 +1708,22 @@
     </row>
     <row r="14" spans="3:3" ht="40.5">
       <c r="C14" s="3" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="3:3" ht="40.5">
       <c r="C15" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="3:3" ht="54">
       <c r="C16" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="40.5">
       <c r="C17" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="54">
@@ -1673,7 +1731,7 @@
         <v>45739</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19" spans="2:3">
@@ -1683,12 +1741,38 @@
     </row>
     <row r="20" spans="2:3" ht="54">
       <c r="C20" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="67.5">
       <c r="C21" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3">
+      <c r="B22" s="1">
+        <v>45740</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" ht="40.5">
+      <c r="C23" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" ht="40.5">
+      <c r="B24" s="1">
+        <v>45741</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3">
+      <c r="B25" s="1">
+        <v>45742</v>
       </c>
     </row>
   </sheetData>

--- a/Vite-Vercel開発.xlsx
+++ b/Vite-Vercel開発.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17F332A2-6698-4CBA-9FE3-A825928C5CE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{824605D8-FB7B-4D95-89B1-F04F705FFD97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-135" yWindow="-135" windowWidth="29070" windowHeight="15750" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="よく使うこまんど" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="96">
   <si>
     <t>npm install -g vercel</t>
     <phoneticPr fontId="1"/>
@@ -743,6 +743,10 @@
     <rPh sb="10" eb="12">
       <t>カイゼン</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>vercel --prod</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1158,7 +1162,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="D4:D10"/>
+  <dimension ref="D4:D11"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="4" max="4" width="40.125" bestFit="1" customWidth="1"/>
@@ -1197,6 +1201,11 @@
     <row r="10" spans="4:4">
       <c r="D10" t="s">
         <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="4:4">
+      <c r="D11" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -1614,6 +1623,12 @@
       <c r="C29" t="s">
         <v>89</v>
       </c>
+      <c r="D29" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29" s="1">
+        <v>45743</v>
+      </c>
     </row>
     <row r="30" spans="2:6">
       <c r="B30">
@@ -1622,6 +1637,12 @@
       </c>
       <c r="C30" t="s">
         <v>93</v>
+      </c>
+      <c r="D30" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" s="1">
+        <v>45743</v>
       </c>
     </row>
     <row r="31" spans="2:6">

--- a/Vite-Vercel開発.xlsx
+++ b/Vite-Vercel開発.xlsx
@@ -1,20 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28623"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{824605D8-FB7B-4D95-89B1-F04F705FFD97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEDDAF0E-F239-4ED7-8D34-643A1B2E5A03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-135" yWindow="-135" windowWidth="29070" windowHeight="15750" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="よく使うこまんど" sheetId="1" r:id="rId1"/>
     <sheet name="ToDo" sheetId="2" r:id="rId2"/>
     <sheet name="プロンプト" sheetId="5" r:id="rId3"/>
-    <sheet name="開発環境" sheetId="3" r:id="rId4"/>
-    <sheet name="コンポーネント分割案" sheetId="4" r:id="rId5"/>
+    <sheet name="VSCodeExtension" sheetId="6" r:id="rId4"/>
+    <sheet name="開発環境" sheetId="3" r:id="rId5"/>
+    <sheet name="コンポーネント分割案" sheetId="4" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -32,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="140">
   <si>
     <t>npm install -g vercel</t>
     <phoneticPr fontId="1"/>
@@ -749,12 +751,615 @@
     <t>vercel --prod</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>code --list-extensions &gt; vscode-extensions-list.txt</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>cat vscode-extensions-list.txt | xargs -L 1 code --install-extension</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>✅ 推奨・維持したほうがよい（必要性が高い）拡張機能</t>
+  </si>
+  <si>
+    <r>
+      <t>dart-code.dart-code, dart-code.flutter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（Flutter開発に必須）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ms-python.python, ms-python.vscode-pylance, ms-python.debugpy, ms-python.isort</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（Python開発）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ms-vscode.cpptools</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（C/C++開発）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>golang.go</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（Go開発）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>rust-lang.rust-analyzer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（Rust開発）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>vue.volar</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（Vue 3向け推奨）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>dbaeumer.vscode-eslint</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（JavaScript, TypeScript開発に推奨）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>esbenp.prettier-vscode</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（コードフォーマット必須級）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>bradlc.vscode-tailwindcss</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（Tailwind CSSを使うなら必須）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>eamodio.gitlens</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（Git管理が格段に便利）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>hediet.vscode-drawio</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（図を簡単に作成できる）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>github.vscode-pull-request-github</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（GitHub利用なら非常に便利）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>pkief.material-icon-theme</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（視覚的にファイルがわかりやすくなる）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>editorconfig.editorconfig</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（チーム開発・設定共有に有効）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>streetsidesoftware.code-spell-checker</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（英文スペルチェックに有効）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ms-azuretools.vscode-docker</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（Docker利用者は必須）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>zeitnergmbh.auto-git</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（自動でGitコミットができる）</t>
+    </r>
+  </si>
+  <si>
+    <t>⚠️ 状況次第（用途次第で残す）</t>
+  </si>
+  <si>
+    <r>
+      <t>formulahendry.code-runner</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（スクリプト言語を簡単に実行したい場合）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>leizongmin.node-module-intellisense</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（Node.jsを頻繁に使う場合に便利）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>christian-kohler.npm-intellisense</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（npmのパッケージ名補完が便利だが、pnpm中心なら利用頻度低）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ms-toolsai.jupyter, ms-toolsai.jupyter-各種</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（データ分析を行うなら必須）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ms-dotnettools.csharp, ms-dotnettools.vscode-dotnet-runtime</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（.NET開発をする場合）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>msjsdiag.vscode-react-native</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（React Native開発する場合）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>firefox-devtools.vscode-firefox-debug, ms-edgedevtools.vscode-edge-devtools</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（ブラウザデバッグ用に）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>googlecloudtools.cloudcode</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（GCPを使う場合）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>shopify.ruby-lsp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（Ruby開発の場合）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>pkosta2005.heroku-command</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（Herokuを利用する場合）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>octref.vetur</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（Vue 2用の拡張機能、Vue3なら不要）</t>
+    </r>
+  </si>
+  <si>
+    <t>❌ あまり使わない場合、削除を検討してよい</t>
+  </si>
+  <si>
+    <r>
+      <t>anysphere.pyright</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（Pylanceがあれば通常不要）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>csstools.postcss</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（PostCSS特化のプロジェクト以外不要）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>davidanson.vscode-markdownlint</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（Markdownを頻繁に書かないなら削除）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>donjayamanne.githistory</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（GitLensと役割重複）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>dotjoshjohnson.xml</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（XMLをあまり扱わないなら削除）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>felipecaputo.git-project-manager</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（複数プロジェクト管理頻繁でなければ削除可）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>mrorz.language-gettext</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（gettext利用が少なければ削除）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>reditorsupport.r, rdebugger.r-debugger</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（R言語を使わないなら削除）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>sysoev.language-stylus</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（Stylusを使用しなければ削除）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>xdebug.php-debug, xdebug.php-pack, zobo.php-intellisense</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（PHP開発しないなら削除）</t>
+    </r>
+  </si>
+  <si>
+    <t>Uninstall</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -803,6 +1408,15 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -1162,10 +1776,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="D4:D11"/>
+  <dimension ref="D4:D13"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="4" max="4" width="40.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="61.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="4" spans="4:4">
@@ -1206,6 +1820,16 @@
     <row r="11" spans="4:4">
       <c r="D11" t="s">
         <v>95</v>
+      </c>
+    </row>
+    <row r="12" spans="4:4">
+      <c r="D12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="13" spans="4:4">
+      <c r="D13" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -1312,7 +1936,7 @@
         <v>45731</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="67.5">
+    <row r="9" spans="2:6" ht="54">
       <c r="B9">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1329,7 +1953,7 @@
     </row>
     <row r="10" spans="2:6" ht="27">
       <c r="B10">
-        <f>B9+1</f>
+        <f t="shared" ref="B10:B31" si="1">B9+1</f>
         <v>7</v>
       </c>
       <c r="C10" t="s">
@@ -1347,7 +1971,7 @@
     </row>
     <row r="11" spans="2:6">
       <c r="B11">
-        <f>B10+1</f>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="C11" t="s">
@@ -1362,7 +1986,7 @@
     </row>
     <row r="12" spans="2:6">
       <c r="B12">
-        <f>B11+1</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="C12" t="s">
@@ -1377,7 +2001,7 @@
     </row>
     <row r="13" spans="2:6">
       <c r="B13">
-        <f>B12+1</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="C13" t="s">
@@ -1392,7 +2016,7 @@
     </row>
     <row r="14" spans="2:6">
       <c r="B14">
-        <f>B13+1</f>
+        <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="C14" t="s">
@@ -1407,7 +2031,7 @@
     </row>
     <row r="15" spans="2:6">
       <c r="B15">
-        <f>B14+1</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="C15" t="s">
@@ -1422,7 +2046,7 @@
     </row>
     <row r="16" spans="2:6">
       <c r="B16">
-        <f>B15+1</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="C16" t="s">
@@ -1437,7 +2061,7 @@
     </row>
     <row r="17" spans="2:6">
       <c r="B17">
-        <f>B16+1</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="C17" t="s">
@@ -1452,7 +2076,7 @@
     </row>
     <row r="18" spans="2:6">
       <c r="B18">
-        <f>B17+1</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="C18" t="s">
@@ -1467,7 +2091,7 @@
     </row>
     <row r="19" spans="2:6">
       <c r="B19">
-        <f>B18+1</f>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="C19" t="s">
@@ -1482,7 +2106,7 @@
     </row>
     <row r="20" spans="2:6">
       <c r="B20">
-        <f>B19+1</f>
+        <f t="shared" si="1"/>
         <v>17</v>
       </c>
       <c r="C20" t="s">
@@ -1497,7 +2121,7 @@
     </row>
     <row r="21" spans="2:6">
       <c r="B21">
-        <f>B20+1</f>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="C21" t="s">
@@ -1512,7 +2136,7 @@
     </row>
     <row r="22" spans="2:6">
       <c r="B22">
-        <f>B21+1</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="C22" t="s">
@@ -1527,7 +2151,7 @@
     </row>
     <row r="23" spans="2:6">
       <c r="B23">
-        <f>B22+1</f>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="C23" t="s">
@@ -1542,7 +2166,7 @@
     </row>
     <row r="24" spans="2:6">
       <c r="B24">
-        <f>B23+1</f>
+        <f t="shared" si="1"/>
         <v>21</v>
       </c>
       <c r="C24" t="s">
@@ -1557,7 +2181,7 @@
     </row>
     <row r="25" spans="2:6">
       <c r="B25">
-        <f>B24+1</f>
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="C25" t="s">
@@ -1572,7 +2196,7 @@
     </row>
     <row r="26" spans="2:6">
       <c r="B26">
-        <f>B25+1</f>
+        <f t="shared" si="1"/>
         <v>23</v>
       </c>
       <c r="C26" t="s">
@@ -1587,7 +2211,7 @@
     </row>
     <row r="27" spans="2:6">
       <c r="B27">
-        <f>B26+1</f>
+        <f t="shared" si="1"/>
         <v>24</v>
       </c>
       <c r="C27" t="s">
@@ -1602,7 +2226,7 @@
     </row>
     <row r="28" spans="2:6" ht="27">
       <c r="B28">
-        <f>B27+1</f>
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
       <c r="C28" s="3" t="s">
@@ -1617,7 +2241,7 @@
     </row>
     <row r="29" spans="2:6">
       <c r="B29">
-        <f>B28+1</f>
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
       <c r="C29" t="s">
@@ -1632,7 +2256,7 @@
     </row>
     <row r="30" spans="2:6">
       <c r="B30">
-        <f>B29+1</f>
+        <f t="shared" si="1"/>
         <v>27</v>
       </c>
       <c r="C30" t="s">
@@ -1647,7 +2271,7 @@
     </row>
     <row r="31" spans="2:6">
       <c r="B31">
-        <f>B30+1</f>
+        <f t="shared" si="1"/>
         <v>28</v>
       </c>
       <c r="C31" t="s">
@@ -1803,6 +2427,339 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F88E2D65-ECA4-4EF7-BEC6-93BAB5468A01}">
+  <dimension ref="B3:C83"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetData>
+    <row r="3" spans="3:3" ht="21">
+      <c r="C3" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="4" spans="3:3">
+      <c r="C4" s="7"/>
+    </row>
+    <row r="5" spans="3:3">
+      <c r="C5" s="8" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="3:3">
+      <c r="C6" s="7"/>
+    </row>
+    <row r="7" spans="3:3">
+      <c r="C7" s="8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="3:3">
+      <c r="C8" s="7"/>
+    </row>
+    <row r="9" spans="3:3">
+      <c r="C9" s="8" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="10" spans="3:3">
+      <c r="C10" s="7"/>
+    </row>
+    <row r="11" spans="3:3">
+      <c r="C11" s="8" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="12" spans="3:3">
+      <c r="C12" s="7"/>
+    </row>
+    <row r="13" spans="3:3">
+      <c r="C13" s="8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="14" spans="3:3">
+      <c r="C14" s="7"/>
+    </row>
+    <row r="15" spans="3:3">
+      <c r="C15" s="8" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="16" spans="3:3">
+      <c r="C16" s="7"/>
+    </row>
+    <row r="17" spans="3:3">
+      <c r="C17" s="8" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="18" spans="3:3">
+      <c r="C18" s="7"/>
+    </row>
+    <row r="19" spans="3:3">
+      <c r="C19" s="8" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="20" spans="3:3">
+      <c r="C20" s="7"/>
+    </row>
+    <row r="21" spans="3:3">
+      <c r="C21" s="8" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="22" spans="3:3">
+      <c r="C22" s="7"/>
+    </row>
+    <row r="23" spans="3:3">
+      <c r="C23" s="8" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="24" spans="3:3">
+      <c r="C24" s="7"/>
+    </row>
+    <row r="25" spans="3:3">
+      <c r="C25" s="8" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="26" spans="3:3">
+      <c r="C26" s="7"/>
+    </row>
+    <row r="27" spans="3:3">
+      <c r="C27" s="8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="28" spans="3:3">
+      <c r="C28" s="7"/>
+    </row>
+    <row r="29" spans="3:3">
+      <c r="C29" s="8" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="30" spans="3:3">
+      <c r="C30" s="7"/>
+    </row>
+    <row r="31" spans="3:3">
+      <c r="C31" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="32" spans="3:3">
+      <c r="C32" s="7"/>
+    </row>
+    <row r="33" spans="3:3">
+      <c r="C33" s="8" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="34" spans="3:3">
+      <c r="C34" s="7"/>
+    </row>
+    <row r="35" spans="3:3">
+      <c r="C35" s="8" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="36" spans="3:3">
+      <c r="C36" s="7"/>
+    </row>
+    <row r="37" spans="3:3">
+      <c r="C37" s="8" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="39" spans="3:3" ht="21">
+      <c r="C39" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="40" spans="3:3">
+      <c r="C40" s="7"/>
+    </row>
+    <row r="41" spans="3:3">
+      <c r="C41" s="8" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="42" spans="3:3">
+      <c r="C42" s="7"/>
+    </row>
+    <row r="43" spans="3:3">
+      <c r="C43" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="44" spans="3:3">
+      <c r="C44" s="7"/>
+    </row>
+    <row r="45" spans="3:3">
+      <c r="C45" s="8" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="46" spans="3:3">
+      <c r="C46" s="7"/>
+    </row>
+    <row r="47" spans="3:3">
+      <c r="C47" s="7" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="48" spans="3:3">
+      <c r="C48" s="7"/>
+    </row>
+    <row r="49" spans="3:3">
+      <c r="C49" s="8" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="50" spans="3:3">
+      <c r="C50" s="7"/>
+    </row>
+    <row r="51" spans="3:3">
+      <c r="C51" s="8" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="52" spans="3:3">
+      <c r="C52" s="7"/>
+    </row>
+    <row r="53" spans="3:3">
+      <c r="C53" s="8" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="54" spans="3:3">
+      <c r="C54" s="7"/>
+    </row>
+    <row r="55" spans="3:3">
+      <c r="C55" s="8" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="56" spans="3:3">
+      <c r="C56" s="7"/>
+    </row>
+    <row r="57" spans="3:3">
+      <c r="C57" s="8" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="58" spans="3:3">
+      <c r="C58" s="7"/>
+    </row>
+    <row r="59" spans="3:3">
+      <c r="C59" s="8" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="60" spans="3:3">
+      <c r="C60" s="7"/>
+    </row>
+    <row r="61" spans="3:3">
+      <c r="C61" s="8" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="63" spans="3:3" ht="21">
+      <c r="C63" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="64" spans="3:3">
+      <c r="C64" s="7"/>
+    </row>
+    <row r="65" spans="3:3">
+      <c r="C65" s="8" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="66" spans="3:3">
+      <c r="C66" s="7"/>
+    </row>
+    <row r="67" spans="3:3">
+      <c r="C67" s="8" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="68" spans="3:3">
+      <c r="C68" s="7"/>
+    </row>
+    <row r="69" spans="3:3">
+      <c r="C69" s="8" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="70" spans="3:3">
+      <c r="C70" s="7"/>
+    </row>
+    <row r="71" spans="3:3">
+      <c r="C71" s="8" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="72" spans="3:3">
+      <c r="C72" s="7"/>
+    </row>
+    <row r="73" spans="3:3">
+      <c r="C73" s="8" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="74" spans="3:3">
+      <c r="C74" s="7"/>
+    </row>
+    <row r="75" spans="3:3">
+      <c r="C75" s="8" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="76" spans="3:3">
+      <c r="C76" s="7"/>
+    </row>
+    <row r="77" spans="3:3">
+      <c r="C77" s="8" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="78" spans="3:3">
+      <c r="C78" s="7"/>
+    </row>
+    <row r="79" spans="3:3">
+      <c r="C79" s="8" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="80" spans="3:3">
+      <c r="C80" s="7"/>
+    </row>
+    <row r="81" spans="2:3">
+      <c r="C81" s="8" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="82" spans="2:3">
+      <c r="C82" s="7"/>
+    </row>
+    <row r="83" spans="2:3">
+      <c r="B83" t="s">
+        <v>139</v>
+      </c>
+      <c r="C83" s="8" t="s">
+        <v>138</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C954C604-59FA-4E71-B562-0C51EBE0CA48}">
   <dimension ref="C3:D5"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -1845,7 +2802,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57B697DF-EBFB-495C-BA65-6BC1E0B5AF25}">
   <dimension ref="B3:B52"/>
   <sheetFormatPr defaultRowHeight="13.5"/>

--- a/Vite-Vercel開発.xlsx
+++ b/Vite-Vercel開発.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28623"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEDDAF0E-F239-4ED7-8D34-643A1B2E5A03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38F8A5A1-FFCA-4293-917D-3E6E4132B181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="よく使うこまんど" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="145">
   <si>
     <t>npm install -g vercel</t>
     <phoneticPr fontId="1"/>
@@ -1352,6 +1352,37 @@
   </si>
   <si>
     <t>Uninstall</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>pnpm clean</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>pnpm store prune</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>pnpm --recursive exec -- rm -rf node_modules
+pnpm store prune
+pnpm install</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>pnpm rebuild</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ローカルストレージ保存は全部直す</t>
+    <rPh sb="9" eb="11">
+      <t>ホゾン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ゼンブ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ナオ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1776,7 +1807,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="D4:D13"/>
+  <dimension ref="D4:D17"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="4" max="4" width="61.125" bestFit="1" customWidth="1"/>
@@ -1830,6 +1861,26 @@
     <row r="13" spans="4:4">
       <c r="D13" t="s">
         <v>97</v>
+      </c>
+    </row>
+    <row r="14" spans="4:4">
+      <c r="D14" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="15" spans="4:4">
+      <c r="D15" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="16" spans="4:4" ht="40.5">
+      <c r="D16" s="3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="17" spans="4:4">
+      <c r="D17" t="s">
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -1841,7 +1892,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29E011BA-FF28-4838-A033-18A49EB7C30B}">
-  <dimension ref="B4:F31"/>
+  <dimension ref="B4:F32"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="3.5" bestFit="1" customWidth="1"/>
@@ -1953,7 +2004,7 @@
     </row>
     <row r="10" spans="2:6" ht="27">
       <c r="B10">
-        <f t="shared" ref="B10:B31" si="1">B9+1</f>
+        <f t="shared" ref="B10:B32" si="1">B9+1</f>
         <v>7</v>
       </c>
       <c r="C10" t="s">
@@ -2276,6 +2327,21 @@
       </c>
       <c r="C31" t="s">
         <v>94</v>
+      </c>
+      <c r="D31" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31" s="1">
+        <v>45747</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6" ht="27">
+      <c r="B32">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>144</v>
       </c>
     </row>
   </sheetData>

--- a/Vite-Vercel開発.xlsx
+++ b/Vite-Vercel開発.xlsx
@@ -3,17 +3,18 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28623"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38F8A5A1-FFCA-4293-917D-3E6E4132B181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9A3B0B5-912C-4873-A6A2-EB70C2497142}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-135" yWindow="-135" windowWidth="29070" windowHeight="15750" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="よく使うこまんど" sheetId="1" r:id="rId1"/>
     <sheet name="ToDo" sheetId="2" r:id="rId2"/>
-    <sheet name="プロンプト" sheetId="5" r:id="rId3"/>
-    <sheet name="VSCodeExtension" sheetId="6" r:id="rId4"/>
-    <sheet name="開発環境" sheetId="3" r:id="rId5"/>
-    <sheet name="コンポーネント分割案" sheetId="4" r:id="rId6"/>
+    <sheet name="開発ToDo" sheetId="7" r:id="rId3"/>
+    <sheet name="プロンプト" sheetId="5" r:id="rId4"/>
+    <sheet name="VSCodeExtension" sheetId="6" r:id="rId5"/>
+    <sheet name="開発環境" sheetId="3" r:id="rId6"/>
+    <sheet name="コンポーネント分割案" sheetId="4" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <fileRecoveryPr repairLoad="1"/>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="161">
   <si>
     <t>npm install -g vercel</t>
     <phoneticPr fontId="1"/>
@@ -1382,6 +1383,100 @@
     </rPh>
     <rPh sb="14" eb="15">
       <t>ナオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>pnpm remove react-beautiful-dnd</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>pnpm add @hello-pangea/dnd</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>通知機能のAPI連携</t>
+    <rPh sb="0" eb="2">
+      <t>ツウチ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>レンケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>通知機能の実装</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>現在、通知機能はモックデータを使用していますが、これを実際のAPIと連携させましょう。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>src/services/api/notificationApi.js</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>通知機能のAPI実装</t>
+    <rPh sb="0" eb="2">
+      <t>ツウチ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次に、Layout.tsxコンポーネントで通知機能の実装部分を更新します。モックデータの代わりに実際のAPIを使用するよう変更しましょう。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Layout.tsx</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Layout.tsx - 通知機能の改善</t>
+    <rPh sb="13" eb="15">
+      <t>ツウチ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>カイゼン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次に、通知機能の表示部分を改善し、未読/既読状態の視覚的な区別や操作性を向上させましょう。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>src/components/notifications/NotificationItem.tsx</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NotificationItem コンポーネント</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次に、サブスクリプション管理機能を改善し、実際の決済システムと連携できるようにしましょう。Stripeを使った決済システムの実装例を作成します。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>src/pages/SubscriptionManagement.tsx</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サブスクリプション管理ページ</t>
+    <rPh sb="9" eb="11">
+      <t>カンリ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1807,7 +1902,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="D4:D17"/>
+  <dimension ref="D4:D19"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="4" max="4" width="61.125" bestFit="1" customWidth="1"/>
@@ -1881,6 +1976,16 @@
     <row r="17" spans="4:4">
       <c r="D17" t="s">
         <v>143</v>
+      </c>
+    </row>
+    <row r="18" spans="4:4">
+      <c r="D18" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="19" spans="4:4">
+      <c r="D19" t="s">
+        <v>146</v>
       </c>
     </row>
   </sheetData>
@@ -1892,7 +1997,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29E011BA-FF28-4838-A033-18A49EB7C30B}">
-  <dimension ref="B4:F32"/>
+  <dimension ref="B4:F33"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="3.5" bestFit="1" customWidth="1"/>
@@ -2004,7 +2109,7 @@
     </row>
     <row r="10" spans="2:6" ht="27">
       <c r="B10">
-        <f t="shared" ref="B10:B32" si="1">B9+1</f>
+        <f t="shared" ref="B10:B33" si="1">B9+1</f>
         <v>7</v>
       </c>
       <c r="C10" t="s">
@@ -2342,6 +2447,15 @@
       </c>
       <c r="C32" s="3" t="s">
         <v>144</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3">
+      <c r="B33">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="C33" t="s">
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -2354,6 +2468,74 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42DE40CD-4CA6-4FF4-B0DA-D079807C6662}">
+  <dimension ref="B3:F6"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.125" customWidth="1"/>
+    <col min="5" max="5" width="45.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:6" ht="40.5">
+      <c r="B3" s="1">
+        <v>45747</v>
+      </c>
+      <c r="C3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" ht="54">
+      <c r="D4" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="E4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F4" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" ht="40.5">
+      <c r="D5" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="E5" t="s">
+        <v>156</v>
+      </c>
+      <c r="F5" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" ht="54">
+      <c r="D6" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E6" t="s">
+        <v>159</v>
+      </c>
+      <c r="F6" t="s">
+        <v>160</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6313D91D-4E4E-4302-B673-A8C3F21575BA}">
   <dimension ref="B3:C25"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -2492,7 +2674,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F88E2D65-ECA4-4EF7-BEC6-93BAB5468A01}">
   <dimension ref="B3:C83"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -2825,7 +3007,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C954C604-59FA-4E71-B562-0C51EBE0CA48}">
   <dimension ref="C3:D5"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -2868,7 +3050,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57B697DF-EBFB-495C-BA65-6BC1E0B5AF25}">
   <dimension ref="B3:B52"/>
   <sheetFormatPr defaultRowHeight="13.5"/>

--- a/Vite-Vercel開発.xlsx
+++ b/Vite-Vercel開発.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28623"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9A3B0B5-912C-4873-A6A2-EB70C2497142}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF9979DC-8DF2-4118-B63C-DBB366F14468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-135" yWindow="-135" windowWidth="29070" windowHeight="15750" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="174">
   <si>
     <t>npm install -g vercel</t>
     <phoneticPr fontId="1"/>
@@ -1478,6 +1478,57 @@
     <rPh sb="9" eb="11">
       <t>カンリ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ご指定いただいたとおり、まずは通知機能のAPI実装から始めたいと思います。他のAPIと同様のスタイルで通知用のAPIを実装します。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>src/services/api/notificationApi.ts</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次に、Layout.tsxコンポーネントで通知機能の実装部分を更新してください。モックデータの代わりに実際のAPIを使用するよう変更してください。一気に全部出力せずにひとつずつでお願いします。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>まずは、通知機能のAPI実装からお願いします。一気に全部出力せずにひとつずつでお願いします。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>〇</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次にNotificationItem.tsxの部分を実装してください。一気に全部出力せずにひとつずつでお願いします。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>他のバックエンド処理と合わせた形で通知API（Notification API）の実装を行います。まずはモデル部分から実装しましょう。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>src\server\models\Notification.ts</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次に、通知設定を管理するためのモデルを作成します。これによりユーザーごとに通知設定を保存できるようになります。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>src\server\models\NotificationSettings.ts</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次に、通知のルーティング処理を実装します。これには通知の取得、既読設定、削除などの機能が含まれます。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>src\server\routes\notificationRoutes.ts</t>
+  </si>
+  <si>
+    <t>src\server\routes\notificationRoutes.ts</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2469,17 +2520,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42DE40CD-4CA6-4FF4-B0DA-D079807C6662}">
-  <dimension ref="B3:F6"/>
+  <dimension ref="B3:G13"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="31.125" customWidth="1"/>
     <col min="5" max="5" width="45.375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="37.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:6" ht="40.5">
+    <row r="3" spans="2:7" ht="40.5">
       <c r="B3" s="1">
         <v>45747</v>
       </c>
@@ -2496,7 +2547,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="4" spans="2:6" ht="54">
+    <row r="4" spans="2:7" ht="54">
       <c r="D4" s="3" t="s">
         <v>152</v>
       </c>
@@ -2507,7 +2558,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="5" spans="2:6" ht="40.5">
+    <row r="5" spans="2:7" ht="40.5">
       <c r="D5" s="3" t="s">
         <v>155</v>
       </c>
@@ -2518,7 +2569,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="6" spans="2:6" ht="54">
+    <row r="6" spans="2:7" ht="54">
       <c r="D6" s="3" t="s">
         <v>158</v>
       </c>
@@ -2527,6 +2578,86 @@
       </c>
       <c r="F6" t="s">
         <v>160</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" ht="54">
+      <c r="D7" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="E7" t="s">
+        <v>162</v>
+      </c>
+      <c r="F7" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" ht="40.5">
+      <c r="D8" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="E8" t="s">
+        <v>162</v>
+      </c>
+      <c r="F8" t="s">
+        <v>151</v>
+      </c>
+      <c r="G8" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" ht="81">
+      <c r="D9" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="E9" t="s">
+        <v>153</v>
+      </c>
+      <c r="F9" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" ht="40.5">
+      <c r="D10" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="E10" t="s">
+        <v>156</v>
+      </c>
+      <c r="F10" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" ht="54">
+      <c r="D11" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="E11" t="s">
+        <v>168</v>
+      </c>
+      <c r="F11" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" ht="54">
+      <c r="D12" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="E12" t="s">
+        <v>170</v>
+      </c>
+      <c r="F12" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" ht="40.5">
+      <c r="D13" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E13" t="s">
+        <v>173</v>
+      </c>
+      <c r="F13" t="s">
+        <v>172</v>
       </c>
     </row>
   </sheetData>

--- a/Vite-Vercel開発.xlsx
+++ b/Vite-Vercel開発.xlsx
@@ -3,21 +3,21 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28623"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF9979DC-8DF2-4118-B63C-DBB366F14468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A9F41F6-935D-4FF3-A788-9D15C76D8A7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-135" yWindow="-135" windowWidth="29070" windowHeight="15750" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="よく使うこまんど" sheetId="1" r:id="rId1"/>
-    <sheet name="ToDo" sheetId="2" r:id="rId2"/>
-    <sheet name="開発ToDo" sheetId="7" r:id="rId3"/>
-    <sheet name="プロンプト" sheetId="5" r:id="rId4"/>
-    <sheet name="VSCodeExtension" sheetId="6" r:id="rId5"/>
-    <sheet name="開発環境" sheetId="3" r:id="rId6"/>
-    <sheet name="コンポーネント分割案" sheetId="4" r:id="rId7"/>
+    <sheet name="vercel log" sheetId="8" r:id="rId2"/>
+    <sheet name="ToDo" sheetId="2" r:id="rId3"/>
+    <sheet name="開発ToDo" sheetId="7" r:id="rId4"/>
+    <sheet name="プロンプト" sheetId="5" r:id="rId5"/>
+    <sheet name="VSCodeExtension" sheetId="6" r:id="rId6"/>
+    <sheet name="開発環境" sheetId="3" r:id="rId7"/>
+    <sheet name="コンポーネント分割案" sheetId="4" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="181">
   <si>
     <t>npm install -g vercel</t>
     <phoneticPr fontId="1"/>
@@ -1529,6 +1529,40 @@
   </si>
   <si>
     <t>src\server\routes\notificationRoutes.ts</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最後に、WebSocketを使ったリアルタイム通知のための処理を実装します。これにより、ユーザーがオンライン中に即時通知を受け取ることができます。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>src\services\webSocketService.ts</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最後に、サーバーのmain.jsファイルを更新して、通知ルートとWebSocketサービスを統合します：</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>src\server\server.ts</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>npm install -g @anthropic-ai/claude-code</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>vite v6.2.2 building for production…</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>viteの最新バージョン確認</t>
+    <rPh sb="5" eb="7">
+      <t>サイシン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>カクニン</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1953,7 +1987,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="D4:D19"/>
+  <dimension ref="D4:D20"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="4" max="4" width="61.125" bestFit="1" customWidth="1"/>
@@ -2039,6 +2073,11 @@
         <v>146</v>
       </c>
     </row>
+    <row r="20" spans="4:4">
+      <c r="D20" t="s">
+        <v>178</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2047,6 +2086,32 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17156405-9D17-4273-BBE4-E9A6DC809FCB}">
+  <dimension ref="C3:E3"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="3" max="3" width="31.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="3:5">
+      <c r="C3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D3" t="s">
+        <v>180</v>
+      </c>
+      <c r="E3">
+        <v>6.25</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29E011BA-FF28-4838-A033-18A49EB7C30B}">
   <dimension ref="B4:F33"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -2091,7 +2156,7 @@
     </row>
     <row r="6" spans="2:6">
       <c r="B6">
-        <f t="shared" ref="B6:B9" si="0">B5+1</f>
+        <f>B5+1</f>
         <v>3</v>
       </c>
       <c r="C6" t="s">
@@ -2109,7 +2174,7 @@
     </row>
     <row r="7" spans="2:6" ht="40.5">
       <c r="B7">
-        <f t="shared" si="0"/>
+        <f>B6+1</f>
         <v>4</v>
       </c>
       <c r="C7" t="s">
@@ -2127,7 +2192,7 @@
     </row>
     <row r="8" spans="2:6" ht="27">
       <c r="B8">
-        <f t="shared" si="0"/>
+        <f>B7+1</f>
         <v>5</v>
       </c>
       <c r="C8" s="3" t="s">
@@ -2145,7 +2210,7 @@
     </row>
     <row r="9" spans="2:6" ht="54">
       <c r="B9">
-        <f t="shared" si="0"/>
+        <f>B8+1</f>
         <v>6</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -2160,7 +2225,7 @@
     </row>
     <row r="10" spans="2:6" ht="27">
       <c r="B10">
-        <f t="shared" ref="B10:B33" si="1">B9+1</f>
+        <f t="shared" ref="B10:B33" si="0">B9+1</f>
         <v>7</v>
       </c>
       <c r="C10" t="s">
@@ -2178,7 +2243,7 @@
     </row>
     <row r="11" spans="2:6">
       <c r="B11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="C11" t="s">
@@ -2193,7 +2258,7 @@
     </row>
     <row r="12" spans="2:6">
       <c r="B12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="C12" t="s">
@@ -2208,7 +2273,7 @@
     </row>
     <row r="13" spans="2:6">
       <c r="B13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="C13" t="s">
@@ -2223,7 +2288,7 @@
     </row>
     <row r="14" spans="2:6">
       <c r="B14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="C14" t="s">
@@ -2238,7 +2303,7 @@
     </row>
     <row r="15" spans="2:6">
       <c r="B15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="C15" t="s">
@@ -2253,7 +2318,7 @@
     </row>
     <row r="16" spans="2:6">
       <c r="B16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="C16" t="s">
@@ -2268,7 +2333,7 @@
     </row>
     <row r="17" spans="2:6">
       <c r="B17">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="C17" t="s">
@@ -2283,7 +2348,7 @@
     </row>
     <row r="18" spans="2:6">
       <c r="B18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="C18" t="s">
@@ -2298,7 +2363,7 @@
     </row>
     <row r="19" spans="2:6">
       <c r="B19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="C19" t="s">
@@ -2313,7 +2378,7 @@
     </row>
     <row r="20" spans="2:6">
       <c r="B20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="C20" t="s">
@@ -2328,7 +2393,7 @@
     </row>
     <row r="21" spans="2:6">
       <c r="B21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="C21" t="s">
@@ -2343,7 +2408,7 @@
     </row>
     <row r="22" spans="2:6">
       <c r="B22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="C22" t="s">
@@ -2358,7 +2423,7 @@
     </row>
     <row r="23" spans="2:6">
       <c r="B23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="C23" t="s">
@@ -2373,7 +2438,7 @@
     </row>
     <row r="24" spans="2:6">
       <c r="B24">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="C24" t="s">
@@ -2388,7 +2453,7 @@
     </row>
     <row r="25" spans="2:6">
       <c r="B25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="C25" t="s">
@@ -2403,7 +2468,7 @@
     </row>
     <row r="26" spans="2:6">
       <c r="B26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="C26" t="s">
@@ -2418,7 +2483,7 @@
     </row>
     <row r="27" spans="2:6">
       <c r="B27">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="C27" t="s">
@@ -2433,7 +2498,7 @@
     </row>
     <row r="28" spans="2:6" ht="27">
       <c r="B28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="C28" s="3" t="s">
@@ -2448,7 +2513,7 @@
     </row>
     <row r="29" spans="2:6">
       <c r="B29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="C29" t="s">
@@ -2463,7 +2528,7 @@
     </row>
     <row r="30" spans="2:6">
       <c r="B30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="C30" t="s">
@@ -2478,7 +2543,7 @@
     </row>
     <row r="31" spans="2:6">
       <c r="B31">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="C31" t="s">
@@ -2493,7 +2558,7 @@
     </row>
     <row r="32" spans="2:6" ht="27">
       <c r="B32">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="C32" s="3" t="s">
@@ -2502,7 +2567,7 @@
     </row>
     <row r="33" spans="2:3">
       <c r="B33">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="C33" t="s">
@@ -2518,9 +2583,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42DE40CD-4CA6-4FF4-B0DA-D079807C6662}">
-  <dimension ref="B3:G13"/>
+  <dimension ref="B3:G15"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
@@ -2660,13 +2725,35 @@
         <v>172</v>
       </c>
     </row>
+    <row r="14" spans="2:7" ht="54">
+      <c r="D14" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="E14" t="s">
+        <v>175</v>
+      </c>
+      <c r="F14" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" ht="40.5">
+      <c r="D15" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="E15" t="s">
+        <v>177</v>
+      </c>
+      <c r="F15" t="s">
+        <v>177</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6313D91D-4E4E-4302-B673-A8C3F21575BA}">
   <dimension ref="B3:C25"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -2805,7 +2892,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F88E2D65-ECA4-4EF7-BEC6-93BAB5468A01}">
   <dimension ref="B3:C83"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -3138,7 +3225,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C954C604-59FA-4E71-B562-0C51EBE0CA48}">
   <dimension ref="C3:D5"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -3181,7 +3268,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57B697DF-EBFB-495C-BA65-6BC1E0B5AF25}">
   <dimension ref="B3:B52"/>
   <sheetFormatPr defaultRowHeight="13.5"/>

--- a/Vite-Vercel開発.xlsx
+++ b/Vite-Vercel開発.xlsx
@@ -1,23 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28730"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A9F41F6-935D-4FF3-A788-9D15C76D8A7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{486C1422-B8DF-4C99-A331-9786E1E861CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-135" yWindow="-135" windowWidth="29070" windowHeight="15750" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="よく使うこまんど" sheetId="1" r:id="rId1"/>
-    <sheet name="vercel log" sheetId="8" r:id="rId2"/>
-    <sheet name="ToDo" sheetId="2" r:id="rId3"/>
-    <sheet name="開発ToDo" sheetId="7" r:id="rId4"/>
-    <sheet name="プロンプト" sheetId="5" r:id="rId5"/>
-    <sheet name="VSCodeExtension" sheetId="6" r:id="rId6"/>
-    <sheet name="開発環境" sheetId="3" r:id="rId7"/>
-    <sheet name="コンポーネント分割案" sheetId="4" r:id="rId8"/>
+    <sheet name="AI連携" sheetId="9" r:id="rId2"/>
+    <sheet name="vercel log" sheetId="8" r:id="rId3"/>
+    <sheet name="ToDo" sheetId="2" r:id="rId4"/>
+    <sheet name="開発ToDo" sheetId="7" r:id="rId5"/>
+    <sheet name="プロンプト" sheetId="5" r:id="rId6"/>
+    <sheet name="VSCodeExtension" sheetId="6" r:id="rId7"/>
+    <sheet name="開発環境" sheetId="3" r:id="rId8"/>
+    <sheet name="コンポーネント分割案" sheetId="4" r:id="rId9"/>
+    <sheet name="コンポーネント分割" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -35,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="255">
   <si>
     <t>npm install -g vercel</t>
     <phoneticPr fontId="1"/>
@@ -1565,12 +1568,455 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>pnpm update</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>pnpm update --latest
+# 依存関係のみ更新
+pnpm update --latest --prod
+# 開発依存関係のみ更新
+pnpm update --latest --dev</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>pnpm self-update</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Geminiとの連携は、あなたのTodoアプリケーションに確かに追加できます。Reactコンポーネントを見ると、現在は基本的なTodo管理機能が実装されていますが、Gemini APIを統合することで、タスク管理をより強力にできるでしょう。</t>
+  </si>
+  <si>
+    <t>Gemini APIを使って次のような機能を追加できます：</t>
+  </si>
+  <si>
+    <t>1. タスクの自動分類（インプット/アウトプット）</t>
+  </si>
+  <si>
+    <t>2. タスクの優先順位付けの提案</t>
+  </si>
+  <si>
+    <t>3. 関連タスクの提案</t>
+  </si>
+  <si>
+    <t>4. タスク完了に向けたステップの生成</t>
+  </si>
+  <si>
+    <t>5. 日々の振り返りと進捗分析</t>
+  </si>
+  <si>
+    <t>これらの機能を実装するには、Google AIのGemini APIとの連携が必要になります。実装のために何か特定の機能に興味がありますか？それとも基本的な統合方法についての説明が必要でしょうか？</t>
+  </si>
+  <si>
+    <t>src/services/GeminiService.ts</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>src/components/DailyTodoReminderWithGemini.tsx</t>
+  </si>
+  <si>
+    <t># .env.local</t>
+  </si>
+  <si>
+    <t>Gemini APIを使った自動タスク分類機能を実装しました。この実装では以下の機能が追加されています：</t>
+  </si>
+  <si>
+    <r>
+      <t>1. Gemini APIサービス</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <t>タスクの文章を分析して「インプット」か「アウトプット」かを自動判定</t>
+  </si>
+  <si>
+    <t>確信度と判断理由も返却</t>
+  </si>
+  <si>
+    <r>
+      <t>2. ユーザーインターフェースの拡張</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <t>タスク入力中にリアルタイムで分析（デバウンス処理付き）</t>
+  </si>
+  <si>
+    <t>AI提案バッジで分類結果を表示</t>
+  </si>
+  <si>
+    <t>入力中の「分析中...」インジケーター</t>
+  </si>
+  <si>
+    <r>
+      <t>3. UXの改善</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <t>確信度が高い場合のみ提案を表示</t>
+  </si>
+  <si>
+    <t>分類結果を確認ダイアログにも表示</t>
+  </si>
+  <si>
+    <t>ユーザーは常に手動で変更可能</t>
+  </si>
+  <si>
+    <t>使用方法</t>
+  </si>
+  <si>
+    <r>
+      <t>2. GeminiService.ts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>をプロジェクトの</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>src/services/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ディレクトリに配置します。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>3. 既存の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>DailyTodoReminder</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>コンポーネントを</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>DailyTodoReminderWithGemini</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>に置き換えるか、参考にして機能を統合します。</t>
+    </r>
+  </si>
+  <si>
+    <t>4. 必要なパッケージをインストールします：</t>
+  </si>
+  <si>
+    <t>bash</t>
+  </si>
+  <si>
+    <r>
+      <t>npm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4078F2"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>install</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF383A42"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> axios</t>
+    </r>
+  </si>
+  <si>
+    <t>動作の流れ</t>
+  </si>
+  <si>
+    <t>1. ユーザーがタスクを入力し始めると、テキストが3文字以上になった時点で自動分析が始まります。</t>
+  </si>
+  <si>
+    <t>2. 分析中は小さなローディングインジケーターが表示されます。</t>
+  </si>
+  <si>
+    <t>3. Gemini APIがタスクを分析し、結果が返ってくると：</t>
+  </si>
+  <si>
+    <t>自動的にタスクタイプが設定されます</t>
+  </si>
+  <si>
+    <t>確信度が高い場合は提案バッジが表示されます</t>
+  </si>
+  <si>
+    <t>4. ユーザーはいつでも手動でタイプを変更できます。</t>
+  </si>
+  <si>
+    <t>5. タスク追加確認ダイアログにもAI分析結果が表示されます。</t>
+  </si>
+  <si>
+    <t>この実装によって、ユーザーはタスクのタイプを考える手間が省け、より正確な分類ができるようになります。また、AIからのフィードバックにより、ユーザー自身もタスクの性質をより深く理解できるようになります。</t>
+  </si>
+  <si>
+    <t>追加のGemini連携機能（タスクの優先順位付け提案、関連タスクの提案など）も同様の方法で実装できます。さらに機能を追加したい場合は、お知らせください。</t>
+  </si>
+  <si>
+    <r>
+      <t>1. まず、Google AI StudioでGemini APIキーを取得し、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>.env.local</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ファイルに設定します。</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Google AI StudioでGemini APIキーを取得する方法</t>
+  </si>
+  <si>
+    <t>Google AI StudioでGemini APIキーを取得するには、以下の手順に従ってください：</t>
+  </si>
+  <si>
+    <t>1. Google AI Studioにアクセス</t>
+  </si>
+  <si>
+    <t>Google AI Studioにアクセスします。</t>
+  </si>
+  <si>
+    <t>Googleアカウントでログインします。初めての場合は利用規約に同意する必要があります。</t>
+  </si>
+  <si>
+    <t>2. APIキーのセクションに移動</t>
+  </si>
+  <si>
+    <t>ログイン後、左側のナビゲーションメニューから「API Keys」または「APIキー」のセクションを選択します。</t>
+  </si>
+  <si>
+    <t>または直接 https://makersuite.google.com/app/apikey にアクセスします。</t>
+  </si>
+  <si>
+    <t>3. 新しいAPIキーを作成</t>
+  </si>
+  <si>
+    <t>「Create API key」または「APIキーを作成」ボタンをクリックします。</t>
+  </si>
+  <si>
+    <t>キーの名前を入力するか、デフォルトの名前をそのまま使用します。</t>
+  </si>
+  <si>
+    <t>「Create」または「作成」をクリックして、キーを生成します。</t>
+  </si>
+  <si>
+    <t>4. APIキーをコピー</t>
+  </si>
+  <si>
+    <t>生成されたAPIキーが表示されます。</t>
+  </si>
+  <si>
+    <t>「Copy」または「コピー」ボタンをクリックして、キーをクリップボードにコピーします。</t>
+  </si>
+  <si>
+    <t>このキーは再表示されないので、安全な場所に保存してください。</t>
+  </si>
+  <si>
+    <t>5. プロジェクトに設定</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">コピーしたAPIキーを </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>.env.local</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ファイルの </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NEXT_PUBLIC_GEMINI_API_KEY=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> の後に貼り付けます。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">例: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NEXT_PUBLIC_GEMINI_API_KEY=AIzaSyA1B2C3D4E5F6G7H8I9J0K1L2M3N4O5P6</t>
+    </r>
+  </si>
+  <si>
+    <t>6. GeminiService.tsを更新</t>
+  </si>
+  <si>
+    <t>GeminiService.tsファイル内の以下の部分を環境変数を使うように更新します：</t>
+  </si>
+  <si>
+    <t>const API_KEY = process.env.NEXT_PUBLIC_GEMINI_API_KEY;</t>
+  </si>
+  <si>
+    <t>注意点：</t>
+  </si>
+  <si>
+    <t>APIキーは秘密情報です。コードリポジトリにコミットしないでください。</t>
+  </si>
+  <si>
+    <t>無料利用枠があり、月間のリクエスト制限があります。</t>
+  </si>
+  <si>
+    <t>ブラウザのフロントエンドで直接APIキーを使用すると公開されてしまうリスクがあります。本番環境では、バックエンドAPIを通してGemini APIを呼び出す方が安全です。</t>
+  </si>
+  <si>
+    <t>Google AI StudioのUIは変更される場合がありますので、最新の情報はGoogle公式ドキュメントを参照してください。</t>
+  </si>
+  <si>
+    <t>このコンポーネントの改善をしてください。一つか二つのファイルのコピペだけでできる簡単な改善にとどめてください。日本語でお願いします。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>200行以上のコンポーネントは一部をサブコンポーネントとして切り出したいです。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>src\components\HabitTracker.tsx</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>このコンポーネントを改善してください。未実装の部分やモックデータを使用している部分を一つづつでいいので本番用に実装してください。将来的にはこのサイトを世界最高のサイトに改善し、有料でサブスクしたユーザーだけが使用できるサービスとしてリリースしたいです。1ファイルのサイズは200行以内として、超える場合は一部をサブコンポーネントとして切り出したいです。日本語でお願いします。</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1635,6 +2081,40 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FFA0A1A7"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF383A42"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF383A42"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF4078F2"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1657,7 +2137,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
@@ -1682,6 +2162,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
@@ -1698,6 +2192,65 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/activeX/activeX1.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>1</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>41</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>1</xdr:col>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>42</xdr:row>
+          <xdr:rowOff>76200</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="9217" name="Control 1" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s9217"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5BCD94BB-4911-25EC-D070-188CF39A2367}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1987,10 +2540,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="D4:D20"/>
+  <dimension ref="D4:E22"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="4" max="4" width="61.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="4" spans="4:4">
@@ -2058,24 +2612,37 @@
         <v>142</v>
       </c>
     </row>
-    <row r="17" spans="4:4">
+    <row r="17" spans="4:5">
       <c r="D17" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="18" spans="4:4">
+    <row r="18" spans="4:5">
       <c r="D18" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="19" spans="4:4">
+    <row r="19" spans="4:5">
       <c r="D19" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="20" spans="4:4">
+    <row r="20" spans="4:5">
       <c r="D20" t="s">
         <v>178</v>
+      </c>
+    </row>
+    <row r="21" spans="4:5" ht="94.5">
+      <c r="D21" t="s">
+        <v>181</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="22" spans="4:5">
+      <c r="D22" t="s">
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -2085,7 +2652,491 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C6614D2-9BE2-4DBF-BE3B-CC381AB3F591}">
+  <dimension ref="B4:D4"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="2:4">
+      <c r="B4" s="1">
+        <v>45776</v>
+      </c>
+      <c r="C4" t="s">
+        <v>253</v>
+      </c>
+      <c r="D4">
+        <v>261</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E418F96-9DED-4C44-AAF0-D4A9C9E57DCB}">
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="B3:B109"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetData>
+    <row r="3" spans="2:2">
+      <c r="B3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2">
+      <c r="B5" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2">
+      <c r="B6" s="7"/>
+    </row>
+    <row r="7" spans="2:2">
+      <c r="B7" s="7" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2">
+      <c r="B8" s="7" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2">
+      <c r="B9" s="7" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2">
+      <c r="B10" s="7" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2">
+      <c r="B11" s="7" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2">
+      <c r="B13" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="15" spans="2:2">
+      <c r="B15" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" ht="15">
+      <c r="B17" s="10" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" ht="15">
+      <c r="B19" s="11" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2">
+      <c r="B21" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2">
+      <c r="B22" s="7"/>
+    </row>
+    <row r="23" spans="2:2">
+      <c r="B23" s="8" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2">
+      <c r="B24" s="9" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2">
+      <c r="B25" s="9" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2">
+      <c r="B26" s="8" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2">
+      <c r="B27" s="9" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2">
+      <c r="B28" s="9" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2">
+      <c r="B29" s="9" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2">
+      <c r="B30" s="8" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2">
+      <c r="B31" s="9" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2">
+      <c r="B32" s="9" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2">
+      <c r="B33" s="9" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" ht="16.5">
+      <c r="B35" s="5" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2">
+      <c r="B36" s="7"/>
+    </row>
+    <row r="37" spans="2:2">
+      <c r="B37" s="7" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2">
+      <c r="B38" s="12" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2">
+      <c r="B39" s="7" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2">
+      <c r="B40" s="7" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="41" spans="2:2">
+      <c r="B41" s="6"/>
+    </row>
+    <row r="42" spans="2:2">
+      <c r="B42" s="6"/>
+    </row>
+    <row r="43" spans="2:2">
+      <c r="B43" s="6" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="44" spans="2:2">
+      <c r="B44" s="13" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="46" spans="2:2" ht="16.5">
+      <c r="B46" s="5" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2">
+      <c r="B47" s="7"/>
+    </row>
+    <row r="48" spans="2:2">
+      <c r="B48" s="7" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2">
+      <c r="B49" s="7" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2">
+      <c r="B50" s="7" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2">
+      <c r="B51" s="9" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2">
+      <c r="B52" s="9" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="53" spans="2:2">
+      <c r="B53" s="7" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="54" spans="2:2">
+      <c r="B54" s="7" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="56" spans="2:2">
+      <c r="B56" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="58" spans="2:2">
+      <c r="B58" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="60" spans="2:2" ht="28.5">
+      <c r="B60" s="14" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="62" spans="2:2">
+      <c r="B62" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="63" spans="2:2">
+      <c r="B63" s="7"/>
+    </row>
+    <row r="64" spans="2:2">
+      <c r="B64" s="8" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="65" spans="2:2">
+      <c r="B65" s="7"/>
+    </row>
+    <row r="66" spans="2:2">
+      <c r="B66" s="7"/>
+    </row>
+    <row r="67" spans="2:2">
+      <c r="B67" s="15" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="68" spans="2:2">
+      <c r="B68" s="9" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="69" spans="2:2">
+      <c r="B69" s="7"/>
+    </row>
+    <row r="70" spans="2:2">
+      <c r="B70" s="8" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="71" spans="2:2">
+      <c r="B71" s="7"/>
+    </row>
+    <row r="72" spans="2:2">
+      <c r="B72" s="7"/>
+    </row>
+    <row r="73" spans="2:2">
+      <c r="B73" s="9" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="74" spans="2:2">
+      <c r="B74" s="9" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="75" spans="2:2">
+      <c r="B75" s="7"/>
+    </row>
+    <row r="76" spans="2:2">
+      <c r="B76" s="8" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="77" spans="2:2">
+      <c r="B77" s="7"/>
+    </row>
+    <row r="78" spans="2:2">
+      <c r="B78" s="7"/>
+    </row>
+    <row r="79" spans="2:2">
+      <c r="B79" s="9" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="80" spans="2:2">
+      <c r="B80" s="9" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="81" spans="2:2">
+      <c r="B81" s="9" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="82" spans="2:2">
+      <c r="B82" s="7"/>
+    </row>
+    <row r="83" spans="2:2">
+      <c r="B83" s="8" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="84" spans="2:2">
+      <c r="B84" s="7"/>
+    </row>
+    <row r="85" spans="2:2">
+      <c r="B85" s="7"/>
+    </row>
+    <row r="86" spans="2:2">
+      <c r="B86" s="9" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="87" spans="2:2">
+      <c r="B87" s="9" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="88" spans="2:2">
+      <c r="B88" s="9" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="89" spans="2:2">
+      <c r="B89" s="7"/>
+    </row>
+    <row r="90" spans="2:2">
+      <c r="B90" s="8" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="91" spans="2:2">
+      <c r="B91" s="7"/>
+    </row>
+    <row r="92" spans="2:2">
+      <c r="B92" s="7"/>
+    </row>
+    <row r="93" spans="2:2">
+      <c r="B93" s="9" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="94" spans="2:2">
+      <c r="B94" s="9" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="95" spans="2:2">
+      <c r="B95" s="7"/>
+    </row>
+    <row r="96" spans="2:2">
+      <c r="B96" s="8" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="97" spans="2:2">
+      <c r="B97" s="7"/>
+    </row>
+    <row r="98" spans="2:2">
+      <c r="B98" s="7"/>
+    </row>
+    <row r="99" spans="2:2">
+      <c r="B99" s="9" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="100" spans="2:2">
+      <c r="B100" s="7"/>
+    </row>
+    <row r="101" spans="2:2">
+      <c r="B101" s="12" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="103" spans="2:2">
+      <c r="B103" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="104" spans="2:2">
+      <c r="B104" s="7"/>
+    </row>
+    <row r="105" spans="2:2">
+      <c r="B105" s="7" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="106" spans="2:2">
+      <c r="B106" s="7" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="107" spans="2:2">
+      <c r="B107" s="7" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="109" spans="2:2">
+      <c r="B109" t="s">
+        <v>250</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="B67" r:id="rId1" display="https://makersuite.google.com/app/apikey" xr:uid="{771DD001-7E09-4F62-86F2-758C98D1481F}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+  <controls>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="9217" r:id="rId4" name="Control 1">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>41</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>42</xdr:row>
+                <xdr:rowOff>76200</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="9217" r:id="rId4" name="Control 1"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+  </controls>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17156405-9D17-4273-BBE4-E9A6DC809FCB}">
   <dimension ref="C3:E3"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -2111,7 +3162,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29E011BA-FF28-4838-A033-18A49EB7C30B}">
   <dimension ref="B4:F33"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -2583,7 +3634,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42DE40CD-4CA6-4FF4-B0DA-D079807C6662}">
   <dimension ref="B3:G15"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -2753,9 +3804,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6313D91D-4E4E-4302-B673-A8C3F21575BA}">
-  <dimension ref="B3:C25"/>
+  <dimension ref="B3:C27"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
@@ -2881,9 +3932,25 @@
         <v>92</v>
       </c>
     </row>
-    <row r="25" spans="2:3">
+    <row r="25" spans="2:3" ht="27">
       <c r="B25" s="1">
         <v>45742</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3">
+      <c r="B26" s="1">
+        <v>45776</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" ht="54">
+      <c r="C27" s="3" t="s">
+        <v>254</v>
       </c>
     </row>
   </sheetData>
@@ -2892,7 +3959,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F88E2D65-ECA4-4EF7-BEC6-93BAB5468A01}">
   <dimension ref="B3:C83"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -3225,7 +4292,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C954C604-59FA-4E71-B562-0C51EBE0CA48}">
   <dimension ref="C3:D5"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -3268,7 +4335,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57B697DF-EBFB-495C-BA65-6BC1E0B5AF25}">
   <dimension ref="B3:B52"/>
   <sheetFormatPr defaultRowHeight="13.5"/>

--- a/Vite-Vercel開発.xlsx
+++ b/Vite-Vercel開発.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kanta\GitHub\work-time-tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{9F4DB3CD-EADF-457A-A9FE-46C52A6BD6FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DEDBB40F-9D1E-4009-BC80-61C5DFD6FD50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-135" yWindow="-135" windowWidth="29070" windowHeight="15750" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="よく使うこまんど" sheetId="1" r:id="rId1"/>
@@ -22,10 +22,11 @@
     <sheet name="ChatGPT活動記録" sheetId="13" r:id="rId7"/>
     <sheet name="活動記録" sheetId="12" r:id="rId8"/>
     <sheet name="ADHD" sheetId="14" r:id="rId9"/>
-    <sheet name="VSCodeExtension" sheetId="6" r:id="rId10"/>
-    <sheet name="開発環境" sheetId="3" r:id="rId11"/>
-    <sheet name="コンポーネント分割案" sheetId="4" r:id="rId12"/>
-    <sheet name="コンポーネント分割" sheetId="10" r:id="rId13"/>
+    <sheet name="Sheet6" sheetId="15" r:id="rId10"/>
+    <sheet name="VSCodeExtension" sheetId="6" r:id="rId11"/>
+    <sheet name="開発環境" sheetId="3" r:id="rId12"/>
+    <sheet name="コンポーネント分割案" sheetId="4" r:id="rId13"/>
+    <sheet name="コンポーネント分割" sheetId="10" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <fileRecoveryPr repairLoad="1"/>
@@ -46,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1270" uniqueCount="676">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1273" uniqueCount="679">
   <si>
     <t>npm install -g vercel</t>
     <phoneticPr fontId="1"/>
@@ -2089,21 +2090,6 @@
 9. **Discord** - ゲーマーから始まり、現在では様々な興味を持つコミュニティのためのコミュニケーションプラットフォームとして発展しています。
 10. **LINE（Z Holdings）** - 日本や東南アジアを中心に強いプレゼンスを持ち、メッセージングを起点に様々なサービスを展開しています。
 これらの企業は、ユーザー数、市場価値、サービスの革新性、社会的影響力などを総合的に考慮したランキングです。SNS市場は常に変化しており、新しいプラットフォームの台頭や既存プラットフォームの進化により、このランキングも今後変動する可能性があります。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>モバイル関連サービスに特化した企業に絞ると、世界トップクラスのランキングは以下のようになります：
-1. **Apple** - iPhoneとiOSエコシステムを通じて、ハードウェアとソフトウェアを緊密に統合した高品質なモバイル体験を提供し、App Storeを通じて巨大なアプリエコノミーを創出しています。
-2. **Google (Alphabet)** - Androidオペレーティングシステムを開発・提供し、世界のスマートフォン市場の約70%を占めるとともに、Google PlayやGoogleマップなどの主要モバイルサービスを提供しています。
-3. **Samsung** - 世界最大のスマートフォンメーカーとして多様な価格帯の端末を提供し、独自のモバイルサービスエコシステムも構築しています。
-4. **Tencent** - WeChat（微信）を中心に、モバイル決済、ゲーム、エンターテイメントなど包括的なモバイルサービスを提供し、特に中国市場で強力なプレゼンスを持っています。
-5. **Uber** - モビリティサービスの先駆者として、配車からフードデリバリーまで、モバイルを活用した生活インフラサービスを世界中で展開しています。
-6. **Spotify** - モバイル音楽ストリーミングの最大手として、パーソナライズされた音楽体験とポッドキャストサービスを提供しています。
-7. **Snap Inc.** - Snapchatを通じて、特に若年層向けにモバイルファーストのソーシャルメディア体験とAR技術を提供しています。
-8. **LINE (Z Holdings)** - 日本およびアジア地域で強いプレゼンスを持ち、メッセージングを中心に、ゲーム、決済、配信など総合的なモバイルサービスを提供しています。
-9. **Grab** - 東南アジアを中心に、配車、フードデリバリー、決済など日常生活の多くの側面をカバーするスーパーアプリとして成長しています。
-10. **Airbnb** - 宿泊施設の検索・予約をモバイルで簡単に行えるようにし、旅行体験を変革したサービスを提供しています。
-これらの企業は、モバイルサービスの革新性、ユーザー数、市場価値、業界への影響力などを総合的に考慮したランキングです。モバイル市場は技術の進化とともに常に変化しており、このランキングも今後変動する可能性があります。</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -2211,56 +2197,6 @@
     <rPh sb="273" eb="275">
       <t>ケントウ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>このコンポーネントを改善してください。未実装の部分やモックデータを使用している部分を一つづつでいいので本番用に実装してください。将来的にはこのサイトを世界最高のサイトに改善し、有料でサブスクしたユーザーだけが使用できるサービスとしてリリースしたいです。1ファイルのサイズは200行以内として、超える場合は一部をサブコンポーネントとして切り出したいです。またESLintのエラーや警告が絶対にでないように複数回の検証を繰り返してからコードを提供してください。命名規則や型定義にも一貫性をもたせてください。日本語でお願いします。下記に列挙する企業のサービスを上回るという観点で検討してください。
-Microsoft
-Apple
-Amazon
-Google (Alphabet)
-Salesforce
-NVIDIA
-Adobe
-ServiceNow
-Oracle
-SAP
-Zoom
-Atlassian
-HubSpot
-Workday
-Shopify
-Slack
-OpenAI
-Anthropic
-Stability AI
-Midjourney
-Cohere
-Hugging Face
-Inflection AI
-Runway
-Meta (旧Facebook)
-ByteDance
-X (旧Twitter)
-Tencent
-LinkedIn
-Snapchat (Snap Inc.)
-Pinterest
-Reddit
-Discord
-LINE (Z Holdings)
-Samsung
-Uber
-Spotify
-Grab
-Airbnb
-Match Group
-Bumble
-Indeed (Recruit Holdings)
-TaskRabbit
-Fiverr
-Upwork
-Meetup</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -3767,12 +3703,140 @@
   <si>
     <t>就寝</t>
   </si>
+  <si>
+    <t>ADHDは怠け者の言い訳だもっと努力 すればできる誰もが無意識に同じ人間同じ</t>
+  </si>
+  <si>
+    <t>ようなことができるはずという思い込みが あります大間違いですadhDの脳は普通</t>
+  </si>
+  <si>
+    <t>の人の脳が一般常用者としたらレーシング カー街中の道路を時速60kmで走るよう</t>
+  </si>
+  <si>
+    <t>メモ管理は Obsidian in  Cursor が最強。
+Obsidianはmd ファイルとして一つ一つが独立して存在している。これらをcursor agent に読み込ませることでmcp みたいな運用ができる。具体的な運用方法は以下リプに載せる。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>このコンポーネントを改善してください。未実装の部分やモックデータを使用している部分を一つづつでいいので本番用に実装してください。将来的にはこのサイトを世界最高のサイトに改善し、有料でサブスクしたユーザーだけが使用できるサービスとしてリリースしたいです。1ファイルのサイズは200行以内として、超える場合は一部をサブコンポーネントとして切り出したいです。またESLintのエラーや警告が絶対にでないように複数回の検証を繰り返してからコードを提供してください。これまで必ずEsLint指摘がでているのでなんとか改善してください。特に、no-unused-vars、no-explicit-anyのエラーが絶対にでないように複数回の検証を行ってください。命名規則や型定義にも一貫性をもたせてください。ファイルパスやファイル名はコピペできるように出力してください。フォルダー構成についても改善案があれば提示してください。日本語でお願いします。下記に列挙する企業のサービスを上回るという観点で検討してください。
+Microsoft
+Apple
+Amazon
+Google (Alphabet)
+Salesforce
+NVIDIA
+Adobe
+ServiceNow
+Oracle
+SAP
+Zoom
+Atlassian
+HubSpot
+Workday
+Shopify
+Slack
+OpenAI
+Anthropic
+Stability AI
+Midjourney
+Cohere
+Hugging Face
+Inflection AI
+Runway
+Meta (旧Facebook)
+ByteDance
+X (旧Twitter)
+Tencent
+LinkedIn
+Snapchat (Snap Inc.)
+Pinterest
+Reddit
+Discord
+LINE (Z Holdings)
+Samsung
+Uber
+Spotify
+Grab
+Airbnb
+Match Group
+Bumble
+Indeed (Recruit Holdings)
+TaskRabbit
+Fiverr
+Upwork
+Meetup
+回答が長くなりすぎて途中で切れてしまうようであれば、複数回に分割して出力することも検討してください。</t>
+    <rPh sb="232" eb="233">
+      <t>カナラ</t>
+    </rPh>
+    <rPh sb="240" eb="242">
+      <t>シテキ</t>
+    </rPh>
+    <rPh sb="253" eb="255">
+      <t>カイゼン</t>
+    </rPh>
+    <rPh sb="262" eb="263">
+      <t>トク</t>
+    </rPh>
+    <rPh sb="300" eb="302">
+      <t>ゼッタイ</t>
+    </rPh>
+    <rPh sb="309" eb="312">
+      <t>フクスウカイ</t>
+    </rPh>
+    <rPh sb="313" eb="315">
+      <t>ケンショウ</t>
+    </rPh>
+    <rPh sb="316" eb="317">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="358" eb="359">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="369" eb="371">
+      <t>シュツリョク</t>
+    </rPh>
+    <rPh sb="383" eb="385">
+      <t>コウセイ</t>
+    </rPh>
+    <rPh sb="390" eb="393">
+      <t>カイゼンアン</t>
+    </rPh>
+    <rPh sb="397" eb="399">
+      <t>テイジ</t>
+    </rPh>
+    <rPh sb="897" eb="899">
+      <t>カイトウ</t>
+    </rPh>
+    <rPh sb="900" eb="901">
+      <t>ナガ</t>
+    </rPh>
+    <rPh sb="907" eb="909">
+      <t>トチュウ</t>
+    </rPh>
+    <rPh sb="910" eb="911">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="923" eb="926">
+      <t>フクスウカイ</t>
+    </rPh>
+    <rPh sb="927" eb="929">
+      <t>ブンカツ</t>
+    </rPh>
+    <rPh sb="931" eb="933">
+      <t>シュツリョク</t>
+    </rPh>
+    <rPh sb="938" eb="940">
+      <t>ケントウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3883,6 +3947,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF065FD4"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -3920,7 +3990,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
@@ -3960,14 +4030,14 @@
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -3977,6 +4047,9 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3994,14 +4067,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
+          <bgColor theme="6" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4477,6 +4550,25 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{316E5208-1AA2-4457-A1CF-56BEFB0E0D49}">
+  <dimension ref="C3"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="3" max="3" width="65" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="3:3" ht="54">
+      <c r="C3" s="3" t="s">
+        <v>677</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F88E2D65-ECA4-4EF7-BEC6-93BAB5468A01}">
   <dimension ref="B3:C83"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -4810,7 +4902,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C954C604-59FA-4E71-B562-0C51EBE0CA48}">
   <dimension ref="C3:D5"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -4854,7 +4946,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57B697DF-EBFB-495C-BA65-6BC1E0B5AF25}">
   <dimension ref="B3:B52"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -5065,7 +5157,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C6614D2-9BE2-4DBF-BE3B-CC381AB3F591}">
   <dimension ref="B4:D4"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -6379,7 +6471,7 @@
         <v>45776</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="29" spans="2:4" ht="409.5">
@@ -6411,28 +6503,26 @@
         <v>261</v>
       </c>
       <c r="D32" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="33" spans="3:4">
+      <c r="C33" s="3"/>
+      <c r="D33" t="s">
         <v>264</v>
-      </c>
-    </row>
-    <row r="33" spans="3:4" ht="409.5">
-      <c r="C33" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="D33" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="34" spans="3:4" ht="409.5">
       <c r="C34" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="35" spans="3:4" ht="409.5">
       <c r="C35" s="3" t="s">
-        <v>268</v>
+        <v>678</v>
       </c>
     </row>
   </sheetData>
@@ -6455,39 +6545,39 @@
   <sheetData>
     <row r="3" spans="2:5">
       <c r="D3" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E3" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="4" spans="2:5" ht="243">
       <c r="D4" s="3" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="5" spans="2:5" ht="40.5">
       <c r="D5" s="3" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="6" spans="2:5" ht="216">
       <c r="D6" s="3" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="7" spans="2:5">
       <c r="D7" s="3" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="E7" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="8" spans="2:5" ht="409.5">
@@ -6498,10 +6588,10 @@
         <v>0.82777777777777772</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="9" spans="2:5" ht="409.5">
@@ -6512,10 +6602,10 @@
         <v>0.82986111111111116</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
   </sheetData>
@@ -6531,10 +6621,10 @@
   <cols>
     <col min="1" max="3" width="5.875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="30" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="30" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8.25" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.5" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="8.25" bestFit="1" customWidth="1"/>
@@ -6600,208 +6690,208 @@
       MOD(NOW(),1),
       TIME(0,5,0)
     ),"HH:mm")</f>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B2" s="19"/>
       <c r="D2" s="1">
         <f ca="1">TODAY()</f>
-        <v>45780</v>
+        <v>45788</v>
       </c>
     </row>
     <row r="3" spans="1:65">
       <c r="A3" s="19" t="str">
         <f ca="1">TEXT(NOW(),"HH:mm")</f>
-        <v>13:33</v>
+        <v>08:26</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="17" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D3" s="18">
         <v>45778</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="F3" s="18">
         <v>45779</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="H3" s="18">
         <v>45780</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="J3" s="18">
         <v>45781</v>
       </c>
       <c r="K3" s="21" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="L3" s="18">
         <v>45782</v>
       </c>
       <c r="M3" s="21" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N3" s="18">
         <v>45783</v>
       </c>
       <c r="O3" s="21" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="P3" s="18">
         <v>45784</v>
       </c>
       <c r="Q3" s="21" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="R3" s="18">
         <v>45785</v>
       </c>
       <c r="S3" s="21" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="T3" s="18">
         <v>45786</v>
       </c>
       <c r="U3" s="21" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="V3" s="18">
         <v>45787</v>
       </c>
       <c r="W3" s="21" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="X3" s="18">
         <v>45788</v>
       </c>
       <c r="Y3" s="21" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Z3" s="18">
         <v>45789</v>
       </c>
       <c r="AA3" s="21" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="AB3" s="18">
         <v>45790</v>
       </c>
       <c r="AC3" s="21" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="AD3" s="18">
         <v>45791</v>
       </c>
       <c r="AE3" s="21" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="AF3" s="18">
         <v>45792</v>
       </c>
       <c r="AG3" s="21" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="AH3" s="18">
         <v>45793</v>
       </c>
       <c r="AI3" s="21" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="AJ3" s="18">
         <v>45794</v>
       </c>
       <c r="AK3" s="21" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="AL3" s="18">
         <v>45795</v>
       </c>
       <c r="AM3" s="21" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="AN3" s="18">
         <v>45796</v>
       </c>
       <c r="AO3" s="21" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="AP3" s="18">
         <v>45797</v>
       </c>
       <c r="AQ3" s="21" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="AR3" s="18">
         <v>45798</v>
       </c>
       <c r="AS3" s="21" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="AT3" s="18">
         <v>45799</v>
       </c>
       <c r="AU3" s="21" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="AV3" s="18">
         <v>45800</v>
       </c>
       <c r="AW3" s="21" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="AX3" s="18">
         <v>45801</v>
       </c>
       <c r="AY3" s="21" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="AZ3" s="18">
         <v>45802</v>
       </c>
       <c r="BA3" s="21" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="BB3" s="18">
         <v>45803</v>
       </c>
       <c r="BC3" s="21" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="BD3" s="18">
         <v>45804</v>
       </c>
       <c r="BE3" s="21" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="BF3" s="18">
         <v>45805</v>
       </c>
       <c r="BG3" s="21" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="BH3" s="18">
         <v>45806</v>
       </c>
       <c r="BI3" s="21" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="BJ3" s="18">
         <v>45807</v>
       </c>
       <c r="BK3" s="21" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="BL3" s="18">
         <v>45808</v>
       </c>
       <c r="BM3" s="21" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
     <row r="4" spans="1:65">
@@ -6810,21 +6900,21 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B4" t="str">
         <f t="shared" ref="B4:B67" si="1">TEXT($C4, "HH:mm")</f>
         <v>04:00</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E4" s="22"/>
       <c r="F4" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G4" s="22"/>
       <c r="H4" s="22"/>
@@ -6889,21 +6979,21 @@
     <row r="5" spans="1:65">
       <c r="A5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B5" t="str">
         <f t="shared" si="1"/>
         <v>04:05</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E5" s="22"/>
       <c r="F5" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G5" s="22"/>
       <c r="H5" s="22"/>
@@ -6968,21 +7058,21 @@
     <row r="6" spans="1:65">
       <c r="A6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B6" t="str">
         <f t="shared" si="1"/>
         <v>04:10</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E6" s="22"/>
       <c r="F6" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G6" s="22"/>
       <c r="H6" s="22"/>
@@ -7047,21 +7137,21 @@
     <row r="7" spans="1:65">
       <c r="A7" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B7" t="str">
         <f t="shared" si="1"/>
         <v>04:15</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E7" s="22"/>
       <c r="F7" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G7" s="22"/>
       <c r="H7" s="22"/>
@@ -7126,21 +7216,21 @@
     <row r="8" spans="1:65">
       <c r="A8" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B8" t="str">
         <f t="shared" si="1"/>
         <v>04:20</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E8" s="22"/>
       <c r="F8" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G8" s="22"/>
       <c r="H8" s="22"/>
@@ -7205,21 +7295,21 @@
     <row r="9" spans="1:65">
       <c r="A9" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B9" t="str">
         <f t="shared" si="1"/>
         <v>04:25</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E9" s="22"/>
       <c r="F9" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G9" s="22"/>
       <c r="H9" s="22"/>
@@ -7284,21 +7374,21 @@
     <row r="10" spans="1:65">
       <c r="A10" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B10" t="str">
         <f t="shared" si="1"/>
         <v>04:30</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E10" s="22"/>
       <c r="F10" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G10" s="22"/>
       <c r="H10" s="22"/>
@@ -7363,21 +7453,21 @@
     <row r="11" spans="1:65">
       <c r="A11" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B11" t="str">
         <f t="shared" si="1"/>
         <v>04:35</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E11" s="22"/>
       <c r="F11" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G11" s="22"/>
       <c r="H11" s="22"/>
@@ -7442,21 +7532,21 @@
     <row r="12" spans="1:65">
       <c r="A12" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B12" t="str">
         <f t="shared" si="1"/>
         <v>04:40</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E12" s="22"/>
       <c r="F12" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G12" s="22"/>
       <c r="H12" s="22"/>
@@ -7521,21 +7611,21 @@
     <row r="13" spans="1:65">
       <c r="A13" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B13" t="str">
         <f t="shared" si="1"/>
         <v>04:45</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E13" s="22"/>
       <c r="F13" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G13" s="22"/>
       <c r="H13" s="22"/>
@@ -7600,21 +7690,21 @@
     <row r="14" spans="1:65">
       <c r="A14" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B14" t="str">
         <f t="shared" si="1"/>
         <v>04:50</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E14" s="22"/>
       <c r="F14" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G14" s="22"/>
       <c r="H14" s="22"/>
@@ -7679,21 +7769,21 @@
     <row r="15" spans="1:65">
       <c r="A15" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B15" t="str">
         <f t="shared" si="1"/>
         <v>04:55</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E15" s="22"/>
       <c r="F15" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G15" s="22"/>
       <c r="H15" s="22"/>
@@ -7758,21 +7848,21 @@
     <row r="16" spans="1:65">
       <c r="A16" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B16" t="str">
         <f t="shared" si="1"/>
         <v>05:00</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E16" s="22"/>
       <c r="F16" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G16" s="22"/>
       <c r="H16" s="22"/>
@@ -7837,21 +7927,21 @@
     <row r="17" spans="1:65">
       <c r="A17" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B17" t="str">
         <f t="shared" si="1"/>
         <v>05:05</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E17" s="22"/>
       <c r="F17" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G17" s="22"/>
       <c r="H17" s="22"/>
@@ -7916,21 +8006,21 @@
     <row r="18" spans="1:65">
       <c r="A18" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B18" t="str">
         <f t="shared" si="1"/>
         <v>05:10</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E18" s="22"/>
       <c r="F18" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G18" s="22"/>
       <c r="H18" s="22"/>
@@ -7995,21 +8085,21 @@
     <row r="19" spans="1:65">
       <c r="A19" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B19" t="str">
         <f t="shared" si="1"/>
         <v>05:15</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E19" s="22"/>
       <c r="F19" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G19" s="22"/>
       <c r="H19" s="22"/>
@@ -8074,21 +8164,21 @@
     <row r="20" spans="1:65">
       <c r="A20" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B20" t="str">
         <f t="shared" si="1"/>
         <v>05:20</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E20" s="22"/>
       <c r="F20" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G20" s="22"/>
       <c r="H20" s="22"/>
@@ -8153,21 +8243,21 @@
     <row r="21" spans="1:65">
       <c r="A21" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B21" t="str">
         <f t="shared" si="1"/>
         <v>05:25</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E21" s="22"/>
       <c r="F21" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G21" s="22"/>
       <c r="H21" s="22"/>
@@ -8232,21 +8322,21 @@
     <row r="22" spans="1:65">
       <c r="A22" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B22" t="str">
         <f t="shared" si="1"/>
         <v>05:30</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E22" s="22"/>
       <c r="F22" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G22" s="22"/>
       <c r="H22" s="22"/>
@@ -8311,21 +8401,21 @@
     <row r="23" spans="1:65">
       <c r="A23" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B23" t="str">
         <f t="shared" si="1"/>
         <v>05:35</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E23" s="22"/>
       <c r="F23" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G23" s="22"/>
       <c r="H23" s="22"/>
@@ -8390,21 +8480,21 @@
     <row r="24" spans="1:65">
       <c r="A24" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B24" t="str">
         <f t="shared" si="1"/>
         <v>05:40</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E24" s="22"/>
       <c r="F24" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G24" s="22"/>
       <c r="H24" s="22"/>
@@ -8469,21 +8559,21 @@
     <row r="25" spans="1:65">
       <c r="A25" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B25" t="str">
         <f t="shared" si="1"/>
         <v>05:45</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E25" s="22"/>
       <c r="F25" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G25" s="22"/>
       <c r="H25" s="22"/>
@@ -8548,21 +8638,21 @@
     <row r="26" spans="1:65">
       <c r="A26" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B26" t="str">
         <f t="shared" si="1"/>
         <v>05:50</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E26" s="22"/>
       <c r="F26" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G26" s="22"/>
       <c r="H26" s="22"/>
@@ -8627,21 +8717,21 @@
     <row r="27" spans="1:65">
       <c r="A27" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B27" t="str">
         <f t="shared" si="1"/>
         <v>05:55</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E27" s="22"/>
       <c r="F27" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G27" s="22"/>
       <c r="H27" s="22"/>
@@ -8706,25 +8796,25 @@
     <row r="28" spans="1:65">
       <c r="A28" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B28" t="str">
         <f t="shared" si="1"/>
         <v>06:00</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E28" s="22"/>
       <c r="F28" s="22" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="G28" s="22"/>
       <c r="H28" s="22" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="I28" s="22"/>
       <c r="J28" s="22"/>
@@ -8787,25 +8877,25 @@
     <row r="29" spans="1:65">
       <c r="A29" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B29" t="str">
         <f t="shared" si="1"/>
         <v>06:05</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E29" s="22"/>
       <c r="F29" s="22" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="G29" s="22"/>
       <c r="H29" s="22" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="I29" s="22"/>
       <c r="J29" s="22"/>
@@ -8868,25 +8958,25 @@
     <row r="30" spans="1:65">
       <c r="A30" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B30" t="str">
         <f t="shared" si="1"/>
         <v>06:10</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E30" s="22"/>
       <c r="F30" s="22" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="G30" s="22"/>
       <c r="H30" s="22" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="I30" s="22"/>
       <c r="J30" s="22"/>
@@ -8949,21 +9039,21 @@
     <row r="31" spans="1:65">
       <c r="A31" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B31" t="str">
         <f t="shared" si="1"/>
         <v>06:15</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E31" s="22"/>
       <c r="F31" s="22" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="G31" s="22"/>
       <c r="H31" s="22"/>
@@ -9028,21 +9118,21 @@
     <row r="32" spans="1:65">
       <c r="A32" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B32" t="str">
         <f t="shared" si="1"/>
         <v>06:20</v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D32" s="17" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E32" s="22"/>
       <c r="F32" s="22" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="G32" s="22"/>
       <c r="H32" s="22"/>
@@ -9107,21 +9197,21 @@
     <row r="33" spans="1:65">
       <c r="A33" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B33" t="str">
         <f t="shared" si="1"/>
         <v>06:25</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E33" s="22"/>
       <c r="F33" s="22" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="G33" s="22"/>
       <c r="H33" s="22"/>
@@ -9186,25 +9276,25 @@
     <row r="34" spans="1:65">
       <c r="A34" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B34" t="str">
         <f t="shared" si="1"/>
         <v>06:30</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D34" s="17" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E34" s="22"/>
       <c r="F34" s="22" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="G34" s="22"/>
       <c r="H34" s="22" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="I34" s="22"/>
       <c r="J34" s="22"/>
@@ -9267,25 +9357,25 @@
     <row r="35" spans="1:65">
       <c r="A35" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B35" t="str">
         <f t="shared" si="1"/>
         <v>06:35</v>
       </c>
       <c r="C35" s="17" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D35" s="17" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E35" s="22"/>
       <c r="F35" s="22" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="G35" s="22"/>
       <c r="H35" s="22" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="I35" s="22"/>
       <c r="J35" s="22"/>
@@ -9348,25 +9438,25 @@
     <row r="36" spans="1:65">
       <c r="A36" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B36" t="str">
         <f t="shared" si="1"/>
         <v>06:40</v>
       </c>
       <c r="C36" s="17" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D36" s="17" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E36" s="22"/>
       <c r="F36" s="22" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="G36" s="22"/>
       <c r="H36" s="22" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="I36" s="22"/>
       <c r="J36" s="22"/>
@@ -9429,21 +9519,21 @@
     <row r="37" spans="1:65">
       <c r="A37" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B37" t="str">
         <f t="shared" si="1"/>
         <v>06:45</v>
       </c>
       <c r="C37" s="17" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D37" s="17" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E37" s="22"/>
       <c r="F37" s="22" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="G37" s="22"/>
       <c r="H37" s="22"/>
@@ -9508,21 +9598,21 @@
     <row r="38" spans="1:65">
       <c r="A38" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B38" t="str">
         <f t="shared" si="1"/>
         <v>06:50</v>
       </c>
       <c r="C38" s="17" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D38" s="17" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E38" s="22"/>
       <c r="F38" s="22" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="G38" s="22"/>
       <c r="H38" s="22"/>
@@ -9587,21 +9677,21 @@
     <row r="39" spans="1:65">
       <c r="A39" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B39" t="str">
         <f t="shared" si="1"/>
         <v>06:55</v>
       </c>
       <c r="C39" s="17" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D39" s="17" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E39" s="22"/>
       <c r="F39" s="22" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="G39" s="22"/>
       <c r="H39" s="22"/>
@@ -9666,21 +9756,21 @@
     <row r="40" spans="1:65">
       <c r="A40" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B40" t="str">
         <f t="shared" si="1"/>
         <v>07:00</v>
       </c>
       <c r="C40" s="17" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D40" s="17" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="E40" s="22"/>
       <c r="F40" s="22" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="G40" s="22"/>
       <c r="H40" s="22"/>
@@ -9745,21 +9835,21 @@
     <row r="41" spans="1:65">
       <c r="A41" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B41" t="str">
         <f t="shared" si="1"/>
         <v>07:05</v>
       </c>
       <c r="C41" s="17" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D41" s="17" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="E41" s="22"/>
       <c r="F41" s="22" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="G41" s="22"/>
       <c r="H41" s="22"/>
@@ -9824,25 +9914,25 @@
     <row r="42" spans="1:65">
       <c r="A42" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B42" t="str">
         <f t="shared" si="1"/>
         <v>07:10</v>
       </c>
       <c r="C42" s="17" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D42" s="17" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="E42" s="22"/>
       <c r="F42" s="22" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="G42" s="22"/>
       <c r="H42" s="22" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="I42" s="22"/>
       <c r="J42" s="22"/>
@@ -9905,25 +9995,25 @@
     <row r="43" spans="1:65">
       <c r="A43" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B43" t="str">
         <f t="shared" si="1"/>
         <v>07:15</v>
       </c>
       <c r="C43" s="17" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D43" s="17" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="E43" s="22"/>
       <c r="F43" s="22" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="G43" s="22"/>
       <c r="H43" s="22" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="I43" s="22"/>
       <c r="J43" s="22"/>
@@ -9986,21 +10076,21 @@
     <row r="44" spans="1:65">
       <c r="A44" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B44" t="str">
         <f t="shared" si="1"/>
         <v>07:20</v>
       </c>
       <c r="C44" s="17" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D44" s="17" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="E44" s="22"/>
       <c r="F44" s="22" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="G44" s="22"/>
       <c r="H44" s="22"/>
@@ -10065,21 +10155,21 @@
     <row r="45" spans="1:65">
       <c r="A45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B45" t="str">
         <f t="shared" si="1"/>
         <v>07:25</v>
       </c>
       <c r="C45" s="17" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D45" s="17" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="E45" s="22"/>
       <c r="F45" s="22" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="G45" s="22"/>
       <c r="H45" s="22"/>
@@ -10144,21 +10234,21 @@
     <row r="46" spans="1:65">
       <c r="A46" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B46" t="str">
         <f t="shared" si="1"/>
         <v>07:30</v>
       </c>
       <c r="C46" s="17" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D46" s="17" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E46" s="22"/>
       <c r="F46" s="22" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="G46" s="22"/>
       <c r="H46" s="22"/>
@@ -10223,21 +10313,21 @@
     <row r="47" spans="1:65">
       <c r="A47" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B47" t="str">
         <f t="shared" si="1"/>
         <v>07:35</v>
       </c>
       <c r="C47" s="17" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D47" s="17" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E47" s="22"/>
       <c r="F47" s="22" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="G47" s="22"/>
       <c r="H47" s="22"/>
@@ -10302,21 +10392,21 @@
     <row r="48" spans="1:65">
       <c r="A48" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B48" t="str">
         <f t="shared" si="1"/>
         <v>07:40</v>
       </c>
       <c r="C48" s="17" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D48" s="17" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E48" s="22"/>
       <c r="F48" s="22" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="G48" s="22"/>
       <c r="H48" s="22"/>
@@ -10381,25 +10471,25 @@
     <row r="49" spans="1:65">
       <c r="A49" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B49" t="str">
         <f t="shared" si="1"/>
         <v>07:45</v>
       </c>
       <c r="C49" s="17" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D49" s="17" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E49" s="22"/>
       <c r="F49" s="22" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="G49" s="22"/>
       <c r="H49" s="22" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="I49" s="22"/>
       <c r="J49" s="22"/>
@@ -10462,25 +10552,25 @@
     <row r="50" spans="1:65">
       <c r="A50" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B50" t="str">
         <f t="shared" si="1"/>
         <v>07:50</v>
       </c>
       <c r="C50" s="17" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D50" s="17" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E50" s="22"/>
       <c r="F50" s="22" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="G50" s="22"/>
       <c r="H50" s="22" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I50" s="22"/>
       <c r="J50" s="22"/>
@@ -10543,21 +10633,21 @@
     <row r="51" spans="1:65">
       <c r="A51" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B51" t="str">
         <f t="shared" si="1"/>
         <v>07:55</v>
       </c>
       <c r="C51" s="17" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D51" s="17" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E51" s="22"/>
       <c r="F51" s="22" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="G51" s="22"/>
       <c r="H51" s="22"/>
@@ -10622,21 +10712,21 @@
     <row r="52" spans="1:65">
       <c r="A52" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B52" t="str">
         <f t="shared" si="1"/>
         <v>08:00</v>
       </c>
       <c r="C52" s="17" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D52" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E52" s="22"/>
       <c r="F52" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G52" s="22"/>
       <c r="H52" s="22"/>
@@ -10701,21 +10791,21 @@
     <row r="53" spans="1:65">
       <c r="A53" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B53" t="str">
         <f t="shared" si="1"/>
         <v>08:05</v>
       </c>
       <c r="C53" s="17" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D53" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E53" s="22"/>
       <c r="F53" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G53" s="22"/>
       <c r="H53" s="22"/>
@@ -10780,21 +10870,21 @@
     <row r="54" spans="1:65">
       <c r="A54" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B54" t="str">
         <f t="shared" si="1"/>
         <v>08:10</v>
       </c>
       <c r="C54" s="17" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D54" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E54" s="22"/>
       <c r="F54" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G54" s="22"/>
       <c r="H54" s="22"/>
@@ -10859,21 +10949,21 @@
     <row r="55" spans="1:65">
       <c r="A55" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B55" t="str">
         <f t="shared" si="1"/>
         <v>08:15</v>
       </c>
       <c r="C55" s="17" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D55" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E55" s="22"/>
       <c r="F55" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G55" s="22"/>
       <c r="H55" s="22"/>
@@ -10938,25 +11028,25 @@
     <row r="56" spans="1:65">
       <c r="A56" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B56" t="str">
         <f t="shared" si="1"/>
         <v>08:20</v>
       </c>
       <c r="C56" s="17" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D56" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E56" s="22"/>
       <c r="F56" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G56" s="22"/>
       <c r="H56" s="22" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="I56" s="22"/>
       <c r="J56" s="22"/>
@@ -11019,21 +11109,21 @@
     <row r="57" spans="1:65">
       <c r="A57" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B57" t="str">
         <f t="shared" si="1"/>
         <v>08:25</v>
       </c>
       <c r="C57" s="17" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D57" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E57" s="22"/>
       <c r="F57" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G57" s="22"/>
       <c r="H57" s="22"/>
@@ -11098,25 +11188,25 @@
     <row r="58" spans="1:65">
       <c r="A58" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B58" t="str">
         <f t="shared" si="1"/>
         <v>08:30</v>
       </c>
       <c r="C58" s="17" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D58" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E58" s="22"/>
       <c r="F58" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G58" s="22"/>
       <c r="H58" s="22" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="I58" s="22"/>
       <c r="J58" s="22"/>
@@ -11179,21 +11269,21 @@
     <row r="59" spans="1:65">
       <c r="A59" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B59" t="str">
         <f t="shared" si="1"/>
         <v>08:35</v>
       </c>
       <c r="C59" s="17" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D59" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E59" s="22"/>
       <c r="F59" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G59" s="22"/>
       <c r="H59" s="22"/>
@@ -11258,21 +11348,21 @@
     <row r="60" spans="1:65">
       <c r="A60" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B60" t="str">
         <f t="shared" si="1"/>
         <v>08:40</v>
       </c>
       <c r="C60" s="17" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D60" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E60" s="22"/>
       <c r="F60" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G60" s="22"/>
       <c r="H60" s="22"/>
@@ -11337,21 +11427,21 @@
     <row r="61" spans="1:65">
       <c r="A61" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B61" t="str">
         <f t="shared" si="1"/>
         <v>08:45</v>
       </c>
       <c r="C61" s="17" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D61" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E61" s="22"/>
       <c r="F61" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G61" s="22"/>
       <c r="H61" s="22"/>
@@ -11416,21 +11506,21 @@
     <row r="62" spans="1:65">
       <c r="A62" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B62" t="str">
         <f t="shared" si="1"/>
         <v>08:50</v>
       </c>
       <c r="C62" s="17" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D62" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E62" s="22"/>
       <c r="F62" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G62" s="22"/>
       <c r="H62" s="22"/>
@@ -11495,21 +11585,21 @@
     <row r="63" spans="1:65">
       <c r="A63" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B63" t="str">
         <f t="shared" si="1"/>
         <v>08:55</v>
       </c>
       <c r="C63" s="17" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D63" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E63" s="22"/>
       <c r="F63" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G63" s="22"/>
       <c r="H63" s="22"/>
@@ -11574,25 +11664,25 @@
     <row r="64" spans="1:65">
       <c r="A64" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B64" t="str">
         <f t="shared" si="1"/>
         <v>09:00</v>
       </c>
       <c r="C64" s="17" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D64" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E64" s="22"/>
       <c r="F64" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G64" s="22"/>
       <c r="H64" s="22" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="I64" s="22"/>
       <c r="J64" s="22"/>
@@ -11655,21 +11745,21 @@
     <row r="65" spans="1:65">
       <c r="A65" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B65" t="str">
         <f t="shared" si="1"/>
         <v>09:05</v>
       </c>
       <c r="C65" s="17" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D65" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E65" s="22"/>
       <c r="F65" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G65" s="22"/>
       <c r="H65" s="22"/>
@@ -11734,21 +11824,21 @@
     <row r="66" spans="1:65">
       <c r="A66" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B66" t="str">
         <f t="shared" si="1"/>
         <v>09:10</v>
       </c>
       <c r="C66" s="17" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D66" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E66" s="22"/>
       <c r="F66" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G66" s="22"/>
       <c r="H66" s="22"/>
@@ -11813,21 +11903,21 @@
     <row r="67" spans="1:65">
       <c r="A67" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B67" t="str">
         <f t="shared" si="1"/>
         <v>09:15</v>
       </c>
       <c r="C67" s="17" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D67" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E67" s="22"/>
       <c r="F67" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G67" s="22"/>
       <c r="H67" s="22"/>
@@ -11895,21 +11985,21 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B68" t="str">
         <f t="shared" ref="B68:B131" si="3">TEXT($C68, "HH:mm")</f>
         <v>09:20</v>
       </c>
       <c r="C68" s="17" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D68" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E68" s="22"/>
       <c r="F68" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G68" s="22"/>
       <c r="H68" s="22"/>
@@ -11974,21 +12064,21 @@
     <row r="69" spans="1:65">
       <c r="A69" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B69" t="str">
         <f t="shared" si="3"/>
         <v>09:25</v>
       </c>
       <c r="C69" s="17" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D69" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E69" s="22"/>
       <c r="F69" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G69" s="22"/>
       <c r="H69" s="22"/>
@@ -12053,21 +12143,21 @@
     <row r="70" spans="1:65">
       <c r="A70" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B70" t="str">
         <f t="shared" si="3"/>
         <v>09:30</v>
       </c>
       <c r="C70" s="17" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D70" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E70" s="22"/>
       <c r="F70" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G70" s="22"/>
       <c r="H70" s="22"/>
@@ -12132,21 +12222,21 @@
     <row r="71" spans="1:65">
       <c r="A71" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B71" t="str">
         <f t="shared" si="3"/>
         <v>09:35</v>
       </c>
       <c r="C71" s="17" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D71" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E71" s="22"/>
       <c r="F71" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G71" s="22"/>
       <c r="H71" s="22"/>
@@ -12211,21 +12301,21 @@
     <row r="72" spans="1:65">
       <c r="A72" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B72" t="str">
         <f t="shared" si="3"/>
         <v>09:40</v>
       </c>
       <c r="C72" s="17" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D72" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E72" s="22"/>
       <c r="F72" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G72" s="22"/>
       <c r="H72" s="22"/>
@@ -12290,21 +12380,21 @@
     <row r="73" spans="1:65">
       <c r="A73" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B73" t="str">
         <f t="shared" si="3"/>
         <v>09:45</v>
       </c>
       <c r="C73" s="17" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D73" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E73" s="22"/>
       <c r="F73" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G73" s="22"/>
       <c r="H73" s="22"/>
@@ -12369,21 +12459,21 @@
     <row r="74" spans="1:65">
       <c r="A74" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B74" t="str">
         <f t="shared" si="3"/>
         <v>09:50</v>
       </c>
       <c r="C74" s="17" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D74" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E74" s="22"/>
       <c r="F74" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G74" s="22"/>
       <c r="H74" s="22"/>
@@ -12448,21 +12538,21 @@
     <row r="75" spans="1:65">
       <c r="A75" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B75" t="str">
         <f t="shared" si="3"/>
         <v>09:55</v>
       </c>
       <c r="C75" s="17" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D75" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E75" s="22"/>
       <c r="F75" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G75" s="22"/>
       <c r="H75" s="22"/>
@@ -12527,21 +12617,21 @@
     <row r="76" spans="1:65">
       <c r="A76" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B76" t="str">
         <f t="shared" si="3"/>
         <v>10:00</v>
       </c>
       <c r="C76" s="17" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D76" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E76" s="22"/>
       <c r="F76" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G76" s="22"/>
       <c r="H76" s="22"/>
@@ -12606,21 +12696,21 @@
     <row r="77" spans="1:65">
       <c r="A77" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B77" t="str">
         <f t="shared" si="3"/>
         <v>10:05</v>
       </c>
       <c r="C77" s="17" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D77" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E77" s="22"/>
       <c r="F77" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G77" s="22"/>
       <c r="H77" s="22"/>
@@ -12685,21 +12775,21 @@
     <row r="78" spans="1:65">
       <c r="A78" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B78" t="str">
         <f t="shared" si="3"/>
         <v>10:10</v>
       </c>
       <c r="C78" s="17" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D78" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E78" s="22"/>
       <c r="F78" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G78" s="22"/>
       <c r="H78" s="22"/>
@@ -12764,21 +12854,21 @@
     <row r="79" spans="1:65">
       <c r="A79" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B79" t="str">
         <f t="shared" si="3"/>
         <v>10:15</v>
       </c>
       <c r="C79" s="17" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D79" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E79" s="22"/>
       <c r="F79" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G79" s="22"/>
       <c r="H79" s="22"/>
@@ -12843,21 +12933,21 @@
     <row r="80" spans="1:65">
       <c r="A80" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B80" t="str">
         <f t="shared" si="3"/>
         <v>10:20</v>
       </c>
       <c r="C80" s="17" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D80" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E80" s="22"/>
       <c r="F80" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G80" s="22"/>
       <c r="H80" s="22"/>
@@ -12922,21 +13012,21 @@
     <row r="81" spans="1:65">
       <c r="A81" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B81" t="str">
         <f t="shared" si="3"/>
         <v>10:25</v>
       </c>
       <c r="C81" s="17" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D81" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E81" s="22"/>
       <c r="F81" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G81" s="22"/>
       <c r="H81" s="22"/>
@@ -13001,21 +13091,21 @@
     <row r="82" spans="1:65">
       <c r="A82" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B82" t="str">
         <f t="shared" si="3"/>
         <v>10:30</v>
       </c>
       <c r="C82" s="17" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D82" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E82" s="22"/>
       <c r="F82" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G82" s="22"/>
       <c r="H82" s="22"/>
@@ -13080,21 +13170,21 @@
     <row r="83" spans="1:65">
       <c r="A83" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B83" t="str">
         <f t="shared" si="3"/>
         <v>10:35</v>
       </c>
       <c r="C83" s="17" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D83" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E83" s="22"/>
       <c r="F83" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G83" s="22"/>
       <c r="H83" s="22"/>
@@ -13159,21 +13249,21 @@
     <row r="84" spans="1:65">
       <c r="A84" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B84" t="str">
         <f t="shared" si="3"/>
         <v>10:40</v>
       </c>
       <c r="C84" s="17" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D84" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E84" s="22"/>
       <c r="F84" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G84" s="22"/>
       <c r="H84" s="22"/>
@@ -13238,21 +13328,21 @@
     <row r="85" spans="1:65">
       <c r="A85" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B85" t="str">
         <f t="shared" si="3"/>
         <v>10:45</v>
       </c>
       <c r="C85" s="17" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D85" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E85" s="22"/>
       <c r="F85" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G85" s="22"/>
       <c r="H85" s="22"/>
@@ -13317,21 +13407,21 @@
     <row r="86" spans="1:65">
       <c r="A86" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B86" t="str">
         <f t="shared" si="3"/>
         <v>10:50</v>
       </c>
       <c r="C86" s="17" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D86" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E86" s="22"/>
       <c r="F86" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G86" s="22"/>
       <c r="H86" s="22"/>
@@ -13396,21 +13486,21 @@
     <row r="87" spans="1:65">
       <c r="A87" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B87" t="str">
         <f t="shared" si="3"/>
         <v>10:55</v>
       </c>
       <c r="C87" s="17" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D87" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E87" s="22"/>
       <c r="F87" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G87" s="22"/>
       <c r="H87" s="22"/>
@@ -13475,21 +13565,21 @@
     <row r="88" spans="1:65">
       <c r="A88" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B88" t="str">
         <f t="shared" si="3"/>
         <v>11:00</v>
       </c>
       <c r="C88" s="17" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="D88" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E88" s="22"/>
       <c r="F88" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G88" s="22"/>
       <c r="H88" s="22"/>
@@ -13554,21 +13644,21 @@
     <row r="89" spans="1:65">
       <c r="A89" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B89" t="str">
         <f t="shared" si="3"/>
         <v>11:05</v>
       </c>
       <c r="C89" s="17" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D89" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E89" s="22"/>
       <c r="F89" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G89" s="22"/>
       <c r="H89" s="22"/>
@@ -13633,21 +13723,21 @@
     <row r="90" spans="1:65">
       <c r="A90" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B90" t="str">
         <f t="shared" si="3"/>
         <v>11:10</v>
       </c>
       <c r="C90" s="17" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="D90" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E90" s="22"/>
       <c r="F90" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G90" s="22"/>
       <c r="H90" s="22"/>
@@ -13712,21 +13802,21 @@
     <row r="91" spans="1:65">
       <c r="A91" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B91" t="str">
         <f t="shared" si="3"/>
         <v>11:15</v>
       </c>
       <c r="C91" s="17" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D91" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E91" s="22"/>
       <c r="F91" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G91" s="22"/>
       <c r="H91" s="22"/>
@@ -13791,21 +13881,21 @@
     <row r="92" spans="1:65">
       <c r="A92" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B92" t="str">
         <f t="shared" si="3"/>
         <v>11:20</v>
       </c>
       <c r="C92" s="17" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D92" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E92" s="22"/>
       <c r="F92" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G92" s="22"/>
       <c r="H92" s="22"/>
@@ -13870,21 +13960,21 @@
     <row r="93" spans="1:65">
       <c r="A93" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B93" t="str">
         <f t="shared" si="3"/>
         <v>11:25</v>
       </c>
       <c r="C93" s="17" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D93" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E93" s="22"/>
       <c r="F93" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G93" s="22"/>
       <c r="H93" s="22"/>
@@ -13949,21 +14039,21 @@
     <row r="94" spans="1:65">
       <c r="A94" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B94" t="str">
         <f t="shared" si="3"/>
         <v>11:30</v>
       </c>
       <c r="C94" s="17" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D94" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E94" s="22"/>
       <c r="F94" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G94" s="22"/>
       <c r="H94" s="22"/>
@@ -14028,21 +14118,21 @@
     <row r="95" spans="1:65">
       <c r="A95" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B95" t="str">
         <f t="shared" si="3"/>
         <v>11:35</v>
       </c>
       <c r="C95" s="17" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D95" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E95" s="22"/>
       <c r="F95" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G95" s="22"/>
       <c r="H95" s="22"/>
@@ -14107,21 +14197,21 @@
     <row r="96" spans="1:65">
       <c r="A96" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B96" t="str">
         <f t="shared" si="3"/>
         <v>11:40</v>
       </c>
       <c r="C96" s="17" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D96" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E96" s="22"/>
       <c r="F96" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G96" s="22"/>
       <c r="H96" s="22"/>
@@ -14186,21 +14276,21 @@
     <row r="97" spans="1:65">
       <c r="A97" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B97" t="str">
         <f t="shared" si="3"/>
         <v>11:45</v>
       </c>
       <c r="C97" s="17" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D97" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E97" s="22"/>
       <c r="F97" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G97" s="22"/>
       <c r="H97" s="22"/>
@@ -14265,21 +14355,21 @@
     <row r="98" spans="1:65">
       <c r="A98" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B98" t="str">
         <f t="shared" si="3"/>
         <v>11:50</v>
       </c>
       <c r="C98" s="17" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="D98" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E98" s="22"/>
       <c r="F98" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G98" s="22"/>
       <c r="H98" s="22"/>
@@ -14344,21 +14434,21 @@
     <row r="99" spans="1:65">
       <c r="A99" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B99" t="str">
         <f t="shared" si="3"/>
         <v>11:55</v>
       </c>
       <c r="C99" s="17" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D99" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E99" s="22"/>
       <c r="F99" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G99" s="22"/>
       <c r="H99" s="22"/>
@@ -14423,25 +14513,25 @@
     <row r="100" spans="1:65">
       <c r="A100" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B100" t="str">
         <f t="shared" si="3"/>
         <v>12:00</v>
       </c>
       <c r="C100" s="17" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="D100" s="17" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="E100" s="22"/>
       <c r="F100" s="22" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="G100" s="22"/>
       <c r="H100" s="22" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="I100" s="22"/>
       <c r="J100" s="22"/>
@@ -14504,21 +14594,21 @@
     <row r="101" spans="1:65">
       <c r="A101" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B101" t="str">
         <f t="shared" si="3"/>
         <v>12:05</v>
       </c>
       <c r="C101" s="17" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="D101" s="17" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="E101" s="22"/>
       <c r="F101" s="22" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="G101" s="22"/>
       <c r="H101" s="22"/>
@@ -14583,21 +14673,21 @@
     <row r="102" spans="1:65">
       <c r="A102" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B102" t="str">
         <f t="shared" si="3"/>
         <v>12:10</v>
       </c>
       <c r="C102" s="17" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D102" s="17" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="E102" s="22"/>
       <c r="F102" s="22" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="G102" s="22"/>
       <c r="H102" s="22"/>
@@ -14662,21 +14752,21 @@
     <row r="103" spans="1:65">
       <c r="A103" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B103" t="str">
         <f t="shared" si="3"/>
         <v>12:15</v>
       </c>
       <c r="C103" s="17" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D103" s="17" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="E103" s="22"/>
       <c r="F103" s="22" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="G103" s="22"/>
       <c r="H103" s="22"/>
@@ -14741,21 +14831,21 @@
     <row r="104" spans="1:65">
       <c r="A104" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B104" t="str">
         <f t="shared" si="3"/>
         <v>12:20</v>
       </c>
       <c r="C104" s="17" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D104" s="17" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="E104" s="22"/>
       <c r="F104" s="22" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="G104" s="22"/>
       <c r="H104" s="22"/>
@@ -14820,21 +14910,21 @@
     <row r="105" spans="1:65">
       <c r="A105" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B105" t="str">
         <f t="shared" si="3"/>
         <v>12:25</v>
       </c>
       <c r="C105" s="17" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D105" s="17" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="E105" s="22"/>
       <c r="F105" s="22" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="G105" s="22"/>
       <c r="H105" s="22"/>
@@ -14899,25 +14989,25 @@
     <row r="106" spans="1:65">
       <c r="A106" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B106" t="str">
         <f t="shared" si="3"/>
         <v>12:30</v>
       </c>
       <c r="C106" s="17" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D106" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E106" s="22"/>
       <c r="F106" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G106" s="22"/>
       <c r="H106" s="22" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="I106" s="22"/>
       <c r="J106" s="22"/>
@@ -14980,25 +15070,25 @@
     <row r="107" spans="1:65">
       <c r="A107" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B107" t="str">
         <f t="shared" si="3"/>
         <v>12:35</v>
       </c>
       <c r="C107" s="17" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D107" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E107" s="22"/>
       <c r="F107" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G107" s="22"/>
       <c r="H107" s="22" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="I107" s="22"/>
       <c r="J107" s="22"/>
@@ -15061,21 +15151,21 @@
     <row r="108" spans="1:65">
       <c r="A108" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B108" t="str">
         <f t="shared" si="3"/>
         <v>12:40</v>
       </c>
       <c r="C108" s="17" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D108" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E108" s="22"/>
       <c r="F108" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G108" s="22"/>
       <c r="H108" s="22"/>
@@ -15140,21 +15230,21 @@
     <row r="109" spans="1:65">
       <c r="A109" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B109" t="str">
         <f t="shared" si="3"/>
         <v>12:45</v>
       </c>
       <c r="C109" s="17" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D109" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E109" s="22"/>
       <c r="F109" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G109" s="22"/>
       <c r="H109" s="22"/>
@@ -15219,21 +15309,21 @@
     <row r="110" spans="1:65">
       <c r="A110" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B110" t="str">
         <f t="shared" si="3"/>
         <v>12:50</v>
       </c>
       <c r="C110" s="17" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D110" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E110" s="22"/>
       <c r="F110" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G110" s="22"/>
       <c r="H110" s="22"/>
@@ -15298,21 +15388,21 @@
     <row r="111" spans="1:65">
       <c r="A111" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B111" t="str">
         <f t="shared" si="3"/>
         <v>12:55</v>
       </c>
       <c r="C111" s="17" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D111" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E111" s="22"/>
       <c r="F111" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G111" s="22"/>
       <c r="H111" s="22"/>
@@ -15377,25 +15467,25 @@
     <row r="112" spans="1:65">
       <c r="A112" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B112" t="str">
         <f t="shared" si="3"/>
         <v>13:00</v>
       </c>
       <c r="C112" s="17" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D112" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E112" s="22"/>
       <c r="F112" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G112" s="22"/>
       <c r="H112" s="22" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="I112" s="22"/>
       <c r="J112" s="22"/>
@@ -15458,21 +15548,21 @@
     <row r="113" spans="1:65">
       <c r="A113" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B113" t="str">
         <f t="shared" si="3"/>
         <v>13:05</v>
       </c>
       <c r="C113" s="17" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D113" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E113" s="22"/>
       <c r="F113" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G113" s="22"/>
       <c r="H113" s="22"/>
@@ -15537,21 +15627,21 @@
     <row r="114" spans="1:65">
       <c r="A114" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B114" t="str">
         <f t="shared" si="3"/>
         <v>13:10</v>
       </c>
       <c r="C114" s="17" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D114" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E114" s="22"/>
       <c r="F114" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G114" s="22"/>
       <c r="H114" s="22"/>
@@ -15616,21 +15706,21 @@
     <row r="115" spans="1:65">
       <c r="A115" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B115" t="str">
         <f t="shared" si="3"/>
         <v>13:15</v>
       </c>
       <c r="C115" s="17" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D115" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E115" s="22"/>
       <c r="F115" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G115" s="22"/>
       <c r="H115" s="22"/>
@@ -15695,21 +15785,21 @@
     <row r="116" spans="1:65">
       <c r="A116" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B116" t="str">
         <f t="shared" si="3"/>
         <v>13:20</v>
       </c>
       <c r="C116" s="17" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D116" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E116" s="22"/>
       <c r="F116" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G116" s="22"/>
       <c r="H116" s="22"/>
@@ -15774,21 +15864,21 @@
     <row r="117" spans="1:65">
       <c r="A117" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B117" t="str">
         <f t="shared" si="3"/>
         <v>13:25</v>
       </c>
       <c r="C117" s="17" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D117" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E117" s="22"/>
       <c r="F117" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G117" s="22"/>
       <c r="H117" s="22"/>
@@ -15853,21 +15943,21 @@
     <row r="118" spans="1:65">
       <c r="A118" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B118" t="str">
         <f t="shared" si="3"/>
         <v>13:30</v>
       </c>
       <c r="C118" s="17" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D118" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E118" s="22"/>
       <c r="F118" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G118" s="22"/>
       <c r="H118" s="22"/>
@@ -15932,21 +16022,21 @@
     <row r="119" spans="1:65">
       <c r="A119" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B119" t="str">
         <f t="shared" si="3"/>
         <v>13:35</v>
       </c>
       <c r="C119" s="17" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="D119" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E119" s="22"/>
       <c r="F119" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G119" s="22"/>
       <c r="H119" s="22"/>
@@ -16011,21 +16101,21 @@
     <row r="120" spans="1:65">
       <c r="A120" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B120" t="str">
         <f t="shared" si="3"/>
         <v>13:40</v>
       </c>
       <c r="C120" s="17" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D120" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E120" s="22"/>
       <c r="F120" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G120" s="22"/>
       <c r="H120" s="22"/>
@@ -16090,21 +16180,21 @@
     <row r="121" spans="1:65">
       <c r="A121" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B121" t="str">
         <f t="shared" si="3"/>
         <v>13:45</v>
       </c>
       <c r="C121" s="17" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D121" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E121" s="22"/>
       <c r="F121" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G121" s="22"/>
       <c r="H121" s="22"/>
@@ -16169,21 +16259,21 @@
     <row r="122" spans="1:65">
       <c r="A122" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B122" t="str">
         <f t="shared" si="3"/>
         <v>13:50</v>
       </c>
       <c r="C122" s="17" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D122" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E122" s="22"/>
       <c r="F122" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G122" s="22"/>
       <c r="H122" s="22"/>
@@ -16248,21 +16338,21 @@
     <row r="123" spans="1:65">
       <c r="A123" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B123" t="str">
         <f t="shared" si="3"/>
         <v>13:55</v>
       </c>
       <c r="C123" s="17" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D123" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E123" s="22"/>
       <c r="F123" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G123" s="22"/>
       <c r="H123" s="22"/>
@@ -16327,25 +16417,25 @@
     <row r="124" spans="1:65">
       <c r="A124" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B124" t="str">
         <f t="shared" si="3"/>
         <v>14:00</v>
       </c>
       <c r="C124" s="17" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D124" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E124" s="22"/>
       <c r="F124" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G124" s="22"/>
       <c r="H124" s="22" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="I124" s="22"/>
       <c r="J124" s="22"/>
@@ -16408,25 +16498,25 @@
     <row r="125" spans="1:65">
       <c r="A125" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B125" t="str">
         <f t="shared" si="3"/>
         <v>14:05</v>
       </c>
       <c r="C125" s="17" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D125" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E125" s="22"/>
       <c r="F125" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G125" s="22"/>
       <c r="H125" s="22" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="I125" s="22"/>
       <c r="J125" s="22"/>
@@ -16489,21 +16579,21 @@
     <row r="126" spans="1:65">
       <c r="A126" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B126" t="str">
         <f t="shared" si="3"/>
         <v>14:10</v>
       </c>
       <c r="C126" s="17" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D126" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E126" s="22"/>
       <c r="F126" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G126" s="22"/>
       <c r="H126" s="22"/>
@@ -16568,21 +16658,21 @@
     <row r="127" spans="1:65">
       <c r="A127" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B127" t="str">
         <f t="shared" si="3"/>
         <v>14:15</v>
       </c>
       <c r="C127" s="17" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D127" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E127" s="22"/>
       <c r="F127" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G127" s="22"/>
       <c r="H127" s="22"/>
@@ -16647,21 +16737,21 @@
     <row r="128" spans="1:65">
       <c r="A128" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B128" t="str">
         <f t="shared" si="3"/>
         <v>14:20</v>
       </c>
       <c r="C128" s="17" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D128" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E128" s="22"/>
       <c r="F128" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G128" s="22"/>
       <c r="H128" s="22"/>
@@ -16726,21 +16816,21 @@
     <row r="129" spans="1:65">
       <c r="A129" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B129" t="str">
         <f t="shared" si="3"/>
         <v>14:25</v>
       </c>
       <c r="C129" s="17" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D129" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E129" s="22"/>
       <c r="F129" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G129" s="22"/>
       <c r="H129" s="22"/>
@@ -16805,21 +16895,21 @@
     <row r="130" spans="1:65">
       <c r="A130" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B130" t="str">
         <f t="shared" si="3"/>
         <v>14:30</v>
       </c>
       <c r="C130" s="17" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D130" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E130" s="22"/>
       <c r="F130" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G130" s="22"/>
       <c r="H130" s="22"/>
@@ -16884,21 +16974,21 @@
     <row r="131" spans="1:65">
       <c r="A131" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B131" t="str">
         <f t="shared" si="3"/>
         <v>14:35</v>
       </c>
       <c r="C131" s="17" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D131" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E131" s="22"/>
       <c r="F131" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G131" s="22"/>
       <c r="H131" s="22"/>
@@ -16966,21 +17056,21 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B132" t="str">
         <f t="shared" ref="B132:B168" si="5">TEXT($C132, "HH:mm")</f>
         <v>14:40</v>
       </c>
       <c r="C132" s="17" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D132" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E132" s="22"/>
       <c r="F132" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G132" s="22"/>
       <c r="H132" s="22"/>
@@ -17045,21 +17135,21 @@
     <row r="133" spans="1:65">
       <c r="A133" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B133" t="str">
         <f t="shared" si="5"/>
         <v>14:45</v>
       </c>
       <c r="C133" s="17" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D133" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E133" s="22"/>
       <c r="F133" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G133" s="22"/>
       <c r="H133" s="22"/>
@@ -17124,21 +17214,21 @@
     <row r="134" spans="1:65">
       <c r="A134" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B134" t="str">
         <f t="shared" si="5"/>
         <v>14:50</v>
       </c>
       <c r="C134" s="17" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D134" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E134" s="22"/>
       <c r="F134" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G134" s="22"/>
       <c r="H134" s="22"/>
@@ -17203,21 +17293,21 @@
     <row r="135" spans="1:65">
       <c r="A135" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B135" t="str">
         <f t="shared" si="5"/>
         <v>14:55</v>
       </c>
       <c r="C135" s="17" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D135" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E135" s="22"/>
       <c r="F135" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G135" s="22"/>
       <c r="H135" s="22"/>
@@ -17282,25 +17372,25 @@
     <row r="136" spans="1:65">
       <c r="A136" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B136" t="str">
         <f t="shared" si="5"/>
         <v>15:00</v>
       </c>
       <c r="C136" s="17" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="D136" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E136" s="22"/>
       <c r="F136" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G136" s="22"/>
       <c r="H136" s="22" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="I136" s="22"/>
       <c r="J136" s="22"/>
@@ -17363,25 +17453,25 @@
     <row r="137" spans="1:65">
       <c r="A137" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B137" t="str">
         <f t="shared" si="5"/>
         <v>15:05</v>
       </c>
       <c r="C137" s="17" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="D137" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E137" s="22"/>
       <c r="F137" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G137" s="22"/>
       <c r="H137" s="22" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="I137" s="22"/>
       <c r="J137" s="22"/>
@@ -17444,21 +17534,21 @@
     <row r="138" spans="1:65">
       <c r="A138" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B138" t="str">
         <f t="shared" si="5"/>
         <v>15:10</v>
       </c>
       <c r="C138" s="17" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D138" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E138" s="22"/>
       <c r="F138" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G138" s="22"/>
       <c r="H138" s="22"/>
@@ -17523,21 +17613,21 @@
     <row r="139" spans="1:65">
       <c r="A139" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B139" t="str">
         <f t="shared" si="5"/>
         <v>15:15</v>
       </c>
       <c r="C139" s="17" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D139" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E139" s="22"/>
       <c r="F139" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G139" s="22"/>
       <c r="H139" s="22"/>
@@ -17602,21 +17692,21 @@
     <row r="140" spans="1:65">
       <c r="A140" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B140" t="str">
         <f t="shared" si="5"/>
         <v>15:20</v>
       </c>
       <c r="C140" s="17" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="D140" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E140" s="22"/>
       <c r="F140" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G140" s="22"/>
       <c r="H140" s="22"/>
@@ -17681,21 +17771,21 @@
     <row r="141" spans="1:65">
       <c r="A141" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B141" t="str">
         <f t="shared" si="5"/>
         <v>15:25</v>
       </c>
       <c r="C141" s="17" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D141" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E141" s="22"/>
       <c r="F141" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G141" s="22"/>
       <c r="H141" s="22"/>
@@ -17760,21 +17850,21 @@
     <row r="142" spans="1:65">
       <c r="A142" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B142" t="str">
         <f t="shared" si="5"/>
         <v>15:30</v>
       </c>
       <c r="C142" s="17" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D142" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E142" s="22"/>
       <c r="F142" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G142" s="22"/>
       <c r="H142" s="22"/>
@@ -17839,21 +17929,21 @@
     <row r="143" spans="1:65">
       <c r="A143" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B143" t="str">
         <f t="shared" si="5"/>
         <v>15:35</v>
       </c>
       <c r="C143" s="17" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D143" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E143" s="22"/>
       <c r="F143" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G143" s="22"/>
       <c r="H143" s="22"/>
@@ -17918,21 +18008,21 @@
     <row r="144" spans="1:65">
       <c r="A144" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B144" t="str">
         <f t="shared" si="5"/>
         <v>15:40</v>
       </c>
       <c r="C144" s="17" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D144" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E144" s="22"/>
       <c r="F144" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G144" s="22"/>
       <c r="H144" s="22"/>
@@ -17997,21 +18087,21 @@
     <row r="145" spans="1:65">
       <c r="A145" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B145" t="str">
         <f t="shared" si="5"/>
         <v>15:45</v>
       </c>
       <c r="C145" s="17" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D145" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E145" s="22"/>
       <c r="F145" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G145" s="22"/>
       <c r="H145" s="22"/>
@@ -18076,21 +18166,21 @@
     <row r="146" spans="1:65">
       <c r="A146" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B146" t="str">
         <f t="shared" si="5"/>
         <v>15:50</v>
       </c>
       <c r="C146" s="17" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D146" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E146" s="22"/>
       <c r="F146" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G146" s="22"/>
       <c r="H146" s="22"/>
@@ -18155,21 +18245,21 @@
     <row r="147" spans="1:65">
       <c r="A147" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B147" t="str">
         <f t="shared" si="5"/>
         <v>15:55</v>
       </c>
       <c r="C147" s="17" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D147" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E147" s="22"/>
       <c r="F147" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G147" s="22"/>
       <c r="H147" s="22"/>
@@ -18234,25 +18324,25 @@
     <row r="148" spans="1:65">
       <c r="A148" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B148" t="str">
         <f t="shared" si="5"/>
         <v>16:00</v>
       </c>
       <c r="C148" s="17" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D148" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E148" s="22"/>
       <c r="F148" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G148" s="22"/>
       <c r="H148" s="22" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="I148" s="22"/>
       <c r="J148" s="22"/>
@@ -18315,21 +18405,21 @@
     <row r="149" spans="1:65">
       <c r="A149" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B149" t="str">
         <f t="shared" si="5"/>
         <v>16:05</v>
       </c>
       <c r="C149" s="17" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D149" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E149" s="22"/>
       <c r="F149" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G149" s="22"/>
       <c r="H149" s="22"/>
@@ -18394,21 +18484,21 @@
     <row r="150" spans="1:65">
       <c r="A150" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B150" t="str">
         <f t="shared" si="5"/>
         <v>16:10</v>
       </c>
       <c r="C150" s="17" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D150" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E150" s="22"/>
       <c r="F150" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G150" s="22"/>
       <c r="H150" s="22"/>
@@ -18473,21 +18563,21 @@
     <row r="151" spans="1:65">
       <c r="A151" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B151" t="str">
         <f t="shared" si="5"/>
         <v>16:15</v>
       </c>
       <c r="C151" s="17" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D151" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E151" s="22"/>
       <c r="F151" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G151" s="22"/>
       <c r="H151" s="22"/>
@@ -18552,21 +18642,21 @@
     <row r="152" spans="1:65">
       <c r="A152" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B152" t="str">
         <f t="shared" si="5"/>
         <v>16:20</v>
       </c>
       <c r="C152" s="17" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D152" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E152" s="22"/>
       <c r="F152" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G152" s="22"/>
       <c r="H152" s="22"/>
@@ -18631,21 +18721,21 @@
     <row r="153" spans="1:65">
       <c r="A153" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B153" t="str">
         <f t="shared" si="5"/>
         <v>16:25</v>
       </c>
       <c r="C153" s="17" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="D153" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E153" s="22"/>
       <c r="F153" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G153" s="22"/>
       <c r="H153" s="22"/>
@@ -18710,21 +18800,21 @@
     <row r="154" spans="1:65">
       <c r="A154" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B154" t="str">
         <f t="shared" si="5"/>
         <v>16:30</v>
       </c>
       <c r="C154" s="17" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D154" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E154" s="22"/>
       <c r="F154" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G154" s="22"/>
       <c r="H154" s="22"/>
@@ -18789,21 +18879,21 @@
     <row r="155" spans="1:65">
       <c r="A155" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B155" t="str">
         <f t="shared" si="5"/>
         <v>16:35</v>
       </c>
       <c r="C155" s="17" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="D155" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E155" s="22"/>
       <c r="F155" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G155" s="22"/>
       <c r="H155" s="22"/>
@@ -18868,21 +18958,21 @@
     <row r="156" spans="1:65">
       <c r="A156" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B156" t="str">
         <f t="shared" si="5"/>
         <v>16:40</v>
       </c>
       <c r="C156" s="17" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D156" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E156" s="22"/>
       <c r="F156" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G156" s="22"/>
       <c r="H156" s="22"/>
@@ -18947,21 +19037,21 @@
     <row r="157" spans="1:65">
       <c r="A157" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B157" t="str">
         <f t="shared" si="5"/>
         <v>16:45</v>
       </c>
       <c r="C157" s="17" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D157" s="17" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="E157" s="22"/>
       <c r="F157" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G157" s="22"/>
       <c r="H157" s="22"/>
@@ -19026,21 +19116,21 @@
     <row r="158" spans="1:65">
       <c r="A158" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B158" t="str">
         <f t="shared" si="5"/>
         <v>16:50</v>
       </c>
       <c r="C158" s="17" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D158" s="17" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="E158" s="22"/>
       <c r="F158" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G158" s="22"/>
       <c r="H158" s="22"/>
@@ -19105,21 +19195,21 @@
     <row r="159" spans="1:65">
       <c r="A159" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B159" t="str">
         <f t="shared" si="5"/>
         <v>16:55</v>
       </c>
       <c r="C159" s="17" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D159" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E159" s="22"/>
       <c r="F159" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G159" s="22"/>
       <c r="H159" s="22"/>
@@ -19184,21 +19274,21 @@
     <row r="160" spans="1:65">
       <c r="A160" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B160" t="str">
         <f t="shared" si="5"/>
         <v>17:00</v>
       </c>
       <c r="C160" s="17" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="D160" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E160" s="22"/>
       <c r="F160" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G160" s="22"/>
       <c r="H160" s="22"/>
@@ -19263,21 +19353,21 @@
     <row r="161" spans="1:65">
       <c r="A161" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B161" t="str">
         <f t="shared" si="5"/>
         <v>17:05</v>
       </c>
       <c r="C161" s="17" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D161" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E161" s="22"/>
       <c r="F161" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G161" s="22"/>
       <c r="H161" s="22"/>
@@ -19342,21 +19432,21 @@
     <row r="162" spans="1:65">
       <c r="A162" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B162" t="str">
         <f t="shared" si="5"/>
         <v>17:10</v>
       </c>
       <c r="C162" s="17" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D162" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E162" s="22"/>
       <c r="F162" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G162" s="22"/>
       <c r="H162" s="22"/>
@@ -19421,21 +19511,21 @@
     <row r="163" spans="1:65">
       <c r="A163" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B163" t="str">
         <f t="shared" si="5"/>
         <v>17:15</v>
       </c>
       <c r="C163" s="17" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D163" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E163" s="22"/>
       <c r="F163" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G163" s="22"/>
       <c r="H163" s="22"/>
@@ -19500,21 +19590,21 @@
     <row r="164" spans="1:65">
       <c r="A164" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B164" t="str">
         <f t="shared" si="5"/>
         <v>17:20</v>
       </c>
       <c r="C164" s="17" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D164" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E164" s="22"/>
       <c r="F164" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G164" s="22"/>
       <c r="H164" s="22"/>
@@ -19579,21 +19669,21 @@
     <row r="165" spans="1:65">
       <c r="A165" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B165" t="str">
         <f t="shared" si="5"/>
         <v>17:25</v>
       </c>
       <c r="C165" s="17" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="D165" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E165" s="22"/>
       <c r="F165" s="22" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G165" s="22"/>
       <c r="H165" s="22"/>
@@ -19658,25 +19748,25 @@
     <row r="166" spans="1:65">
       <c r="A166" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B166" t="str">
         <f t="shared" si="5"/>
         <v>17:30</v>
       </c>
       <c r="C166" s="17" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="D166" s="17" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E166" s="22"/>
       <c r="F166" s="22" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="G166" s="22"/>
       <c r="H166" s="22" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="I166" s="22"/>
       <c r="J166" s="22"/>
@@ -19739,21 +19829,21 @@
     <row r="167" spans="1:65">
       <c r="A167" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B167" t="str">
         <f t="shared" si="5"/>
         <v>17:35</v>
       </c>
       <c r="C167" s="17" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D167" s="17" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E167" s="22"/>
       <c r="F167" s="22" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="G167" s="22"/>
       <c r="H167" s="22"/>
@@ -19818,21 +19908,21 @@
     <row r="168" spans="1:65">
       <c r="A168" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B168" t="str">
         <f t="shared" si="5"/>
         <v>17:40</v>
       </c>
       <c r="C168" s="17" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D168" s="17" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="E168" s="22"/>
       <c r="F168" s="22" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="G168" s="22"/>
       <c r="H168" s="22"/>
@@ -19900,7 +19990,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B169" t="str">
         <f>TEXT($C169, "HH:mm")</f>
@@ -19910,11 +20000,11 @@
         <v>0.73958333333333337</v>
       </c>
       <c r="D169" s="17" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E169" s="22"/>
       <c r="F169" s="22" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="G169" s="22"/>
       <c r="H169" s="22"/>
@@ -19982,7 +20072,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B170" t="str">
         <f t="shared" ref="B170:B233" si="7">TEXT($C170, "HH:mm")</f>
@@ -19992,11 +20082,11 @@
         <v>0.74305555555555558</v>
       </c>
       <c r="D170" s="17" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E170" s="22"/>
       <c r="F170" s="22" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="G170" s="22"/>
       <c r="H170" s="22"/>
@@ -20061,21 +20151,21 @@
     <row r="171" spans="1:65">
       <c r="A171" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B171" t="str">
         <f t="shared" si="7"/>
         <v>17:55</v>
       </c>
       <c r="C171" s="17" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D171" s="17" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E171" s="22"/>
       <c r="F171" s="22" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="G171" s="22"/>
       <c r="H171" s="22"/>
@@ -20140,25 +20230,25 @@
     <row r="172" spans="1:65">
       <c r="A172" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B172" t="str">
         <f t="shared" si="7"/>
         <v>18:00</v>
       </c>
       <c r="C172" s="17" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D172" s="17" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E172" s="22"/>
       <c r="F172" s="22" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="G172" s="22"/>
       <c r="H172" s="22" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="I172" s="22"/>
       <c r="J172" s="22"/>
@@ -20221,21 +20311,21 @@
     <row r="173" spans="1:65">
       <c r="A173" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B173" t="str">
         <f t="shared" si="7"/>
         <v>18:05</v>
       </c>
       <c r="C173" s="17" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D173" s="17" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E173" s="22"/>
       <c r="F173" s="22" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="G173" s="22"/>
       <c r="H173" s="22"/>
@@ -20300,21 +20390,21 @@
     <row r="174" spans="1:65">
       <c r="A174" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B174" t="str">
         <f t="shared" si="7"/>
         <v>18:10</v>
       </c>
       <c r="C174" s="17" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D174" s="17" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E174" s="22"/>
       <c r="F174" s="22" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="G174" s="22"/>
       <c r="H174" s="22"/>
@@ -20379,21 +20469,21 @@
     <row r="175" spans="1:65">
       <c r="A175" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B175" t="str">
         <f t="shared" si="7"/>
         <v>18:15</v>
       </c>
       <c r="C175" s="17" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D175" s="17" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E175" s="22"/>
       <c r="F175" s="22" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="G175" s="22"/>
       <c r="H175" s="22"/>
@@ -20458,21 +20548,21 @@
     <row r="176" spans="1:65">
       <c r="A176" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B176" t="str">
         <f t="shared" si="7"/>
         <v>18:20</v>
       </c>
       <c r="C176" s="17" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D176" s="17" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E176" s="22"/>
       <c r="F176" s="22" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="G176" s="22"/>
       <c r="H176" s="22"/>
@@ -20537,21 +20627,21 @@
     <row r="177" spans="1:65">
       <c r="A177" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B177" t="str">
         <f t="shared" si="7"/>
         <v>18:25</v>
       </c>
       <c r="C177" s="17" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="D177" s="17" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E177" s="22"/>
       <c r="F177" s="22" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="G177" s="22"/>
       <c r="H177" s="22"/>
@@ -20616,25 +20706,25 @@
     <row r="178" spans="1:65">
       <c r="A178" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B178" t="str">
         <f t="shared" si="7"/>
         <v>18:30</v>
       </c>
       <c r="C178" s="17" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D178" s="17" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E178" s="22"/>
       <c r="F178" s="22" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="G178" s="22"/>
       <c r="H178" s="22" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="I178" s="22"/>
       <c r="J178" s="22"/>
@@ -20697,21 +20787,21 @@
     <row r="179" spans="1:65">
       <c r="A179" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B179" t="str">
         <f t="shared" si="7"/>
         <v>18:35</v>
       </c>
       <c r="C179" s="17" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="D179" s="17" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="E179" s="22"/>
       <c r="F179" s="22" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="G179" s="22"/>
       <c r="H179" s="22"/>
@@ -20776,21 +20866,21 @@
     <row r="180" spans="1:65">
       <c r="A180" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B180" t="str">
         <f t="shared" si="7"/>
         <v>18:40</v>
       </c>
       <c r="C180" s="17" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="D180" s="17" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E180" s="22"/>
       <c r="F180" s="22" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="G180" s="22"/>
       <c r="H180" s="22"/>
@@ -20855,25 +20945,25 @@
     <row r="181" spans="1:65">
       <c r="A181" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B181" t="str">
         <f t="shared" si="7"/>
         <v>18:45</v>
       </c>
       <c r="C181" s="17" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D181" s="17" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E181" s="22"/>
       <c r="F181" s="22" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="G181" s="22"/>
       <c r="H181" s="22" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="I181" s="22"/>
       <c r="J181" s="22"/>
@@ -20936,23 +21026,23 @@
     <row r="182" spans="1:65">
       <c r="A182" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B182" t="str">
         <f t="shared" si="7"/>
         <v>18:50</v>
       </c>
       <c r="C182" s="17" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="D182" s="17" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="E182" s="22" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="F182" s="22" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="G182" s="22"/>
       <c r="H182" s="22"/>
@@ -21017,23 +21107,23 @@
     <row r="183" spans="1:65">
       <c r="A183" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B183" t="str">
         <f t="shared" si="7"/>
         <v>18:55</v>
       </c>
       <c r="C183" s="17" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="D183" s="17" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="E183" s="22" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="F183" s="22" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="G183" s="22"/>
       <c r="H183" s="22"/>
@@ -21098,27 +21188,27 @@
     <row r="184" spans="1:65">
       <c r="A184" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B184" t="str">
         <f t="shared" si="7"/>
         <v>19:00</v>
       </c>
       <c r="C184" s="17" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D184" s="17" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="E184" s="22" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="F184" s="22" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="G184" s="22"/>
       <c r="H184" s="22" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="I184" s="22"/>
       <c r="J184" s="22"/>
@@ -21181,23 +21271,23 @@
     <row r="185" spans="1:65">
       <c r="A185" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B185" t="str">
         <f t="shared" si="7"/>
         <v>19:05</v>
       </c>
       <c r="C185" s="17" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="D185" s="17" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="E185" s="22" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="F185" s="22" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="G185" s="22"/>
       <c r="H185" s="22"/>
@@ -21262,23 +21352,23 @@
     <row r="186" spans="1:65">
       <c r="A186" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B186" t="str">
         <f t="shared" si="7"/>
         <v>19:10</v>
       </c>
       <c r="C186" s="17" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D186" s="17" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="E186" s="22" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="F186" s="22" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="G186" s="22"/>
       <c r="H186" s="22"/>
@@ -21343,23 +21433,23 @@
     <row r="187" spans="1:65">
       <c r="A187" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B187" t="str">
         <f t="shared" si="7"/>
         <v>19:15</v>
       </c>
       <c r="C187" s="17" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="D187" s="17" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="E187" s="22" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="F187" s="22" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="G187" s="22"/>
       <c r="H187" s="22"/>
@@ -21424,23 +21514,23 @@
     <row r="188" spans="1:65">
       <c r="A188" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B188" t="str">
         <f t="shared" si="7"/>
         <v>19:20</v>
       </c>
       <c r="C188" s="17" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="D188" s="17" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="E188" s="22" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="F188" s="22" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="G188" s="22"/>
       <c r="H188" s="22"/>
@@ -21505,23 +21595,23 @@
     <row r="189" spans="1:65">
       <c r="A189" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B189" t="str">
         <f t="shared" si="7"/>
         <v>19:25</v>
       </c>
       <c r="C189" s="17" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D189" s="17" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="E189" s="22" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="F189" s="22" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="G189" s="22"/>
       <c r="H189" s="22"/>
@@ -21586,26 +21676,26 @@
     <row r="190" spans="1:65">
       <c r="A190" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B190" t="str">
         <f t="shared" si="7"/>
         <v>19:30</v>
       </c>
       <c r="C190" s="17" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="D190" s="17" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="E190" s="22" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="F190" s="22" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="G190" s="22" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="H190" s="22"/>
       <c r="I190" s="22"/>
@@ -21669,26 +21759,26 @@
     <row r="191" spans="1:65">
       <c r="A191" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B191" t="str">
         <f t="shared" si="7"/>
         <v>19:35</v>
       </c>
       <c r="C191" s="17" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="D191" s="17" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="E191" s="22" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="F191" s="22" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="G191" s="22" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="H191" s="22"/>
       <c r="I191" s="22"/>
@@ -21752,26 +21842,26 @@
     <row r="192" spans="1:65">
       <c r="A192" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B192" t="str">
         <f t="shared" si="7"/>
         <v>19:40</v>
       </c>
       <c r="C192" s="17" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="D192" s="17" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="E192" s="22" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="F192" s="22" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="G192" s="22" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="H192" s="22"/>
       <c r="I192" s="22"/>
@@ -21835,26 +21925,26 @@
     <row r="193" spans="1:65">
       <c r="A193" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B193" t="str">
         <f t="shared" si="7"/>
         <v>19:45</v>
       </c>
       <c r="C193" s="17" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="D193" s="17" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="E193" s="22" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="F193" s="22" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="G193" s="22" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="H193" s="22"/>
       <c r="I193" s="22"/>
@@ -21918,23 +22008,23 @@
     <row r="194" spans="1:65">
       <c r="A194" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B194" t="str">
         <f t="shared" si="7"/>
         <v>19:50</v>
       </c>
       <c r="C194" s="17" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D194" s="17" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="E194" s="22" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="F194" s="22" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="G194" s="22"/>
       <c r="H194" s="22"/>
@@ -21999,23 +22089,23 @@
     <row r="195" spans="1:65">
       <c r="A195" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B195" t="str">
         <f t="shared" si="7"/>
         <v>19:55</v>
       </c>
       <c r="C195" s="17" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="D195" s="17" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="E195" s="22" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="F195" s="22" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="G195" s="22"/>
       <c r="H195" s="22"/>
@@ -22080,27 +22170,27 @@
     <row r="196" spans="1:65">
       <c r="A196" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B196" t="str">
         <f t="shared" si="7"/>
         <v>20:00</v>
       </c>
       <c r="C196" s="17" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="D196" s="17" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="E196" s="22" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="F196" s="22" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="G196" s="22"/>
       <c r="H196" s="22" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="I196" s="22"/>
       <c r="J196" s="22"/>
@@ -22163,21 +22253,21 @@
     <row r="197" spans="1:65">
       <c r="A197" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B197" t="str">
         <f t="shared" si="7"/>
         <v>20:05</v>
       </c>
       <c r="C197" s="17" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D197" s="17" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E197" s="22"/>
       <c r="F197" s="22" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="G197" s="22"/>
       <c r="H197" s="22"/>
@@ -22242,21 +22332,21 @@
     <row r="198" spans="1:65">
       <c r="A198" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B198" t="str">
         <f t="shared" si="7"/>
         <v>20:10</v>
       </c>
       <c r="C198" s="17" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="D198" s="17" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="E198" s="22"/>
       <c r="F198" s="22" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="G198" s="22"/>
       <c r="H198" s="22"/>
@@ -22321,21 +22411,21 @@
     <row r="199" spans="1:65">
       <c r="A199" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B199" t="str">
         <f t="shared" si="7"/>
         <v>20:15</v>
       </c>
       <c r="C199" s="17" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D199" s="17" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="E199" s="22"/>
       <c r="F199" s="22" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="G199" s="22"/>
       <c r="H199" s="22"/>
@@ -22400,21 +22490,21 @@
     <row r="200" spans="1:65">
       <c r="A200" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B200" t="str">
         <f t="shared" si="7"/>
         <v>20:20</v>
       </c>
       <c r="C200" s="17" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D200" s="17" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="E200" s="22"/>
       <c r="F200" s="22" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="G200" s="22"/>
       <c r="H200" s="22"/>
@@ -22479,21 +22569,21 @@
     <row r="201" spans="1:65">
       <c r="A201" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B201" t="str">
         <f t="shared" si="7"/>
         <v>20:25</v>
       </c>
       <c r="C201" s="17" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="D201" s="17" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="E201" s="22"/>
       <c r="F201" s="22" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="G201" s="22"/>
       <c r="H201" s="22"/>
@@ -22558,25 +22648,25 @@
     <row r="202" spans="1:65">
       <c r="A202" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B202" t="str">
         <f t="shared" si="7"/>
         <v>20:30</v>
       </c>
       <c r="C202" s="17" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D202" s="17" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="E202" s="22"/>
       <c r="F202" s="22" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="G202" s="22"/>
       <c r="H202" s="22" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="I202" s="22"/>
       <c r="J202" s="22"/>
@@ -22639,21 +22729,21 @@
     <row r="203" spans="1:65">
       <c r="A203" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B203" t="str">
         <f t="shared" si="7"/>
         <v>20:35</v>
       </c>
       <c r="C203" s="17" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="D203" s="17" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="E203" s="22"/>
       <c r="F203" s="22" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="G203" s="22"/>
       <c r="H203" s="22"/>
@@ -22718,21 +22808,21 @@
     <row r="204" spans="1:65">
       <c r="A204" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B204" t="str">
         <f t="shared" si="7"/>
         <v>20:40</v>
       </c>
       <c r="C204" s="17" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D204" s="17" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="E204" s="22"/>
       <c r="F204" s="22" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="G204" s="22"/>
       <c r="H204" s="22"/>
@@ -22797,21 +22887,21 @@
     <row r="205" spans="1:65">
       <c r="A205" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B205" t="str">
         <f t="shared" si="7"/>
         <v>20:45</v>
       </c>
       <c r="C205" s="17" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="D205" s="17" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="E205" s="22"/>
       <c r="F205" s="22" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="G205" s="22"/>
       <c r="H205" s="22"/>
@@ -22876,21 +22966,21 @@
     <row r="206" spans="1:65">
       <c r="A206" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B206" t="str">
         <f t="shared" si="7"/>
         <v>20:50</v>
       </c>
       <c r="C206" s="17" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="D206" s="17" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="E206" s="22"/>
       <c r="F206" s="22" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="G206" s="22"/>
       <c r="H206" s="22"/>
@@ -22955,21 +23045,21 @@
     <row r="207" spans="1:65">
       <c r="A207" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B207" t="str">
         <f t="shared" si="7"/>
         <v>20:55</v>
       </c>
       <c r="C207" s="17" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="D207" s="17" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="E207" s="22"/>
       <c r="F207" s="22" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="G207" s="22"/>
       <c r="H207" s="22"/>
@@ -23034,25 +23124,25 @@
     <row r="208" spans="1:65">
       <c r="A208" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B208" t="str">
         <f t="shared" si="7"/>
         <v>21:00</v>
       </c>
       <c r="C208" s="17" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D208" s="17" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E208" s="22"/>
       <c r="F208" s="22" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="G208" s="22"/>
       <c r="H208" s="22" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="I208" s="22"/>
       <c r="J208" s="22"/>
@@ -23115,21 +23205,21 @@
     <row r="209" spans="1:65">
       <c r="A209" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B209" t="str">
         <f t="shared" si="7"/>
         <v>21:05</v>
       </c>
       <c r="C209" s="17" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D209" s="17" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E209" s="22"/>
       <c r="F209" s="22" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="G209" s="22"/>
       <c r="H209" s="22"/>
@@ -23194,21 +23284,21 @@
     <row r="210" spans="1:65">
       <c r="A210" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B210" t="str">
         <f t="shared" si="7"/>
         <v>21:10</v>
       </c>
       <c r="C210" s="17" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D210" s="17" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E210" s="22"/>
       <c r="F210" s="22" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="G210" s="22"/>
       <c r="H210" s="22"/>
@@ -23273,25 +23363,25 @@
     <row r="211" spans="1:65">
       <c r="A211" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B211" t="str">
         <f t="shared" si="7"/>
         <v>21:15</v>
       </c>
       <c r="C211" s="17" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="D211" s="17" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E211" s="22"/>
       <c r="F211" s="22" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="G211" s="22"/>
       <c r="H211" s="22" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="I211" s="22"/>
       <c r="J211" s="22"/>
@@ -23354,21 +23444,21 @@
     <row r="212" spans="1:65">
       <c r="A212" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B212" t="str">
         <f t="shared" si="7"/>
         <v>21:20</v>
       </c>
       <c r="C212" s="17" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="D212" s="17" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E212" s="22"/>
       <c r="F212" s="22" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="G212" s="22"/>
       <c r="H212" s="22"/>
@@ -23433,21 +23523,21 @@
     <row r="213" spans="1:65">
       <c r="A213" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B213" t="str">
         <f t="shared" si="7"/>
         <v>21:25</v>
       </c>
       <c r="C213" s="17" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D213" s="17" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E213" s="22"/>
       <c r="F213" s="22" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="G213" s="22"/>
       <c r="H213" s="22"/>
@@ -23512,21 +23602,21 @@
     <row r="214" spans="1:65">
       <c r="A214" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B214" t="str">
         <f t="shared" si="7"/>
         <v>21:30</v>
       </c>
       <c r="C214" s="17" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D214" s="17" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E214" s="22"/>
       <c r="F214" s="22" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="G214" s="22"/>
       <c r="H214" s="22"/>
@@ -23591,21 +23681,21 @@
     <row r="215" spans="1:65">
       <c r="A215" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B215" t="str">
         <f t="shared" si="7"/>
         <v>21:35</v>
       </c>
       <c r="C215" s="17" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D215" s="17" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E215" s="22"/>
       <c r="F215" s="22" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="G215" s="22"/>
       <c r="H215" s="22"/>
@@ -23670,21 +23760,21 @@
     <row r="216" spans="1:65">
       <c r="A216" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B216" t="str">
         <f t="shared" si="7"/>
         <v>21:40</v>
       </c>
       <c r="C216" s="17" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="D216" s="17" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E216" s="22"/>
       <c r="F216" s="22" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="G216" s="22"/>
       <c r="H216" s="22"/>
@@ -23749,21 +23839,21 @@
     <row r="217" spans="1:65">
       <c r="A217" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B217" t="str">
         <f t="shared" si="7"/>
         <v>21:45</v>
       </c>
       <c r="C217" s="17" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="D217" s="17" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E217" s="22"/>
       <c r="F217" s="22" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="G217" s="22"/>
       <c r="H217" s="22"/>
@@ -23828,21 +23918,21 @@
     <row r="218" spans="1:65">
       <c r="A218" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B218" t="str">
         <f t="shared" si="7"/>
         <v>21:50</v>
       </c>
       <c r="C218" s="17" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D218" s="17" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E218" s="22"/>
       <c r="F218" s="22" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="G218" s="22"/>
       <c r="H218" s="22"/>
@@ -23907,21 +23997,21 @@
     <row r="219" spans="1:65">
       <c r="A219" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B219" t="str">
         <f t="shared" si="7"/>
         <v>21:55</v>
       </c>
       <c r="C219" s="17" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D219" s="17" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E219" s="22"/>
       <c r="F219" s="22" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="G219" s="22"/>
       <c r="H219" s="22"/>
@@ -23986,25 +24076,25 @@
     <row r="220" spans="1:65">
       <c r="A220" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B220" t="str">
         <f t="shared" si="7"/>
         <v>22:00</v>
       </c>
       <c r="C220" s="17" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D220" s="17" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="E220" s="22"/>
       <c r="F220" s="22" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="G220" s="22"/>
       <c r="H220" s="22" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="I220" s="22"/>
       <c r="J220" s="22"/>
@@ -24067,21 +24157,21 @@
     <row r="221" spans="1:65">
       <c r="A221" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B221" t="str">
         <f t="shared" si="7"/>
         <v>22:05</v>
       </c>
       <c r="C221" s="17" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="D221" s="17" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="E221" s="22"/>
       <c r="F221" s="22" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="G221" s="22"/>
       <c r="H221" s="22"/>
@@ -24146,21 +24236,21 @@
     <row r="222" spans="1:65">
       <c r="A222" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B222" t="str">
         <f t="shared" si="7"/>
         <v>22:10</v>
       </c>
       <c r="C222" s="17" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D222" s="17" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="E222" s="22"/>
       <c r="F222" s="22" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="G222" s="22"/>
       <c r="H222" s="22"/>
@@ -24225,21 +24315,21 @@
     <row r="223" spans="1:65">
       <c r="A223" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B223" t="str">
         <f t="shared" si="7"/>
         <v>22:15</v>
       </c>
       <c r="C223" s="17" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D223" s="17" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="E223" s="22"/>
       <c r="F223" s="22" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="G223" s="22"/>
       <c r="H223" s="22"/>
@@ -24304,21 +24394,21 @@
     <row r="224" spans="1:65">
       <c r="A224" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B224" t="str">
         <f t="shared" si="7"/>
         <v>22:20</v>
       </c>
       <c r="C224" s="17" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="D224" s="17" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="E224" s="22"/>
       <c r="F224" s="22" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="G224" s="22"/>
       <c r="H224" s="22"/>
@@ -24383,21 +24473,21 @@
     <row r="225" spans="1:65">
       <c r="A225" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B225" t="str">
         <f t="shared" si="7"/>
         <v>22:25</v>
       </c>
       <c r="C225" s="17" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="D225" s="17" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="E225" s="22"/>
       <c r="F225" s="22" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="G225" s="22"/>
       <c r="H225" s="22"/>
@@ -24462,21 +24552,21 @@
     <row r="226" spans="1:65">
       <c r="A226" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B226" t="str">
         <f t="shared" si="7"/>
         <v>22:30</v>
       </c>
       <c r="C226" s="17" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="D226" s="17" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="E226" s="22"/>
       <c r="F226" s="22" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="G226" s="22"/>
       <c r="H226" s="22"/>
@@ -24541,21 +24631,21 @@
     <row r="227" spans="1:65">
       <c r="A227" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B227" t="str">
         <f t="shared" si="7"/>
         <v>22:35</v>
       </c>
       <c r="C227" s="17" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D227" s="17" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="E227" s="22"/>
       <c r="F227" s="22" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="G227" s="22"/>
       <c r="H227" s="22"/>
@@ -24620,21 +24710,21 @@
     <row r="228" spans="1:65">
       <c r="A228" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B228" t="str">
         <f t="shared" si="7"/>
         <v>22:40</v>
       </c>
       <c r="C228" s="17" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D228" s="17" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="E228" s="22"/>
       <c r="F228" s="22" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="G228" s="22"/>
       <c r="H228" s="22"/>
@@ -24699,21 +24789,21 @@
     <row r="229" spans="1:65">
       <c r="A229" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B229" t="str">
         <f t="shared" si="7"/>
         <v>22:45</v>
       </c>
       <c r="C229" s="17" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="D229" s="17" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="E229" s="22"/>
       <c r="F229" s="22" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="G229" s="22"/>
       <c r="H229" s="22"/>
@@ -24778,21 +24868,21 @@
     <row r="230" spans="1:65">
       <c r="A230" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B230" t="str">
         <f t="shared" si="7"/>
         <v>22:50</v>
       </c>
       <c r="C230" s="17" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D230" s="17" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="E230" s="22"/>
       <c r="F230" s="22" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="G230" s="22"/>
       <c r="H230" s="22"/>
@@ -24857,21 +24947,21 @@
     <row r="231" spans="1:65">
       <c r="A231" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B231" t="str">
         <f t="shared" si="7"/>
         <v>22:55</v>
       </c>
       <c r="C231" s="17" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D231" s="17" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="E231" s="22"/>
       <c r="F231" s="22" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="G231" s="22"/>
       <c r="H231" s="22"/>
@@ -24936,21 +25026,21 @@
     <row r="232" spans="1:65">
       <c r="A232" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B232" t="str">
         <f t="shared" si="7"/>
         <v>23:00</v>
       </c>
       <c r="C232" s="17" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="D232" s="17" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="E232" s="22"/>
       <c r="F232" s="22" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="G232" s="22"/>
       <c r="H232" s="22"/>
@@ -25015,21 +25105,21 @@
     <row r="233" spans="1:65">
       <c r="A233" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B233" t="str">
         <f t="shared" si="7"/>
         <v>23:05</v>
       </c>
       <c r="C233" s="17" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="D233" s="17" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="E233" s="22"/>
       <c r="F233" s="22" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="G233" s="22"/>
       <c r="H233" s="22"/>
@@ -25097,21 +25187,21 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B234" t="str">
         <f t="shared" ref="B234:B291" si="9">TEXT($C234, "HH:mm")</f>
         <v>23:10</v>
       </c>
       <c r="C234" s="17" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D234" s="17" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="E234" s="22"/>
       <c r="F234" s="22" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="G234" s="22"/>
       <c r="H234" s="22"/>
@@ -25176,21 +25266,21 @@
     <row r="235" spans="1:65">
       <c r="A235" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B235" t="str">
         <f t="shared" si="9"/>
         <v>23:15</v>
       </c>
       <c r="C235" s="17" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="D235" s="17" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="E235" s="22"/>
       <c r="F235" s="22" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="G235" s="22"/>
       <c r="H235" s="22"/>
@@ -25255,21 +25345,21 @@
     <row r="236" spans="1:65">
       <c r="A236" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B236" t="str">
         <f t="shared" si="9"/>
         <v>23:20</v>
       </c>
       <c r="C236" s="17" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="D236" s="17" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="E236" s="22"/>
       <c r="F236" s="22" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="G236" s="22"/>
       <c r="H236" s="22"/>
@@ -25334,21 +25424,21 @@
     <row r="237" spans="1:65">
       <c r="A237" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B237" t="str">
         <f t="shared" si="9"/>
         <v>23:25</v>
       </c>
       <c r="C237" s="17" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D237" s="17" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="E237" s="22"/>
       <c r="F237" s="22" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="G237" s="22"/>
       <c r="H237" s="22"/>
@@ -25413,21 +25503,21 @@
     <row r="238" spans="1:65">
       <c r="A238" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B238" t="str">
         <f t="shared" si="9"/>
         <v>23:30</v>
       </c>
       <c r="C238" s="17" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="D238" s="17" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="E238" s="22"/>
       <c r="F238" s="22" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="G238" s="22"/>
       <c r="H238" s="22"/>
@@ -25492,21 +25582,21 @@
     <row r="239" spans="1:65">
       <c r="A239" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B239" t="str">
         <f t="shared" si="9"/>
         <v>23:35</v>
       </c>
       <c r="C239" s="17" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="D239" s="17" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="E239" s="22"/>
       <c r="F239" s="22" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="G239" s="22"/>
       <c r="H239" s="22"/>
@@ -25571,21 +25661,21 @@
     <row r="240" spans="1:65">
       <c r="A240" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B240" t="str">
         <f t="shared" si="9"/>
         <v>23:40</v>
       </c>
       <c r="C240" s="17" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="D240" s="17" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="E240" s="22"/>
       <c r="F240" s="22" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="G240" s="22"/>
       <c r="H240" s="22"/>
@@ -25650,21 +25740,21 @@
     <row r="241" spans="1:65">
       <c r="A241" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B241" t="str">
         <f t="shared" si="9"/>
         <v>23:45</v>
       </c>
       <c r="C241" s="17" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="D241" s="17" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="E241" s="22"/>
       <c r="F241" s="22" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="G241" s="22"/>
       <c r="H241" s="22"/>
@@ -25729,21 +25819,21 @@
     <row r="242" spans="1:65">
       <c r="A242" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B242" t="str">
         <f t="shared" si="9"/>
         <v>23:50</v>
       </c>
       <c r="C242" s="17" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="D242" s="17" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="E242" s="22"/>
       <c r="F242" s="22" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="G242" s="22"/>
       <c r="H242" s="22"/>
@@ -25808,21 +25898,21 @@
     <row r="243" spans="1:65">
       <c r="A243" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B243" t="str">
         <f t="shared" si="9"/>
         <v>23:55</v>
       </c>
       <c r="C243" s="17" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="D243" s="17" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="E243" s="22"/>
       <c r="F243" s="22" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="G243" s="22"/>
       <c r="H243" s="22"/>
@@ -25887,21 +25977,21 @@
     <row r="244" spans="1:65">
       <c r="A244" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B244" t="str">
         <f t="shared" si="9"/>
         <v>00:00</v>
       </c>
       <c r="C244" s="17" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="D244" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E244" s="22"/>
       <c r="F244" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G244" s="22"/>
       <c r="H244" s="22"/>
@@ -25966,21 +26056,21 @@
     <row r="245" spans="1:65">
       <c r="A245" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B245" t="str">
         <f t="shared" si="9"/>
         <v>00:05</v>
       </c>
       <c r="C245" s="17" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="D245" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E245" s="22"/>
       <c r="F245" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G245" s="22"/>
       <c r="H245" s="22"/>
@@ -26045,21 +26135,21 @@
     <row r="246" spans="1:65">
       <c r="A246" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B246" t="str">
         <f t="shared" si="9"/>
         <v>00:10</v>
       </c>
       <c r="C246" s="17" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="D246" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E246" s="22"/>
       <c r="F246" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G246" s="22"/>
       <c r="H246" s="22"/>
@@ -26124,21 +26214,21 @@
     <row r="247" spans="1:65">
       <c r="A247" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B247" t="str">
         <f t="shared" si="9"/>
         <v>00:15</v>
       </c>
       <c r="C247" s="17" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="D247" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E247" s="22"/>
       <c r="F247" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G247" s="22"/>
       <c r="H247" s="22"/>
@@ -26203,21 +26293,21 @@
     <row r="248" spans="1:65">
       <c r="A248" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B248" t="str">
         <f t="shared" si="9"/>
         <v>00:20</v>
       </c>
       <c r="C248" s="17" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="D248" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E248" s="22"/>
       <c r="F248" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G248" s="22"/>
       <c r="H248" s="22"/>
@@ -26282,21 +26372,21 @@
     <row r="249" spans="1:65">
       <c r="A249" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B249" t="str">
         <f t="shared" si="9"/>
         <v>00:25</v>
       </c>
       <c r="C249" s="17" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="D249" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E249" s="22"/>
       <c r="F249" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G249" s="22"/>
       <c r="H249" s="22"/>
@@ -26361,21 +26451,21 @@
     <row r="250" spans="1:65">
       <c r="A250" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B250" t="str">
         <f t="shared" si="9"/>
         <v>00:30</v>
       </c>
       <c r="C250" s="17" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="D250" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E250" s="22"/>
       <c r="F250" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G250" s="22"/>
       <c r="H250" s="22"/>
@@ -26440,21 +26530,21 @@
     <row r="251" spans="1:65">
       <c r="A251" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B251" t="str">
         <f t="shared" si="9"/>
         <v>00:35</v>
       </c>
       <c r="C251" s="17" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="D251" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E251" s="22"/>
       <c r="F251" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G251" s="22"/>
       <c r="H251" s="22"/>
@@ -26519,21 +26609,21 @@
     <row r="252" spans="1:65">
       <c r="A252" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B252" t="str">
         <f t="shared" si="9"/>
         <v>00:40</v>
       </c>
       <c r="C252" s="17" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="D252" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E252" s="22"/>
       <c r="F252" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G252" s="22"/>
       <c r="H252" s="22"/>
@@ -26598,21 +26688,21 @@
     <row r="253" spans="1:65">
       <c r="A253" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B253" t="str">
         <f t="shared" si="9"/>
         <v>00:45</v>
       </c>
       <c r="C253" s="17" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="D253" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E253" s="22"/>
       <c r="F253" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G253" s="22"/>
       <c r="H253" s="22"/>
@@ -26677,21 +26767,21 @@
     <row r="254" spans="1:65">
       <c r="A254" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B254" t="str">
         <f t="shared" si="9"/>
         <v>00:50</v>
       </c>
       <c r="C254" s="17" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="D254" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E254" s="22"/>
       <c r="F254" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G254" s="22"/>
       <c r="H254" s="22"/>
@@ -26756,21 +26846,21 @@
     <row r="255" spans="1:65">
       <c r="A255" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B255" t="str">
         <f t="shared" si="9"/>
         <v>00:55</v>
       </c>
       <c r="C255" s="17" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="D255" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E255" s="22"/>
       <c r="F255" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G255" s="22"/>
       <c r="H255" s="22"/>
@@ -26835,21 +26925,21 @@
     <row r="256" spans="1:65">
       <c r="A256" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B256" t="str">
         <f t="shared" si="9"/>
         <v>01:00</v>
       </c>
       <c r="C256" s="17" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D256" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E256" s="22"/>
       <c r="F256" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G256" s="22"/>
       <c r="H256" s="22"/>
@@ -26914,21 +27004,21 @@
     <row r="257" spans="1:65">
       <c r="A257" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B257" t="str">
         <f t="shared" si="9"/>
         <v>01:05</v>
       </c>
       <c r="C257" s="17" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="D257" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E257" s="22"/>
       <c r="F257" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G257" s="22"/>
       <c r="H257" s="22"/>
@@ -26993,21 +27083,21 @@
     <row r="258" spans="1:65">
       <c r="A258" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B258" t="str">
         <f t="shared" si="9"/>
         <v>01:10</v>
       </c>
       <c r="C258" s="17" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="D258" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E258" s="22"/>
       <c r="F258" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G258" s="22"/>
       <c r="H258" s="22"/>
@@ -27072,21 +27162,21 @@
     <row r="259" spans="1:65">
       <c r="A259" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B259" t="str">
         <f t="shared" si="9"/>
         <v>01:15</v>
       </c>
       <c r="C259" s="17" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="D259" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E259" s="22"/>
       <c r="F259" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G259" s="22"/>
       <c r="H259" s="22"/>
@@ -27151,21 +27241,21 @@
     <row r="260" spans="1:65">
       <c r="A260" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B260" t="str">
         <f t="shared" si="9"/>
         <v>01:20</v>
       </c>
       <c r="C260" s="17" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="D260" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E260" s="22"/>
       <c r="F260" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G260" s="22"/>
       <c r="H260" s="22"/>
@@ -27230,21 +27320,21 @@
     <row r="261" spans="1:65">
       <c r="A261" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B261" t="str">
         <f t="shared" si="9"/>
         <v>01:25</v>
       </c>
       <c r="C261" s="17" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="D261" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E261" s="22"/>
       <c r="F261" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G261" s="22"/>
       <c r="H261" s="22"/>
@@ -27309,21 +27399,21 @@
     <row r="262" spans="1:65">
       <c r="A262" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B262" t="str">
         <f t="shared" si="9"/>
         <v>01:30</v>
       </c>
       <c r="C262" s="17" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="D262" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E262" s="22"/>
       <c r="F262" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G262" s="22"/>
       <c r="H262" s="22"/>
@@ -27388,21 +27478,21 @@
     <row r="263" spans="1:65">
       <c r="A263" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B263" t="str">
         <f t="shared" si="9"/>
         <v>01:35</v>
       </c>
       <c r="C263" s="17" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D263" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E263" s="22"/>
       <c r="F263" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G263" s="22"/>
       <c r="H263" s="22"/>
@@ -27467,21 +27557,21 @@
     <row r="264" spans="1:65">
       <c r="A264" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B264" t="str">
         <f t="shared" si="9"/>
         <v>01:40</v>
       </c>
       <c r="C264" s="17" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="D264" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E264" s="22"/>
       <c r="F264" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G264" s="22"/>
       <c r="H264" s="22"/>
@@ -27546,21 +27636,21 @@
     <row r="265" spans="1:65">
       <c r="A265" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B265" t="str">
         <f t="shared" si="9"/>
         <v>01:45</v>
       </c>
       <c r="C265" s="17" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="D265" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E265" s="22"/>
       <c r="F265" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G265" s="22"/>
       <c r="H265" s="22"/>
@@ -27625,21 +27715,21 @@
     <row r="266" spans="1:65">
       <c r="A266" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B266" t="str">
         <f t="shared" si="9"/>
         <v>01:50</v>
       </c>
       <c r="C266" s="17" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="D266" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E266" s="22"/>
       <c r="F266" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G266" s="22"/>
       <c r="H266" s="22"/>
@@ -27704,21 +27794,21 @@
     <row r="267" spans="1:65">
       <c r="A267" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B267" t="str">
         <f t="shared" si="9"/>
         <v>01:55</v>
       </c>
       <c r="C267" s="17" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="D267" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E267" s="22"/>
       <c r="F267" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G267" s="22"/>
       <c r="H267" s="22"/>
@@ -27783,21 +27873,21 @@
     <row r="268" spans="1:65">
       <c r="A268" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B268" t="str">
         <f t="shared" si="9"/>
         <v>02:00</v>
       </c>
       <c r="C268" s="17" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="D268" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E268" s="22"/>
       <c r="F268" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G268" s="22"/>
       <c r="H268" s="22"/>
@@ -27862,21 +27952,21 @@
     <row r="269" spans="1:65">
       <c r="A269" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B269" t="str">
         <f t="shared" si="9"/>
         <v>02:05</v>
       </c>
       <c r="C269" s="17" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="D269" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E269" s="22"/>
       <c r="F269" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G269" s="22"/>
       <c r="H269" s="22"/>
@@ -27941,21 +28031,21 @@
     <row r="270" spans="1:65">
       <c r="A270" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B270" t="str">
         <f t="shared" si="9"/>
         <v>02:10</v>
       </c>
       <c r="C270" s="17" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="D270" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E270" s="22"/>
       <c r="F270" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G270" s="22"/>
       <c r="H270" s="22"/>
@@ -28020,21 +28110,21 @@
     <row r="271" spans="1:65">
       <c r="A271" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B271" t="str">
         <f t="shared" si="9"/>
         <v>02:15</v>
       </c>
       <c r="C271" s="17" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="D271" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E271" s="22"/>
       <c r="F271" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G271" s="22"/>
       <c r="H271" s="22"/>
@@ -28099,21 +28189,21 @@
     <row r="272" spans="1:65">
       <c r="A272" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B272" t="str">
         <f t="shared" si="9"/>
         <v>02:20</v>
       </c>
       <c r="C272" s="17" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="D272" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E272" s="22"/>
       <c r="F272" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G272" s="22"/>
       <c r="H272" s="22"/>
@@ -28178,21 +28268,21 @@
     <row r="273" spans="1:65">
       <c r="A273" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B273" t="str">
         <f t="shared" si="9"/>
         <v>02:25</v>
       </c>
       <c r="C273" s="17" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="D273" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E273" s="22"/>
       <c r="F273" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G273" s="22"/>
       <c r="H273" s="22"/>
@@ -28257,21 +28347,21 @@
     <row r="274" spans="1:65">
       <c r="A274" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B274" t="str">
         <f t="shared" si="9"/>
         <v>02:30</v>
       </c>
       <c r="C274" s="17" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="D274" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E274" s="22"/>
       <c r="F274" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G274" s="22"/>
       <c r="H274" s="22"/>
@@ -28336,21 +28426,21 @@
     <row r="275" spans="1:65">
       <c r="A275" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B275" t="str">
         <f t="shared" si="9"/>
         <v>02:35</v>
       </c>
       <c r="C275" s="17" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="D275" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E275" s="22"/>
       <c r="F275" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G275" s="22"/>
       <c r="H275" s="22"/>
@@ -28415,21 +28505,21 @@
     <row r="276" spans="1:65">
       <c r="A276" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B276" t="str">
         <f t="shared" si="9"/>
         <v>02:40</v>
       </c>
       <c r="C276" s="17" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="D276" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E276" s="22"/>
       <c r="F276" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G276" s="22"/>
       <c r="H276" s="22"/>
@@ -28494,21 +28584,21 @@
     <row r="277" spans="1:65">
       <c r="A277" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B277" t="str">
         <f t="shared" si="9"/>
         <v>02:45</v>
       </c>
       <c r="C277" s="17" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="D277" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E277" s="22"/>
       <c r="F277" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G277" s="22"/>
       <c r="H277" s="22"/>
@@ -28573,21 +28663,21 @@
     <row r="278" spans="1:65">
       <c r="A278" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B278" t="str">
         <f t="shared" si="9"/>
         <v>02:50</v>
       </c>
       <c r="C278" s="17" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="D278" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E278" s="22"/>
       <c r="F278" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G278" s="22"/>
       <c r="H278" s="22"/>
@@ -28652,21 +28742,21 @@
     <row r="279" spans="1:65">
       <c r="A279" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B279" t="str">
         <f t="shared" si="9"/>
         <v>02:55</v>
       </c>
       <c r="C279" s="17" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="D279" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E279" s="22"/>
       <c r="F279" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G279" s="22"/>
       <c r="H279" s="22"/>
@@ -28731,21 +28821,21 @@
     <row r="280" spans="1:65">
       <c r="A280" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B280" t="str">
         <f t="shared" si="9"/>
         <v>03:00</v>
       </c>
       <c r="C280" s="17" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="D280" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E280" s="22"/>
       <c r="F280" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G280" s="22"/>
       <c r="H280" s="22"/>
@@ -28810,21 +28900,21 @@
     <row r="281" spans="1:65">
       <c r="A281" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B281" t="str">
         <f t="shared" si="9"/>
         <v>03:05</v>
       </c>
       <c r="C281" s="17" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D281" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E281" s="22"/>
       <c r="F281" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G281" s="22"/>
       <c r="H281" s="22"/>
@@ -28889,21 +28979,21 @@
     <row r="282" spans="1:65">
       <c r="A282" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B282" t="str">
         <f t="shared" si="9"/>
         <v>03:10</v>
       </c>
       <c r="C282" s="17" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="D282" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E282" s="22"/>
       <c r="F282" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G282" s="22"/>
       <c r="H282" s="22"/>
@@ -28968,21 +29058,21 @@
     <row r="283" spans="1:65">
       <c r="A283" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B283" t="str">
         <f t="shared" si="9"/>
         <v>03:15</v>
       </c>
       <c r="C283" s="17" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="D283" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E283" s="22"/>
       <c r="F283" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G283" s="22"/>
       <c r="H283" s="22"/>
@@ -29047,21 +29137,21 @@
     <row r="284" spans="1:65">
       <c r="A284" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B284" t="str">
         <f t="shared" si="9"/>
         <v>03:20</v>
       </c>
       <c r="C284" s="17" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D284" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E284" s="22"/>
       <c r="F284" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G284" s="22"/>
       <c r="H284" s="22"/>
@@ -29126,21 +29216,21 @@
     <row r="285" spans="1:65">
       <c r="A285" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B285" t="str">
         <f t="shared" si="9"/>
         <v>03:25</v>
       </c>
       <c r="C285" s="17" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="D285" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E285" s="22"/>
       <c r="F285" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G285" s="22"/>
       <c r="H285" s="22"/>
@@ -29205,21 +29295,21 @@
     <row r="286" spans="1:65">
       <c r="A286" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B286" t="str">
         <f t="shared" si="9"/>
         <v>03:30</v>
       </c>
       <c r="C286" s="17" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="D286" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E286" s="22"/>
       <c r="F286" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G286" s="22"/>
       <c r="H286" s="22"/>
@@ -29284,21 +29374,21 @@
     <row r="287" spans="1:65">
       <c r="A287" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B287" t="str">
         <f t="shared" si="9"/>
         <v>03:35</v>
       </c>
       <c r="C287" s="17" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="D287" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E287" s="22"/>
       <c r="F287" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G287" s="22"/>
       <c r="H287" s="22"/>
@@ -29363,21 +29453,21 @@
     <row r="288" spans="1:65">
       <c r="A288" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B288" t="str">
         <f t="shared" si="9"/>
         <v>03:40</v>
       </c>
       <c r="C288" s="17" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="D288" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E288" s="22"/>
       <c r="F288" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G288" s="22"/>
       <c r="H288" s="22"/>
@@ -29442,21 +29532,21 @@
     <row r="289" spans="1:65">
       <c r="A289" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B289" t="str">
         <f t="shared" si="9"/>
         <v>03:45</v>
       </c>
       <c r="C289" s="17" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="D289" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E289" s="22"/>
       <c r="F289" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G289" s="22"/>
       <c r="H289" s="22"/>
@@ -29521,21 +29611,21 @@
     <row r="290" spans="1:65">
       <c r="A290" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B290" t="str">
         <f t="shared" si="9"/>
         <v>03:50</v>
       </c>
       <c r="C290" s="17" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="D290" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E290" s="22"/>
       <c r="F290" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G290" s="22"/>
       <c r="H290" s="22"/>
@@ -29600,17 +29690,17 @@
     <row r="291" spans="1:65">
       <c r="A291" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>13:30</v>
+        <v>08:25</v>
       </c>
       <c r="B291" t="str">
         <f t="shared" si="9"/>
         <v>03:55</v>
       </c>
       <c r="C291" s="17" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="D291" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E291" s="22"/>
       <c r="F291" s="22"/>
@@ -29676,12 +29766,14 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="A1:AG2 A4:AG1048576 A3:BM3">
-    <cfRule type="expression" dxfId="2" priority="4">
+  <conditionalFormatting sqref="A1:AG2 A3:BM3 A4:AG1048576">
+    <cfRule type="expression" dxfId="2" priority="7">
+      <formula>A$3=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A4:AG1048576 A1:AG2 A3:BM3">
+    <cfRule type="expression" dxfId="1" priority="4">
       <formula>TEXT(FLOOR( MOD(NOW(),1), TIME(0,5,0)),"HH:mm")=TEXT($C1,"HH:mm")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="7">
-      <formula>A$3=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:B291">
@@ -29696,12 +29788,12 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63958C87-2C93-43E5-8405-38AB5C73D6BE}">
-  <dimension ref="B3:B7"/>
+  <dimension ref="B3:B13"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <sheetData>
     <row r="3" spans="2:2">
       <c r="B3" s="2" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
     </row>
     <row r="4" spans="2:2" ht="14.25">
@@ -29711,7 +29803,7 @@
     </row>
     <row r="5" spans="2:2" ht="14.25">
       <c r="B5" s="24" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
     </row>
     <row r="6" spans="2:2" ht="14.25">
@@ -29721,7 +29813,37 @@
     </row>
     <row r="7" spans="2:2" ht="14.25">
       <c r="B7" s="24" t="s">
-        <v>652</v>
+        <v>650</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2" ht="14.25">
+      <c r="B8" s="23">
+        <v>8.3333333333333332E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2" ht="14.25">
+      <c r="B9" s="24" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2" ht="14.25">
+      <c r="B10" s="23">
+        <v>1.3194444444444444E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2" ht="14.25">
+      <c r="B11" s="24" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2">
+      <c r="B12" s="25">
+        <v>1.7361111111111112E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2">
+      <c r="B13" t="s">
+        <v>676</v>
       </c>
     </row>
   </sheetData>

--- a/Vite-Vercel開発.xlsx
+++ b/Vite-Vercel開発.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kanta\GitHub\work-time-tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DEDBB40F-9D1E-4009-BC80-61C5DFD6FD50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAAE0499-E5F7-49AA-A217-0AD58A2A3730}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-135" yWindow="-135" windowWidth="29070" windowHeight="15750" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="よく使うこまんど" sheetId="1" r:id="rId1"/>
@@ -19,17 +19,17 @@
     <sheet name="ToDo" sheetId="2" r:id="rId4"/>
     <sheet name="開発ToDo" sheetId="7" r:id="rId5"/>
     <sheet name="プロンプト" sheetId="5" r:id="rId6"/>
-    <sheet name="ChatGPT活動記録" sheetId="13" r:id="rId7"/>
-    <sheet name="活動記録" sheetId="12" r:id="rId8"/>
-    <sheet name="ADHD" sheetId="14" r:id="rId9"/>
-    <sheet name="Sheet6" sheetId="15" r:id="rId10"/>
-    <sheet name="VSCodeExtension" sheetId="6" r:id="rId11"/>
-    <sheet name="開発環境" sheetId="3" r:id="rId12"/>
-    <sheet name="コンポーネント分割案" sheetId="4" r:id="rId13"/>
-    <sheet name="コンポーネント分割" sheetId="10" r:id="rId14"/>
+    <sheet name="エラー修正" sheetId="16" r:id="rId7"/>
+    <sheet name="ChatGPT活動記録" sheetId="13" r:id="rId8"/>
+    <sheet name="活動記録" sheetId="12" r:id="rId9"/>
+    <sheet name="ADHD" sheetId="14" r:id="rId10"/>
+    <sheet name="Sheet6" sheetId="15" r:id="rId11"/>
+    <sheet name="VSCodeExtension" sheetId="6" r:id="rId12"/>
+    <sheet name="開発環境" sheetId="3" r:id="rId13"/>
+    <sheet name="コンポーネント分割案" sheetId="4" r:id="rId14"/>
+    <sheet name="コンポーネント分割" sheetId="10" r:id="rId15"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1273" uniqueCount="679">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1278" uniqueCount="683">
   <si>
     <t>npm install -g vercel</t>
     <phoneticPr fontId="1"/>
@@ -3828,6 +3828,100 @@
     </rPh>
     <rPh sb="938" eb="940">
       <t>ケントウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>src/
+└── core/
+    └── ai/
+        ├── cache/
+        │   ├── AICacheManager.ts（メインファイル）
+        │   ├── CacheKeyGenerator.ts（キャッシュキー生成を分離）
+        │   ├── CacheStorage.ts（ストレージ操作を分離）
+        │   └── types/
+        │       └── CacheTypes.ts（キャッシュ関連の型定義）
+        └── ... (その他のディレクトリ)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>src/
+└── core/
+    └── ai/
+        ├── cache/
+        │   ├── AICacheManager.ts（メインファイル）
+        │   ├── CacheKeyGenerator.ts（キー生成機能）
+        │   ├── CacheStorage.ts（ストレージ操作）
+        │   ├── CachePriorityQueue.ts（優先順位ベースのキャッシュ管理）
+        │   ├── MemoryUsageMonitor.ts（メモリ使用量監視）
+        │   ├── DistributedCacheClient.ts（分散キャッシュ連携）
+        │   ├── CacheMetricsCollector.ts（メトリクス収集）
+        │   └── types/
+        │       └── CacheTypes.ts（型定義）
+        └── ... (その他のディレクトリ)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エラーを修正してください。日本語でお願いします。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>このコンポーネントを改善してください。未実装の部分やモックデータを使用している部分を一つづつでいいので本番用に実装してください。将来的にはこのサイトを世界最高のサイトに改善し、有料でサブスクしたユーザーだけが使用できるサービスとしてリリースしたいです。1ファイルのサイズは200行以内として、超える場合は一部をサブコンポーネントとして切り出したいです。またESLintのエラーや警告が絶対にでないように複数回の検証を繰り返してからコードを提供してください。これまで必ずEsLint指摘がでているのでなんとか改善してください。特に、no-unused-vars、no-explicit-anyのエラーが絶対にでないように複数回の検証を行ってください。命名規則や型定義にも一貫性をもたせてください。ファイルパスやファイル名はコピペできるように出力してください。フォルダー構成についても改善案があれば提示してください。また、開発スケジュールやリリーススケジュールも必ず考慮してください。日本語でお願いします。下記に列挙する企業のサービスを上回るという観点で検討してください。
+Microsoft
+Apple
+Amazon
+Google (Alphabet)
+Salesforce
+NVIDIA
+Adobe
+ServiceNow
+Oracle
+SAP
+Zoom
+Atlassian
+HubSpot
+Workday
+Shopify
+Slack
+OpenAI
+Anthropic
+Stability AI
+Midjourney
+Cohere
+Hugging Face
+Inflection AI
+Runway
+Meta (旧Facebook)
+ByteDance
+X (旧Twitter)
+Tencent
+LinkedIn
+Snapchat (Snap Inc.)
+Pinterest
+Reddit
+Discord
+LINE (Z Holdings)
+Samsung
+Uber
+Spotify
+Grab
+Airbnb
+Match Group
+Bumble
+Indeed (Recruit Holdings)
+TaskRabbit
+Fiverr
+Upwork
+Meetup
+回答が長くなりすぎて途中で切れてしまうようであれば、複数回に分割して出力することも検討してください。</t>
+    <rPh sb="409" eb="411">
+      <t>カイハツ</t>
+    </rPh>
+    <rPh sb="429" eb="430">
+      <t>カナラ</t>
+    </rPh>
+    <rPh sb="431" eb="433">
+      <t>コウリョ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4120,7 +4214,7 @@
                   <a14:compatExt spid="_x0000_s9217"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5BCD94BB-4911-25EC-D070-188CF39A2367}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000001240000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4550,6 +4644,75 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63958C87-2C93-43E5-8405-38AB5C73D6BE}">
+  <dimension ref="B3:B13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetData>
+    <row r="3" spans="2:2">
+      <c r="B3" s="2" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" ht="14.25">
+      <c r="B4" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2" ht="14.25">
+      <c r="B5" s="24" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" ht="14.25">
+      <c r="B6" s="23">
+        <v>4.1666666666666666E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2" ht="14.25">
+      <c r="B7" s="24" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2" ht="14.25">
+      <c r="B8" s="23">
+        <v>8.3333333333333332E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2" ht="14.25">
+      <c r="B9" s="24" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2" ht="14.25">
+      <c r="B10" s="23">
+        <v>1.3194444444444444E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2" ht="14.25">
+      <c r="B11" s="24" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2">
+      <c r="B12" s="25">
+        <v>1.7361111111111112E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2">
+      <c r="B13" t="s">
+        <v>676</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="B3" r:id="rId1" xr:uid="{1592C6E0-7587-42B0-BF1B-3FBFEDF00B08}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{316E5208-1AA2-4457-A1CF-56BEFB0E0D49}">
   <dimension ref="C3"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -4568,7 +4731,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F88E2D65-ECA4-4EF7-BEC6-93BAB5468A01}">
   <dimension ref="B3:C83"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -4902,7 +5065,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C954C604-59FA-4E71-B562-0C51EBE0CA48}">
   <dimension ref="C3:D5"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -4946,7 +5109,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57B697DF-EBFB-495C-BA65-6BC1E0B5AF25}">
   <dimension ref="B3:B52"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -5157,7 +5320,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C6614D2-9BE2-4DBF-BE3B-CC381AB3F591}">
   <dimension ref="B4:D4"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -6316,7 +6479,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6313D91D-4E4E-4302-B673-A8C3F21575BA}">
-  <dimension ref="B3:D35"/>
+  <dimension ref="B3:D39"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
@@ -6525,6 +6688,26 @@
         <v>678</v>
       </c>
     </row>
+    <row r="36" spans="3:4" ht="135">
+      <c r="C36" s="3" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="37" spans="3:4" ht="189">
+      <c r="C37" s="3" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="38" spans="3:4">
+      <c r="C38" s="3" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="39" spans="3:4" ht="409.5">
+      <c r="C39" s="3" t="s">
+        <v>682</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6533,6 +6716,25 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{083174DA-A42C-4F9C-978E-61AEAAD9DDFF}">
+  <dimension ref="C3"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="3" max="3" width="44" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="3:3">
+      <c r="C3" t="s">
+        <v>681</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D23E4F9-E544-431D-8912-173026FA7A6D}">
   <dimension ref="B3:E9"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -6614,7 +6816,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A375A8A-C1C1-4426-AFA3-B95CA8BCFB52}">
   <dimension ref="A2:BM291"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -6690,18 +6892,18 @@
       MOD(NOW(),1),
       TIME(0,5,0)
     ),"HH:mm")</f>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B2" s="19"/>
       <c r="D2" s="1">
         <f ca="1">TODAY()</f>
-        <v>45788</v>
+        <v>45791</v>
       </c>
     </row>
     <row r="3" spans="1:65">
       <c r="A3" s="19" t="str">
         <f ca="1">TEXT(NOW(),"HH:mm")</f>
-        <v>08:26</v>
+        <v>04:55</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="17" t="s">
@@ -6900,7 +7102,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B4" t="str">
         <f t="shared" ref="B4:B67" si="1">TEXT($C4, "HH:mm")</f>
@@ -6979,7 +7181,7 @@
     <row r="5" spans="1:65">
       <c r="A5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B5" t="str">
         <f t="shared" si="1"/>
@@ -7058,7 +7260,7 @@
     <row r="6" spans="1:65">
       <c r="A6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B6" t="str">
         <f t="shared" si="1"/>
@@ -7137,7 +7339,7 @@
     <row r="7" spans="1:65">
       <c r="A7" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B7" t="str">
         <f t="shared" si="1"/>
@@ -7216,7 +7418,7 @@
     <row r="8" spans="1:65">
       <c r="A8" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B8" t="str">
         <f t="shared" si="1"/>
@@ -7295,7 +7497,7 @@
     <row r="9" spans="1:65">
       <c r="A9" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B9" t="str">
         <f t="shared" si="1"/>
@@ -7374,7 +7576,7 @@
     <row r="10" spans="1:65">
       <c r="A10" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B10" t="str">
         <f t="shared" si="1"/>
@@ -7453,7 +7655,7 @@
     <row r="11" spans="1:65">
       <c r="A11" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B11" t="str">
         <f t="shared" si="1"/>
@@ -7532,7 +7734,7 @@
     <row r="12" spans="1:65">
       <c r="A12" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B12" t="str">
         <f t="shared" si="1"/>
@@ -7611,7 +7813,7 @@
     <row r="13" spans="1:65">
       <c r="A13" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B13" t="str">
         <f t="shared" si="1"/>
@@ -7690,7 +7892,7 @@
     <row r="14" spans="1:65">
       <c r="A14" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B14" t="str">
         <f t="shared" si="1"/>
@@ -7769,7 +7971,7 @@
     <row r="15" spans="1:65">
       <c r="A15" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B15" t="str">
         <f t="shared" si="1"/>
@@ -7848,7 +8050,7 @@
     <row r="16" spans="1:65">
       <c r="A16" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B16" t="str">
         <f t="shared" si="1"/>
@@ -7927,7 +8129,7 @@
     <row r="17" spans="1:65">
       <c r="A17" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B17" t="str">
         <f t="shared" si="1"/>
@@ -8006,7 +8208,7 @@
     <row r="18" spans="1:65">
       <c r="A18" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B18" t="str">
         <f t="shared" si="1"/>
@@ -8085,7 +8287,7 @@
     <row r="19" spans="1:65">
       <c r="A19" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B19" t="str">
         <f t="shared" si="1"/>
@@ -8164,7 +8366,7 @@
     <row r="20" spans="1:65">
       <c r="A20" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B20" t="str">
         <f t="shared" si="1"/>
@@ -8243,7 +8445,7 @@
     <row r="21" spans="1:65">
       <c r="A21" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B21" t="str">
         <f t="shared" si="1"/>
@@ -8322,7 +8524,7 @@
     <row r="22" spans="1:65">
       <c r="A22" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B22" t="str">
         <f t="shared" si="1"/>
@@ -8401,7 +8603,7 @@
     <row r="23" spans="1:65">
       <c r="A23" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B23" t="str">
         <f t="shared" si="1"/>
@@ -8480,7 +8682,7 @@
     <row r="24" spans="1:65">
       <c r="A24" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B24" t="str">
         <f t="shared" si="1"/>
@@ -8559,7 +8761,7 @@
     <row r="25" spans="1:65">
       <c r="A25" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B25" t="str">
         <f t="shared" si="1"/>
@@ -8638,7 +8840,7 @@
     <row r="26" spans="1:65">
       <c r="A26" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B26" t="str">
         <f t="shared" si="1"/>
@@ -8717,7 +8919,7 @@
     <row r="27" spans="1:65">
       <c r="A27" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B27" t="str">
         <f t="shared" si="1"/>
@@ -8796,7 +8998,7 @@
     <row r="28" spans="1:65">
       <c r="A28" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B28" t="str">
         <f t="shared" si="1"/>
@@ -8877,7 +9079,7 @@
     <row r="29" spans="1:65">
       <c r="A29" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B29" t="str">
         <f t="shared" si="1"/>
@@ -8958,7 +9160,7 @@
     <row r="30" spans="1:65">
       <c r="A30" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B30" t="str">
         <f t="shared" si="1"/>
@@ -9039,7 +9241,7 @@
     <row r="31" spans="1:65">
       <c r="A31" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B31" t="str">
         <f t="shared" si="1"/>
@@ -9118,7 +9320,7 @@
     <row r="32" spans="1:65">
       <c r="A32" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B32" t="str">
         <f t="shared" si="1"/>
@@ -9197,7 +9399,7 @@
     <row r="33" spans="1:65">
       <c r="A33" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B33" t="str">
         <f t="shared" si="1"/>
@@ -9276,7 +9478,7 @@
     <row r="34" spans="1:65">
       <c r="A34" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B34" t="str">
         <f t="shared" si="1"/>
@@ -9357,7 +9559,7 @@
     <row r="35" spans="1:65">
       <c r="A35" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B35" t="str">
         <f t="shared" si="1"/>
@@ -9438,7 +9640,7 @@
     <row r="36" spans="1:65">
       <c r="A36" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B36" t="str">
         <f t="shared" si="1"/>
@@ -9519,7 +9721,7 @@
     <row r="37" spans="1:65">
       <c r="A37" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B37" t="str">
         <f t="shared" si="1"/>
@@ -9598,7 +9800,7 @@
     <row r="38" spans="1:65">
       <c r="A38" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B38" t="str">
         <f t="shared" si="1"/>
@@ -9677,7 +9879,7 @@
     <row r="39" spans="1:65">
       <c r="A39" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B39" t="str">
         <f t="shared" si="1"/>
@@ -9756,7 +9958,7 @@
     <row r="40" spans="1:65">
       <c r="A40" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B40" t="str">
         <f t="shared" si="1"/>
@@ -9835,7 +10037,7 @@
     <row r="41" spans="1:65">
       <c r="A41" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B41" t="str">
         <f t="shared" si="1"/>
@@ -9914,7 +10116,7 @@
     <row r="42" spans="1:65">
       <c r="A42" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B42" t="str">
         <f t="shared" si="1"/>
@@ -9995,7 +10197,7 @@
     <row r="43" spans="1:65">
       <c r="A43" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B43" t="str">
         <f t="shared" si="1"/>
@@ -10076,7 +10278,7 @@
     <row r="44" spans="1:65">
       <c r="A44" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B44" t="str">
         <f t="shared" si="1"/>
@@ -10155,7 +10357,7 @@
     <row r="45" spans="1:65">
       <c r="A45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B45" t="str">
         <f t="shared" si="1"/>
@@ -10234,7 +10436,7 @@
     <row r="46" spans="1:65">
       <c r="A46" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B46" t="str">
         <f t="shared" si="1"/>
@@ -10313,7 +10515,7 @@
     <row r="47" spans="1:65">
       <c r="A47" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B47" t="str">
         <f t="shared" si="1"/>
@@ -10392,7 +10594,7 @@
     <row r="48" spans="1:65">
       <c r="A48" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B48" t="str">
         <f t="shared" si="1"/>
@@ -10471,7 +10673,7 @@
     <row r="49" spans="1:65">
       <c r="A49" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B49" t="str">
         <f t="shared" si="1"/>
@@ -10552,7 +10754,7 @@
     <row r="50" spans="1:65">
       <c r="A50" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B50" t="str">
         <f t="shared" si="1"/>
@@ -10633,7 +10835,7 @@
     <row r="51" spans="1:65">
       <c r="A51" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B51" t="str">
         <f t="shared" si="1"/>
@@ -10712,7 +10914,7 @@
     <row r="52" spans="1:65">
       <c r="A52" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B52" t="str">
         <f t="shared" si="1"/>
@@ -10791,7 +10993,7 @@
     <row r="53" spans="1:65">
       <c r="A53" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B53" t="str">
         <f t="shared" si="1"/>
@@ -10870,7 +11072,7 @@
     <row r="54" spans="1:65">
       <c r="A54" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B54" t="str">
         <f t="shared" si="1"/>
@@ -10949,7 +11151,7 @@
     <row r="55" spans="1:65">
       <c r="A55" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B55" t="str">
         <f t="shared" si="1"/>
@@ -11028,7 +11230,7 @@
     <row r="56" spans="1:65">
       <c r="A56" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B56" t="str">
         <f t="shared" si="1"/>
@@ -11109,7 +11311,7 @@
     <row r="57" spans="1:65">
       <c r="A57" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B57" t="str">
         <f t="shared" si="1"/>
@@ -11188,7 +11390,7 @@
     <row r="58" spans="1:65">
       <c r="A58" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B58" t="str">
         <f t="shared" si="1"/>
@@ -11269,7 +11471,7 @@
     <row r="59" spans="1:65">
       <c r="A59" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B59" t="str">
         <f t="shared" si="1"/>
@@ -11348,7 +11550,7 @@
     <row r="60" spans="1:65">
       <c r="A60" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B60" t="str">
         <f t="shared" si="1"/>
@@ -11427,7 +11629,7 @@
     <row r="61" spans="1:65">
       <c r="A61" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B61" t="str">
         <f t="shared" si="1"/>
@@ -11506,7 +11708,7 @@
     <row r="62" spans="1:65">
       <c r="A62" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B62" t="str">
         <f t="shared" si="1"/>
@@ -11585,7 +11787,7 @@
     <row r="63" spans="1:65">
       <c r="A63" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B63" t="str">
         <f t="shared" si="1"/>
@@ -11664,7 +11866,7 @@
     <row r="64" spans="1:65">
       <c r="A64" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B64" t="str">
         <f t="shared" si="1"/>
@@ -11745,7 +11947,7 @@
     <row r="65" spans="1:65">
       <c r="A65" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B65" t="str">
         <f t="shared" si="1"/>
@@ -11824,7 +12026,7 @@
     <row r="66" spans="1:65">
       <c r="A66" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B66" t="str">
         <f t="shared" si="1"/>
@@ -11903,7 +12105,7 @@
     <row r="67" spans="1:65">
       <c r="A67" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B67" t="str">
         <f t="shared" si="1"/>
@@ -11985,7 +12187,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B68" t="str">
         <f t="shared" ref="B68:B131" si="3">TEXT($C68, "HH:mm")</f>
@@ -12064,7 +12266,7 @@
     <row r="69" spans="1:65">
       <c r="A69" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B69" t="str">
         <f t="shared" si="3"/>
@@ -12143,7 +12345,7 @@
     <row r="70" spans="1:65">
       <c r="A70" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B70" t="str">
         <f t="shared" si="3"/>
@@ -12222,7 +12424,7 @@
     <row r="71" spans="1:65">
       <c r="A71" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B71" t="str">
         <f t="shared" si="3"/>
@@ -12301,7 +12503,7 @@
     <row r="72" spans="1:65">
       <c r="A72" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B72" t="str">
         <f t="shared" si="3"/>
@@ -12380,7 +12582,7 @@
     <row r="73" spans="1:65">
       <c r="A73" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B73" t="str">
         <f t="shared" si="3"/>
@@ -12459,7 +12661,7 @@
     <row r="74" spans="1:65">
       <c r="A74" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B74" t="str">
         <f t="shared" si="3"/>
@@ -12538,7 +12740,7 @@
     <row r="75" spans="1:65">
       <c r="A75" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B75" t="str">
         <f t="shared" si="3"/>
@@ -12617,7 +12819,7 @@
     <row r="76" spans="1:65">
       <c r="A76" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B76" t="str">
         <f t="shared" si="3"/>
@@ -12696,7 +12898,7 @@
     <row r="77" spans="1:65">
       <c r="A77" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B77" t="str">
         <f t="shared" si="3"/>
@@ -12775,7 +12977,7 @@
     <row r="78" spans="1:65">
       <c r="A78" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B78" t="str">
         <f t="shared" si="3"/>
@@ -12854,7 +13056,7 @@
     <row r="79" spans="1:65">
       <c r="A79" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B79" t="str">
         <f t="shared" si="3"/>
@@ -12933,7 +13135,7 @@
     <row r="80" spans="1:65">
       <c r="A80" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B80" t="str">
         <f t="shared" si="3"/>
@@ -13012,7 +13214,7 @@
     <row r="81" spans="1:65">
       <c r="A81" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B81" t="str">
         <f t="shared" si="3"/>
@@ -13091,7 +13293,7 @@
     <row r="82" spans="1:65">
       <c r="A82" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B82" t="str">
         <f t="shared" si="3"/>
@@ -13170,7 +13372,7 @@
     <row r="83" spans="1:65">
       <c r="A83" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B83" t="str">
         <f t="shared" si="3"/>
@@ -13249,7 +13451,7 @@
     <row r="84" spans="1:65">
       <c r="A84" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B84" t="str">
         <f t="shared" si="3"/>
@@ -13328,7 +13530,7 @@
     <row r="85" spans="1:65">
       <c r="A85" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B85" t="str">
         <f t="shared" si="3"/>
@@ -13407,7 +13609,7 @@
     <row r="86" spans="1:65">
       <c r="A86" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B86" t="str">
         <f t="shared" si="3"/>
@@ -13486,7 +13688,7 @@
     <row r="87" spans="1:65">
       <c r="A87" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B87" t="str">
         <f t="shared" si="3"/>
@@ -13565,7 +13767,7 @@
     <row r="88" spans="1:65">
       <c r="A88" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B88" t="str">
         <f t="shared" si="3"/>
@@ -13644,7 +13846,7 @@
     <row r="89" spans="1:65">
       <c r="A89" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B89" t="str">
         <f t="shared" si="3"/>
@@ -13723,7 +13925,7 @@
     <row r="90" spans="1:65">
       <c r="A90" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B90" t="str">
         <f t="shared" si="3"/>
@@ -13802,7 +14004,7 @@
     <row r="91" spans="1:65">
       <c r="A91" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B91" t="str">
         <f t="shared" si="3"/>
@@ -13881,7 +14083,7 @@
     <row r="92" spans="1:65">
       <c r="A92" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B92" t="str">
         <f t="shared" si="3"/>
@@ -13960,7 +14162,7 @@
     <row r="93" spans="1:65">
       <c r="A93" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B93" t="str">
         <f t="shared" si="3"/>
@@ -14039,7 +14241,7 @@
     <row r="94" spans="1:65">
       <c r="A94" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B94" t="str">
         <f t="shared" si="3"/>
@@ -14118,7 +14320,7 @@
     <row r="95" spans="1:65">
       <c r="A95" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B95" t="str">
         <f t="shared" si="3"/>
@@ -14197,7 +14399,7 @@
     <row r="96" spans="1:65">
       <c r="A96" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B96" t="str">
         <f t="shared" si="3"/>
@@ -14276,7 +14478,7 @@
     <row r="97" spans="1:65">
       <c r="A97" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B97" t="str">
         <f t="shared" si="3"/>
@@ -14355,7 +14557,7 @@
     <row r="98" spans="1:65">
       <c r="A98" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B98" t="str">
         <f t="shared" si="3"/>
@@ -14434,7 +14636,7 @@
     <row r="99" spans="1:65">
       <c r="A99" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B99" t="str">
         <f t="shared" si="3"/>
@@ -14513,7 +14715,7 @@
     <row r="100" spans="1:65">
       <c r="A100" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B100" t="str">
         <f t="shared" si="3"/>
@@ -14594,7 +14796,7 @@
     <row r="101" spans="1:65">
       <c r="A101" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B101" t="str">
         <f t="shared" si="3"/>
@@ -14673,7 +14875,7 @@
     <row r="102" spans="1:65">
       <c r="A102" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B102" t="str">
         <f t="shared" si="3"/>
@@ -14752,7 +14954,7 @@
     <row r="103" spans="1:65">
       <c r="A103" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B103" t="str">
         <f t="shared" si="3"/>
@@ -14831,7 +15033,7 @@
     <row r="104" spans="1:65">
       <c r="A104" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B104" t="str">
         <f t="shared" si="3"/>
@@ -14910,7 +15112,7 @@
     <row r="105" spans="1:65">
       <c r="A105" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B105" t="str">
         <f t="shared" si="3"/>
@@ -14989,7 +15191,7 @@
     <row r="106" spans="1:65">
       <c r="A106" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B106" t="str">
         <f t="shared" si="3"/>
@@ -15070,7 +15272,7 @@
     <row r="107" spans="1:65">
       <c r="A107" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B107" t="str">
         <f t="shared" si="3"/>
@@ -15151,7 +15353,7 @@
     <row r="108" spans="1:65">
       <c r="A108" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B108" t="str">
         <f t="shared" si="3"/>
@@ -15230,7 +15432,7 @@
     <row r="109" spans="1:65">
       <c r="A109" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B109" t="str">
         <f t="shared" si="3"/>
@@ -15309,7 +15511,7 @@
     <row r="110" spans="1:65">
       <c r="A110" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B110" t="str">
         <f t="shared" si="3"/>
@@ -15388,7 +15590,7 @@
     <row r="111" spans="1:65">
       <c r="A111" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B111" t="str">
         <f t="shared" si="3"/>
@@ -15467,7 +15669,7 @@
     <row r="112" spans="1:65">
       <c r="A112" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B112" t="str">
         <f t="shared" si="3"/>
@@ -15548,7 +15750,7 @@
     <row r="113" spans="1:65">
       <c r="A113" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B113" t="str">
         <f t="shared" si="3"/>
@@ -15627,7 +15829,7 @@
     <row r="114" spans="1:65">
       <c r="A114" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B114" t="str">
         <f t="shared" si="3"/>
@@ -15706,7 +15908,7 @@
     <row r="115" spans="1:65">
       <c r="A115" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B115" t="str">
         <f t="shared" si="3"/>
@@ -15785,7 +15987,7 @@
     <row r="116" spans="1:65">
       <c r="A116" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B116" t="str">
         <f t="shared" si="3"/>
@@ -15864,7 +16066,7 @@
     <row r="117" spans="1:65">
       <c r="A117" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B117" t="str">
         <f t="shared" si="3"/>
@@ -15943,7 +16145,7 @@
     <row r="118" spans="1:65">
       <c r="A118" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B118" t="str">
         <f t="shared" si="3"/>
@@ -16022,7 +16224,7 @@
     <row r="119" spans="1:65">
       <c r="A119" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B119" t="str">
         <f t="shared" si="3"/>
@@ -16101,7 +16303,7 @@
     <row r="120" spans="1:65">
       <c r="A120" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B120" t="str">
         <f t="shared" si="3"/>
@@ -16180,7 +16382,7 @@
     <row r="121" spans="1:65">
       <c r="A121" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B121" t="str">
         <f t="shared" si="3"/>
@@ -16259,7 +16461,7 @@
     <row r="122" spans="1:65">
       <c r="A122" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B122" t="str">
         <f t="shared" si="3"/>
@@ -16338,7 +16540,7 @@
     <row r="123" spans="1:65">
       <c r="A123" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B123" t="str">
         <f t="shared" si="3"/>
@@ -16417,7 +16619,7 @@
     <row r="124" spans="1:65">
       <c r="A124" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B124" t="str">
         <f t="shared" si="3"/>
@@ -16498,7 +16700,7 @@
     <row r="125" spans="1:65">
       <c r="A125" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B125" t="str">
         <f t="shared" si="3"/>
@@ -16579,7 +16781,7 @@
     <row r="126" spans="1:65">
       <c r="A126" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B126" t="str">
         <f t="shared" si="3"/>
@@ -16658,7 +16860,7 @@
     <row r="127" spans="1:65">
       <c r="A127" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B127" t="str">
         <f t="shared" si="3"/>
@@ -16737,7 +16939,7 @@
     <row r="128" spans="1:65">
       <c r="A128" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B128" t="str">
         <f t="shared" si="3"/>
@@ -16816,7 +17018,7 @@
     <row r="129" spans="1:65">
       <c r="A129" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B129" t="str">
         <f t="shared" si="3"/>
@@ -16895,7 +17097,7 @@
     <row r="130" spans="1:65">
       <c r="A130" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B130" t="str">
         <f t="shared" si="3"/>
@@ -16974,7 +17176,7 @@
     <row r="131" spans="1:65">
       <c r="A131" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B131" t="str">
         <f t="shared" si="3"/>
@@ -17056,7 +17258,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B132" t="str">
         <f t="shared" ref="B132:B168" si="5">TEXT($C132, "HH:mm")</f>
@@ -17135,7 +17337,7 @@
     <row r="133" spans="1:65">
       <c r="A133" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B133" t="str">
         <f t="shared" si="5"/>
@@ -17214,7 +17416,7 @@
     <row r="134" spans="1:65">
       <c r="A134" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B134" t="str">
         <f t="shared" si="5"/>
@@ -17293,7 +17495,7 @@
     <row r="135" spans="1:65">
       <c r="A135" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B135" t="str">
         <f t="shared" si="5"/>
@@ -17372,7 +17574,7 @@
     <row r="136" spans="1:65">
       <c r="A136" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B136" t="str">
         <f t="shared" si="5"/>
@@ -17453,7 +17655,7 @@
     <row r="137" spans="1:65">
       <c r="A137" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B137" t="str">
         <f t="shared" si="5"/>
@@ -17534,7 +17736,7 @@
     <row r="138" spans="1:65">
       <c r="A138" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B138" t="str">
         <f t="shared" si="5"/>
@@ -17613,7 +17815,7 @@
     <row r="139" spans="1:65">
       <c r="A139" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B139" t="str">
         <f t="shared" si="5"/>
@@ -17692,7 +17894,7 @@
     <row r="140" spans="1:65">
       <c r="A140" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B140" t="str">
         <f t="shared" si="5"/>
@@ -17771,7 +17973,7 @@
     <row r="141" spans="1:65">
       <c r="A141" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B141" t="str">
         <f t="shared" si="5"/>
@@ -17850,7 +18052,7 @@
     <row r="142" spans="1:65">
       <c r="A142" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B142" t="str">
         <f t="shared" si="5"/>
@@ -17929,7 +18131,7 @@
     <row r="143" spans="1:65">
       <c r="A143" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B143" t="str">
         <f t="shared" si="5"/>
@@ -18008,7 +18210,7 @@
     <row r="144" spans="1:65">
       <c r="A144" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B144" t="str">
         <f t="shared" si="5"/>
@@ -18087,7 +18289,7 @@
     <row r="145" spans="1:65">
       <c r="A145" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B145" t="str">
         <f t="shared" si="5"/>
@@ -18166,7 +18368,7 @@
     <row r="146" spans="1:65">
       <c r="A146" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B146" t="str">
         <f t="shared" si="5"/>
@@ -18245,7 +18447,7 @@
     <row r="147" spans="1:65">
       <c r="A147" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B147" t="str">
         <f t="shared" si="5"/>
@@ -18324,7 +18526,7 @@
     <row r="148" spans="1:65">
       <c r="A148" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B148" t="str">
         <f t="shared" si="5"/>
@@ -18405,7 +18607,7 @@
     <row r="149" spans="1:65">
       <c r="A149" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B149" t="str">
         <f t="shared" si="5"/>
@@ -18484,7 +18686,7 @@
     <row r="150" spans="1:65">
       <c r="A150" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B150" t="str">
         <f t="shared" si="5"/>
@@ -18563,7 +18765,7 @@
     <row r="151" spans="1:65">
       <c r="A151" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B151" t="str">
         <f t="shared" si="5"/>
@@ -18642,7 +18844,7 @@
     <row r="152" spans="1:65">
       <c r="A152" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B152" t="str">
         <f t="shared" si="5"/>
@@ -18721,7 +18923,7 @@
     <row r="153" spans="1:65">
       <c r="A153" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B153" t="str">
         <f t="shared" si="5"/>
@@ -18800,7 +19002,7 @@
     <row r="154" spans="1:65">
       <c r="A154" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B154" t="str">
         <f t="shared" si="5"/>
@@ -18879,7 +19081,7 @@
     <row r="155" spans="1:65">
       <c r="A155" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B155" t="str">
         <f t="shared" si="5"/>
@@ -18958,7 +19160,7 @@
     <row r="156" spans="1:65">
       <c r="A156" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B156" t="str">
         <f t="shared" si="5"/>
@@ -19037,7 +19239,7 @@
     <row r="157" spans="1:65">
       <c r="A157" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B157" t="str">
         <f t="shared" si="5"/>
@@ -19116,7 +19318,7 @@
     <row r="158" spans="1:65">
       <c r="A158" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B158" t="str">
         <f t="shared" si="5"/>
@@ -19195,7 +19397,7 @@
     <row r="159" spans="1:65">
       <c r="A159" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B159" t="str">
         <f t="shared" si="5"/>
@@ -19274,7 +19476,7 @@
     <row r="160" spans="1:65">
       <c r="A160" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B160" t="str">
         <f t="shared" si="5"/>
@@ -19353,7 +19555,7 @@
     <row r="161" spans="1:65">
       <c r="A161" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B161" t="str">
         <f t="shared" si="5"/>
@@ -19432,7 +19634,7 @@
     <row r="162" spans="1:65">
       <c r="A162" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B162" t="str">
         <f t="shared" si="5"/>
@@ -19511,7 +19713,7 @@
     <row r="163" spans="1:65">
       <c r="A163" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B163" t="str">
         <f t="shared" si="5"/>
@@ -19590,7 +19792,7 @@
     <row r="164" spans="1:65">
       <c r="A164" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B164" t="str">
         <f t="shared" si="5"/>
@@ -19669,7 +19871,7 @@
     <row r="165" spans="1:65">
       <c r="A165" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B165" t="str">
         <f t="shared" si="5"/>
@@ -19748,7 +19950,7 @@
     <row r="166" spans="1:65">
       <c r="A166" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B166" t="str">
         <f t="shared" si="5"/>
@@ -19829,7 +20031,7 @@
     <row r="167" spans="1:65">
       <c r="A167" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B167" t="str">
         <f t="shared" si="5"/>
@@ -19908,7 +20110,7 @@
     <row r="168" spans="1:65">
       <c r="A168" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B168" t="str">
         <f t="shared" si="5"/>
@@ -19990,7 +20192,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B169" t="str">
         <f>TEXT($C169, "HH:mm")</f>
@@ -20072,7 +20274,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B170" t="str">
         <f t="shared" ref="B170:B233" si="7">TEXT($C170, "HH:mm")</f>
@@ -20151,7 +20353,7 @@
     <row r="171" spans="1:65">
       <c r="A171" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B171" t="str">
         <f t="shared" si="7"/>
@@ -20230,7 +20432,7 @@
     <row r="172" spans="1:65">
       <c r="A172" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B172" t="str">
         <f t="shared" si="7"/>
@@ -20311,7 +20513,7 @@
     <row r="173" spans="1:65">
       <c r="A173" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B173" t="str">
         <f t="shared" si="7"/>
@@ -20390,7 +20592,7 @@
     <row r="174" spans="1:65">
       <c r="A174" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B174" t="str">
         <f t="shared" si="7"/>
@@ -20469,7 +20671,7 @@
     <row r="175" spans="1:65">
       <c r="A175" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B175" t="str">
         <f t="shared" si="7"/>
@@ -20548,7 +20750,7 @@
     <row r="176" spans="1:65">
       <c r="A176" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B176" t="str">
         <f t="shared" si="7"/>
@@ -20627,7 +20829,7 @@
     <row r="177" spans="1:65">
       <c r="A177" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B177" t="str">
         <f t="shared" si="7"/>
@@ -20706,7 +20908,7 @@
     <row r="178" spans="1:65">
       <c r="A178" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B178" t="str">
         <f t="shared" si="7"/>
@@ -20787,7 +20989,7 @@
     <row r="179" spans="1:65">
       <c r="A179" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B179" t="str">
         <f t="shared" si="7"/>
@@ -20866,7 +21068,7 @@
     <row r="180" spans="1:65">
       <c r="A180" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B180" t="str">
         <f t="shared" si="7"/>
@@ -20945,7 +21147,7 @@
     <row r="181" spans="1:65">
       <c r="A181" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B181" t="str">
         <f t="shared" si="7"/>
@@ -21026,7 +21228,7 @@
     <row r="182" spans="1:65">
       <c r="A182" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B182" t="str">
         <f t="shared" si="7"/>
@@ -21107,7 +21309,7 @@
     <row r="183" spans="1:65">
       <c r="A183" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B183" t="str">
         <f t="shared" si="7"/>
@@ -21188,7 +21390,7 @@
     <row r="184" spans="1:65">
       <c r="A184" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B184" t="str">
         <f t="shared" si="7"/>
@@ -21271,7 +21473,7 @@
     <row r="185" spans="1:65">
       <c r="A185" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B185" t="str">
         <f t="shared" si="7"/>
@@ -21352,7 +21554,7 @@
     <row r="186" spans="1:65">
       <c r="A186" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B186" t="str">
         <f t="shared" si="7"/>
@@ -21433,7 +21635,7 @@
     <row r="187" spans="1:65">
       <c r="A187" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B187" t="str">
         <f t="shared" si="7"/>
@@ -21514,7 +21716,7 @@
     <row r="188" spans="1:65">
       <c r="A188" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B188" t="str">
         <f t="shared" si="7"/>
@@ -21595,7 +21797,7 @@
     <row r="189" spans="1:65">
       <c r="A189" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B189" t="str">
         <f t="shared" si="7"/>
@@ -21676,7 +21878,7 @@
     <row r="190" spans="1:65">
       <c r="A190" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B190" t="str">
         <f t="shared" si="7"/>
@@ -21759,7 +21961,7 @@
     <row r="191" spans="1:65">
       <c r="A191" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B191" t="str">
         <f t="shared" si="7"/>
@@ -21842,7 +22044,7 @@
     <row r="192" spans="1:65">
       <c r="A192" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B192" t="str">
         <f t="shared" si="7"/>
@@ -21925,7 +22127,7 @@
     <row r="193" spans="1:65">
       <c r="A193" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B193" t="str">
         <f t="shared" si="7"/>
@@ -22008,7 +22210,7 @@
     <row r="194" spans="1:65">
       <c r="A194" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B194" t="str">
         <f t="shared" si="7"/>
@@ -22089,7 +22291,7 @@
     <row r="195" spans="1:65">
       <c r="A195" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B195" t="str">
         <f t="shared" si="7"/>
@@ -22170,7 +22372,7 @@
     <row r="196" spans="1:65">
       <c r="A196" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B196" t="str">
         <f t="shared" si="7"/>
@@ -22253,7 +22455,7 @@
     <row r="197" spans="1:65">
       <c r="A197" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B197" t="str">
         <f t="shared" si="7"/>
@@ -22332,7 +22534,7 @@
     <row r="198" spans="1:65">
       <c r="A198" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B198" t="str">
         <f t="shared" si="7"/>
@@ -22411,7 +22613,7 @@
     <row r="199" spans="1:65">
       <c r="A199" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B199" t="str">
         <f t="shared" si="7"/>
@@ -22490,7 +22692,7 @@
     <row r="200" spans="1:65">
       <c r="A200" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B200" t="str">
         <f t="shared" si="7"/>
@@ -22569,7 +22771,7 @@
     <row r="201" spans="1:65">
       <c r="A201" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B201" t="str">
         <f t="shared" si="7"/>
@@ -22648,7 +22850,7 @@
     <row r="202" spans="1:65">
       <c r="A202" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B202" t="str">
         <f t="shared" si="7"/>
@@ -22729,7 +22931,7 @@
     <row r="203" spans="1:65">
       <c r="A203" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B203" t="str">
         <f t="shared" si="7"/>
@@ -22808,7 +23010,7 @@
     <row r="204" spans="1:65">
       <c r="A204" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B204" t="str">
         <f t="shared" si="7"/>
@@ -22887,7 +23089,7 @@
     <row r="205" spans="1:65">
       <c r="A205" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B205" t="str">
         <f t="shared" si="7"/>
@@ -22966,7 +23168,7 @@
     <row r="206" spans="1:65">
       <c r="A206" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B206" t="str">
         <f t="shared" si="7"/>
@@ -23045,7 +23247,7 @@
     <row r="207" spans="1:65">
       <c r="A207" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B207" t="str">
         <f t="shared" si="7"/>
@@ -23124,7 +23326,7 @@
     <row r="208" spans="1:65">
       <c r="A208" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B208" t="str">
         <f t="shared" si="7"/>
@@ -23205,7 +23407,7 @@
     <row r="209" spans="1:65">
       <c r="A209" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B209" t="str">
         <f t="shared" si="7"/>
@@ -23284,7 +23486,7 @@
     <row r="210" spans="1:65">
       <c r="A210" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B210" t="str">
         <f t="shared" si="7"/>
@@ -23363,7 +23565,7 @@
     <row r="211" spans="1:65">
       <c r="A211" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B211" t="str">
         <f t="shared" si="7"/>
@@ -23444,7 +23646,7 @@
     <row r="212" spans="1:65">
       <c r="A212" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B212" t="str">
         <f t="shared" si="7"/>
@@ -23523,7 +23725,7 @@
     <row r="213" spans="1:65">
       <c r="A213" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B213" t="str">
         <f t="shared" si="7"/>
@@ -23602,7 +23804,7 @@
     <row r="214" spans="1:65">
       <c r="A214" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B214" t="str">
         <f t="shared" si="7"/>
@@ -23681,7 +23883,7 @@
     <row r="215" spans="1:65">
       <c r="A215" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B215" t="str">
         <f t="shared" si="7"/>
@@ -23760,7 +23962,7 @@
     <row r="216" spans="1:65">
       <c r="A216" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B216" t="str">
         <f t="shared" si="7"/>
@@ -23839,7 +24041,7 @@
     <row r="217" spans="1:65">
       <c r="A217" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B217" t="str">
         <f t="shared" si="7"/>
@@ -23918,7 +24120,7 @@
     <row r="218" spans="1:65">
       <c r="A218" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B218" t="str">
         <f t="shared" si="7"/>
@@ -23997,7 +24199,7 @@
     <row r="219" spans="1:65">
       <c r="A219" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B219" t="str">
         <f t="shared" si="7"/>
@@ -24076,7 +24278,7 @@
     <row r="220" spans="1:65">
       <c r="A220" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B220" t="str">
         <f t="shared" si="7"/>
@@ -24157,7 +24359,7 @@
     <row r="221" spans="1:65">
       <c r="A221" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B221" t="str">
         <f t="shared" si="7"/>
@@ -24236,7 +24438,7 @@
     <row r="222" spans="1:65">
       <c r="A222" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B222" t="str">
         <f t="shared" si="7"/>
@@ -24315,7 +24517,7 @@
     <row r="223" spans="1:65">
       <c r="A223" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B223" t="str">
         <f t="shared" si="7"/>
@@ -24394,7 +24596,7 @@
     <row r="224" spans="1:65">
       <c r="A224" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B224" t="str">
         <f t="shared" si="7"/>
@@ -24473,7 +24675,7 @@
     <row r="225" spans="1:65">
       <c r="A225" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B225" t="str">
         <f t="shared" si="7"/>
@@ -24552,7 +24754,7 @@
     <row r="226" spans="1:65">
       <c r="A226" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B226" t="str">
         <f t="shared" si="7"/>
@@ -24631,7 +24833,7 @@
     <row r="227" spans="1:65">
       <c r="A227" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B227" t="str">
         <f t="shared" si="7"/>
@@ -24710,7 +24912,7 @@
     <row r="228" spans="1:65">
       <c r="A228" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B228" t="str">
         <f t="shared" si="7"/>
@@ -24789,7 +24991,7 @@
     <row r="229" spans="1:65">
       <c r="A229" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B229" t="str">
         <f t="shared" si="7"/>
@@ -24868,7 +25070,7 @@
     <row r="230" spans="1:65">
       <c r="A230" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B230" t="str">
         <f t="shared" si="7"/>
@@ -24947,7 +25149,7 @@
     <row r="231" spans="1:65">
       <c r="A231" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B231" t="str">
         <f t="shared" si="7"/>
@@ -25026,7 +25228,7 @@
     <row r="232" spans="1:65">
       <c r="A232" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B232" t="str">
         <f t="shared" si="7"/>
@@ -25105,7 +25307,7 @@
     <row r="233" spans="1:65">
       <c r="A233" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B233" t="str">
         <f t="shared" si="7"/>
@@ -25187,7 +25389,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B234" t="str">
         <f t="shared" ref="B234:B291" si="9">TEXT($C234, "HH:mm")</f>
@@ -25266,7 +25468,7 @@
     <row r="235" spans="1:65">
       <c r="A235" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B235" t="str">
         <f t="shared" si="9"/>
@@ -25345,7 +25547,7 @@
     <row r="236" spans="1:65">
       <c r="A236" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B236" t="str">
         <f t="shared" si="9"/>
@@ -25424,7 +25626,7 @@
     <row r="237" spans="1:65">
       <c r="A237" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B237" t="str">
         <f t="shared" si="9"/>
@@ -25503,7 +25705,7 @@
     <row r="238" spans="1:65">
       <c r="A238" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B238" t="str">
         <f t="shared" si="9"/>
@@ -25582,7 +25784,7 @@
     <row r="239" spans="1:65">
       <c r="A239" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B239" t="str">
         <f t="shared" si="9"/>
@@ -25661,7 +25863,7 @@
     <row r="240" spans="1:65">
       <c r="A240" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B240" t="str">
         <f t="shared" si="9"/>
@@ -25740,7 +25942,7 @@
     <row r="241" spans="1:65">
       <c r="A241" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B241" t="str">
         <f t="shared" si="9"/>
@@ -25819,7 +26021,7 @@
     <row r="242" spans="1:65">
       <c r="A242" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B242" t="str">
         <f t="shared" si="9"/>
@@ -25898,7 +26100,7 @@
     <row r="243" spans="1:65">
       <c r="A243" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B243" t="str">
         <f t="shared" si="9"/>
@@ -25977,7 +26179,7 @@
     <row r="244" spans="1:65">
       <c r="A244" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B244" t="str">
         <f t="shared" si="9"/>
@@ -26056,7 +26258,7 @@
     <row r="245" spans="1:65">
       <c r="A245" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B245" t="str">
         <f t="shared" si="9"/>
@@ -26135,7 +26337,7 @@
     <row r="246" spans="1:65">
       <c r="A246" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B246" t="str">
         <f t="shared" si="9"/>
@@ -26214,7 +26416,7 @@
     <row r="247" spans="1:65">
       <c r="A247" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B247" t="str">
         <f t="shared" si="9"/>
@@ -26293,7 +26495,7 @@
     <row r="248" spans="1:65">
       <c r="A248" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B248" t="str">
         <f t="shared" si="9"/>
@@ -26372,7 +26574,7 @@
     <row r="249" spans="1:65">
       <c r="A249" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B249" t="str">
         <f t="shared" si="9"/>
@@ -26451,7 +26653,7 @@
     <row r="250" spans="1:65">
       <c r="A250" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B250" t="str">
         <f t="shared" si="9"/>
@@ -26530,7 +26732,7 @@
     <row r="251" spans="1:65">
       <c r="A251" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B251" t="str">
         <f t="shared" si="9"/>
@@ -26609,7 +26811,7 @@
     <row r="252" spans="1:65">
       <c r="A252" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B252" t="str">
         <f t="shared" si="9"/>
@@ -26688,7 +26890,7 @@
     <row r="253" spans="1:65">
       <c r="A253" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B253" t="str">
         <f t="shared" si="9"/>
@@ -26767,7 +26969,7 @@
     <row r="254" spans="1:65">
       <c r="A254" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B254" t="str">
         <f t="shared" si="9"/>
@@ -26846,7 +27048,7 @@
     <row r="255" spans="1:65">
       <c r="A255" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B255" t="str">
         <f t="shared" si="9"/>
@@ -26925,7 +27127,7 @@
     <row r="256" spans="1:65">
       <c r="A256" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B256" t="str">
         <f t="shared" si="9"/>
@@ -27004,7 +27206,7 @@
     <row r="257" spans="1:65">
       <c r="A257" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B257" t="str">
         <f t="shared" si="9"/>
@@ -27083,7 +27285,7 @@
     <row r="258" spans="1:65">
       <c r="A258" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B258" t="str">
         <f t="shared" si="9"/>
@@ -27162,7 +27364,7 @@
     <row r="259" spans="1:65">
       <c r="A259" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B259" t="str">
         <f t="shared" si="9"/>
@@ -27241,7 +27443,7 @@
     <row r="260" spans="1:65">
       <c r="A260" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B260" t="str">
         <f t="shared" si="9"/>
@@ -27320,7 +27522,7 @@
     <row r="261" spans="1:65">
       <c r="A261" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B261" t="str">
         <f t="shared" si="9"/>
@@ -27399,7 +27601,7 @@
     <row r="262" spans="1:65">
       <c r="A262" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B262" t="str">
         <f t="shared" si="9"/>
@@ -27478,7 +27680,7 @@
     <row r="263" spans="1:65">
       <c r="A263" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B263" t="str">
         <f t="shared" si="9"/>
@@ -27557,7 +27759,7 @@
     <row r="264" spans="1:65">
       <c r="A264" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B264" t="str">
         <f t="shared" si="9"/>
@@ -27636,7 +27838,7 @@
     <row r="265" spans="1:65">
       <c r="A265" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B265" t="str">
         <f t="shared" si="9"/>
@@ -27715,7 +27917,7 @@
     <row r="266" spans="1:65">
       <c r="A266" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B266" t="str">
         <f t="shared" si="9"/>
@@ -27794,7 +27996,7 @@
     <row r="267" spans="1:65">
       <c r="A267" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B267" t="str">
         <f t="shared" si="9"/>
@@ -27873,7 +28075,7 @@
     <row r="268" spans="1:65">
       <c r="A268" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B268" t="str">
         <f t="shared" si="9"/>
@@ -27952,7 +28154,7 @@
     <row r="269" spans="1:65">
       <c r="A269" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B269" t="str">
         <f t="shared" si="9"/>
@@ -28031,7 +28233,7 @@
     <row r="270" spans="1:65">
       <c r="A270" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B270" t="str">
         <f t="shared" si="9"/>
@@ -28110,7 +28312,7 @@
     <row r="271" spans="1:65">
       <c r="A271" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B271" t="str">
         <f t="shared" si="9"/>
@@ -28189,7 +28391,7 @@
     <row r="272" spans="1:65">
       <c r="A272" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B272" t="str">
         <f t="shared" si="9"/>
@@ -28268,7 +28470,7 @@
     <row r="273" spans="1:65">
       <c r="A273" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B273" t="str">
         <f t="shared" si="9"/>
@@ -28347,7 +28549,7 @@
     <row r="274" spans="1:65">
       <c r="A274" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B274" t="str">
         <f t="shared" si="9"/>
@@ -28426,7 +28628,7 @@
     <row r="275" spans="1:65">
       <c r="A275" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B275" t="str">
         <f t="shared" si="9"/>
@@ -28505,7 +28707,7 @@
     <row r="276" spans="1:65">
       <c r="A276" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B276" t="str">
         <f t="shared" si="9"/>
@@ -28584,7 +28786,7 @@
     <row r="277" spans="1:65">
       <c r="A277" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B277" t="str">
         <f t="shared" si="9"/>
@@ -28663,7 +28865,7 @@
     <row r="278" spans="1:65">
       <c r="A278" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B278" t="str">
         <f t="shared" si="9"/>
@@ -28742,7 +28944,7 @@
     <row r="279" spans="1:65">
       <c r="A279" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B279" t="str">
         <f t="shared" si="9"/>
@@ -28821,7 +29023,7 @@
     <row r="280" spans="1:65">
       <c r="A280" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B280" t="str">
         <f t="shared" si="9"/>
@@ -28900,7 +29102,7 @@
     <row r="281" spans="1:65">
       <c r="A281" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B281" t="str">
         <f t="shared" si="9"/>
@@ -28979,7 +29181,7 @@
     <row r="282" spans="1:65">
       <c r="A282" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B282" t="str">
         <f t="shared" si="9"/>
@@ -29058,7 +29260,7 @@
     <row r="283" spans="1:65">
       <c r="A283" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B283" t="str">
         <f t="shared" si="9"/>
@@ -29137,7 +29339,7 @@
     <row r="284" spans="1:65">
       <c r="A284" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B284" t="str">
         <f t="shared" si="9"/>
@@ -29216,7 +29418,7 @@
     <row r="285" spans="1:65">
       <c r="A285" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B285" t="str">
         <f t="shared" si="9"/>
@@ -29295,7 +29497,7 @@
     <row r="286" spans="1:65">
       <c r="A286" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B286" t="str">
         <f t="shared" si="9"/>
@@ -29374,7 +29576,7 @@
     <row r="287" spans="1:65">
       <c r="A287" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B287" t="str">
         <f t="shared" si="9"/>
@@ -29453,7 +29655,7 @@
     <row r="288" spans="1:65">
       <c r="A288" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B288" t="str">
         <f t="shared" si="9"/>
@@ -29532,7 +29734,7 @@
     <row r="289" spans="1:65">
       <c r="A289" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B289" t="str">
         <f t="shared" si="9"/>
@@ -29611,7 +29813,7 @@
     <row r="290" spans="1:65">
       <c r="A290" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B290" t="str">
         <f t="shared" si="9"/>
@@ -29690,7 +29892,7 @@
     <row r="291" spans="1:65">
       <c r="A291" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>08:25</v>
+        <v>04:55</v>
       </c>
       <c r="B291" t="str">
         <f t="shared" si="9"/>
@@ -29784,73 +29986,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63958C87-2C93-43E5-8405-38AB5C73D6BE}">
-  <dimension ref="B3:B13"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
-  <sheetData>
-    <row r="3" spans="2:2">
-      <c r="B3" s="2" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="4" spans="2:2" ht="14.25">
-      <c r="B4" s="23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="2:2" ht="14.25">
-      <c r="B5" s="24" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="6" spans="2:2" ht="14.25">
-      <c r="B6" s="23">
-        <v>4.1666666666666666E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="2:2" ht="14.25">
-      <c r="B7" s="24" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="8" spans="2:2" ht="14.25">
-      <c r="B8" s="23">
-        <v>8.3333333333333332E-3</v>
-      </c>
-    </row>
-    <row r="9" spans="2:2" ht="14.25">
-      <c r="B9" s="24" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="10" spans="2:2" ht="14.25">
-      <c r="B10" s="23">
-        <v>1.3194444444444444E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="2:2" ht="14.25">
-      <c r="B11" s="24" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="12" spans="2:2">
-      <c r="B12" s="25">
-        <v>1.7361111111111112E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="2:2">
-      <c r="B13" t="s">
-        <v>676</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <hyperlinks>
-    <hyperlink ref="B3" r:id="rId1" xr:uid="{1592C6E0-7587-42B0-BF1B-3FBFEDF00B08}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Vite-Vercel開発.xlsx
+++ b/Vite-Vercel開発.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kanta\GitHub\work-time-tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAAE0499-E5F7-49AA-A217-0AD58A2A3730}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B380C323-14B8-42CD-8580-F5275C2F97F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-135" yWindow="-135" windowWidth="29070" windowHeight="15750" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="よく使うこまんど" sheetId="1" r:id="rId1"/>
@@ -19,15 +19,19 @@
     <sheet name="ToDo" sheetId="2" r:id="rId4"/>
     <sheet name="開発ToDo" sheetId="7" r:id="rId5"/>
     <sheet name="プロンプト" sheetId="5" r:id="rId6"/>
-    <sheet name="エラー修正" sheetId="16" r:id="rId7"/>
-    <sheet name="ChatGPT活動記録" sheetId="13" r:id="rId8"/>
-    <sheet name="活動記録" sheetId="12" r:id="rId9"/>
-    <sheet name="ADHD" sheetId="14" r:id="rId10"/>
-    <sheet name="Sheet6" sheetId="15" r:id="rId11"/>
-    <sheet name="VSCodeExtension" sheetId="6" r:id="rId12"/>
-    <sheet name="開発環境" sheetId="3" r:id="rId13"/>
-    <sheet name="コンポーネント分割案" sheetId="4" r:id="rId14"/>
-    <sheet name="コンポーネント分割" sheetId="10" r:id="rId15"/>
+    <sheet name="Cursor" sheetId="20" r:id="rId7"/>
+    <sheet name="AI-CICD" sheetId="19" r:id="rId8"/>
+    <sheet name="コンポーネント改善" sheetId="17" r:id="rId9"/>
+    <sheet name="エラー修正" sheetId="16" r:id="rId10"/>
+    <sheet name="ChatGPT活動記録" sheetId="13" r:id="rId11"/>
+    <sheet name="活動記録" sheetId="12" r:id="rId12"/>
+    <sheet name="ADHD" sheetId="14" r:id="rId13"/>
+    <sheet name="メモ管理" sheetId="15" r:id="rId14"/>
+    <sheet name="Claude" sheetId="18" r:id="rId15"/>
+    <sheet name="VSCodeExtension" sheetId="6" r:id="rId16"/>
+    <sheet name="開発環境" sheetId="3" r:id="rId17"/>
+    <sheet name="コンポーネント分割案" sheetId="4" r:id="rId18"/>
+    <sheet name="コンポーネント分割" sheetId="10" r:id="rId19"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1278" uniqueCount="683">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1525" uniqueCount="903">
   <si>
     <t>npm install -g vercel</t>
     <phoneticPr fontId="1"/>
@@ -3925,12 +3929,1375 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>src\components\dailyToDoReminder\controls\TodoViewControls.tsx</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>src\components\dailyToDoReminder\DailyTodoReminder.tsx</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>使用箇所</t>
+    <rPh sb="0" eb="4">
+      <t>シヨウカショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>src\components\dailyToDoReminder\todo\TodoFilters.tsx</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>src\components\dailyToDoReminder\InviteFriendsComponent.tsx</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>src\components\dailyToDoReminder\todo\TodoItem.tsx</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>src\components\dailyToDoReminder\todo\TodoList.tsx</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>src\components\EventModal.tsx</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>src\components\dailyToDoReminder\components\TodoHeader.tsx</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://github.com/umezawakanta/work-time-tracker
+このサイトを改善してください。未実装の部分やモックデータを使用している部分を一つづつでいいので本番用に実装してください。将来的にはこのサイトを世界最高のサイトに改善し、有料でサブスクしたユーザーだけが使用できるサービスとしてリリースしたいです。1ファイルのサイズは200行以内として、超える場合は一部をサブコンポーネントとして切り出したいです。またESLintのエラーや警告が絶対にでないように複数回の検証を繰り返してからコードを提供してください。これまで必ずEsLint指摘がでているのでなんとか改善してください。特に、no-unused-vars、no-explicit-anyのエラーが絶対にでないように複数回の検証を行ってください。命名規則や型定義にも一貫性をもたせてください。ファイルパスやファイル名はコピペできるように出力してください。フォルダー構成についても改善案があれば提示してください。また、開発スケジュールやリリーススケジュールも必ず考慮してください。また、このサイト自体の開発スケジュールをWBSとしてサイト上で表示できるようにしたいです。日本語でお願いします。下記に列挙する企業のサービスを上回るという観点で検討してください。
+Microsoft
+Apple
+Amazon
+Google (Alphabet)
+Salesforce
+NVIDIA
+Adobe
+ServiceNow
+Oracle
+SAP
+Zoom
+Atlassian
+HubSpot
+Workday
+Shopify
+Slack
+OpenAI
+Anthropic
+Stability AI
+Midjourney
+Cohere
+Hugging Face
+Inflection AI
+Runway
+Meta (旧Facebook)
+ByteDance
+X (旧Twitter)
+Tencent
+LinkedIn
+Snapchat (Snap Inc.)
+Pinterest
+Reddit
+Discord
+LINE (Z Holdings)
+Samsung
+Uber
+Spotify
+Grab
+Airbnb
+Match Group
+Bumble
+Indeed (Recruit Holdings)
+TaskRabbit
+Fiverr
+Upwork
+Meetup
+回答が長くなりすぎて途中で切れてしまうようであれば、複数回に分割して出力することも検討してください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ローカル開発環境のセットアップ</t>
+  </si>
+  <si>
+    <t>1. pnpmで依存関係をインストール</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t># 現在のディレクトリで
+cd C:\Users\kanta\OneDrive\work\GitHub\work-time-tracker</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>理解</t>
+    <rPh sb="0" eb="2">
+      <t>リカイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>実行</t>
+    <rPh sb="0" eb="2">
+      <t>ジッコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t># クリーンインストール
+Remove-Item node_modules -Recurse -Force -ErrorAction SilentlyContinue</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4. クリーンインストール</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Git リモートリポジトリの設定</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t># Gitリポジトリの状態確認
+git status</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t># リモートリポジトリの確認
+git remote -v</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2. Gitリポジトリの初期化と接続</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t># もしGitリポジトリでない場合
+git init</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t># リモートリポジトリを追加
+git remote add origin https://github.com/umezawakanta/work-time-tracker.git</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t># 確認
+git remote -v</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3. 既存のコードをGitHubにプッシュ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t># 現在のブランチ名を確認
+git branch</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>5. プロジェクトのNode.js要件を更新</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Start-Process "https://github.com/umezawakanta/work-time-tracker"</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t># Cursorでプロジェクトを開く
+cursor .</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t># 自動修正可能なエラーを修正
+pnpm run lint:fix</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t># eslint.config.jsの内容を確認
+Get-Content eslint.config.js</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t># バックアップを作成
+Copy-Item eslint.config.js eslint.config.js.bak</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t># 古い設定ファイルを削除
+Remove-Item .eslintrc.js -ErrorAction SilentlyContinue</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t># キャッシュをクリア
+Remove-Item .eslintcache -ErrorAction SilentlyContinue</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t># scriptsフォルダを作成
+New-Item -ItemType Directory -Path scripts -Force</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Google DriveとCursorとClaude Opus4でAI-CICDフローを確立してください。
+https://github.com/umezawakanta/work-time-tracker</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ChatGPT</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>以下の手順で、Google Drive をアーティファクト保存先とし、Cursor と Claude Opus 4 を AI アシスタントとして組み込んだ CI/CD ワークフローを GitHub Actions 上に構築できます。</t>
+  </si>
+  <si>
+    <t>1. 概要</t>
+  </si>
+  <si>
+    <t>1. 開発者ローカル</t>
+  </si>
+  <si>
+    <t>Cursor: コード補完・リファクタリング支援</t>
+  </si>
+  <si>
+    <t>2. GitHub Actions</t>
+  </si>
+  <si>
+    <t>ビルド→テスト</t>
+  </si>
+  <si>
+    <t>Claude Opus 4 で追加テスト生成・コードレビュー</t>
+  </si>
+  <si>
+    <t>Cursor CLI でドキュメント生成</t>
+  </si>
+  <si>
+    <t>成果物（テストレポート・カバレッジなど）を Google Drive にアップロード</t>
+  </si>
+  <si>
+    <t>3. デプロイ</t>
+  </si>
+  <si>
+    <t>（例）Vercel や Firebase Hosting などへの自動デプロイ</t>
+  </si>
+  <si>
+    <t>2. 前提条件</t>
+  </si>
+  <si>
+    <t>1. Google Drive API</t>
+  </si>
+  <si>
+    <t>GCP コンソールで Drive API を有効化</t>
+  </si>
+  <si>
+    <t>サービスアカウント or OAuth クライアントを作成し、アクセストークンを取得</t>
+  </si>
+  <si>
+    <t>アップロード先フォルダ ID を控える</t>
+  </si>
+  <si>
+    <t>2. Claude Opus 4 API</t>
+  </si>
+  <si>
+    <t>Anthropic コンソールで API キー取得</t>
+  </si>
+  <si>
+    <t>3. Cursor CLI</t>
+  </si>
+  <si>
+    <r>
+      <t>npm / Homebrew などでインストール (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>npm install -g @cursor.dev/cli</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 等)</t>
+    </r>
+  </si>
+  <si>
+    <t>API キーを取得</t>
+  </si>
+  <si>
+    <t>4. GitHub リポジトリの Secrets</t>
+  </si>
+  <si>
+    <r>
+      <t>GDRIVE_CREDENTIALS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（JSON 文字列）</t>
+    </r>
+  </si>
+  <si>
+    <t>GDRIVE_FOLDER_ID</t>
+  </si>
+  <si>
+    <t>CLAUDE_API_KEY</t>
+  </si>
+  <si>
+    <t>CURSOR_API_KEY</t>
+  </si>
+  <si>
+    <t>3. GitHub Actions ワークフロー例</t>
+  </si>
+  <si>
+    <r>
+      <t>.github/workflows/ai-cicd.yml</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> を以下のように作成します。</t>
+    </r>
+  </si>
+  <si>
+    <t>name: AI-CICD</t>
+  </si>
+  <si>
+    <t>on:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  push:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    branches: [ main ]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  pull_request:</t>
+  </si>
+  <si>
+    <t>jobs:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ai-cicd:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    runs-on: ubuntu-latest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    steps:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      # 1) コード取得と Node.js 準備</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      - uses: actions/checkout@v3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      - uses: actions/setup-node@v3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        with:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">          node-version: '18'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      - run: |</t>
+  </si>
+  <si>
+    <t xml:space="preserve">          pnpm install</t>
+  </si>
+  <si>
+    <t xml:space="preserve">          pnpm build</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      # 2) 通常テスト実行</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      - name: Run tests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        run: pnpm test -- --coverage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      # 3) Claude Opus 4 による追加テスト生成</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      - name: Generate tests with Claude Opus4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        env:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">          ANTHROPIC_API_KEY: ${{ secrets.CLAUDE_API_KEY }}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        run: |</t>
+  </si>
+  <si>
+    <t xml:space="preserve">          curl https://api.anthropic.com/v1/complete \</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            -H "x-api-key: $ANTHROPIC_API_KEY" \</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            -H "Content-Type: application/json" \</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            -d '{</t>
+  </si>
+  <si>
+    <t xml:space="preserve">              "model":"claude-ops-4",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">              "prompt":"以下の差分に対してユニットテストを生成してください：\n'$(git diff origin/main --name-only)'\n出力はJavaScriptで。"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            }' \</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            &gt; ai-generated-tests.js</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      - name: Run AI-generated tests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        run: node ai-generated-tests.js</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      # 4) Cursor CLI によるドキュメント生成</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      - name: Generate docs with Cursor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">          CURSOR_API_KEY: ${{ secrets.CURSOR_API_KEY }}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">          cursor docgen --source src/ --out docs/AI_DOCS.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      # 5) テストレポートを Google Drive にアップロード</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      - name: Upload coverage report to Google Drive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        uses: google-github-actions/upload-drive@v0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">          credentials_json: ${{ secrets.GDRIVE_CREDENTIALS }}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">          folder_id: ${{ secrets.GDRIVE_FOLDER_ID }}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">          src: coverage/**</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      # 6) （必要に応じて）デプロイ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      - name: Deploy to Vercel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        uses: amondnet/vercel-action@v20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">          vercel-token: ${{ secrets.VERCEL_TOKEN }}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">          vercel-args: "--prod"</t>
+  </si>
+  <si>
+    <t>ポイント解説</t>
+  </si>
+  <si>
+    <r>
+      <t>Claude Opus 4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>：差分を渡してユニットテストやコードレビューコメントを自動生成</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Cursor CLI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>：コードベースからドキュメントを生成</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Google Drive</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>：成果物（カバレッジレポートや AI が書いたドキュメント）を一元管理</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>GitHub Secrets</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>：API キーや認証情報を安全に保管</t>
+    </r>
+  </si>
+  <si>
+    <t>4. ローカルでの開発フロー（Cursor 活用例）</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. VSCode 上で </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cursor</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> プラグインを有効化</t>
+    </r>
+  </si>
+  <si>
+    <t>2. コーディングしながら</t>
+  </si>
+  <si>
+    <r>
+      <t>// TODO:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> コメントを入れる</t>
+    </r>
+  </si>
+  <si>
+    <t>Cursor のコード補完でリファクタリング</t>
+  </si>
+  <si>
+    <t>3. コードをコミット → GitHub Actions が自動で上記ワークフローを実行</t>
+  </si>
+  <si>
+    <t>5. 運用のポイント</t>
+  </si>
+  <si>
+    <t>モデルプロンプトのチューニング</t>
+  </si>
+  <si>
+    <t>Claude に渡すプロンプトは、実際の差分やプロジェクト規約に合わせて調整</t>
+  </si>
+  <si>
+    <t>成果物のバージョン管理</t>
+  </si>
+  <si>
+    <t>Google Drive 上に日付ごとのフォルダを作成し、レポートを整理</t>
+  </si>
+  <si>
+    <t>ガバナンス</t>
+  </si>
+  <si>
+    <t>AI 生成コードは必ず人間がレビューし、自動マージポリシーは設定しない</t>
+  </si>
+  <si>
+    <t>これで、Google Drive ⇆ GitHub Actions ⇆ Cursor ⇆ Claude Opus 4 の AI-CICD フローが確立され、テスト生成からドキュメント整備、成果物管理までを自動化できます。ぜひリポジトリにこのワークフローを組み込んでみてください。</t>
+  </si>
+  <si>
+    <t>下記のやり方を詳細に説明してください。</t>
+  </si>
+  <si>
+    <t>Google Drive API</t>
+  </si>
+  <si>
+    <t>以下では、Google Drive API を使い始めるための手順をステップバイステップで詳細に解説します。GCP コンソール上での設定から、サービスアカウント／OAuth クライアントの作成、アクセストークン取得、そしてアップロード先フォルダ ID の把握までをカバーします。</t>
+  </si>
+  <si>
+    <t>1. Google Drive API とは</t>
+  </si>
+  <si>
+    <r>
+      <t>Google Drive API</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> は、プログラムから Google Drive 上のファイルやフォルダを操作できる RESTful API です。</t>
+    </r>
+  </si>
+  <si>
+    <t>ファイルのアップロード・ダウンロード、フォルダの作成、権限設定などを自動化できます。</t>
+  </si>
+  <si>
+    <t>2. GCP コンソールで Drive API を有効化</t>
+  </si>
+  <si>
+    <r>
+      <t>1. GCP コンソール</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="10"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（https://console.cloud.google.com/ ）にアクセスし、対象のプロジェクトを選択または新規作成します。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2. 左側メニューの </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>「API とサービス」 &gt; 「ライブラリ」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> を開きます。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">3. 検索ボックスに「Drive API」と入力し、表示された </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>「Google Drive API」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> をクリック。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">4. API の概要ページで </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>「有効にする」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> をクリック。</t>
+    </r>
+  </si>
+  <si>
+    <t>5. 成功するとダッシュボードに「有効な API とサービス」として Drive API がリストされます。</t>
+  </si>
+  <si>
+    <t>ポイント</t>
+  </si>
+  <si>
+    <t>プロジェクトごとに API の有効化が必要です。</t>
+  </si>
+  <si>
+    <t>複数プロジェクトで使う場合は、それぞれで同様の手順を行ってください。</t>
+  </si>
+  <si>
+    <t>3. サービスアカウント or OAuth クライアントの作成とアクセストークン取得</t>
+  </si>
+  <si>
+    <t>Drive API にアクセスする方法は大きく２通りあります。用途に応じて選んでください。</t>
+  </si>
+  <si>
+    <t>認証方式</t>
+  </si>
+  <si>
+    <t>用途</t>
+  </si>
+  <si>
+    <t>サービスアカウント</t>
+  </si>
+  <si>
+    <t>バックエンド→Drive 操作（ユーザー個別同意不要）</t>
+  </si>
+  <si>
+    <t>OAuth クライアント</t>
+  </si>
+  <si>
+    <t>エンドユーザーの Drive を操作（同意フローあり）</t>
+  </si>
+  <si>
+    <t>A. サービスアカウントを使う場合</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. GCP コンソールの左側メニューから </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>「IAM と管理」 &gt; 「サービスアカウント」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> を選択。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2. 「サービス アカウントを作成」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> をクリックし、</t>
+    </r>
+  </si>
+  <si>
+    <t>ID：自動生成可</t>
+  </si>
+  <si>
+    <t>説明：任意</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">3. 次の画面で </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ロール</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> を付与。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">最低限 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>Drive ファイル作成者</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>roles/drive.file</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）を選ぶと、作ったファイル／フォルダにのみアクセス権が付与され、安全です。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">4. サービスアカウント一覧に戻り、作成した行の </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>︙ &gt; 「鍵を作成」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> を選択。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>5. JSON</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 形式で鍵を生成し、マシンにダウンロード（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>drive-uploader-sa-xxxxx.json</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）。</t>
+    </r>
+  </si>
+  <si>
+    <t>アクセストークン取得例（gcloud CLI）</t>
+  </si>
+  <si>
+    <t># 鍵ファイルを環境変数にセット</t>
+  </si>
+  <si>
+    <t>export GOOGLE_APPLICATION_CREDENTIALS="/path/to/drive-uploader-sa-xxxxx.json"</t>
+  </si>
+  <si>
+    <t># アクセストークンを取得</t>
+  </si>
+  <si>
+    <t>gcloud auth application-default print-access-token</t>
+  </si>
+  <si>
+    <t>このトークンを HTTP Authorization ヘッダに載せて API 呼び出しします。</t>
+  </si>
+  <si>
+    <t>Authorization: Bearer &lt;取得したアクセストークン&gt;</t>
+  </si>
+  <si>
+    <t>B. OAuth クライアントを使う場合</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. GCP コンソールの </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>「API とサービス」 &gt; 「認証情報」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> を開き、</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>「認証情報を作成」 &gt; 「OAuth クライアント ID」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> を選択。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2. アプリケーションの種類</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> を選択（例：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>ウェブアプリケーション</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>デスクトップアプリ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>3. リダイレクト URI（例：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>http://localhost:8080/oauth2callback</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）を設定し、クライアント ID／秘密鍵を取得。</t>
+    </r>
+  </si>
+  <si>
+    <t>4. アプリ側でライブラリ（Google 提供の OAuth2 クライアント）を使い、認可 URL を生成。</t>
+  </si>
+  <si>
+    <t>5. ユーザーが同意画面を通過すると、返ってきた認可コードを用いてアクセストークン／リフレッシュトークンを取得。</t>
+  </si>
+  <si>
+    <r>
+      <t>Node.js 例（</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>googleapis</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ライブラリ）</t>
+    </r>
+  </si>
+  <si>
+    <t>import {google} from 'googleapis';</t>
+  </si>
+  <si>
+    <t>const oauth2Client = new google.auth.OAuth2(</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  CLIENT_ID, CLIENT_SECRET, REDIRECT_URI</t>
+  </si>
+  <si>
+    <t>);</t>
+  </si>
+  <si>
+    <t>// 1) 認可 URL 作成</t>
+  </si>
+  <si>
+    <t>const authUrl = oauth2Client.generateAuthUrl({</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  scope: ['https://www.googleapis.com/auth/drive.file'],</t>
+  </si>
+  <si>
+    <t>});</t>
+  </si>
+  <si>
+    <t>console.log('Visit this URL to authorize:', authUrl);</t>
+  </si>
+  <si>
+    <t>// 2) コード取得後に実行</t>
+  </si>
+  <si>
+    <t>const {tokens} = await oauth2Client.getToken(AUTHORIZATION_CODE);</t>
+  </si>
+  <si>
+    <t>oauth2Client.setCredentials(tokens);</t>
+  </si>
+  <si>
+    <t>// 3) アクセストークンを使って API 呼び出し</t>
+  </si>
+  <si>
+    <t>const drive = google.drive({version: 'v3', auth: oauth2Client});</t>
+  </si>
+  <si>
+    <t>4. アップロード先フォルダ ID を控える</t>
+  </si>
+  <si>
+    <t>1. ブラウザで Google Drive を開き、アップロードしたいフォルダを開きます。</t>
+  </si>
+  <si>
+    <t>2. URL の末尾にある文字列がフォルダ ID です。</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/**1A2bC3dEfGhIjKlMnOpQrStUvWxYz**?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">3. その ID（この例では </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>1A2bC3dEfGhIjKlMnOpQrStUvWxYz</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）をメモしておきます。</t>
+    </r>
+  </si>
+  <si>
+    <t>Tip</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">プログラム内で </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>folderId</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> パラメータとして指定すると、そのフォルダ以下にファイルを作成できます。</t>
+    </r>
+  </si>
+  <si>
+    <t>サービスアカウントを使う場合は、フォルダの共有設定で「編集者」としてサービスアカウントのメールアドレスを追加する必要があります。</t>
+  </si>
+  <si>
+    <t>以上の手順で、Google Drive API の有効化から認証情報の取得、フォルダ ID の把握まで完了です。これをベースに、CI/CD ワークフローやバッチ処理で Drive へのアップロード自動化を組み込むことができます。</t>
+  </si>
+  <si>
+    <t>https://console.cloud.google.com/welcome?inv=1&amp;invt=AbyjMA&amp;project=ai-cicd-461122</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://console.cloud.google.com/apis/library?inv=1&amp;invt=AbyjMA&amp;project=ai-cicd-461122</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://console.cloud.google.com/marketplace/product/google/drive.googleapis.com?q=search&amp;referrer=search&amp;inv=1&amp;invt=AbyjMA&amp;project=ai-cicd-461122</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://console.cloud.google.com/iam-admin/serviceaccounts?inv=1&amp;invt=AbyjMA&amp;project=ai-cicd-461122</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://console.cloud.google.com/iam-admin/serviceaccounts/create?inv=1&amp;invt=AbyjMA&amp;project=ai-cicd-461122</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">名前：例 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>drive-uploader-sa</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ai-cicd-461122-e27fdc150e96.json</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>pnpmとvercelとMongoDBとGiHubとOneDriveとGoogle DriveとCursorとClaude Opus4とChatGPTでAI-CICDフローを確立してください。
+https://github.com/umezawakanta/work-time-tracker</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>pnpmとViteとReactとVercelとMongoDBとGitHubとOneDriveとGoogle DriveとCursorとClaude Opus4とChatGPTとGeminiとGrokとNortionとSlackとTeamsでAI-CICDフローを確立してください。 https://github.com/umezawakanta/work-time-tracker</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Ctrl + Shift + D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Fix in Chat</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Ctrl + N</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>New Text File</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Ctrl + Enter</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Accept All</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Ctrl + Shift + N</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Open New Window</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4047,6 +5414,31 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -4084,7 +5476,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
@@ -4144,6 +5536,31 @@
     </xf>
     <xf numFmtId="20" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4644,85 +6061,56 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63958C87-2C93-43E5-8405-38AB5C73D6BE}">
-  <dimension ref="B3:B13"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
-  <sheetData>
-    <row r="3" spans="2:2">
-      <c r="B3" s="2" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="4" spans="2:2" ht="14.25">
-      <c r="B4" s="23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="2:2" ht="14.25">
-      <c r="B5" s="24" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="6" spans="2:2" ht="14.25">
-      <c r="B6" s="23">
-        <v>4.1666666666666666E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="2:2" ht="14.25">
-      <c r="B7" s="24" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="8" spans="2:2" ht="14.25">
-      <c r="B8" s="23">
-        <v>8.3333333333333332E-3</v>
-      </c>
-    </row>
-    <row r="9" spans="2:2" ht="14.25">
-      <c r="B9" s="24" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="10" spans="2:2" ht="14.25">
-      <c r="B10" s="23">
-        <v>1.3194444444444444E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="2:2" ht="14.25">
-      <c r="B11" s="24" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="12" spans="2:2">
-      <c r="B12" s="25">
-        <v>1.7361111111111112E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="2:2">
-      <c r="B13" t="s">
-        <v>676</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <hyperlinks>
-    <hyperlink ref="B3" r:id="rId1" xr:uid="{1592C6E0-7587-42B0-BF1B-3FBFEDF00B08}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{316E5208-1AA2-4457-A1CF-56BEFB0E0D49}">
-  <dimension ref="C3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{083174DA-A42C-4F9C-978E-61AEAAD9DDFF}">
+  <dimension ref="C2:D8"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="3" max="3" width="65" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="61.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="68.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:3" ht="54">
-      <c r="C3" s="3" t="s">
-        <v>677</v>
+    <row r="2" spans="3:4">
+      <c r="D2" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="3" spans="3:4">
+      <c r="C3" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="4" spans="3:4">
+      <c r="C4" t="s">
+        <v>683</v>
+      </c>
+      <c r="D4" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="5" spans="3:4">
+      <c r="C5" t="s">
+        <v>686</v>
+      </c>
+      <c r="D5" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="6" spans="3:4">
+      <c r="C6" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="7" spans="3:4">
+      <c r="C7" t="s">
+        <v>688</v>
+      </c>
+      <c r="D7" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="8" spans="3:4">
+      <c r="C8" t="s">
+        <v>690</v>
       </c>
     </row>
   </sheetData>
@@ -4731,2010 +6119,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F88E2D65-ECA4-4EF7-BEC6-93BAB5468A01}">
-  <dimension ref="B3:C83"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
-  <sheetData>
-    <row r="3" spans="3:3" ht="21">
-      <c r="C3" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="4" spans="3:3">
-      <c r="C4" s="7"/>
-    </row>
-    <row r="5" spans="3:3">
-      <c r="C5" s="8" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="6" spans="3:3">
-      <c r="C6" s="7"/>
-    </row>
-    <row r="7" spans="3:3">
-      <c r="C7" s="8" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="3:3">
-      <c r="C8" s="7"/>
-    </row>
-    <row r="9" spans="3:3">
-      <c r="C9" s="8" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="10" spans="3:3">
-      <c r="C10" s="7"/>
-    </row>
-    <row r="11" spans="3:3">
-      <c r="C11" s="8" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="12" spans="3:3">
-      <c r="C12" s="7"/>
-    </row>
-    <row r="13" spans="3:3">
-      <c r="C13" s="8" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="14" spans="3:3">
-      <c r="C14" s="7"/>
-    </row>
-    <row r="15" spans="3:3">
-      <c r="C15" s="8" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="16" spans="3:3">
-      <c r="C16" s="7"/>
-    </row>
-    <row r="17" spans="3:3">
-      <c r="C17" s="8" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="18" spans="3:3">
-      <c r="C18" s="7"/>
-    </row>
-    <row r="19" spans="3:3">
-      <c r="C19" s="8" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="20" spans="3:3">
-      <c r="C20" s="7"/>
-    </row>
-    <row r="21" spans="3:3">
-      <c r="C21" s="8" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="22" spans="3:3">
-      <c r="C22" s="7"/>
-    </row>
-    <row r="23" spans="3:3">
-      <c r="C23" s="8" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="24" spans="3:3">
-      <c r="C24" s="7"/>
-    </row>
-    <row r="25" spans="3:3">
-      <c r="C25" s="8" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="26" spans="3:3">
-      <c r="C26" s="7"/>
-    </row>
-    <row r="27" spans="3:3">
-      <c r="C27" s="8" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="28" spans="3:3">
-      <c r="C28" s="7"/>
-    </row>
-    <row r="29" spans="3:3">
-      <c r="C29" s="8" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="30" spans="3:3">
-      <c r="C30" s="7"/>
-    </row>
-    <row r="31" spans="3:3">
-      <c r="C31" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="32" spans="3:3">
-      <c r="C32" s="7"/>
-    </row>
-    <row r="33" spans="3:3">
-      <c r="C33" s="8" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="34" spans="3:3">
-      <c r="C34" s="7"/>
-    </row>
-    <row r="35" spans="3:3">
-      <c r="C35" s="8" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="36" spans="3:3">
-      <c r="C36" s="7"/>
-    </row>
-    <row r="37" spans="3:3">
-      <c r="C37" s="8" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="39" spans="3:3" ht="21">
-      <c r="C39" s="4" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="40" spans="3:3">
-      <c r="C40" s="7"/>
-    </row>
-    <row r="41" spans="3:3">
-      <c r="C41" s="8" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="42" spans="3:3">
-      <c r="C42" s="7"/>
-    </row>
-    <row r="43" spans="3:3">
-      <c r="C43" s="8" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="44" spans="3:3">
-      <c r="C44" s="7"/>
-    </row>
-    <row r="45" spans="3:3">
-      <c r="C45" s="8" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="46" spans="3:3">
-      <c r="C46" s="7"/>
-    </row>
-    <row r="47" spans="3:3">
-      <c r="C47" s="7" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="48" spans="3:3">
-      <c r="C48" s="7"/>
-    </row>
-    <row r="49" spans="3:3">
-      <c r="C49" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="50" spans="3:3">
-      <c r="C50" s="7"/>
-    </row>
-    <row r="51" spans="3:3">
-      <c r="C51" s="8" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="52" spans="3:3">
-      <c r="C52" s="7"/>
-    </row>
-    <row r="53" spans="3:3">
-      <c r="C53" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="54" spans="3:3">
-      <c r="C54" s="7"/>
-    </row>
-    <row r="55" spans="3:3">
-      <c r="C55" s="8" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="56" spans="3:3">
-      <c r="C56" s="7"/>
-    </row>
-    <row r="57" spans="3:3">
-      <c r="C57" s="8" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="58" spans="3:3">
-      <c r="C58" s="7"/>
-    </row>
-    <row r="59" spans="3:3">
-      <c r="C59" s="8" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="60" spans="3:3">
-      <c r="C60" s="7"/>
-    </row>
-    <row r="61" spans="3:3">
-      <c r="C61" s="8" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="63" spans="3:3" ht="21">
-      <c r="C63" s="4" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="64" spans="3:3">
-      <c r="C64" s="7"/>
-    </row>
-    <row r="65" spans="3:3">
-      <c r="C65" s="8" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="66" spans="3:3">
-      <c r="C66" s="7"/>
-    </row>
-    <row r="67" spans="3:3">
-      <c r="C67" s="8" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="68" spans="3:3">
-      <c r="C68" s="7"/>
-    </row>
-    <row r="69" spans="3:3">
-      <c r="C69" s="8" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="70" spans="3:3">
-      <c r="C70" s="7"/>
-    </row>
-    <row r="71" spans="3:3">
-      <c r="C71" s="8" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="72" spans="3:3">
-      <c r="C72" s="7"/>
-    </row>
-    <row r="73" spans="3:3">
-      <c r="C73" s="8" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="74" spans="3:3">
-      <c r="C74" s="7"/>
-    </row>
-    <row r="75" spans="3:3">
-      <c r="C75" s="8" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="76" spans="3:3">
-      <c r="C76" s="7"/>
-    </row>
-    <row r="77" spans="3:3">
-      <c r="C77" s="8" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="78" spans="3:3">
-      <c r="C78" s="7"/>
-    </row>
-    <row r="79" spans="3:3">
-      <c r="C79" s="8" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="80" spans="3:3">
-      <c r="C80" s="7"/>
-    </row>
-    <row r="81" spans="2:3">
-      <c r="C81" s="8" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="82" spans="2:3">
-      <c r="C82" s="7"/>
-    </row>
-    <row r="83" spans="2:3">
-      <c r="B83" t="s">
-        <v>139</v>
-      </c>
-      <c r="C83" s="8" t="s">
-        <v>138</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C954C604-59FA-4E71-B562-0C51EBE0CA48}">
-  <dimension ref="C3:D5"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
-  <cols>
-    <col min="3" max="3" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="82" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="3:4">
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="3:4">
-      <c r="C4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="3:4">
-      <c r="C5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <hyperlinks>
-    <hyperlink ref="D4" r:id="rId1" xr:uid="{ABD404D3-B385-4979-8E15-E31861E65E28}"/>
-    <hyperlink ref="D5" r:id="rId2" xr:uid="{5796EFDF-5CB9-4253-80FF-8BF4337CB0B6}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57B697DF-EBFB-495C-BA65-6BC1E0B5AF25}">
-  <dimension ref="B3:B52"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
-  <sheetData>
-    <row r="3" spans="2:2" ht="21">
-      <c r="B3" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="2:2" ht="16.5">
-      <c r="B5" s="5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="2:2">
-      <c r="B7" s="6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="2:2">
-      <c r="B8" s="6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="2:2">
-      <c r="B9" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="2:2">
-      <c r="B10" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="2:2">
-      <c r="B11" s="6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" spans="2:2">
-      <c r="B12" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="2:2">
-      <c r="B13" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="14" spans="2:2">
-      <c r="B14" s="6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="15" spans="2:2">
-      <c r="B15" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" ht="16.5">
-      <c r="B17" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="18" spans="2:2">
-      <c r="B18" s="7"/>
-    </row>
-    <row r="19" spans="2:2">
-      <c r="B19" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="20" spans="2:2">
-      <c r="B20" s="7"/>
-    </row>
-    <row r="21" spans="2:2">
-      <c r="B21" s="7"/>
-    </row>
-    <row r="22" spans="2:2">
-      <c r="B22" s="9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="23" spans="2:2">
-      <c r="B23" s="9" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="24" spans="2:2">
-      <c r="B24" s="9" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="25" spans="2:2">
-      <c r="B25" s="7"/>
-    </row>
-    <row r="26" spans="2:2">
-      <c r="B26" s="8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="27" spans="2:2">
-      <c r="B27" s="7"/>
-    </row>
-    <row r="28" spans="2:2">
-      <c r="B28" s="7"/>
-    </row>
-    <row r="29" spans="2:2">
-      <c r="B29" s="9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="30" spans="2:2">
-      <c r="B30" s="7"/>
-    </row>
-    <row r="31" spans="2:2">
-      <c r="B31" s="8" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="32" spans="2:2">
-      <c r="B32" s="7"/>
-    </row>
-    <row r="33" spans="2:2">
-      <c r="B33" s="7"/>
-    </row>
-    <row r="34" spans="2:2">
-      <c r="B34" s="9" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="35" spans="2:2">
-      <c r="B35" s="7"/>
-    </row>
-    <row r="36" spans="2:2">
-      <c r="B36" s="8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="37" spans="2:2">
-      <c r="B37" s="7"/>
-    </row>
-    <row r="38" spans="2:2">
-      <c r="B38" s="7"/>
-    </row>
-    <row r="39" spans="2:2">
-      <c r="B39" s="9" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="40" spans="2:2">
-      <c r="B40" s="9" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="41" spans="2:2">
-      <c r="B41" s="7"/>
-    </row>
-    <row r="42" spans="2:2">
-      <c r="B42" s="8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="43" spans="2:2">
-      <c r="B43" s="7"/>
-    </row>
-    <row r="44" spans="2:2">
-      <c r="B44" s="7"/>
-    </row>
-    <row r="45" spans="2:2">
-      <c r="B45" s="9" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="46" spans="2:2">
-      <c r="B46" s="9" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="47" spans="2:2">
-      <c r="B47" s="7"/>
-    </row>
-    <row r="48" spans="2:2">
-      <c r="B48" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="49" spans="2:2">
-      <c r="B49" s="7"/>
-    </row>
-    <row r="50" spans="2:2">
-      <c r="B50" s="7"/>
-    </row>
-    <row r="51" spans="2:2">
-      <c r="B51" s="9" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="52" spans="2:2">
-      <c r="B52" s="9" t="s">
-        <v>51</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C6614D2-9BE2-4DBF-BE3B-CC381AB3F591}">
-  <dimension ref="B4:D4"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
-  <cols>
-    <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.5" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="4" spans="2:4">
-      <c r="B4" s="1">
-        <v>45776</v>
-      </c>
-      <c r="C4" t="s">
-        <v>253</v>
-      </c>
-      <c r="D4">
-        <v>261</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E418F96-9DED-4C44-AAF0-D4A9C9E57DCB}">
-  <sheetPr codeName="Sheet1"/>
-  <dimension ref="B3:B109"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
-  <sheetData>
-    <row r="3" spans="2:2">
-      <c r="B3" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="5" spans="2:2">
-      <c r="B5" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="6" spans="2:2">
-      <c r="B6" s="7"/>
-    </row>
-    <row r="7" spans="2:2">
-      <c r="B7" s="7" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="8" spans="2:2">
-      <c r="B8" s="7" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="9" spans="2:2">
-      <c r="B9" s="7" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="10" spans="2:2">
-      <c r="B10" s="7" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="11" spans="2:2">
-      <c r="B11" s="7" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="13" spans="2:2">
-      <c r="B13" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="15" spans="2:2">
-      <c r="B15" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" ht="15">
-      <c r="B17" s="10" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="19" spans="2:2" ht="15">
-      <c r="B19" s="11" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="21" spans="2:2">
-      <c r="B21" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="22" spans="2:2">
-      <c r="B22" s="7"/>
-    </row>
-    <row r="23" spans="2:2">
-      <c r="B23" s="8" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="24" spans="2:2">
-      <c r="B24" s="9" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="25" spans="2:2">
-      <c r="B25" s="9" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="26" spans="2:2">
-      <c r="B26" s="8" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="27" spans="2:2">
-      <c r="B27" s="9" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="28" spans="2:2">
-      <c r="B28" s="9" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="29" spans="2:2">
-      <c r="B29" s="9" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="30" spans="2:2">
-      <c r="B30" s="8" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="31" spans="2:2">
-      <c r="B31" s="9" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="32" spans="2:2">
-      <c r="B32" s="9" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="33" spans="2:2">
-      <c r="B33" s="9" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="35" spans="2:2" ht="16.5">
-      <c r="B35" s="5" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="36" spans="2:2">
-      <c r="B36" s="7"/>
-    </row>
-    <row r="37" spans="2:2">
-      <c r="B37" s="7" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="38" spans="2:2">
-      <c r="B38" s="12" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="39" spans="2:2">
-      <c r="B39" s="7" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="40" spans="2:2">
-      <c r="B40" s="7" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="41" spans="2:2">
-      <c r="B41" s="6"/>
-    </row>
-    <row r="42" spans="2:2">
-      <c r="B42" s="6"/>
-    </row>
-    <row r="43" spans="2:2">
-      <c r="B43" s="6" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="44" spans="2:2">
-      <c r="B44" s="13" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="46" spans="2:2" ht="16.5">
-      <c r="B46" s="5" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="47" spans="2:2">
-      <c r="B47" s="7"/>
-    </row>
-    <row r="48" spans="2:2">
-      <c r="B48" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="49" spans="2:2">
-      <c r="B49" s="7" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="50" spans="2:2">
-      <c r="B50" s="7" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="51" spans="2:2">
-      <c r="B51" s="9" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="52" spans="2:2">
-      <c r="B52" s="9" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="53" spans="2:2">
-      <c r="B53" s="7" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="54" spans="2:2">
-      <c r="B54" s="7" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="56" spans="2:2">
-      <c r="B56" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="58" spans="2:2">
-      <c r="B58" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="60" spans="2:2" ht="28.5">
-      <c r="B60" s="14" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="62" spans="2:2">
-      <c r="B62" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="63" spans="2:2">
-      <c r="B63" s="7"/>
-    </row>
-    <row r="64" spans="2:2">
-      <c r="B64" s="8" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="65" spans="2:2">
-      <c r="B65" s="7"/>
-    </row>
-    <row r="66" spans="2:2">
-      <c r="B66" s="7"/>
-    </row>
-    <row r="67" spans="2:2">
-      <c r="B67" s="15" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="68" spans="2:2">
-      <c r="B68" s="9" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="69" spans="2:2">
-      <c r="B69" s="7"/>
-    </row>
-    <row r="70" spans="2:2">
-      <c r="B70" s="8" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="71" spans="2:2">
-      <c r="B71" s="7"/>
-    </row>
-    <row r="72" spans="2:2">
-      <c r="B72" s="7"/>
-    </row>
-    <row r="73" spans="2:2">
-      <c r="B73" s="9" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="74" spans="2:2">
-      <c r="B74" s="9" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="75" spans="2:2">
-      <c r="B75" s="7"/>
-    </row>
-    <row r="76" spans="2:2">
-      <c r="B76" s="8" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="77" spans="2:2">
-      <c r="B77" s="7"/>
-    </row>
-    <row r="78" spans="2:2">
-      <c r="B78" s="7"/>
-    </row>
-    <row r="79" spans="2:2">
-      <c r="B79" s="9" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="80" spans="2:2">
-      <c r="B80" s="9" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="81" spans="2:2">
-      <c r="B81" s="9" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="82" spans="2:2">
-      <c r="B82" s="7"/>
-    </row>
-    <row r="83" spans="2:2">
-      <c r="B83" s="8" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="84" spans="2:2">
-      <c r="B84" s="7"/>
-    </row>
-    <row r="85" spans="2:2">
-      <c r="B85" s="7"/>
-    </row>
-    <row r="86" spans="2:2">
-      <c r="B86" s="9" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="87" spans="2:2">
-      <c r="B87" s="9" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="88" spans="2:2">
-      <c r="B88" s="9" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="89" spans="2:2">
-      <c r="B89" s="7"/>
-    </row>
-    <row r="90" spans="2:2">
-      <c r="B90" s="8" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="91" spans="2:2">
-      <c r="B91" s="7"/>
-    </row>
-    <row r="92" spans="2:2">
-      <c r="B92" s="7"/>
-    </row>
-    <row r="93" spans="2:2">
-      <c r="B93" s="9" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="94" spans="2:2">
-      <c r="B94" s="9" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="95" spans="2:2">
-      <c r="B95" s="7"/>
-    </row>
-    <row r="96" spans="2:2">
-      <c r="B96" s="8" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="97" spans="2:2">
-      <c r="B97" s="7"/>
-    </row>
-    <row r="98" spans="2:2">
-      <c r="B98" s="7"/>
-    </row>
-    <row r="99" spans="2:2">
-      <c r="B99" s="9" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="100" spans="2:2">
-      <c r="B100" s="7"/>
-    </row>
-    <row r="101" spans="2:2">
-      <c r="B101" s="12" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="103" spans="2:2">
-      <c r="B103" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="104" spans="2:2">
-      <c r="B104" s="7"/>
-    </row>
-    <row r="105" spans="2:2">
-      <c r="B105" s="7" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="106" spans="2:2">
-      <c r="B106" s="7" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="107" spans="2:2">
-      <c r="B107" s="7" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="109" spans="2:2">
-      <c r="B109" t="s">
-        <v>250</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <hyperlinks>
-    <hyperlink ref="B67" r:id="rId1" display="https://makersuite.google.com/app/apikey" xr:uid="{771DD001-7E09-4F62-86F2-758C98D1481F}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
-  <drawing r:id="rId3"/>
-  <legacyDrawing r:id="rId4"/>
-  <controls>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="9217" r:id="rId5" name="Control 1">
-          <controlPr defaultSize="0" r:id="rId6">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>41</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>257175</xdr:colOff>
-                <xdr:row>42</xdr:row>
-                <xdr:rowOff>76200</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="9217" r:id="rId5" name="Control 1"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-  </controls>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17156405-9D17-4273-BBE4-E9A6DC809FCB}">
-  <dimension ref="C3:E3"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
-  <cols>
-    <col min="3" max="3" width="31.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="3:5">
-      <c r="C3" t="s">
-        <v>179</v>
-      </c>
-      <c r="D3" t="s">
-        <v>180</v>
-      </c>
-      <c r="E3">
-        <v>6.25</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29E011BA-FF28-4838-A033-18A49EB7C30B}">
-  <dimension ref="B4:F33"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
-  <cols>
-    <col min="2" max="2" width="3.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="4" spans="2:6">
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4" s="1">
-        <v>45729</v>
-      </c>
-    </row>
-    <row r="5" spans="2:6">
-      <c r="B5">
-        <f>B4+1</f>
-        <v>2</v>
-      </c>
-      <c r="C5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="1">
-        <v>45729</v>
-      </c>
-    </row>
-    <row r="6" spans="2:6">
-      <c r="B6">
-        <f>B5+1</f>
-        <v>3</v>
-      </c>
-      <c r="C6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="1">
-        <v>45729</v>
-      </c>
-    </row>
-    <row r="7" spans="2:6" ht="40.5">
-      <c r="B7">
-        <f>B6+1</f>
-        <v>4</v>
-      </c>
-      <c r="C7" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F7" s="1">
-        <v>45729</v>
-      </c>
-    </row>
-    <row r="8" spans="2:6" ht="27">
-      <c r="B8">
-        <f>B7+1</f>
-        <v>5</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" s="1">
-        <v>45731</v>
-      </c>
-    </row>
-    <row r="9" spans="2:6" ht="54">
-      <c r="B9">
-        <f>B8+1</f>
-        <v>6</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="1">
-        <v>45735</v>
-      </c>
-    </row>
-    <row r="10" spans="2:6" ht="27">
-      <c r="B10">
-        <f t="shared" ref="B10:B33" si="0">B9+1</f>
-        <v>7</v>
-      </c>
-      <c r="C10" t="s">
-        <v>54</v>
-      </c>
-      <c r="D10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F10" s="1">
-        <v>45735</v>
-      </c>
-    </row>
-    <row r="11" spans="2:6">
-      <c r="B11">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="C11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" s="1">
-        <v>45735</v>
-      </c>
-    </row>
-    <row r="12" spans="2:6">
-      <c r="B12">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="C12" t="s">
-        <v>58</v>
-      </c>
-      <c r="D12" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" s="1">
-        <v>45738</v>
-      </c>
-    </row>
-    <row r="13" spans="2:6">
-      <c r="B13">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="C13" t="s">
-        <v>59</v>
-      </c>
-      <c r="D13" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" s="1">
-        <v>45739</v>
-      </c>
-    </row>
-    <row r="14" spans="2:6">
-      <c r="B14">
-        <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="C14" t="s">
-        <v>60</v>
-      </c>
-      <c r="D14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" s="1">
-        <v>45739</v>
-      </c>
-    </row>
-    <row r="15" spans="2:6">
-      <c r="B15">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="C15" t="s">
-        <v>64</v>
-      </c>
-      <c r="D15" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" s="1">
-        <v>45739</v>
-      </c>
-    </row>
-    <row r="16" spans="2:6">
-      <c r="B16">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="C16" t="s">
-        <v>65</v>
-      </c>
-      <c r="D16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" s="1">
-        <v>45739</v>
-      </c>
-    </row>
-    <row r="17" spans="2:6">
-      <c r="B17">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="C17" t="s">
-        <v>67</v>
-      </c>
-      <c r="D17" t="s">
-        <v>11</v>
-      </c>
-      <c r="F17" s="1">
-        <v>45739</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6">
-      <c r="B18">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="C18" t="s">
-        <v>69</v>
-      </c>
-      <c r="D18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F18" s="1">
-        <v>45739</v>
-      </c>
-    </row>
-    <row r="19" spans="2:6">
-      <c r="B19">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="C19" t="s">
-        <v>72</v>
-      </c>
-      <c r="D19" t="s">
-        <v>11</v>
-      </c>
-      <c r="F19" s="1">
-        <v>45739</v>
-      </c>
-    </row>
-    <row r="20" spans="2:6">
-      <c r="B20">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="C20" t="s">
-        <v>74</v>
-      </c>
-      <c r="D20" t="s">
-        <v>11</v>
-      </c>
-      <c r="F20" s="1">
-        <v>45739</v>
-      </c>
-    </row>
-    <row r="21" spans="2:6">
-      <c r="B21">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="C21" t="s">
-        <v>76</v>
-      </c>
-      <c r="D21" t="s">
-        <v>11</v>
-      </c>
-      <c r="F21" s="1">
-        <v>45739</v>
-      </c>
-    </row>
-    <row r="22" spans="2:6">
-      <c r="B22">
-        <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="C22" t="s">
-        <v>78</v>
-      </c>
-      <c r="D22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F22" s="1">
-        <v>45739</v>
-      </c>
-    </row>
-    <row r="23" spans="2:6">
-      <c r="B23">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="C23" t="s">
-        <v>80</v>
-      </c>
-      <c r="D23" t="s">
-        <v>11</v>
-      </c>
-      <c r="F23" s="1">
-        <v>45739</v>
-      </c>
-    </row>
-    <row r="24" spans="2:6">
-      <c r="B24">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="C24" t="s">
-        <v>82</v>
-      </c>
-      <c r="D24" t="s">
-        <v>11</v>
-      </c>
-      <c r="F24" s="1">
-        <v>45739</v>
-      </c>
-    </row>
-    <row r="25" spans="2:6">
-      <c r="B25">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="C25" t="s">
-        <v>83</v>
-      </c>
-      <c r="D25" t="s">
-        <v>11</v>
-      </c>
-      <c r="F25" s="1">
-        <v>45739</v>
-      </c>
-    </row>
-    <row r="26" spans="2:6">
-      <c r="B26">
-        <f t="shared" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="C26" t="s">
-        <v>82</v>
-      </c>
-      <c r="D26" t="s">
-        <v>11</v>
-      </c>
-      <c r="F26" s="1">
-        <v>45739</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6">
-      <c r="B27">
-        <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="C27" t="s">
-        <v>13</v>
-      </c>
-      <c r="D27" t="s">
-        <v>11</v>
-      </c>
-      <c r="F27" s="1">
-        <v>45739</v>
-      </c>
-    </row>
-    <row r="28" spans="2:6" ht="27">
-      <c r="B28">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="D28" t="s">
-        <v>11</v>
-      </c>
-      <c r="F28" s="1">
-        <v>45739</v>
-      </c>
-    </row>
-    <row r="29" spans="2:6">
-      <c r="B29">
-        <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="C29" t="s">
-        <v>89</v>
-      </c>
-      <c r="D29" t="s">
-        <v>11</v>
-      </c>
-      <c r="F29" s="1">
-        <v>45743</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6">
-      <c r="B30">
-        <f t="shared" si="0"/>
-        <v>27</v>
-      </c>
-      <c r="C30" t="s">
-        <v>93</v>
-      </c>
-      <c r="D30" t="s">
-        <v>11</v>
-      </c>
-      <c r="F30" s="1">
-        <v>45743</v>
-      </c>
-    </row>
-    <row r="31" spans="2:6">
-      <c r="B31">
-        <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
-      <c r="C31" t="s">
-        <v>94</v>
-      </c>
-      <c r="D31" t="s">
-        <v>11</v>
-      </c>
-      <c r="F31" s="1">
-        <v>45747</v>
-      </c>
-    </row>
-    <row r="32" spans="2:6" ht="27">
-      <c r="B32">
-        <f t="shared" si="0"/>
-        <v>29</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="33" spans="2:3">
-      <c r="B33">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="C33" t="s">
-        <v>147</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <hyperlinks>
-    <hyperlink ref="E5" r:id="rId1" xr:uid="{710BA6B0-B0F6-4236-8BB2-74C40F796674}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42DE40CD-4CA6-4FF4-B0DA-D079807C6662}">
-  <dimension ref="B3:G15"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
-  <cols>
-    <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.125" customWidth="1"/>
-    <col min="5" max="5" width="45.375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="37.75" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="2:7" ht="40.5">
-      <c r="B3" s="1">
-        <v>45747</v>
-      </c>
-      <c r="C3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="E3" t="s">
-        <v>150</v>
-      </c>
-      <c r="F3" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" ht="54">
-      <c r="D4" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="E4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F4" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" ht="40.5">
-      <c r="D5" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="E5" t="s">
-        <v>156</v>
-      </c>
-      <c r="F5" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7" ht="54">
-      <c r="D6" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="E6" t="s">
-        <v>159</v>
-      </c>
-      <c r="F6" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="7" spans="2:7" ht="54">
-      <c r="D7" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="E7" t="s">
-        <v>162</v>
-      </c>
-      <c r="F7" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" ht="40.5">
-      <c r="D8" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E8" t="s">
-        <v>162</v>
-      </c>
-      <c r="F8" t="s">
-        <v>151</v>
-      </c>
-      <c r="G8" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7" ht="81">
-      <c r="D9" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="E9" t="s">
-        <v>153</v>
-      </c>
-      <c r="F9" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" ht="40.5">
-      <c r="D10" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="E10" t="s">
-        <v>156</v>
-      </c>
-      <c r="F10" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7" ht="54">
-      <c r="D11" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="E11" t="s">
-        <v>168</v>
-      </c>
-      <c r="F11" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="12" spans="2:7" ht="54">
-      <c r="D12" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="E12" t="s">
-        <v>170</v>
-      </c>
-      <c r="F12" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="13" spans="2:7" ht="40.5">
-      <c r="D13" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="E13" t="s">
-        <v>173</v>
-      </c>
-      <c r="F13" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="14" spans="2:7" ht="54">
-      <c r="D14" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="E14" t="s">
-        <v>175</v>
-      </c>
-      <c r="F14" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="15" spans="2:7" ht="40.5">
-      <c r="D15" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="E15" t="s">
-        <v>177</v>
-      </c>
-      <c r="F15" t="s">
-        <v>177</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6313D91D-4E4E-4302-B673-A8C3F21575BA}">
-  <dimension ref="B3:D39"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
-  <cols>
-    <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="83.75" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="3:3" ht="40.5">
-      <c r="C3" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="4" spans="3:3" ht="40.5">
-      <c r="C4" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="5" spans="3:3" ht="94.5">
-      <c r="C5" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="6" spans="3:3" ht="27">
-      <c r="C6" s="3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="7" spans="3:3" ht="54">
-      <c r="C7" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="8" spans="3:3" ht="40.5">
-      <c r="C8" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="9" spans="3:3" ht="40.5">
-      <c r="C9" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="10" spans="3:3">
-      <c r="C10" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="11" spans="3:3" ht="40.5">
-      <c r="C11" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="12" spans="3:3" ht="54">
-      <c r="C12" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="13" spans="3:3" ht="40.5">
-      <c r="C13" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="14" spans="3:3" ht="40.5">
-      <c r="C14" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="15" spans="3:3" ht="40.5">
-      <c r="C15" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="16" spans="3:3" ht="54">
-      <c r="C16" s="3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4" ht="40.5">
-      <c r="C17" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4" ht="54">
-      <c r="B18" s="1">
-        <v>45739</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="19" spans="2:4">
-      <c r="C19" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="20" spans="2:4" ht="54">
-      <c r="C20" s="3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="21" spans="2:4" ht="67.5">
-      <c r="C21" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="22" spans="2:4">
-      <c r="B22" s="1">
-        <v>45740</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="23" spans="2:4" ht="40.5">
-      <c r="C23" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="24" spans="2:4" ht="40.5">
-      <c r="B24" s="1">
-        <v>45741</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="25" spans="2:4" ht="27">
-      <c r="B25" s="1">
-        <v>45742</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="26" spans="2:4">
-      <c r="B26" s="1">
-        <v>45776</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="27" spans="2:4" ht="54">
-      <c r="B27" s="1">
-        <v>45776</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="28" spans="2:4" ht="409.5">
-      <c r="B28" s="1">
-        <v>45776</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="29" spans="2:4" ht="409.5">
-      <c r="C29" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="D29" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="30" spans="2:4" ht="409.5">
-      <c r="C30" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="D30" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="31" spans="2:4" ht="409.5">
-      <c r="C31" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="D31" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="32" spans="2:4" ht="409.5">
-      <c r="C32" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="D32" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="33" spans="3:4">
-      <c r="C33" s="3"/>
-      <c r="D33" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="34" spans="3:4" ht="409.5">
-      <c r="C34" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="D34" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="35" spans="3:4" ht="409.5">
-      <c r="C35" s="3" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="36" spans="3:4" ht="135">
-      <c r="C36" s="3" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="37" spans="3:4" ht="189">
-      <c r="C37" s="3" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="38" spans="3:4">
-      <c r="C38" s="3" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="39" spans="3:4" ht="409.5">
-      <c r="C39" s="3" t="s">
-        <v>682</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{083174DA-A42C-4F9C-978E-61AEAAD9DDFF}">
-  <dimension ref="C3"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
-  <cols>
-    <col min="3" max="3" width="44" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="3:3">
-      <c r="C3" t="s">
-        <v>681</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D23E4F9-E544-431D-8912-173026FA7A6D}">
   <dimension ref="B3:E9"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -6816,7 +6201,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A375A8A-C1C1-4426-AFA3-B95CA8BCFB52}">
   <dimension ref="A2:BM291"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -6892,18 +6277,18 @@
       MOD(NOW(),1),
       TIME(0,5,0)
     ),"HH:mm")</f>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B2" s="19"/>
       <c r="D2" s="1">
         <f ca="1">TODAY()</f>
-        <v>45791</v>
+        <v>45806</v>
       </c>
     </row>
     <row r="3" spans="1:65">
       <c r="A3" s="19" t="str">
         <f ca="1">TEXT(NOW(),"HH:mm")</f>
-        <v>04:55</v>
+        <v>23:57</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="17" t="s">
@@ -7102,7 +6487,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B4" t="str">
         <f t="shared" ref="B4:B67" si="1">TEXT($C4, "HH:mm")</f>
@@ -7181,7 +6566,7 @@
     <row r="5" spans="1:65">
       <c r="A5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B5" t="str">
         <f t="shared" si="1"/>
@@ -7260,7 +6645,7 @@
     <row r="6" spans="1:65">
       <c r="A6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B6" t="str">
         <f t="shared" si="1"/>
@@ -7339,7 +6724,7 @@
     <row r="7" spans="1:65">
       <c r="A7" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B7" t="str">
         <f t="shared" si="1"/>
@@ -7418,7 +6803,7 @@
     <row r="8" spans="1:65">
       <c r="A8" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B8" t="str">
         <f t="shared" si="1"/>
@@ -7497,7 +6882,7 @@
     <row r="9" spans="1:65">
       <c r="A9" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B9" t="str">
         <f t="shared" si="1"/>
@@ -7576,7 +6961,7 @@
     <row r="10" spans="1:65">
       <c r="A10" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B10" t="str">
         <f t="shared" si="1"/>
@@ -7655,7 +7040,7 @@
     <row r="11" spans="1:65">
       <c r="A11" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B11" t="str">
         <f t="shared" si="1"/>
@@ -7734,7 +7119,7 @@
     <row r="12" spans="1:65">
       <c r="A12" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B12" t="str">
         <f t="shared" si="1"/>
@@ -7813,7 +7198,7 @@
     <row r="13" spans="1:65">
       <c r="A13" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B13" t="str">
         <f t="shared" si="1"/>
@@ -7892,7 +7277,7 @@
     <row r="14" spans="1:65">
       <c r="A14" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B14" t="str">
         <f t="shared" si="1"/>
@@ -7971,7 +7356,7 @@
     <row r="15" spans="1:65">
       <c r="A15" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B15" t="str">
         <f t="shared" si="1"/>
@@ -8050,7 +7435,7 @@
     <row r="16" spans="1:65">
       <c r="A16" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B16" t="str">
         <f t="shared" si="1"/>
@@ -8129,7 +7514,7 @@
     <row r="17" spans="1:65">
       <c r="A17" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B17" t="str">
         <f t="shared" si="1"/>
@@ -8208,7 +7593,7 @@
     <row r="18" spans="1:65">
       <c r="A18" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B18" t="str">
         <f t="shared" si="1"/>
@@ -8287,7 +7672,7 @@
     <row r="19" spans="1:65">
       <c r="A19" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B19" t="str">
         <f t="shared" si="1"/>
@@ -8366,7 +7751,7 @@
     <row r="20" spans="1:65">
       <c r="A20" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B20" t="str">
         <f t="shared" si="1"/>
@@ -8445,7 +7830,7 @@
     <row r="21" spans="1:65">
       <c r="A21" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B21" t="str">
         <f t="shared" si="1"/>
@@ -8524,7 +7909,7 @@
     <row r="22" spans="1:65">
       <c r="A22" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B22" t="str">
         <f t="shared" si="1"/>
@@ -8603,7 +7988,7 @@
     <row r="23" spans="1:65">
       <c r="A23" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B23" t="str">
         <f t="shared" si="1"/>
@@ -8682,7 +8067,7 @@
     <row r="24" spans="1:65">
       <c r="A24" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B24" t="str">
         <f t="shared" si="1"/>
@@ -8761,7 +8146,7 @@
     <row r="25" spans="1:65">
       <c r="A25" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B25" t="str">
         <f t="shared" si="1"/>
@@ -8840,7 +8225,7 @@
     <row r="26" spans="1:65">
       <c r="A26" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B26" t="str">
         <f t="shared" si="1"/>
@@ -8919,7 +8304,7 @@
     <row r="27" spans="1:65">
       <c r="A27" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B27" t="str">
         <f t="shared" si="1"/>
@@ -8998,7 +8383,7 @@
     <row r="28" spans="1:65">
       <c r="A28" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B28" t="str">
         <f t="shared" si="1"/>
@@ -9079,7 +8464,7 @@
     <row r="29" spans="1:65">
       <c r="A29" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B29" t="str">
         <f t="shared" si="1"/>
@@ -9160,7 +8545,7 @@
     <row r="30" spans="1:65">
       <c r="A30" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B30" t="str">
         <f t="shared" si="1"/>
@@ -9241,7 +8626,7 @@
     <row r="31" spans="1:65">
       <c r="A31" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B31" t="str">
         <f t="shared" si="1"/>
@@ -9320,7 +8705,7 @@
     <row r="32" spans="1:65">
       <c r="A32" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B32" t="str">
         <f t="shared" si="1"/>
@@ -9399,7 +8784,7 @@
     <row r="33" spans="1:65">
       <c r="A33" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B33" t="str">
         <f t="shared" si="1"/>
@@ -9478,7 +8863,7 @@
     <row r="34" spans="1:65">
       <c r="A34" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B34" t="str">
         <f t="shared" si="1"/>
@@ -9559,7 +8944,7 @@
     <row r="35" spans="1:65">
       <c r="A35" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B35" t="str">
         <f t="shared" si="1"/>
@@ -9640,7 +9025,7 @@
     <row r="36" spans="1:65">
       <c r="A36" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B36" t="str">
         <f t="shared" si="1"/>
@@ -9721,7 +9106,7 @@
     <row r="37" spans="1:65">
       <c r="A37" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B37" t="str">
         <f t="shared" si="1"/>
@@ -9800,7 +9185,7 @@
     <row r="38" spans="1:65">
       <c r="A38" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B38" t="str">
         <f t="shared" si="1"/>
@@ -9879,7 +9264,7 @@
     <row r="39" spans="1:65">
       <c r="A39" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B39" t="str">
         <f t="shared" si="1"/>
@@ -9958,7 +9343,7 @@
     <row r="40" spans="1:65">
       <c r="A40" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B40" t="str">
         <f t="shared" si="1"/>
@@ -10037,7 +9422,7 @@
     <row r="41" spans="1:65">
       <c r="A41" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B41" t="str">
         <f t="shared" si="1"/>
@@ -10116,7 +9501,7 @@
     <row r="42" spans="1:65">
       <c r="A42" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B42" t="str">
         <f t="shared" si="1"/>
@@ -10197,7 +9582,7 @@
     <row r="43" spans="1:65">
       <c r="A43" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B43" t="str">
         <f t="shared" si="1"/>
@@ -10278,7 +9663,7 @@
     <row r="44" spans="1:65">
       <c r="A44" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B44" t="str">
         <f t="shared" si="1"/>
@@ -10357,7 +9742,7 @@
     <row r="45" spans="1:65">
       <c r="A45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B45" t="str">
         <f t="shared" si="1"/>
@@ -10436,7 +9821,7 @@
     <row r="46" spans="1:65">
       <c r="A46" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B46" t="str">
         <f t="shared" si="1"/>
@@ -10515,7 +9900,7 @@
     <row r="47" spans="1:65">
       <c r="A47" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B47" t="str">
         <f t="shared" si="1"/>
@@ -10594,7 +9979,7 @@
     <row r="48" spans="1:65">
       <c r="A48" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B48" t="str">
         <f t="shared" si="1"/>
@@ -10673,7 +10058,7 @@
     <row r="49" spans="1:65">
       <c r="A49" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B49" t="str">
         <f t="shared" si="1"/>
@@ -10754,7 +10139,7 @@
     <row r="50" spans="1:65">
       <c r="A50" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B50" t="str">
         <f t="shared" si="1"/>
@@ -10835,7 +10220,7 @@
     <row r="51" spans="1:65">
       <c r="A51" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B51" t="str">
         <f t="shared" si="1"/>
@@ -10914,7 +10299,7 @@
     <row r="52" spans="1:65">
       <c r="A52" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B52" t="str">
         <f t="shared" si="1"/>
@@ -10993,7 +10378,7 @@
     <row r="53" spans="1:65">
       <c r="A53" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B53" t="str">
         <f t="shared" si="1"/>
@@ -11072,7 +10457,7 @@
     <row r="54" spans="1:65">
       <c r="A54" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B54" t="str">
         <f t="shared" si="1"/>
@@ -11151,7 +10536,7 @@
     <row r="55" spans="1:65">
       <c r="A55" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B55" t="str">
         <f t="shared" si="1"/>
@@ -11230,7 +10615,7 @@
     <row r="56" spans="1:65">
       <c r="A56" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B56" t="str">
         <f t="shared" si="1"/>
@@ -11311,7 +10696,7 @@
     <row r="57" spans="1:65">
       <c r="A57" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B57" t="str">
         <f t="shared" si="1"/>
@@ -11390,7 +10775,7 @@
     <row r="58" spans="1:65">
       <c r="A58" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B58" t="str">
         <f t="shared" si="1"/>
@@ -11471,7 +10856,7 @@
     <row r="59" spans="1:65">
       <c r="A59" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B59" t="str">
         <f t="shared" si="1"/>
@@ -11550,7 +10935,7 @@
     <row r="60" spans="1:65">
       <c r="A60" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B60" t="str">
         <f t="shared" si="1"/>
@@ -11629,7 +11014,7 @@
     <row r="61" spans="1:65">
       <c r="A61" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B61" t="str">
         <f t="shared" si="1"/>
@@ -11708,7 +11093,7 @@
     <row r="62" spans="1:65">
       <c r="A62" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B62" t="str">
         <f t="shared" si="1"/>
@@ -11787,7 +11172,7 @@
     <row r="63" spans="1:65">
       <c r="A63" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B63" t="str">
         <f t="shared" si="1"/>
@@ -11866,7 +11251,7 @@
     <row r="64" spans="1:65">
       <c r="A64" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B64" t="str">
         <f t="shared" si="1"/>
@@ -11947,7 +11332,7 @@
     <row r="65" spans="1:65">
       <c r="A65" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B65" t="str">
         <f t="shared" si="1"/>
@@ -12026,7 +11411,7 @@
     <row r="66" spans="1:65">
       <c r="A66" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B66" t="str">
         <f t="shared" si="1"/>
@@ -12105,7 +11490,7 @@
     <row r="67" spans="1:65">
       <c r="A67" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B67" t="str">
         <f t="shared" si="1"/>
@@ -12187,7 +11572,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B68" t="str">
         <f t="shared" ref="B68:B131" si="3">TEXT($C68, "HH:mm")</f>
@@ -12266,7 +11651,7 @@
     <row r="69" spans="1:65">
       <c r="A69" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B69" t="str">
         <f t="shared" si="3"/>
@@ -12345,7 +11730,7 @@
     <row r="70" spans="1:65">
       <c r="A70" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B70" t="str">
         <f t="shared" si="3"/>
@@ -12424,7 +11809,7 @@
     <row r="71" spans="1:65">
       <c r="A71" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B71" t="str">
         <f t="shared" si="3"/>
@@ -12503,7 +11888,7 @@
     <row r="72" spans="1:65">
       <c r="A72" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B72" t="str">
         <f t="shared" si="3"/>
@@ -12582,7 +11967,7 @@
     <row r="73" spans="1:65">
       <c r="A73" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B73" t="str">
         <f t="shared" si="3"/>
@@ -12661,7 +12046,7 @@
     <row r="74" spans="1:65">
       <c r="A74" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B74" t="str">
         <f t="shared" si="3"/>
@@ -12740,7 +12125,7 @@
     <row r="75" spans="1:65">
       <c r="A75" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B75" t="str">
         <f t="shared" si="3"/>
@@ -12819,7 +12204,7 @@
     <row r="76" spans="1:65">
       <c r="A76" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B76" t="str">
         <f t="shared" si="3"/>
@@ -12898,7 +12283,7 @@
     <row r="77" spans="1:65">
       <c r="A77" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B77" t="str">
         <f t="shared" si="3"/>
@@ -12977,7 +12362,7 @@
     <row r="78" spans="1:65">
       <c r="A78" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B78" t="str">
         <f t="shared" si="3"/>
@@ -13056,7 +12441,7 @@
     <row r="79" spans="1:65">
       <c r="A79" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B79" t="str">
         <f t="shared" si="3"/>
@@ -13135,7 +12520,7 @@
     <row r="80" spans="1:65">
       <c r="A80" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B80" t="str">
         <f t="shared" si="3"/>
@@ -13214,7 +12599,7 @@
     <row r="81" spans="1:65">
       <c r="A81" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B81" t="str">
         <f t="shared" si="3"/>
@@ -13293,7 +12678,7 @@
     <row r="82" spans="1:65">
       <c r="A82" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B82" t="str">
         <f t="shared" si="3"/>
@@ -13372,7 +12757,7 @@
     <row r="83" spans="1:65">
       <c r="A83" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B83" t="str">
         <f t="shared" si="3"/>
@@ -13451,7 +12836,7 @@
     <row r="84" spans="1:65">
       <c r="A84" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B84" t="str">
         <f t="shared" si="3"/>
@@ -13530,7 +12915,7 @@
     <row r="85" spans="1:65">
       <c r="A85" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B85" t="str">
         <f t="shared" si="3"/>
@@ -13609,7 +12994,7 @@
     <row r="86" spans="1:65">
       <c r="A86" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B86" t="str">
         <f t="shared" si="3"/>
@@ -13688,7 +13073,7 @@
     <row r="87" spans="1:65">
       <c r="A87" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B87" t="str">
         <f t="shared" si="3"/>
@@ -13767,7 +13152,7 @@
     <row r="88" spans="1:65">
       <c r="A88" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B88" t="str">
         <f t="shared" si="3"/>
@@ -13846,7 +13231,7 @@
     <row r="89" spans="1:65">
       <c r="A89" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B89" t="str">
         <f t="shared" si="3"/>
@@ -13925,7 +13310,7 @@
     <row r="90" spans="1:65">
       <c r="A90" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B90" t="str">
         <f t="shared" si="3"/>
@@ -14004,7 +13389,7 @@
     <row r="91" spans="1:65">
       <c r="A91" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B91" t="str">
         <f t="shared" si="3"/>
@@ -14083,7 +13468,7 @@
     <row r="92" spans="1:65">
       <c r="A92" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B92" t="str">
         <f t="shared" si="3"/>
@@ -14162,7 +13547,7 @@
     <row r="93" spans="1:65">
       <c r="A93" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B93" t="str">
         <f t="shared" si="3"/>
@@ -14241,7 +13626,7 @@
     <row r="94" spans="1:65">
       <c r="A94" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B94" t="str">
         <f t="shared" si="3"/>
@@ -14320,7 +13705,7 @@
     <row r="95" spans="1:65">
       <c r="A95" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B95" t="str">
         <f t="shared" si="3"/>
@@ -14399,7 +13784,7 @@
     <row r="96" spans="1:65">
       <c r="A96" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B96" t="str">
         <f t="shared" si="3"/>
@@ -14478,7 +13863,7 @@
     <row r="97" spans="1:65">
       <c r="A97" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B97" t="str">
         <f t="shared" si="3"/>
@@ -14557,7 +13942,7 @@
     <row r="98" spans="1:65">
       <c r="A98" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B98" t="str">
         <f t="shared" si="3"/>
@@ -14636,7 +14021,7 @@
     <row r="99" spans="1:65">
       <c r="A99" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B99" t="str">
         <f t="shared" si="3"/>
@@ -14715,7 +14100,7 @@
     <row r="100" spans="1:65">
       <c r="A100" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B100" t="str">
         <f t="shared" si="3"/>
@@ -14796,7 +14181,7 @@
     <row r="101" spans="1:65">
       <c r="A101" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B101" t="str">
         <f t="shared" si="3"/>
@@ -14875,7 +14260,7 @@
     <row r="102" spans="1:65">
       <c r="A102" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B102" t="str">
         <f t="shared" si="3"/>
@@ -14954,7 +14339,7 @@
     <row r="103" spans="1:65">
       <c r="A103" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B103" t="str">
         <f t="shared" si="3"/>
@@ -15033,7 +14418,7 @@
     <row r="104" spans="1:65">
       <c r="A104" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B104" t="str">
         <f t="shared" si="3"/>
@@ -15112,7 +14497,7 @@
     <row r="105" spans="1:65">
       <c r="A105" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B105" t="str">
         <f t="shared" si="3"/>
@@ -15191,7 +14576,7 @@
     <row r="106" spans="1:65">
       <c r="A106" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B106" t="str">
         <f t="shared" si="3"/>
@@ -15272,7 +14657,7 @@
     <row r="107" spans="1:65">
       <c r="A107" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B107" t="str">
         <f t="shared" si="3"/>
@@ -15353,7 +14738,7 @@
     <row r="108" spans="1:65">
       <c r="A108" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B108" t="str">
         <f t="shared" si="3"/>
@@ -15432,7 +14817,7 @@
     <row r="109" spans="1:65">
       <c r="A109" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B109" t="str">
         <f t="shared" si="3"/>
@@ -15511,7 +14896,7 @@
     <row r="110" spans="1:65">
       <c r="A110" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B110" t="str">
         <f t="shared" si="3"/>
@@ -15590,7 +14975,7 @@
     <row r="111" spans="1:65">
       <c r="A111" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B111" t="str">
         <f t="shared" si="3"/>
@@ -15669,7 +15054,7 @@
     <row r="112" spans="1:65">
       <c r="A112" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B112" t="str">
         <f t="shared" si="3"/>
@@ -15750,7 +15135,7 @@
     <row r="113" spans="1:65">
       <c r="A113" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B113" t="str">
         <f t="shared" si="3"/>
@@ -15829,7 +15214,7 @@
     <row r="114" spans="1:65">
       <c r="A114" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B114" t="str">
         <f t="shared" si="3"/>
@@ -15908,7 +15293,7 @@
     <row r="115" spans="1:65">
       <c r="A115" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B115" t="str">
         <f t="shared" si="3"/>
@@ -15987,7 +15372,7 @@
     <row r="116" spans="1:65">
       <c r="A116" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B116" t="str">
         <f t="shared" si="3"/>
@@ -16066,7 +15451,7 @@
     <row r="117" spans="1:65">
       <c r="A117" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B117" t="str">
         <f t="shared" si="3"/>
@@ -16145,7 +15530,7 @@
     <row r="118" spans="1:65">
       <c r="A118" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B118" t="str">
         <f t="shared" si="3"/>
@@ -16224,7 +15609,7 @@
     <row r="119" spans="1:65">
       <c r="A119" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B119" t="str">
         <f t="shared" si="3"/>
@@ -16303,7 +15688,7 @@
     <row r="120" spans="1:65">
       <c r="A120" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B120" t="str">
         <f t="shared" si="3"/>
@@ -16382,7 +15767,7 @@
     <row r="121" spans="1:65">
       <c r="A121" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B121" t="str">
         <f t="shared" si="3"/>
@@ -16461,7 +15846,7 @@
     <row r="122" spans="1:65">
       <c r="A122" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B122" t="str">
         <f t="shared" si="3"/>
@@ -16540,7 +15925,7 @@
     <row r="123" spans="1:65">
       <c r="A123" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B123" t="str">
         <f t="shared" si="3"/>
@@ -16619,7 +16004,7 @@
     <row r="124" spans="1:65">
       <c r="A124" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B124" t="str">
         <f t="shared" si="3"/>
@@ -16700,7 +16085,7 @@
     <row r="125" spans="1:65">
       <c r="A125" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B125" t="str">
         <f t="shared" si="3"/>
@@ -16781,7 +16166,7 @@
     <row r="126" spans="1:65">
       <c r="A126" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B126" t="str">
         <f t="shared" si="3"/>
@@ -16860,7 +16245,7 @@
     <row r="127" spans="1:65">
       <c r="A127" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B127" t="str">
         <f t="shared" si="3"/>
@@ -16939,7 +16324,7 @@
     <row r="128" spans="1:65">
       <c r="A128" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B128" t="str">
         <f t="shared" si="3"/>
@@ -17018,7 +16403,7 @@
     <row r="129" spans="1:65">
       <c r="A129" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B129" t="str">
         <f t="shared" si="3"/>
@@ -17097,7 +16482,7 @@
     <row r="130" spans="1:65">
       <c r="A130" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B130" t="str">
         <f t="shared" si="3"/>
@@ -17176,7 +16561,7 @@
     <row r="131" spans="1:65">
       <c r="A131" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B131" t="str">
         <f t="shared" si="3"/>
@@ -17258,7 +16643,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B132" t="str">
         <f t="shared" ref="B132:B168" si="5">TEXT($C132, "HH:mm")</f>
@@ -17337,7 +16722,7 @@
     <row r="133" spans="1:65">
       <c r="A133" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B133" t="str">
         <f t="shared" si="5"/>
@@ -17416,7 +16801,7 @@
     <row r="134" spans="1:65">
       <c r="A134" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B134" t="str">
         <f t="shared" si="5"/>
@@ -17495,7 +16880,7 @@
     <row r="135" spans="1:65">
       <c r="A135" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B135" t="str">
         <f t="shared" si="5"/>
@@ -17574,7 +16959,7 @@
     <row r="136" spans="1:65">
       <c r="A136" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B136" t="str">
         <f t="shared" si="5"/>
@@ -17655,7 +17040,7 @@
     <row r="137" spans="1:65">
       <c r="A137" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B137" t="str">
         <f t="shared" si="5"/>
@@ -17736,7 +17121,7 @@
     <row r="138" spans="1:65">
       <c r="A138" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B138" t="str">
         <f t="shared" si="5"/>
@@ -17815,7 +17200,7 @@
     <row r="139" spans="1:65">
       <c r="A139" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B139" t="str">
         <f t="shared" si="5"/>
@@ -17894,7 +17279,7 @@
     <row r="140" spans="1:65">
       <c r="A140" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B140" t="str">
         <f t="shared" si="5"/>
@@ -17973,7 +17358,7 @@
     <row r="141" spans="1:65">
       <c r="A141" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B141" t="str">
         <f t="shared" si="5"/>
@@ -18052,7 +17437,7 @@
     <row r="142" spans="1:65">
       <c r="A142" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B142" t="str">
         <f t="shared" si="5"/>
@@ -18131,7 +17516,7 @@
     <row r="143" spans="1:65">
       <c r="A143" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B143" t="str">
         <f t="shared" si="5"/>
@@ -18210,7 +17595,7 @@
     <row r="144" spans="1:65">
       <c r="A144" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B144" t="str">
         <f t="shared" si="5"/>
@@ -18289,7 +17674,7 @@
     <row r="145" spans="1:65">
       <c r="A145" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B145" t="str">
         <f t="shared" si="5"/>
@@ -18368,7 +17753,7 @@
     <row r="146" spans="1:65">
       <c r="A146" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B146" t="str">
         <f t="shared" si="5"/>
@@ -18447,7 +17832,7 @@
     <row r="147" spans="1:65">
       <c r="A147" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B147" t="str">
         <f t="shared" si="5"/>
@@ -18526,7 +17911,7 @@
     <row r="148" spans="1:65">
       <c r="A148" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B148" t="str">
         <f t="shared" si="5"/>
@@ -18607,7 +17992,7 @@
     <row r="149" spans="1:65">
       <c r="A149" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B149" t="str">
         <f t="shared" si="5"/>
@@ -18686,7 +18071,7 @@
     <row r="150" spans="1:65">
       <c r="A150" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B150" t="str">
         <f t="shared" si="5"/>
@@ -18765,7 +18150,7 @@
     <row r="151" spans="1:65">
       <c r="A151" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B151" t="str">
         <f t="shared" si="5"/>
@@ -18844,7 +18229,7 @@
     <row r="152" spans="1:65">
       <c r="A152" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B152" t="str">
         <f t="shared" si="5"/>
@@ -18923,7 +18308,7 @@
     <row r="153" spans="1:65">
       <c r="A153" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B153" t="str">
         <f t="shared" si="5"/>
@@ -19002,7 +18387,7 @@
     <row r="154" spans="1:65">
       <c r="A154" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B154" t="str">
         <f t="shared" si="5"/>
@@ -19081,7 +18466,7 @@
     <row r="155" spans="1:65">
       <c r="A155" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B155" t="str">
         <f t="shared" si="5"/>
@@ -19160,7 +18545,7 @@
     <row r="156" spans="1:65">
       <c r="A156" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B156" t="str">
         <f t="shared" si="5"/>
@@ -19239,7 +18624,7 @@
     <row r="157" spans="1:65">
       <c r="A157" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B157" t="str">
         <f t="shared" si="5"/>
@@ -19318,7 +18703,7 @@
     <row r="158" spans="1:65">
       <c r="A158" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B158" t="str">
         <f t="shared" si="5"/>
@@ -19397,7 +18782,7 @@
     <row r="159" spans="1:65">
       <c r="A159" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B159" t="str">
         <f t="shared" si="5"/>
@@ -19476,7 +18861,7 @@
     <row r="160" spans="1:65">
       <c r="A160" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B160" t="str">
         <f t="shared" si="5"/>
@@ -19555,7 +18940,7 @@
     <row r="161" spans="1:65">
       <c r="A161" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B161" t="str">
         <f t="shared" si="5"/>
@@ -19634,7 +19019,7 @@
     <row r="162" spans="1:65">
       <c r="A162" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B162" t="str">
         <f t="shared" si="5"/>
@@ -19713,7 +19098,7 @@
     <row r="163" spans="1:65">
       <c r="A163" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B163" t="str">
         <f t="shared" si="5"/>
@@ -19792,7 +19177,7 @@
     <row r="164" spans="1:65">
       <c r="A164" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B164" t="str">
         <f t="shared" si="5"/>
@@ -19871,7 +19256,7 @@
     <row r="165" spans="1:65">
       <c r="A165" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B165" t="str">
         <f t="shared" si="5"/>
@@ -19950,7 +19335,7 @@
     <row r="166" spans="1:65">
       <c r="A166" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B166" t="str">
         <f t="shared" si="5"/>
@@ -20031,7 +19416,7 @@
     <row r="167" spans="1:65">
       <c r="A167" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B167" t="str">
         <f t="shared" si="5"/>
@@ -20110,7 +19495,7 @@
     <row r="168" spans="1:65">
       <c r="A168" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B168" t="str">
         <f t="shared" si="5"/>
@@ -20192,7 +19577,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B169" t="str">
         <f>TEXT($C169, "HH:mm")</f>
@@ -20274,7 +19659,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B170" t="str">
         <f t="shared" ref="B170:B233" si="7">TEXT($C170, "HH:mm")</f>
@@ -20353,7 +19738,7 @@
     <row r="171" spans="1:65">
       <c r="A171" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B171" t="str">
         <f t="shared" si="7"/>
@@ -20432,7 +19817,7 @@
     <row r="172" spans="1:65">
       <c r="A172" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B172" t="str">
         <f t="shared" si="7"/>
@@ -20513,7 +19898,7 @@
     <row r="173" spans="1:65">
       <c r="A173" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B173" t="str">
         <f t="shared" si="7"/>
@@ -20592,7 +19977,7 @@
     <row r="174" spans="1:65">
       <c r="A174" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B174" t="str">
         <f t="shared" si="7"/>
@@ -20671,7 +20056,7 @@
     <row r="175" spans="1:65">
       <c r="A175" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B175" t="str">
         <f t="shared" si="7"/>
@@ -20750,7 +20135,7 @@
     <row r="176" spans="1:65">
       <c r="A176" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B176" t="str">
         <f t="shared" si="7"/>
@@ -20829,7 +20214,7 @@
     <row r="177" spans="1:65">
       <c r="A177" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B177" t="str">
         <f t="shared" si="7"/>
@@ -20908,7 +20293,7 @@
     <row r="178" spans="1:65">
       <c r="A178" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B178" t="str">
         <f t="shared" si="7"/>
@@ -20989,7 +20374,7 @@
     <row r="179" spans="1:65">
       <c r="A179" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B179" t="str">
         <f t="shared" si="7"/>
@@ -21068,7 +20453,7 @@
     <row r="180" spans="1:65">
       <c r="A180" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B180" t="str">
         <f t="shared" si="7"/>
@@ -21147,7 +20532,7 @@
     <row r="181" spans="1:65">
       <c r="A181" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B181" t="str">
         <f t="shared" si="7"/>
@@ -21228,7 +20613,7 @@
     <row r="182" spans="1:65">
       <c r="A182" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B182" t="str">
         <f t="shared" si="7"/>
@@ -21309,7 +20694,7 @@
     <row r="183" spans="1:65">
       <c r="A183" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B183" t="str">
         <f t="shared" si="7"/>
@@ -21390,7 +20775,7 @@
     <row r="184" spans="1:65">
       <c r="A184" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B184" t="str">
         <f t="shared" si="7"/>
@@ -21473,7 +20858,7 @@
     <row r="185" spans="1:65">
       <c r="A185" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B185" t="str">
         <f t="shared" si="7"/>
@@ -21554,7 +20939,7 @@
     <row r="186" spans="1:65">
       <c r="A186" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B186" t="str">
         <f t="shared" si="7"/>
@@ -21635,7 +21020,7 @@
     <row r="187" spans="1:65">
       <c r="A187" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B187" t="str">
         <f t="shared" si="7"/>
@@ -21716,7 +21101,7 @@
     <row r="188" spans="1:65">
       <c r="A188" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B188" t="str">
         <f t="shared" si="7"/>
@@ -21797,7 +21182,7 @@
     <row r="189" spans="1:65">
       <c r="A189" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B189" t="str">
         <f t="shared" si="7"/>
@@ -21878,7 +21263,7 @@
     <row r="190" spans="1:65">
       <c r="A190" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B190" t="str">
         <f t="shared" si="7"/>
@@ -21961,7 +21346,7 @@
     <row r="191" spans="1:65">
       <c r="A191" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B191" t="str">
         <f t="shared" si="7"/>
@@ -22044,7 +21429,7 @@
     <row r="192" spans="1:65">
       <c r="A192" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B192" t="str">
         <f t="shared" si="7"/>
@@ -22127,7 +21512,7 @@
     <row r="193" spans="1:65">
       <c r="A193" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B193" t="str">
         <f t="shared" si="7"/>
@@ -22210,7 +21595,7 @@
     <row r="194" spans="1:65">
       <c r="A194" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B194" t="str">
         <f t="shared" si="7"/>
@@ -22291,7 +21676,7 @@
     <row r="195" spans="1:65">
       <c r="A195" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B195" t="str">
         <f t="shared" si="7"/>
@@ -22372,7 +21757,7 @@
     <row r="196" spans="1:65">
       <c r="A196" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B196" t="str">
         <f t="shared" si="7"/>
@@ -22455,7 +21840,7 @@
     <row r="197" spans="1:65">
       <c r="A197" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B197" t="str">
         <f t="shared" si="7"/>
@@ -22534,7 +21919,7 @@
     <row r="198" spans="1:65">
       <c r="A198" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B198" t="str">
         <f t="shared" si="7"/>
@@ -22613,7 +21998,7 @@
     <row r="199" spans="1:65">
       <c r="A199" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B199" t="str">
         <f t="shared" si="7"/>
@@ -22692,7 +22077,7 @@
     <row r="200" spans="1:65">
       <c r="A200" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B200" t="str">
         <f t="shared" si="7"/>
@@ -22771,7 +22156,7 @@
     <row r="201" spans="1:65">
       <c r="A201" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B201" t="str">
         <f t="shared" si="7"/>
@@ -22850,7 +22235,7 @@
     <row r="202" spans="1:65">
       <c r="A202" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B202" t="str">
         <f t="shared" si="7"/>
@@ -22931,7 +22316,7 @@
     <row r="203" spans="1:65">
       <c r="A203" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B203" t="str">
         <f t="shared" si="7"/>
@@ -23010,7 +22395,7 @@
     <row r="204" spans="1:65">
       <c r="A204" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B204" t="str">
         <f t="shared" si="7"/>
@@ -23089,7 +22474,7 @@
     <row r="205" spans="1:65">
       <c r="A205" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B205" t="str">
         <f t="shared" si="7"/>
@@ -23168,7 +22553,7 @@
     <row r="206" spans="1:65">
       <c r="A206" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B206" t="str">
         <f t="shared" si="7"/>
@@ -23247,7 +22632,7 @@
     <row r="207" spans="1:65">
       <c r="A207" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B207" t="str">
         <f t="shared" si="7"/>
@@ -23326,7 +22711,7 @@
     <row r="208" spans="1:65">
       <c r="A208" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B208" t="str">
         <f t="shared" si="7"/>
@@ -23407,7 +22792,7 @@
     <row r="209" spans="1:65">
       <c r="A209" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B209" t="str">
         <f t="shared" si="7"/>
@@ -23486,7 +22871,7 @@
     <row r="210" spans="1:65">
       <c r="A210" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B210" t="str">
         <f t="shared" si="7"/>
@@ -23565,7 +22950,7 @@
     <row r="211" spans="1:65">
       <c r="A211" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B211" t="str">
         <f t="shared" si="7"/>
@@ -23646,7 +23031,7 @@
     <row r="212" spans="1:65">
       <c r="A212" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B212" t="str">
         <f t="shared" si="7"/>
@@ -23725,7 +23110,7 @@
     <row r="213" spans="1:65">
       <c r="A213" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B213" t="str">
         <f t="shared" si="7"/>
@@ -23804,7 +23189,7 @@
     <row r="214" spans="1:65">
       <c r="A214" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B214" t="str">
         <f t="shared" si="7"/>
@@ -23883,7 +23268,7 @@
     <row r="215" spans="1:65">
       <c r="A215" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B215" t="str">
         <f t="shared" si="7"/>
@@ -23962,7 +23347,7 @@
     <row r="216" spans="1:65">
       <c r="A216" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B216" t="str">
         <f t="shared" si="7"/>
@@ -24041,7 +23426,7 @@
     <row r="217" spans="1:65">
       <c r="A217" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B217" t="str">
         <f t="shared" si="7"/>
@@ -24120,7 +23505,7 @@
     <row r="218" spans="1:65">
       <c r="A218" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B218" t="str">
         <f t="shared" si="7"/>
@@ -24199,7 +23584,7 @@
     <row r="219" spans="1:65">
       <c r="A219" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B219" t="str">
         <f t="shared" si="7"/>
@@ -24278,7 +23663,7 @@
     <row r="220" spans="1:65">
       <c r="A220" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B220" t="str">
         <f t="shared" si="7"/>
@@ -24359,7 +23744,7 @@
     <row r="221" spans="1:65">
       <c r="A221" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B221" t="str">
         <f t="shared" si="7"/>
@@ -24438,7 +23823,7 @@
     <row r="222" spans="1:65">
       <c r="A222" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B222" t="str">
         <f t="shared" si="7"/>
@@ -24517,7 +23902,7 @@
     <row r="223" spans="1:65">
       <c r="A223" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B223" t="str">
         <f t="shared" si="7"/>
@@ -24596,7 +23981,7 @@
     <row r="224" spans="1:65">
       <c r="A224" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B224" t="str">
         <f t="shared" si="7"/>
@@ -24675,7 +24060,7 @@
     <row r="225" spans="1:65">
       <c r="A225" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B225" t="str">
         <f t="shared" si="7"/>
@@ -24754,7 +24139,7 @@
     <row r="226" spans="1:65">
       <c r="A226" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B226" t="str">
         <f t="shared" si="7"/>
@@ -24833,7 +24218,7 @@
     <row r="227" spans="1:65">
       <c r="A227" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B227" t="str">
         <f t="shared" si="7"/>
@@ -24912,7 +24297,7 @@
     <row r="228" spans="1:65">
       <c r="A228" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B228" t="str">
         <f t="shared" si="7"/>
@@ -24991,7 +24376,7 @@
     <row r="229" spans="1:65">
       <c r="A229" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B229" t="str">
         <f t="shared" si="7"/>
@@ -25070,7 +24455,7 @@
     <row r="230" spans="1:65">
       <c r="A230" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B230" t="str">
         <f t="shared" si="7"/>
@@ -25149,7 +24534,7 @@
     <row r="231" spans="1:65">
       <c r="A231" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B231" t="str">
         <f t="shared" si="7"/>
@@ -25228,7 +24613,7 @@
     <row r="232" spans="1:65">
       <c r="A232" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B232" t="str">
         <f t="shared" si="7"/>
@@ -25307,7 +24692,7 @@
     <row r="233" spans="1:65">
       <c r="A233" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B233" t="str">
         <f t="shared" si="7"/>
@@ -25389,7 +24774,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B234" t="str">
         <f t="shared" ref="B234:B291" si="9">TEXT($C234, "HH:mm")</f>
@@ -25468,7 +24853,7 @@
     <row r="235" spans="1:65">
       <c r="A235" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B235" t="str">
         <f t="shared" si="9"/>
@@ -25547,7 +24932,7 @@
     <row r="236" spans="1:65">
       <c r="A236" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B236" t="str">
         <f t="shared" si="9"/>
@@ -25626,7 +25011,7 @@
     <row r="237" spans="1:65">
       <c r="A237" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B237" t="str">
         <f t="shared" si="9"/>
@@ -25705,7 +25090,7 @@
     <row r="238" spans="1:65">
       <c r="A238" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B238" t="str">
         <f t="shared" si="9"/>
@@ -25784,7 +25169,7 @@
     <row r="239" spans="1:65">
       <c r="A239" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B239" t="str">
         <f t="shared" si="9"/>
@@ -25863,7 +25248,7 @@
     <row r="240" spans="1:65">
       <c r="A240" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B240" t="str">
         <f t="shared" si="9"/>
@@ -25942,7 +25327,7 @@
     <row r="241" spans="1:65">
       <c r="A241" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B241" t="str">
         <f t="shared" si="9"/>
@@ -26021,7 +25406,7 @@
     <row r="242" spans="1:65">
       <c r="A242" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B242" t="str">
         <f t="shared" si="9"/>
@@ -26100,7 +25485,7 @@
     <row r="243" spans="1:65">
       <c r="A243" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B243" t="str">
         <f t="shared" si="9"/>
@@ -26179,7 +25564,7 @@
     <row r="244" spans="1:65">
       <c r="A244" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B244" t="str">
         <f t="shared" si="9"/>
@@ -26258,7 +25643,7 @@
     <row r="245" spans="1:65">
       <c r="A245" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B245" t="str">
         <f t="shared" si="9"/>
@@ -26337,7 +25722,7 @@
     <row r="246" spans="1:65">
       <c r="A246" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B246" t="str">
         <f t="shared" si="9"/>
@@ -26416,7 +25801,7 @@
     <row r="247" spans="1:65">
       <c r="A247" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B247" t="str">
         <f t="shared" si="9"/>
@@ -26495,7 +25880,7 @@
     <row r="248" spans="1:65">
       <c r="A248" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B248" t="str">
         <f t="shared" si="9"/>
@@ -26574,7 +25959,7 @@
     <row r="249" spans="1:65">
       <c r="A249" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B249" t="str">
         <f t="shared" si="9"/>
@@ -26653,7 +26038,7 @@
     <row r="250" spans="1:65">
       <c r="A250" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B250" t="str">
         <f t="shared" si="9"/>
@@ -26732,7 +26117,7 @@
     <row r="251" spans="1:65">
       <c r="A251" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B251" t="str">
         <f t="shared" si="9"/>
@@ -26811,7 +26196,7 @@
     <row r="252" spans="1:65">
       <c r="A252" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B252" t="str">
         <f t="shared" si="9"/>
@@ -26890,7 +26275,7 @@
     <row r="253" spans="1:65">
       <c r="A253" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B253" t="str">
         <f t="shared" si="9"/>
@@ -26969,7 +26354,7 @@
     <row r="254" spans="1:65">
       <c r="A254" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B254" t="str">
         <f t="shared" si="9"/>
@@ -27048,7 +26433,7 @@
     <row r="255" spans="1:65">
       <c r="A255" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B255" t="str">
         <f t="shared" si="9"/>
@@ -27127,7 +26512,7 @@
     <row r="256" spans="1:65">
       <c r="A256" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B256" t="str">
         <f t="shared" si="9"/>
@@ -27206,7 +26591,7 @@
     <row r="257" spans="1:65">
       <c r="A257" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B257" t="str">
         <f t="shared" si="9"/>
@@ -27285,7 +26670,7 @@
     <row r="258" spans="1:65">
       <c r="A258" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B258" t="str">
         <f t="shared" si="9"/>
@@ -27364,7 +26749,7 @@
     <row r="259" spans="1:65">
       <c r="A259" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B259" t="str">
         <f t="shared" si="9"/>
@@ -27443,7 +26828,7 @@
     <row r="260" spans="1:65">
       <c r="A260" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B260" t="str">
         <f t="shared" si="9"/>
@@ -27522,7 +26907,7 @@
     <row r="261" spans="1:65">
       <c r="A261" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B261" t="str">
         <f t="shared" si="9"/>
@@ -27601,7 +26986,7 @@
     <row r="262" spans="1:65">
       <c r="A262" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B262" t="str">
         <f t="shared" si="9"/>
@@ -27680,7 +27065,7 @@
     <row r="263" spans="1:65">
       <c r="A263" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B263" t="str">
         <f t="shared" si="9"/>
@@ -27759,7 +27144,7 @@
     <row r="264" spans="1:65">
       <c r="A264" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B264" t="str">
         <f t="shared" si="9"/>
@@ -27838,7 +27223,7 @@
     <row r="265" spans="1:65">
       <c r="A265" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B265" t="str">
         <f t="shared" si="9"/>
@@ -27917,7 +27302,7 @@
     <row r="266" spans="1:65">
       <c r="A266" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B266" t="str">
         <f t="shared" si="9"/>
@@ -27996,7 +27381,7 @@
     <row r="267" spans="1:65">
       <c r="A267" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B267" t="str">
         <f t="shared" si="9"/>
@@ -28075,7 +27460,7 @@
     <row r="268" spans="1:65">
       <c r="A268" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B268" t="str">
         <f t="shared" si="9"/>
@@ -28154,7 +27539,7 @@
     <row r="269" spans="1:65">
       <c r="A269" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B269" t="str">
         <f t="shared" si="9"/>
@@ -28233,7 +27618,7 @@
     <row r="270" spans="1:65">
       <c r="A270" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B270" t="str">
         <f t="shared" si="9"/>
@@ -28312,7 +27697,7 @@
     <row r="271" spans="1:65">
       <c r="A271" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B271" t="str">
         <f t="shared" si="9"/>
@@ -28391,7 +27776,7 @@
     <row r="272" spans="1:65">
       <c r="A272" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B272" t="str">
         <f t="shared" si="9"/>
@@ -28470,7 +27855,7 @@
     <row r="273" spans="1:65">
       <c r="A273" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B273" t="str">
         <f t="shared" si="9"/>
@@ -28549,7 +27934,7 @@
     <row r="274" spans="1:65">
       <c r="A274" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B274" t="str">
         <f t="shared" si="9"/>
@@ -28628,7 +28013,7 @@
     <row r="275" spans="1:65">
       <c r="A275" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B275" t="str">
         <f t="shared" si="9"/>
@@ -28707,7 +28092,7 @@
     <row r="276" spans="1:65">
       <c r="A276" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B276" t="str">
         <f t="shared" si="9"/>
@@ -28786,7 +28171,7 @@
     <row r="277" spans="1:65">
       <c r="A277" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B277" t="str">
         <f t="shared" si="9"/>
@@ -28865,7 +28250,7 @@
     <row r="278" spans="1:65">
       <c r="A278" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B278" t="str">
         <f t="shared" si="9"/>
@@ -28944,7 +28329,7 @@
     <row r="279" spans="1:65">
       <c r="A279" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B279" t="str">
         <f t="shared" si="9"/>
@@ -29023,7 +28408,7 @@
     <row r="280" spans="1:65">
       <c r="A280" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B280" t="str">
         <f t="shared" si="9"/>
@@ -29102,7 +28487,7 @@
     <row r="281" spans="1:65">
       <c r="A281" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B281" t="str">
         <f t="shared" si="9"/>
@@ -29181,7 +28566,7 @@
     <row r="282" spans="1:65">
       <c r="A282" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B282" t="str">
         <f t="shared" si="9"/>
@@ -29260,7 +28645,7 @@
     <row r="283" spans="1:65">
       <c r="A283" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B283" t="str">
         <f t="shared" si="9"/>
@@ -29339,7 +28724,7 @@
     <row r="284" spans="1:65">
       <c r="A284" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B284" t="str">
         <f t="shared" si="9"/>
@@ -29418,7 +28803,7 @@
     <row r="285" spans="1:65">
       <c r="A285" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B285" t="str">
         <f t="shared" si="9"/>
@@ -29497,7 +28882,7 @@
     <row r="286" spans="1:65">
       <c r="A286" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B286" t="str">
         <f t="shared" si="9"/>
@@ -29576,7 +28961,7 @@
     <row r="287" spans="1:65">
       <c r="A287" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B287" t="str">
         <f t="shared" si="9"/>
@@ -29655,7 +29040,7 @@
     <row r="288" spans="1:65">
       <c r="A288" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B288" t="str">
         <f t="shared" si="9"/>
@@ -29734,7 +29119,7 @@
     <row r="289" spans="1:65">
       <c r="A289" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B289" t="str">
         <f t="shared" si="9"/>
@@ -29813,7 +29198,7 @@
     <row r="290" spans="1:65">
       <c r="A290" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B290" t="str">
         <f t="shared" si="9"/>
@@ -29892,7 +29277,7 @@
     <row r="291" spans="1:65">
       <c r="A291" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>04:55</v>
+        <v>23:55</v>
       </c>
       <c r="B291" t="str">
         <f t="shared" si="9"/>
@@ -29986,4 +29371,3601 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63958C87-2C93-43E5-8405-38AB5C73D6BE}">
+  <dimension ref="B3:B13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetData>
+    <row r="3" spans="2:2">
+      <c r="B3" s="2" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" ht="14.25">
+      <c r="B4" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2" ht="14.25">
+      <c r="B5" s="24" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" ht="14.25">
+      <c r="B6" s="23">
+        <v>4.1666666666666666E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2" ht="14.25">
+      <c r="B7" s="24" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2" ht="14.25">
+      <c r="B8" s="23">
+        <v>8.3333333333333332E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2" ht="14.25">
+      <c r="B9" s="24" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2" ht="14.25">
+      <c r="B10" s="23">
+        <v>1.3194444444444444E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2" ht="14.25">
+      <c r="B11" s="24" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2">
+      <c r="B12" s="25">
+        <v>1.7361111111111112E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2">
+      <c r="B13" t="s">
+        <v>676</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="B3" r:id="rId1" xr:uid="{1592C6E0-7587-42B0-BF1B-3FBFEDF00B08}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{316E5208-1AA2-4457-A1CF-56BEFB0E0D49}">
+  <dimension ref="C3"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="3" max="3" width="65" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="3:3" ht="54">
+      <c r="C3" s="3" t="s">
+        <v>677</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26DD176E-9EB8-44B3-9B79-201E189F863E}">
+  <dimension ref="B2:E25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="71.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:5">
+      <c r="D2" t="s">
+        <v>696</v>
+      </c>
+      <c r="E2" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5">
+      <c r="B3" s="1">
+        <v>45802</v>
+      </c>
+      <c r="C3" t="s">
+        <v>693</v>
+      </c>
+      <c r="D3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5">
+      <c r="C4" t="s">
+        <v>694</v>
+      </c>
+      <c r="D4" t="s">
+        <v>165</v>
+      </c>
+      <c r="E4" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" ht="27">
+      <c r="C5" s="3" t="s">
+        <v>695</v>
+      </c>
+      <c r="D5" t="s">
+        <v>165</v>
+      </c>
+      <c r="E5" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" ht="27">
+      <c r="C6" s="3" t="s">
+        <v>698</v>
+      </c>
+      <c r="D6" t="s">
+        <v>165</v>
+      </c>
+      <c r="E6" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5">
+      <c r="C7" t="s">
+        <v>699</v>
+      </c>
+      <c r="D7" t="s">
+        <v>165</v>
+      </c>
+      <c r="E7" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5">
+      <c r="C8" t="s">
+        <v>700</v>
+      </c>
+      <c r="D8" t="s">
+        <v>165</v>
+      </c>
+      <c r="E8" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" ht="27">
+      <c r="C9" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="D9" t="s">
+        <v>165</v>
+      </c>
+      <c r="E9" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" ht="27">
+      <c r="C10" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="D10" t="s">
+        <v>165</v>
+      </c>
+      <c r="E10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5">
+      <c r="C11" s="3" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" ht="27">
+      <c r="C12" s="3" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" ht="27">
+      <c r="C13" s="3" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" ht="27">
+      <c r="C14" s="3" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5">
+      <c r="C15" s="3" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" ht="27">
+      <c r="C16" s="3" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="17" spans="3:3">
+      <c r="C17" s="3" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="18" spans="3:3">
+      <c r="C18" s="3" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="19" spans="3:3" ht="27">
+      <c r="C19" s="3" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="20" spans="3:3" ht="27">
+      <c r="C20" s="3" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="21" spans="3:3" ht="27">
+      <c r="C21" s="3" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="22" spans="3:3" ht="27">
+      <c r="C22" s="3" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="23" spans="3:3" ht="27">
+      <c r="C23" s="3" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="24" spans="3:3" ht="27">
+      <c r="C24" s="3" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="25" spans="3:3" ht="27">
+      <c r="C25" s="3" t="s">
+        <v>717</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F88E2D65-ECA4-4EF7-BEC6-93BAB5468A01}">
+  <dimension ref="B3:C83"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetData>
+    <row r="3" spans="3:3" ht="21">
+      <c r="C3" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="4" spans="3:3">
+      <c r="C4" s="7"/>
+    </row>
+    <row r="5" spans="3:3">
+      <c r="C5" s="8" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="3:3">
+      <c r="C6" s="7"/>
+    </row>
+    <row r="7" spans="3:3">
+      <c r="C7" s="8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="3:3">
+      <c r="C8" s="7"/>
+    </row>
+    <row r="9" spans="3:3">
+      <c r="C9" s="8" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="10" spans="3:3">
+      <c r="C10" s="7"/>
+    </row>
+    <row r="11" spans="3:3">
+      <c r="C11" s="8" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="12" spans="3:3">
+      <c r="C12" s="7"/>
+    </row>
+    <row r="13" spans="3:3">
+      <c r="C13" s="8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="14" spans="3:3">
+      <c r="C14" s="7"/>
+    </row>
+    <row r="15" spans="3:3">
+      <c r="C15" s="8" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="16" spans="3:3">
+      <c r="C16" s="7"/>
+    </row>
+    <row r="17" spans="3:3">
+      <c r="C17" s="8" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="18" spans="3:3">
+      <c r="C18" s="7"/>
+    </row>
+    <row r="19" spans="3:3">
+      <c r="C19" s="8" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="20" spans="3:3">
+      <c r="C20" s="7"/>
+    </row>
+    <row r="21" spans="3:3">
+      <c r="C21" s="8" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="22" spans="3:3">
+      <c r="C22" s="7"/>
+    </row>
+    <row r="23" spans="3:3">
+      <c r="C23" s="8" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="24" spans="3:3">
+      <c r="C24" s="7"/>
+    </row>
+    <row r="25" spans="3:3">
+      <c r="C25" s="8" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="26" spans="3:3">
+      <c r="C26" s="7"/>
+    </row>
+    <row r="27" spans="3:3">
+      <c r="C27" s="8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="28" spans="3:3">
+      <c r="C28" s="7"/>
+    </row>
+    <row r="29" spans="3:3">
+      <c r="C29" s="8" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="30" spans="3:3">
+      <c r="C30" s="7"/>
+    </row>
+    <row r="31" spans="3:3">
+      <c r="C31" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="32" spans="3:3">
+      <c r="C32" s="7"/>
+    </row>
+    <row r="33" spans="3:3">
+      <c r="C33" s="8" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="34" spans="3:3">
+      <c r="C34" s="7"/>
+    </row>
+    <row r="35" spans="3:3">
+      <c r="C35" s="8" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="36" spans="3:3">
+      <c r="C36" s="7"/>
+    </row>
+    <row r="37" spans="3:3">
+      <c r="C37" s="8" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="39" spans="3:3" ht="21">
+      <c r="C39" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="40" spans="3:3">
+      <c r="C40" s="7"/>
+    </row>
+    <row r="41" spans="3:3">
+      <c r="C41" s="8" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="42" spans="3:3">
+      <c r="C42" s="7"/>
+    </row>
+    <row r="43" spans="3:3">
+      <c r="C43" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="44" spans="3:3">
+      <c r="C44" s="7"/>
+    </row>
+    <row r="45" spans="3:3">
+      <c r="C45" s="8" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="46" spans="3:3">
+      <c r="C46" s="7"/>
+    </row>
+    <row r="47" spans="3:3">
+      <c r="C47" s="7" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="48" spans="3:3">
+      <c r="C48" s="7"/>
+    </row>
+    <row r="49" spans="3:3">
+      <c r="C49" s="8" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="50" spans="3:3">
+      <c r="C50" s="7"/>
+    </row>
+    <row r="51" spans="3:3">
+      <c r="C51" s="8" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="52" spans="3:3">
+      <c r="C52" s="7"/>
+    </row>
+    <row r="53" spans="3:3">
+      <c r="C53" s="8" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="54" spans="3:3">
+      <c r="C54" s="7"/>
+    </row>
+    <row r="55" spans="3:3">
+      <c r="C55" s="8" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="56" spans="3:3">
+      <c r="C56" s="7"/>
+    </row>
+    <row r="57" spans="3:3">
+      <c r="C57" s="8" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="58" spans="3:3">
+      <c r="C58" s="7"/>
+    </row>
+    <row r="59" spans="3:3">
+      <c r="C59" s="8" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="60" spans="3:3">
+      <c r="C60" s="7"/>
+    </row>
+    <row r="61" spans="3:3">
+      <c r="C61" s="8" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="63" spans="3:3" ht="21">
+      <c r="C63" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="64" spans="3:3">
+      <c r="C64" s="7"/>
+    </row>
+    <row r="65" spans="3:3">
+      <c r="C65" s="8" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="66" spans="3:3">
+      <c r="C66" s="7"/>
+    </row>
+    <row r="67" spans="3:3">
+      <c r="C67" s="8" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="68" spans="3:3">
+      <c r="C68" s="7"/>
+    </row>
+    <row r="69" spans="3:3">
+      <c r="C69" s="8" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="70" spans="3:3">
+      <c r="C70" s="7"/>
+    </row>
+    <row r="71" spans="3:3">
+      <c r="C71" s="8" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="72" spans="3:3">
+      <c r="C72" s="7"/>
+    </row>
+    <row r="73" spans="3:3">
+      <c r="C73" s="8" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="74" spans="3:3">
+      <c r="C74" s="7"/>
+    </row>
+    <row r="75" spans="3:3">
+      <c r="C75" s="8" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="76" spans="3:3">
+      <c r="C76" s="7"/>
+    </row>
+    <row r="77" spans="3:3">
+      <c r="C77" s="8" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="78" spans="3:3">
+      <c r="C78" s="7"/>
+    </row>
+    <row r="79" spans="3:3">
+      <c r="C79" s="8" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="80" spans="3:3">
+      <c r="C80" s="7"/>
+    </row>
+    <row r="81" spans="2:3">
+      <c r="C81" s="8" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="82" spans="2:3">
+      <c r="C82" s="7"/>
+    </row>
+    <row r="83" spans="2:3">
+      <c r="B83" t="s">
+        <v>139</v>
+      </c>
+      <c r="C83" s="8" t="s">
+        <v>138</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C954C604-59FA-4E71-B562-0C51EBE0CA48}">
+  <dimension ref="C3:D5"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="3" max="3" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="82" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="3:4">
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="3:4">
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="3:4">
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="D4" r:id="rId1" xr:uid="{ABD404D3-B385-4979-8E15-E31861E65E28}"/>
+    <hyperlink ref="D5" r:id="rId2" xr:uid="{5796EFDF-5CB9-4253-80FF-8BF4337CB0B6}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57B697DF-EBFB-495C-BA65-6BC1E0B5AF25}">
+  <dimension ref="B3:B52"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetData>
+    <row r="3" spans="2:2" ht="21">
+      <c r="B3" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2" ht="16.5">
+      <c r="B5" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2">
+      <c r="B7" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2">
+      <c r="B8" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2">
+      <c r="B9" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2">
+      <c r="B10" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2">
+      <c r="B11" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2">
+      <c r="B12" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2">
+      <c r="B13" s="6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2">
+      <c r="B14" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="2:2">
+      <c r="B15" s="6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" ht="16.5">
+      <c r="B17" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2">
+      <c r="B18" s="7"/>
+    </row>
+    <row r="19" spans="2:2">
+      <c r="B19" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2">
+      <c r="B20" s="7"/>
+    </row>
+    <row r="21" spans="2:2">
+      <c r="B21" s="7"/>
+    </row>
+    <row r="22" spans="2:2">
+      <c r="B22" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2">
+      <c r="B23" s="9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2">
+      <c r="B24" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2">
+      <c r="B25" s="7"/>
+    </row>
+    <row r="26" spans="2:2">
+      <c r="B26" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2">
+      <c r="B27" s="7"/>
+    </row>
+    <row r="28" spans="2:2">
+      <c r="B28" s="7"/>
+    </row>
+    <row r="29" spans="2:2">
+      <c r="B29" s="9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2">
+      <c r="B30" s="7"/>
+    </row>
+    <row r="31" spans="2:2">
+      <c r="B31" s="8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2">
+      <c r="B32" s="7"/>
+    </row>
+    <row r="33" spans="2:2">
+      <c r="B33" s="7"/>
+    </row>
+    <row r="34" spans="2:2">
+      <c r="B34" s="9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2">
+      <c r="B35" s="7"/>
+    </row>
+    <row r="36" spans="2:2">
+      <c r="B36" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2">
+      <c r="B37" s="7"/>
+    </row>
+    <row r="38" spans="2:2">
+      <c r="B38" s="7"/>
+    </row>
+    <row r="39" spans="2:2">
+      <c r="B39" s="9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2">
+      <c r="B40" s="9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="41" spans="2:2">
+      <c r="B41" s="7"/>
+    </row>
+    <row r="42" spans="2:2">
+      <c r="B42" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="43" spans="2:2">
+      <c r="B43" s="7"/>
+    </row>
+    <row r="44" spans="2:2">
+      <c r="B44" s="7"/>
+    </row>
+    <row r="45" spans="2:2">
+      <c r="B45" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="46" spans="2:2">
+      <c r="B46" s="9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2">
+      <c r="B47" s="7"/>
+    </row>
+    <row r="48" spans="2:2">
+      <c r="B48" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2">
+      <c r="B49" s="7"/>
+    </row>
+    <row r="50" spans="2:2">
+      <c r="B50" s="7"/>
+    </row>
+    <row r="51" spans="2:2">
+      <c r="B51" s="9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2">
+      <c r="B52" s="9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C6614D2-9BE2-4DBF-BE3B-CC381AB3F591}">
+  <dimension ref="B4:D4"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="2:4">
+      <c r="B4" s="1">
+        <v>45776</v>
+      </c>
+      <c r="C4" t="s">
+        <v>253</v>
+      </c>
+      <c r="D4">
+        <v>261</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E418F96-9DED-4C44-AAF0-D4A9C9E57DCB}">
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="B3:B109"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetData>
+    <row r="3" spans="2:2">
+      <c r="B3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2">
+      <c r="B5" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2">
+      <c r="B6" s="7"/>
+    </row>
+    <row r="7" spans="2:2">
+      <c r="B7" s="7" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2">
+      <c r="B8" s="7" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2">
+      <c r="B9" s="7" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2">
+      <c r="B10" s="7" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2">
+      <c r="B11" s="7" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2">
+      <c r="B13" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="15" spans="2:2">
+      <c r="B15" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" ht="15">
+      <c r="B17" s="10" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" ht="15">
+      <c r="B19" s="11" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2">
+      <c r="B21" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2">
+      <c r="B22" s="7"/>
+    </row>
+    <row r="23" spans="2:2">
+      <c r="B23" s="8" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2">
+      <c r="B24" s="9" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2">
+      <c r="B25" s="9" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2">
+      <c r="B26" s="8" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2">
+      <c r="B27" s="9" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2">
+      <c r="B28" s="9" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2">
+      <c r="B29" s="9" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2">
+      <c r="B30" s="8" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2">
+      <c r="B31" s="9" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2">
+      <c r="B32" s="9" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2">
+      <c r="B33" s="9" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" ht="16.5">
+      <c r="B35" s="5" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2">
+      <c r="B36" s="7"/>
+    </row>
+    <row r="37" spans="2:2">
+      <c r="B37" s="7" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2">
+      <c r="B38" s="12" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2">
+      <c r="B39" s="7" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2">
+      <c r="B40" s="7" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="41" spans="2:2">
+      <c r="B41" s="6"/>
+    </row>
+    <row r="42" spans="2:2">
+      <c r="B42" s="6"/>
+    </row>
+    <row r="43" spans="2:2">
+      <c r="B43" s="6" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="44" spans="2:2">
+      <c r="B44" s="13" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="46" spans="2:2" ht="16.5">
+      <c r="B46" s="5" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2">
+      <c r="B47" s="7"/>
+    </row>
+    <row r="48" spans="2:2">
+      <c r="B48" s="7" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2">
+      <c r="B49" s="7" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2">
+      <c r="B50" s="7" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2">
+      <c r="B51" s="9" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2">
+      <c r="B52" s="9" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="53" spans="2:2">
+      <c r="B53" s="7" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="54" spans="2:2">
+      <c r="B54" s="7" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="56" spans="2:2">
+      <c r="B56" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="58" spans="2:2">
+      <c r="B58" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="60" spans="2:2" ht="28.5">
+      <c r="B60" s="14" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="62" spans="2:2">
+      <c r="B62" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="63" spans="2:2">
+      <c r="B63" s="7"/>
+    </row>
+    <row r="64" spans="2:2">
+      <c r="B64" s="8" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="65" spans="2:2">
+      <c r="B65" s="7"/>
+    </row>
+    <row r="66" spans="2:2">
+      <c r="B66" s="7"/>
+    </row>
+    <row r="67" spans="2:2">
+      <c r="B67" s="15" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="68" spans="2:2">
+      <c r="B68" s="9" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="69" spans="2:2">
+      <c r="B69" s="7"/>
+    </row>
+    <row r="70" spans="2:2">
+      <c r="B70" s="8" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="71" spans="2:2">
+      <c r="B71" s="7"/>
+    </row>
+    <row r="72" spans="2:2">
+      <c r="B72" s="7"/>
+    </row>
+    <row r="73" spans="2:2">
+      <c r="B73" s="9" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="74" spans="2:2">
+      <c r="B74" s="9" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="75" spans="2:2">
+      <c r="B75" s="7"/>
+    </row>
+    <row r="76" spans="2:2">
+      <c r="B76" s="8" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="77" spans="2:2">
+      <c r="B77" s="7"/>
+    </row>
+    <row r="78" spans="2:2">
+      <c r="B78" s="7"/>
+    </row>
+    <row r="79" spans="2:2">
+      <c r="B79" s="9" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="80" spans="2:2">
+      <c r="B80" s="9" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="81" spans="2:2">
+      <c r="B81" s="9" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="82" spans="2:2">
+      <c r="B82" s="7"/>
+    </row>
+    <row r="83" spans="2:2">
+      <c r="B83" s="8" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="84" spans="2:2">
+      <c r="B84" s="7"/>
+    </row>
+    <row r="85" spans="2:2">
+      <c r="B85" s="7"/>
+    </row>
+    <row r="86" spans="2:2">
+      <c r="B86" s="9" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="87" spans="2:2">
+      <c r="B87" s="9" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="88" spans="2:2">
+      <c r="B88" s="9" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="89" spans="2:2">
+      <c r="B89" s="7"/>
+    </row>
+    <row r="90" spans="2:2">
+      <c r="B90" s="8" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="91" spans="2:2">
+      <c r="B91" s="7"/>
+    </row>
+    <row r="92" spans="2:2">
+      <c r="B92" s="7"/>
+    </row>
+    <row r="93" spans="2:2">
+      <c r="B93" s="9" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="94" spans="2:2">
+      <c r="B94" s="9" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="95" spans="2:2">
+      <c r="B95" s="7"/>
+    </row>
+    <row r="96" spans="2:2">
+      <c r="B96" s="8" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="97" spans="2:2">
+      <c r="B97" s="7"/>
+    </row>
+    <row r="98" spans="2:2">
+      <c r="B98" s="7"/>
+    </row>
+    <row r="99" spans="2:2">
+      <c r="B99" s="9" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="100" spans="2:2">
+      <c r="B100" s="7"/>
+    </row>
+    <row r="101" spans="2:2">
+      <c r="B101" s="12" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="103" spans="2:2">
+      <c r="B103" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="104" spans="2:2">
+      <c r="B104" s="7"/>
+    </row>
+    <row r="105" spans="2:2">
+      <c r="B105" s="7" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="106" spans="2:2">
+      <c r="B106" s="7" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="107" spans="2:2">
+      <c r="B107" s="7" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="109" spans="2:2">
+      <c r="B109" t="s">
+        <v>250</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="B67" r:id="rId1" display="https://makersuite.google.com/app/apikey" xr:uid="{771DD001-7E09-4F62-86F2-758C98D1481F}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <drawing r:id="rId3"/>
+  <legacyDrawing r:id="rId4"/>
+  <controls>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="9217" r:id="rId5" name="Control 1">
+          <controlPr defaultSize="0" r:id="rId6">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>41</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>42</xdr:row>
+                <xdr:rowOff>76200</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="9217" r:id="rId5" name="Control 1"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+  </controls>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17156405-9D17-4273-BBE4-E9A6DC809FCB}">
+  <dimension ref="C3:E3"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="3" max="3" width="31.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="3:5">
+      <c r="C3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D3" t="s">
+        <v>180</v>
+      </c>
+      <c r="E3">
+        <v>6.25</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29E011BA-FF28-4838-A033-18A49EB7C30B}">
+  <dimension ref="B4:F33"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="2" max="2" width="3.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="2:6">
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="1">
+        <v>45729</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6">
+      <c r="B5">
+        <f>B4+1</f>
+        <v>2</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="1">
+        <v>45729</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6">
+      <c r="B6">
+        <f>B5+1</f>
+        <v>3</v>
+      </c>
+      <c r="C6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="1">
+        <v>45729</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" ht="40.5">
+      <c r="B7">
+        <f>B6+1</f>
+        <v>4</v>
+      </c>
+      <c r="C7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="1">
+        <v>45729</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" ht="27">
+      <c r="B8">
+        <f>B7+1</f>
+        <v>5</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="1">
+        <v>45731</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" ht="54">
+      <c r="B9">
+        <f>B8+1</f>
+        <v>6</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="1">
+        <v>45735</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" ht="27">
+      <c r="B10">
+        <f t="shared" ref="B10:B33" si="0">B9+1</f>
+        <v>7</v>
+      </c>
+      <c r="C10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" s="1">
+        <v>45735</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6">
+      <c r="B11">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="C11" t="s">
+        <v>56</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="1">
+        <v>45735</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6">
+      <c r="B12">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="C12" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="1">
+        <v>45738</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6">
+      <c r="B13">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="C13" t="s">
+        <v>59</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="1">
+        <v>45739</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6">
+      <c r="B14">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="C14" t="s">
+        <v>60</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="1">
+        <v>45739</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6">
+      <c r="B15">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="C15" t="s">
+        <v>64</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="1">
+        <v>45739</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6">
+      <c r="B16">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="C16" t="s">
+        <v>65</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="1">
+        <v>45739</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6">
+      <c r="B17">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="C17" t="s">
+        <v>67</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="1">
+        <v>45739</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6">
+      <c r="B18">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="C18" t="s">
+        <v>69</v>
+      </c>
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" s="1">
+        <v>45739</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6">
+      <c r="B19">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C19" t="s">
+        <v>72</v>
+      </c>
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" s="1">
+        <v>45739</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6">
+      <c r="B20">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="C20" t="s">
+        <v>74</v>
+      </c>
+      <c r="D20" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" s="1">
+        <v>45739</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6">
+      <c r="B21">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="C21" t="s">
+        <v>76</v>
+      </c>
+      <c r="D21" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21" s="1">
+        <v>45739</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6">
+      <c r="B22">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="C22" t="s">
+        <v>78</v>
+      </c>
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="1">
+        <v>45739</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6">
+      <c r="B23">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="C23" t="s">
+        <v>80</v>
+      </c>
+      <c r="D23" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" s="1">
+        <v>45739</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6">
+      <c r="B24">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="C24" t="s">
+        <v>82</v>
+      </c>
+      <c r="D24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" s="1">
+        <v>45739</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6">
+      <c r="B25">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="C25" t="s">
+        <v>83</v>
+      </c>
+      <c r="D25" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" s="1">
+        <v>45739</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6">
+      <c r="B26">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="C26" t="s">
+        <v>82</v>
+      </c>
+      <c r="D26" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" s="1">
+        <v>45739</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
+      <c r="B27">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="C27" t="s">
+        <v>13</v>
+      </c>
+      <c r="D27" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" s="1">
+        <v>45739</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6" ht="27">
+      <c r="B28">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D28" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" s="1">
+        <v>45739</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6">
+      <c r="B29">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="C29" t="s">
+        <v>89</v>
+      </c>
+      <c r="D29" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29" s="1">
+        <v>45743</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
+      <c r="B30">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="C30" t="s">
+        <v>93</v>
+      </c>
+      <c r="D30" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" s="1">
+        <v>45743</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6">
+      <c r="B31">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="C31" t="s">
+        <v>94</v>
+      </c>
+      <c r="D31" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31" s="1">
+        <v>45747</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6" ht="27">
+      <c r="B32">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3">
+      <c r="B33">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="C33" t="s">
+        <v>147</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="E5" r:id="rId1" xr:uid="{710BA6B0-B0F6-4236-8BB2-74C40F796674}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42DE40CD-4CA6-4FF4-B0DA-D079807C6662}">
+  <dimension ref="B3:G15"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.125" customWidth="1"/>
+    <col min="5" max="5" width="45.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="37.75" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:7" ht="40.5">
+      <c r="B3" s="1">
+        <v>45747</v>
+      </c>
+      <c r="C3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" ht="54">
+      <c r="D4" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="E4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F4" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" ht="40.5">
+      <c r="D5" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="E5" t="s">
+        <v>156</v>
+      </c>
+      <c r="F5" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" ht="54">
+      <c r="D6" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E6" t="s">
+        <v>159</v>
+      </c>
+      <c r="F6" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" ht="54">
+      <c r="D7" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="E7" t="s">
+        <v>162</v>
+      </c>
+      <c r="F7" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" ht="40.5">
+      <c r="D8" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="E8" t="s">
+        <v>162</v>
+      </c>
+      <c r="F8" t="s">
+        <v>151</v>
+      </c>
+      <c r="G8" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" ht="81">
+      <c r="D9" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="E9" t="s">
+        <v>153</v>
+      </c>
+      <c r="F9" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" ht="40.5">
+      <c r="D10" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="E10" t="s">
+        <v>156</v>
+      </c>
+      <c r="F10" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" ht="54">
+      <c r="D11" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="E11" t="s">
+        <v>168</v>
+      </c>
+      <c r="F11" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" ht="54">
+      <c r="D12" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="E12" t="s">
+        <v>170</v>
+      </c>
+      <c r="F12" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" ht="40.5">
+      <c r="D13" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E13" t="s">
+        <v>173</v>
+      </c>
+      <c r="F13" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" ht="54">
+      <c r="D14" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="E14" t="s">
+        <v>175</v>
+      </c>
+      <c r="F14" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" ht="40.5">
+      <c r="D15" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="E15" t="s">
+        <v>177</v>
+      </c>
+      <c r="F15" t="s">
+        <v>177</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6313D91D-4E4E-4302-B673-A8C3F21575BA}">
+  <dimension ref="B3:D43"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="83.75" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="3:3" ht="40.5">
+      <c r="C3" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="3:3" ht="40.5">
+      <c r="C4" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="3:3" ht="94.5">
+      <c r="C5" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" spans="3:3" ht="27">
+      <c r="C6" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="3:3" ht="54">
+      <c r="C7" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" spans="3:3" ht="40.5">
+      <c r="C8" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="9" spans="3:3" ht="40.5">
+      <c r="C9" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10" spans="3:3">
+      <c r="C10" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="3:3" ht="40.5">
+      <c r="C11" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="3:3" ht="54">
+      <c r="C12" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="13" spans="3:3" ht="40.5">
+      <c r="C13" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" spans="3:3" ht="40.5">
+      <c r="C14" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="15" spans="3:3" ht="40.5">
+      <c r="C15" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="16" spans="3:3" ht="54">
+      <c r="C16" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" ht="40.5">
+      <c r="C17" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" ht="54">
+      <c r="B18" s="1">
+        <v>45739</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4">
+      <c r="C19" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" ht="54">
+      <c r="C20" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" ht="67.5">
+      <c r="C21" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4">
+      <c r="B22" s="1">
+        <v>45740</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" ht="40.5">
+      <c r="C23" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" ht="40.5">
+      <c r="B24" s="1">
+        <v>45741</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" ht="27">
+      <c r="B25" s="1">
+        <v>45742</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4">
+      <c r="B26" s="1">
+        <v>45776</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4" ht="54">
+      <c r="B27" s="1">
+        <v>45776</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4" ht="409.5">
+      <c r="B28" s="1">
+        <v>45776</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4" ht="409.5">
+      <c r="C29" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="D29" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4" ht="409.5">
+      <c r="C30" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="D30" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4" ht="409.5">
+      <c r="C31" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="D31" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4" ht="409.5">
+      <c r="C32" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="D32" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="33" spans="3:4">
+      <c r="C33" s="3"/>
+      <c r="D33" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="34" spans="3:4" ht="409.5">
+      <c r="C34" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="D34" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="35" spans="3:4" ht="409.5">
+      <c r="C35" s="3" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="36" spans="3:4" ht="135">
+      <c r="C36" s="3" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="37" spans="3:4" ht="189">
+      <c r="C37" s="3" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="38" spans="3:4">
+      <c r="C38" s="3" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="39" spans="3:4" ht="409.5">
+      <c r="C39" s="3" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="40" spans="3:4" ht="409.5">
+      <c r="C40" s="26" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="41" spans="3:4" ht="40.5">
+      <c r="C41" s="3" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="42" spans="3:4" ht="54">
+      <c r="C42" s="3" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="43" spans="3:4" ht="40.5">
+      <c r="C43" s="3" t="s">
+        <v>894</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="C40" r:id="rId1" display="https://github.com/umezawakanta/work-time-tracker_x000a__x000a_このサイトを改善してください。未実装の部分やモックデータを使用している部分を一つづつでいいので本番用に実装してください。将来的にはこのサイトを世界最高のサイトに改善し、有料でサブスクしたユーザーだけが使用できるサービスとしてリリースしたいです。1ファイルのサイズは200行以内として、超える場合は一部をサブコンポーネントとして切り出したいです。またESLintのエラーや警告が絶対にでないように複数回の検証を繰り返してからコードを提供してください。これまで必ずEsLint指摘がでているのでなんとか改善してください。特に、no-unused-vars、no-explicit-anyのエラーが絶対にでないように複数回の検証を行ってください。命名規則や型定義にも一貫性をもたせてください。ファイルパスやファイル名はコピペできるように出力してください。フォルダー構成についても改善案があれば提示してください。また、開発スケジュールやリリーススケジュールも必ず考慮してください。また、このサイト自体の開発スケジュールをWBSとしてサイト上で表示できるようにしたいです。日本語でお願いします。下記に列挙する企業のサービスを上回るという観点で検討してください。_x000a_Microsoft_x000a_Apple_x000a_Amazon_x000a_Google (Alphabet)_x000a_Salesforce_x000a_NVIDIA_x000a_Adobe_x000a_ServiceNow_x000a_Oracle_x000a_SAP_x000a_Zoom_x000a_Atlassian_x000a_HubSpot_x000a_Workday_x000a_Shopify_x000a_Slack_x000a_OpenAI_x000a_Anthropic_x000a_Stability AI_x000a_Midjourney_x000a_Cohere_x000a_Hugging Face_x000a_Inflection AI_x000a_Runway_x000a_Meta (旧Facebook)_x000a_ByteDance_x000a_X (旧Twitter)_x000a_Tencent_x000a_LinkedIn_x000a_Snapchat (Snap Inc.)_x000a_Pinterest_x000a_Reddit_x000a_Discord_x000a_LINE (Z Holdings)_x000a_Samsung_x000a_Uber_x000a_Spotify_x000a_Grab_x000a_Airbnb_x000a_Match Group_x000a_Bumble_x000a_Indeed (Recruit Holdings)_x000a_TaskRabbit_x000a_Fiverr_x000a_Upwork_x000a_Meetup_x000a_回答が長くなりすぎて途中で切れてしまうようであれば、複数回に分割して出力することも検討してください。" xr:uid="{E8F3ED09-11C9-4BFA-A06D-422A282024D2}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7DD1F4F-4FBA-4AD3-8545-6C67C68E9F78}">
+  <dimension ref="C3:D6"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="3" max="3" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="3:4">
+      <c r="C3" t="s">
+        <v>895</v>
+      </c>
+      <c r="D3" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="4" spans="3:4">
+      <c r="C4" t="s">
+        <v>897</v>
+      </c>
+      <c r="D4" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="5" spans="3:4">
+      <c r="C5" t="s">
+        <v>899</v>
+      </c>
+      <c r="D5" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="6" spans="3:4">
+      <c r="C6" t="s">
+        <v>901</v>
+      </c>
+      <c r="D6" t="s">
+        <v>902</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E48D234-365F-4B51-8CC9-CA1EEC7E09FC}">
+  <dimension ref="B3:F333"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="65" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="229.25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:5" ht="40.5">
+      <c r="B3" s="1">
+        <v>45805</v>
+      </c>
+      <c r="C3" t="s">
+        <v>719</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>718</v>
+      </c>
+      <c r="E3" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" ht="21">
+      <c r="E7" s="4" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5">
+      <c r="E8" s="7"/>
+    </row>
+    <row r="9" spans="2:5">
+      <c r="E9" s="8" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5">
+      <c r="E10" s="7"/>
+    </row>
+    <row r="11" spans="2:5">
+      <c r="E11" s="7"/>
+    </row>
+    <row r="12" spans="2:5">
+      <c r="E12" s="9"/>
+    </row>
+    <row r="13" spans="2:5">
+      <c r="E13" s="9" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5">
+      <c r="E14" s="7"/>
+    </row>
+    <row r="15" spans="2:5">
+      <c r="E15" s="8" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5">
+      <c r="E16" s="7"/>
+    </row>
+    <row r="17" spans="5:5">
+      <c r="E17" s="7"/>
+    </row>
+    <row r="18" spans="5:5">
+      <c r="E18" s="9"/>
+    </row>
+    <row r="19" spans="5:5">
+      <c r="E19" s="9" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="20" spans="5:5">
+      <c r="E20" s="9"/>
+    </row>
+    <row r="21" spans="5:5">
+      <c r="E21" s="9" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="22" spans="5:5">
+      <c r="E22" s="9"/>
+    </row>
+    <row r="23" spans="5:5">
+      <c r="E23" s="9" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="24" spans="5:5">
+      <c r="E24" s="9"/>
+    </row>
+    <row r="25" spans="5:5">
+      <c r="E25" s="9" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="26" spans="5:5">
+      <c r="E26" s="7"/>
+    </row>
+    <row r="27" spans="5:5">
+      <c r="E27" s="8" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="28" spans="5:5">
+      <c r="E28" s="7"/>
+    </row>
+    <row r="29" spans="5:5">
+      <c r="E29" s="7"/>
+    </row>
+    <row r="30" spans="5:5">
+      <c r="E30" s="9"/>
+    </row>
+    <row r="31" spans="5:5">
+      <c r="E31" s="9" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="35" spans="5:5" ht="21">
+      <c r="E35" s="4" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="36" spans="5:5">
+      <c r="E36" s="7"/>
+    </row>
+    <row r="37" spans="5:5">
+      <c r="E37" s="8" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="38" spans="5:5">
+      <c r="E38" s="7"/>
+    </row>
+    <row r="39" spans="5:5">
+      <c r="E39" s="7"/>
+    </row>
+    <row r="40" spans="5:5">
+      <c r="E40" s="9"/>
+    </row>
+    <row r="41" spans="5:5">
+      <c r="E41" s="9" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="42" spans="5:5">
+      <c r="E42" s="9"/>
+    </row>
+    <row r="43" spans="5:5">
+      <c r="E43" s="9" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="44" spans="5:5">
+      <c r="E44" s="9"/>
+    </row>
+    <row r="45" spans="5:5">
+      <c r="E45" s="9" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="46" spans="5:5">
+      <c r="E46" s="7"/>
+    </row>
+    <row r="47" spans="5:5">
+      <c r="E47" s="8" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="48" spans="5:5">
+      <c r="E48" s="7"/>
+    </row>
+    <row r="49" spans="5:5">
+      <c r="E49" s="7"/>
+    </row>
+    <row r="50" spans="5:5">
+      <c r="E50" s="9"/>
+    </row>
+    <row r="51" spans="5:5">
+      <c r="E51" s="9" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="52" spans="5:5">
+      <c r="E52" s="7"/>
+    </row>
+    <row r="53" spans="5:5">
+      <c r="E53" s="8" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="54" spans="5:5">
+      <c r="E54" s="7"/>
+    </row>
+    <row r="55" spans="5:5">
+      <c r="E55" s="7"/>
+    </row>
+    <row r="56" spans="5:5">
+      <c r="E56" s="9"/>
+    </row>
+    <row r="57" spans="5:5">
+      <c r="E57" s="9" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="58" spans="5:5">
+      <c r="E58" s="9"/>
+    </row>
+    <row r="59" spans="5:5">
+      <c r="E59" s="9" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="60" spans="5:5">
+      <c r="E60" s="7"/>
+    </row>
+    <row r="61" spans="5:5">
+      <c r="E61" s="8" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="62" spans="5:5">
+      <c r="E62" s="7"/>
+    </row>
+    <row r="63" spans="5:5">
+      <c r="E63" s="7"/>
+    </row>
+    <row r="64" spans="5:5">
+      <c r="E64" s="9"/>
+    </row>
+    <row r="65" spans="5:5">
+      <c r="E65" s="29" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="66" spans="5:5">
+      <c r="E66" s="9"/>
+    </row>
+    <row r="67" spans="5:5">
+      <c r="E67" s="29" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="68" spans="5:5">
+      <c r="E68" s="9"/>
+    </row>
+    <row r="69" spans="5:5">
+      <c r="E69" s="29" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="70" spans="5:5">
+      <c r="E70" s="9"/>
+    </row>
+    <row r="71" spans="5:5">
+      <c r="E71" s="29" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="75" spans="5:5" ht="21">
+      <c r="E75" s="4" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="77" spans="5:5" ht="14.25">
+      <c r="E77" s="28" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="79" spans="5:5">
+      <c r="E79" s="6" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="80" spans="5:5">
+      <c r="E80" s="27"/>
+    </row>
+    <row r="81" spans="5:5">
+      <c r="E81" s="6" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="82" spans="5:5">
+      <c r="E82" s="6" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="83" spans="5:5">
+      <c r="E83" s="6" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="84" spans="5:5">
+      <c r="E84" s="6" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="85" spans="5:5">
+      <c r="E85" s="6" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="86" spans="5:5">
+      <c r="E86" s="27"/>
+    </row>
+    <row r="87" spans="5:5">
+      <c r="E87" s="6" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="88" spans="5:5">
+      <c r="E88" s="6" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="89" spans="5:5">
+      <c r="E89" s="6" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="90" spans="5:5">
+      <c r="E90" s="6" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="91" spans="5:5">
+      <c r="E91" s="6" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="92" spans="5:5">
+      <c r="E92" s="6" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="93" spans="5:5">
+      <c r="E93" s="6" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="94" spans="5:5">
+      <c r="E94" s="6" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="95" spans="5:5">
+      <c r="E95" s="6" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="96" spans="5:5">
+      <c r="E96" s="6" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="97" spans="5:5">
+      <c r="E97" s="6" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="98" spans="5:5">
+      <c r="E98" s="6" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="99" spans="5:5">
+      <c r="E99" s="27"/>
+    </row>
+    <row r="100" spans="5:5">
+      <c r="E100" s="6" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="101" spans="5:5">
+      <c r="E101" s="6" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="102" spans="5:5">
+      <c r="E102" s="6" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="103" spans="5:5">
+      <c r="E103" s="27"/>
+    </row>
+    <row r="104" spans="5:5">
+      <c r="E104" s="6" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="105" spans="5:5">
+      <c r="E105" s="6" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="106" spans="5:5">
+      <c r="E106" s="6" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="107" spans="5:5">
+      <c r="E107" s="6" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="108" spans="5:5">
+      <c r="E108" s="6" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="109" spans="5:5">
+      <c r="E109" s="6" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="110" spans="5:5">
+      <c r="E110" s="6" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="111" spans="5:5">
+      <c r="E111" s="6" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="112" spans="5:5">
+      <c r="E112" s="6" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="113" spans="5:5">
+      <c r="E113" s="6" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="114" spans="5:5">
+      <c r="E114" s="6" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="115" spans="5:5">
+      <c r="E115" s="6" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="116" spans="5:5">
+      <c r="E116" s="6" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="117" spans="5:5">
+      <c r="E117" s="6" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="118" spans="5:5">
+      <c r="E118" s="6" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="119" spans="5:5">
+      <c r="E119" s="27"/>
+    </row>
+    <row r="120" spans="5:5">
+      <c r="E120" s="6" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="121" spans="5:5">
+      <c r="E121" s="6" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="122" spans="5:5">
+      <c r="E122" s="6" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="123" spans="5:5">
+      <c r="E123" s="6" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="124" spans="5:5">
+      <c r="E124" s="6" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="125" spans="5:5">
+      <c r="E125" s="6" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="126" spans="5:5">
+      <c r="E126" s="27"/>
+    </row>
+    <row r="127" spans="5:5">
+      <c r="E127" s="6" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="128" spans="5:5">
+      <c r="E128" s="6" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="129" spans="5:5">
+      <c r="E129" s="6" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="130" spans="5:5">
+      <c r="E130" s="6" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="131" spans="5:5">
+      <c r="E131" s="6" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="132" spans="5:5">
+      <c r="E132" s="6" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="133" spans="5:5">
+      <c r="E133" s="6" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="134" spans="5:5">
+      <c r="E134" s="27"/>
+    </row>
+    <row r="135" spans="5:5">
+      <c r="E135" s="6" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="136" spans="5:5">
+      <c r="E136" s="6" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="137" spans="5:5">
+      <c r="E137" s="6" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="138" spans="5:5">
+      <c r="E138" s="6" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="139" spans="5:5">
+      <c r="E139" s="6" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="140" spans="5:5">
+      <c r="E140" s="6" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="141" spans="5:5">
+      <c r="E141" s="7"/>
+    </row>
+    <row r="142" spans="5:5">
+      <c r="E142" s="8" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="143" spans="5:5">
+      <c r="E143" s="9"/>
+    </row>
+    <row r="144" spans="5:5">
+      <c r="E144" s="30" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="145" spans="5:5">
+      <c r="E145" s="9"/>
+    </row>
+    <row r="146" spans="5:5">
+      <c r="E146" s="30" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="147" spans="5:5">
+      <c r="E147" s="9"/>
+    </row>
+    <row r="148" spans="5:5">
+      <c r="E148" s="30" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="149" spans="5:5">
+      <c r="E149" s="9"/>
+    </row>
+    <row r="150" spans="5:5">
+      <c r="E150" s="30" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="154" spans="5:5" ht="21">
+      <c r="E154" s="4" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="155" spans="5:5">
+      <c r="E155" s="7"/>
+    </row>
+    <row r="156" spans="5:5">
+      <c r="E156" s="7" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="157" spans="5:5">
+      <c r="E157" s="7"/>
+    </row>
+    <row r="158" spans="5:5">
+      <c r="E158" s="7" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="159" spans="5:5">
+      <c r="E159" s="7"/>
+    </row>
+    <row r="160" spans="5:5">
+      <c r="E160" s="7"/>
+    </row>
+    <row r="161" spans="5:5">
+      <c r="E161" s="9"/>
+    </row>
+    <row r="162" spans="5:5">
+      <c r="E162" s="29" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="163" spans="5:5">
+      <c r="E163" s="9"/>
+    </row>
+    <row r="164" spans="5:5">
+      <c r="E164" s="9" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="165" spans="5:5">
+      <c r="E165" s="7"/>
+    </row>
+    <row r="166" spans="5:5">
+      <c r="E166" s="7" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="170" spans="5:5" ht="21">
+      <c r="E170" s="4" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="171" spans="5:5">
+      <c r="E171" s="7"/>
+    </row>
+    <row r="172" spans="5:5">
+      <c r="E172" s="8" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="173" spans="5:5">
+      <c r="E173" s="7"/>
+    </row>
+    <row r="174" spans="5:5">
+      <c r="E174" s="7"/>
+    </row>
+    <row r="175" spans="5:5">
+      <c r="E175" s="9"/>
+    </row>
+    <row r="176" spans="5:5">
+      <c r="E176" s="9" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="177" spans="5:5">
+      <c r="E177" s="7"/>
+    </row>
+    <row r="178" spans="5:5">
+      <c r="E178" s="8" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="179" spans="5:5">
+      <c r="E179" s="7"/>
+    </row>
+    <row r="180" spans="5:5">
+      <c r="E180" s="7"/>
+    </row>
+    <row r="181" spans="5:5">
+      <c r="E181" s="9"/>
+    </row>
+    <row r="182" spans="5:5">
+      <c r="E182" s="9" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="183" spans="5:5">
+      <c r="E183" s="7"/>
+    </row>
+    <row r="184" spans="5:5">
+      <c r="E184" s="8" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="185" spans="5:5">
+      <c r="E185" s="7"/>
+    </row>
+    <row r="186" spans="5:5">
+      <c r="E186" s="7"/>
+    </row>
+    <row r="187" spans="5:5">
+      <c r="E187" s="9"/>
+    </row>
+    <row r="188" spans="5:5">
+      <c r="E188" s="9" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="192" spans="5:5">
+      <c r="E192" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="193" spans="4:5">
+      <c r="D193" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="195" spans="4:5">
+      <c r="D195" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="197" spans="4:5">
+      <c r="D197" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="199" spans="4:5">
+      <c r="D199" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="201" spans="4:5">
+      <c r="D201" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="202" spans="4:5">
+      <c r="E202" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="206" spans="4:5" ht="21">
+      <c r="E206" s="4" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="207" spans="4:5">
+      <c r="E207" s="7"/>
+    </row>
+    <row r="208" spans="4:5">
+      <c r="E208" s="8" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="209" spans="5:5">
+      <c r="E209" s="7"/>
+    </row>
+    <row r="210" spans="5:5">
+      <c r="E210" s="7" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="214" spans="5:5" ht="21">
+      <c r="E214" s="4" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="215" spans="5:5">
+      <c r="E215" s="7"/>
+    </row>
+    <row r="216" spans="5:5">
+      <c r="E216" s="31" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="217" spans="5:5">
+      <c r="E217" s="31" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="218" spans="5:5">
+      <c r="E218" s="7" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="219" spans="5:5">
+      <c r="E219" s="31" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="220" spans="5:5">
+      <c r="E220" s="7" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="221" spans="5:5">
+      <c r="E221" s="31" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="222" spans="5:5">
+      <c r="E222" s="7" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="223" spans="5:5">
+      <c r="E223" s="7" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="224" spans="5:5">
+      <c r="E224" s="7" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="225" spans="5:6">
+      <c r="E225" s="7"/>
+    </row>
+    <row r="226" spans="5:6">
+      <c r="E226" s="8" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="227" spans="5:6">
+      <c r="E227" s="9"/>
+    </row>
+    <row r="228" spans="5:6">
+      <c r="E228" s="9" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="229" spans="5:6">
+      <c r="E229" s="9"/>
+    </row>
+    <row r="230" spans="5:6">
+      <c r="E230" s="9" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="234" spans="5:6" ht="21">
+      <c r="E234" s="4" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="236" spans="5:6">
+      <c r="E236" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="238" spans="5:6">
+      <c r="E238" s="32" t="s">
+        <v>834</v>
+      </c>
+      <c r="F238" s="32" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="239" spans="5:6" ht="81">
+      <c r="E239" s="33" t="s">
+        <v>836</v>
+      </c>
+      <c r="F239" s="33" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="240" spans="5:6" ht="67.5">
+      <c r="E240" s="33" t="s">
+        <v>838</v>
+      </c>
+      <c r="F240" s="33" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="242" spans="5:5" ht="16.5">
+      <c r="E242" s="5" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="243" spans="5:5">
+      <c r="E243" s="7"/>
+    </row>
+    <row r="244" spans="5:5">
+      <c r="E244" s="7" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="245" spans="5:5">
+      <c r="E245" s="31" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="246" spans="5:5">
+      <c r="E246" s="8" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="247" spans="5:5">
+      <c r="E247" s="31" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="248" spans="5:5">
+      <c r="E248" s="7"/>
+    </row>
+    <row r="249" spans="5:5">
+      <c r="E249" s="9"/>
+    </row>
+    <row r="250" spans="5:5">
+      <c r="E250" s="9" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="251" spans="5:5">
+      <c r="E251" s="9"/>
+    </row>
+    <row r="252" spans="5:5">
+      <c r="E252" s="9" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="253" spans="5:5">
+      <c r="E253" s="9"/>
+    </row>
+    <row r="254" spans="5:5">
+      <c r="E254" s="9" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="255" spans="5:5">
+      <c r="E255" s="7"/>
+    </row>
+    <row r="256" spans="5:5">
+      <c r="E256" s="7" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="257" spans="5:5">
+      <c r="E257" s="7"/>
+    </row>
+    <row r="258" spans="5:5">
+      <c r="E258" s="7"/>
+    </row>
+    <row r="259" spans="5:5">
+      <c r="E259" s="9"/>
+    </row>
+    <row r="260" spans="5:5">
+      <c r="E260" s="9" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="261" spans="5:5">
+      <c r="E261" s="7"/>
+    </row>
+    <row r="262" spans="5:5">
+      <c r="E262" s="7" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="263" spans="5:5">
+      <c r="E263" s="7"/>
+    </row>
+    <row r="264" spans="5:5">
+      <c r="E264" s="8" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="265" spans="5:5">
+      <c r="E265" s="7" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="266" spans="5:5" ht="14.25">
+      <c r="E266" s="34" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="268" spans="5:5">
+      <c r="E268" s="6" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="269" spans="5:5">
+      <c r="E269" s="6" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="270" spans="5:5">
+      <c r="E270" s="27"/>
+    </row>
+    <row r="271" spans="5:5">
+      <c r="E271" s="6" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="272" spans="5:5">
+      <c r="E272" s="6" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="274" spans="5:5">
+      <c r="E274" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="276" spans="5:5">
+      <c r="E276" s="6" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="280" spans="5:5" ht="16.5">
+      <c r="E280" s="5" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="281" spans="5:5">
+      <c r="E281" s="7"/>
+    </row>
+    <row r="282" spans="5:5">
+      <c r="E282" s="7" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="283" spans="5:5">
+      <c r="E283" s="7"/>
+    </row>
+    <row r="284" spans="5:5">
+      <c r="E284" s="8" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="285" spans="5:5">
+      <c r="E285" s="7"/>
+    </row>
+    <row r="286" spans="5:5">
+      <c r="E286" s="7" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="287" spans="5:5">
+      <c r="E287" s="7"/>
+    </row>
+    <row r="288" spans="5:5">
+      <c r="E288" s="7" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="289" spans="5:5">
+      <c r="E289" s="7"/>
+    </row>
+    <row r="290" spans="5:5">
+      <c r="E290" s="7" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="292" spans="5:5" ht="14.25">
+      <c r="E292" s="34" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="294" spans="5:5">
+      <c r="E294" s="6" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="295" spans="5:5">
+      <c r="E295" s="27"/>
+    </row>
+    <row r="296" spans="5:5">
+      <c r="E296" s="6" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="297" spans="5:5">
+      <c r="E297" s="6" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="298" spans="5:5">
+      <c r="E298" s="6" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="299" spans="5:5">
+      <c r="E299" s="27"/>
+    </row>
+    <row r="300" spans="5:5">
+      <c r="E300" s="6" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="301" spans="5:5">
+      <c r="E301" s="6" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="302" spans="5:5">
+      <c r="E302" s="6" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="303" spans="5:5">
+      <c r="E303" s="6" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="304" spans="5:5">
+      <c r="E304" s="6" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="305" spans="5:5">
+      <c r="E305" s="27"/>
+    </row>
+    <row r="306" spans="5:5">
+      <c r="E306" s="6" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="307" spans="5:5">
+      <c r="E307" s="6" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="308" spans="5:5">
+      <c r="E308" s="6" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="309" spans="5:5">
+      <c r="E309" s="27"/>
+    </row>
+    <row r="310" spans="5:5">
+      <c r="E310" s="6" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="311" spans="5:5">
+      <c r="E311" s="6" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="315" spans="5:5" ht="21">
+      <c r="E315" s="4" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="316" spans="5:5">
+      <c r="E316" s="7"/>
+    </row>
+    <row r="317" spans="5:5">
+      <c r="E317" s="7" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="318" spans="5:5">
+      <c r="E318" s="7"/>
+    </row>
+    <row r="319" spans="5:5">
+      <c r="E319" s="7" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="320" spans="5:5">
+      <c r="E320" s="7"/>
+    </row>
+    <row r="321" spans="5:5">
+      <c r="E321" s="12" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="322" spans="5:5">
+      <c r="E322" s="7"/>
+    </row>
+    <row r="323" spans="5:5">
+      <c r="E323" s="7" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="324" spans="5:5">
+      <c r="E324" s="7"/>
+    </row>
+    <row r="325" spans="5:5">
+      <c r="E325" s="8" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="326" spans="5:5">
+      <c r="E326" s="9"/>
+    </row>
+    <row r="327" spans="5:5">
+      <c r="E327" s="9" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="328" spans="5:5">
+      <c r="E328" s="9"/>
+    </row>
+    <row r="329" spans="5:5">
+      <c r="E329" s="9" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="333" spans="5:5">
+      <c r="E333" t="s">
+        <v>885</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="E216" r:id="rId1" display="https://console.cloud.google.com/" xr:uid="{C22AE040-F098-4AD9-89CF-A383D040926C}"/>
+    <hyperlink ref="E217" r:id="rId2" xr:uid="{E38476E8-6DBA-42FB-B4B7-1EB8CEDE4E88}"/>
+    <hyperlink ref="E219" r:id="rId3" xr:uid="{B6AE74F3-E379-48F4-8B8D-7B49A90D86A2}"/>
+    <hyperlink ref="E221" r:id="rId4" xr:uid="{5955D8BB-4302-4C1C-8232-A252B8E35C87}"/>
+    <hyperlink ref="E245" r:id="rId5" xr:uid="{F47D0F3F-D694-495A-B0BD-B2E374DC9A03}"/>
+    <hyperlink ref="E247" r:id="rId6" xr:uid="{97A7A4C4-EB2E-48AD-8E7B-F6A56F068F5E}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5712A840-B254-407E-8891-3992F636D229}">
+  <dimension ref="B4:C4"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="2" max="2" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="66.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="2:3">
+      <c r="B4" s="1">
+        <v>45801</v>
+      </c>
+      <c r="C4" t="s">
+        <v>691</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Vite-Vercel開発.xlsx
+++ b/Vite-Vercel開発.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kanta\GitHub\work-time-tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B380C323-14B8-42CD-8580-F5275C2F97F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1928CA11-C4AD-40E9-B1C5-143667E830EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="よく使うこまんど" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1525" uniqueCount="903">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1535" uniqueCount="913">
   <si>
     <t>npm install -g vercel</t>
     <phoneticPr fontId="1"/>
@@ -5290,6 +5290,46 @@
   </si>
   <si>
     <t>Open New Window</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Found 131 errors in 30 files.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">     5  src/components/calendar/AssetCalendar.tsx:132</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Found 126 errors in 29 files.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">     1  src/components/chart/PoliticalLineChart.tsx:186</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Ctrl + L</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Add to Chat</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Found 125 errors in 28 files.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">     2  src/components/chart/PoliticalTrendsCard.tsx:9</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Found 123 errors in 27 files.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Found 119 errors in 27 files.</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -6062,24 +6102,25 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{083174DA-A42C-4F9C-978E-61AEAAD9DDFF}">
-  <dimension ref="C2:D8"/>
+  <dimension ref="B2:D17"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
+    <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="61.75" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="68.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:4">
+    <row r="2" spans="2:4">
       <c r="D2" t="s">
         <v>685</v>
       </c>
     </row>
-    <row r="3" spans="3:4">
+    <row r="3" spans="2:4">
       <c r="C3" t="s">
         <v>681</v>
       </c>
     </row>
-    <row r="4" spans="3:4">
+    <row r="4" spans="2:4">
       <c r="C4" t="s">
         <v>683</v>
       </c>
@@ -6087,7 +6128,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="5" spans="3:4">
+    <row r="5" spans="2:4">
       <c r="C5" t="s">
         <v>686</v>
       </c>
@@ -6095,12 +6136,12 @@
         <v>683</v>
       </c>
     </row>
-    <row r="6" spans="3:4">
+    <row r="6" spans="2:4">
       <c r="C6" t="s">
         <v>687</v>
       </c>
     </row>
-    <row r="7" spans="3:4">
+    <row r="7" spans="2:4">
       <c r="C7" t="s">
         <v>688</v>
       </c>
@@ -6108,9 +6149,52 @@
         <v>689</v>
       </c>
     </row>
-    <row r="8" spans="3:4">
+    <row r="8" spans="2:4">
       <c r="C8" t="s">
         <v>690</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4">
+      <c r="B10" s="1">
+        <v>45807</v>
+      </c>
+      <c r="C10" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4">
+      <c r="C11" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4">
+      <c r="C12" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4">
+      <c r="C13" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4">
+      <c r="C14" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4">
+      <c r="C15" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4">
+      <c r="C16" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="17" spans="3:3">
+      <c r="C17" t="s">
+        <v>912</v>
       </c>
     </row>
   </sheetData>
@@ -6277,18 +6361,18 @@
       MOD(NOW(),1),
       TIME(0,5,0)
     ),"HH:mm")</f>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B2" s="19"/>
       <c r="D2" s="1">
         <f ca="1">TODAY()</f>
-        <v>45806</v>
+        <v>45807</v>
       </c>
     </row>
     <row r="3" spans="1:65">
       <c r="A3" s="19" t="str">
         <f ca="1">TEXT(NOW(),"HH:mm")</f>
-        <v>23:57</v>
+        <v>00:59</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="17" t="s">
@@ -6487,7 +6571,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B4" t="str">
         <f t="shared" ref="B4:B67" si="1">TEXT($C4, "HH:mm")</f>
@@ -6566,7 +6650,7 @@
     <row r="5" spans="1:65">
       <c r="A5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B5" t="str">
         <f t="shared" si="1"/>
@@ -6645,7 +6729,7 @@
     <row r="6" spans="1:65">
       <c r="A6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B6" t="str">
         <f t="shared" si="1"/>
@@ -6724,7 +6808,7 @@
     <row r="7" spans="1:65">
       <c r="A7" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B7" t="str">
         <f t="shared" si="1"/>
@@ -6803,7 +6887,7 @@
     <row r="8" spans="1:65">
       <c r="A8" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B8" t="str">
         <f t="shared" si="1"/>
@@ -6882,7 +6966,7 @@
     <row r="9" spans="1:65">
       <c r="A9" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B9" t="str">
         <f t="shared" si="1"/>
@@ -6961,7 +7045,7 @@
     <row r="10" spans="1:65">
       <c r="A10" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B10" t="str">
         <f t="shared" si="1"/>
@@ -7040,7 +7124,7 @@
     <row r="11" spans="1:65">
       <c r="A11" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B11" t="str">
         <f t="shared" si="1"/>
@@ -7119,7 +7203,7 @@
     <row r="12" spans="1:65">
       <c r="A12" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B12" t="str">
         <f t="shared" si="1"/>
@@ -7198,7 +7282,7 @@
     <row r="13" spans="1:65">
       <c r="A13" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B13" t="str">
         <f t="shared" si="1"/>
@@ -7277,7 +7361,7 @@
     <row r="14" spans="1:65">
       <c r="A14" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B14" t="str">
         <f t="shared" si="1"/>
@@ -7356,7 +7440,7 @@
     <row r="15" spans="1:65">
       <c r="A15" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B15" t="str">
         <f t="shared" si="1"/>
@@ -7435,7 +7519,7 @@
     <row r="16" spans="1:65">
       <c r="A16" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B16" t="str">
         <f t="shared" si="1"/>
@@ -7514,7 +7598,7 @@
     <row r="17" spans="1:65">
       <c r="A17" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B17" t="str">
         <f t="shared" si="1"/>
@@ -7593,7 +7677,7 @@
     <row r="18" spans="1:65">
       <c r="A18" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B18" t="str">
         <f t="shared" si="1"/>
@@ -7672,7 +7756,7 @@
     <row r="19" spans="1:65">
       <c r="A19" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B19" t="str">
         <f t="shared" si="1"/>
@@ -7751,7 +7835,7 @@
     <row r="20" spans="1:65">
       <c r="A20" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B20" t="str">
         <f t="shared" si="1"/>
@@ -7830,7 +7914,7 @@
     <row r="21" spans="1:65">
       <c r="A21" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B21" t="str">
         <f t="shared" si="1"/>
@@ -7909,7 +7993,7 @@
     <row r="22" spans="1:65">
       <c r="A22" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B22" t="str">
         <f t="shared" si="1"/>
@@ -7988,7 +8072,7 @@
     <row r="23" spans="1:65">
       <c r="A23" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B23" t="str">
         <f t="shared" si="1"/>
@@ -8067,7 +8151,7 @@
     <row r="24" spans="1:65">
       <c r="A24" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B24" t="str">
         <f t="shared" si="1"/>
@@ -8146,7 +8230,7 @@
     <row r="25" spans="1:65">
       <c r="A25" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B25" t="str">
         <f t="shared" si="1"/>
@@ -8225,7 +8309,7 @@
     <row r="26" spans="1:65">
       <c r="A26" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B26" t="str">
         <f t="shared" si="1"/>
@@ -8304,7 +8388,7 @@
     <row r="27" spans="1:65">
       <c r="A27" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B27" t="str">
         <f t="shared" si="1"/>
@@ -8383,7 +8467,7 @@
     <row r="28" spans="1:65">
       <c r="A28" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B28" t="str">
         <f t="shared" si="1"/>
@@ -8464,7 +8548,7 @@
     <row r="29" spans="1:65">
       <c r="A29" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B29" t="str">
         <f t="shared" si="1"/>
@@ -8545,7 +8629,7 @@
     <row r="30" spans="1:65">
       <c r="A30" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B30" t="str">
         <f t="shared" si="1"/>
@@ -8626,7 +8710,7 @@
     <row r="31" spans="1:65">
       <c r="A31" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B31" t="str">
         <f t="shared" si="1"/>
@@ -8705,7 +8789,7 @@
     <row r="32" spans="1:65">
       <c r="A32" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B32" t="str">
         <f t="shared" si="1"/>
@@ -8784,7 +8868,7 @@
     <row r="33" spans="1:65">
       <c r="A33" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B33" t="str">
         <f t="shared" si="1"/>
@@ -8863,7 +8947,7 @@
     <row r="34" spans="1:65">
       <c r="A34" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B34" t="str">
         <f t="shared" si="1"/>
@@ -8944,7 +9028,7 @@
     <row r="35" spans="1:65">
       <c r="A35" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B35" t="str">
         <f t="shared" si="1"/>
@@ -9025,7 +9109,7 @@
     <row r="36" spans="1:65">
       <c r="A36" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B36" t="str">
         <f t="shared" si="1"/>
@@ -9106,7 +9190,7 @@
     <row r="37" spans="1:65">
       <c r="A37" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B37" t="str">
         <f t="shared" si="1"/>
@@ -9185,7 +9269,7 @@
     <row r="38" spans="1:65">
       <c r="A38" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B38" t="str">
         <f t="shared" si="1"/>
@@ -9264,7 +9348,7 @@
     <row r="39" spans="1:65">
       <c r="A39" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B39" t="str">
         <f t="shared" si="1"/>
@@ -9343,7 +9427,7 @@
     <row r="40" spans="1:65">
       <c r="A40" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B40" t="str">
         <f t="shared" si="1"/>
@@ -9422,7 +9506,7 @@
     <row r="41" spans="1:65">
       <c r="A41" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B41" t="str">
         <f t="shared" si="1"/>
@@ -9501,7 +9585,7 @@
     <row r="42" spans="1:65">
       <c r="A42" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B42" t="str">
         <f t="shared" si="1"/>
@@ -9582,7 +9666,7 @@
     <row r="43" spans="1:65">
       <c r="A43" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B43" t="str">
         <f t="shared" si="1"/>
@@ -9663,7 +9747,7 @@
     <row r="44" spans="1:65">
       <c r="A44" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B44" t="str">
         <f t="shared" si="1"/>
@@ -9742,7 +9826,7 @@
     <row r="45" spans="1:65">
       <c r="A45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B45" t="str">
         <f t="shared" si="1"/>
@@ -9821,7 +9905,7 @@
     <row r="46" spans="1:65">
       <c r="A46" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B46" t="str">
         <f t="shared" si="1"/>
@@ -9900,7 +9984,7 @@
     <row r="47" spans="1:65">
       <c r="A47" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B47" t="str">
         <f t="shared" si="1"/>
@@ -9979,7 +10063,7 @@
     <row r="48" spans="1:65">
       <c r="A48" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B48" t="str">
         <f t="shared" si="1"/>
@@ -10058,7 +10142,7 @@
     <row r="49" spans="1:65">
       <c r="A49" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B49" t="str">
         <f t="shared" si="1"/>
@@ -10139,7 +10223,7 @@
     <row r="50" spans="1:65">
       <c r="A50" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B50" t="str">
         <f t="shared" si="1"/>
@@ -10220,7 +10304,7 @@
     <row r="51" spans="1:65">
       <c r="A51" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B51" t="str">
         <f t="shared" si="1"/>
@@ -10299,7 +10383,7 @@
     <row r="52" spans="1:65">
       <c r="A52" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B52" t="str">
         <f t="shared" si="1"/>
@@ -10378,7 +10462,7 @@
     <row r="53" spans="1:65">
       <c r="A53" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B53" t="str">
         <f t="shared" si="1"/>
@@ -10457,7 +10541,7 @@
     <row r="54" spans="1:65">
       <c r="A54" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B54" t="str">
         <f t="shared" si="1"/>
@@ -10536,7 +10620,7 @@
     <row r="55" spans="1:65">
       <c r="A55" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B55" t="str">
         <f t="shared" si="1"/>
@@ -10615,7 +10699,7 @@
     <row r="56" spans="1:65">
       <c r="A56" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B56" t="str">
         <f t="shared" si="1"/>
@@ -10696,7 +10780,7 @@
     <row r="57" spans="1:65">
       <c r="A57" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B57" t="str">
         <f t="shared" si="1"/>
@@ -10775,7 +10859,7 @@
     <row r="58" spans="1:65">
       <c r="A58" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B58" t="str">
         <f t="shared" si="1"/>
@@ -10856,7 +10940,7 @@
     <row r="59" spans="1:65">
       <c r="A59" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B59" t="str">
         <f t="shared" si="1"/>
@@ -10935,7 +11019,7 @@
     <row r="60" spans="1:65">
       <c r="A60" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B60" t="str">
         <f t="shared" si="1"/>
@@ -11014,7 +11098,7 @@
     <row r="61" spans="1:65">
       <c r="A61" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B61" t="str">
         <f t="shared" si="1"/>
@@ -11093,7 +11177,7 @@
     <row r="62" spans="1:65">
       <c r="A62" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B62" t="str">
         <f t="shared" si="1"/>
@@ -11172,7 +11256,7 @@
     <row r="63" spans="1:65">
       <c r="A63" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B63" t="str">
         <f t="shared" si="1"/>
@@ -11251,7 +11335,7 @@
     <row r="64" spans="1:65">
       <c r="A64" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B64" t="str">
         <f t="shared" si="1"/>
@@ -11332,7 +11416,7 @@
     <row r="65" spans="1:65">
       <c r="A65" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B65" t="str">
         <f t="shared" si="1"/>
@@ -11411,7 +11495,7 @@
     <row r="66" spans="1:65">
       <c r="A66" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B66" t="str">
         <f t="shared" si="1"/>
@@ -11490,7 +11574,7 @@
     <row r="67" spans="1:65">
       <c r="A67" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B67" t="str">
         <f t="shared" si="1"/>
@@ -11572,7 +11656,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B68" t="str">
         <f t="shared" ref="B68:B131" si="3">TEXT($C68, "HH:mm")</f>
@@ -11651,7 +11735,7 @@
     <row r="69" spans="1:65">
       <c r="A69" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B69" t="str">
         <f t="shared" si="3"/>
@@ -11730,7 +11814,7 @@
     <row r="70" spans="1:65">
       <c r="A70" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B70" t="str">
         <f t="shared" si="3"/>
@@ -11809,7 +11893,7 @@
     <row r="71" spans="1:65">
       <c r="A71" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B71" t="str">
         <f t="shared" si="3"/>
@@ -11888,7 +11972,7 @@
     <row r="72" spans="1:65">
       <c r="A72" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B72" t="str">
         <f t="shared" si="3"/>
@@ -11967,7 +12051,7 @@
     <row r="73" spans="1:65">
       <c r="A73" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B73" t="str">
         <f t="shared" si="3"/>
@@ -12046,7 +12130,7 @@
     <row r="74" spans="1:65">
       <c r="A74" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B74" t="str">
         <f t="shared" si="3"/>
@@ -12125,7 +12209,7 @@
     <row r="75" spans="1:65">
       <c r="A75" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B75" t="str">
         <f t="shared" si="3"/>
@@ -12204,7 +12288,7 @@
     <row r="76" spans="1:65">
       <c r="A76" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B76" t="str">
         <f t="shared" si="3"/>
@@ -12283,7 +12367,7 @@
     <row r="77" spans="1:65">
       <c r="A77" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B77" t="str">
         <f t="shared" si="3"/>
@@ -12362,7 +12446,7 @@
     <row r="78" spans="1:65">
       <c r="A78" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B78" t="str">
         <f t="shared" si="3"/>
@@ -12441,7 +12525,7 @@
     <row r="79" spans="1:65">
       <c r="A79" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B79" t="str">
         <f t="shared" si="3"/>
@@ -12520,7 +12604,7 @@
     <row r="80" spans="1:65">
       <c r="A80" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B80" t="str">
         <f t="shared" si="3"/>
@@ -12599,7 +12683,7 @@
     <row r="81" spans="1:65">
       <c r="A81" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B81" t="str">
         <f t="shared" si="3"/>
@@ -12678,7 +12762,7 @@
     <row r="82" spans="1:65">
       <c r="A82" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B82" t="str">
         <f t="shared" si="3"/>
@@ -12757,7 +12841,7 @@
     <row r="83" spans="1:65">
       <c r="A83" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B83" t="str">
         <f t="shared" si="3"/>
@@ -12836,7 +12920,7 @@
     <row r="84" spans="1:65">
       <c r="A84" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B84" t="str">
         <f t="shared" si="3"/>
@@ -12915,7 +12999,7 @@
     <row r="85" spans="1:65">
       <c r="A85" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B85" t="str">
         <f t="shared" si="3"/>
@@ -12994,7 +13078,7 @@
     <row r="86" spans="1:65">
       <c r="A86" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B86" t="str">
         <f t="shared" si="3"/>
@@ -13073,7 +13157,7 @@
     <row r="87" spans="1:65">
       <c r="A87" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B87" t="str">
         <f t="shared" si="3"/>
@@ -13152,7 +13236,7 @@
     <row r="88" spans="1:65">
       <c r="A88" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B88" t="str">
         <f t="shared" si="3"/>
@@ -13231,7 +13315,7 @@
     <row r="89" spans="1:65">
       <c r="A89" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B89" t="str">
         <f t="shared" si="3"/>
@@ -13310,7 +13394,7 @@
     <row r="90" spans="1:65">
       <c r="A90" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B90" t="str">
         <f t="shared" si="3"/>
@@ -13389,7 +13473,7 @@
     <row r="91" spans="1:65">
       <c r="A91" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B91" t="str">
         <f t="shared" si="3"/>
@@ -13468,7 +13552,7 @@
     <row r="92" spans="1:65">
       <c r="A92" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B92" t="str">
         <f t="shared" si="3"/>
@@ -13547,7 +13631,7 @@
     <row r="93" spans="1:65">
       <c r="A93" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B93" t="str">
         <f t="shared" si="3"/>
@@ -13626,7 +13710,7 @@
     <row r="94" spans="1:65">
       <c r="A94" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B94" t="str">
         <f t="shared" si="3"/>
@@ -13705,7 +13789,7 @@
     <row r="95" spans="1:65">
       <c r="A95" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B95" t="str">
         <f t="shared" si="3"/>
@@ -13784,7 +13868,7 @@
     <row r="96" spans="1:65">
       <c r="A96" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B96" t="str">
         <f t="shared" si="3"/>
@@ -13863,7 +13947,7 @@
     <row r="97" spans="1:65">
       <c r="A97" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B97" t="str">
         <f t="shared" si="3"/>
@@ -13942,7 +14026,7 @@
     <row r="98" spans="1:65">
       <c r="A98" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B98" t="str">
         <f t="shared" si="3"/>
@@ -14021,7 +14105,7 @@
     <row r="99" spans="1:65">
       <c r="A99" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B99" t="str">
         <f t="shared" si="3"/>
@@ -14100,7 +14184,7 @@
     <row r="100" spans="1:65">
       <c r="A100" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B100" t="str">
         <f t="shared" si="3"/>
@@ -14181,7 +14265,7 @@
     <row r="101" spans="1:65">
       <c r="A101" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B101" t="str">
         <f t="shared" si="3"/>
@@ -14260,7 +14344,7 @@
     <row r="102" spans="1:65">
       <c r="A102" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B102" t="str">
         <f t="shared" si="3"/>
@@ -14339,7 +14423,7 @@
     <row r="103" spans="1:65">
       <c r="A103" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B103" t="str">
         <f t="shared" si="3"/>
@@ -14418,7 +14502,7 @@
     <row r="104" spans="1:65">
       <c r="A104" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B104" t="str">
         <f t="shared" si="3"/>
@@ -14497,7 +14581,7 @@
     <row r="105" spans="1:65">
       <c r="A105" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B105" t="str">
         <f t="shared" si="3"/>
@@ -14576,7 +14660,7 @@
     <row r="106" spans="1:65">
       <c r="A106" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B106" t="str">
         <f t="shared" si="3"/>
@@ -14657,7 +14741,7 @@
     <row r="107" spans="1:65">
       <c r="A107" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B107" t="str">
         <f t="shared" si="3"/>
@@ -14738,7 +14822,7 @@
     <row r="108" spans="1:65">
       <c r="A108" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B108" t="str">
         <f t="shared" si="3"/>
@@ -14817,7 +14901,7 @@
     <row r="109" spans="1:65">
       <c r="A109" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B109" t="str">
         <f t="shared" si="3"/>
@@ -14896,7 +14980,7 @@
     <row r="110" spans="1:65">
       <c r="A110" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B110" t="str">
         <f t="shared" si="3"/>
@@ -14975,7 +15059,7 @@
     <row r="111" spans="1:65">
       <c r="A111" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B111" t="str">
         <f t="shared" si="3"/>
@@ -15054,7 +15138,7 @@
     <row r="112" spans="1:65">
       <c r="A112" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B112" t="str">
         <f t="shared" si="3"/>
@@ -15135,7 +15219,7 @@
     <row r="113" spans="1:65">
       <c r="A113" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B113" t="str">
         <f t="shared" si="3"/>
@@ -15214,7 +15298,7 @@
     <row r="114" spans="1:65">
       <c r="A114" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B114" t="str">
         <f t="shared" si="3"/>
@@ -15293,7 +15377,7 @@
     <row r="115" spans="1:65">
       <c r="A115" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B115" t="str">
         <f t="shared" si="3"/>
@@ -15372,7 +15456,7 @@
     <row r="116" spans="1:65">
       <c r="A116" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B116" t="str">
         <f t="shared" si="3"/>
@@ -15451,7 +15535,7 @@
     <row r="117" spans="1:65">
       <c r="A117" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B117" t="str">
         <f t="shared" si="3"/>
@@ -15530,7 +15614,7 @@
     <row r="118" spans="1:65">
       <c r="A118" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B118" t="str">
         <f t="shared" si="3"/>
@@ -15609,7 +15693,7 @@
     <row r="119" spans="1:65">
       <c r="A119" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B119" t="str">
         <f t="shared" si="3"/>
@@ -15688,7 +15772,7 @@
     <row r="120" spans="1:65">
       <c r="A120" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B120" t="str">
         <f t="shared" si="3"/>
@@ -15767,7 +15851,7 @@
     <row r="121" spans="1:65">
       <c r="A121" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B121" t="str">
         <f t="shared" si="3"/>
@@ -15846,7 +15930,7 @@
     <row r="122" spans="1:65">
       <c r="A122" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B122" t="str">
         <f t="shared" si="3"/>
@@ -15925,7 +16009,7 @@
     <row r="123" spans="1:65">
       <c r="A123" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B123" t="str">
         <f t="shared" si="3"/>
@@ -16004,7 +16088,7 @@
     <row r="124" spans="1:65">
       <c r="A124" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B124" t="str">
         <f t="shared" si="3"/>
@@ -16085,7 +16169,7 @@
     <row r="125" spans="1:65">
       <c r="A125" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B125" t="str">
         <f t="shared" si="3"/>
@@ -16166,7 +16250,7 @@
     <row r="126" spans="1:65">
       <c r="A126" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B126" t="str">
         <f t="shared" si="3"/>
@@ -16245,7 +16329,7 @@
     <row r="127" spans="1:65">
       <c r="A127" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B127" t="str">
         <f t="shared" si="3"/>
@@ -16324,7 +16408,7 @@
     <row r="128" spans="1:65">
       <c r="A128" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B128" t="str">
         <f t="shared" si="3"/>
@@ -16403,7 +16487,7 @@
     <row r="129" spans="1:65">
       <c r="A129" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B129" t="str">
         <f t="shared" si="3"/>
@@ -16482,7 +16566,7 @@
     <row r="130" spans="1:65">
       <c r="A130" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B130" t="str">
         <f t="shared" si="3"/>
@@ -16561,7 +16645,7 @@
     <row r="131" spans="1:65">
       <c r="A131" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B131" t="str">
         <f t="shared" si="3"/>
@@ -16643,7 +16727,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B132" t="str">
         <f t="shared" ref="B132:B168" si="5">TEXT($C132, "HH:mm")</f>
@@ -16722,7 +16806,7 @@
     <row r="133" spans="1:65">
       <c r="A133" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B133" t="str">
         <f t="shared" si="5"/>
@@ -16801,7 +16885,7 @@
     <row r="134" spans="1:65">
       <c r="A134" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B134" t="str">
         <f t="shared" si="5"/>
@@ -16880,7 +16964,7 @@
     <row r="135" spans="1:65">
       <c r="A135" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B135" t="str">
         <f t="shared" si="5"/>
@@ -16959,7 +17043,7 @@
     <row r="136" spans="1:65">
       <c r="A136" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B136" t="str">
         <f t="shared" si="5"/>
@@ -17040,7 +17124,7 @@
     <row r="137" spans="1:65">
       <c r="A137" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B137" t="str">
         <f t="shared" si="5"/>
@@ -17121,7 +17205,7 @@
     <row r="138" spans="1:65">
       <c r="A138" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B138" t="str">
         <f t="shared" si="5"/>
@@ -17200,7 +17284,7 @@
     <row r="139" spans="1:65">
       <c r="A139" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B139" t="str">
         <f t="shared" si="5"/>
@@ -17279,7 +17363,7 @@
     <row r="140" spans="1:65">
       <c r="A140" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B140" t="str">
         <f t="shared" si="5"/>
@@ -17358,7 +17442,7 @@
     <row r="141" spans="1:65">
       <c r="A141" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B141" t="str">
         <f t="shared" si="5"/>
@@ -17437,7 +17521,7 @@
     <row r="142" spans="1:65">
       <c r="A142" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B142" t="str">
         <f t="shared" si="5"/>
@@ -17516,7 +17600,7 @@
     <row r="143" spans="1:65">
       <c r="A143" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B143" t="str">
         <f t="shared" si="5"/>
@@ -17595,7 +17679,7 @@
     <row r="144" spans="1:65">
       <c r="A144" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B144" t="str">
         <f t="shared" si="5"/>
@@ -17674,7 +17758,7 @@
     <row r="145" spans="1:65">
       <c r="A145" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B145" t="str">
         <f t="shared" si="5"/>
@@ -17753,7 +17837,7 @@
     <row r="146" spans="1:65">
       <c r="A146" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B146" t="str">
         <f t="shared" si="5"/>
@@ -17832,7 +17916,7 @@
     <row r="147" spans="1:65">
       <c r="A147" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B147" t="str">
         <f t="shared" si="5"/>
@@ -17911,7 +17995,7 @@
     <row r="148" spans="1:65">
       <c r="A148" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B148" t="str">
         <f t="shared" si="5"/>
@@ -17992,7 +18076,7 @@
     <row r="149" spans="1:65">
       <c r="A149" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B149" t="str">
         <f t="shared" si="5"/>
@@ -18071,7 +18155,7 @@
     <row r="150" spans="1:65">
       <c r="A150" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B150" t="str">
         <f t="shared" si="5"/>
@@ -18150,7 +18234,7 @@
     <row r="151" spans="1:65">
       <c r="A151" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B151" t="str">
         <f t="shared" si="5"/>
@@ -18229,7 +18313,7 @@
     <row r="152" spans="1:65">
       <c r="A152" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B152" t="str">
         <f t="shared" si="5"/>
@@ -18308,7 +18392,7 @@
     <row r="153" spans="1:65">
       <c r="A153" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B153" t="str">
         <f t="shared" si="5"/>
@@ -18387,7 +18471,7 @@
     <row r="154" spans="1:65">
       <c r="A154" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B154" t="str">
         <f t="shared" si="5"/>
@@ -18466,7 +18550,7 @@
     <row r="155" spans="1:65">
       <c r="A155" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B155" t="str">
         <f t="shared" si="5"/>
@@ -18545,7 +18629,7 @@
     <row r="156" spans="1:65">
       <c r="A156" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B156" t="str">
         <f t="shared" si="5"/>
@@ -18624,7 +18708,7 @@
     <row r="157" spans="1:65">
       <c r="A157" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B157" t="str">
         <f t="shared" si="5"/>
@@ -18703,7 +18787,7 @@
     <row r="158" spans="1:65">
       <c r="A158" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B158" t="str">
         <f t="shared" si="5"/>
@@ -18782,7 +18866,7 @@
     <row r="159" spans="1:65">
       <c r="A159" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B159" t="str">
         <f t="shared" si="5"/>
@@ -18861,7 +18945,7 @@
     <row r="160" spans="1:65">
       <c r="A160" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B160" t="str">
         <f t="shared" si="5"/>
@@ -18940,7 +19024,7 @@
     <row r="161" spans="1:65">
       <c r="A161" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B161" t="str">
         <f t="shared" si="5"/>
@@ -19019,7 +19103,7 @@
     <row r="162" spans="1:65">
       <c r="A162" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B162" t="str">
         <f t="shared" si="5"/>
@@ -19098,7 +19182,7 @@
     <row r="163" spans="1:65">
       <c r="A163" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B163" t="str">
         <f t="shared" si="5"/>
@@ -19177,7 +19261,7 @@
     <row r="164" spans="1:65">
       <c r="A164" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B164" t="str">
         <f t="shared" si="5"/>
@@ -19256,7 +19340,7 @@
     <row r="165" spans="1:65">
       <c r="A165" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B165" t="str">
         <f t="shared" si="5"/>
@@ -19335,7 +19419,7 @@
     <row r="166" spans="1:65">
       <c r="A166" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B166" t="str">
         <f t="shared" si="5"/>
@@ -19416,7 +19500,7 @@
     <row r="167" spans="1:65">
       <c r="A167" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B167" t="str">
         <f t="shared" si="5"/>
@@ -19495,7 +19579,7 @@
     <row r="168" spans="1:65">
       <c r="A168" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B168" t="str">
         <f t="shared" si="5"/>
@@ -19577,7 +19661,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B169" t="str">
         <f>TEXT($C169, "HH:mm")</f>
@@ -19659,7 +19743,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B170" t="str">
         <f t="shared" ref="B170:B233" si="7">TEXT($C170, "HH:mm")</f>
@@ -19738,7 +19822,7 @@
     <row r="171" spans="1:65">
       <c r="A171" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B171" t="str">
         <f t="shared" si="7"/>
@@ -19817,7 +19901,7 @@
     <row r="172" spans="1:65">
       <c r="A172" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B172" t="str">
         <f t="shared" si="7"/>
@@ -19898,7 +19982,7 @@
     <row r="173" spans="1:65">
       <c r="A173" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B173" t="str">
         <f t="shared" si="7"/>
@@ -19977,7 +20061,7 @@
     <row r="174" spans="1:65">
       <c r="A174" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B174" t="str">
         <f t="shared" si="7"/>
@@ -20056,7 +20140,7 @@
     <row r="175" spans="1:65">
       <c r="A175" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B175" t="str">
         <f t="shared" si="7"/>
@@ -20135,7 +20219,7 @@
     <row r="176" spans="1:65">
       <c r="A176" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B176" t="str">
         <f t="shared" si="7"/>
@@ -20214,7 +20298,7 @@
     <row r="177" spans="1:65">
       <c r="A177" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B177" t="str">
         <f t="shared" si="7"/>
@@ -20293,7 +20377,7 @@
     <row r="178" spans="1:65">
       <c r="A178" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B178" t="str">
         <f t="shared" si="7"/>
@@ -20374,7 +20458,7 @@
     <row r="179" spans="1:65">
       <c r="A179" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B179" t="str">
         <f t="shared" si="7"/>
@@ -20453,7 +20537,7 @@
     <row r="180" spans="1:65">
       <c r="A180" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B180" t="str">
         <f t="shared" si="7"/>
@@ -20532,7 +20616,7 @@
     <row r="181" spans="1:65">
       <c r="A181" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B181" t="str">
         <f t="shared" si="7"/>
@@ -20613,7 +20697,7 @@
     <row r="182" spans="1:65">
       <c r="A182" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B182" t="str">
         <f t="shared" si="7"/>
@@ -20694,7 +20778,7 @@
     <row r="183" spans="1:65">
       <c r="A183" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B183" t="str">
         <f t="shared" si="7"/>
@@ -20775,7 +20859,7 @@
     <row r="184" spans="1:65">
       <c r="A184" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B184" t="str">
         <f t="shared" si="7"/>
@@ -20858,7 +20942,7 @@
     <row r="185" spans="1:65">
       <c r="A185" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B185" t="str">
         <f t="shared" si="7"/>
@@ -20939,7 +21023,7 @@
     <row r="186" spans="1:65">
       <c r="A186" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B186" t="str">
         <f t="shared" si="7"/>
@@ -21020,7 +21104,7 @@
     <row r="187" spans="1:65">
       <c r="A187" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B187" t="str">
         <f t="shared" si="7"/>
@@ -21101,7 +21185,7 @@
     <row r="188" spans="1:65">
       <c r="A188" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B188" t="str">
         <f t="shared" si="7"/>
@@ -21182,7 +21266,7 @@
     <row r="189" spans="1:65">
       <c r="A189" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B189" t="str">
         <f t="shared" si="7"/>
@@ -21263,7 +21347,7 @@
     <row r="190" spans="1:65">
       <c r="A190" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B190" t="str">
         <f t="shared" si="7"/>
@@ -21346,7 +21430,7 @@
     <row r="191" spans="1:65">
       <c r="A191" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B191" t="str">
         <f t="shared" si="7"/>
@@ -21429,7 +21513,7 @@
     <row r="192" spans="1:65">
       <c r="A192" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B192" t="str">
         <f t="shared" si="7"/>
@@ -21512,7 +21596,7 @@
     <row r="193" spans="1:65">
       <c r="A193" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B193" t="str">
         <f t="shared" si="7"/>
@@ -21595,7 +21679,7 @@
     <row r="194" spans="1:65">
       <c r="A194" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B194" t="str">
         <f t="shared" si="7"/>
@@ -21676,7 +21760,7 @@
     <row r="195" spans="1:65">
       <c r="A195" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B195" t="str">
         <f t="shared" si="7"/>
@@ -21757,7 +21841,7 @@
     <row r="196" spans="1:65">
       <c r="A196" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B196" t="str">
         <f t="shared" si="7"/>
@@ -21840,7 +21924,7 @@
     <row r="197" spans="1:65">
       <c r="A197" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B197" t="str">
         <f t="shared" si="7"/>
@@ -21919,7 +22003,7 @@
     <row r="198" spans="1:65">
       <c r="A198" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B198" t="str">
         <f t="shared" si="7"/>
@@ -21998,7 +22082,7 @@
     <row r="199" spans="1:65">
       <c r="A199" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B199" t="str">
         <f t="shared" si="7"/>
@@ -22077,7 +22161,7 @@
     <row r="200" spans="1:65">
       <c r="A200" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B200" t="str">
         <f t="shared" si="7"/>
@@ -22156,7 +22240,7 @@
     <row r="201" spans="1:65">
       <c r="A201" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B201" t="str">
         <f t="shared" si="7"/>
@@ -22235,7 +22319,7 @@
     <row r="202" spans="1:65">
       <c r="A202" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B202" t="str">
         <f t="shared" si="7"/>
@@ -22316,7 +22400,7 @@
     <row r="203" spans="1:65">
       <c r="A203" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B203" t="str">
         <f t="shared" si="7"/>
@@ -22395,7 +22479,7 @@
     <row r="204" spans="1:65">
       <c r="A204" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B204" t="str">
         <f t="shared" si="7"/>
@@ -22474,7 +22558,7 @@
     <row r="205" spans="1:65">
       <c r="A205" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B205" t="str">
         <f t="shared" si="7"/>
@@ -22553,7 +22637,7 @@
     <row r="206" spans="1:65">
       <c r="A206" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B206" t="str">
         <f t="shared" si="7"/>
@@ -22632,7 +22716,7 @@
     <row r="207" spans="1:65">
       <c r="A207" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B207" t="str">
         <f t="shared" si="7"/>
@@ -22711,7 +22795,7 @@
     <row r="208" spans="1:65">
       <c r="A208" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B208" t="str">
         <f t="shared" si="7"/>
@@ -22792,7 +22876,7 @@
     <row r="209" spans="1:65">
       <c r="A209" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B209" t="str">
         <f t="shared" si="7"/>
@@ -22871,7 +22955,7 @@
     <row r="210" spans="1:65">
       <c r="A210" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B210" t="str">
         <f t="shared" si="7"/>
@@ -22950,7 +23034,7 @@
     <row r="211" spans="1:65">
       <c r="A211" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B211" t="str">
         <f t="shared" si="7"/>
@@ -23031,7 +23115,7 @@
     <row r="212" spans="1:65">
       <c r="A212" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B212" t="str">
         <f t="shared" si="7"/>
@@ -23110,7 +23194,7 @@
     <row r="213" spans="1:65">
       <c r="A213" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B213" t="str">
         <f t="shared" si="7"/>
@@ -23189,7 +23273,7 @@
     <row r="214" spans="1:65">
       <c r="A214" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B214" t="str">
         <f t="shared" si="7"/>
@@ -23268,7 +23352,7 @@
     <row r="215" spans="1:65">
       <c r="A215" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B215" t="str">
         <f t="shared" si="7"/>
@@ -23347,7 +23431,7 @@
     <row r="216" spans="1:65">
       <c r="A216" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B216" t="str">
         <f t="shared" si="7"/>
@@ -23426,7 +23510,7 @@
     <row r="217" spans="1:65">
       <c r="A217" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B217" t="str">
         <f t="shared" si="7"/>
@@ -23505,7 +23589,7 @@
     <row r="218" spans="1:65">
       <c r="A218" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B218" t="str">
         <f t="shared" si="7"/>
@@ -23584,7 +23668,7 @@
     <row r="219" spans="1:65">
       <c r="A219" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B219" t="str">
         <f t="shared" si="7"/>
@@ -23663,7 +23747,7 @@
     <row r="220" spans="1:65">
       <c r="A220" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B220" t="str">
         <f t="shared" si="7"/>
@@ -23744,7 +23828,7 @@
     <row r="221" spans="1:65">
       <c r="A221" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B221" t="str">
         <f t="shared" si="7"/>
@@ -23823,7 +23907,7 @@
     <row r="222" spans="1:65">
       <c r="A222" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B222" t="str">
         <f t="shared" si="7"/>
@@ -23902,7 +23986,7 @@
     <row r="223" spans="1:65">
       <c r="A223" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B223" t="str">
         <f t="shared" si="7"/>
@@ -23981,7 +24065,7 @@
     <row r="224" spans="1:65">
       <c r="A224" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B224" t="str">
         <f t="shared" si="7"/>
@@ -24060,7 +24144,7 @@
     <row r="225" spans="1:65">
       <c r="A225" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B225" t="str">
         <f t="shared" si="7"/>
@@ -24139,7 +24223,7 @@
     <row r="226" spans="1:65">
       <c r="A226" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B226" t="str">
         <f t="shared" si="7"/>
@@ -24218,7 +24302,7 @@
     <row r="227" spans="1:65">
       <c r="A227" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B227" t="str">
         <f t="shared" si="7"/>
@@ -24297,7 +24381,7 @@
     <row r="228" spans="1:65">
       <c r="A228" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B228" t="str">
         <f t="shared" si="7"/>
@@ -24376,7 +24460,7 @@
     <row r="229" spans="1:65">
       <c r="A229" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B229" t="str">
         <f t="shared" si="7"/>
@@ -24455,7 +24539,7 @@
     <row r="230" spans="1:65">
       <c r="A230" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B230" t="str">
         <f t="shared" si="7"/>
@@ -24534,7 +24618,7 @@
     <row r="231" spans="1:65">
       <c r="A231" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B231" t="str">
         <f t="shared" si="7"/>
@@ -24613,7 +24697,7 @@
     <row r="232" spans="1:65">
       <c r="A232" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B232" t="str">
         <f t="shared" si="7"/>
@@ -24692,7 +24776,7 @@
     <row r="233" spans="1:65">
       <c r="A233" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B233" t="str">
         <f t="shared" si="7"/>
@@ -24774,7 +24858,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B234" t="str">
         <f t="shared" ref="B234:B291" si="9">TEXT($C234, "HH:mm")</f>
@@ -24853,7 +24937,7 @@
     <row r="235" spans="1:65">
       <c r="A235" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B235" t="str">
         <f t="shared" si="9"/>
@@ -24932,7 +25016,7 @@
     <row r="236" spans="1:65">
       <c r="A236" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B236" t="str">
         <f t="shared" si="9"/>
@@ -25011,7 +25095,7 @@
     <row r="237" spans="1:65">
       <c r="A237" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B237" t="str">
         <f t="shared" si="9"/>
@@ -25090,7 +25174,7 @@
     <row r="238" spans="1:65">
       <c r="A238" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B238" t="str">
         <f t="shared" si="9"/>
@@ -25169,7 +25253,7 @@
     <row r="239" spans="1:65">
       <c r="A239" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B239" t="str">
         <f t="shared" si="9"/>
@@ -25248,7 +25332,7 @@
     <row r="240" spans="1:65">
       <c r="A240" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B240" t="str">
         <f t="shared" si="9"/>
@@ -25327,7 +25411,7 @@
     <row r="241" spans="1:65">
       <c r="A241" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B241" t="str">
         <f t="shared" si="9"/>
@@ -25406,7 +25490,7 @@
     <row r="242" spans="1:65">
       <c r="A242" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B242" t="str">
         <f t="shared" si="9"/>
@@ -25485,7 +25569,7 @@
     <row r="243" spans="1:65">
       <c r="A243" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B243" t="str">
         <f t="shared" si="9"/>
@@ -25564,7 +25648,7 @@
     <row r="244" spans="1:65">
       <c r="A244" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B244" t="str">
         <f t="shared" si="9"/>
@@ -25643,7 +25727,7 @@
     <row r="245" spans="1:65">
       <c r="A245" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B245" t="str">
         <f t="shared" si="9"/>
@@ -25722,7 +25806,7 @@
     <row r="246" spans="1:65">
       <c r="A246" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B246" t="str">
         <f t="shared" si="9"/>
@@ -25801,7 +25885,7 @@
     <row r="247" spans="1:65">
       <c r="A247" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B247" t="str">
         <f t="shared" si="9"/>
@@ -25880,7 +25964,7 @@
     <row r="248" spans="1:65">
       <c r="A248" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B248" t="str">
         <f t="shared" si="9"/>
@@ -25959,7 +26043,7 @@
     <row r="249" spans="1:65">
       <c r="A249" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B249" t="str">
         <f t="shared" si="9"/>
@@ -26038,7 +26122,7 @@
     <row r="250" spans="1:65">
       <c r="A250" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B250" t="str">
         <f t="shared" si="9"/>
@@ -26117,7 +26201,7 @@
     <row r="251" spans="1:65">
       <c r="A251" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B251" t="str">
         <f t="shared" si="9"/>
@@ -26196,7 +26280,7 @@
     <row r="252" spans="1:65">
       <c r="A252" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B252" t="str">
         <f t="shared" si="9"/>
@@ -26275,7 +26359,7 @@
     <row r="253" spans="1:65">
       <c r="A253" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B253" t="str">
         <f t="shared" si="9"/>
@@ -26354,7 +26438,7 @@
     <row r="254" spans="1:65">
       <c r="A254" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B254" t="str">
         <f t="shared" si="9"/>
@@ -26433,7 +26517,7 @@
     <row r="255" spans="1:65">
       <c r="A255" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B255" t="str">
         <f t="shared" si="9"/>
@@ -26512,7 +26596,7 @@
     <row r="256" spans="1:65">
       <c r="A256" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B256" t="str">
         <f t="shared" si="9"/>
@@ -26591,7 +26675,7 @@
     <row r="257" spans="1:65">
       <c r="A257" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B257" t="str">
         <f t="shared" si="9"/>
@@ -26670,7 +26754,7 @@
     <row r="258" spans="1:65">
       <c r="A258" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B258" t="str">
         <f t="shared" si="9"/>
@@ -26749,7 +26833,7 @@
     <row r="259" spans="1:65">
       <c r="A259" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B259" t="str">
         <f t="shared" si="9"/>
@@ -26828,7 +26912,7 @@
     <row r="260" spans="1:65">
       <c r="A260" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B260" t="str">
         <f t="shared" si="9"/>
@@ -26907,7 +26991,7 @@
     <row r="261" spans="1:65">
       <c r="A261" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B261" t="str">
         <f t="shared" si="9"/>
@@ -26986,7 +27070,7 @@
     <row r="262" spans="1:65">
       <c r="A262" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B262" t="str">
         <f t="shared" si="9"/>
@@ -27065,7 +27149,7 @@
     <row r="263" spans="1:65">
       <c r="A263" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B263" t="str">
         <f t="shared" si="9"/>
@@ -27144,7 +27228,7 @@
     <row r="264" spans="1:65">
       <c r="A264" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B264" t="str">
         <f t="shared" si="9"/>
@@ -27223,7 +27307,7 @@
     <row r="265" spans="1:65">
       <c r="A265" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B265" t="str">
         <f t="shared" si="9"/>
@@ -27302,7 +27386,7 @@
     <row r="266" spans="1:65">
       <c r="A266" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B266" t="str">
         <f t="shared" si="9"/>
@@ -27381,7 +27465,7 @@
     <row r="267" spans="1:65">
       <c r="A267" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B267" t="str">
         <f t="shared" si="9"/>
@@ -27460,7 +27544,7 @@
     <row r="268" spans="1:65">
       <c r="A268" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B268" t="str">
         <f t="shared" si="9"/>
@@ -27539,7 +27623,7 @@
     <row r="269" spans="1:65">
       <c r="A269" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B269" t="str">
         <f t="shared" si="9"/>
@@ -27618,7 +27702,7 @@
     <row r="270" spans="1:65">
       <c r="A270" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B270" t="str">
         <f t="shared" si="9"/>
@@ -27697,7 +27781,7 @@
     <row r="271" spans="1:65">
       <c r="A271" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B271" t="str">
         <f t="shared" si="9"/>
@@ -27776,7 +27860,7 @@
     <row r="272" spans="1:65">
       <c r="A272" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B272" t="str">
         <f t="shared" si="9"/>
@@ -27855,7 +27939,7 @@
     <row r="273" spans="1:65">
       <c r="A273" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B273" t="str">
         <f t="shared" si="9"/>
@@ -27934,7 +28018,7 @@
     <row r="274" spans="1:65">
       <c r="A274" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B274" t="str">
         <f t="shared" si="9"/>
@@ -28013,7 +28097,7 @@
     <row r="275" spans="1:65">
       <c r="A275" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B275" t="str">
         <f t="shared" si="9"/>
@@ -28092,7 +28176,7 @@
     <row r="276" spans="1:65">
       <c r="A276" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B276" t="str">
         <f t="shared" si="9"/>
@@ -28171,7 +28255,7 @@
     <row r="277" spans="1:65">
       <c r="A277" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B277" t="str">
         <f t="shared" si="9"/>
@@ -28250,7 +28334,7 @@
     <row r="278" spans="1:65">
       <c r="A278" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B278" t="str">
         <f t="shared" si="9"/>
@@ -28329,7 +28413,7 @@
     <row r="279" spans="1:65">
       <c r="A279" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B279" t="str">
         <f t="shared" si="9"/>
@@ -28408,7 +28492,7 @@
     <row r="280" spans="1:65">
       <c r="A280" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B280" t="str">
         <f t="shared" si="9"/>
@@ -28487,7 +28571,7 @@
     <row r="281" spans="1:65">
       <c r="A281" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B281" t="str">
         <f t="shared" si="9"/>
@@ -28566,7 +28650,7 @@
     <row r="282" spans="1:65">
       <c r="A282" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B282" t="str">
         <f t="shared" si="9"/>
@@ -28645,7 +28729,7 @@
     <row r="283" spans="1:65">
       <c r="A283" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B283" t="str">
         <f t="shared" si="9"/>
@@ -28724,7 +28808,7 @@
     <row r="284" spans="1:65">
       <c r="A284" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B284" t="str">
         <f t="shared" si="9"/>
@@ -28803,7 +28887,7 @@
     <row r="285" spans="1:65">
       <c r="A285" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B285" t="str">
         <f t="shared" si="9"/>
@@ -28882,7 +28966,7 @@
     <row r="286" spans="1:65">
       <c r="A286" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B286" t="str">
         <f t="shared" si="9"/>
@@ -28961,7 +29045,7 @@
     <row r="287" spans="1:65">
       <c r="A287" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B287" t="str">
         <f t="shared" si="9"/>
@@ -29040,7 +29124,7 @@
     <row r="288" spans="1:65">
       <c r="A288" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B288" t="str">
         <f t="shared" si="9"/>
@@ -29119,7 +29203,7 @@
     <row r="289" spans="1:65">
       <c r="A289" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B289" t="str">
         <f t="shared" si="9"/>
@@ -29198,7 +29282,7 @@
     <row r="290" spans="1:65">
       <c r="A290" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B290" t="str">
         <f t="shared" si="9"/>
@@ -29277,7 +29361,7 @@
     <row r="291" spans="1:65">
       <c r="A291" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>23:55</v>
+        <v>00:55</v>
       </c>
       <c r="B291" t="str">
         <f t="shared" si="9"/>
@@ -31659,7 +31743,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7DD1F4F-4FBA-4AD3-8545-6C67C68E9F78}">
-  <dimension ref="C3:D6"/>
+  <dimension ref="C3:D7"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="3" max="3" width="14.25" bestFit="1" customWidth="1"/>
@@ -31696,6 +31780,14 @@
       </c>
       <c r="D6" t="s">
         <v>902</v>
+      </c>
+    </row>
+    <row r="7" spans="3:4">
+      <c r="C7" t="s">
+        <v>907</v>
+      </c>
+      <c r="D7" t="s">
+        <v>908</v>
       </c>
     </row>
   </sheetData>

--- a/Vite-Vercel開発.xlsx
+++ b/Vite-Vercel開発.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kanta\GitHub\work-time-tracker\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2c67ec30e06f060f/work/GitHub/work-time-tracker/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1928CA11-C4AD-40E9-B1C5-143667E830EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{1928CA11-C4AD-40E9-B1C5-143667E830EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09F32D22-F5A6-44FD-81FA-90E5497223C3}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1535" uniqueCount="913">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1536" uniqueCount="914">
   <si>
     <t>npm install -g vercel</t>
     <phoneticPr fontId="1"/>
@@ -5330,6 +5330,10 @@
   </si>
   <si>
     <t>Found 119 errors in 27 files.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Found 101 errors in 26 files.</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -6102,7 +6106,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{083174DA-A42C-4F9C-978E-61AEAAD9DDFF}">
-  <dimension ref="B2:D17"/>
+  <dimension ref="B2:D18"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
@@ -6195,6 +6199,11 @@
     <row r="17" spans="3:3">
       <c r="C17" t="s">
         <v>912</v>
+      </c>
+    </row>
+    <row r="18" spans="3:3">
+      <c r="C18" t="s">
+        <v>913</v>
       </c>
     </row>
   </sheetData>
@@ -6361,7 +6370,7 @@
       MOD(NOW(),1),
       TIME(0,5,0)
     ),"HH:mm")</f>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B2" s="19"/>
       <c r="D2" s="1">
@@ -6372,7 +6381,7 @@
     <row r="3" spans="1:65">
       <c r="A3" s="19" t="str">
         <f ca="1">TEXT(NOW(),"HH:mm")</f>
-        <v>00:59</v>
+        <v>01:04</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="17" t="s">
@@ -6571,7 +6580,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B4" t="str">
         <f t="shared" ref="B4:B67" si="1">TEXT($C4, "HH:mm")</f>
@@ -6650,7 +6659,7 @@
     <row r="5" spans="1:65">
       <c r="A5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B5" t="str">
         <f t="shared" si="1"/>
@@ -6729,7 +6738,7 @@
     <row r="6" spans="1:65">
       <c r="A6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B6" t="str">
         <f t="shared" si="1"/>
@@ -6808,7 +6817,7 @@
     <row r="7" spans="1:65">
       <c r="A7" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B7" t="str">
         <f t="shared" si="1"/>
@@ -6887,7 +6896,7 @@
     <row r="8" spans="1:65">
       <c r="A8" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B8" t="str">
         <f t="shared" si="1"/>
@@ -6966,7 +6975,7 @@
     <row r="9" spans="1:65">
       <c r="A9" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B9" t="str">
         <f t="shared" si="1"/>
@@ -7045,7 +7054,7 @@
     <row r="10" spans="1:65">
       <c r="A10" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B10" t="str">
         <f t="shared" si="1"/>
@@ -7124,7 +7133,7 @@
     <row r="11" spans="1:65">
       <c r="A11" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B11" t="str">
         <f t="shared" si="1"/>
@@ -7203,7 +7212,7 @@
     <row r="12" spans="1:65">
       <c r="A12" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B12" t="str">
         <f t="shared" si="1"/>
@@ -7282,7 +7291,7 @@
     <row r="13" spans="1:65">
       <c r="A13" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B13" t="str">
         <f t="shared" si="1"/>
@@ -7361,7 +7370,7 @@
     <row r="14" spans="1:65">
       <c r="A14" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B14" t="str">
         <f t="shared" si="1"/>
@@ -7440,7 +7449,7 @@
     <row r="15" spans="1:65">
       <c r="A15" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B15" t="str">
         <f t="shared" si="1"/>
@@ -7519,7 +7528,7 @@
     <row r="16" spans="1:65">
       <c r="A16" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B16" t="str">
         <f t="shared" si="1"/>
@@ -7598,7 +7607,7 @@
     <row r="17" spans="1:65">
       <c r="A17" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B17" t="str">
         <f t="shared" si="1"/>
@@ -7677,7 +7686,7 @@
     <row r="18" spans="1:65">
       <c r="A18" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B18" t="str">
         <f t="shared" si="1"/>
@@ -7756,7 +7765,7 @@
     <row r="19" spans="1:65">
       <c r="A19" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B19" t="str">
         <f t="shared" si="1"/>
@@ -7835,7 +7844,7 @@
     <row r="20" spans="1:65">
       <c r="A20" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B20" t="str">
         <f t="shared" si="1"/>
@@ -7914,7 +7923,7 @@
     <row r="21" spans="1:65">
       <c r="A21" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B21" t="str">
         <f t="shared" si="1"/>
@@ -7993,7 +8002,7 @@
     <row r="22" spans="1:65">
       <c r="A22" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B22" t="str">
         <f t="shared" si="1"/>
@@ -8072,7 +8081,7 @@
     <row r="23" spans="1:65">
       <c r="A23" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B23" t="str">
         <f t="shared" si="1"/>
@@ -8151,7 +8160,7 @@
     <row r="24" spans="1:65">
       <c r="A24" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B24" t="str">
         <f t="shared" si="1"/>
@@ -8230,7 +8239,7 @@
     <row r="25" spans="1:65">
       <c r="A25" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B25" t="str">
         <f t="shared" si="1"/>
@@ -8309,7 +8318,7 @@
     <row r="26" spans="1:65">
       <c r="A26" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B26" t="str">
         <f t="shared" si="1"/>
@@ -8388,7 +8397,7 @@
     <row r="27" spans="1:65">
       <c r="A27" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B27" t="str">
         <f t="shared" si="1"/>
@@ -8467,7 +8476,7 @@
     <row r="28" spans="1:65">
       <c r="A28" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B28" t="str">
         <f t="shared" si="1"/>
@@ -8548,7 +8557,7 @@
     <row r="29" spans="1:65">
       <c r="A29" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B29" t="str">
         <f t="shared" si="1"/>
@@ -8629,7 +8638,7 @@
     <row r="30" spans="1:65">
       <c r="A30" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B30" t="str">
         <f t="shared" si="1"/>
@@ -8710,7 +8719,7 @@
     <row r="31" spans="1:65">
       <c r="A31" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B31" t="str">
         <f t="shared" si="1"/>
@@ -8789,7 +8798,7 @@
     <row r="32" spans="1:65">
       <c r="A32" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B32" t="str">
         <f t="shared" si="1"/>
@@ -8868,7 +8877,7 @@
     <row r="33" spans="1:65">
       <c r="A33" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B33" t="str">
         <f t="shared" si="1"/>
@@ -8947,7 +8956,7 @@
     <row r="34" spans="1:65">
       <c r="A34" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B34" t="str">
         <f t="shared" si="1"/>
@@ -9028,7 +9037,7 @@
     <row r="35" spans="1:65">
       <c r="A35" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B35" t="str">
         <f t="shared" si="1"/>
@@ -9109,7 +9118,7 @@
     <row r="36" spans="1:65">
       <c r="A36" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B36" t="str">
         <f t="shared" si="1"/>
@@ -9190,7 +9199,7 @@
     <row r="37" spans="1:65">
       <c r="A37" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B37" t="str">
         <f t="shared" si="1"/>
@@ -9269,7 +9278,7 @@
     <row r="38" spans="1:65">
       <c r="A38" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B38" t="str">
         <f t="shared" si="1"/>
@@ -9348,7 +9357,7 @@
     <row r="39" spans="1:65">
       <c r="A39" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B39" t="str">
         <f t="shared" si="1"/>
@@ -9427,7 +9436,7 @@
     <row r="40" spans="1:65">
       <c r="A40" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B40" t="str">
         <f t="shared" si="1"/>
@@ -9506,7 +9515,7 @@
     <row r="41" spans="1:65">
       <c r="A41" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B41" t="str">
         <f t="shared" si="1"/>
@@ -9585,7 +9594,7 @@
     <row r="42" spans="1:65">
       <c r="A42" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B42" t="str">
         <f t="shared" si="1"/>
@@ -9666,7 +9675,7 @@
     <row r="43" spans="1:65">
       <c r="A43" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B43" t="str">
         <f t="shared" si="1"/>
@@ -9747,7 +9756,7 @@
     <row r="44" spans="1:65">
       <c r="A44" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B44" t="str">
         <f t="shared" si="1"/>
@@ -9826,7 +9835,7 @@
     <row r="45" spans="1:65">
       <c r="A45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B45" t="str">
         <f t="shared" si="1"/>
@@ -9905,7 +9914,7 @@
     <row r="46" spans="1:65">
       <c r="A46" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B46" t="str">
         <f t="shared" si="1"/>
@@ -9984,7 +9993,7 @@
     <row r="47" spans="1:65">
       <c r="A47" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B47" t="str">
         <f t="shared" si="1"/>
@@ -10063,7 +10072,7 @@
     <row r="48" spans="1:65">
       <c r="A48" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B48" t="str">
         <f t="shared" si="1"/>
@@ -10142,7 +10151,7 @@
     <row r="49" spans="1:65">
       <c r="A49" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B49" t="str">
         <f t="shared" si="1"/>
@@ -10223,7 +10232,7 @@
     <row r="50" spans="1:65">
       <c r="A50" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B50" t="str">
         <f t="shared" si="1"/>
@@ -10304,7 +10313,7 @@
     <row r="51" spans="1:65">
       <c r="A51" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B51" t="str">
         <f t="shared" si="1"/>
@@ -10383,7 +10392,7 @@
     <row r="52" spans="1:65">
       <c r="A52" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B52" t="str">
         <f t="shared" si="1"/>
@@ -10462,7 +10471,7 @@
     <row r="53" spans="1:65">
       <c r="A53" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B53" t="str">
         <f t="shared" si="1"/>
@@ -10541,7 +10550,7 @@
     <row r="54" spans="1:65">
       <c r="A54" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B54" t="str">
         <f t="shared" si="1"/>
@@ -10620,7 +10629,7 @@
     <row r="55" spans="1:65">
       <c r="A55" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B55" t="str">
         <f t="shared" si="1"/>
@@ -10699,7 +10708,7 @@
     <row r="56" spans="1:65">
       <c r="A56" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B56" t="str">
         <f t="shared" si="1"/>
@@ -10780,7 +10789,7 @@
     <row r="57" spans="1:65">
       <c r="A57" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B57" t="str">
         <f t="shared" si="1"/>
@@ -10859,7 +10868,7 @@
     <row r="58" spans="1:65">
       <c r="A58" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B58" t="str">
         <f t="shared" si="1"/>
@@ -10940,7 +10949,7 @@
     <row r="59" spans="1:65">
       <c r="A59" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B59" t="str">
         <f t="shared" si="1"/>
@@ -11019,7 +11028,7 @@
     <row r="60" spans="1:65">
       <c r="A60" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B60" t="str">
         <f t="shared" si="1"/>
@@ -11098,7 +11107,7 @@
     <row r="61" spans="1:65">
       <c r="A61" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B61" t="str">
         <f t="shared" si="1"/>
@@ -11177,7 +11186,7 @@
     <row r="62" spans="1:65">
       <c r="A62" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B62" t="str">
         <f t="shared" si="1"/>
@@ -11256,7 +11265,7 @@
     <row r="63" spans="1:65">
       <c r="A63" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B63" t="str">
         <f t="shared" si="1"/>
@@ -11335,7 +11344,7 @@
     <row r="64" spans="1:65">
       <c r="A64" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B64" t="str">
         <f t="shared" si="1"/>
@@ -11416,7 +11425,7 @@
     <row r="65" spans="1:65">
       <c r="A65" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B65" t="str">
         <f t="shared" si="1"/>
@@ -11495,7 +11504,7 @@
     <row r="66" spans="1:65">
       <c r="A66" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B66" t="str">
         <f t="shared" si="1"/>
@@ -11574,7 +11583,7 @@
     <row r="67" spans="1:65">
       <c r="A67" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B67" t="str">
         <f t="shared" si="1"/>
@@ -11656,7 +11665,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B68" t="str">
         <f t="shared" ref="B68:B131" si="3">TEXT($C68, "HH:mm")</f>
@@ -11735,7 +11744,7 @@
     <row r="69" spans="1:65">
       <c r="A69" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B69" t="str">
         <f t="shared" si="3"/>
@@ -11814,7 +11823,7 @@
     <row r="70" spans="1:65">
       <c r="A70" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B70" t="str">
         <f t="shared" si="3"/>
@@ -11893,7 +11902,7 @@
     <row r="71" spans="1:65">
       <c r="A71" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B71" t="str">
         <f t="shared" si="3"/>
@@ -11972,7 +11981,7 @@
     <row r="72" spans="1:65">
       <c r="A72" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B72" t="str">
         <f t="shared" si="3"/>
@@ -12051,7 +12060,7 @@
     <row r="73" spans="1:65">
       <c r="A73" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B73" t="str">
         <f t="shared" si="3"/>
@@ -12130,7 +12139,7 @@
     <row r="74" spans="1:65">
       <c r="A74" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B74" t="str">
         <f t="shared" si="3"/>
@@ -12209,7 +12218,7 @@
     <row r="75" spans="1:65">
       <c r="A75" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B75" t="str">
         <f t="shared" si="3"/>
@@ -12288,7 +12297,7 @@
     <row r="76" spans="1:65">
       <c r="A76" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B76" t="str">
         <f t="shared" si="3"/>
@@ -12367,7 +12376,7 @@
     <row r="77" spans="1:65">
       <c r="A77" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B77" t="str">
         <f t="shared" si="3"/>
@@ -12446,7 +12455,7 @@
     <row r="78" spans="1:65">
       <c r="A78" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B78" t="str">
         <f t="shared" si="3"/>
@@ -12525,7 +12534,7 @@
     <row r="79" spans="1:65">
       <c r="A79" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B79" t="str">
         <f t="shared" si="3"/>
@@ -12604,7 +12613,7 @@
     <row r="80" spans="1:65">
       <c r="A80" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B80" t="str">
         <f t="shared" si="3"/>
@@ -12683,7 +12692,7 @@
     <row r="81" spans="1:65">
       <c r="A81" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B81" t="str">
         <f t="shared" si="3"/>
@@ -12762,7 +12771,7 @@
     <row r="82" spans="1:65">
       <c r="A82" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B82" t="str">
         <f t="shared" si="3"/>
@@ -12841,7 +12850,7 @@
     <row r="83" spans="1:65">
       <c r="A83" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B83" t="str">
         <f t="shared" si="3"/>
@@ -12920,7 +12929,7 @@
     <row r="84" spans="1:65">
       <c r="A84" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B84" t="str">
         <f t="shared" si="3"/>
@@ -12999,7 +13008,7 @@
     <row r="85" spans="1:65">
       <c r="A85" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B85" t="str">
         <f t="shared" si="3"/>
@@ -13078,7 +13087,7 @@
     <row r="86" spans="1:65">
       <c r="A86" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B86" t="str">
         <f t="shared" si="3"/>
@@ -13157,7 +13166,7 @@
     <row r="87" spans="1:65">
       <c r="A87" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B87" t="str">
         <f t="shared" si="3"/>
@@ -13236,7 +13245,7 @@
     <row r="88" spans="1:65">
       <c r="A88" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B88" t="str">
         <f t="shared" si="3"/>
@@ -13315,7 +13324,7 @@
     <row r="89" spans="1:65">
       <c r="A89" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B89" t="str">
         <f t="shared" si="3"/>
@@ -13394,7 +13403,7 @@
     <row r="90" spans="1:65">
       <c r="A90" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B90" t="str">
         <f t="shared" si="3"/>
@@ -13473,7 +13482,7 @@
     <row r="91" spans="1:65">
       <c r="A91" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B91" t="str">
         <f t="shared" si="3"/>
@@ -13552,7 +13561,7 @@
     <row r="92" spans="1:65">
       <c r="A92" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B92" t="str">
         <f t="shared" si="3"/>
@@ -13631,7 +13640,7 @@
     <row r="93" spans="1:65">
       <c r="A93" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B93" t="str">
         <f t="shared" si="3"/>
@@ -13710,7 +13719,7 @@
     <row r="94" spans="1:65">
       <c r="A94" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B94" t="str">
         <f t="shared" si="3"/>
@@ -13789,7 +13798,7 @@
     <row r="95" spans="1:65">
       <c r="A95" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B95" t="str">
         <f t="shared" si="3"/>
@@ -13868,7 +13877,7 @@
     <row r="96" spans="1:65">
       <c r="A96" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B96" t="str">
         <f t="shared" si="3"/>
@@ -13947,7 +13956,7 @@
     <row r="97" spans="1:65">
       <c r="A97" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B97" t="str">
         <f t="shared" si="3"/>
@@ -14026,7 +14035,7 @@
     <row r="98" spans="1:65">
       <c r="A98" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B98" t="str">
         <f t="shared" si="3"/>
@@ -14105,7 +14114,7 @@
     <row r="99" spans="1:65">
       <c r="A99" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B99" t="str">
         <f t="shared" si="3"/>
@@ -14184,7 +14193,7 @@
     <row r="100" spans="1:65">
       <c r="A100" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B100" t="str">
         <f t="shared" si="3"/>
@@ -14265,7 +14274,7 @@
     <row r="101" spans="1:65">
       <c r="A101" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B101" t="str">
         <f t="shared" si="3"/>
@@ -14344,7 +14353,7 @@
     <row r="102" spans="1:65">
       <c r="A102" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B102" t="str">
         <f t="shared" si="3"/>
@@ -14423,7 +14432,7 @@
     <row r="103" spans="1:65">
       <c r="A103" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B103" t="str">
         <f t="shared" si="3"/>
@@ -14502,7 +14511,7 @@
     <row r="104" spans="1:65">
       <c r="A104" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B104" t="str">
         <f t="shared" si="3"/>
@@ -14581,7 +14590,7 @@
     <row r="105" spans="1:65">
       <c r="A105" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B105" t="str">
         <f t="shared" si="3"/>
@@ -14660,7 +14669,7 @@
     <row r="106" spans="1:65">
       <c r="A106" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B106" t="str">
         <f t="shared" si="3"/>
@@ -14741,7 +14750,7 @@
     <row r="107" spans="1:65">
       <c r="A107" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B107" t="str">
         <f t="shared" si="3"/>
@@ -14822,7 +14831,7 @@
     <row r="108" spans="1:65">
       <c r="A108" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B108" t="str">
         <f t="shared" si="3"/>
@@ -14901,7 +14910,7 @@
     <row r="109" spans="1:65">
       <c r="A109" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B109" t="str">
         <f t="shared" si="3"/>
@@ -14980,7 +14989,7 @@
     <row r="110" spans="1:65">
       <c r="A110" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B110" t="str">
         <f t="shared" si="3"/>
@@ -15059,7 +15068,7 @@
     <row r="111" spans="1:65">
       <c r="A111" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B111" t="str">
         <f t="shared" si="3"/>
@@ -15138,7 +15147,7 @@
     <row r="112" spans="1:65">
       <c r="A112" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B112" t="str">
         <f t="shared" si="3"/>
@@ -15219,7 +15228,7 @@
     <row r="113" spans="1:65">
       <c r="A113" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B113" t="str">
         <f t="shared" si="3"/>
@@ -15298,7 +15307,7 @@
     <row r="114" spans="1:65">
       <c r="A114" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B114" t="str">
         <f t="shared" si="3"/>
@@ -15377,7 +15386,7 @@
     <row r="115" spans="1:65">
       <c r="A115" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B115" t="str">
         <f t="shared" si="3"/>
@@ -15456,7 +15465,7 @@
     <row r="116" spans="1:65">
       <c r="A116" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B116" t="str">
         <f t="shared" si="3"/>
@@ -15535,7 +15544,7 @@
     <row r="117" spans="1:65">
       <c r="A117" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B117" t="str">
         <f t="shared" si="3"/>
@@ -15614,7 +15623,7 @@
     <row r="118" spans="1:65">
       <c r="A118" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B118" t="str">
         <f t="shared" si="3"/>
@@ -15693,7 +15702,7 @@
     <row r="119" spans="1:65">
       <c r="A119" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B119" t="str">
         <f t="shared" si="3"/>
@@ -15772,7 +15781,7 @@
     <row r="120" spans="1:65">
       <c r="A120" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B120" t="str">
         <f t="shared" si="3"/>
@@ -15851,7 +15860,7 @@
     <row r="121" spans="1:65">
       <c r="A121" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B121" t="str">
         <f t="shared" si="3"/>
@@ -15930,7 +15939,7 @@
     <row r="122" spans="1:65">
       <c r="A122" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B122" t="str">
         <f t="shared" si="3"/>
@@ -16009,7 +16018,7 @@
     <row r="123" spans="1:65">
       <c r="A123" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B123" t="str">
         <f t="shared" si="3"/>
@@ -16088,7 +16097,7 @@
     <row r="124" spans="1:65">
       <c r="A124" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B124" t="str">
         <f t="shared" si="3"/>
@@ -16169,7 +16178,7 @@
     <row r="125" spans="1:65">
       <c r="A125" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B125" t="str">
         <f t="shared" si="3"/>
@@ -16250,7 +16259,7 @@
     <row r="126" spans="1:65">
       <c r="A126" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B126" t="str">
         <f t="shared" si="3"/>
@@ -16329,7 +16338,7 @@
     <row r="127" spans="1:65">
       <c r="A127" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B127" t="str">
         <f t="shared" si="3"/>
@@ -16408,7 +16417,7 @@
     <row r="128" spans="1:65">
       <c r="A128" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B128" t="str">
         <f t="shared" si="3"/>
@@ -16487,7 +16496,7 @@
     <row r="129" spans="1:65">
       <c r="A129" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B129" t="str">
         <f t="shared" si="3"/>
@@ -16566,7 +16575,7 @@
     <row r="130" spans="1:65">
       <c r="A130" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B130" t="str">
         <f t="shared" si="3"/>
@@ -16645,7 +16654,7 @@
     <row r="131" spans="1:65">
       <c r="A131" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B131" t="str">
         <f t="shared" si="3"/>
@@ -16727,7 +16736,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B132" t="str">
         <f t="shared" ref="B132:B168" si="5">TEXT($C132, "HH:mm")</f>
@@ -16806,7 +16815,7 @@
     <row r="133" spans="1:65">
       <c r="A133" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B133" t="str">
         <f t="shared" si="5"/>
@@ -16885,7 +16894,7 @@
     <row r="134" spans="1:65">
       <c r="A134" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B134" t="str">
         <f t="shared" si="5"/>
@@ -16964,7 +16973,7 @@
     <row r="135" spans="1:65">
       <c r="A135" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B135" t="str">
         <f t="shared" si="5"/>
@@ -17043,7 +17052,7 @@
     <row r="136" spans="1:65">
       <c r="A136" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B136" t="str">
         <f t="shared" si="5"/>
@@ -17124,7 +17133,7 @@
     <row r="137" spans="1:65">
       <c r="A137" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B137" t="str">
         <f t="shared" si="5"/>
@@ -17205,7 +17214,7 @@
     <row r="138" spans="1:65">
       <c r="A138" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B138" t="str">
         <f t="shared" si="5"/>
@@ -17284,7 +17293,7 @@
     <row r="139" spans="1:65">
       <c r="A139" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B139" t="str">
         <f t="shared" si="5"/>
@@ -17363,7 +17372,7 @@
     <row r="140" spans="1:65">
       <c r="A140" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B140" t="str">
         <f t="shared" si="5"/>
@@ -17442,7 +17451,7 @@
     <row r="141" spans="1:65">
       <c r="A141" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B141" t="str">
         <f t="shared" si="5"/>
@@ -17521,7 +17530,7 @@
     <row r="142" spans="1:65">
       <c r="A142" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B142" t="str">
         <f t="shared" si="5"/>
@@ -17600,7 +17609,7 @@
     <row r="143" spans="1:65">
       <c r="A143" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B143" t="str">
         <f t="shared" si="5"/>
@@ -17679,7 +17688,7 @@
     <row r="144" spans="1:65">
       <c r="A144" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B144" t="str">
         <f t="shared" si="5"/>
@@ -17758,7 +17767,7 @@
     <row r="145" spans="1:65">
       <c r="A145" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B145" t="str">
         <f t="shared" si="5"/>
@@ -17837,7 +17846,7 @@
     <row r="146" spans="1:65">
       <c r="A146" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B146" t="str">
         <f t="shared" si="5"/>
@@ -17916,7 +17925,7 @@
     <row r="147" spans="1:65">
       <c r="A147" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B147" t="str">
         <f t="shared" si="5"/>
@@ -17995,7 +18004,7 @@
     <row r="148" spans="1:65">
       <c r="A148" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B148" t="str">
         <f t="shared" si="5"/>
@@ -18076,7 +18085,7 @@
     <row r="149" spans="1:65">
       <c r="A149" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B149" t="str">
         <f t="shared" si="5"/>
@@ -18155,7 +18164,7 @@
     <row r="150" spans="1:65">
       <c r="A150" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B150" t="str">
         <f t="shared" si="5"/>
@@ -18234,7 +18243,7 @@
     <row r="151" spans="1:65">
       <c r="A151" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B151" t="str">
         <f t="shared" si="5"/>
@@ -18313,7 +18322,7 @@
     <row r="152" spans="1:65">
       <c r="A152" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B152" t="str">
         <f t="shared" si="5"/>
@@ -18392,7 +18401,7 @@
     <row r="153" spans="1:65">
       <c r="A153" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B153" t="str">
         <f t="shared" si="5"/>
@@ -18471,7 +18480,7 @@
     <row r="154" spans="1:65">
       <c r="A154" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B154" t="str">
         <f t="shared" si="5"/>
@@ -18550,7 +18559,7 @@
     <row r="155" spans="1:65">
       <c r="A155" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B155" t="str">
         <f t="shared" si="5"/>
@@ -18629,7 +18638,7 @@
     <row r="156" spans="1:65">
       <c r="A156" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B156" t="str">
         <f t="shared" si="5"/>
@@ -18708,7 +18717,7 @@
     <row r="157" spans="1:65">
       <c r="A157" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B157" t="str">
         <f t="shared" si="5"/>
@@ -18787,7 +18796,7 @@
     <row r="158" spans="1:65">
       <c r="A158" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B158" t="str">
         <f t="shared" si="5"/>
@@ -18866,7 +18875,7 @@
     <row r="159" spans="1:65">
       <c r="A159" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B159" t="str">
         <f t="shared" si="5"/>
@@ -18945,7 +18954,7 @@
     <row r="160" spans="1:65">
       <c r="A160" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B160" t="str">
         <f t="shared" si="5"/>
@@ -19024,7 +19033,7 @@
     <row r="161" spans="1:65">
       <c r="A161" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B161" t="str">
         <f t="shared" si="5"/>
@@ -19103,7 +19112,7 @@
     <row r="162" spans="1:65">
       <c r="A162" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B162" t="str">
         <f t="shared" si="5"/>
@@ -19182,7 +19191,7 @@
     <row r="163" spans="1:65">
       <c r="A163" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B163" t="str">
         <f t="shared" si="5"/>
@@ -19261,7 +19270,7 @@
     <row r="164" spans="1:65">
       <c r="A164" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B164" t="str">
         <f t="shared" si="5"/>
@@ -19340,7 +19349,7 @@
     <row r="165" spans="1:65">
       <c r="A165" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B165" t="str">
         <f t="shared" si="5"/>
@@ -19419,7 +19428,7 @@
     <row r="166" spans="1:65">
       <c r="A166" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B166" t="str">
         <f t="shared" si="5"/>
@@ -19500,7 +19509,7 @@
     <row r="167" spans="1:65">
       <c r="A167" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B167" t="str">
         <f t="shared" si="5"/>
@@ -19579,7 +19588,7 @@
     <row r="168" spans="1:65">
       <c r="A168" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B168" t="str">
         <f t="shared" si="5"/>
@@ -19661,7 +19670,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B169" t="str">
         <f>TEXT($C169, "HH:mm")</f>
@@ -19743,7 +19752,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B170" t="str">
         <f t="shared" ref="B170:B233" si="7">TEXT($C170, "HH:mm")</f>
@@ -19822,7 +19831,7 @@
     <row r="171" spans="1:65">
       <c r="A171" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B171" t="str">
         <f t="shared" si="7"/>
@@ -19901,7 +19910,7 @@
     <row r="172" spans="1:65">
       <c r="A172" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B172" t="str">
         <f t="shared" si="7"/>
@@ -19982,7 +19991,7 @@
     <row r="173" spans="1:65">
       <c r="A173" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B173" t="str">
         <f t="shared" si="7"/>
@@ -20061,7 +20070,7 @@
     <row r="174" spans="1:65">
       <c r="A174" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B174" t="str">
         <f t="shared" si="7"/>
@@ -20140,7 +20149,7 @@
     <row r="175" spans="1:65">
       <c r="A175" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B175" t="str">
         <f t="shared" si="7"/>
@@ -20219,7 +20228,7 @@
     <row r="176" spans="1:65">
       <c r="A176" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B176" t="str">
         <f t="shared" si="7"/>
@@ -20298,7 +20307,7 @@
     <row r="177" spans="1:65">
       <c r="A177" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B177" t="str">
         <f t="shared" si="7"/>
@@ -20377,7 +20386,7 @@
     <row r="178" spans="1:65">
       <c r="A178" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B178" t="str">
         <f t="shared" si="7"/>
@@ -20458,7 +20467,7 @@
     <row r="179" spans="1:65">
       <c r="A179" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B179" t="str">
         <f t="shared" si="7"/>
@@ -20537,7 +20546,7 @@
     <row r="180" spans="1:65">
       <c r="A180" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B180" t="str">
         <f t="shared" si="7"/>
@@ -20616,7 +20625,7 @@
     <row r="181" spans="1:65">
       <c r="A181" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B181" t="str">
         <f t="shared" si="7"/>
@@ -20697,7 +20706,7 @@
     <row r="182" spans="1:65">
       <c r="A182" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B182" t="str">
         <f t="shared" si="7"/>
@@ -20778,7 +20787,7 @@
     <row r="183" spans="1:65">
       <c r="A183" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B183" t="str">
         <f t="shared" si="7"/>
@@ -20859,7 +20868,7 @@
     <row r="184" spans="1:65">
       <c r="A184" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B184" t="str">
         <f t="shared" si="7"/>
@@ -20942,7 +20951,7 @@
     <row r="185" spans="1:65">
       <c r="A185" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B185" t="str">
         <f t="shared" si="7"/>
@@ -21023,7 +21032,7 @@
     <row r="186" spans="1:65">
       <c r="A186" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B186" t="str">
         <f t="shared" si="7"/>
@@ -21104,7 +21113,7 @@
     <row r="187" spans="1:65">
       <c r="A187" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B187" t="str">
         <f t="shared" si="7"/>
@@ -21185,7 +21194,7 @@
     <row r="188" spans="1:65">
       <c r="A188" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B188" t="str">
         <f t="shared" si="7"/>
@@ -21266,7 +21275,7 @@
     <row r="189" spans="1:65">
       <c r="A189" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B189" t="str">
         <f t="shared" si="7"/>
@@ -21347,7 +21356,7 @@
     <row r="190" spans="1:65">
       <c r="A190" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B190" t="str">
         <f t="shared" si="7"/>
@@ -21430,7 +21439,7 @@
     <row r="191" spans="1:65">
       <c r="A191" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B191" t="str">
         <f t="shared" si="7"/>
@@ -21513,7 +21522,7 @@
     <row r="192" spans="1:65">
       <c r="A192" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B192" t="str">
         <f t="shared" si="7"/>
@@ -21596,7 +21605,7 @@
     <row r="193" spans="1:65">
       <c r="A193" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B193" t="str">
         <f t="shared" si="7"/>
@@ -21679,7 +21688,7 @@
     <row r="194" spans="1:65">
       <c r="A194" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B194" t="str">
         <f t="shared" si="7"/>
@@ -21760,7 +21769,7 @@
     <row r="195" spans="1:65">
       <c r="A195" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B195" t="str">
         <f t="shared" si="7"/>
@@ -21841,7 +21850,7 @@
     <row r="196" spans="1:65">
       <c r="A196" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B196" t="str">
         <f t="shared" si="7"/>
@@ -21924,7 +21933,7 @@
     <row r="197" spans="1:65">
       <c r="A197" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B197" t="str">
         <f t="shared" si="7"/>
@@ -22003,7 +22012,7 @@
     <row r="198" spans="1:65">
       <c r="A198" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B198" t="str">
         <f t="shared" si="7"/>
@@ -22082,7 +22091,7 @@
     <row r="199" spans="1:65">
       <c r="A199" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B199" t="str">
         <f t="shared" si="7"/>
@@ -22161,7 +22170,7 @@
     <row r="200" spans="1:65">
       <c r="A200" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B200" t="str">
         <f t="shared" si="7"/>
@@ -22240,7 +22249,7 @@
     <row r="201" spans="1:65">
       <c r="A201" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B201" t="str">
         <f t="shared" si="7"/>
@@ -22319,7 +22328,7 @@
     <row r="202" spans="1:65">
       <c r="A202" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B202" t="str">
         <f t="shared" si="7"/>
@@ -22400,7 +22409,7 @@
     <row r="203" spans="1:65">
       <c r="A203" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B203" t="str">
         <f t="shared" si="7"/>
@@ -22479,7 +22488,7 @@
     <row r="204" spans="1:65">
       <c r="A204" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B204" t="str">
         <f t="shared" si="7"/>
@@ -22558,7 +22567,7 @@
     <row r="205" spans="1:65">
       <c r="A205" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B205" t="str">
         <f t="shared" si="7"/>
@@ -22637,7 +22646,7 @@
     <row r="206" spans="1:65">
       <c r="A206" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B206" t="str">
         <f t="shared" si="7"/>
@@ -22716,7 +22725,7 @@
     <row r="207" spans="1:65">
       <c r="A207" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B207" t="str">
         <f t="shared" si="7"/>
@@ -22795,7 +22804,7 @@
     <row r="208" spans="1:65">
       <c r="A208" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B208" t="str">
         <f t="shared" si="7"/>
@@ -22876,7 +22885,7 @@
     <row r="209" spans="1:65">
       <c r="A209" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B209" t="str">
         <f t="shared" si="7"/>
@@ -22955,7 +22964,7 @@
     <row r="210" spans="1:65">
       <c r="A210" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B210" t="str">
         <f t="shared" si="7"/>
@@ -23034,7 +23043,7 @@
     <row r="211" spans="1:65">
       <c r="A211" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B211" t="str">
         <f t="shared" si="7"/>
@@ -23115,7 +23124,7 @@
     <row r="212" spans="1:65">
       <c r="A212" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B212" t="str">
         <f t="shared" si="7"/>
@@ -23194,7 +23203,7 @@
     <row r="213" spans="1:65">
       <c r="A213" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B213" t="str">
         <f t="shared" si="7"/>
@@ -23273,7 +23282,7 @@
     <row r="214" spans="1:65">
       <c r="A214" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B214" t="str">
         <f t="shared" si="7"/>
@@ -23352,7 +23361,7 @@
     <row r="215" spans="1:65">
       <c r="A215" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B215" t="str">
         <f t="shared" si="7"/>
@@ -23431,7 +23440,7 @@
     <row r="216" spans="1:65">
       <c r="A216" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B216" t="str">
         <f t="shared" si="7"/>
@@ -23510,7 +23519,7 @@
     <row r="217" spans="1:65">
       <c r="A217" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B217" t="str">
         <f t="shared" si="7"/>
@@ -23589,7 +23598,7 @@
     <row r="218" spans="1:65">
       <c r="A218" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B218" t="str">
         <f t="shared" si="7"/>
@@ -23668,7 +23677,7 @@
     <row r="219" spans="1:65">
       <c r="A219" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B219" t="str">
         <f t="shared" si="7"/>
@@ -23747,7 +23756,7 @@
     <row r="220" spans="1:65">
       <c r="A220" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B220" t="str">
         <f t="shared" si="7"/>
@@ -23828,7 +23837,7 @@
     <row r="221" spans="1:65">
       <c r="A221" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B221" t="str">
         <f t="shared" si="7"/>
@@ -23907,7 +23916,7 @@
     <row r="222" spans="1:65">
       <c r="A222" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B222" t="str">
         <f t="shared" si="7"/>
@@ -23986,7 +23995,7 @@
     <row r="223" spans="1:65">
       <c r="A223" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B223" t="str">
         <f t="shared" si="7"/>
@@ -24065,7 +24074,7 @@
     <row r="224" spans="1:65">
       <c r="A224" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B224" t="str">
         <f t="shared" si="7"/>
@@ -24144,7 +24153,7 @@
     <row r="225" spans="1:65">
       <c r="A225" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B225" t="str">
         <f t="shared" si="7"/>
@@ -24223,7 +24232,7 @@
     <row r="226" spans="1:65">
       <c r="A226" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B226" t="str">
         <f t="shared" si="7"/>
@@ -24302,7 +24311,7 @@
     <row r="227" spans="1:65">
       <c r="A227" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B227" t="str">
         <f t="shared" si="7"/>
@@ -24381,7 +24390,7 @@
     <row r="228" spans="1:65">
       <c r="A228" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B228" t="str">
         <f t="shared" si="7"/>
@@ -24460,7 +24469,7 @@
     <row r="229" spans="1:65">
       <c r="A229" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B229" t="str">
         <f t="shared" si="7"/>
@@ -24539,7 +24548,7 @@
     <row r="230" spans="1:65">
       <c r="A230" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B230" t="str">
         <f t="shared" si="7"/>
@@ -24618,7 +24627,7 @@
     <row r="231" spans="1:65">
       <c r="A231" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B231" t="str">
         <f t="shared" si="7"/>
@@ -24697,7 +24706,7 @@
     <row r="232" spans="1:65">
       <c r="A232" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B232" t="str">
         <f t="shared" si="7"/>
@@ -24776,7 +24785,7 @@
     <row r="233" spans="1:65">
       <c r="A233" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B233" t="str">
         <f t="shared" si="7"/>
@@ -24858,7 +24867,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B234" t="str">
         <f t="shared" ref="B234:B291" si="9">TEXT($C234, "HH:mm")</f>
@@ -24937,7 +24946,7 @@
     <row r="235" spans="1:65">
       <c r="A235" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B235" t="str">
         <f t="shared" si="9"/>
@@ -25016,7 +25025,7 @@
     <row r="236" spans="1:65">
       <c r="A236" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B236" t="str">
         <f t="shared" si="9"/>
@@ -25095,7 +25104,7 @@
     <row r="237" spans="1:65">
       <c r="A237" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B237" t="str">
         <f t="shared" si="9"/>
@@ -25174,7 +25183,7 @@
     <row r="238" spans="1:65">
       <c r="A238" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B238" t="str">
         <f t="shared" si="9"/>
@@ -25253,7 +25262,7 @@
     <row r="239" spans="1:65">
       <c r="A239" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B239" t="str">
         <f t="shared" si="9"/>
@@ -25332,7 +25341,7 @@
     <row r="240" spans="1:65">
       <c r="A240" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B240" t="str">
         <f t="shared" si="9"/>
@@ -25411,7 +25420,7 @@
     <row r="241" spans="1:65">
       <c r="A241" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B241" t="str">
         <f t="shared" si="9"/>
@@ -25490,7 +25499,7 @@
     <row r="242" spans="1:65">
       <c r="A242" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B242" t="str">
         <f t="shared" si="9"/>
@@ -25569,7 +25578,7 @@
     <row r="243" spans="1:65">
       <c r="A243" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B243" t="str">
         <f t="shared" si="9"/>
@@ -25648,7 +25657,7 @@
     <row r="244" spans="1:65">
       <c r="A244" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B244" t="str">
         <f t="shared" si="9"/>
@@ -25727,7 +25736,7 @@
     <row r="245" spans="1:65">
       <c r="A245" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B245" t="str">
         <f t="shared" si="9"/>
@@ -25806,7 +25815,7 @@
     <row r="246" spans="1:65">
       <c r="A246" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B246" t="str">
         <f t="shared" si="9"/>
@@ -25885,7 +25894,7 @@
     <row r="247" spans="1:65">
       <c r="A247" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B247" t="str">
         <f t="shared" si="9"/>
@@ -25964,7 +25973,7 @@
     <row r="248" spans="1:65">
       <c r="A248" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B248" t="str">
         <f t="shared" si="9"/>
@@ -26043,7 +26052,7 @@
     <row r="249" spans="1:65">
       <c r="A249" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B249" t="str">
         <f t="shared" si="9"/>
@@ -26122,7 +26131,7 @@
     <row r="250" spans="1:65">
       <c r="A250" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B250" t="str">
         <f t="shared" si="9"/>
@@ -26201,7 +26210,7 @@
     <row r="251" spans="1:65">
       <c r="A251" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B251" t="str">
         <f t="shared" si="9"/>
@@ -26280,7 +26289,7 @@
     <row r="252" spans="1:65">
       <c r="A252" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B252" t="str">
         <f t="shared" si="9"/>
@@ -26359,7 +26368,7 @@
     <row r="253" spans="1:65">
       <c r="A253" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B253" t="str">
         <f t="shared" si="9"/>
@@ -26438,7 +26447,7 @@
     <row r="254" spans="1:65">
       <c r="A254" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B254" t="str">
         <f t="shared" si="9"/>
@@ -26517,7 +26526,7 @@
     <row r="255" spans="1:65">
       <c r="A255" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B255" t="str">
         <f t="shared" si="9"/>
@@ -26596,7 +26605,7 @@
     <row r="256" spans="1:65">
       <c r="A256" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B256" t="str">
         <f t="shared" si="9"/>
@@ -26675,7 +26684,7 @@
     <row r="257" spans="1:65">
       <c r="A257" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B257" t="str">
         <f t="shared" si="9"/>
@@ -26754,7 +26763,7 @@
     <row r="258" spans="1:65">
       <c r="A258" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B258" t="str">
         <f t="shared" si="9"/>
@@ -26833,7 +26842,7 @@
     <row r="259" spans="1:65">
       <c r="A259" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B259" t="str">
         <f t="shared" si="9"/>
@@ -26912,7 +26921,7 @@
     <row r="260" spans="1:65">
       <c r="A260" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B260" t="str">
         <f t="shared" si="9"/>
@@ -26991,7 +27000,7 @@
     <row r="261" spans="1:65">
       <c r="A261" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B261" t="str">
         <f t="shared" si="9"/>
@@ -27070,7 +27079,7 @@
     <row r="262" spans="1:65">
       <c r="A262" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B262" t="str">
         <f t="shared" si="9"/>
@@ -27149,7 +27158,7 @@
     <row r="263" spans="1:65">
       <c r="A263" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B263" t="str">
         <f t="shared" si="9"/>
@@ -27228,7 +27237,7 @@
     <row r="264" spans="1:65">
       <c r="A264" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B264" t="str">
         <f t="shared" si="9"/>
@@ -27307,7 +27316,7 @@
     <row r="265" spans="1:65">
       <c r="A265" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B265" t="str">
         <f t="shared" si="9"/>
@@ -27386,7 +27395,7 @@
     <row r="266" spans="1:65">
       <c r="A266" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B266" t="str">
         <f t="shared" si="9"/>
@@ -27465,7 +27474,7 @@
     <row r="267" spans="1:65">
       <c r="A267" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B267" t="str">
         <f t="shared" si="9"/>
@@ -27544,7 +27553,7 @@
     <row r="268" spans="1:65">
       <c r="A268" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B268" t="str">
         <f t="shared" si="9"/>
@@ -27623,7 +27632,7 @@
     <row r="269" spans="1:65">
       <c r="A269" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B269" t="str">
         <f t="shared" si="9"/>
@@ -27702,7 +27711,7 @@
     <row r="270" spans="1:65">
       <c r="A270" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B270" t="str">
         <f t="shared" si="9"/>
@@ -27781,7 +27790,7 @@
     <row r="271" spans="1:65">
       <c r="A271" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B271" t="str">
         <f t="shared" si="9"/>
@@ -27860,7 +27869,7 @@
     <row r="272" spans="1:65">
       <c r="A272" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B272" t="str">
         <f t="shared" si="9"/>
@@ -27939,7 +27948,7 @@
     <row r="273" spans="1:65">
       <c r="A273" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B273" t="str">
         <f t="shared" si="9"/>
@@ -28018,7 +28027,7 @@
     <row r="274" spans="1:65">
       <c r="A274" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B274" t="str">
         <f t="shared" si="9"/>
@@ -28097,7 +28106,7 @@
     <row r="275" spans="1:65">
       <c r="A275" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B275" t="str">
         <f t="shared" si="9"/>
@@ -28176,7 +28185,7 @@
     <row r="276" spans="1:65">
       <c r="A276" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B276" t="str">
         <f t="shared" si="9"/>
@@ -28255,7 +28264,7 @@
     <row r="277" spans="1:65">
       <c r="A277" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B277" t="str">
         <f t="shared" si="9"/>
@@ -28334,7 +28343,7 @@
     <row r="278" spans="1:65">
       <c r="A278" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B278" t="str">
         <f t="shared" si="9"/>
@@ -28413,7 +28422,7 @@
     <row r="279" spans="1:65">
       <c r="A279" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B279" t="str">
         <f t="shared" si="9"/>
@@ -28492,7 +28501,7 @@
     <row r="280" spans="1:65">
       <c r="A280" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B280" t="str">
         <f t="shared" si="9"/>
@@ -28571,7 +28580,7 @@
     <row r="281" spans="1:65">
       <c r="A281" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B281" t="str">
         <f t="shared" si="9"/>
@@ -28650,7 +28659,7 @@
     <row r="282" spans="1:65">
       <c r="A282" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B282" t="str">
         <f t="shared" si="9"/>
@@ -28729,7 +28738,7 @@
     <row r="283" spans="1:65">
       <c r="A283" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B283" t="str">
         <f t="shared" si="9"/>
@@ -28808,7 +28817,7 @@
     <row r="284" spans="1:65">
       <c r="A284" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B284" t="str">
         <f t="shared" si="9"/>
@@ -28887,7 +28896,7 @@
     <row r="285" spans="1:65">
       <c r="A285" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B285" t="str">
         <f t="shared" si="9"/>
@@ -28966,7 +28975,7 @@
     <row r="286" spans="1:65">
       <c r="A286" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B286" t="str">
         <f t="shared" si="9"/>
@@ -29045,7 +29054,7 @@
     <row r="287" spans="1:65">
       <c r="A287" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B287" t="str">
         <f t="shared" si="9"/>
@@ -29124,7 +29133,7 @@
     <row r="288" spans="1:65">
       <c r="A288" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B288" t="str">
         <f t="shared" si="9"/>
@@ -29203,7 +29212,7 @@
     <row r="289" spans="1:65">
       <c r="A289" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B289" t="str">
         <f t="shared" si="9"/>
@@ -29282,7 +29291,7 @@
     <row r="290" spans="1:65">
       <c r="A290" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B290" t="str">
         <f t="shared" si="9"/>
@@ -29361,7 +29370,7 @@
     <row r="291" spans="1:65">
       <c r="A291" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>00:55</v>
+        <v>01:00</v>
       </c>
       <c r="B291" t="str">
         <f t="shared" si="9"/>

--- a/Vite-Vercel開発.xlsx
+++ b/Vite-Vercel開発.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2c67ec30e06f060f/work/GitHub/work-time-tracker/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{1928CA11-C4AD-40E9-B1C5-143667E830EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09F32D22-F5A6-44FD-81FA-90E5497223C3}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{1928CA11-C4AD-40E9-B1C5-143667E830EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4CCFE37C-B670-4A3E-B71B-AFEDFBD76204}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1536" uniqueCount="914">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1537" uniqueCount="915">
   <si>
     <t>npm install -g vercel</t>
     <phoneticPr fontId="1"/>
@@ -5334,6 +5334,10 @@
   </si>
   <si>
     <t>Found 101 errors in 26 files.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Found 89 errors in 20 files.</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -6106,7 +6110,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{083174DA-A42C-4F9C-978E-61AEAAD9DDFF}">
-  <dimension ref="B2:D18"/>
+  <dimension ref="B2:D19"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
@@ -6204,6 +6208,11 @@
     <row r="18" spans="3:3">
       <c r="C18" t="s">
         <v>913</v>
+      </c>
+    </row>
+    <row r="19" spans="3:3">
+      <c r="C19" t="s">
+        <v>914</v>
       </c>
     </row>
   </sheetData>
@@ -6370,7 +6379,7 @@
       MOD(NOW(),1),
       TIME(0,5,0)
     ),"HH:mm")</f>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B2" s="19"/>
       <c r="D2" s="1">
@@ -6381,7 +6390,7 @@
     <row r="3" spans="1:65">
       <c r="A3" s="19" t="str">
         <f ca="1">TEXT(NOW(),"HH:mm")</f>
-        <v>01:04</v>
+        <v>01:08</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="17" t="s">
@@ -6580,7 +6589,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B4" t="str">
         <f t="shared" ref="B4:B67" si="1">TEXT($C4, "HH:mm")</f>
@@ -6659,7 +6668,7 @@
     <row r="5" spans="1:65">
       <c r="A5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B5" t="str">
         <f t="shared" si="1"/>
@@ -6738,7 +6747,7 @@
     <row r="6" spans="1:65">
       <c r="A6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B6" t="str">
         <f t="shared" si="1"/>
@@ -6817,7 +6826,7 @@
     <row r="7" spans="1:65">
       <c r="A7" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B7" t="str">
         <f t="shared" si="1"/>
@@ -6896,7 +6905,7 @@
     <row r="8" spans="1:65">
       <c r="A8" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B8" t="str">
         <f t="shared" si="1"/>
@@ -6975,7 +6984,7 @@
     <row r="9" spans="1:65">
       <c r="A9" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B9" t="str">
         <f t="shared" si="1"/>
@@ -7054,7 +7063,7 @@
     <row r="10" spans="1:65">
       <c r="A10" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B10" t="str">
         <f t="shared" si="1"/>
@@ -7133,7 +7142,7 @@
     <row r="11" spans="1:65">
       <c r="A11" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B11" t="str">
         <f t="shared" si="1"/>
@@ -7212,7 +7221,7 @@
     <row r="12" spans="1:65">
       <c r="A12" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B12" t="str">
         <f t="shared" si="1"/>
@@ -7291,7 +7300,7 @@
     <row r="13" spans="1:65">
       <c r="A13" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B13" t="str">
         <f t="shared" si="1"/>
@@ -7370,7 +7379,7 @@
     <row r="14" spans="1:65">
       <c r="A14" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B14" t="str">
         <f t="shared" si="1"/>
@@ -7449,7 +7458,7 @@
     <row r="15" spans="1:65">
       <c r="A15" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B15" t="str">
         <f t="shared" si="1"/>
@@ -7528,7 +7537,7 @@
     <row r="16" spans="1:65">
       <c r="A16" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B16" t="str">
         <f t="shared" si="1"/>
@@ -7607,7 +7616,7 @@
     <row r="17" spans="1:65">
       <c r="A17" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B17" t="str">
         <f t="shared" si="1"/>
@@ -7686,7 +7695,7 @@
     <row r="18" spans="1:65">
       <c r="A18" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B18" t="str">
         <f t="shared" si="1"/>
@@ -7765,7 +7774,7 @@
     <row r="19" spans="1:65">
       <c r="A19" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B19" t="str">
         <f t="shared" si="1"/>
@@ -7844,7 +7853,7 @@
     <row r="20" spans="1:65">
       <c r="A20" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B20" t="str">
         <f t="shared" si="1"/>
@@ -7923,7 +7932,7 @@
     <row r="21" spans="1:65">
       <c r="A21" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B21" t="str">
         <f t="shared" si="1"/>
@@ -8002,7 +8011,7 @@
     <row r="22" spans="1:65">
       <c r="A22" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B22" t="str">
         <f t="shared" si="1"/>
@@ -8081,7 +8090,7 @@
     <row r="23" spans="1:65">
       <c r="A23" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B23" t="str">
         <f t="shared" si="1"/>
@@ -8160,7 +8169,7 @@
     <row r="24" spans="1:65">
       <c r="A24" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B24" t="str">
         <f t="shared" si="1"/>
@@ -8239,7 +8248,7 @@
     <row r="25" spans="1:65">
       <c r="A25" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B25" t="str">
         <f t="shared" si="1"/>
@@ -8318,7 +8327,7 @@
     <row r="26" spans="1:65">
       <c r="A26" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B26" t="str">
         <f t="shared" si="1"/>
@@ -8397,7 +8406,7 @@
     <row r="27" spans="1:65">
       <c r="A27" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B27" t="str">
         <f t="shared" si="1"/>
@@ -8476,7 +8485,7 @@
     <row r="28" spans="1:65">
       <c r="A28" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B28" t="str">
         <f t="shared" si="1"/>
@@ -8557,7 +8566,7 @@
     <row r="29" spans="1:65">
       <c r="A29" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B29" t="str">
         <f t="shared" si="1"/>
@@ -8638,7 +8647,7 @@
     <row r="30" spans="1:65">
       <c r="A30" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B30" t="str">
         <f t="shared" si="1"/>
@@ -8719,7 +8728,7 @@
     <row r="31" spans="1:65">
       <c r="A31" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B31" t="str">
         <f t="shared" si="1"/>
@@ -8798,7 +8807,7 @@
     <row r="32" spans="1:65">
       <c r="A32" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B32" t="str">
         <f t="shared" si="1"/>
@@ -8877,7 +8886,7 @@
     <row r="33" spans="1:65">
       <c r="A33" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B33" t="str">
         <f t="shared" si="1"/>
@@ -8956,7 +8965,7 @@
     <row r="34" spans="1:65">
       <c r="A34" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B34" t="str">
         <f t="shared" si="1"/>
@@ -9037,7 +9046,7 @@
     <row r="35" spans="1:65">
       <c r="A35" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B35" t="str">
         <f t="shared" si="1"/>
@@ -9118,7 +9127,7 @@
     <row r="36" spans="1:65">
       <c r="A36" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B36" t="str">
         <f t="shared" si="1"/>
@@ -9199,7 +9208,7 @@
     <row r="37" spans="1:65">
       <c r="A37" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B37" t="str">
         <f t="shared" si="1"/>
@@ -9278,7 +9287,7 @@
     <row r="38" spans="1:65">
       <c r="A38" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B38" t="str">
         <f t="shared" si="1"/>
@@ -9357,7 +9366,7 @@
     <row r="39" spans="1:65">
       <c r="A39" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B39" t="str">
         <f t="shared" si="1"/>
@@ -9436,7 +9445,7 @@
     <row r="40" spans="1:65">
       <c r="A40" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B40" t="str">
         <f t="shared" si="1"/>
@@ -9515,7 +9524,7 @@
     <row r="41" spans="1:65">
       <c r="A41" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B41" t="str">
         <f t="shared" si="1"/>
@@ -9594,7 +9603,7 @@
     <row r="42" spans="1:65">
       <c r="A42" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B42" t="str">
         <f t="shared" si="1"/>
@@ -9675,7 +9684,7 @@
     <row r="43" spans="1:65">
       <c r="A43" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B43" t="str">
         <f t="shared" si="1"/>
@@ -9756,7 +9765,7 @@
     <row r="44" spans="1:65">
       <c r="A44" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B44" t="str">
         <f t="shared" si="1"/>
@@ -9835,7 +9844,7 @@
     <row r="45" spans="1:65">
       <c r="A45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B45" t="str">
         <f t="shared" si="1"/>
@@ -9914,7 +9923,7 @@
     <row r="46" spans="1:65">
       <c r="A46" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B46" t="str">
         <f t="shared" si="1"/>
@@ -9993,7 +10002,7 @@
     <row r="47" spans="1:65">
       <c r="A47" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B47" t="str">
         <f t="shared" si="1"/>
@@ -10072,7 +10081,7 @@
     <row r="48" spans="1:65">
       <c r="A48" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B48" t="str">
         <f t="shared" si="1"/>
@@ -10151,7 +10160,7 @@
     <row r="49" spans="1:65">
       <c r="A49" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B49" t="str">
         <f t="shared" si="1"/>
@@ -10232,7 +10241,7 @@
     <row r="50" spans="1:65">
       <c r="A50" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B50" t="str">
         <f t="shared" si="1"/>
@@ -10313,7 +10322,7 @@
     <row r="51" spans="1:65">
       <c r="A51" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B51" t="str">
         <f t="shared" si="1"/>
@@ -10392,7 +10401,7 @@
     <row r="52" spans="1:65">
       <c r="A52" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B52" t="str">
         <f t="shared" si="1"/>
@@ -10471,7 +10480,7 @@
     <row r="53" spans="1:65">
       <c r="A53" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B53" t="str">
         <f t="shared" si="1"/>
@@ -10550,7 +10559,7 @@
     <row r="54" spans="1:65">
       <c r="A54" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B54" t="str">
         <f t="shared" si="1"/>
@@ -10629,7 +10638,7 @@
     <row r="55" spans="1:65">
       <c r="A55" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B55" t="str">
         <f t="shared" si="1"/>
@@ -10708,7 +10717,7 @@
     <row r="56" spans="1:65">
       <c r="A56" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B56" t="str">
         <f t="shared" si="1"/>
@@ -10789,7 +10798,7 @@
     <row r="57" spans="1:65">
       <c r="A57" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B57" t="str">
         <f t="shared" si="1"/>
@@ -10868,7 +10877,7 @@
     <row r="58" spans="1:65">
       <c r="A58" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B58" t="str">
         <f t="shared" si="1"/>
@@ -10949,7 +10958,7 @@
     <row r="59" spans="1:65">
       <c r="A59" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B59" t="str">
         <f t="shared" si="1"/>
@@ -11028,7 +11037,7 @@
     <row r="60" spans="1:65">
       <c r="A60" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B60" t="str">
         <f t="shared" si="1"/>
@@ -11107,7 +11116,7 @@
     <row r="61" spans="1:65">
       <c r="A61" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B61" t="str">
         <f t="shared" si="1"/>
@@ -11186,7 +11195,7 @@
     <row r="62" spans="1:65">
       <c r="A62" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B62" t="str">
         <f t="shared" si="1"/>
@@ -11265,7 +11274,7 @@
     <row r="63" spans="1:65">
       <c r="A63" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B63" t="str">
         <f t="shared" si="1"/>
@@ -11344,7 +11353,7 @@
     <row r="64" spans="1:65">
       <c r="A64" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B64" t="str">
         <f t="shared" si="1"/>
@@ -11425,7 +11434,7 @@
     <row r="65" spans="1:65">
       <c r="A65" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B65" t="str">
         <f t="shared" si="1"/>
@@ -11504,7 +11513,7 @@
     <row r="66" spans="1:65">
       <c r="A66" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B66" t="str">
         <f t="shared" si="1"/>
@@ -11583,7 +11592,7 @@
     <row r="67" spans="1:65">
       <c r="A67" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B67" t="str">
         <f t="shared" si="1"/>
@@ -11665,7 +11674,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B68" t="str">
         <f t="shared" ref="B68:B131" si="3">TEXT($C68, "HH:mm")</f>
@@ -11744,7 +11753,7 @@
     <row r="69" spans="1:65">
       <c r="A69" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B69" t="str">
         <f t="shared" si="3"/>
@@ -11823,7 +11832,7 @@
     <row r="70" spans="1:65">
       <c r="A70" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B70" t="str">
         <f t="shared" si="3"/>
@@ -11902,7 +11911,7 @@
     <row r="71" spans="1:65">
       <c r="A71" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B71" t="str">
         <f t="shared" si="3"/>
@@ -11981,7 +11990,7 @@
     <row r="72" spans="1:65">
       <c r="A72" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B72" t="str">
         <f t="shared" si="3"/>
@@ -12060,7 +12069,7 @@
     <row r="73" spans="1:65">
       <c r="A73" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B73" t="str">
         <f t="shared" si="3"/>
@@ -12139,7 +12148,7 @@
     <row r="74" spans="1:65">
       <c r="A74" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B74" t="str">
         <f t="shared" si="3"/>
@@ -12218,7 +12227,7 @@
     <row r="75" spans="1:65">
       <c r="A75" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B75" t="str">
         <f t="shared" si="3"/>
@@ -12297,7 +12306,7 @@
     <row r="76" spans="1:65">
       <c r="A76" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B76" t="str">
         <f t="shared" si="3"/>
@@ -12376,7 +12385,7 @@
     <row r="77" spans="1:65">
       <c r="A77" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B77" t="str">
         <f t="shared" si="3"/>
@@ -12455,7 +12464,7 @@
     <row r="78" spans="1:65">
       <c r="A78" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B78" t="str">
         <f t="shared" si="3"/>
@@ -12534,7 +12543,7 @@
     <row r="79" spans="1:65">
       <c r="A79" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B79" t="str">
         <f t="shared" si="3"/>
@@ -12613,7 +12622,7 @@
     <row r="80" spans="1:65">
       <c r="A80" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B80" t="str">
         <f t="shared" si="3"/>
@@ -12692,7 +12701,7 @@
     <row r="81" spans="1:65">
       <c r="A81" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B81" t="str">
         <f t="shared" si="3"/>
@@ -12771,7 +12780,7 @@
     <row r="82" spans="1:65">
       <c r="A82" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B82" t="str">
         <f t="shared" si="3"/>
@@ -12850,7 +12859,7 @@
     <row r="83" spans="1:65">
       <c r="A83" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B83" t="str">
         <f t="shared" si="3"/>
@@ -12929,7 +12938,7 @@
     <row r="84" spans="1:65">
       <c r="A84" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B84" t="str">
         <f t="shared" si="3"/>
@@ -13008,7 +13017,7 @@
     <row r="85" spans="1:65">
       <c r="A85" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B85" t="str">
         <f t="shared" si="3"/>
@@ -13087,7 +13096,7 @@
     <row r="86" spans="1:65">
       <c r="A86" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B86" t="str">
         <f t="shared" si="3"/>
@@ -13166,7 +13175,7 @@
     <row r="87" spans="1:65">
       <c r="A87" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B87" t="str">
         <f t="shared" si="3"/>
@@ -13245,7 +13254,7 @@
     <row r="88" spans="1:65">
       <c r="A88" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B88" t="str">
         <f t="shared" si="3"/>
@@ -13324,7 +13333,7 @@
     <row r="89" spans="1:65">
       <c r="A89" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B89" t="str">
         <f t="shared" si="3"/>
@@ -13403,7 +13412,7 @@
     <row r="90" spans="1:65">
       <c r="A90" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B90" t="str">
         <f t="shared" si="3"/>
@@ -13482,7 +13491,7 @@
     <row r="91" spans="1:65">
       <c r="A91" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B91" t="str">
         <f t="shared" si="3"/>
@@ -13561,7 +13570,7 @@
     <row r="92" spans="1:65">
       <c r="A92" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B92" t="str">
         <f t="shared" si="3"/>
@@ -13640,7 +13649,7 @@
     <row r="93" spans="1:65">
       <c r="A93" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B93" t="str">
         <f t="shared" si="3"/>
@@ -13719,7 +13728,7 @@
     <row r="94" spans="1:65">
       <c r="A94" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B94" t="str">
         <f t="shared" si="3"/>
@@ -13798,7 +13807,7 @@
     <row r="95" spans="1:65">
       <c r="A95" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B95" t="str">
         <f t="shared" si="3"/>
@@ -13877,7 +13886,7 @@
     <row r="96" spans="1:65">
       <c r="A96" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B96" t="str">
         <f t="shared" si="3"/>
@@ -13956,7 +13965,7 @@
     <row r="97" spans="1:65">
       <c r="A97" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B97" t="str">
         <f t="shared" si="3"/>
@@ -14035,7 +14044,7 @@
     <row r="98" spans="1:65">
       <c r="A98" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B98" t="str">
         <f t="shared" si="3"/>
@@ -14114,7 +14123,7 @@
     <row r="99" spans="1:65">
       <c r="A99" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B99" t="str">
         <f t="shared" si="3"/>
@@ -14193,7 +14202,7 @@
     <row r="100" spans="1:65">
       <c r="A100" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B100" t="str">
         <f t="shared" si="3"/>
@@ -14274,7 +14283,7 @@
     <row r="101" spans="1:65">
       <c r="A101" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B101" t="str">
         <f t="shared" si="3"/>
@@ -14353,7 +14362,7 @@
     <row r="102" spans="1:65">
       <c r="A102" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B102" t="str">
         <f t="shared" si="3"/>
@@ -14432,7 +14441,7 @@
     <row r="103" spans="1:65">
       <c r="A103" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B103" t="str">
         <f t="shared" si="3"/>
@@ -14511,7 +14520,7 @@
     <row r="104" spans="1:65">
       <c r="A104" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B104" t="str">
         <f t="shared" si="3"/>
@@ -14590,7 +14599,7 @@
     <row r="105" spans="1:65">
       <c r="A105" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B105" t="str">
         <f t="shared" si="3"/>
@@ -14669,7 +14678,7 @@
     <row r="106" spans="1:65">
       <c r="A106" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B106" t="str">
         <f t="shared" si="3"/>
@@ -14750,7 +14759,7 @@
     <row r="107" spans="1:65">
       <c r="A107" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B107" t="str">
         <f t="shared" si="3"/>
@@ -14831,7 +14840,7 @@
     <row r="108" spans="1:65">
       <c r="A108" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B108" t="str">
         <f t="shared" si="3"/>
@@ -14910,7 +14919,7 @@
     <row r="109" spans="1:65">
       <c r="A109" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B109" t="str">
         <f t="shared" si="3"/>
@@ -14989,7 +14998,7 @@
     <row r="110" spans="1:65">
       <c r="A110" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B110" t="str">
         <f t="shared" si="3"/>
@@ -15068,7 +15077,7 @@
     <row r="111" spans="1:65">
       <c r="A111" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B111" t="str">
         <f t="shared" si="3"/>
@@ -15147,7 +15156,7 @@
     <row r="112" spans="1:65">
       <c r="A112" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B112" t="str">
         <f t="shared" si="3"/>
@@ -15228,7 +15237,7 @@
     <row r="113" spans="1:65">
       <c r="A113" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B113" t="str">
         <f t="shared" si="3"/>
@@ -15307,7 +15316,7 @@
     <row r="114" spans="1:65">
       <c r="A114" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B114" t="str">
         <f t="shared" si="3"/>
@@ -15386,7 +15395,7 @@
     <row r="115" spans="1:65">
       <c r="A115" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B115" t="str">
         <f t="shared" si="3"/>
@@ -15465,7 +15474,7 @@
     <row r="116" spans="1:65">
       <c r="A116" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B116" t="str">
         <f t="shared" si="3"/>
@@ -15544,7 +15553,7 @@
     <row r="117" spans="1:65">
       <c r="A117" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B117" t="str">
         <f t="shared" si="3"/>
@@ -15623,7 +15632,7 @@
     <row r="118" spans="1:65">
       <c r="A118" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B118" t="str">
         <f t="shared" si="3"/>
@@ -15702,7 +15711,7 @@
     <row r="119" spans="1:65">
       <c r="A119" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B119" t="str">
         <f t="shared" si="3"/>
@@ -15781,7 +15790,7 @@
     <row r="120" spans="1:65">
       <c r="A120" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B120" t="str">
         <f t="shared" si="3"/>
@@ -15860,7 +15869,7 @@
     <row r="121" spans="1:65">
       <c r="A121" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B121" t="str">
         <f t="shared" si="3"/>
@@ -15939,7 +15948,7 @@
     <row r="122" spans="1:65">
       <c r="A122" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B122" t="str">
         <f t="shared" si="3"/>
@@ -16018,7 +16027,7 @@
     <row r="123" spans="1:65">
       <c r="A123" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B123" t="str">
         <f t="shared" si="3"/>
@@ -16097,7 +16106,7 @@
     <row r="124" spans="1:65">
       <c r="A124" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B124" t="str">
         <f t="shared" si="3"/>
@@ -16178,7 +16187,7 @@
     <row r="125" spans="1:65">
       <c r="A125" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B125" t="str">
         <f t="shared" si="3"/>
@@ -16259,7 +16268,7 @@
     <row r="126" spans="1:65">
       <c r="A126" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B126" t="str">
         <f t="shared" si="3"/>
@@ -16338,7 +16347,7 @@
     <row r="127" spans="1:65">
       <c r="A127" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B127" t="str">
         <f t="shared" si="3"/>
@@ -16417,7 +16426,7 @@
     <row r="128" spans="1:65">
       <c r="A128" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B128" t="str">
         <f t="shared" si="3"/>
@@ -16496,7 +16505,7 @@
     <row r="129" spans="1:65">
       <c r="A129" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B129" t="str">
         <f t="shared" si="3"/>
@@ -16575,7 +16584,7 @@
     <row r="130" spans="1:65">
       <c r="A130" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B130" t="str">
         <f t="shared" si="3"/>
@@ -16654,7 +16663,7 @@
     <row r="131" spans="1:65">
       <c r="A131" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B131" t="str">
         <f t="shared" si="3"/>
@@ -16736,7 +16745,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B132" t="str">
         <f t="shared" ref="B132:B168" si="5">TEXT($C132, "HH:mm")</f>
@@ -16815,7 +16824,7 @@
     <row r="133" spans="1:65">
       <c r="A133" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B133" t="str">
         <f t="shared" si="5"/>
@@ -16894,7 +16903,7 @@
     <row r="134" spans="1:65">
       <c r="A134" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B134" t="str">
         <f t="shared" si="5"/>
@@ -16973,7 +16982,7 @@
     <row r="135" spans="1:65">
       <c r="A135" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B135" t="str">
         <f t="shared" si="5"/>
@@ -17052,7 +17061,7 @@
     <row r="136" spans="1:65">
       <c r="A136" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B136" t="str">
         <f t="shared" si="5"/>
@@ -17133,7 +17142,7 @@
     <row r="137" spans="1:65">
       <c r="A137" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B137" t="str">
         <f t="shared" si="5"/>
@@ -17214,7 +17223,7 @@
     <row r="138" spans="1:65">
       <c r="A138" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B138" t="str">
         <f t="shared" si="5"/>
@@ -17293,7 +17302,7 @@
     <row r="139" spans="1:65">
       <c r="A139" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B139" t="str">
         <f t="shared" si="5"/>
@@ -17372,7 +17381,7 @@
     <row r="140" spans="1:65">
       <c r="A140" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B140" t="str">
         <f t="shared" si="5"/>
@@ -17451,7 +17460,7 @@
     <row r="141" spans="1:65">
       <c r="A141" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B141" t="str">
         <f t="shared" si="5"/>
@@ -17530,7 +17539,7 @@
     <row r="142" spans="1:65">
       <c r="A142" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B142" t="str">
         <f t="shared" si="5"/>
@@ -17609,7 +17618,7 @@
     <row r="143" spans="1:65">
       <c r="A143" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B143" t="str">
         <f t="shared" si="5"/>
@@ -17688,7 +17697,7 @@
     <row r="144" spans="1:65">
       <c r="A144" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B144" t="str">
         <f t="shared" si="5"/>
@@ -17767,7 +17776,7 @@
     <row r="145" spans="1:65">
       <c r="A145" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B145" t="str">
         <f t="shared" si="5"/>
@@ -17846,7 +17855,7 @@
     <row r="146" spans="1:65">
       <c r="A146" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B146" t="str">
         <f t="shared" si="5"/>
@@ -17925,7 +17934,7 @@
     <row r="147" spans="1:65">
       <c r="A147" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B147" t="str">
         <f t="shared" si="5"/>
@@ -18004,7 +18013,7 @@
     <row r="148" spans="1:65">
       <c r="A148" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B148" t="str">
         <f t="shared" si="5"/>
@@ -18085,7 +18094,7 @@
     <row r="149" spans="1:65">
       <c r="A149" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B149" t="str">
         <f t="shared" si="5"/>
@@ -18164,7 +18173,7 @@
     <row r="150" spans="1:65">
       <c r="A150" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B150" t="str">
         <f t="shared" si="5"/>
@@ -18243,7 +18252,7 @@
     <row r="151" spans="1:65">
       <c r="A151" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B151" t="str">
         <f t="shared" si="5"/>
@@ -18322,7 +18331,7 @@
     <row r="152" spans="1:65">
       <c r="A152" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B152" t="str">
         <f t="shared" si="5"/>
@@ -18401,7 +18410,7 @@
     <row r="153" spans="1:65">
       <c r="A153" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B153" t="str">
         <f t="shared" si="5"/>
@@ -18480,7 +18489,7 @@
     <row r="154" spans="1:65">
       <c r="A154" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B154" t="str">
         <f t="shared" si="5"/>
@@ -18559,7 +18568,7 @@
     <row r="155" spans="1:65">
       <c r="A155" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B155" t="str">
         <f t="shared" si="5"/>
@@ -18638,7 +18647,7 @@
     <row r="156" spans="1:65">
       <c r="A156" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B156" t="str">
         <f t="shared" si="5"/>
@@ -18717,7 +18726,7 @@
     <row r="157" spans="1:65">
       <c r="A157" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B157" t="str">
         <f t="shared" si="5"/>
@@ -18796,7 +18805,7 @@
     <row r="158" spans="1:65">
       <c r="A158" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B158" t="str">
         <f t="shared" si="5"/>
@@ -18875,7 +18884,7 @@
     <row r="159" spans="1:65">
       <c r="A159" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B159" t="str">
         <f t="shared" si="5"/>
@@ -18954,7 +18963,7 @@
     <row r="160" spans="1:65">
       <c r="A160" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B160" t="str">
         <f t="shared" si="5"/>
@@ -19033,7 +19042,7 @@
     <row r="161" spans="1:65">
       <c r="A161" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B161" t="str">
         <f t="shared" si="5"/>
@@ -19112,7 +19121,7 @@
     <row r="162" spans="1:65">
       <c r="A162" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B162" t="str">
         <f t="shared" si="5"/>
@@ -19191,7 +19200,7 @@
     <row r="163" spans="1:65">
       <c r="A163" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B163" t="str">
         <f t="shared" si="5"/>
@@ -19270,7 +19279,7 @@
     <row r="164" spans="1:65">
       <c r="A164" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B164" t="str">
         <f t="shared" si="5"/>
@@ -19349,7 +19358,7 @@
     <row r="165" spans="1:65">
       <c r="A165" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B165" t="str">
         <f t="shared" si="5"/>
@@ -19428,7 +19437,7 @@
     <row r="166" spans="1:65">
       <c r="A166" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B166" t="str">
         <f t="shared" si="5"/>
@@ -19509,7 +19518,7 @@
     <row r="167" spans="1:65">
       <c r="A167" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B167" t="str">
         <f t="shared" si="5"/>
@@ -19588,7 +19597,7 @@
     <row r="168" spans="1:65">
       <c r="A168" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B168" t="str">
         <f t="shared" si="5"/>
@@ -19670,7 +19679,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B169" t="str">
         <f>TEXT($C169, "HH:mm")</f>
@@ -19752,7 +19761,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B170" t="str">
         <f t="shared" ref="B170:B233" si="7">TEXT($C170, "HH:mm")</f>
@@ -19831,7 +19840,7 @@
     <row r="171" spans="1:65">
       <c r="A171" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B171" t="str">
         <f t="shared" si="7"/>
@@ -19910,7 +19919,7 @@
     <row r="172" spans="1:65">
       <c r="A172" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B172" t="str">
         <f t="shared" si="7"/>
@@ -19991,7 +20000,7 @@
     <row r="173" spans="1:65">
       <c r="A173" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B173" t="str">
         <f t="shared" si="7"/>
@@ -20070,7 +20079,7 @@
     <row r="174" spans="1:65">
       <c r="A174" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B174" t="str">
         <f t="shared" si="7"/>
@@ -20149,7 +20158,7 @@
     <row r="175" spans="1:65">
       <c r="A175" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B175" t="str">
         <f t="shared" si="7"/>
@@ -20228,7 +20237,7 @@
     <row r="176" spans="1:65">
       <c r="A176" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B176" t="str">
         <f t="shared" si="7"/>
@@ -20307,7 +20316,7 @@
     <row r="177" spans="1:65">
       <c r="A177" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B177" t="str">
         <f t="shared" si="7"/>
@@ -20386,7 +20395,7 @@
     <row r="178" spans="1:65">
       <c r="A178" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B178" t="str">
         <f t="shared" si="7"/>
@@ -20467,7 +20476,7 @@
     <row r="179" spans="1:65">
       <c r="A179" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B179" t="str">
         <f t="shared" si="7"/>
@@ -20546,7 +20555,7 @@
     <row r="180" spans="1:65">
       <c r="A180" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B180" t="str">
         <f t="shared" si="7"/>
@@ -20625,7 +20634,7 @@
     <row r="181" spans="1:65">
       <c r="A181" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B181" t="str">
         <f t="shared" si="7"/>
@@ -20706,7 +20715,7 @@
     <row r="182" spans="1:65">
       <c r="A182" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B182" t="str">
         <f t="shared" si="7"/>
@@ -20787,7 +20796,7 @@
     <row r="183" spans="1:65">
       <c r="A183" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B183" t="str">
         <f t="shared" si="7"/>
@@ -20868,7 +20877,7 @@
     <row r="184" spans="1:65">
       <c r="A184" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B184" t="str">
         <f t="shared" si="7"/>
@@ -20951,7 +20960,7 @@
     <row r="185" spans="1:65">
       <c r="A185" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B185" t="str">
         <f t="shared" si="7"/>
@@ -21032,7 +21041,7 @@
     <row r="186" spans="1:65">
       <c r="A186" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B186" t="str">
         <f t="shared" si="7"/>
@@ -21113,7 +21122,7 @@
     <row r="187" spans="1:65">
       <c r="A187" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B187" t="str">
         <f t="shared" si="7"/>
@@ -21194,7 +21203,7 @@
     <row r="188" spans="1:65">
       <c r="A188" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B188" t="str">
         <f t="shared" si="7"/>
@@ -21275,7 +21284,7 @@
     <row r="189" spans="1:65">
       <c r="A189" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B189" t="str">
         <f t="shared" si="7"/>
@@ -21356,7 +21365,7 @@
     <row r="190" spans="1:65">
       <c r="A190" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B190" t="str">
         <f t="shared" si="7"/>
@@ -21439,7 +21448,7 @@
     <row r="191" spans="1:65">
       <c r="A191" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B191" t="str">
         <f t="shared" si="7"/>
@@ -21522,7 +21531,7 @@
     <row r="192" spans="1:65">
       <c r="A192" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B192" t="str">
         <f t="shared" si="7"/>
@@ -21605,7 +21614,7 @@
     <row r="193" spans="1:65">
       <c r="A193" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B193" t="str">
         <f t="shared" si="7"/>
@@ -21688,7 +21697,7 @@
     <row r="194" spans="1:65">
       <c r="A194" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B194" t="str">
         <f t="shared" si="7"/>
@@ -21769,7 +21778,7 @@
     <row r="195" spans="1:65">
       <c r="A195" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B195" t="str">
         <f t="shared" si="7"/>
@@ -21850,7 +21859,7 @@
     <row r="196" spans="1:65">
       <c r="A196" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B196" t="str">
         <f t="shared" si="7"/>
@@ -21933,7 +21942,7 @@
     <row r="197" spans="1:65">
       <c r="A197" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B197" t="str">
         <f t="shared" si="7"/>
@@ -22012,7 +22021,7 @@
     <row r="198" spans="1:65">
       <c r="A198" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B198" t="str">
         <f t="shared" si="7"/>
@@ -22091,7 +22100,7 @@
     <row r="199" spans="1:65">
       <c r="A199" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B199" t="str">
         <f t="shared" si="7"/>
@@ -22170,7 +22179,7 @@
     <row r="200" spans="1:65">
       <c r="A200" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B200" t="str">
         <f t="shared" si="7"/>
@@ -22249,7 +22258,7 @@
     <row r="201" spans="1:65">
       <c r="A201" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B201" t="str">
         <f t="shared" si="7"/>
@@ -22328,7 +22337,7 @@
     <row r="202" spans="1:65">
       <c r="A202" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B202" t="str">
         <f t="shared" si="7"/>
@@ -22409,7 +22418,7 @@
     <row r="203" spans="1:65">
       <c r="A203" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B203" t="str">
         <f t="shared" si="7"/>
@@ -22488,7 +22497,7 @@
     <row r="204" spans="1:65">
       <c r="A204" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B204" t="str">
         <f t="shared" si="7"/>
@@ -22567,7 +22576,7 @@
     <row r="205" spans="1:65">
       <c r="A205" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B205" t="str">
         <f t="shared" si="7"/>
@@ -22646,7 +22655,7 @@
     <row r="206" spans="1:65">
       <c r="A206" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B206" t="str">
         <f t="shared" si="7"/>
@@ -22725,7 +22734,7 @@
     <row r="207" spans="1:65">
       <c r="A207" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B207" t="str">
         <f t="shared" si="7"/>
@@ -22804,7 +22813,7 @@
     <row r="208" spans="1:65">
       <c r="A208" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B208" t="str">
         <f t="shared" si="7"/>
@@ -22885,7 +22894,7 @@
     <row r="209" spans="1:65">
       <c r="A209" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B209" t="str">
         <f t="shared" si="7"/>
@@ -22964,7 +22973,7 @@
     <row r="210" spans="1:65">
       <c r="A210" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B210" t="str">
         <f t="shared" si="7"/>
@@ -23043,7 +23052,7 @@
     <row r="211" spans="1:65">
       <c r="A211" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B211" t="str">
         <f t="shared" si="7"/>
@@ -23124,7 +23133,7 @@
     <row r="212" spans="1:65">
       <c r="A212" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B212" t="str">
         <f t="shared" si="7"/>
@@ -23203,7 +23212,7 @@
     <row r="213" spans="1:65">
       <c r="A213" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B213" t="str">
         <f t="shared" si="7"/>
@@ -23282,7 +23291,7 @@
     <row r="214" spans="1:65">
       <c r="A214" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B214" t="str">
         <f t="shared" si="7"/>
@@ -23361,7 +23370,7 @@
     <row r="215" spans="1:65">
       <c r="A215" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B215" t="str">
         <f t="shared" si="7"/>
@@ -23440,7 +23449,7 @@
     <row r="216" spans="1:65">
       <c r="A216" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B216" t="str">
         <f t="shared" si="7"/>
@@ -23519,7 +23528,7 @@
     <row r="217" spans="1:65">
       <c r="A217" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B217" t="str">
         <f t="shared" si="7"/>
@@ -23598,7 +23607,7 @@
     <row r="218" spans="1:65">
       <c r="A218" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B218" t="str">
         <f t="shared" si="7"/>
@@ -23677,7 +23686,7 @@
     <row r="219" spans="1:65">
       <c r="A219" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B219" t="str">
         <f t="shared" si="7"/>
@@ -23756,7 +23765,7 @@
     <row r="220" spans="1:65">
       <c r="A220" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B220" t="str">
         <f t="shared" si="7"/>
@@ -23837,7 +23846,7 @@
     <row r="221" spans="1:65">
       <c r="A221" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B221" t="str">
         <f t="shared" si="7"/>
@@ -23916,7 +23925,7 @@
     <row r="222" spans="1:65">
       <c r="A222" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B222" t="str">
         <f t="shared" si="7"/>
@@ -23995,7 +24004,7 @@
     <row r="223" spans="1:65">
       <c r="A223" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B223" t="str">
         <f t="shared" si="7"/>
@@ -24074,7 +24083,7 @@
     <row r="224" spans="1:65">
       <c r="A224" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B224" t="str">
         <f t="shared" si="7"/>
@@ -24153,7 +24162,7 @@
     <row r="225" spans="1:65">
       <c r="A225" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B225" t="str">
         <f t="shared" si="7"/>
@@ -24232,7 +24241,7 @@
     <row r="226" spans="1:65">
       <c r="A226" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B226" t="str">
         <f t="shared" si="7"/>
@@ -24311,7 +24320,7 @@
     <row r="227" spans="1:65">
       <c r="A227" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B227" t="str">
         <f t="shared" si="7"/>
@@ -24390,7 +24399,7 @@
     <row r="228" spans="1:65">
       <c r="A228" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B228" t="str">
         <f t="shared" si="7"/>
@@ -24469,7 +24478,7 @@
     <row r="229" spans="1:65">
       <c r="A229" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B229" t="str">
         <f t="shared" si="7"/>
@@ -24548,7 +24557,7 @@
     <row r="230" spans="1:65">
       <c r="A230" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B230" t="str">
         <f t="shared" si="7"/>
@@ -24627,7 +24636,7 @@
     <row r="231" spans="1:65">
       <c r="A231" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B231" t="str">
         <f t="shared" si="7"/>
@@ -24706,7 +24715,7 @@
     <row r="232" spans="1:65">
       <c r="A232" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B232" t="str">
         <f t="shared" si="7"/>
@@ -24785,7 +24794,7 @@
     <row r="233" spans="1:65">
       <c r="A233" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B233" t="str">
         <f t="shared" si="7"/>
@@ -24867,7 +24876,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B234" t="str">
         <f t="shared" ref="B234:B291" si="9">TEXT($C234, "HH:mm")</f>
@@ -24946,7 +24955,7 @@
     <row r="235" spans="1:65">
       <c r="A235" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B235" t="str">
         <f t="shared" si="9"/>
@@ -25025,7 +25034,7 @@
     <row r="236" spans="1:65">
       <c r="A236" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B236" t="str">
         <f t="shared" si="9"/>
@@ -25104,7 +25113,7 @@
     <row r="237" spans="1:65">
       <c r="A237" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B237" t="str">
         <f t="shared" si="9"/>
@@ -25183,7 +25192,7 @@
     <row r="238" spans="1:65">
       <c r="A238" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B238" t="str">
         <f t="shared" si="9"/>
@@ -25262,7 +25271,7 @@
     <row r="239" spans="1:65">
       <c r="A239" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B239" t="str">
         <f t="shared" si="9"/>
@@ -25341,7 +25350,7 @@
     <row r="240" spans="1:65">
       <c r="A240" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B240" t="str">
         <f t="shared" si="9"/>
@@ -25420,7 +25429,7 @@
     <row r="241" spans="1:65">
       <c r="A241" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B241" t="str">
         <f t="shared" si="9"/>
@@ -25499,7 +25508,7 @@
     <row r="242" spans="1:65">
       <c r="A242" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B242" t="str">
         <f t="shared" si="9"/>
@@ -25578,7 +25587,7 @@
     <row r="243" spans="1:65">
       <c r="A243" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B243" t="str">
         <f t="shared" si="9"/>
@@ -25657,7 +25666,7 @@
     <row r="244" spans="1:65">
       <c r="A244" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B244" t="str">
         <f t="shared" si="9"/>
@@ -25736,7 +25745,7 @@
     <row r="245" spans="1:65">
       <c r="A245" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B245" t="str">
         <f t="shared" si="9"/>
@@ -25815,7 +25824,7 @@
     <row r="246" spans="1:65">
       <c r="A246" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B246" t="str">
         <f t="shared" si="9"/>
@@ -25894,7 +25903,7 @@
     <row r="247" spans="1:65">
       <c r="A247" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B247" t="str">
         <f t="shared" si="9"/>
@@ -25973,7 +25982,7 @@
     <row r="248" spans="1:65">
       <c r="A248" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B248" t="str">
         <f t="shared" si="9"/>
@@ -26052,7 +26061,7 @@
     <row r="249" spans="1:65">
       <c r="A249" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B249" t="str">
         <f t="shared" si="9"/>
@@ -26131,7 +26140,7 @@
     <row r="250" spans="1:65">
       <c r="A250" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B250" t="str">
         <f t="shared" si="9"/>
@@ -26210,7 +26219,7 @@
     <row r="251" spans="1:65">
       <c r="A251" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B251" t="str">
         <f t="shared" si="9"/>
@@ -26289,7 +26298,7 @@
     <row r="252" spans="1:65">
       <c r="A252" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B252" t="str">
         <f t="shared" si="9"/>
@@ -26368,7 +26377,7 @@
     <row r="253" spans="1:65">
       <c r="A253" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B253" t="str">
         <f t="shared" si="9"/>
@@ -26447,7 +26456,7 @@
     <row r="254" spans="1:65">
       <c r="A254" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B254" t="str">
         <f t="shared" si="9"/>
@@ -26526,7 +26535,7 @@
     <row r="255" spans="1:65">
       <c r="A255" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B255" t="str">
         <f t="shared" si="9"/>
@@ -26605,7 +26614,7 @@
     <row r="256" spans="1:65">
       <c r="A256" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B256" t="str">
         <f t="shared" si="9"/>
@@ -26684,7 +26693,7 @@
     <row r="257" spans="1:65">
       <c r="A257" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B257" t="str">
         <f t="shared" si="9"/>
@@ -26763,7 +26772,7 @@
     <row r="258" spans="1:65">
       <c r="A258" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B258" t="str">
         <f t="shared" si="9"/>
@@ -26842,7 +26851,7 @@
     <row r="259" spans="1:65">
       <c r="A259" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B259" t="str">
         <f t="shared" si="9"/>
@@ -26921,7 +26930,7 @@
     <row r="260" spans="1:65">
       <c r="A260" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B260" t="str">
         <f t="shared" si="9"/>
@@ -27000,7 +27009,7 @@
     <row r="261" spans="1:65">
       <c r="A261" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B261" t="str">
         <f t="shared" si="9"/>
@@ -27079,7 +27088,7 @@
     <row r="262" spans="1:65">
       <c r="A262" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B262" t="str">
         <f t="shared" si="9"/>
@@ -27158,7 +27167,7 @@
     <row r="263" spans="1:65">
       <c r="A263" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B263" t="str">
         <f t="shared" si="9"/>
@@ -27237,7 +27246,7 @@
     <row r="264" spans="1:65">
       <c r="A264" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B264" t="str">
         <f t="shared" si="9"/>
@@ -27316,7 +27325,7 @@
     <row r="265" spans="1:65">
       <c r="A265" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B265" t="str">
         <f t="shared" si="9"/>
@@ -27395,7 +27404,7 @@
     <row r="266" spans="1:65">
       <c r="A266" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B266" t="str">
         <f t="shared" si="9"/>
@@ -27474,7 +27483,7 @@
     <row r="267" spans="1:65">
       <c r="A267" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B267" t="str">
         <f t="shared" si="9"/>
@@ -27553,7 +27562,7 @@
     <row r="268" spans="1:65">
       <c r="A268" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B268" t="str">
         <f t="shared" si="9"/>
@@ -27632,7 +27641,7 @@
     <row r="269" spans="1:65">
       <c r="A269" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B269" t="str">
         <f t="shared" si="9"/>
@@ -27711,7 +27720,7 @@
     <row r="270" spans="1:65">
       <c r="A270" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B270" t="str">
         <f t="shared" si="9"/>
@@ -27790,7 +27799,7 @@
     <row r="271" spans="1:65">
       <c r="A271" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B271" t="str">
         <f t="shared" si="9"/>
@@ -27869,7 +27878,7 @@
     <row r="272" spans="1:65">
       <c r="A272" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B272" t="str">
         <f t="shared" si="9"/>
@@ -27948,7 +27957,7 @@
     <row r="273" spans="1:65">
       <c r="A273" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B273" t="str">
         <f t="shared" si="9"/>
@@ -28027,7 +28036,7 @@
     <row r="274" spans="1:65">
       <c r="A274" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B274" t="str">
         <f t="shared" si="9"/>
@@ -28106,7 +28115,7 @@
     <row r="275" spans="1:65">
       <c r="A275" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B275" t="str">
         <f t="shared" si="9"/>
@@ -28185,7 +28194,7 @@
     <row r="276" spans="1:65">
       <c r="A276" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B276" t="str">
         <f t="shared" si="9"/>
@@ -28264,7 +28273,7 @@
     <row r="277" spans="1:65">
       <c r="A277" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B277" t="str">
         <f t="shared" si="9"/>
@@ -28343,7 +28352,7 @@
     <row r="278" spans="1:65">
       <c r="A278" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B278" t="str">
         <f t="shared" si="9"/>
@@ -28422,7 +28431,7 @@
     <row r="279" spans="1:65">
       <c r="A279" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B279" t="str">
         <f t="shared" si="9"/>
@@ -28501,7 +28510,7 @@
     <row r="280" spans="1:65">
       <c r="A280" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B280" t="str">
         <f t="shared" si="9"/>
@@ -28580,7 +28589,7 @@
     <row r="281" spans="1:65">
       <c r="A281" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B281" t="str">
         <f t="shared" si="9"/>
@@ -28659,7 +28668,7 @@
     <row r="282" spans="1:65">
       <c r="A282" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B282" t="str">
         <f t="shared" si="9"/>
@@ -28738,7 +28747,7 @@
     <row r="283" spans="1:65">
       <c r="A283" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B283" t="str">
         <f t="shared" si="9"/>
@@ -28817,7 +28826,7 @@
     <row r="284" spans="1:65">
       <c r="A284" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B284" t="str">
         <f t="shared" si="9"/>
@@ -28896,7 +28905,7 @@
     <row r="285" spans="1:65">
       <c r="A285" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B285" t="str">
         <f t="shared" si="9"/>
@@ -28975,7 +28984,7 @@
     <row r="286" spans="1:65">
       <c r="A286" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B286" t="str">
         <f t="shared" si="9"/>
@@ -29054,7 +29063,7 @@
     <row r="287" spans="1:65">
       <c r="A287" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B287" t="str">
         <f t="shared" si="9"/>
@@ -29133,7 +29142,7 @@
     <row r="288" spans="1:65">
       <c r="A288" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B288" t="str">
         <f t="shared" si="9"/>
@@ -29212,7 +29221,7 @@
     <row r="289" spans="1:65">
       <c r="A289" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B289" t="str">
         <f t="shared" si="9"/>
@@ -29291,7 +29300,7 @@
     <row r="290" spans="1:65">
       <c r="A290" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B290" t="str">
         <f t="shared" si="9"/>
@@ -29370,7 +29379,7 @@
     <row r="291" spans="1:65">
       <c r="A291" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:00</v>
+        <v>01:05</v>
       </c>
       <c r="B291" t="str">
         <f t="shared" si="9"/>

--- a/Vite-Vercel開発.xlsx
+++ b/Vite-Vercel開発.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2c67ec30e06f060f/work/GitHub/work-time-tracker/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{1928CA11-C4AD-40E9-B1C5-143667E830EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4CCFE37C-B670-4A3E-B71B-AFEDFBD76204}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{1928CA11-C4AD-40E9-B1C5-143667E830EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7EE54340-E54A-421B-B29B-BE15F35AB19F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1537" uniqueCount="915">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1538" uniqueCount="916">
   <si>
     <t>npm install -g vercel</t>
     <phoneticPr fontId="1"/>
@@ -5338,6 +5338,10 @@
   </si>
   <si>
     <t>Found 89 errors in 20 files.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Found 74 errors in 18 files.</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -6110,7 +6114,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{083174DA-A42C-4F9C-978E-61AEAAD9DDFF}">
-  <dimension ref="B2:D19"/>
+  <dimension ref="B2:D20"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
@@ -6213,6 +6217,11 @@
     <row r="19" spans="3:3">
       <c r="C19" t="s">
         <v>914</v>
+      </c>
+    </row>
+    <row r="20" spans="3:3">
+      <c r="C20" t="s">
+        <v>915</v>
       </c>
     </row>
   </sheetData>
@@ -6379,7 +6388,7 @@
       MOD(NOW(),1),
       TIME(0,5,0)
     ),"HH:mm")</f>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B2" s="19"/>
       <c r="D2" s="1">
@@ -6390,7 +6399,7 @@
     <row r="3" spans="1:65">
       <c r="A3" s="19" t="str">
         <f ca="1">TEXT(NOW(),"HH:mm")</f>
-        <v>01:08</v>
+        <v>01:12</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="17" t="s">
@@ -6589,7 +6598,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B4" t="str">
         <f t="shared" ref="B4:B67" si="1">TEXT($C4, "HH:mm")</f>
@@ -6668,7 +6677,7 @@
     <row r="5" spans="1:65">
       <c r="A5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B5" t="str">
         <f t="shared" si="1"/>
@@ -6747,7 +6756,7 @@
     <row r="6" spans="1:65">
       <c r="A6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B6" t="str">
         <f t="shared" si="1"/>
@@ -6826,7 +6835,7 @@
     <row r="7" spans="1:65">
       <c r="A7" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B7" t="str">
         <f t="shared" si="1"/>
@@ -6905,7 +6914,7 @@
     <row r="8" spans="1:65">
       <c r="A8" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B8" t="str">
         <f t="shared" si="1"/>
@@ -6984,7 +6993,7 @@
     <row r="9" spans="1:65">
       <c r="A9" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B9" t="str">
         <f t="shared" si="1"/>
@@ -7063,7 +7072,7 @@
     <row r="10" spans="1:65">
       <c r="A10" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B10" t="str">
         <f t="shared" si="1"/>
@@ -7142,7 +7151,7 @@
     <row r="11" spans="1:65">
       <c r="A11" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B11" t="str">
         <f t="shared" si="1"/>
@@ -7221,7 +7230,7 @@
     <row r="12" spans="1:65">
       <c r="A12" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B12" t="str">
         <f t="shared" si="1"/>
@@ -7300,7 +7309,7 @@
     <row r="13" spans="1:65">
       <c r="A13" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B13" t="str">
         <f t="shared" si="1"/>
@@ -7379,7 +7388,7 @@
     <row r="14" spans="1:65">
       <c r="A14" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B14" t="str">
         <f t="shared" si="1"/>
@@ -7458,7 +7467,7 @@
     <row r="15" spans="1:65">
       <c r="A15" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B15" t="str">
         <f t="shared" si="1"/>
@@ -7537,7 +7546,7 @@
     <row r="16" spans="1:65">
       <c r="A16" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B16" t="str">
         <f t="shared" si="1"/>
@@ -7616,7 +7625,7 @@
     <row r="17" spans="1:65">
       <c r="A17" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B17" t="str">
         <f t="shared" si="1"/>
@@ -7695,7 +7704,7 @@
     <row r="18" spans="1:65">
       <c r="A18" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B18" t="str">
         <f t="shared" si="1"/>
@@ -7774,7 +7783,7 @@
     <row r="19" spans="1:65">
       <c r="A19" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B19" t="str">
         <f t="shared" si="1"/>
@@ -7853,7 +7862,7 @@
     <row r="20" spans="1:65">
       <c r="A20" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B20" t="str">
         <f t="shared" si="1"/>
@@ -7932,7 +7941,7 @@
     <row r="21" spans="1:65">
       <c r="A21" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B21" t="str">
         <f t="shared" si="1"/>
@@ -8011,7 +8020,7 @@
     <row r="22" spans="1:65">
       <c r="A22" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B22" t="str">
         <f t="shared" si="1"/>
@@ -8090,7 +8099,7 @@
     <row r="23" spans="1:65">
       <c r="A23" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B23" t="str">
         <f t="shared" si="1"/>
@@ -8169,7 +8178,7 @@
     <row r="24" spans="1:65">
       <c r="A24" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B24" t="str">
         <f t="shared" si="1"/>
@@ -8248,7 +8257,7 @@
     <row r="25" spans="1:65">
       <c r="A25" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B25" t="str">
         <f t="shared" si="1"/>
@@ -8327,7 +8336,7 @@
     <row r="26" spans="1:65">
       <c r="A26" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B26" t="str">
         <f t="shared" si="1"/>
@@ -8406,7 +8415,7 @@
     <row r="27" spans="1:65">
       <c r="A27" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B27" t="str">
         <f t="shared" si="1"/>
@@ -8485,7 +8494,7 @@
     <row r="28" spans="1:65">
       <c r="A28" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B28" t="str">
         <f t="shared" si="1"/>
@@ -8566,7 +8575,7 @@
     <row r="29" spans="1:65">
       <c r="A29" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B29" t="str">
         <f t="shared" si="1"/>
@@ -8647,7 +8656,7 @@
     <row r="30" spans="1:65">
       <c r="A30" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B30" t="str">
         <f t="shared" si="1"/>
@@ -8728,7 +8737,7 @@
     <row r="31" spans="1:65">
       <c r="A31" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B31" t="str">
         <f t="shared" si="1"/>
@@ -8807,7 +8816,7 @@
     <row r="32" spans="1:65">
       <c r="A32" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B32" t="str">
         <f t="shared" si="1"/>
@@ -8886,7 +8895,7 @@
     <row r="33" spans="1:65">
       <c r="A33" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B33" t="str">
         <f t="shared" si="1"/>
@@ -8965,7 +8974,7 @@
     <row r="34" spans="1:65">
       <c r="A34" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B34" t="str">
         <f t="shared" si="1"/>
@@ -9046,7 +9055,7 @@
     <row r="35" spans="1:65">
       <c r="A35" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B35" t="str">
         <f t="shared" si="1"/>
@@ -9127,7 +9136,7 @@
     <row r="36" spans="1:65">
       <c r="A36" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B36" t="str">
         <f t="shared" si="1"/>
@@ -9208,7 +9217,7 @@
     <row r="37" spans="1:65">
       <c r="A37" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B37" t="str">
         <f t="shared" si="1"/>
@@ -9287,7 +9296,7 @@
     <row r="38" spans="1:65">
       <c r="A38" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B38" t="str">
         <f t="shared" si="1"/>
@@ -9366,7 +9375,7 @@
     <row r="39" spans="1:65">
       <c r="A39" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B39" t="str">
         <f t="shared" si="1"/>
@@ -9445,7 +9454,7 @@
     <row r="40" spans="1:65">
       <c r="A40" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B40" t="str">
         <f t="shared" si="1"/>
@@ -9524,7 +9533,7 @@
     <row r="41" spans="1:65">
       <c r="A41" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B41" t="str">
         <f t="shared" si="1"/>
@@ -9603,7 +9612,7 @@
     <row r="42" spans="1:65">
       <c r="A42" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B42" t="str">
         <f t="shared" si="1"/>
@@ -9684,7 +9693,7 @@
     <row r="43" spans="1:65">
       <c r="A43" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B43" t="str">
         <f t="shared" si="1"/>
@@ -9765,7 +9774,7 @@
     <row r="44" spans="1:65">
       <c r="A44" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B44" t="str">
         <f t="shared" si="1"/>
@@ -9844,7 +9853,7 @@
     <row r="45" spans="1:65">
       <c r="A45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B45" t="str">
         <f t="shared" si="1"/>
@@ -9923,7 +9932,7 @@
     <row r="46" spans="1:65">
       <c r="A46" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B46" t="str">
         <f t="shared" si="1"/>
@@ -10002,7 +10011,7 @@
     <row r="47" spans="1:65">
       <c r="A47" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B47" t="str">
         <f t="shared" si="1"/>
@@ -10081,7 +10090,7 @@
     <row r="48" spans="1:65">
       <c r="A48" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B48" t="str">
         <f t="shared" si="1"/>
@@ -10160,7 +10169,7 @@
     <row r="49" spans="1:65">
       <c r="A49" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B49" t="str">
         <f t="shared" si="1"/>
@@ -10241,7 +10250,7 @@
     <row r="50" spans="1:65">
       <c r="A50" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B50" t="str">
         <f t="shared" si="1"/>
@@ -10322,7 +10331,7 @@
     <row r="51" spans="1:65">
       <c r="A51" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B51" t="str">
         <f t="shared" si="1"/>
@@ -10401,7 +10410,7 @@
     <row r="52" spans="1:65">
       <c r="A52" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B52" t="str">
         <f t="shared" si="1"/>
@@ -10480,7 +10489,7 @@
     <row r="53" spans="1:65">
       <c r="A53" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B53" t="str">
         <f t="shared" si="1"/>
@@ -10559,7 +10568,7 @@
     <row r="54" spans="1:65">
       <c r="A54" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B54" t="str">
         <f t="shared" si="1"/>
@@ -10638,7 +10647,7 @@
     <row r="55" spans="1:65">
       <c r="A55" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B55" t="str">
         <f t="shared" si="1"/>
@@ -10717,7 +10726,7 @@
     <row r="56" spans="1:65">
       <c r="A56" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B56" t="str">
         <f t="shared" si="1"/>
@@ -10798,7 +10807,7 @@
     <row r="57" spans="1:65">
       <c r="A57" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B57" t="str">
         <f t="shared" si="1"/>
@@ -10877,7 +10886,7 @@
     <row r="58" spans="1:65">
       <c r="A58" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B58" t="str">
         <f t="shared" si="1"/>
@@ -10958,7 +10967,7 @@
     <row r="59" spans="1:65">
       <c r="A59" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B59" t="str">
         <f t="shared" si="1"/>
@@ -11037,7 +11046,7 @@
     <row r="60" spans="1:65">
       <c r="A60" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B60" t="str">
         <f t="shared" si="1"/>
@@ -11116,7 +11125,7 @@
     <row r="61" spans="1:65">
       <c r="A61" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B61" t="str">
         <f t="shared" si="1"/>
@@ -11195,7 +11204,7 @@
     <row r="62" spans="1:65">
       <c r="A62" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B62" t="str">
         <f t="shared" si="1"/>
@@ -11274,7 +11283,7 @@
     <row r="63" spans="1:65">
       <c r="A63" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B63" t="str">
         <f t="shared" si="1"/>
@@ -11353,7 +11362,7 @@
     <row r="64" spans="1:65">
       <c r="A64" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B64" t="str">
         <f t="shared" si="1"/>
@@ -11434,7 +11443,7 @@
     <row r="65" spans="1:65">
       <c r="A65" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B65" t="str">
         <f t="shared" si="1"/>
@@ -11513,7 +11522,7 @@
     <row r="66" spans="1:65">
       <c r="A66" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B66" t="str">
         <f t="shared" si="1"/>
@@ -11592,7 +11601,7 @@
     <row r="67" spans="1:65">
       <c r="A67" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B67" t="str">
         <f t="shared" si="1"/>
@@ -11674,7 +11683,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B68" t="str">
         <f t="shared" ref="B68:B131" si="3">TEXT($C68, "HH:mm")</f>
@@ -11753,7 +11762,7 @@
     <row r="69" spans="1:65">
       <c r="A69" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B69" t="str">
         <f t="shared" si="3"/>
@@ -11832,7 +11841,7 @@
     <row r="70" spans="1:65">
       <c r="A70" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B70" t="str">
         <f t="shared" si="3"/>
@@ -11911,7 +11920,7 @@
     <row r="71" spans="1:65">
       <c r="A71" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B71" t="str">
         <f t="shared" si="3"/>
@@ -11990,7 +11999,7 @@
     <row r="72" spans="1:65">
       <c r="A72" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B72" t="str">
         <f t="shared" si="3"/>
@@ -12069,7 +12078,7 @@
     <row r="73" spans="1:65">
       <c r="A73" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B73" t="str">
         <f t="shared" si="3"/>
@@ -12148,7 +12157,7 @@
     <row r="74" spans="1:65">
       <c r="A74" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B74" t="str">
         <f t="shared" si="3"/>
@@ -12227,7 +12236,7 @@
     <row r="75" spans="1:65">
       <c r="A75" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B75" t="str">
         <f t="shared" si="3"/>
@@ -12306,7 +12315,7 @@
     <row r="76" spans="1:65">
       <c r="A76" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B76" t="str">
         <f t="shared" si="3"/>
@@ -12385,7 +12394,7 @@
     <row r="77" spans="1:65">
       <c r="A77" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B77" t="str">
         <f t="shared" si="3"/>
@@ -12464,7 +12473,7 @@
     <row r="78" spans="1:65">
       <c r="A78" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B78" t="str">
         <f t="shared" si="3"/>
@@ -12543,7 +12552,7 @@
     <row r="79" spans="1:65">
       <c r="A79" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B79" t="str">
         <f t="shared" si="3"/>
@@ -12622,7 +12631,7 @@
     <row r="80" spans="1:65">
       <c r="A80" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B80" t="str">
         <f t="shared" si="3"/>
@@ -12701,7 +12710,7 @@
     <row r="81" spans="1:65">
       <c r="A81" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B81" t="str">
         <f t="shared" si="3"/>
@@ -12780,7 +12789,7 @@
     <row r="82" spans="1:65">
       <c r="A82" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B82" t="str">
         <f t="shared" si="3"/>
@@ -12859,7 +12868,7 @@
     <row r="83" spans="1:65">
       <c r="A83" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B83" t="str">
         <f t="shared" si="3"/>
@@ -12938,7 +12947,7 @@
     <row r="84" spans="1:65">
       <c r="A84" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B84" t="str">
         <f t="shared" si="3"/>
@@ -13017,7 +13026,7 @@
     <row r="85" spans="1:65">
       <c r="A85" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B85" t="str">
         <f t="shared" si="3"/>
@@ -13096,7 +13105,7 @@
     <row r="86" spans="1:65">
       <c r="A86" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B86" t="str">
         <f t="shared" si="3"/>
@@ -13175,7 +13184,7 @@
     <row r="87" spans="1:65">
       <c r="A87" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B87" t="str">
         <f t="shared" si="3"/>
@@ -13254,7 +13263,7 @@
     <row r="88" spans="1:65">
       <c r="A88" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B88" t="str">
         <f t="shared" si="3"/>
@@ -13333,7 +13342,7 @@
     <row r="89" spans="1:65">
       <c r="A89" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B89" t="str">
         <f t="shared" si="3"/>
@@ -13412,7 +13421,7 @@
     <row r="90" spans="1:65">
       <c r="A90" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B90" t="str">
         <f t="shared" si="3"/>
@@ -13491,7 +13500,7 @@
     <row r="91" spans="1:65">
       <c r="A91" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B91" t="str">
         <f t="shared" si="3"/>
@@ -13570,7 +13579,7 @@
     <row r="92" spans="1:65">
       <c r="A92" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B92" t="str">
         <f t="shared" si="3"/>
@@ -13649,7 +13658,7 @@
     <row r="93" spans="1:65">
       <c r="A93" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B93" t="str">
         <f t="shared" si="3"/>
@@ -13728,7 +13737,7 @@
     <row r="94" spans="1:65">
       <c r="A94" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B94" t="str">
         <f t="shared" si="3"/>
@@ -13807,7 +13816,7 @@
     <row r="95" spans="1:65">
       <c r="A95" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B95" t="str">
         <f t="shared" si="3"/>
@@ -13886,7 +13895,7 @@
     <row r="96" spans="1:65">
       <c r="A96" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B96" t="str">
         <f t="shared" si="3"/>
@@ -13965,7 +13974,7 @@
     <row r="97" spans="1:65">
       <c r="A97" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B97" t="str">
         <f t="shared" si="3"/>
@@ -14044,7 +14053,7 @@
     <row r="98" spans="1:65">
       <c r="A98" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B98" t="str">
         <f t="shared" si="3"/>
@@ -14123,7 +14132,7 @@
     <row r="99" spans="1:65">
       <c r="A99" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B99" t="str">
         <f t="shared" si="3"/>
@@ -14202,7 +14211,7 @@
     <row r="100" spans="1:65">
       <c r="A100" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B100" t="str">
         <f t="shared" si="3"/>
@@ -14283,7 +14292,7 @@
     <row r="101" spans="1:65">
       <c r="A101" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B101" t="str">
         <f t="shared" si="3"/>
@@ -14362,7 +14371,7 @@
     <row r="102" spans="1:65">
       <c r="A102" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B102" t="str">
         <f t="shared" si="3"/>
@@ -14441,7 +14450,7 @@
     <row r="103" spans="1:65">
       <c r="A103" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B103" t="str">
         <f t="shared" si="3"/>
@@ -14520,7 +14529,7 @@
     <row r="104" spans="1:65">
       <c r="A104" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B104" t="str">
         <f t="shared" si="3"/>
@@ -14599,7 +14608,7 @@
     <row r="105" spans="1:65">
       <c r="A105" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B105" t="str">
         <f t="shared" si="3"/>
@@ -14678,7 +14687,7 @@
     <row r="106" spans="1:65">
       <c r="A106" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B106" t="str">
         <f t="shared" si="3"/>
@@ -14759,7 +14768,7 @@
     <row r="107" spans="1:65">
       <c r="A107" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B107" t="str">
         <f t="shared" si="3"/>
@@ -14840,7 +14849,7 @@
     <row r="108" spans="1:65">
       <c r="A108" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B108" t="str">
         <f t="shared" si="3"/>
@@ -14919,7 +14928,7 @@
     <row r="109" spans="1:65">
       <c r="A109" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B109" t="str">
         <f t="shared" si="3"/>
@@ -14998,7 +15007,7 @@
     <row r="110" spans="1:65">
       <c r="A110" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B110" t="str">
         <f t="shared" si="3"/>
@@ -15077,7 +15086,7 @@
     <row r="111" spans="1:65">
       <c r="A111" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B111" t="str">
         <f t="shared" si="3"/>
@@ -15156,7 +15165,7 @@
     <row r="112" spans="1:65">
       <c r="A112" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B112" t="str">
         <f t="shared" si="3"/>
@@ -15237,7 +15246,7 @@
     <row r="113" spans="1:65">
       <c r="A113" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B113" t="str">
         <f t="shared" si="3"/>
@@ -15316,7 +15325,7 @@
     <row r="114" spans="1:65">
       <c r="A114" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B114" t="str">
         <f t="shared" si="3"/>
@@ -15395,7 +15404,7 @@
     <row r="115" spans="1:65">
       <c r="A115" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B115" t="str">
         <f t="shared" si="3"/>
@@ -15474,7 +15483,7 @@
     <row r="116" spans="1:65">
       <c r="A116" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B116" t="str">
         <f t="shared" si="3"/>
@@ -15553,7 +15562,7 @@
     <row r="117" spans="1:65">
       <c r="A117" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B117" t="str">
         <f t="shared" si="3"/>
@@ -15632,7 +15641,7 @@
     <row r="118" spans="1:65">
       <c r="A118" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B118" t="str">
         <f t="shared" si="3"/>
@@ -15711,7 +15720,7 @@
     <row r="119" spans="1:65">
       <c r="A119" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B119" t="str">
         <f t="shared" si="3"/>
@@ -15790,7 +15799,7 @@
     <row r="120" spans="1:65">
       <c r="A120" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B120" t="str">
         <f t="shared" si="3"/>
@@ -15869,7 +15878,7 @@
     <row r="121" spans="1:65">
       <c r="A121" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B121" t="str">
         <f t="shared" si="3"/>
@@ -15948,7 +15957,7 @@
     <row r="122" spans="1:65">
       <c r="A122" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B122" t="str">
         <f t="shared" si="3"/>
@@ -16027,7 +16036,7 @@
     <row r="123" spans="1:65">
       <c r="A123" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B123" t="str">
         <f t="shared" si="3"/>
@@ -16106,7 +16115,7 @@
     <row r="124" spans="1:65">
       <c r="A124" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B124" t="str">
         <f t="shared" si="3"/>
@@ -16187,7 +16196,7 @@
     <row r="125" spans="1:65">
       <c r="A125" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B125" t="str">
         <f t="shared" si="3"/>
@@ -16268,7 +16277,7 @@
     <row r="126" spans="1:65">
       <c r="A126" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B126" t="str">
         <f t="shared" si="3"/>
@@ -16347,7 +16356,7 @@
     <row r="127" spans="1:65">
       <c r="A127" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B127" t="str">
         <f t="shared" si="3"/>
@@ -16426,7 +16435,7 @@
     <row r="128" spans="1:65">
       <c r="A128" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B128" t="str">
         <f t="shared" si="3"/>
@@ -16505,7 +16514,7 @@
     <row r="129" spans="1:65">
       <c r="A129" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B129" t="str">
         <f t="shared" si="3"/>
@@ -16584,7 +16593,7 @@
     <row r="130" spans="1:65">
       <c r="A130" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B130" t="str">
         <f t="shared" si="3"/>
@@ -16663,7 +16672,7 @@
     <row r="131" spans="1:65">
       <c r="A131" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B131" t="str">
         <f t="shared" si="3"/>
@@ -16745,7 +16754,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B132" t="str">
         <f t="shared" ref="B132:B168" si="5">TEXT($C132, "HH:mm")</f>
@@ -16824,7 +16833,7 @@
     <row r="133" spans="1:65">
       <c r="A133" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B133" t="str">
         <f t="shared" si="5"/>
@@ -16903,7 +16912,7 @@
     <row r="134" spans="1:65">
       <c r="A134" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B134" t="str">
         <f t="shared" si="5"/>
@@ -16982,7 +16991,7 @@
     <row r="135" spans="1:65">
       <c r="A135" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B135" t="str">
         <f t="shared" si="5"/>
@@ -17061,7 +17070,7 @@
     <row r="136" spans="1:65">
       <c r="A136" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B136" t="str">
         <f t="shared" si="5"/>
@@ -17142,7 +17151,7 @@
     <row r="137" spans="1:65">
       <c r="A137" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B137" t="str">
         <f t="shared" si="5"/>
@@ -17223,7 +17232,7 @@
     <row r="138" spans="1:65">
       <c r="A138" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B138" t="str">
         <f t="shared" si="5"/>
@@ -17302,7 +17311,7 @@
     <row r="139" spans="1:65">
       <c r="A139" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B139" t="str">
         <f t="shared" si="5"/>
@@ -17381,7 +17390,7 @@
     <row r="140" spans="1:65">
       <c r="A140" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B140" t="str">
         <f t="shared" si="5"/>
@@ -17460,7 +17469,7 @@
     <row r="141" spans="1:65">
       <c r="A141" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B141" t="str">
         <f t="shared" si="5"/>
@@ -17539,7 +17548,7 @@
     <row r="142" spans="1:65">
       <c r="A142" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B142" t="str">
         <f t="shared" si="5"/>
@@ -17618,7 +17627,7 @@
     <row r="143" spans="1:65">
       <c r="A143" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B143" t="str">
         <f t="shared" si="5"/>
@@ -17697,7 +17706,7 @@
     <row r="144" spans="1:65">
       <c r="A144" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B144" t="str">
         <f t="shared" si="5"/>
@@ -17776,7 +17785,7 @@
     <row r="145" spans="1:65">
       <c r="A145" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B145" t="str">
         <f t="shared" si="5"/>
@@ -17855,7 +17864,7 @@
     <row r="146" spans="1:65">
       <c r="A146" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B146" t="str">
         <f t="shared" si="5"/>
@@ -17934,7 +17943,7 @@
     <row r="147" spans="1:65">
       <c r="A147" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B147" t="str">
         <f t="shared" si="5"/>
@@ -18013,7 +18022,7 @@
     <row r="148" spans="1:65">
       <c r="A148" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B148" t="str">
         <f t="shared" si="5"/>
@@ -18094,7 +18103,7 @@
     <row r="149" spans="1:65">
       <c r="A149" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B149" t="str">
         <f t="shared" si="5"/>
@@ -18173,7 +18182,7 @@
     <row r="150" spans="1:65">
       <c r="A150" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B150" t="str">
         <f t="shared" si="5"/>
@@ -18252,7 +18261,7 @@
     <row r="151" spans="1:65">
       <c r="A151" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B151" t="str">
         <f t="shared" si="5"/>
@@ -18331,7 +18340,7 @@
     <row r="152" spans="1:65">
       <c r="A152" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B152" t="str">
         <f t="shared" si="5"/>
@@ -18410,7 +18419,7 @@
     <row r="153" spans="1:65">
       <c r="A153" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B153" t="str">
         <f t="shared" si="5"/>
@@ -18489,7 +18498,7 @@
     <row r="154" spans="1:65">
       <c r="A154" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B154" t="str">
         <f t="shared" si="5"/>
@@ -18568,7 +18577,7 @@
     <row r="155" spans="1:65">
       <c r="A155" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B155" t="str">
         <f t="shared" si="5"/>
@@ -18647,7 +18656,7 @@
     <row r="156" spans="1:65">
       <c r="A156" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B156" t="str">
         <f t="shared" si="5"/>
@@ -18726,7 +18735,7 @@
     <row r="157" spans="1:65">
       <c r="A157" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B157" t="str">
         <f t="shared" si="5"/>
@@ -18805,7 +18814,7 @@
     <row r="158" spans="1:65">
       <c r="A158" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B158" t="str">
         <f t="shared" si="5"/>
@@ -18884,7 +18893,7 @@
     <row r="159" spans="1:65">
       <c r="A159" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B159" t="str">
         <f t="shared" si="5"/>
@@ -18963,7 +18972,7 @@
     <row r="160" spans="1:65">
       <c r="A160" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B160" t="str">
         <f t="shared" si="5"/>
@@ -19042,7 +19051,7 @@
     <row r="161" spans="1:65">
       <c r="A161" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B161" t="str">
         <f t="shared" si="5"/>
@@ -19121,7 +19130,7 @@
     <row r="162" spans="1:65">
       <c r="A162" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B162" t="str">
         <f t="shared" si="5"/>
@@ -19200,7 +19209,7 @@
     <row r="163" spans="1:65">
       <c r="A163" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B163" t="str">
         <f t="shared" si="5"/>
@@ -19279,7 +19288,7 @@
     <row r="164" spans="1:65">
       <c r="A164" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B164" t="str">
         <f t="shared" si="5"/>
@@ -19358,7 +19367,7 @@
     <row r="165" spans="1:65">
       <c r="A165" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B165" t="str">
         <f t="shared" si="5"/>
@@ -19437,7 +19446,7 @@
     <row r="166" spans="1:65">
       <c r="A166" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B166" t="str">
         <f t="shared" si="5"/>
@@ -19518,7 +19527,7 @@
     <row r="167" spans="1:65">
       <c r="A167" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B167" t="str">
         <f t="shared" si="5"/>
@@ -19597,7 +19606,7 @@
     <row r="168" spans="1:65">
       <c r="A168" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B168" t="str">
         <f t="shared" si="5"/>
@@ -19679,7 +19688,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B169" t="str">
         <f>TEXT($C169, "HH:mm")</f>
@@ -19761,7 +19770,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B170" t="str">
         <f t="shared" ref="B170:B233" si="7">TEXT($C170, "HH:mm")</f>
@@ -19840,7 +19849,7 @@
     <row r="171" spans="1:65">
       <c r="A171" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B171" t="str">
         <f t="shared" si="7"/>
@@ -19919,7 +19928,7 @@
     <row r="172" spans="1:65">
       <c r="A172" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B172" t="str">
         <f t="shared" si="7"/>
@@ -20000,7 +20009,7 @@
     <row r="173" spans="1:65">
       <c r="A173" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B173" t="str">
         <f t="shared" si="7"/>
@@ -20079,7 +20088,7 @@
     <row r="174" spans="1:65">
       <c r="A174" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B174" t="str">
         <f t="shared" si="7"/>
@@ -20158,7 +20167,7 @@
     <row r="175" spans="1:65">
       <c r="A175" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B175" t="str">
         <f t="shared" si="7"/>
@@ -20237,7 +20246,7 @@
     <row r="176" spans="1:65">
       <c r="A176" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B176" t="str">
         <f t="shared" si="7"/>
@@ -20316,7 +20325,7 @@
     <row r="177" spans="1:65">
       <c r="A177" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B177" t="str">
         <f t="shared" si="7"/>
@@ -20395,7 +20404,7 @@
     <row r="178" spans="1:65">
       <c r="A178" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B178" t="str">
         <f t="shared" si="7"/>
@@ -20476,7 +20485,7 @@
     <row r="179" spans="1:65">
       <c r="A179" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B179" t="str">
         <f t="shared" si="7"/>
@@ -20555,7 +20564,7 @@
     <row r="180" spans="1:65">
       <c r="A180" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B180" t="str">
         <f t="shared" si="7"/>
@@ -20634,7 +20643,7 @@
     <row r="181" spans="1:65">
       <c r="A181" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B181" t="str">
         <f t="shared" si="7"/>
@@ -20715,7 +20724,7 @@
     <row r="182" spans="1:65">
       <c r="A182" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B182" t="str">
         <f t="shared" si="7"/>
@@ -20796,7 +20805,7 @@
     <row r="183" spans="1:65">
       <c r="A183" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B183" t="str">
         <f t="shared" si="7"/>
@@ -20877,7 +20886,7 @@
     <row r="184" spans="1:65">
       <c r="A184" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B184" t="str">
         <f t="shared" si="7"/>
@@ -20960,7 +20969,7 @@
     <row r="185" spans="1:65">
       <c r="A185" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B185" t="str">
         <f t="shared" si="7"/>
@@ -21041,7 +21050,7 @@
     <row r="186" spans="1:65">
       <c r="A186" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B186" t="str">
         <f t="shared" si="7"/>
@@ -21122,7 +21131,7 @@
     <row r="187" spans="1:65">
       <c r="A187" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B187" t="str">
         <f t="shared" si="7"/>
@@ -21203,7 +21212,7 @@
     <row r="188" spans="1:65">
       <c r="A188" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B188" t="str">
         <f t="shared" si="7"/>
@@ -21284,7 +21293,7 @@
     <row r="189" spans="1:65">
       <c r="A189" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B189" t="str">
         <f t="shared" si="7"/>
@@ -21365,7 +21374,7 @@
     <row r="190" spans="1:65">
       <c r="A190" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B190" t="str">
         <f t="shared" si="7"/>
@@ -21448,7 +21457,7 @@
     <row r="191" spans="1:65">
       <c r="A191" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B191" t="str">
         <f t="shared" si="7"/>
@@ -21531,7 +21540,7 @@
     <row r="192" spans="1:65">
       <c r="A192" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B192" t="str">
         <f t="shared" si="7"/>
@@ -21614,7 +21623,7 @@
     <row r="193" spans="1:65">
       <c r="A193" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B193" t="str">
         <f t="shared" si="7"/>
@@ -21697,7 +21706,7 @@
     <row r="194" spans="1:65">
       <c r="A194" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B194" t="str">
         <f t="shared" si="7"/>
@@ -21778,7 +21787,7 @@
     <row r="195" spans="1:65">
       <c r="A195" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B195" t="str">
         <f t="shared" si="7"/>
@@ -21859,7 +21868,7 @@
     <row r="196" spans="1:65">
       <c r="A196" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B196" t="str">
         <f t="shared" si="7"/>
@@ -21942,7 +21951,7 @@
     <row r="197" spans="1:65">
       <c r="A197" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B197" t="str">
         <f t="shared" si="7"/>
@@ -22021,7 +22030,7 @@
     <row r="198" spans="1:65">
       <c r="A198" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B198" t="str">
         <f t="shared" si="7"/>
@@ -22100,7 +22109,7 @@
     <row r="199" spans="1:65">
       <c r="A199" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B199" t="str">
         <f t="shared" si="7"/>
@@ -22179,7 +22188,7 @@
     <row r="200" spans="1:65">
       <c r="A200" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B200" t="str">
         <f t="shared" si="7"/>
@@ -22258,7 +22267,7 @@
     <row r="201" spans="1:65">
       <c r="A201" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B201" t="str">
         <f t="shared" si="7"/>
@@ -22337,7 +22346,7 @@
     <row r="202" spans="1:65">
       <c r="A202" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B202" t="str">
         <f t="shared" si="7"/>
@@ -22418,7 +22427,7 @@
     <row r="203" spans="1:65">
       <c r="A203" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B203" t="str">
         <f t="shared" si="7"/>
@@ -22497,7 +22506,7 @@
     <row r="204" spans="1:65">
       <c r="A204" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B204" t="str">
         <f t="shared" si="7"/>
@@ -22576,7 +22585,7 @@
     <row r="205" spans="1:65">
       <c r="A205" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B205" t="str">
         <f t="shared" si="7"/>
@@ -22655,7 +22664,7 @@
     <row r="206" spans="1:65">
       <c r="A206" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B206" t="str">
         <f t="shared" si="7"/>
@@ -22734,7 +22743,7 @@
     <row r="207" spans="1:65">
       <c r="A207" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B207" t="str">
         <f t="shared" si="7"/>
@@ -22813,7 +22822,7 @@
     <row r="208" spans="1:65">
       <c r="A208" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B208" t="str">
         <f t="shared" si="7"/>
@@ -22894,7 +22903,7 @@
     <row r="209" spans="1:65">
       <c r="A209" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B209" t="str">
         <f t="shared" si="7"/>
@@ -22973,7 +22982,7 @@
     <row r="210" spans="1:65">
       <c r="A210" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B210" t="str">
         <f t="shared" si="7"/>
@@ -23052,7 +23061,7 @@
     <row r="211" spans="1:65">
       <c r="A211" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B211" t="str">
         <f t="shared" si="7"/>
@@ -23133,7 +23142,7 @@
     <row r="212" spans="1:65">
       <c r="A212" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B212" t="str">
         <f t="shared" si="7"/>
@@ -23212,7 +23221,7 @@
     <row r="213" spans="1:65">
       <c r="A213" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B213" t="str">
         <f t="shared" si="7"/>
@@ -23291,7 +23300,7 @@
     <row r="214" spans="1:65">
       <c r="A214" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B214" t="str">
         <f t="shared" si="7"/>
@@ -23370,7 +23379,7 @@
     <row r="215" spans="1:65">
       <c r="A215" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B215" t="str">
         <f t="shared" si="7"/>
@@ -23449,7 +23458,7 @@
     <row r="216" spans="1:65">
       <c r="A216" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B216" t="str">
         <f t="shared" si="7"/>
@@ -23528,7 +23537,7 @@
     <row r="217" spans="1:65">
       <c r="A217" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B217" t="str">
         <f t="shared" si="7"/>
@@ -23607,7 +23616,7 @@
     <row r="218" spans="1:65">
       <c r="A218" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B218" t="str">
         <f t="shared" si="7"/>
@@ -23686,7 +23695,7 @@
     <row r="219" spans="1:65">
       <c r="A219" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B219" t="str">
         <f t="shared" si="7"/>
@@ -23765,7 +23774,7 @@
     <row r="220" spans="1:65">
       <c r="A220" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B220" t="str">
         <f t="shared" si="7"/>
@@ -23846,7 +23855,7 @@
     <row r="221" spans="1:65">
       <c r="A221" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B221" t="str">
         <f t="shared" si="7"/>
@@ -23925,7 +23934,7 @@
     <row r="222" spans="1:65">
       <c r="A222" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B222" t="str">
         <f t="shared" si="7"/>
@@ -24004,7 +24013,7 @@
     <row r="223" spans="1:65">
       <c r="A223" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B223" t="str">
         <f t="shared" si="7"/>
@@ -24083,7 +24092,7 @@
     <row r="224" spans="1:65">
       <c r="A224" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B224" t="str">
         <f t="shared" si="7"/>
@@ -24162,7 +24171,7 @@
     <row r="225" spans="1:65">
       <c r="A225" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B225" t="str">
         <f t="shared" si="7"/>
@@ -24241,7 +24250,7 @@
     <row r="226" spans="1:65">
       <c r="A226" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B226" t="str">
         <f t="shared" si="7"/>
@@ -24320,7 +24329,7 @@
     <row r="227" spans="1:65">
       <c r="A227" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B227" t="str">
         <f t="shared" si="7"/>
@@ -24399,7 +24408,7 @@
     <row r="228" spans="1:65">
       <c r="A228" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B228" t="str">
         <f t="shared" si="7"/>
@@ -24478,7 +24487,7 @@
     <row r="229" spans="1:65">
       <c r="A229" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B229" t="str">
         <f t="shared" si="7"/>
@@ -24557,7 +24566,7 @@
     <row r="230" spans="1:65">
       <c r="A230" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B230" t="str">
         <f t="shared" si="7"/>
@@ -24636,7 +24645,7 @@
     <row r="231" spans="1:65">
       <c r="A231" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B231" t="str">
         <f t="shared" si="7"/>
@@ -24715,7 +24724,7 @@
     <row r="232" spans="1:65">
       <c r="A232" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B232" t="str">
         <f t="shared" si="7"/>
@@ -24794,7 +24803,7 @@
     <row r="233" spans="1:65">
       <c r="A233" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B233" t="str">
         <f t="shared" si="7"/>
@@ -24876,7 +24885,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B234" t="str">
         <f t="shared" ref="B234:B291" si="9">TEXT($C234, "HH:mm")</f>
@@ -24955,7 +24964,7 @@
     <row r="235" spans="1:65">
       <c r="A235" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B235" t="str">
         <f t="shared" si="9"/>
@@ -25034,7 +25043,7 @@
     <row r="236" spans="1:65">
       <c r="A236" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B236" t="str">
         <f t="shared" si="9"/>
@@ -25113,7 +25122,7 @@
     <row r="237" spans="1:65">
       <c r="A237" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B237" t="str">
         <f t="shared" si="9"/>
@@ -25192,7 +25201,7 @@
     <row r="238" spans="1:65">
       <c r="A238" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B238" t="str">
         <f t="shared" si="9"/>
@@ -25271,7 +25280,7 @@
     <row r="239" spans="1:65">
       <c r="A239" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B239" t="str">
         <f t="shared" si="9"/>
@@ -25350,7 +25359,7 @@
     <row r="240" spans="1:65">
       <c r="A240" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B240" t="str">
         <f t="shared" si="9"/>
@@ -25429,7 +25438,7 @@
     <row r="241" spans="1:65">
       <c r="A241" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B241" t="str">
         <f t="shared" si="9"/>
@@ -25508,7 +25517,7 @@
     <row r="242" spans="1:65">
       <c r="A242" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B242" t="str">
         <f t="shared" si="9"/>
@@ -25587,7 +25596,7 @@
     <row r="243" spans="1:65">
       <c r="A243" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B243" t="str">
         <f t="shared" si="9"/>
@@ -25666,7 +25675,7 @@
     <row r="244" spans="1:65">
       <c r="A244" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B244" t="str">
         <f t="shared" si="9"/>
@@ -25745,7 +25754,7 @@
     <row r="245" spans="1:65">
       <c r="A245" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B245" t="str">
         <f t="shared" si="9"/>
@@ -25824,7 +25833,7 @@
     <row r="246" spans="1:65">
       <c r="A246" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B246" t="str">
         <f t="shared" si="9"/>
@@ -25903,7 +25912,7 @@
     <row r="247" spans="1:65">
       <c r="A247" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B247" t="str">
         <f t="shared" si="9"/>
@@ -25982,7 +25991,7 @@
     <row r="248" spans="1:65">
       <c r="A248" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B248" t="str">
         <f t="shared" si="9"/>
@@ -26061,7 +26070,7 @@
     <row r="249" spans="1:65">
       <c r="A249" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B249" t="str">
         <f t="shared" si="9"/>
@@ -26140,7 +26149,7 @@
     <row r="250" spans="1:65">
       <c r="A250" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B250" t="str">
         <f t="shared" si="9"/>
@@ -26219,7 +26228,7 @@
     <row r="251" spans="1:65">
       <c r="A251" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B251" t="str">
         <f t="shared" si="9"/>
@@ -26298,7 +26307,7 @@
     <row r="252" spans="1:65">
       <c r="A252" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B252" t="str">
         <f t="shared" si="9"/>
@@ -26377,7 +26386,7 @@
     <row r="253" spans="1:65">
       <c r="A253" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B253" t="str">
         <f t="shared" si="9"/>
@@ -26456,7 +26465,7 @@
     <row r="254" spans="1:65">
       <c r="A254" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B254" t="str">
         <f t="shared" si="9"/>
@@ -26535,7 +26544,7 @@
     <row r="255" spans="1:65">
       <c r="A255" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B255" t="str">
         <f t="shared" si="9"/>
@@ -26614,7 +26623,7 @@
     <row r="256" spans="1:65">
       <c r="A256" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B256" t="str">
         <f t="shared" si="9"/>
@@ -26693,7 +26702,7 @@
     <row r="257" spans="1:65">
       <c r="A257" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B257" t="str">
         <f t="shared" si="9"/>
@@ -26772,7 +26781,7 @@
     <row r="258" spans="1:65">
       <c r="A258" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B258" t="str">
         <f t="shared" si="9"/>
@@ -26851,7 +26860,7 @@
     <row r="259" spans="1:65">
       <c r="A259" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B259" t="str">
         <f t="shared" si="9"/>
@@ -26930,7 +26939,7 @@
     <row r="260" spans="1:65">
       <c r="A260" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B260" t="str">
         <f t="shared" si="9"/>
@@ -27009,7 +27018,7 @@
     <row r="261" spans="1:65">
       <c r="A261" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B261" t="str">
         <f t="shared" si="9"/>
@@ -27088,7 +27097,7 @@
     <row r="262" spans="1:65">
       <c r="A262" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B262" t="str">
         <f t="shared" si="9"/>
@@ -27167,7 +27176,7 @@
     <row r="263" spans="1:65">
       <c r="A263" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B263" t="str">
         <f t="shared" si="9"/>
@@ -27246,7 +27255,7 @@
     <row r="264" spans="1:65">
       <c r="A264" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B264" t="str">
         <f t="shared" si="9"/>
@@ -27325,7 +27334,7 @@
     <row r="265" spans="1:65">
       <c r="A265" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B265" t="str">
         <f t="shared" si="9"/>
@@ -27404,7 +27413,7 @@
     <row r="266" spans="1:65">
       <c r="A266" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B266" t="str">
         <f t="shared" si="9"/>
@@ -27483,7 +27492,7 @@
     <row r="267" spans="1:65">
       <c r="A267" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B267" t="str">
         <f t="shared" si="9"/>
@@ -27562,7 +27571,7 @@
     <row r="268" spans="1:65">
       <c r="A268" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B268" t="str">
         <f t="shared" si="9"/>
@@ -27641,7 +27650,7 @@
     <row r="269" spans="1:65">
       <c r="A269" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B269" t="str">
         <f t="shared" si="9"/>
@@ -27720,7 +27729,7 @@
     <row r="270" spans="1:65">
       <c r="A270" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B270" t="str">
         <f t="shared" si="9"/>
@@ -27799,7 +27808,7 @@
     <row r="271" spans="1:65">
       <c r="A271" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B271" t="str">
         <f t="shared" si="9"/>
@@ -27878,7 +27887,7 @@
     <row r="272" spans="1:65">
       <c r="A272" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B272" t="str">
         <f t="shared" si="9"/>
@@ -27957,7 +27966,7 @@
     <row r="273" spans="1:65">
       <c r="A273" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B273" t="str">
         <f t="shared" si="9"/>
@@ -28036,7 +28045,7 @@
     <row r="274" spans="1:65">
       <c r="A274" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B274" t="str">
         <f t="shared" si="9"/>
@@ -28115,7 +28124,7 @@
     <row r="275" spans="1:65">
       <c r="A275" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B275" t="str">
         <f t="shared" si="9"/>
@@ -28194,7 +28203,7 @@
     <row r="276" spans="1:65">
       <c r="A276" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B276" t="str">
         <f t="shared" si="9"/>
@@ -28273,7 +28282,7 @@
     <row r="277" spans="1:65">
       <c r="A277" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B277" t="str">
         <f t="shared" si="9"/>
@@ -28352,7 +28361,7 @@
     <row r="278" spans="1:65">
       <c r="A278" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B278" t="str">
         <f t="shared" si="9"/>
@@ -28431,7 +28440,7 @@
     <row r="279" spans="1:65">
       <c r="A279" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B279" t="str">
         <f t="shared" si="9"/>
@@ -28510,7 +28519,7 @@
     <row r="280" spans="1:65">
       <c r="A280" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B280" t="str">
         <f t="shared" si="9"/>
@@ -28589,7 +28598,7 @@
     <row r="281" spans="1:65">
       <c r="A281" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B281" t="str">
         <f t="shared" si="9"/>
@@ -28668,7 +28677,7 @@
     <row r="282" spans="1:65">
       <c r="A282" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B282" t="str">
         <f t="shared" si="9"/>
@@ -28747,7 +28756,7 @@
     <row r="283" spans="1:65">
       <c r="A283" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B283" t="str">
         <f t="shared" si="9"/>
@@ -28826,7 +28835,7 @@
     <row r="284" spans="1:65">
       <c r="A284" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B284" t="str">
         <f t="shared" si="9"/>
@@ -28905,7 +28914,7 @@
     <row r="285" spans="1:65">
       <c r="A285" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B285" t="str">
         <f t="shared" si="9"/>
@@ -28984,7 +28993,7 @@
     <row r="286" spans="1:65">
       <c r="A286" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B286" t="str">
         <f t="shared" si="9"/>
@@ -29063,7 +29072,7 @@
     <row r="287" spans="1:65">
       <c r="A287" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B287" t="str">
         <f t="shared" si="9"/>
@@ -29142,7 +29151,7 @@
     <row r="288" spans="1:65">
       <c r="A288" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B288" t="str">
         <f t="shared" si="9"/>
@@ -29221,7 +29230,7 @@
     <row r="289" spans="1:65">
       <c r="A289" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B289" t="str">
         <f t="shared" si="9"/>
@@ -29300,7 +29309,7 @@
     <row r="290" spans="1:65">
       <c r="A290" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B290" t="str">
         <f t="shared" si="9"/>
@@ -29379,7 +29388,7 @@
     <row r="291" spans="1:65">
       <c r="A291" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:05</v>
+        <v>01:10</v>
       </c>
       <c r="B291" t="str">
         <f t="shared" si="9"/>

--- a/Vite-Vercel開発.xlsx
+++ b/Vite-Vercel開発.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2c67ec30e06f060f/work/GitHub/work-time-tracker/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{1928CA11-C4AD-40E9-B1C5-143667E830EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7EE54340-E54A-421B-B29B-BE15F35AB19F}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{1928CA11-C4AD-40E9-B1C5-143667E830EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DCDB1AAB-A003-4583-BAA9-1606A15D15FB}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1538" uniqueCount="916">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1539" uniqueCount="917">
   <si>
     <t>npm install -g vercel</t>
     <phoneticPr fontId="1"/>
@@ -5342,6 +5342,10 @@
   </si>
   <si>
     <t>Found 74 errors in 18 files.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Found 68 errors in 18 files.</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -6114,7 +6118,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{083174DA-A42C-4F9C-978E-61AEAAD9DDFF}">
-  <dimension ref="B2:D20"/>
+  <dimension ref="B2:D21"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
@@ -6222,6 +6226,11 @@
     <row r="20" spans="3:3">
       <c r="C20" t="s">
         <v>915</v>
+      </c>
+    </row>
+    <row r="21" spans="3:3">
+      <c r="C21" t="s">
+        <v>916</v>
       </c>
     </row>
   </sheetData>
@@ -6388,7 +6397,7 @@
       MOD(NOW(),1),
       TIME(0,5,0)
     ),"HH:mm")</f>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B2" s="19"/>
       <c r="D2" s="1">
@@ -6399,7 +6408,7 @@
     <row r="3" spans="1:65">
       <c r="A3" s="19" t="str">
         <f ca="1">TEXT(NOW(),"HH:mm")</f>
-        <v>01:12</v>
+        <v>01:16</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="17" t="s">
@@ -6598,7 +6607,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B4" t="str">
         <f t="shared" ref="B4:B67" si="1">TEXT($C4, "HH:mm")</f>
@@ -6677,7 +6686,7 @@
     <row r="5" spans="1:65">
       <c r="A5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B5" t="str">
         <f t="shared" si="1"/>
@@ -6756,7 +6765,7 @@
     <row r="6" spans="1:65">
       <c r="A6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B6" t="str">
         <f t="shared" si="1"/>
@@ -6835,7 +6844,7 @@
     <row r="7" spans="1:65">
       <c r="A7" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B7" t="str">
         <f t="shared" si="1"/>
@@ -6914,7 +6923,7 @@
     <row r="8" spans="1:65">
       <c r="A8" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B8" t="str">
         <f t="shared" si="1"/>
@@ -6993,7 +7002,7 @@
     <row r="9" spans="1:65">
       <c r="A9" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B9" t="str">
         <f t="shared" si="1"/>
@@ -7072,7 +7081,7 @@
     <row r="10" spans="1:65">
       <c r="A10" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B10" t="str">
         <f t="shared" si="1"/>
@@ -7151,7 +7160,7 @@
     <row r="11" spans="1:65">
       <c r="A11" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B11" t="str">
         <f t="shared" si="1"/>
@@ -7230,7 +7239,7 @@
     <row r="12" spans="1:65">
       <c r="A12" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B12" t="str">
         <f t="shared" si="1"/>
@@ -7309,7 +7318,7 @@
     <row r="13" spans="1:65">
       <c r="A13" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B13" t="str">
         <f t="shared" si="1"/>
@@ -7388,7 +7397,7 @@
     <row r="14" spans="1:65">
       <c r="A14" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B14" t="str">
         <f t="shared" si="1"/>
@@ -7467,7 +7476,7 @@
     <row r="15" spans="1:65">
       <c r="A15" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B15" t="str">
         <f t="shared" si="1"/>
@@ -7546,7 +7555,7 @@
     <row r="16" spans="1:65">
       <c r="A16" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B16" t="str">
         <f t="shared" si="1"/>
@@ -7625,7 +7634,7 @@
     <row r="17" spans="1:65">
       <c r="A17" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B17" t="str">
         <f t="shared" si="1"/>
@@ -7704,7 +7713,7 @@
     <row r="18" spans="1:65">
       <c r="A18" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B18" t="str">
         <f t="shared" si="1"/>
@@ -7783,7 +7792,7 @@
     <row r="19" spans="1:65">
       <c r="A19" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B19" t="str">
         <f t="shared" si="1"/>
@@ -7862,7 +7871,7 @@
     <row r="20" spans="1:65">
       <c r="A20" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B20" t="str">
         <f t="shared" si="1"/>
@@ -7941,7 +7950,7 @@
     <row r="21" spans="1:65">
       <c r="A21" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B21" t="str">
         <f t="shared" si="1"/>
@@ -8020,7 +8029,7 @@
     <row r="22" spans="1:65">
       <c r="A22" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B22" t="str">
         <f t="shared" si="1"/>
@@ -8099,7 +8108,7 @@
     <row r="23" spans="1:65">
       <c r="A23" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B23" t="str">
         <f t="shared" si="1"/>
@@ -8178,7 +8187,7 @@
     <row r="24" spans="1:65">
       <c r="A24" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B24" t="str">
         <f t="shared" si="1"/>
@@ -8257,7 +8266,7 @@
     <row r="25" spans="1:65">
       <c r="A25" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B25" t="str">
         <f t="shared" si="1"/>
@@ -8336,7 +8345,7 @@
     <row r="26" spans="1:65">
       <c r="A26" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B26" t="str">
         <f t="shared" si="1"/>
@@ -8415,7 +8424,7 @@
     <row r="27" spans="1:65">
       <c r="A27" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B27" t="str">
         <f t="shared" si="1"/>
@@ -8494,7 +8503,7 @@
     <row r="28" spans="1:65">
       <c r="A28" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B28" t="str">
         <f t="shared" si="1"/>
@@ -8575,7 +8584,7 @@
     <row r="29" spans="1:65">
       <c r="A29" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B29" t="str">
         <f t="shared" si="1"/>
@@ -8656,7 +8665,7 @@
     <row r="30" spans="1:65">
       <c r="A30" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B30" t="str">
         <f t="shared" si="1"/>
@@ -8737,7 +8746,7 @@
     <row r="31" spans="1:65">
       <c r="A31" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B31" t="str">
         <f t="shared" si="1"/>
@@ -8816,7 +8825,7 @@
     <row r="32" spans="1:65">
       <c r="A32" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B32" t="str">
         <f t="shared" si="1"/>
@@ -8895,7 +8904,7 @@
     <row r="33" spans="1:65">
       <c r="A33" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B33" t="str">
         <f t="shared" si="1"/>
@@ -8974,7 +8983,7 @@
     <row r="34" spans="1:65">
       <c r="A34" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B34" t="str">
         <f t="shared" si="1"/>
@@ -9055,7 +9064,7 @@
     <row r="35" spans="1:65">
       <c r="A35" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B35" t="str">
         <f t="shared" si="1"/>
@@ -9136,7 +9145,7 @@
     <row r="36" spans="1:65">
       <c r="A36" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B36" t="str">
         <f t="shared" si="1"/>
@@ -9217,7 +9226,7 @@
     <row r="37" spans="1:65">
       <c r="A37" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B37" t="str">
         <f t="shared" si="1"/>
@@ -9296,7 +9305,7 @@
     <row r="38" spans="1:65">
       <c r="A38" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B38" t="str">
         <f t="shared" si="1"/>
@@ -9375,7 +9384,7 @@
     <row r="39" spans="1:65">
       <c r="A39" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B39" t="str">
         <f t="shared" si="1"/>
@@ -9454,7 +9463,7 @@
     <row r="40" spans="1:65">
       <c r="A40" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B40" t="str">
         <f t="shared" si="1"/>
@@ -9533,7 +9542,7 @@
     <row r="41" spans="1:65">
       <c r="A41" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B41" t="str">
         <f t="shared" si="1"/>
@@ -9612,7 +9621,7 @@
     <row r="42" spans="1:65">
       <c r="A42" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B42" t="str">
         <f t="shared" si="1"/>
@@ -9693,7 +9702,7 @@
     <row r="43" spans="1:65">
       <c r="A43" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B43" t="str">
         <f t="shared" si="1"/>
@@ -9774,7 +9783,7 @@
     <row r="44" spans="1:65">
       <c r="A44" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B44" t="str">
         <f t="shared" si="1"/>
@@ -9853,7 +9862,7 @@
     <row r="45" spans="1:65">
       <c r="A45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B45" t="str">
         <f t="shared" si="1"/>
@@ -9932,7 +9941,7 @@
     <row r="46" spans="1:65">
       <c r="A46" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B46" t="str">
         <f t="shared" si="1"/>
@@ -10011,7 +10020,7 @@
     <row r="47" spans="1:65">
       <c r="A47" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B47" t="str">
         <f t="shared" si="1"/>
@@ -10090,7 +10099,7 @@
     <row r="48" spans="1:65">
       <c r="A48" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B48" t="str">
         <f t="shared" si="1"/>
@@ -10169,7 +10178,7 @@
     <row r="49" spans="1:65">
       <c r="A49" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B49" t="str">
         <f t="shared" si="1"/>
@@ -10250,7 +10259,7 @@
     <row r="50" spans="1:65">
       <c r="A50" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B50" t="str">
         <f t="shared" si="1"/>
@@ -10331,7 +10340,7 @@
     <row r="51" spans="1:65">
       <c r="A51" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B51" t="str">
         <f t="shared" si="1"/>
@@ -10410,7 +10419,7 @@
     <row r="52" spans="1:65">
       <c r="A52" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B52" t="str">
         <f t="shared" si="1"/>
@@ -10489,7 +10498,7 @@
     <row r="53" spans="1:65">
       <c r="A53" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B53" t="str">
         <f t="shared" si="1"/>
@@ -10568,7 +10577,7 @@
     <row r="54" spans="1:65">
       <c r="A54" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B54" t="str">
         <f t="shared" si="1"/>
@@ -10647,7 +10656,7 @@
     <row r="55" spans="1:65">
       <c r="A55" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B55" t="str">
         <f t="shared" si="1"/>
@@ -10726,7 +10735,7 @@
     <row r="56" spans="1:65">
       <c r="A56" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B56" t="str">
         <f t="shared" si="1"/>
@@ -10807,7 +10816,7 @@
     <row r="57" spans="1:65">
       <c r="A57" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B57" t="str">
         <f t="shared" si="1"/>
@@ -10886,7 +10895,7 @@
     <row r="58" spans="1:65">
       <c r="A58" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B58" t="str">
         <f t="shared" si="1"/>
@@ -10967,7 +10976,7 @@
     <row r="59" spans="1:65">
       <c r="A59" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B59" t="str">
         <f t="shared" si="1"/>
@@ -11046,7 +11055,7 @@
     <row r="60" spans="1:65">
       <c r="A60" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B60" t="str">
         <f t="shared" si="1"/>
@@ -11125,7 +11134,7 @@
     <row r="61" spans="1:65">
       <c r="A61" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B61" t="str">
         <f t="shared" si="1"/>
@@ -11204,7 +11213,7 @@
     <row r="62" spans="1:65">
       <c r="A62" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B62" t="str">
         <f t="shared" si="1"/>
@@ -11283,7 +11292,7 @@
     <row r="63" spans="1:65">
       <c r="A63" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B63" t="str">
         <f t="shared" si="1"/>
@@ -11362,7 +11371,7 @@
     <row r="64" spans="1:65">
       <c r="A64" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B64" t="str">
         <f t="shared" si="1"/>
@@ -11443,7 +11452,7 @@
     <row r="65" spans="1:65">
       <c r="A65" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B65" t="str">
         <f t="shared" si="1"/>
@@ -11522,7 +11531,7 @@
     <row r="66" spans="1:65">
       <c r="A66" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B66" t="str">
         <f t="shared" si="1"/>
@@ -11601,7 +11610,7 @@
     <row r="67" spans="1:65">
       <c r="A67" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B67" t="str">
         <f t="shared" si="1"/>
@@ -11683,7 +11692,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B68" t="str">
         <f t="shared" ref="B68:B131" si="3">TEXT($C68, "HH:mm")</f>
@@ -11762,7 +11771,7 @@
     <row r="69" spans="1:65">
       <c r="A69" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B69" t="str">
         <f t="shared" si="3"/>
@@ -11841,7 +11850,7 @@
     <row r="70" spans="1:65">
       <c r="A70" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B70" t="str">
         <f t="shared" si="3"/>
@@ -11920,7 +11929,7 @@
     <row r="71" spans="1:65">
       <c r="A71" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B71" t="str">
         <f t="shared" si="3"/>
@@ -11999,7 +12008,7 @@
     <row r="72" spans="1:65">
       <c r="A72" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B72" t="str">
         <f t="shared" si="3"/>
@@ -12078,7 +12087,7 @@
     <row r="73" spans="1:65">
       <c r="A73" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B73" t="str">
         <f t="shared" si="3"/>
@@ -12157,7 +12166,7 @@
     <row r="74" spans="1:65">
       <c r="A74" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B74" t="str">
         <f t="shared" si="3"/>
@@ -12236,7 +12245,7 @@
     <row r="75" spans="1:65">
       <c r="A75" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B75" t="str">
         <f t="shared" si="3"/>
@@ -12315,7 +12324,7 @@
     <row r="76" spans="1:65">
       <c r="A76" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B76" t="str">
         <f t="shared" si="3"/>
@@ -12394,7 +12403,7 @@
     <row r="77" spans="1:65">
       <c r="A77" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B77" t="str">
         <f t="shared" si="3"/>
@@ -12473,7 +12482,7 @@
     <row r="78" spans="1:65">
       <c r="A78" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B78" t="str">
         <f t="shared" si="3"/>
@@ -12552,7 +12561,7 @@
     <row r="79" spans="1:65">
       <c r="A79" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B79" t="str">
         <f t="shared" si="3"/>
@@ -12631,7 +12640,7 @@
     <row r="80" spans="1:65">
       <c r="A80" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B80" t="str">
         <f t="shared" si="3"/>
@@ -12710,7 +12719,7 @@
     <row r="81" spans="1:65">
       <c r="A81" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B81" t="str">
         <f t="shared" si="3"/>
@@ -12789,7 +12798,7 @@
     <row r="82" spans="1:65">
       <c r="A82" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B82" t="str">
         <f t="shared" si="3"/>
@@ -12868,7 +12877,7 @@
     <row r="83" spans="1:65">
       <c r="A83" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B83" t="str">
         <f t="shared" si="3"/>
@@ -12947,7 +12956,7 @@
     <row r="84" spans="1:65">
       <c r="A84" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B84" t="str">
         <f t="shared" si="3"/>
@@ -13026,7 +13035,7 @@
     <row r="85" spans="1:65">
       <c r="A85" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B85" t="str">
         <f t="shared" si="3"/>
@@ -13105,7 +13114,7 @@
     <row r="86" spans="1:65">
       <c r="A86" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B86" t="str">
         <f t="shared" si="3"/>
@@ -13184,7 +13193,7 @@
     <row r="87" spans="1:65">
       <c r="A87" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B87" t="str">
         <f t="shared" si="3"/>
@@ -13263,7 +13272,7 @@
     <row r="88" spans="1:65">
       <c r="A88" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B88" t="str">
         <f t="shared" si="3"/>
@@ -13342,7 +13351,7 @@
     <row r="89" spans="1:65">
       <c r="A89" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B89" t="str">
         <f t="shared" si="3"/>
@@ -13421,7 +13430,7 @@
     <row r="90" spans="1:65">
       <c r="A90" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B90" t="str">
         <f t="shared" si="3"/>
@@ -13500,7 +13509,7 @@
     <row r="91" spans="1:65">
       <c r="A91" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B91" t="str">
         <f t="shared" si="3"/>
@@ -13579,7 +13588,7 @@
     <row r="92" spans="1:65">
       <c r="A92" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B92" t="str">
         <f t="shared" si="3"/>
@@ -13658,7 +13667,7 @@
     <row r="93" spans="1:65">
       <c r="A93" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B93" t="str">
         <f t="shared" si="3"/>
@@ -13737,7 +13746,7 @@
     <row r="94" spans="1:65">
       <c r="A94" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B94" t="str">
         <f t="shared" si="3"/>
@@ -13816,7 +13825,7 @@
     <row r="95" spans="1:65">
       <c r="A95" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B95" t="str">
         <f t="shared" si="3"/>
@@ -13895,7 +13904,7 @@
     <row r="96" spans="1:65">
       <c r="A96" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B96" t="str">
         <f t="shared" si="3"/>
@@ -13974,7 +13983,7 @@
     <row r="97" spans="1:65">
       <c r="A97" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B97" t="str">
         <f t="shared" si="3"/>
@@ -14053,7 +14062,7 @@
     <row r="98" spans="1:65">
       <c r="A98" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B98" t="str">
         <f t="shared" si="3"/>
@@ -14132,7 +14141,7 @@
     <row r="99" spans="1:65">
       <c r="A99" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B99" t="str">
         <f t="shared" si="3"/>
@@ -14211,7 +14220,7 @@
     <row r="100" spans="1:65">
       <c r="A100" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B100" t="str">
         <f t="shared" si="3"/>
@@ -14292,7 +14301,7 @@
     <row r="101" spans="1:65">
       <c r="A101" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B101" t="str">
         <f t="shared" si="3"/>
@@ -14371,7 +14380,7 @@
     <row r="102" spans="1:65">
       <c r="A102" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B102" t="str">
         <f t="shared" si="3"/>
@@ -14450,7 +14459,7 @@
     <row r="103" spans="1:65">
       <c r="A103" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B103" t="str">
         <f t="shared" si="3"/>
@@ -14529,7 +14538,7 @@
     <row r="104" spans="1:65">
       <c r="A104" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B104" t="str">
         <f t="shared" si="3"/>
@@ -14608,7 +14617,7 @@
     <row r="105" spans="1:65">
       <c r="A105" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B105" t="str">
         <f t="shared" si="3"/>
@@ -14687,7 +14696,7 @@
     <row r="106" spans="1:65">
       <c r="A106" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B106" t="str">
         <f t="shared" si="3"/>
@@ -14768,7 +14777,7 @@
     <row r="107" spans="1:65">
       <c r="A107" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B107" t="str">
         <f t="shared" si="3"/>
@@ -14849,7 +14858,7 @@
     <row r="108" spans="1:65">
       <c r="A108" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B108" t="str">
         <f t="shared" si="3"/>
@@ -14928,7 +14937,7 @@
     <row r="109" spans="1:65">
       <c r="A109" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B109" t="str">
         <f t="shared" si="3"/>
@@ -15007,7 +15016,7 @@
     <row r="110" spans="1:65">
       <c r="A110" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B110" t="str">
         <f t="shared" si="3"/>
@@ -15086,7 +15095,7 @@
     <row r="111" spans="1:65">
       <c r="A111" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B111" t="str">
         <f t="shared" si="3"/>
@@ -15165,7 +15174,7 @@
     <row r="112" spans="1:65">
       <c r="A112" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B112" t="str">
         <f t="shared" si="3"/>
@@ -15246,7 +15255,7 @@
     <row r="113" spans="1:65">
       <c r="A113" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B113" t="str">
         <f t="shared" si="3"/>
@@ -15325,7 +15334,7 @@
     <row r="114" spans="1:65">
       <c r="A114" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B114" t="str">
         <f t="shared" si="3"/>
@@ -15404,7 +15413,7 @@
     <row r="115" spans="1:65">
       <c r="A115" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B115" t="str">
         <f t="shared" si="3"/>
@@ -15483,7 +15492,7 @@
     <row r="116" spans="1:65">
       <c r="A116" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B116" t="str">
         <f t="shared" si="3"/>
@@ -15562,7 +15571,7 @@
     <row r="117" spans="1:65">
       <c r="A117" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B117" t="str">
         <f t="shared" si="3"/>
@@ -15641,7 +15650,7 @@
     <row r="118" spans="1:65">
       <c r="A118" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B118" t="str">
         <f t="shared" si="3"/>
@@ -15720,7 +15729,7 @@
     <row r="119" spans="1:65">
       <c r="A119" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B119" t="str">
         <f t="shared" si="3"/>
@@ -15799,7 +15808,7 @@
     <row r="120" spans="1:65">
       <c r="A120" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B120" t="str">
         <f t="shared" si="3"/>
@@ -15878,7 +15887,7 @@
     <row r="121" spans="1:65">
       <c r="A121" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B121" t="str">
         <f t="shared" si="3"/>
@@ -15957,7 +15966,7 @@
     <row r="122" spans="1:65">
       <c r="A122" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B122" t="str">
         <f t="shared" si="3"/>
@@ -16036,7 +16045,7 @@
     <row r="123" spans="1:65">
       <c r="A123" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B123" t="str">
         <f t="shared" si="3"/>
@@ -16115,7 +16124,7 @@
     <row r="124" spans="1:65">
       <c r="A124" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B124" t="str">
         <f t="shared" si="3"/>
@@ -16196,7 +16205,7 @@
     <row r="125" spans="1:65">
       <c r="A125" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B125" t="str">
         <f t="shared" si="3"/>
@@ -16277,7 +16286,7 @@
     <row r="126" spans="1:65">
       <c r="A126" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B126" t="str">
         <f t="shared" si="3"/>
@@ -16356,7 +16365,7 @@
     <row r="127" spans="1:65">
       <c r="A127" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B127" t="str">
         <f t="shared" si="3"/>
@@ -16435,7 +16444,7 @@
     <row r="128" spans="1:65">
       <c r="A128" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B128" t="str">
         <f t="shared" si="3"/>
@@ -16514,7 +16523,7 @@
     <row r="129" spans="1:65">
       <c r="A129" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B129" t="str">
         <f t="shared" si="3"/>
@@ -16593,7 +16602,7 @@
     <row r="130" spans="1:65">
       <c r="A130" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B130" t="str">
         <f t="shared" si="3"/>
@@ -16672,7 +16681,7 @@
     <row r="131" spans="1:65">
       <c r="A131" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B131" t="str">
         <f t="shared" si="3"/>
@@ -16754,7 +16763,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B132" t="str">
         <f t="shared" ref="B132:B168" si="5">TEXT($C132, "HH:mm")</f>
@@ -16833,7 +16842,7 @@
     <row r="133" spans="1:65">
       <c r="A133" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B133" t="str">
         <f t="shared" si="5"/>
@@ -16912,7 +16921,7 @@
     <row r="134" spans="1:65">
       <c r="A134" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B134" t="str">
         <f t="shared" si="5"/>
@@ -16991,7 +17000,7 @@
     <row r="135" spans="1:65">
       <c r="A135" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B135" t="str">
         <f t="shared" si="5"/>
@@ -17070,7 +17079,7 @@
     <row r="136" spans="1:65">
       <c r="A136" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B136" t="str">
         <f t="shared" si="5"/>
@@ -17151,7 +17160,7 @@
     <row r="137" spans="1:65">
       <c r="A137" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B137" t="str">
         <f t="shared" si="5"/>
@@ -17232,7 +17241,7 @@
     <row r="138" spans="1:65">
       <c r="A138" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B138" t="str">
         <f t="shared" si="5"/>
@@ -17311,7 +17320,7 @@
     <row r="139" spans="1:65">
       <c r="A139" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B139" t="str">
         <f t="shared" si="5"/>
@@ -17390,7 +17399,7 @@
     <row r="140" spans="1:65">
       <c r="A140" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B140" t="str">
         <f t="shared" si="5"/>
@@ -17469,7 +17478,7 @@
     <row r="141" spans="1:65">
       <c r="A141" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B141" t="str">
         <f t="shared" si="5"/>
@@ -17548,7 +17557,7 @@
     <row r="142" spans="1:65">
       <c r="A142" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B142" t="str">
         <f t="shared" si="5"/>
@@ -17627,7 +17636,7 @@
     <row r="143" spans="1:65">
       <c r="A143" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B143" t="str">
         <f t="shared" si="5"/>
@@ -17706,7 +17715,7 @@
     <row r="144" spans="1:65">
       <c r="A144" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B144" t="str">
         <f t="shared" si="5"/>
@@ -17785,7 +17794,7 @@
     <row r="145" spans="1:65">
       <c r="A145" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B145" t="str">
         <f t="shared" si="5"/>
@@ -17864,7 +17873,7 @@
     <row r="146" spans="1:65">
       <c r="A146" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B146" t="str">
         <f t="shared" si="5"/>
@@ -17943,7 +17952,7 @@
     <row r="147" spans="1:65">
       <c r="A147" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B147" t="str">
         <f t="shared" si="5"/>
@@ -18022,7 +18031,7 @@
     <row r="148" spans="1:65">
       <c r="A148" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B148" t="str">
         <f t="shared" si="5"/>
@@ -18103,7 +18112,7 @@
     <row r="149" spans="1:65">
       <c r="A149" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B149" t="str">
         <f t="shared" si="5"/>
@@ -18182,7 +18191,7 @@
     <row r="150" spans="1:65">
       <c r="A150" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B150" t="str">
         <f t="shared" si="5"/>
@@ -18261,7 +18270,7 @@
     <row r="151" spans="1:65">
       <c r="A151" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B151" t="str">
         <f t="shared" si="5"/>
@@ -18340,7 +18349,7 @@
     <row r="152" spans="1:65">
       <c r="A152" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B152" t="str">
         <f t="shared" si="5"/>
@@ -18419,7 +18428,7 @@
     <row r="153" spans="1:65">
       <c r="A153" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B153" t="str">
         <f t="shared" si="5"/>
@@ -18498,7 +18507,7 @@
     <row r="154" spans="1:65">
       <c r="A154" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B154" t="str">
         <f t="shared" si="5"/>
@@ -18577,7 +18586,7 @@
     <row r="155" spans="1:65">
       <c r="A155" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B155" t="str">
         <f t="shared" si="5"/>
@@ -18656,7 +18665,7 @@
     <row r="156" spans="1:65">
       <c r="A156" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B156" t="str">
         <f t="shared" si="5"/>
@@ -18735,7 +18744,7 @@
     <row r="157" spans="1:65">
       <c r="A157" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B157" t="str">
         <f t="shared" si="5"/>
@@ -18814,7 +18823,7 @@
     <row r="158" spans="1:65">
       <c r="A158" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B158" t="str">
         <f t="shared" si="5"/>
@@ -18893,7 +18902,7 @@
     <row r="159" spans="1:65">
       <c r="A159" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B159" t="str">
         <f t="shared" si="5"/>
@@ -18972,7 +18981,7 @@
     <row r="160" spans="1:65">
       <c r="A160" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B160" t="str">
         <f t="shared" si="5"/>
@@ -19051,7 +19060,7 @@
     <row r="161" spans="1:65">
       <c r="A161" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B161" t="str">
         <f t="shared" si="5"/>
@@ -19130,7 +19139,7 @@
     <row r="162" spans="1:65">
       <c r="A162" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B162" t="str">
         <f t="shared" si="5"/>
@@ -19209,7 +19218,7 @@
     <row r="163" spans="1:65">
       <c r="A163" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B163" t="str">
         <f t="shared" si="5"/>
@@ -19288,7 +19297,7 @@
     <row r="164" spans="1:65">
       <c r="A164" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B164" t="str">
         <f t="shared" si="5"/>
@@ -19367,7 +19376,7 @@
     <row r="165" spans="1:65">
       <c r="A165" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B165" t="str">
         <f t="shared" si="5"/>
@@ -19446,7 +19455,7 @@
     <row r="166" spans="1:65">
       <c r="A166" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B166" t="str">
         <f t="shared" si="5"/>
@@ -19527,7 +19536,7 @@
     <row r="167" spans="1:65">
       <c r="A167" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B167" t="str">
         <f t="shared" si="5"/>
@@ -19606,7 +19615,7 @@
     <row r="168" spans="1:65">
       <c r="A168" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B168" t="str">
         <f t="shared" si="5"/>
@@ -19688,7 +19697,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B169" t="str">
         <f>TEXT($C169, "HH:mm")</f>
@@ -19770,7 +19779,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B170" t="str">
         <f t="shared" ref="B170:B233" si="7">TEXT($C170, "HH:mm")</f>
@@ -19849,7 +19858,7 @@
     <row r="171" spans="1:65">
       <c r="A171" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B171" t="str">
         <f t="shared" si="7"/>
@@ -19928,7 +19937,7 @@
     <row r="172" spans="1:65">
       <c r="A172" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B172" t="str">
         <f t="shared" si="7"/>
@@ -20009,7 +20018,7 @@
     <row r="173" spans="1:65">
       <c r="A173" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B173" t="str">
         <f t="shared" si="7"/>
@@ -20088,7 +20097,7 @@
     <row r="174" spans="1:65">
       <c r="A174" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B174" t="str">
         <f t="shared" si="7"/>
@@ -20167,7 +20176,7 @@
     <row r="175" spans="1:65">
       <c r="A175" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B175" t="str">
         <f t="shared" si="7"/>
@@ -20246,7 +20255,7 @@
     <row r="176" spans="1:65">
       <c r="A176" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B176" t="str">
         <f t="shared" si="7"/>
@@ -20325,7 +20334,7 @@
     <row r="177" spans="1:65">
       <c r="A177" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B177" t="str">
         <f t="shared" si="7"/>
@@ -20404,7 +20413,7 @@
     <row r="178" spans="1:65">
       <c r="A178" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B178" t="str">
         <f t="shared" si="7"/>
@@ -20485,7 +20494,7 @@
     <row r="179" spans="1:65">
       <c r="A179" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B179" t="str">
         <f t="shared" si="7"/>
@@ -20564,7 +20573,7 @@
     <row r="180" spans="1:65">
       <c r="A180" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B180" t="str">
         <f t="shared" si="7"/>
@@ -20643,7 +20652,7 @@
     <row r="181" spans="1:65">
       <c r="A181" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B181" t="str">
         <f t="shared" si="7"/>
@@ -20724,7 +20733,7 @@
     <row r="182" spans="1:65">
       <c r="A182" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B182" t="str">
         <f t="shared" si="7"/>
@@ -20805,7 +20814,7 @@
     <row r="183" spans="1:65">
       <c r="A183" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B183" t="str">
         <f t="shared" si="7"/>
@@ -20886,7 +20895,7 @@
     <row r="184" spans="1:65">
       <c r="A184" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B184" t="str">
         <f t="shared" si="7"/>
@@ -20969,7 +20978,7 @@
     <row r="185" spans="1:65">
       <c r="A185" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B185" t="str">
         <f t="shared" si="7"/>
@@ -21050,7 +21059,7 @@
     <row r="186" spans="1:65">
       <c r="A186" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B186" t="str">
         <f t="shared" si="7"/>
@@ -21131,7 +21140,7 @@
     <row r="187" spans="1:65">
       <c r="A187" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B187" t="str">
         <f t="shared" si="7"/>
@@ -21212,7 +21221,7 @@
     <row r="188" spans="1:65">
       <c r="A188" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B188" t="str">
         <f t="shared" si="7"/>
@@ -21293,7 +21302,7 @@
     <row r="189" spans="1:65">
       <c r="A189" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B189" t="str">
         <f t="shared" si="7"/>
@@ -21374,7 +21383,7 @@
     <row r="190" spans="1:65">
       <c r="A190" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B190" t="str">
         <f t="shared" si="7"/>
@@ -21457,7 +21466,7 @@
     <row r="191" spans="1:65">
       <c r="A191" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B191" t="str">
         <f t="shared" si="7"/>
@@ -21540,7 +21549,7 @@
     <row r="192" spans="1:65">
       <c r="A192" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B192" t="str">
         <f t="shared" si="7"/>
@@ -21623,7 +21632,7 @@
     <row r="193" spans="1:65">
       <c r="A193" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B193" t="str">
         <f t="shared" si="7"/>
@@ -21706,7 +21715,7 @@
     <row r="194" spans="1:65">
       <c r="A194" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B194" t="str">
         <f t="shared" si="7"/>
@@ -21787,7 +21796,7 @@
     <row r="195" spans="1:65">
       <c r="A195" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B195" t="str">
         <f t="shared" si="7"/>
@@ -21868,7 +21877,7 @@
     <row r="196" spans="1:65">
       <c r="A196" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B196" t="str">
         <f t="shared" si="7"/>
@@ -21951,7 +21960,7 @@
     <row r="197" spans="1:65">
       <c r="A197" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B197" t="str">
         <f t="shared" si="7"/>
@@ -22030,7 +22039,7 @@
     <row r="198" spans="1:65">
       <c r="A198" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B198" t="str">
         <f t="shared" si="7"/>
@@ -22109,7 +22118,7 @@
     <row r="199" spans="1:65">
       <c r="A199" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B199" t="str">
         <f t="shared" si="7"/>
@@ -22188,7 +22197,7 @@
     <row r="200" spans="1:65">
       <c r="A200" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B200" t="str">
         <f t="shared" si="7"/>
@@ -22267,7 +22276,7 @@
     <row r="201" spans="1:65">
       <c r="A201" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B201" t="str">
         <f t="shared" si="7"/>
@@ -22346,7 +22355,7 @@
     <row r="202" spans="1:65">
       <c r="A202" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B202" t="str">
         <f t="shared" si="7"/>
@@ -22427,7 +22436,7 @@
     <row r="203" spans="1:65">
       <c r="A203" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B203" t="str">
         <f t="shared" si="7"/>
@@ -22506,7 +22515,7 @@
     <row r="204" spans="1:65">
       <c r="A204" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B204" t="str">
         <f t="shared" si="7"/>
@@ -22585,7 +22594,7 @@
     <row r="205" spans="1:65">
       <c r="A205" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B205" t="str">
         <f t="shared" si="7"/>
@@ -22664,7 +22673,7 @@
     <row r="206" spans="1:65">
       <c r="A206" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B206" t="str">
         <f t="shared" si="7"/>
@@ -22743,7 +22752,7 @@
     <row r="207" spans="1:65">
       <c r="A207" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B207" t="str">
         <f t="shared" si="7"/>
@@ -22822,7 +22831,7 @@
     <row r="208" spans="1:65">
       <c r="A208" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B208" t="str">
         <f t="shared" si="7"/>
@@ -22903,7 +22912,7 @@
     <row r="209" spans="1:65">
       <c r="A209" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B209" t="str">
         <f t="shared" si="7"/>
@@ -22982,7 +22991,7 @@
     <row r="210" spans="1:65">
       <c r="A210" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B210" t="str">
         <f t="shared" si="7"/>
@@ -23061,7 +23070,7 @@
     <row r="211" spans="1:65">
       <c r="A211" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B211" t="str">
         <f t="shared" si="7"/>
@@ -23142,7 +23151,7 @@
     <row r="212" spans="1:65">
       <c r="A212" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B212" t="str">
         <f t="shared" si="7"/>
@@ -23221,7 +23230,7 @@
     <row r="213" spans="1:65">
       <c r="A213" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B213" t="str">
         <f t="shared" si="7"/>
@@ -23300,7 +23309,7 @@
     <row r="214" spans="1:65">
       <c r="A214" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B214" t="str">
         <f t="shared" si="7"/>
@@ -23379,7 +23388,7 @@
     <row r="215" spans="1:65">
       <c r="A215" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B215" t="str">
         <f t="shared" si="7"/>
@@ -23458,7 +23467,7 @@
     <row r="216" spans="1:65">
       <c r="A216" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B216" t="str">
         <f t="shared" si="7"/>
@@ -23537,7 +23546,7 @@
     <row r="217" spans="1:65">
       <c r="A217" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B217" t="str">
         <f t="shared" si="7"/>
@@ -23616,7 +23625,7 @@
     <row r="218" spans="1:65">
       <c r="A218" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B218" t="str">
         <f t="shared" si="7"/>
@@ -23695,7 +23704,7 @@
     <row r="219" spans="1:65">
       <c r="A219" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B219" t="str">
         <f t="shared" si="7"/>
@@ -23774,7 +23783,7 @@
     <row r="220" spans="1:65">
       <c r="A220" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B220" t="str">
         <f t="shared" si="7"/>
@@ -23855,7 +23864,7 @@
     <row r="221" spans="1:65">
       <c r="A221" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B221" t="str">
         <f t="shared" si="7"/>
@@ -23934,7 +23943,7 @@
     <row r="222" spans="1:65">
       <c r="A222" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B222" t="str">
         <f t="shared" si="7"/>
@@ -24013,7 +24022,7 @@
     <row r="223" spans="1:65">
       <c r="A223" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B223" t="str">
         <f t="shared" si="7"/>
@@ -24092,7 +24101,7 @@
     <row r="224" spans="1:65">
       <c r="A224" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B224" t="str">
         <f t="shared" si="7"/>
@@ -24171,7 +24180,7 @@
     <row r="225" spans="1:65">
       <c r="A225" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B225" t="str">
         <f t="shared" si="7"/>
@@ -24250,7 +24259,7 @@
     <row r="226" spans="1:65">
       <c r="A226" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B226" t="str">
         <f t="shared" si="7"/>
@@ -24329,7 +24338,7 @@
     <row r="227" spans="1:65">
       <c r="A227" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B227" t="str">
         <f t="shared" si="7"/>
@@ -24408,7 +24417,7 @@
     <row r="228" spans="1:65">
       <c r="A228" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B228" t="str">
         <f t="shared" si="7"/>
@@ -24487,7 +24496,7 @@
     <row r="229" spans="1:65">
       <c r="A229" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B229" t="str">
         <f t="shared" si="7"/>
@@ -24566,7 +24575,7 @@
     <row r="230" spans="1:65">
       <c r="A230" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B230" t="str">
         <f t="shared" si="7"/>
@@ -24645,7 +24654,7 @@
     <row r="231" spans="1:65">
       <c r="A231" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B231" t="str">
         <f t="shared" si="7"/>
@@ -24724,7 +24733,7 @@
     <row r="232" spans="1:65">
       <c r="A232" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B232" t="str">
         <f t="shared" si="7"/>
@@ -24803,7 +24812,7 @@
     <row r="233" spans="1:65">
       <c r="A233" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B233" t="str">
         <f t="shared" si="7"/>
@@ -24885,7 +24894,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B234" t="str">
         <f t="shared" ref="B234:B291" si="9">TEXT($C234, "HH:mm")</f>
@@ -24964,7 +24973,7 @@
     <row r="235" spans="1:65">
       <c r="A235" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B235" t="str">
         <f t="shared" si="9"/>
@@ -25043,7 +25052,7 @@
     <row r="236" spans="1:65">
       <c r="A236" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B236" t="str">
         <f t="shared" si="9"/>
@@ -25122,7 +25131,7 @@
     <row r="237" spans="1:65">
       <c r="A237" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B237" t="str">
         <f t="shared" si="9"/>
@@ -25201,7 +25210,7 @@
     <row r="238" spans="1:65">
       <c r="A238" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B238" t="str">
         <f t="shared" si="9"/>
@@ -25280,7 +25289,7 @@
     <row r="239" spans="1:65">
       <c r="A239" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B239" t="str">
         <f t="shared" si="9"/>
@@ -25359,7 +25368,7 @@
     <row r="240" spans="1:65">
       <c r="A240" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B240" t="str">
         <f t="shared" si="9"/>
@@ -25438,7 +25447,7 @@
     <row r="241" spans="1:65">
       <c r="A241" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B241" t="str">
         <f t="shared" si="9"/>
@@ -25517,7 +25526,7 @@
     <row r="242" spans="1:65">
       <c r="A242" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B242" t="str">
         <f t="shared" si="9"/>
@@ -25596,7 +25605,7 @@
     <row r="243" spans="1:65">
       <c r="A243" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B243" t="str">
         <f t="shared" si="9"/>
@@ -25675,7 +25684,7 @@
     <row r="244" spans="1:65">
       <c r="A244" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B244" t="str">
         <f t="shared" si="9"/>
@@ -25754,7 +25763,7 @@
     <row r="245" spans="1:65">
       <c r="A245" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B245" t="str">
         <f t="shared" si="9"/>
@@ -25833,7 +25842,7 @@
     <row r="246" spans="1:65">
       <c r="A246" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B246" t="str">
         <f t="shared" si="9"/>
@@ -25912,7 +25921,7 @@
     <row r="247" spans="1:65">
       <c r="A247" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B247" t="str">
         <f t="shared" si="9"/>
@@ -25991,7 +26000,7 @@
     <row r="248" spans="1:65">
       <c r="A248" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B248" t="str">
         <f t="shared" si="9"/>
@@ -26070,7 +26079,7 @@
     <row r="249" spans="1:65">
       <c r="A249" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B249" t="str">
         <f t="shared" si="9"/>
@@ -26149,7 +26158,7 @@
     <row r="250" spans="1:65">
       <c r="A250" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B250" t="str">
         <f t="shared" si="9"/>
@@ -26228,7 +26237,7 @@
     <row r="251" spans="1:65">
       <c r="A251" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B251" t="str">
         <f t="shared" si="9"/>
@@ -26307,7 +26316,7 @@
     <row r="252" spans="1:65">
       <c r="A252" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B252" t="str">
         <f t="shared" si="9"/>
@@ -26386,7 +26395,7 @@
     <row r="253" spans="1:65">
       <c r="A253" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B253" t="str">
         <f t="shared" si="9"/>
@@ -26465,7 +26474,7 @@
     <row r="254" spans="1:65">
       <c r="A254" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B254" t="str">
         <f t="shared" si="9"/>
@@ -26544,7 +26553,7 @@
     <row r="255" spans="1:65">
       <c r="A255" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B255" t="str">
         <f t="shared" si="9"/>
@@ -26623,7 +26632,7 @@
     <row r="256" spans="1:65">
       <c r="A256" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B256" t="str">
         <f t="shared" si="9"/>
@@ -26702,7 +26711,7 @@
     <row r="257" spans="1:65">
       <c r="A257" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B257" t="str">
         <f t="shared" si="9"/>
@@ -26781,7 +26790,7 @@
     <row r="258" spans="1:65">
       <c r="A258" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B258" t="str">
         <f t="shared" si="9"/>
@@ -26860,7 +26869,7 @@
     <row r="259" spans="1:65">
       <c r="A259" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B259" t="str">
         <f t="shared" si="9"/>
@@ -26939,7 +26948,7 @@
     <row r="260" spans="1:65">
       <c r="A260" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B260" t="str">
         <f t="shared" si="9"/>
@@ -27018,7 +27027,7 @@
     <row r="261" spans="1:65">
       <c r="A261" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B261" t="str">
         <f t="shared" si="9"/>
@@ -27097,7 +27106,7 @@
     <row r="262" spans="1:65">
       <c r="A262" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B262" t="str">
         <f t="shared" si="9"/>
@@ -27176,7 +27185,7 @@
     <row r="263" spans="1:65">
       <c r="A263" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B263" t="str">
         <f t="shared" si="9"/>
@@ -27255,7 +27264,7 @@
     <row r="264" spans="1:65">
       <c r="A264" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B264" t="str">
         <f t="shared" si="9"/>
@@ -27334,7 +27343,7 @@
     <row r="265" spans="1:65">
       <c r="A265" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B265" t="str">
         <f t="shared" si="9"/>
@@ -27413,7 +27422,7 @@
     <row r="266" spans="1:65">
       <c r="A266" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B266" t="str">
         <f t="shared" si="9"/>
@@ -27492,7 +27501,7 @@
     <row r="267" spans="1:65">
       <c r="A267" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B267" t="str">
         <f t="shared" si="9"/>
@@ -27571,7 +27580,7 @@
     <row r="268" spans="1:65">
       <c r="A268" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B268" t="str">
         <f t="shared" si="9"/>
@@ -27650,7 +27659,7 @@
     <row r="269" spans="1:65">
       <c r="A269" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B269" t="str">
         <f t="shared" si="9"/>
@@ -27729,7 +27738,7 @@
     <row r="270" spans="1:65">
       <c r="A270" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B270" t="str">
         <f t="shared" si="9"/>
@@ -27808,7 +27817,7 @@
     <row r="271" spans="1:65">
       <c r="A271" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B271" t="str">
         <f t="shared" si="9"/>
@@ -27887,7 +27896,7 @@
     <row r="272" spans="1:65">
       <c r="A272" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B272" t="str">
         <f t="shared" si="9"/>
@@ -27966,7 +27975,7 @@
     <row r="273" spans="1:65">
       <c r="A273" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B273" t="str">
         <f t="shared" si="9"/>
@@ -28045,7 +28054,7 @@
     <row r="274" spans="1:65">
       <c r="A274" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B274" t="str">
         <f t="shared" si="9"/>
@@ -28124,7 +28133,7 @@
     <row r="275" spans="1:65">
       <c r="A275" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B275" t="str">
         <f t="shared" si="9"/>
@@ -28203,7 +28212,7 @@
     <row r="276" spans="1:65">
       <c r="A276" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B276" t="str">
         <f t="shared" si="9"/>
@@ -28282,7 +28291,7 @@
     <row r="277" spans="1:65">
       <c r="A277" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B277" t="str">
         <f t="shared" si="9"/>
@@ -28361,7 +28370,7 @@
     <row r="278" spans="1:65">
       <c r="A278" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B278" t="str">
         <f t="shared" si="9"/>
@@ -28440,7 +28449,7 @@
     <row r="279" spans="1:65">
       <c r="A279" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B279" t="str">
         <f t="shared" si="9"/>
@@ -28519,7 +28528,7 @@
     <row r="280" spans="1:65">
       <c r="A280" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B280" t="str">
         <f t="shared" si="9"/>
@@ -28598,7 +28607,7 @@
     <row r="281" spans="1:65">
       <c r="A281" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B281" t="str">
         <f t="shared" si="9"/>
@@ -28677,7 +28686,7 @@
     <row r="282" spans="1:65">
       <c r="A282" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B282" t="str">
         <f t="shared" si="9"/>
@@ -28756,7 +28765,7 @@
     <row r="283" spans="1:65">
       <c r="A283" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B283" t="str">
         <f t="shared" si="9"/>
@@ -28835,7 +28844,7 @@
     <row r="284" spans="1:65">
       <c r="A284" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B284" t="str">
         <f t="shared" si="9"/>
@@ -28914,7 +28923,7 @@
     <row r="285" spans="1:65">
       <c r="A285" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B285" t="str">
         <f t="shared" si="9"/>
@@ -28993,7 +29002,7 @@
     <row r="286" spans="1:65">
       <c r="A286" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B286" t="str">
         <f t="shared" si="9"/>
@@ -29072,7 +29081,7 @@
     <row r="287" spans="1:65">
       <c r="A287" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B287" t="str">
         <f t="shared" si="9"/>
@@ -29151,7 +29160,7 @@
     <row r="288" spans="1:65">
       <c r="A288" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B288" t="str">
         <f t="shared" si="9"/>
@@ -29230,7 +29239,7 @@
     <row r="289" spans="1:65">
       <c r="A289" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B289" t="str">
         <f t="shared" si="9"/>
@@ -29309,7 +29318,7 @@
     <row r="290" spans="1:65">
       <c r="A290" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B290" t="str">
         <f t="shared" si="9"/>
@@ -29388,7 +29397,7 @@
     <row r="291" spans="1:65">
       <c r="A291" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:10</v>
+        <v>01:15</v>
       </c>
       <c r="B291" t="str">
         <f t="shared" si="9"/>

--- a/Vite-Vercel開発.xlsx
+++ b/Vite-Vercel開発.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2c67ec30e06f060f/work/GitHub/work-time-tracker/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{1928CA11-C4AD-40E9-B1C5-143667E830EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DCDB1AAB-A003-4583-BAA9-1606A15D15FB}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{1928CA11-C4AD-40E9-B1C5-143667E830EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9AC47CEF-5545-4C30-AAEB-10DA74AC6478}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1539" uniqueCount="917">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1540" uniqueCount="918">
   <si>
     <t>npm install -g vercel</t>
     <phoneticPr fontId="1"/>
@@ -5346,6 +5346,10 @@
   </si>
   <si>
     <t>Found 68 errors in 18 files.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Found 67 errors in 17 files.</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -6118,7 +6122,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{083174DA-A42C-4F9C-978E-61AEAAD9DDFF}">
-  <dimension ref="B2:D21"/>
+  <dimension ref="B2:D22"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
@@ -6231,6 +6235,11 @@
     <row r="21" spans="3:3">
       <c r="C21" t="s">
         <v>916</v>
+      </c>
+    </row>
+    <row r="22" spans="3:3">
+      <c r="C22" t="s">
+        <v>917</v>
       </c>
     </row>
   </sheetData>
@@ -6397,7 +6406,7 @@
       MOD(NOW(),1),
       TIME(0,5,0)
     ),"HH:mm")</f>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B2" s="19"/>
       <c r="D2" s="1">
@@ -6408,7 +6417,7 @@
     <row r="3" spans="1:65">
       <c r="A3" s="19" t="str">
         <f ca="1">TEXT(NOW(),"HH:mm")</f>
-        <v>01:16</v>
+        <v>01:21</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="17" t="s">
@@ -6607,7 +6616,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B4" t="str">
         <f t="shared" ref="B4:B67" si="1">TEXT($C4, "HH:mm")</f>
@@ -6686,7 +6695,7 @@
     <row r="5" spans="1:65">
       <c r="A5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B5" t="str">
         <f t="shared" si="1"/>
@@ -6765,7 +6774,7 @@
     <row r="6" spans="1:65">
       <c r="A6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B6" t="str">
         <f t="shared" si="1"/>
@@ -6844,7 +6853,7 @@
     <row r="7" spans="1:65">
       <c r="A7" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B7" t="str">
         <f t="shared" si="1"/>
@@ -6923,7 +6932,7 @@
     <row r="8" spans="1:65">
       <c r="A8" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B8" t="str">
         <f t="shared" si="1"/>
@@ -7002,7 +7011,7 @@
     <row r="9" spans="1:65">
       <c r="A9" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B9" t="str">
         <f t="shared" si="1"/>
@@ -7081,7 +7090,7 @@
     <row r="10" spans="1:65">
       <c r="A10" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B10" t="str">
         <f t="shared" si="1"/>
@@ -7160,7 +7169,7 @@
     <row r="11" spans="1:65">
       <c r="A11" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B11" t="str">
         <f t="shared" si="1"/>
@@ -7239,7 +7248,7 @@
     <row r="12" spans="1:65">
       <c r="A12" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B12" t="str">
         <f t="shared" si="1"/>
@@ -7318,7 +7327,7 @@
     <row r="13" spans="1:65">
       <c r="A13" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B13" t="str">
         <f t="shared" si="1"/>
@@ -7397,7 +7406,7 @@
     <row r="14" spans="1:65">
       <c r="A14" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B14" t="str">
         <f t="shared" si="1"/>
@@ -7476,7 +7485,7 @@
     <row r="15" spans="1:65">
       <c r="A15" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B15" t="str">
         <f t="shared" si="1"/>
@@ -7555,7 +7564,7 @@
     <row r="16" spans="1:65">
       <c r="A16" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B16" t="str">
         <f t="shared" si="1"/>
@@ -7634,7 +7643,7 @@
     <row r="17" spans="1:65">
       <c r="A17" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B17" t="str">
         <f t="shared" si="1"/>
@@ -7713,7 +7722,7 @@
     <row r="18" spans="1:65">
       <c r="A18" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B18" t="str">
         <f t="shared" si="1"/>
@@ -7792,7 +7801,7 @@
     <row r="19" spans="1:65">
       <c r="A19" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B19" t="str">
         <f t="shared" si="1"/>
@@ -7871,7 +7880,7 @@
     <row r="20" spans="1:65">
       <c r="A20" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B20" t="str">
         <f t="shared" si="1"/>
@@ -7950,7 +7959,7 @@
     <row r="21" spans="1:65">
       <c r="A21" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B21" t="str">
         <f t="shared" si="1"/>
@@ -8029,7 +8038,7 @@
     <row r="22" spans="1:65">
       <c r="A22" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B22" t="str">
         <f t="shared" si="1"/>
@@ -8108,7 +8117,7 @@
     <row r="23" spans="1:65">
       <c r="A23" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B23" t="str">
         <f t="shared" si="1"/>
@@ -8187,7 +8196,7 @@
     <row r="24" spans="1:65">
       <c r="A24" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B24" t="str">
         <f t="shared" si="1"/>
@@ -8266,7 +8275,7 @@
     <row r="25" spans="1:65">
       <c r="A25" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B25" t="str">
         <f t="shared" si="1"/>
@@ -8345,7 +8354,7 @@
     <row r="26" spans="1:65">
       <c r="A26" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B26" t="str">
         <f t="shared" si="1"/>
@@ -8424,7 +8433,7 @@
     <row r="27" spans="1:65">
       <c r="A27" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B27" t="str">
         <f t="shared" si="1"/>
@@ -8503,7 +8512,7 @@
     <row r="28" spans="1:65">
       <c r="A28" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B28" t="str">
         <f t="shared" si="1"/>
@@ -8584,7 +8593,7 @@
     <row r="29" spans="1:65">
       <c r="A29" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B29" t="str">
         <f t="shared" si="1"/>
@@ -8665,7 +8674,7 @@
     <row r="30" spans="1:65">
       <c r="A30" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B30" t="str">
         <f t="shared" si="1"/>
@@ -8746,7 +8755,7 @@
     <row r="31" spans="1:65">
       <c r="A31" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B31" t="str">
         <f t="shared" si="1"/>
@@ -8825,7 +8834,7 @@
     <row r="32" spans="1:65">
       <c r="A32" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B32" t="str">
         <f t="shared" si="1"/>
@@ -8904,7 +8913,7 @@
     <row r="33" spans="1:65">
       <c r="A33" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B33" t="str">
         <f t="shared" si="1"/>
@@ -8983,7 +8992,7 @@
     <row r="34" spans="1:65">
       <c r="A34" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B34" t="str">
         <f t="shared" si="1"/>
@@ -9064,7 +9073,7 @@
     <row r="35" spans="1:65">
       <c r="A35" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B35" t="str">
         <f t="shared" si="1"/>
@@ -9145,7 +9154,7 @@
     <row r="36" spans="1:65">
       <c r="A36" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B36" t="str">
         <f t="shared" si="1"/>
@@ -9226,7 +9235,7 @@
     <row r="37" spans="1:65">
       <c r="A37" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B37" t="str">
         <f t="shared" si="1"/>
@@ -9305,7 +9314,7 @@
     <row r="38" spans="1:65">
       <c r="A38" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B38" t="str">
         <f t="shared" si="1"/>
@@ -9384,7 +9393,7 @@
     <row r="39" spans="1:65">
       <c r="A39" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B39" t="str">
         <f t="shared" si="1"/>
@@ -9463,7 +9472,7 @@
     <row r="40" spans="1:65">
       <c r="A40" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B40" t="str">
         <f t="shared" si="1"/>
@@ -9542,7 +9551,7 @@
     <row r="41" spans="1:65">
       <c r="A41" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B41" t="str">
         <f t="shared" si="1"/>
@@ -9621,7 +9630,7 @@
     <row r="42" spans="1:65">
       <c r="A42" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B42" t="str">
         <f t="shared" si="1"/>
@@ -9702,7 +9711,7 @@
     <row r="43" spans="1:65">
       <c r="A43" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B43" t="str">
         <f t="shared" si="1"/>
@@ -9783,7 +9792,7 @@
     <row r="44" spans="1:65">
       <c r="A44" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B44" t="str">
         <f t="shared" si="1"/>
@@ -9862,7 +9871,7 @@
     <row r="45" spans="1:65">
       <c r="A45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B45" t="str">
         <f t="shared" si="1"/>
@@ -9941,7 +9950,7 @@
     <row r="46" spans="1:65">
       <c r="A46" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B46" t="str">
         <f t="shared" si="1"/>
@@ -10020,7 +10029,7 @@
     <row r="47" spans="1:65">
       <c r="A47" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B47" t="str">
         <f t="shared" si="1"/>
@@ -10099,7 +10108,7 @@
     <row r="48" spans="1:65">
       <c r="A48" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B48" t="str">
         <f t="shared" si="1"/>
@@ -10178,7 +10187,7 @@
     <row r="49" spans="1:65">
       <c r="A49" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B49" t="str">
         <f t="shared" si="1"/>
@@ -10259,7 +10268,7 @@
     <row r="50" spans="1:65">
       <c r="A50" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B50" t="str">
         <f t="shared" si="1"/>
@@ -10340,7 +10349,7 @@
     <row r="51" spans="1:65">
       <c r="A51" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B51" t="str">
         <f t="shared" si="1"/>
@@ -10419,7 +10428,7 @@
     <row r="52" spans="1:65">
       <c r="A52" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B52" t="str">
         <f t="shared" si="1"/>
@@ -10498,7 +10507,7 @@
     <row r="53" spans="1:65">
       <c r="A53" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B53" t="str">
         <f t="shared" si="1"/>
@@ -10577,7 +10586,7 @@
     <row r="54" spans="1:65">
       <c r="A54" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B54" t="str">
         <f t="shared" si="1"/>
@@ -10656,7 +10665,7 @@
     <row r="55" spans="1:65">
       <c r="A55" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B55" t="str">
         <f t="shared" si="1"/>
@@ -10735,7 +10744,7 @@
     <row r="56" spans="1:65">
       <c r="A56" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B56" t="str">
         <f t="shared" si="1"/>
@@ -10816,7 +10825,7 @@
     <row r="57" spans="1:65">
       <c r="A57" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B57" t="str">
         <f t="shared" si="1"/>
@@ -10895,7 +10904,7 @@
     <row r="58" spans="1:65">
       <c r="A58" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B58" t="str">
         <f t="shared" si="1"/>
@@ -10976,7 +10985,7 @@
     <row r="59" spans="1:65">
       <c r="A59" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B59" t="str">
         <f t="shared" si="1"/>
@@ -11055,7 +11064,7 @@
     <row r="60" spans="1:65">
       <c r="A60" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B60" t="str">
         <f t="shared" si="1"/>
@@ -11134,7 +11143,7 @@
     <row r="61" spans="1:65">
       <c r="A61" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B61" t="str">
         <f t="shared" si="1"/>
@@ -11213,7 +11222,7 @@
     <row r="62" spans="1:65">
       <c r="A62" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B62" t="str">
         <f t="shared" si="1"/>
@@ -11292,7 +11301,7 @@
     <row r="63" spans="1:65">
       <c r="A63" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B63" t="str">
         <f t="shared" si="1"/>
@@ -11371,7 +11380,7 @@
     <row r="64" spans="1:65">
       <c r="A64" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B64" t="str">
         <f t="shared" si="1"/>
@@ -11452,7 +11461,7 @@
     <row r="65" spans="1:65">
       <c r="A65" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B65" t="str">
         <f t="shared" si="1"/>
@@ -11531,7 +11540,7 @@
     <row r="66" spans="1:65">
       <c r="A66" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B66" t="str">
         <f t="shared" si="1"/>
@@ -11610,7 +11619,7 @@
     <row r="67" spans="1:65">
       <c r="A67" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B67" t="str">
         <f t="shared" si="1"/>
@@ -11692,7 +11701,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B68" t="str">
         <f t="shared" ref="B68:B131" si="3">TEXT($C68, "HH:mm")</f>
@@ -11771,7 +11780,7 @@
     <row r="69" spans="1:65">
       <c r="A69" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B69" t="str">
         <f t="shared" si="3"/>
@@ -11850,7 +11859,7 @@
     <row r="70" spans="1:65">
       <c r="A70" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B70" t="str">
         <f t="shared" si="3"/>
@@ -11929,7 +11938,7 @@
     <row r="71" spans="1:65">
       <c r="A71" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B71" t="str">
         <f t="shared" si="3"/>
@@ -12008,7 +12017,7 @@
     <row r="72" spans="1:65">
       <c r="A72" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B72" t="str">
         <f t="shared" si="3"/>
@@ -12087,7 +12096,7 @@
     <row r="73" spans="1:65">
       <c r="A73" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B73" t="str">
         <f t="shared" si="3"/>
@@ -12166,7 +12175,7 @@
     <row r="74" spans="1:65">
       <c r="A74" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B74" t="str">
         <f t="shared" si="3"/>
@@ -12245,7 +12254,7 @@
     <row r="75" spans="1:65">
       <c r="A75" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B75" t="str">
         <f t="shared" si="3"/>
@@ -12324,7 +12333,7 @@
     <row r="76" spans="1:65">
       <c r="A76" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B76" t="str">
         <f t="shared" si="3"/>
@@ -12403,7 +12412,7 @@
     <row r="77" spans="1:65">
       <c r="A77" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B77" t="str">
         <f t="shared" si="3"/>
@@ -12482,7 +12491,7 @@
     <row r="78" spans="1:65">
       <c r="A78" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B78" t="str">
         <f t="shared" si="3"/>
@@ -12561,7 +12570,7 @@
     <row r="79" spans="1:65">
       <c r="A79" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B79" t="str">
         <f t="shared" si="3"/>
@@ -12640,7 +12649,7 @@
     <row r="80" spans="1:65">
       <c r="A80" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B80" t="str">
         <f t="shared" si="3"/>
@@ -12719,7 +12728,7 @@
     <row r="81" spans="1:65">
       <c r="A81" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B81" t="str">
         <f t="shared" si="3"/>
@@ -12798,7 +12807,7 @@
     <row r="82" spans="1:65">
       <c r="A82" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B82" t="str">
         <f t="shared" si="3"/>
@@ -12877,7 +12886,7 @@
     <row r="83" spans="1:65">
       <c r="A83" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B83" t="str">
         <f t="shared" si="3"/>
@@ -12956,7 +12965,7 @@
     <row r="84" spans="1:65">
       <c r="A84" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B84" t="str">
         <f t="shared" si="3"/>
@@ -13035,7 +13044,7 @@
     <row r="85" spans="1:65">
       <c r="A85" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B85" t="str">
         <f t="shared" si="3"/>
@@ -13114,7 +13123,7 @@
     <row r="86" spans="1:65">
       <c r="A86" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B86" t="str">
         <f t="shared" si="3"/>
@@ -13193,7 +13202,7 @@
     <row r="87" spans="1:65">
       <c r="A87" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B87" t="str">
         <f t="shared" si="3"/>
@@ -13272,7 +13281,7 @@
     <row r="88" spans="1:65">
       <c r="A88" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B88" t="str">
         <f t="shared" si="3"/>
@@ -13351,7 +13360,7 @@
     <row r="89" spans="1:65">
       <c r="A89" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B89" t="str">
         <f t="shared" si="3"/>
@@ -13430,7 +13439,7 @@
     <row r="90" spans="1:65">
       <c r="A90" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B90" t="str">
         <f t="shared" si="3"/>
@@ -13509,7 +13518,7 @@
     <row r="91" spans="1:65">
       <c r="A91" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B91" t="str">
         <f t="shared" si="3"/>
@@ -13588,7 +13597,7 @@
     <row r="92" spans="1:65">
       <c r="A92" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B92" t="str">
         <f t="shared" si="3"/>
@@ -13667,7 +13676,7 @@
     <row r="93" spans="1:65">
       <c r="A93" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B93" t="str">
         <f t="shared" si="3"/>
@@ -13746,7 +13755,7 @@
     <row r="94" spans="1:65">
       <c r="A94" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B94" t="str">
         <f t="shared" si="3"/>
@@ -13825,7 +13834,7 @@
     <row r="95" spans="1:65">
       <c r="A95" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B95" t="str">
         <f t="shared" si="3"/>
@@ -13904,7 +13913,7 @@
     <row r="96" spans="1:65">
       <c r="A96" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B96" t="str">
         <f t="shared" si="3"/>
@@ -13983,7 +13992,7 @@
     <row r="97" spans="1:65">
       <c r="A97" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B97" t="str">
         <f t="shared" si="3"/>
@@ -14062,7 +14071,7 @@
     <row r="98" spans="1:65">
       <c r="A98" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B98" t="str">
         <f t="shared" si="3"/>
@@ -14141,7 +14150,7 @@
     <row r="99" spans="1:65">
       <c r="A99" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B99" t="str">
         <f t="shared" si="3"/>
@@ -14220,7 +14229,7 @@
     <row r="100" spans="1:65">
       <c r="A100" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B100" t="str">
         <f t="shared" si="3"/>
@@ -14301,7 +14310,7 @@
     <row r="101" spans="1:65">
       <c r="A101" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B101" t="str">
         <f t="shared" si="3"/>
@@ -14380,7 +14389,7 @@
     <row r="102" spans="1:65">
       <c r="A102" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B102" t="str">
         <f t="shared" si="3"/>
@@ -14459,7 +14468,7 @@
     <row r="103" spans="1:65">
       <c r="A103" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B103" t="str">
         <f t="shared" si="3"/>
@@ -14538,7 +14547,7 @@
     <row r="104" spans="1:65">
       <c r="A104" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B104" t="str">
         <f t="shared" si="3"/>
@@ -14617,7 +14626,7 @@
     <row r="105" spans="1:65">
       <c r="A105" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B105" t="str">
         <f t="shared" si="3"/>
@@ -14696,7 +14705,7 @@
     <row r="106" spans="1:65">
       <c r="A106" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B106" t="str">
         <f t="shared" si="3"/>
@@ -14777,7 +14786,7 @@
     <row r="107" spans="1:65">
       <c r="A107" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B107" t="str">
         <f t="shared" si="3"/>
@@ -14858,7 +14867,7 @@
     <row r="108" spans="1:65">
       <c r="A108" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B108" t="str">
         <f t="shared" si="3"/>
@@ -14937,7 +14946,7 @@
     <row r="109" spans="1:65">
       <c r="A109" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B109" t="str">
         <f t="shared" si="3"/>
@@ -15016,7 +15025,7 @@
     <row r="110" spans="1:65">
       <c r="A110" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B110" t="str">
         <f t="shared" si="3"/>
@@ -15095,7 +15104,7 @@
     <row r="111" spans="1:65">
       <c r="A111" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B111" t="str">
         <f t="shared" si="3"/>
@@ -15174,7 +15183,7 @@
     <row r="112" spans="1:65">
       <c r="A112" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B112" t="str">
         <f t="shared" si="3"/>
@@ -15255,7 +15264,7 @@
     <row r="113" spans="1:65">
       <c r="A113" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B113" t="str">
         <f t="shared" si="3"/>
@@ -15334,7 +15343,7 @@
     <row r="114" spans="1:65">
       <c r="A114" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B114" t="str">
         <f t="shared" si="3"/>
@@ -15413,7 +15422,7 @@
     <row r="115" spans="1:65">
       <c r="A115" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B115" t="str">
         <f t="shared" si="3"/>
@@ -15492,7 +15501,7 @@
     <row r="116" spans="1:65">
       <c r="A116" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B116" t="str">
         <f t="shared" si="3"/>
@@ -15571,7 +15580,7 @@
     <row r="117" spans="1:65">
       <c r="A117" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B117" t="str">
         <f t="shared" si="3"/>
@@ -15650,7 +15659,7 @@
     <row r="118" spans="1:65">
       <c r="A118" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B118" t="str">
         <f t="shared" si="3"/>
@@ -15729,7 +15738,7 @@
     <row r="119" spans="1:65">
       <c r="A119" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B119" t="str">
         <f t="shared" si="3"/>
@@ -15808,7 +15817,7 @@
     <row r="120" spans="1:65">
       <c r="A120" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B120" t="str">
         <f t="shared" si="3"/>
@@ -15887,7 +15896,7 @@
     <row r="121" spans="1:65">
       <c r="A121" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B121" t="str">
         <f t="shared" si="3"/>
@@ -15966,7 +15975,7 @@
     <row r="122" spans="1:65">
       <c r="A122" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B122" t="str">
         <f t="shared" si="3"/>
@@ -16045,7 +16054,7 @@
     <row r="123" spans="1:65">
       <c r="A123" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B123" t="str">
         <f t="shared" si="3"/>
@@ -16124,7 +16133,7 @@
     <row r="124" spans="1:65">
       <c r="A124" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B124" t="str">
         <f t="shared" si="3"/>
@@ -16205,7 +16214,7 @@
     <row r="125" spans="1:65">
       <c r="A125" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B125" t="str">
         <f t="shared" si="3"/>
@@ -16286,7 +16295,7 @@
     <row r="126" spans="1:65">
       <c r="A126" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B126" t="str">
         <f t="shared" si="3"/>
@@ -16365,7 +16374,7 @@
     <row r="127" spans="1:65">
       <c r="A127" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B127" t="str">
         <f t="shared" si="3"/>
@@ -16444,7 +16453,7 @@
     <row r="128" spans="1:65">
       <c r="A128" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B128" t="str">
         <f t="shared" si="3"/>
@@ -16523,7 +16532,7 @@
     <row r="129" spans="1:65">
       <c r="A129" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B129" t="str">
         <f t="shared" si="3"/>
@@ -16602,7 +16611,7 @@
     <row r="130" spans="1:65">
       <c r="A130" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B130" t="str">
         <f t="shared" si="3"/>
@@ -16681,7 +16690,7 @@
     <row r="131" spans="1:65">
       <c r="A131" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B131" t="str">
         <f t="shared" si="3"/>
@@ -16763,7 +16772,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B132" t="str">
         <f t="shared" ref="B132:B168" si="5">TEXT($C132, "HH:mm")</f>
@@ -16842,7 +16851,7 @@
     <row r="133" spans="1:65">
       <c r="A133" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B133" t="str">
         <f t="shared" si="5"/>
@@ -16921,7 +16930,7 @@
     <row r="134" spans="1:65">
       <c r="A134" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B134" t="str">
         <f t="shared" si="5"/>
@@ -17000,7 +17009,7 @@
     <row r="135" spans="1:65">
       <c r="A135" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B135" t="str">
         <f t="shared" si="5"/>
@@ -17079,7 +17088,7 @@
     <row r="136" spans="1:65">
       <c r="A136" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B136" t="str">
         <f t="shared" si="5"/>
@@ -17160,7 +17169,7 @@
     <row r="137" spans="1:65">
       <c r="A137" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B137" t="str">
         <f t="shared" si="5"/>
@@ -17241,7 +17250,7 @@
     <row r="138" spans="1:65">
       <c r="A138" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B138" t="str">
         <f t="shared" si="5"/>
@@ -17320,7 +17329,7 @@
     <row r="139" spans="1:65">
       <c r="A139" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B139" t="str">
         <f t="shared" si="5"/>
@@ -17399,7 +17408,7 @@
     <row r="140" spans="1:65">
       <c r="A140" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B140" t="str">
         <f t="shared" si="5"/>
@@ -17478,7 +17487,7 @@
     <row r="141" spans="1:65">
       <c r="A141" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B141" t="str">
         <f t="shared" si="5"/>
@@ -17557,7 +17566,7 @@
     <row r="142" spans="1:65">
       <c r="A142" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B142" t="str">
         <f t="shared" si="5"/>
@@ -17636,7 +17645,7 @@
     <row r="143" spans="1:65">
       <c r="A143" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B143" t="str">
         <f t="shared" si="5"/>
@@ -17715,7 +17724,7 @@
     <row r="144" spans="1:65">
       <c r="A144" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B144" t="str">
         <f t="shared" si="5"/>
@@ -17794,7 +17803,7 @@
     <row r="145" spans="1:65">
       <c r="A145" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B145" t="str">
         <f t="shared" si="5"/>
@@ -17873,7 +17882,7 @@
     <row r="146" spans="1:65">
       <c r="A146" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B146" t="str">
         <f t="shared" si="5"/>
@@ -17952,7 +17961,7 @@
     <row r="147" spans="1:65">
       <c r="A147" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B147" t="str">
         <f t="shared" si="5"/>
@@ -18031,7 +18040,7 @@
     <row r="148" spans="1:65">
       <c r="A148" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B148" t="str">
         <f t="shared" si="5"/>
@@ -18112,7 +18121,7 @@
     <row r="149" spans="1:65">
       <c r="A149" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B149" t="str">
         <f t="shared" si="5"/>
@@ -18191,7 +18200,7 @@
     <row r="150" spans="1:65">
       <c r="A150" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B150" t="str">
         <f t="shared" si="5"/>
@@ -18270,7 +18279,7 @@
     <row r="151" spans="1:65">
       <c r="A151" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B151" t="str">
         <f t="shared" si="5"/>
@@ -18349,7 +18358,7 @@
     <row r="152" spans="1:65">
       <c r="A152" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B152" t="str">
         <f t="shared" si="5"/>
@@ -18428,7 +18437,7 @@
     <row r="153" spans="1:65">
       <c r="A153" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B153" t="str">
         <f t="shared" si="5"/>
@@ -18507,7 +18516,7 @@
     <row r="154" spans="1:65">
       <c r="A154" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B154" t="str">
         <f t="shared" si="5"/>
@@ -18586,7 +18595,7 @@
     <row r="155" spans="1:65">
       <c r="A155" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B155" t="str">
         <f t="shared" si="5"/>
@@ -18665,7 +18674,7 @@
     <row r="156" spans="1:65">
       <c r="A156" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B156" t="str">
         <f t="shared" si="5"/>
@@ -18744,7 +18753,7 @@
     <row r="157" spans="1:65">
       <c r="A157" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B157" t="str">
         <f t="shared" si="5"/>
@@ -18823,7 +18832,7 @@
     <row r="158" spans="1:65">
       <c r="A158" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B158" t="str">
         <f t="shared" si="5"/>
@@ -18902,7 +18911,7 @@
     <row r="159" spans="1:65">
       <c r="A159" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B159" t="str">
         <f t="shared" si="5"/>
@@ -18981,7 +18990,7 @@
     <row r="160" spans="1:65">
       <c r="A160" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B160" t="str">
         <f t="shared" si="5"/>
@@ -19060,7 +19069,7 @@
     <row r="161" spans="1:65">
       <c r="A161" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B161" t="str">
         <f t="shared" si="5"/>
@@ -19139,7 +19148,7 @@
     <row r="162" spans="1:65">
       <c r="A162" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B162" t="str">
         <f t="shared" si="5"/>
@@ -19218,7 +19227,7 @@
     <row r="163" spans="1:65">
       <c r="A163" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B163" t="str">
         <f t="shared" si="5"/>
@@ -19297,7 +19306,7 @@
     <row r="164" spans="1:65">
       <c r="A164" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B164" t="str">
         <f t="shared" si="5"/>
@@ -19376,7 +19385,7 @@
     <row r="165" spans="1:65">
       <c r="A165" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B165" t="str">
         <f t="shared" si="5"/>
@@ -19455,7 +19464,7 @@
     <row r="166" spans="1:65">
       <c r="A166" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B166" t="str">
         <f t="shared" si="5"/>
@@ -19536,7 +19545,7 @@
     <row r="167" spans="1:65">
       <c r="A167" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B167" t="str">
         <f t="shared" si="5"/>
@@ -19615,7 +19624,7 @@
     <row r="168" spans="1:65">
       <c r="A168" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B168" t="str">
         <f t="shared" si="5"/>
@@ -19697,7 +19706,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B169" t="str">
         <f>TEXT($C169, "HH:mm")</f>
@@ -19779,7 +19788,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B170" t="str">
         <f t="shared" ref="B170:B233" si="7">TEXT($C170, "HH:mm")</f>
@@ -19858,7 +19867,7 @@
     <row r="171" spans="1:65">
       <c r="A171" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B171" t="str">
         <f t="shared" si="7"/>
@@ -19937,7 +19946,7 @@
     <row r="172" spans="1:65">
       <c r="A172" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B172" t="str">
         <f t="shared" si="7"/>
@@ -20018,7 +20027,7 @@
     <row r="173" spans="1:65">
       <c r="A173" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B173" t="str">
         <f t="shared" si="7"/>
@@ -20097,7 +20106,7 @@
     <row r="174" spans="1:65">
       <c r="A174" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B174" t="str">
         <f t="shared" si="7"/>
@@ -20176,7 +20185,7 @@
     <row r="175" spans="1:65">
       <c r="A175" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B175" t="str">
         <f t="shared" si="7"/>
@@ -20255,7 +20264,7 @@
     <row r="176" spans="1:65">
       <c r="A176" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B176" t="str">
         <f t="shared" si="7"/>
@@ -20334,7 +20343,7 @@
     <row r="177" spans="1:65">
       <c r="A177" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B177" t="str">
         <f t="shared" si="7"/>
@@ -20413,7 +20422,7 @@
     <row r="178" spans="1:65">
       <c r="A178" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B178" t="str">
         <f t="shared" si="7"/>
@@ -20494,7 +20503,7 @@
     <row r="179" spans="1:65">
       <c r="A179" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B179" t="str">
         <f t="shared" si="7"/>
@@ -20573,7 +20582,7 @@
     <row r="180" spans="1:65">
       <c r="A180" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B180" t="str">
         <f t="shared" si="7"/>
@@ -20652,7 +20661,7 @@
     <row r="181" spans="1:65">
       <c r="A181" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B181" t="str">
         <f t="shared" si="7"/>
@@ -20733,7 +20742,7 @@
     <row r="182" spans="1:65">
       <c r="A182" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B182" t="str">
         <f t="shared" si="7"/>
@@ -20814,7 +20823,7 @@
     <row r="183" spans="1:65">
       <c r="A183" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B183" t="str">
         <f t="shared" si="7"/>
@@ -20895,7 +20904,7 @@
     <row r="184" spans="1:65">
       <c r="A184" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B184" t="str">
         <f t="shared" si="7"/>
@@ -20978,7 +20987,7 @@
     <row r="185" spans="1:65">
       <c r="A185" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B185" t="str">
         <f t="shared" si="7"/>
@@ -21059,7 +21068,7 @@
     <row r="186" spans="1:65">
       <c r="A186" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B186" t="str">
         <f t="shared" si="7"/>
@@ -21140,7 +21149,7 @@
     <row r="187" spans="1:65">
       <c r="A187" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B187" t="str">
         <f t="shared" si="7"/>
@@ -21221,7 +21230,7 @@
     <row r="188" spans="1:65">
       <c r="A188" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B188" t="str">
         <f t="shared" si="7"/>
@@ -21302,7 +21311,7 @@
     <row r="189" spans="1:65">
       <c r="A189" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B189" t="str">
         <f t="shared" si="7"/>
@@ -21383,7 +21392,7 @@
     <row r="190" spans="1:65">
       <c r="A190" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B190" t="str">
         <f t="shared" si="7"/>
@@ -21466,7 +21475,7 @@
     <row r="191" spans="1:65">
       <c r="A191" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B191" t="str">
         <f t="shared" si="7"/>
@@ -21549,7 +21558,7 @@
     <row r="192" spans="1:65">
       <c r="A192" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B192" t="str">
         <f t="shared" si="7"/>
@@ -21632,7 +21641,7 @@
     <row r="193" spans="1:65">
       <c r="A193" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B193" t="str">
         <f t="shared" si="7"/>
@@ -21715,7 +21724,7 @@
     <row r="194" spans="1:65">
       <c r="A194" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B194" t="str">
         <f t="shared" si="7"/>
@@ -21796,7 +21805,7 @@
     <row r="195" spans="1:65">
       <c r="A195" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B195" t="str">
         <f t="shared" si="7"/>
@@ -21877,7 +21886,7 @@
     <row r="196" spans="1:65">
       <c r="A196" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B196" t="str">
         <f t="shared" si="7"/>
@@ -21960,7 +21969,7 @@
     <row r="197" spans="1:65">
       <c r="A197" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B197" t="str">
         <f t="shared" si="7"/>
@@ -22039,7 +22048,7 @@
     <row r="198" spans="1:65">
       <c r="A198" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B198" t="str">
         <f t="shared" si="7"/>
@@ -22118,7 +22127,7 @@
     <row r="199" spans="1:65">
       <c r="A199" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B199" t="str">
         <f t="shared" si="7"/>
@@ -22197,7 +22206,7 @@
     <row r="200" spans="1:65">
       <c r="A200" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B200" t="str">
         <f t="shared" si="7"/>
@@ -22276,7 +22285,7 @@
     <row r="201" spans="1:65">
       <c r="A201" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B201" t="str">
         <f t="shared" si="7"/>
@@ -22355,7 +22364,7 @@
     <row r="202" spans="1:65">
       <c r="A202" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B202" t="str">
         <f t="shared" si="7"/>
@@ -22436,7 +22445,7 @@
     <row r="203" spans="1:65">
       <c r="A203" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B203" t="str">
         <f t="shared" si="7"/>
@@ -22515,7 +22524,7 @@
     <row r="204" spans="1:65">
       <c r="A204" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B204" t="str">
         <f t="shared" si="7"/>
@@ -22594,7 +22603,7 @@
     <row r="205" spans="1:65">
       <c r="A205" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B205" t="str">
         <f t="shared" si="7"/>
@@ -22673,7 +22682,7 @@
     <row r="206" spans="1:65">
       <c r="A206" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B206" t="str">
         <f t="shared" si="7"/>
@@ -22752,7 +22761,7 @@
     <row r="207" spans="1:65">
       <c r="A207" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B207" t="str">
         <f t="shared" si="7"/>
@@ -22831,7 +22840,7 @@
     <row r="208" spans="1:65">
       <c r="A208" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B208" t="str">
         <f t="shared" si="7"/>
@@ -22912,7 +22921,7 @@
     <row r="209" spans="1:65">
       <c r="A209" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B209" t="str">
         <f t="shared" si="7"/>
@@ -22991,7 +23000,7 @@
     <row r="210" spans="1:65">
       <c r="A210" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B210" t="str">
         <f t="shared" si="7"/>
@@ -23070,7 +23079,7 @@
     <row r="211" spans="1:65">
       <c r="A211" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B211" t="str">
         <f t="shared" si="7"/>
@@ -23151,7 +23160,7 @@
     <row r="212" spans="1:65">
       <c r="A212" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B212" t="str">
         <f t="shared" si="7"/>
@@ -23230,7 +23239,7 @@
     <row r="213" spans="1:65">
       <c r="A213" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B213" t="str">
         <f t="shared" si="7"/>
@@ -23309,7 +23318,7 @@
     <row r="214" spans="1:65">
       <c r="A214" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B214" t="str">
         <f t="shared" si="7"/>
@@ -23388,7 +23397,7 @@
     <row r="215" spans="1:65">
       <c r="A215" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B215" t="str">
         <f t="shared" si="7"/>
@@ -23467,7 +23476,7 @@
     <row r="216" spans="1:65">
       <c r="A216" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B216" t="str">
         <f t="shared" si="7"/>
@@ -23546,7 +23555,7 @@
     <row r="217" spans="1:65">
       <c r="A217" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B217" t="str">
         <f t="shared" si="7"/>
@@ -23625,7 +23634,7 @@
     <row r="218" spans="1:65">
       <c r="A218" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B218" t="str">
         <f t="shared" si="7"/>
@@ -23704,7 +23713,7 @@
     <row r="219" spans="1:65">
       <c r="A219" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B219" t="str">
         <f t="shared" si="7"/>
@@ -23783,7 +23792,7 @@
     <row r="220" spans="1:65">
       <c r="A220" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B220" t="str">
         <f t="shared" si="7"/>
@@ -23864,7 +23873,7 @@
     <row r="221" spans="1:65">
       <c r="A221" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B221" t="str">
         <f t="shared" si="7"/>
@@ -23943,7 +23952,7 @@
     <row r="222" spans="1:65">
       <c r="A222" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B222" t="str">
         <f t="shared" si="7"/>
@@ -24022,7 +24031,7 @@
     <row r="223" spans="1:65">
       <c r="A223" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B223" t="str">
         <f t="shared" si="7"/>
@@ -24101,7 +24110,7 @@
     <row r="224" spans="1:65">
       <c r="A224" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B224" t="str">
         <f t="shared" si="7"/>
@@ -24180,7 +24189,7 @@
     <row r="225" spans="1:65">
       <c r="A225" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B225" t="str">
         <f t="shared" si="7"/>
@@ -24259,7 +24268,7 @@
     <row r="226" spans="1:65">
       <c r="A226" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B226" t="str">
         <f t="shared" si="7"/>
@@ -24338,7 +24347,7 @@
     <row r="227" spans="1:65">
       <c r="A227" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B227" t="str">
         <f t="shared" si="7"/>
@@ -24417,7 +24426,7 @@
     <row r="228" spans="1:65">
       <c r="A228" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B228" t="str">
         <f t="shared" si="7"/>
@@ -24496,7 +24505,7 @@
     <row r="229" spans="1:65">
       <c r="A229" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B229" t="str">
         <f t="shared" si="7"/>
@@ -24575,7 +24584,7 @@
     <row r="230" spans="1:65">
       <c r="A230" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B230" t="str">
         <f t="shared" si="7"/>
@@ -24654,7 +24663,7 @@
     <row r="231" spans="1:65">
       <c r="A231" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B231" t="str">
         <f t="shared" si="7"/>
@@ -24733,7 +24742,7 @@
     <row r="232" spans="1:65">
       <c r="A232" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B232" t="str">
         <f t="shared" si="7"/>
@@ -24812,7 +24821,7 @@
     <row r="233" spans="1:65">
       <c r="A233" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B233" t="str">
         <f t="shared" si="7"/>
@@ -24894,7 +24903,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B234" t="str">
         <f t="shared" ref="B234:B291" si="9">TEXT($C234, "HH:mm")</f>
@@ -24973,7 +24982,7 @@
     <row r="235" spans="1:65">
       <c r="A235" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B235" t="str">
         <f t="shared" si="9"/>
@@ -25052,7 +25061,7 @@
     <row r="236" spans="1:65">
       <c r="A236" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B236" t="str">
         <f t="shared" si="9"/>
@@ -25131,7 +25140,7 @@
     <row r="237" spans="1:65">
       <c r="A237" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B237" t="str">
         <f t="shared" si="9"/>
@@ -25210,7 +25219,7 @@
     <row r="238" spans="1:65">
       <c r="A238" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B238" t="str">
         <f t="shared" si="9"/>
@@ -25289,7 +25298,7 @@
     <row r="239" spans="1:65">
       <c r="A239" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B239" t="str">
         <f t="shared" si="9"/>
@@ -25368,7 +25377,7 @@
     <row r="240" spans="1:65">
       <c r="A240" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B240" t="str">
         <f t="shared" si="9"/>
@@ -25447,7 +25456,7 @@
     <row r="241" spans="1:65">
       <c r="A241" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B241" t="str">
         <f t="shared" si="9"/>
@@ -25526,7 +25535,7 @@
     <row r="242" spans="1:65">
       <c r="A242" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B242" t="str">
         <f t="shared" si="9"/>
@@ -25605,7 +25614,7 @@
     <row r="243" spans="1:65">
       <c r="A243" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B243" t="str">
         <f t="shared" si="9"/>
@@ -25684,7 +25693,7 @@
     <row r="244" spans="1:65">
       <c r="A244" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B244" t="str">
         <f t="shared" si="9"/>
@@ -25763,7 +25772,7 @@
     <row r="245" spans="1:65">
       <c r="A245" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B245" t="str">
         <f t="shared" si="9"/>
@@ -25842,7 +25851,7 @@
     <row r="246" spans="1:65">
       <c r="A246" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B246" t="str">
         <f t="shared" si="9"/>
@@ -25921,7 +25930,7 @@
     <row r="247" spans="1:65">
       <c r="A247" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B247" t="str">
         <f t="shared" si="9"/>
@@ -26000,7 +26009,7 @@
     <row r="248" spans="1:65">
       <c r="A248" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B248" t="str">
         <f t="shared" si="9"/>
@@ -26079,7 +26088,7 @@
     <row r="249" spans="1:65">
       <c r="A249" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B249" t="str">
         <f t="shared" si="9"/>
@@ -26158,7 +26167,7 @@
     <row r="250" spans="1:65">
       <c r="A250" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B250" t="str">
         <f t="shared" si="9"/>
@@ -26237,7 +26246,7 @@
     <row r="251" spans="1:65">
       <c r="A251" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B251" t="str">
         <f t="shared" si="9"/>
@@ -26316,7 +26325,7 @@
     <row r="252" spans="1:65">
       <c r="A252" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B252" t="str">
         <f t="shared" si="9"/>
@@ -26395,7 +26404,7 @@
     <row r="253" spans="1:65">
       <c r="A253" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B253" t="str">
         <f t="shared" si="9"/>
@@ -26474,7 +26483,7 @@
     <row r="254" spans="1:65">
       <c r="A254" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B254" t="str">
         <f t="shared" si="9"/>
@@ -26553,7 +26562,7 @@
     <row r="255" spans="1:65">
       <c r="A255" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B255" t="str">
         <f t="shared" si="9"/>
@@ -26632,7 +26641,7 @@
     <row r="256" spans="1:65">
       <c r="A256" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B256" t="str">
         <f t="shared" si="9"/>
@@ -26711,7 +26720,7 @@
     <row r="257" spans="1:65">
       <c r="A257" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B257" t="str">
         <f t="shared" si="9"/>
@@ -26790,7 +26799,7 @@
     <row r="258" spans="1:65">
       <c r="A258" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B258" t="str">
         <f t="shared" si="9"/>
@@ -26869,7 +26878,7 @@
     <row r="259" spans="1:65">
       <c r="A259" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B259" t="str">
         <f t="shared" si="9"/>
@@ -26948,7 +26957,7 @@
     <row r="260" spans="1:65">
       <c r="A260" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B260" t="str">
         <f t="shared" si="9"/>
@@ -27027,7 +27036,7 @@
     <row r="261" spans="1:65">
       <c r="A261" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B261" t="str">
         <f t="shared" si="9"/>
@@ -27106,7 +27115,7 @@
     <row r="262" spans="1:65">
       <c r="A262" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B262" t="str">
         <f t="shared" si="9"/>
@@ -27185,7 +27194,7 @@
     <row r="263" spans="1:65">
       <c r="A263" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B263" t="str">
         <f t="shared" si="9"/>
@@ -27264,7 +27273,7 @@
     <row r="264" spans="1:65">
       <c r="A264" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B264" t="str">
         <f t="shared" si="9"/>
@@ -27343,7 +27352,7 @@
     <row r="265" spans="1:65">
       <c r="A265" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B265" t="str">
         <f t="shared" si="9"/>
@@ -27422,7 +27431,7 @@
     <row r="266" spans="1:65">
       <c r="A266" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B266" t="str">
         <f t="shared" si="9"/>
@@ -27501,7 +27510,7 @@
     <row r="267" spans="1:65">
       <c r="A267" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B267" t="str">
         <f t="shared" si="9"/>
@@ -27580,7 +27589,7 @@
     <row r="268" spans="1:65">
       <c r="A268" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B268" t="str">
         <f t="shared" si="9"/>
@@ -27659,7 +27668,7 @@
     <row r="269" spans="1:65">
       <c r="A269" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B269" t="str">
         <f t="shared" si="9"/>
@@ -27738,7 +27747,7 @@
     <row r="270" spans="1:65">
       <c r="A270" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B270" t="str">
         <f t="shared" si="9"/>
@@ -27817,7 +27826,7 @@
     <row r="271" spans="1:65">
       <c r="A271" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B271" t="str">
         <f t="shared" si="9"/>
@@ -27896,7 +27905,7 @@
     <row r="272" spans="1:65">
       <c r="A272" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B272" t="str">
         <f t="shared" si="9"/>
@@ -27975,7 +27984,7 @@
     <row r="273" spans="1:65">
       <c r="A273" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B273" t="str">
         <f t="shared" si="9"/>
@@ -28054,7 +28063,7 @@
     <row r="274" spans="1:65">
       <c r="A274" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B274" t="str">
         <f t="shared" si="9"/>
@@ -28133,7 +28142,7 @@
     <row r="275" spans="1:65">
       <c r="A275" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B275" t="str">
         <f t="shared" si="9"/>
@@ -28212,7 +28221,7 @@
     <row r="276" spans="1:65">
       <c r="A276" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B276" t="str">
         <f t="shared" si="9"/>
@@ -28291,7 +28300,7 @@
     <row r="277" spans="1:65">
       <c r="A277" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B277" t="str">
         <f t="shared" si="9"/>
@@ -28370,7 +28379,7 @@
     <row r="278" spans="1:65">
       <c r="A278" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B278" t="str">
         <f t="shared" si="9"/>
@@ -28449,7 +28458,7 @@
     <row r="279" spans="1:65">
       <c r="A279" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B279" t="str">
         <f t="shared" si="9"/>
@@ -28528,7 +28537,7 @@
     <row r="280" spans="1:65">
       <c r="A280" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B280" t="str">
         <f t="shared" si="9"/>
@@ -28607,7 +28616,7 @@
     <row r="281" spans="1:65">
       <c r="A281" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B281" t="str">
         <f t="shared" si="9"/>
@@ -28686,7 +28695,7 @@
     <row r="282" spans="1:65">
       <c r="A282" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B282" t="str">
         <f t="shared" si="9"/>
@@ -28765,7 +28774,7 @@
     <row r="283" spans="1:65">
       <c r="A283" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B283" t="str">
         <f t="shared" si="9"/>
@@ -28844,7 +28853,7 @@
     <row r="284" spans="1:65">
       <c r="A284" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B284" t="str">
         <f t="shared" si="9"/>
@@ -28923,7 +28932,7 @@
     <row r="285" spans="1:65">
       <c r="A285" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B285" t="str">
         <f t="shared" si="9"/>
@@ -29002,7 +29011,7 @@
     <row r="286" spans="1:65">
       <c r="A286" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B286" t="str">
         <f t="shared" si="9"/>
@@ -29081,7 +29090,7 @@
     <row r="287" spans="1:65">
       <c r="A287" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B287" t="str">
         <f t="shared" si="9"/>
@@ -29160,7 +29169,7 @@
     <row r="288" spans="1:65">
       <c r="A288" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B288" t="str">
         <f t="shared" si="9"/>
@@ -29239,7 +29248,7 @@
     <row r="289" spans="1:65">
       <c r="A289" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B289" t="str">
         <f t="shared" si="9"/>
@@ -29318,7 +29327,7 @@
     <row r="290" spans="1:65">
       <c r="A290" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B290" t="str">
         <f t="shared" si="9"/>
@@ -29397,7 +29406,7 @@
     <row r="291" spans="1:65">
       <c r="A291" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:15</v>
+        <v>01:20</v>
       </c>
       <c r="B291" t="str">
         <f t="shared" si="9"/>

--- a/Vite-Vercel開発.xlsx
+++ b/Vite-Vercel開発.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2c67ec30e06f060f/work/GitHub/work-time-tracker/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{1928CA11-C4AD-40E9-B1C5-143667E830EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9AC47CEF-5545-4C30-AAEB-10DA74AC6478}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{1928CA11-C4AD-40E9-B1C5-143667E830EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{64C4BBF7-1515-4183-BBF0-04780074AFB2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1540" uniqueCount="918">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1541" uniqueCount="919">
   <si>
     <t>npm install -g vercel</t>
     <phoneticPr fontId="1"/>
@@ -5350,6 +5350,10 @@
   </si>
   <si>
     <t>Found 67 errors in 17 files.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Found 64 errors in 16 files.</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -6122,7 +6126,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{083174DA-A42C-4F9C-978E-61AEAAD9DDFF}">
-  <dimension ref="B2:D22"/>
+  <dimension ref="B2:D23"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
@@ -6240,6 +6244,11 @@
     <row r="22" spans="3:3">
       <c r="C22" t="s">
         <v>917</v>
+      </c>
+    </row>
+    <row r="23" spans="3:3">
+      <c r="C23" t="s">
+        <v>918</v>
       </c>
     </row>
   </sheetData>
@@ -6406,7 +6415,7 @@
       MOD(NOW(),1),
       TIME(0,5,0)
     ),"HH:mm")</f>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B2" s="19"/>
       <c r="D2" s="1">
@@ -6417,7 +6426,7 @@
     <row r="3" spans="1:65">
       <c r="A3" s="19" t="str">
         <f ca="1">TEXT(NOW(),"HH:mm")</f>
-        <v>01:21</v>
+        <v>01:25</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="17" t="s">
@@ -6616,7 +6625,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B4" t="str">
         <f t="shared" ref="B4:B67" si="1">TEXT($C4, "HH:mm")</f>
@@ -6695,7 +6704,7 @@
     <row r="5" spans="1:65">
       <c r="A5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B5" t="str">
         <f t="shared" si="1"/>
@@ -6774,7 +6783,7 @@
     <row r="6" spans="1:65">
       <c r="A6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B6" t="str">
         <f t="shared" si="1"/>
@@ -6853,7 +6862,7 @@
     <row r="7" spans="1:65">
       <c r="A7" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B7" t="str">
         <f t="shared" si="1"/>
@@ -6932,7 +6941,7 @@
     <row r="8" spans="1:65">
       <c r="A8" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B8" t="str">
         <f t="shared" si="1"/>
@@ -7011,7 +7020,7 @@
     <row r="9" spans="1:65">
       <c r="A9" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B9" t="str">
         <f t="shared" si="1"/>
@@ -7090,7 +7099,7 @@
     <row r="10" spans="1:65">
       <c r="A10" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B10" t="str">
         <f t="shared" si="1"/>
@@ -7169,7 +7178,7 @@
     <row r="11" spans="1:65">
       <c r="A11" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B11" t="str">
         <f t="shared" si="1"/>
@@ -7248,7 +7257,7 @@
     <row r="12" spans="1:65">
       <c r="A12" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B12" t="str">
         <f t="shared" si="1"/>
@@ -7327,7 +7336,7 @@
     <row r="13" spans="1:65">
       <c r="A13" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B13" t="str">
         <f t="shared" si="1"/>
@@ -7406,7 +7415,7 @@
     <row r="14" spans="1:65">
       <c r="A14" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B14" t="str">
         <f t="shared" si="1"/>
@@ -7485,7 +7494,7 @@
     <row r="15" spans="1:65">
       <c r="A15" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B15" t="str">
         <f t="shared" si="1"/>
@@ -7564,7 +7573,7 @@
     <row r="16" spans="1:65">
       <c r="A16" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B16" t="str">
         <f t="shared" si="1"/>
@@ -7643,7 +7652,7 @@
     <row r="17" spans="1:65">
       <c r="A17" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B17" t="str">
         <f t="shared" si="1"/>
@@ -7722,7 +7731,7 @@
     <row r="18" spans="1:65">
       <c r="A18" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B18" t="str">
         <f t="shared" si="1"/>
@@ -7801,7 +7810,7 @@
     <row r="19" spans="1:65">
       <c r="A19" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B19" t="str">
         <f t="shared" si="1"/>
@@ -7880,7 +7889,7 @@
     <row r="20" spans="1:65">
       <c r="A20" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B20" t="str">
         <f t="shared" si="1"/>
@@ -7959,7 +7968,7 @@
     <row r="21" spans="1:65">
       <c r="A21" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B21" t="str">
         <f t="shared" si="1"/>
@@ -8038,7 +8047,7 @@
     <row r="22" spans="1:65">
       <c r="A22" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B22" t="str">
         <f t="shared" si="1"/>
@@ -8117,7 +8126,7 @@
     <row r="23" spans="1:65">
       <c r="A23" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B23" t="str">
         <f t="shared" si="1"/>
@@ -8196,7 +8205,7 @@
     <row r="24" spans="1:65">
       <c r="A24" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B24" t="str">
         <f t="shared" si="1"/>
@@ -8275,7 +8284,7 @@
     <row r="25" spans="1:65">
       <c r="A25" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B25" t="str">
         <f t="shared" si="1"/>
@@ -8354,7 +8363,7 @@
     <row r="26" spans="1:65">
       <c r="A26" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B26" t="str">
         <f t="shared" si="1"/>
@@ -8433,7 +8442,7 @@
     <row r="27" spans="1:65">
       <c r="A27" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B27" t="str">
         <f t="shared" si="1"/>
@@ -8512,7 +8521,7 @@
     <row r="28" spans="1:65">
       <c r="A28" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B28" t="str">
         <f t="shared" si="1"/>
@@ -8593,7 +8602,7 @@
     <row r="29" spans="1:65">
       <c r="A29" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B29" t="str">
         <f t="shared" si="1"/>
@@ -8674,7 +8683,7 @@
     <row r="30" spans="1:65">
       <c r="A30" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B30" t="str">
         <f t="shared" si="1"/>
@@ -8755,7 +8764,7 @@
     <row r="31" spans="1:65">
       <c r="A31" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B31" t="str">
         <f t="shared" si="1"/>
@@ -8834,7 +8843,7 @@
     <row r="32" spans="1:65">
       <c r="A32" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B32" t="str">
         <f t="shared" si="1"/>
@@ -8913,7 +8922,7 @@
     <row r="33" spans="1:65">
       <c r="A33" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B33" t="str">
         <f t="shared" si="1"/>
@@ -8992,7 +9001,7 @@
     <row r="34" spans="1:65">
       <c r="A34" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B34" t="str">
         <f t="shared" si="1"/>
@@ -9073,7 +9082,7 @@
     <row r="35" spans="1:65">
       <c r="A35" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B35" t="str">
         <f t="shared" si="1"/>
@@ -9154,7 +9163,7 @@
     <row r="36" spans="1:65">
       <c r="A36" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B36" t="str">
         <f t="shared" si="1"/>
@@ -9235,7 +9244,7 @@
     <row r="37" spans="1:65">
       <c r="A37" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B37" t="str">
         <f t="shared" si="1"/>
@@ -9314,7 +9323,7 @@
     <row r="38" spans="1:65">
       <c r="A38" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B38" t="str">
         <f t="shared" si="1"/>
@@ -9393,7 +9402,7 @@
     <row r="39" spans="1:65">
       <c r="A39" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B39" t="str">
         <f t="shared" si="1"/>
@@ -9472,7 +9481,7 @@
     <row r="40" spans="1:65">
       <c r="A40" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B40" t="str">
         <f t="shared" si="1"/>
@@ -9551,7 +9560,7 @@
     <row r="41" spans="1:65">
       <c r="A41" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B41" t="str">
         <f t="shared" si="1"/>
@@ -9630,7 +9639,7 @@
     <row r="42" spans="1:65">
       <c r="A42" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B42" t="str">
         <f t="shared" si="1"/>
@@ -9711,7 +9720,7 @@
     <row r="43" spans="1:65">
       <c r="A43" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B43" t="str">
         <f t="shared" si="1"/>
@@ -9792,7 +9801,7 @@
     <row r="44" spans="1:65">
       <c r="A44" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B44" t="str">
         <f t="shared" si="1"/>
@@ -9871,7 +9880,7 @@
     <row r="45" spans="1:65">
       <c r="A45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B45" t="str">
         <f t="shared" si="1"/>
@@ -9950,7 +9959,7 @@
     <row r="46" spans="1:65">
       <c r="A46" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B46" t="str">
         <f t="shared" si="1"/>
@@ -10029,7 +10038,7 @@
     <row r="47" spans="1:65">
       <c r="A47" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B47" t="str">
         <f t="shared" si="1"/>
@@ -10108,7 +10117,7 @@
     <row r="48" spans="1:65">
       <c r="A48" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B48" t="str">
         <f t="shared" si="1"/>
@@ -10187,7 +10196,7 @@
     <row r="49" spans="1:65">
       <c r="A49" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B49" t="str">
         <f t="shared" si="1"/>
@@ -10268,7 +10277,7 @@
     <row r="50" spans="1:65">
       <c r="A50" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B50" t="str">
         <f t="shared" si="1"/>
@@ -10349,7 +10358,7 @@
     <row r="51" spans="1:65">
       <c r="A51" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B51" t="str">
         <f t="shared" si="1"/>
@@ -10428,7 +10437,7 @@
     <row r="52" spans="1:65">
       <c r="A52" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B52" t="str">
         <f t="shared" si="1"/>
@@ -10507,7 +10516,7 @@
     <row r="53" spans="1:65">
       <c r="A53" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B53" t="str">
         <f t="shared" si="1"/>
@@ -10586,7 +10595,7 @@
     <row r="54" spans="1:65">
       <c r="A54" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B54" t="str">
         <f t="shared" si="1"/>
@@ -10665,7 +10674,7 @@
     <row r="55" spans="1:65">
       <c r="A55" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B55" t="str">
         <f t="shared" si="1"/>
@@ -10744,7 +10753,7 @@
     <row r="56" spans="1:65">
       <c r="A56" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B56" t="str">
         <f t="shared" si="1"/>
@@ -10825,7 +10834,7 @@
     <row r="57" spans="1:65">
       <c r="A57" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B57" t="str">
         <f t="shared" si="1"/>
@@ -10904,7 +10913,7 @@
     <row r="58" spans="1:65">
       <c r="A58" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B58" t="str">
         <f t="shared" si="1"/>
@@ -10985,7 +10994,7 @@
     <row r="59" spans="1:65">
       <c r="A59" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B59" t="str">
         <f t="shared" si="1"/>
@@ -11064,7 +11073,7 @@
     <row r="60" spans="1:65">
       <c r="A60" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B60" t="str">
         <f t="shared" si="1"/>
@@ -11143,7 +11152,7 @@
     <row r="61" spans="1:65">
       <c r="A61" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B61" t="str">
         <f t="shared" si="1"/>
@@ -11222,7 +11231,7 @@
     <row r="62" spans="1:65">
       <c r="A62" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B62" t="str">
         <f t="shared" si="1"/>
@@ -11301,7 +11310,7 @@
     <row r="63" spans="1:65">
       <c r="A63" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B63" t="str">
         <f t="shared" si="1"/>
@@ -11380,7 +11389,7 @@
     <row r="64" spans="1:65">
       <c r="A64" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B64" t="str">
         <f t="shared" si="1"/>
@@ -11461,7 +11470,7 @@
     <row r="65" spans="1:65">
       <c r="A65" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B65" t="str">
         <f t="shared" si="1"/>
@@ -11540,7 +11549,7 @@
     <row r="66" spans="1:65">
       <c r="A66" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B66" t="str">
         <f t="shared" si="1"/>
@@ -11619,7 +11628,7 @@
     <row r="67" spans="1:65">
       <c r="A67" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B67" t="str">
         <f t="shared" si="1"/>
@@ -11701,7 +11710,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B68" t="str">
         <f t="shared" ref="B68:B131" si="3">TEXT($C68, "HH:mm")</f>
@@ -11780,7 +11789,7 @@
     <row r="69" spans="1:65">
       <c r="A69" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B69" t="str">
         <f t="shared" si="3"/>
@@ -11859,7 +11868,7 @@
     <row r="70" spans="1:65">
       <c r="A70" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B70" t="str">
         <f t="shared" si="3"/>
@@ -11938,7 +11947,7 @@
     <row r="71" spans="1:65">
       <c r="A71" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B71" t="str">
         <f t="shared" si="3"/>
@@ -12017,7 +12026,7 @@
     <row r="72" spans="1:65">
       <c r="A72" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B72" t="str">
         <f t="shared" si="3"/>
@@ -12096,7 +12105,7 @@
     <row r="73" spans="1:65">
       <c r="A73" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B73" t="str">
         <f t="shared" si="3"/>
@@ -12175,7 +12184,7 @@
     <row r="74" spans="1:65">
       <c r="A74" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B74" t="str">
         <f t="shared" si="3"/>
@@ -12254,7 +12263,7 @@
     <row r="75" spans="1:65">
       <c r="A75" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B75" t="str">
         <f t="shared" si="3"/>
@@ -12333,7 +12342,7 @@
     <row r="76" spans="1:65">
       <c r="A76" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B76" t="str">
         <f t="shared" si="3"/>
@@ -12412,7 +12421,7 @@
     <row r="77" spans="1:65">
       <c r="A77" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B77" t="str">
         <f t="shared" si="3"/>
@@ -12491,7 +12500,7 @@
     <row r="78" spans="1:65">
       <c r="A78" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B78" t="str">
         <f t="shared" si="3"/>
@@ -12570,7 +12579,7 @@
     <row r="79" spans="1:65">
       <c r="A79" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B79" t="str">
         <f t="shared" si="3"/>
@@ -12649,7 +12658,7 @@
     <row r="80" spans="1:65">
       <c r="A80" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B80" t="str">
         <f t="shared" si="3"/>
@@ -12728,7 +12737,7 @@
     <row r="81" spans="1:65">
       <c r="A81" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B81" t="str">
         <f t="shared" si="3"/>
@@ -12807,7 +12816,7 @@
     <row r="82" spans="1:65">
       <c r="A82" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B82" t="str">
         <f t="shared" si="3"/>
@@ -12886,7 +12895,7 @@
     <row r="83" spans="1:65">
       <c r="A83" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B83" t="str">
         <f t="shared" si="3"/>
@@ -12965,7 +12974,7 @@
     <row r="84" spans="1:65">
       <c r="A84" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B84" t="str">
         <f t="shared" si="3"/>
@@ -13044,7 +13053,7 @@
     <row r="85" spans="1:65">
       <c r="A85" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B85" t="str">
         <f t="shared" si="3"/>
@@ -13123,7 +13132,7 @@
     <row r="86" spans="1:65">
       <c r="A86" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B86" t="str">
         <f t="shared" si="3"/>
@@ -13202,7 +13211,7 @@
     <row r="87" spans="1:65">
       <c r="A87" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B87" t="str">
         <f t="shared" si="3"/>
@@ -13281,7 +13290,7 @@
     <row r="88" spans="1:65">
       <c r="A88" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B88" t="str">
         <f t="shared" si="3"/>
@@ -13360,7 +13369,7 @@
     <row r="89" spans="1:65">
       <c r="A89" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B89" t="str">
         <f t="shared" si="3"/>
@@ -13439,7 +13448,7 @@
     <row r="90" spans="1:65">
       <c r="A90" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B90" t="str">
         <f t="shared" si="3"/>
@@ -13518,7 +13527,7 @@
     <row r="91" spans="1:65">
       <c r="A91" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B91" t="str">
         <f t="shared" si="3"/>
@@ -13597,7 +13606,7 @@
     <row r="92" spans="1:65">
       <c r="A92" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B92" t="str">
         <f t="shared" si="3"/>
@@ -13676,7 +13685,7 @@
     <row r="93" spans="1:65">
       <c r="A93" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B93" t="str">
         <f t="shared" si="3"/>
@@ -13755,7 +13764,7 @@
     <row r="94" spans="1:65">
       <c r="A94" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B94" t="str">
         <f t="shared" si="3"/>
@@ -13834,7 +13843,7 @@
     <row r="95" spans="1:65">
       <c r="A95" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B95" t="str">
         <f t="shared" si="3"/>
@@ -13913,7 +13922,7 @@
     <row r="96" spans="1:65">
       <c r="A96" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B96" t="str">
         <f t="shared" si="3"/>
@@ -13992,7 +14001,7 @@
     <row r="97" spans="1:65">
       <c r="A97" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B97" t="str">
         <f t="shared" si="3"/>
@@ -14071,7 +14080,7 @@
     <row r="98" spans="1:65">
       <c r="A98" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B98" t="str">
         <f t="shared" si="3"/>
@@ -14150,7 +14159,7 @@
     <row r="99" spans="1:65">
       <c r="A99" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B99" t="str">
         <f t="shared" si="3"/>
@@ -14229,7 +14238,7 @@
     <row r="100" spans="1:65">
       <c r="A100" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B100" t="str">
         <f t="shared" si="3"/>
@@ -14310,7 +14319,7 @@
     <row r="101" spans="1:65">
       <c r="A101" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B101" t="str">
         <f t="shared" si="3"/>
@@ -14389,7 +14398,7 @@
     <row r="102" spans="1:65">
       <c r="A102" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B102" t="str">
         <f t="shared" si="3"/>
@@ -14468,7 +14477,7 @@
     <row r="103" spans="1:65">
       <c r="A103" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B103" t="str">
         <f t="shared" si="3"/>
@@ -14547,7 +14556,7 @@
     <row r="104" spans="1:65">
       <c r="A104" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B104" t="str">
         <f t="shared" si="3"/>
@@ -14626,7 +14635,7 @@
     <row r="105" spans="1:65">
       <c r="A105" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B105" t="str">
         <f t="shared" si="3"/>
@@ -14705,7 +14714,7 @@
     <row r="106" spans="1:65">
       <c r="A106" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B106" t="str">
         <f t="shared" si="3"/>
@@ -14786,7 +14795,7 @@
     <row r="107" spans="1:65">
       <c r="A107" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B107" t="str">
         <f t="shared" si="3"/>
@@ -14867,7 +14876,7 @@
     <row r="108" spans="1:65">
       <c r="A108" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B108" t="str">
         <f t="shared" si="3"/>
@@ -14946,7 +14955,7 @@
     <row r="109" spans="1:65">
       <c r="A109" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B109" t="str">
         <f t="shared" si="3"/>
@@ -15025,7 +15034,7 @@
     <row r="110" spans="1:65">
       <c r="A110" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B110" t="str">
         <f t="shared" si="3"/>
@@ -15104,7 +15113,7 @@
     <row r="111" spans="1:65">
       <c r="A111" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B111" t="str">
         <f t="shared" si="3"/>
@@ -15183,7 +15192,7 @@
     <row r="112" spans="1:65">
       <c r="A112" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B112" t="str">
         <f t="shared" si="3"/>
@@ -15264,7 +15273,7 @@
     <row r="113" spans="1:65">
       <c r="A113" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B113" t="str">
         <f t="shared" si="3"/>
@@ -15343,7 +15352,7 @@
     <row r="114" spans="1:65">
       <c r="A114" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B114" t="str">
         <f t="shared" si="3"/>
@@ -15422,7 +15431,7 @@
     <row r="115" spans="1:65">
       <c r="A115" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B115" t="str">
         <f t="shared" si="3"/>
@@ -15501,7 +15510,7 @@
     <row r="116" spans="1:65">
       <c r="A116" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B116" t="str">
         <f t="shared" si="3"/>
@@ -15580,7 +15589,7 @@
     <row r="117" spans="1:65">
       <c r="A117" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B117" t="str">
         <f t="shared" si="3"/>
@@ -15659,7 +15668,7 @@
     <row r="118" spans="1:65">
       <c r="A118" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B118" t="str">
         <f t="shared" si="3"/>
@@ -15738,7 +15747,7 @@
     <row r="119" spans="1:65">
       <c r="A119" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B119" t="str">
         <f t="shared" si="3"/>
@@ -15817,7 +15826,7 @@
     <row r="120" spans="1:65">
       <c r="A120" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B120" t="str">
         <f t="shared" si="3"/>
@@ -15896,7 +15905,7 @@
     <row r="121" spans="1:65">
       <c r="A121" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B121" t="str">
         <f t="shared" si="3"/>
@@ -15975,7 +15984,7 @@
     <row r="122" spans="1:65">
       <c r="A122" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B122" t="str">
         <f t="shared" si="3"/>
@@ -16054,7 +16063,7 @@
     <row r="123" spans="1:65">
       <c r="A123" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B123" t="str">
         <f t="shared" si="3"/>
@@ -16133,7 +16142,7 @@
     <row r="124" spans="1:65">
       <c r="A124" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B124" t="str">
         <f t="shared" si="3"/>
@@ -16214,7 +16223,7 @@
     <row r="125" spans="1:65">
       <c r="A125" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B125" t="str">
         <f t="shared" si="3"/>
@@ -16295,7 +16304,7 @@
     <row r="126" spans="1:65">
       <c r="A126" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B126" t="str">
         <f t="shared" si="3"/>
@@ -16374,7 +16383,7 @@
     <row r="127" spans="1:65">
       <c r="A127" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B127" t="str">
         <f t="shared" si="3"/>
@@ -16453,7 +16462,7 @@
     <row r="128" spans="1:65">
       <c r="A128" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B128" t="str">
         <f t="shared" si="3"/>
@@ -16532,7 +16541,7 @@
     <row r="129" spans="1:65">
       <c r="A129" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B129" t="str">
         <f t="shared" si="3"/>
@@ -16611,7 +16620,7 @@
     <row r="130" spans="1:65">
       <c r="A130" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B130" t="str">
         <f t="shared" si="3"/>
@@ -16690,7 +16699,7 @@
     <row r="131" spans="1:65">
       <c r="A131" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B131" t="str">
         <f t="shared" si="3"/>
@@ -16772,7 +16781,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B132" t="str">
         <f t="shared" ref="B132:B168" si="5">TEXT($C132, "HH:mm")</f>
@@ -16851,7 +16860,7 @@
     <row r="133" spans="1:65">
       <c r="A133" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B133" t="str">
         <f t="shared" si="5"/>
@@ -16930,7 +16939,7 @@
     <row r="134" spans="1:65">
       <c r="A134" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B134" t="str">
         <f t="shared" si="5"/>
@@ -17009,7 +17018,7 @@
     <row r="135" spans="1:65">
       <c r="A135" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B135" t="str">
         <f t="shared" si="5"/>
@@ -17088,7 +17097,7 @@
     <row r="136" spans="1:65">
       <c r="A136" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B136" t="str">
         <f t="shared" si="5"/>
@@ -17169,7 +17178,7 @@
     <row r="137" spans="1:65">
       <c r="A137" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B137" t="str">
         <f t="shared" si="5"/>
@@ -17250,7 +17259,7 @@
     <row r="138" spans="1:65">
       <c r="A138" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B138" t="str">
         <f t="shared" si="5"/>
@@ -17329,7 +17338,7 @@
     <row r="139" spans="1:65">
       <c r="A139" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B139" t="str">
         <f t="shared" si="5"/>
@@ -17408,7 +17417,7 @@
     <row r="140" spans="1:65">
       <c r="A140" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B140" t="str">
         <f t="shared" si="5"/>
@@ -17487,7 +17496,7 @@
     <row r="141" spans="1:65">
       <c r="A141" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B141" t="str">
         <f t="shared" si="5"/>
@@ -17566,7 +17575,7 @@
     <row r="142" spans="1:65">
       <c r="A142" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B142" t="str">
         <f t="shared" si="5"/>
@@ -17645,7 +17654,7 @@
     <row r="143" spans="1:65">
       <c r="A143" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B143" t="str">
         <f t="shared" si="5"/>
@@ -17724,7 +17733,7 @@
     <row r="144" spans="1:65">
       <c r="A144" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B144" t="str">
         <f t="shared" si="5"/>
@@ -17803,7 +17812,7 @@
     <row r="145" spans="1:65">
       <c r="A145" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B145" t="str">
         <f t="shared" si="5"/>
@@ -17882,7 +17891,7 @@
     <row r="146" spans="1:65">
       <c r="A146" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B146" t="str">
         <f t="shared" si="5"/>
@@ -17961,7 +17970,7 @@
     <row r="147" spans="1:65">
       <c r="A147" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B147" t="str">
         <f t="shared" si="5"/>
@@ -18040,7 +18049,7 @@
     <row r="148" spans="1:65">
       <c r="A148" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B148" t="str">
         <f t="shared" si="5"/>
@@ -18121,7 +18130,7 @@
     <row r="149" spans="1:65">
       <c r="A149" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B149" t="str">
         <f t="shared" si="5"/>
@@ -18200,7 +18209,7 @@
     <row r="150" spans="1:65">
       <c r="A150" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B150" t="str">
         <f t="shared" si="5"/>
@@ -18279,7 +18288,7 @@
     <row r="151" spans="1:65">
       <c r="A151" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B151" t="str">
         <f t="shared" si="5"/>
@@ -18358,7 +18367,7 @@
     <row r="152" spans="1:65">
       <c r="A152" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B152" t="str">
         <f t="shared" si="5"/>
@@ -18437,7 +18446,7 @@
     <row r="153" spans="1:65">
       <c r="A153" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B153" t="str">
         <f t="shared" si="5"/>
@@ -18516,7 +18525,7 @@
     <row r="154" spans="1:65">
       <c r="A154" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B154" t="str">
         <f t="shared" si="5"/>
@@ -18595,7 +18604,7 @@
     <row r="155" spans="1:65">
       <c r="A155" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B155" t="str">
         <f t="shared" si="5"/>
@@ -18674,7 +18683,7 @@
     <row r="156" spans="1:65">
       <c r="A156" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B156" t="str">
         <f t="shared" si="5"/>
@@ -18753,7 +18762,7 @@
     <row r="157" spans="1:65">
       <c r="A157" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B157" t="str">
         <f t="shared" si="5"/>
@@ -18832,7 +18841,7 @@
     <row r="158" spans="1:65">
       <c r="A158" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B158" t="str">
         <f t="shared" si="5"/>
@@ -18911,7 +18920,7 @@
     <row r="159" spans="1:65">
       <c r="A159" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B159" t="str">
         <f t="shared" si="5"/>
@@ -18990,7 +18999,7 @@
     <row r="160" spans="1:65">
       <c r="A160" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B160" t="str">
         <f t="shared" si="5"/>
@@ -19069,7 +19078,7 @@
     <row r="161" spans="1:65">
       <c r="A161" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B161" t="str">
         <f t="shared" si="5"/>
@@ -19148,7 +19157,7 @@
     <row r="162" spans="1:65">
       <c r="A162" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B162" t="str">
         <f t="shared" si="5"/>
@@ -19227,7 +19236,7 @@
     <row r="163" spans="1:65">
       <c r="A163" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B163" t="str">
         <f t="shared" si="5"/>
@@ -19306,7 +19315,7 @@
     <row r="164" spans="1:65">
       <c r="A164" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B164" t="str">
         <f t="shared" si="5"/>
@@ -19385,7 +19394,7 @@
     <row r="165" spans="1:65">
       <c r="A165" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B165" t="str">
         <f t="shared" si="5"/>
@@ -19464,7 +19473,7 @@
     <row r="166" spans="1:65">
       <c r="A166" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B166" t="str">
         <f t="shared" si="5"/>
@@ -19545,7 +19554,7 @@
     <row r="167" spans="1:65">
       <c r="A167" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B167" t="str">
         <f t="shared" si="5"/>
@@ -19624,7 +19633,7 @@
     <row r="168" spans="1:65">
       <c r="A168" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B168" t="str">
         <f t="shared" si="5"/>
@@ -19706,7 +19715,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B169" t="str">
         <f>TEXT($C169, "HH:mm")</f>
@@ -19788,7 +19797,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B170" t="str">
         <f t="shared" ref="B170:B233" si="7">TEXT($C170, "HH:mm")</f>
@@ -19867,7 +19876,7 @@
     <row r="171" spans="1:65">
       <c r="A171" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B171" t="str">
         <f t="shared" si="7"/>
@@ -19946,7 +19955,7 @@
     <row r="172" spans="1:65">
       <c r="A172" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B172" t="str">
         <f t="shared" si="7"/>
@@ -20027,7 +20036,7 @@
     <row r="173" spans="1:65">
       <c r="A173" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B173" t="str">
         <f t="shared" si="7"/>
@@ -20106,7 +20115,7 @@
     <row r="174" spans="1:65">
       <c r="A174" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B174" t="str">
         <f t="shared" si="7"/>
@@ -20185,7 +20194,7 @@
     <row r="175" spans="1:65">
       <c r="A175" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B175" t="str">
         <f t="shared" si="7"/>
@@ -20264,7 +20273,7 @@
     <row r="176" spans="1:65">
       <c r="A176" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B176" t="str">
         <f t="shared" si="7"/>
@@ -20343,7 +20352,7 @@
     <row r="177" spans="1:65">
       <c r="A177" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B177" t="str">
         <f t="shared" si="7"/>
@@ -20422,7 +20431,7 @@
     <row r="178" spans="1:65">
       <c r="A178" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B178" t="str">
         <f t="shared" si="7"/>
@@ -20503,7 +20512,7 @@
     <row r="179" spans="1:65">
       <c r="A179" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B179" t="str">
         <f t="shared" si="7"/>
@@ -20582,7 +20591,7 @@
     <row r="180" spans="1:65">
       <c r="A180" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B180" t="str">
         <f t="shared" si="7"/>
@@ -20661,7 +20670,7 @@
     <row r="181" spans="1:65">
       <c r="A181" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B181" t="str">
         <f t="shared" si="7"/>
@@ -20742,7 +20751,7 @@
     <row r="182" spans="1:65">
       <c r="A182" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B182" t="str">
         <f t="shared" si="7"/>
@@ -20823,7 +20832,7 @@
     <row r="183" spans="1:65">
       <c r="A183" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B183" t="str">
         <f t="shared" si="7"/>
@@ -20904,7 +20913,7 @@
     <row r="184" spans="1:65">
       <c r="A184" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B184" t="str">
         <f t="shared" si="7"/>
@@ -20987,7 +20996,7 @@
     <row r="185" spans="1:65">
       <c r="A185" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B185" t="str">
         <f t="shared" si="7"/>
@@ -21068,7 +21077,7 @@
     <row r="186" spans="1:65">
       <c r="A186" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B186" t="str">
         <f t="shared" si="7"/>
@@ -21149,7 +21158,7 @@
     <row r="187" spans="1:65">
       <c r="A187" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B187" t="str">
         <f t="shared" si="7"/>
@@ -21230,7 +21239,7 @@
     <row r="188" spans="1:65">
       <c r="A188" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B188" t="str">
         <f t="shared" si="7"/>
@@ -21311,7 +21320,7 @@
     <row r="189" spans="1:65">
       <c r="A189" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B189" t="str">
         <f t="shared" si="7"/>
@@ -21392,7 +21401,7 @@
     <row r="190" spans="1:65">
       <c r="A190" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B190" t="str">
         <f t="shared" si="7"/>
@@ -21475,7 +21484,7 @@
     <row r="191" spans="1:65">
       <c r="A191" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B191" t="str">
         <f t="shared" si="7"/>
@@ -21558,7 +21567,7 @@
     <row r="192" spans="1:65">
       <c r="A192" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B192" t="str">
         <f t="shared" si="7"/>
@@ -21641,7 +21650,7 @@
     <row r="193" spans="1:65">
       <c r="A193" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B193" t="str">
         <f t="shared" si="7"/>
@@ -21724,7 +21733,7 @@
     <row r="194" spans="1:65">
       <c r="A194" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B194" t="str">
         <f t="shared" si="7"/>
@@ -21805,7 +21814,7 @@
     <row r="195" spans="1:65">
       <c r="A195" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B195" t="str">
         <f t="shared" si="7"/>
@@ -21886,7 +21895,7 @@
     <row r="196" spans="1:65">
       <c r="A196" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B196" t="str">
         <f t="shared" si="7"/>
@@ -21969,7 +21978,7 @@
     <row r="197" spans="1:65">
       <c r="A197" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B197" t="str">
         <f t="shared" si="7"/>
@@ -22048,7 +22057,7 @@
     <row r="198" spans="1:65">
       <c r="A198" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B198" t="str">
         <f t="shared" si="7"/>
@@ -22127,7 +22136,7 @@
     <row r="199" spans="1:65">
       <c r="A199" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B199" t="str">
         <f t="shared" si="7"/>
@@ -22206,7 +22215,7 @@
     <row r="200" spans="1:65">
       <c r="A200" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B200" t="str">
         <f t="shared" si="7"/>
@@ -22285,7 +22294,7 @@
     <row r="201" spans="1:65">
       <c r="A201" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B201" t="str">
         <f t="shared" si="7"/>
@@ -22364,7 +22373,7 @@
     <row r="202" spans="1:65">
       <c r="A202" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B202" t="str">
         <f t="shared" si="7"/>
@@ -22445,7 +22454,7 @@
     <row r="203" spans="1:65">
       <c r="A203" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B203" t="str">
         <f t="shared" si="7"/>
@@ -22524,7 +22533,7 @@
     <row r="204" spans="1:65">
       <c r="A204" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B204" t="str">
         <f t="shared" si="7"/>
@@ -22603,7 +22612,7 @@
     <row r="205" spans="1:65">
       <c r="A205" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B205" t="str">
         <f t="shared" si="7"/>
@@ -22682,7 +22691,7 @@
     <row r="206" spans="1:65">
       <c r="A206" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B206" t="str">
         <f t="shared" si="7"/>
@@ -22761,7 +22770,7 @@
     <row r="207" spans="1:65">
       <c r="A207" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B207" t="str">
         <f t="shared" si="7"/>
@@ -22840,7 +22849,7 @@
     <row r="208" spans="1:65">
       <c r="A208" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B208" t="str">
         <f t="shared" si="7"/>
@@ -22921,7 +22930,7 @@
     <row r="209" spans="1:65">
       <c r="A209" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B209" t="str">
         <f t="shared" si="7"/>
@@ -23000,7 +23009,7 @@
     <row r="210" spans="1:65">
       <c r="A210" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B210" t="str">
         <f t="shared" si="7"/>
@@ -23079,7 +23088,7 @@
     <row r="211" spans="1:65">
       <c r="A211" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B211" t="str">
         <f t="shared" si="7"/>
@@ -23160,7 +23169,7 @@
     <row r="212" spans="1:65">
       <c r="A212" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B212" t="str">
         <f t="shared" si="7"/>
@@ -23239,7 +23248,7 @@
     <row r="213" spans="1:65">
       <c r="A213" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B213" t="str">
         <f t="shared" si="7"/>
@@ -23318,7 +23327,7 @@
     <row r="214" spans="1:65">
       <c r="A214" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B214" t="str">
         <f t="shared" si="7"/>
@@ -23397,7 +23406,7 @@
     <row r="215" spans="1:65">
       <c r="A215" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B215" t="str">
         <f t="shared" si="7"/>
@@ -23476,7 +23485,7 @@
     <row r="216" spans="1:65">
       <c r="A216" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B216" t="str">
         <f t="shared" si="7"/>
@@ -23555,7 +23564,7 @@
     <row r="217" spans="1:65">
       <c r="A217" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B217" t="str">
         <f t="shared" si="7"/>
@@ -23634,7 +23643,7 @@
     <row r="218" spans="1:65">
       <c r="A218" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B218" t="str">
         <f t="shared" si="7"/>
@@ -23713,7 +23722,7 @@
     <row r="219" spans="1:65">
       <c r="A219" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B219" t="str">
         <f t="shared" si="7"/>
@@ -23792,7 +23801,7 @@
     <row r="220" spans="1:65">
       <c r="A220" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B220" t="str">
         <f t="shared" si="7"/>
@@ -23873,7 +23882,7 @@
     <row r="221" spans="1:65">
       <c r="A221" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B221" t="str">
         <f t="shared" si="7"/>
@@ -23952,7 +23961,7 @@
     <row r="222" spans="1:65">
       <c r="A222" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B222" t="str">
         <f t="shared" si="7"/>
@@ -24031,7 +24040,7 @@
     <row r="223" spans="1:65">
       <c r="A223" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B223" t="str">
         <f t="shared" si="7"/>
@@ -24110,7 +24119,7 @@
     <row r="224" spans="1:65">
       <c r="A224" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B224" t="str">
         <f t="shared" si="7"/>
@@ -24189,7 +24198,7 @@
     <row r="225" spans="1:65">
       <c r="A225" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B225" t="str">
         <f t="shared" si="7"/>
@@ -24268,7 +24277,7 @@
     <row r="226" spans="1:65">
       <c r="A226" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B226" t="str">
         <f t="shared" si="7"/>
@@ -24347,7 +24356,7 @@
     <row r="227" spans="1:65">
       <c r="A227" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B227" t="str">
         <f t="shared" si="7"/>
@@ -24426,7 +24435,7 @@
     <row r="228" spans="1:65">
       <c r="A228" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B228" t="str">
         <f t="shared" si="7"/>
@@ -24505,7 +24514,7 @@
     <row r="229" spans="1:65">
       <c r="A229" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B229" t="str">
         <f t="shared" si="7"/>
@@ -24584,7 +24593,7 @@
     <row r="230" spans="1:65">
       <c r="A230" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B230" t="str">
         <f t="shared" si="7"/>
@@ -24663,7 +24672,7 @@
     <row r="231" spans="1:65">
       <c r="A231" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B231" t="str">
         <f t="shared" si="7"/>
@@ -24742,7 +24751,7 @@
     <row r="232" spans="1:65">
       <c r="A232" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B232" t="str">
         <f t="shared" si="7"/>
@@ -24821,7 +24830,7 @@
     <row r="233" spans="1:65">
       <c r="A233" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B233" t="str">
         <f t="shared" si="7"/>
@@ -24903,7 +24912,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B234" t="str">
         <f t="shared" ref="B234:B291" si="9">TEXT($C234, "HH:mm")</f>
@@ -24982,7 +24991,7 @@
     <row r="235" spans="1:65">
       <c r="A235" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B235" t="str">
         <f t="shared" si="9"/>
@@ -25061,7 +25070,7 @@
     <row r="236" spans="1:65">
       <c r="A236" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B236" t="str">
         <f t="shared" si="9"/>
@@ -25140,7 +25149,7 @@
     <row r="237" spans="1:65">
       <c r="A237" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B237" t="str">
         <f t="shared" si="9"/>
@@ -25219,7 +25228,7 @@
     <row r="238" spans="1:65">
       <c r="A238" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B238" t="str">
         <f t="shared" si="9"/>
@@ -25298,7 +25307,7 @@
     <row r="239" spans="1:65">
       <c r="A239" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B239" t="str">
         <f t="shared" si="9"/>
@@ -25377,7 +25386,7 @@
     <row r="240" spans="1:65">
       <c r="A240" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B240" t="str">
         <f t="shared" si="9"/>
@@ -25456,7 +25465,7 @@
     <row r="241" spans="1:65">
       <c r="A241" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B241" t="str">
         <f t="shared" si="9"/>
@@ -25535,7 +25544,7 @@
     <row r="242" spans="1:65">
       <c r="A242" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B242" t="str">
         <f t="shared" si="9"/>
@@ -25614,7 +25623,7 @@
     <row r="243" spans="1:65">
       <c r="A243" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B243" t="str">
         <f t="shared" si="9"/>
@@ -25693,7 +25702,7 @@
     <row r="244" spans="1:65">
       <c r="A244" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B244" t="str">
         <f t="shared" si="9"/>
@@ -25772,7 +25781,7 @@
     <row r="245" spans="1:65">
       <c r="A245" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B245" t="str">
         <f t="shared" si="9"/>
@@ -25851,7 +25860,7 @@
     <row r="246" spans="1:65">
       <c r="A246" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B246" t="str">
         <f t="shared" si="9"/>
@@ -25930,7 +25939,7 @@
     <row r="247" spans="1:65">
       <c r="A247" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B247" t="str">
         <f t="shared" si="9"/>
@@ -26009,7 +26018,7 @@
     <row r="248" spans="1:65">
       <c r="A248" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B248" t="str">
         <f t="shared" si="9"/>
@@ -26088,7 +26097,7 @@
     <row r="249" spans="1:65">
       <c r="A249" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B249" t="str">
         <f t="shared" si="9"/>
@@ -26167,7 +26176,7 @@
     <row r="250" spans="1:65">
       <c r="A250" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B250" t="str">
         <f t="shared" si="9"/>
@@ -26246,7 +26255,7 @@
     <row r="251" spans="1:65">
       <c r="A251" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B251" t="str">
         <f t="shared" si="9"/>
@@ -26325,7 +26334,7 @@
     <row r="252" spans="1:65">
       <c r="A252" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B252" t="str">
         <f t="shared" si="9"/>
@@ -26404,7 +26413,7 @@
     <row r="253" spans="1:65">
       <c r="A253" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B253" t="str">
         <f t="shared" si="9"/>
@@ -26483,7 +26492,7 @@
     <row r="254" spans="1:65">
       <c r="A254" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B254" t="str">
         <f t="shared" si="9"/>
@@ -26562,7 +26571,7 @@
     <row r="255" spans="1:65">
       <c r="A255" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B255" t="str">
         <f t="shared" si="9"/>
@@ -26641,7 +26650,7 @@
     <row r="256" spans="1:65">
       <c r="A256" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B256" t="str">
         <f t="shared" si="9"/>
@@ -26720,7 +26729,7 @@
     <row r="257" spans="1:65">
       <c r="A257" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B257" t="str">
         <f t="shared" si="9"/>
@@ -26799,7 +26808,7 @@
     <row r="258" spans="1:65">
       <c r="A258" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B258" t="str">
         <f t="shared" si="9"/>
@@ -26878,7 +26887,7 @@
     <row r="259" spans="1:65">
       <c r="A259" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B259" t="str">
         <f t="shared" si="9"/>
@@ -26957,7 +26966,7 @@
     <row r="260" spans="1:65">
       <c r="A260" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B260" t="str">
         <f t="shared" si="9"/>
@@ -27036,7 +27045,7 @@
     <row r="261" spans="1:65">
       <c r="A261" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B261" t="str">
         <f t="shared" si="9"/>
@@ -27115,7 +27124,7 @@
     <row r="262" spans="1:65">
       <c r="A262" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B262" t="str">
         <f t="shared" si="9"/>
@@ -27194,7 +27203,7 @@
     <row r="263" spans="1:65">
       <c r="A263" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B263" t="str">
         <f t="shared" si="9"/>
@@ -27273,7 +27282,7 @@
     <row r="264" spans="1:65">
       <c r="A264" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B264" t="str">
         <f t="shared" si="9"/>
@@ -27352,7 +27361,7 @@
     <row r="265" spans="1:65">
       <c r="A265" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B265" t="str">
         <f t="shared" si="9"/>
@@ -27431,7 +27440,7 @@
     <row r="266" spans="1:65">
       <c r="A266" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B266" t="str">
         <f t="shared" si="9"/>
@@ -27510,7 +27519,7 @@
     <row r="267" spans="1:65">
       <c r="A267" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B267" t="str">
         <f t="shared" si="9"/>
@@ -27589,7 +27598,7 @@
     <row r="268" spans="1:65">
       <c r="A268" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B268" t="str">
         <f t="shared" si="9"/>
@@ -27668,7 +27677,7 @@
     <row r="269" spans="1:65">
       <c r="A269" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B269" t="str">
         <f t="shared" si="9"/>
@@ -27747,7 +27756,7 @@
     <row r="270" spans="1:65">
       <c r="A270" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B270" t="str">
         <f t="shared" si="9"/>
@@ -27826,7 +27835,7 @@
     <row r="271" spans="1:65">
       <c r="A271" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B271" t="str">
         <f t="shared" si="9"/>
@@ -27905,7 +27914,7 @@
     <row r="272" spans="1:65">
       <c r="A272" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B272" t="str">
         <f t="shared" si="9"/>
@@ -27984,7 +27993,7 @@
     <row r="273" spans="1:65">
       <c r="A273" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B273" t="str">
         <f t="shared" si="9"/>
@@ -28063,7 +28072,7 @@
     <row r="274" spans="1:65">
       <c r="A274" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B274" t="str">
         <f t="shared" si="9"/>
@@ -28142,7 +28151,7 @@
     <row r="275" spans="1:65">
       <c r="A275" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B275" t="str">
         <f t="shared" si="9"/>
@@ -28221,7 +28230,7 @@
     <row r="276" spans="1:65">
       <c r="A276" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B276" t="str">
         <f t="shared" si="9"/>
@@ -28300,7 +28309,7 @@
     <row r="277" spans="1:65">
       <c r="A277" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B277" t="str">
         <f t="shared" si="9"/>
@@ -28379,7 +28388,7 @@
     <row r="278" spans="1:65">
       <c r="A278" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B278" t="str">
         <f t="shared" si="9"/>
@@ -28458,7 +28467,7 @@
     <row r="279" spans="1:65">
       <c r="A279" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B279" t="str">
         <f t="shared" si="9"/>
@@ -28537,7 +28546,7 @@
     <row r="280" spans="1:65">
       <c r="A280" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B280" t="str">
         <f t="shared" si="9"/>
@@ -28616,7 +28625,7 @@
     <row r="281" spans="1:65">
       <c r="A281" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B281" t="str">
         <f t="shared" si="9"/>
@@ -28695,7 +28704,7 @@
     <row r="282" spans="1:65">
       <c r="A282" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B282" t="str">
         <f t="shared" si="9"/>
@@ -28774,7 +28783,7 @@
     <row r="283" spans="1:65">
       <c r="A283" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B283" t="str">
         <f t="shared" si="9"/>
@@ -28853,7 +28862,7 @@
     <row r="284" spans="1:65">
       <c r="A284" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B284" t="str">
         <f t="shared" si="9"/>
@@ -28932,7 +28941,7 @@
     <row r="285" spans="1:65">
       <c r="A285" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B285" t="str">
         <f t="shared" si="9"/>
@@ -29011,7 +29020,7 @@
     <row r="286" spans="1:65">
       <c r="A286" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B286" t="str">
         <f t="shared" si="9"/>
@@ -29090,7 +29099,7 @@
     <row r="287" spans="1:65">
       <c r="A287" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B287" t="str">
         <f t="shared" si="9"/>
@@ -29169,7 +29178,7 @@
     <row r="288" spans="1:65">
       <c r="A288" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B288" t="str">
         <f t="shared" si="9"/>
@@ -29248,7 +29257,7 @@
     <row r="289" spans="1:65">
       <c r="A289" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B289" t="str">
         <f t="shared" si="9"/>
@@ -29327,7 +29336,7 @@
     <row r="290" spans="1:65">
       <c r="A290" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B290" t="str">
         <f t="shared" si="9"/>
@@ -29406,7 +29415,7 @@
     <row r="291" spans="1:65">
       <c r="A291" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:20</v>
+        <v>01:25</v>
       </c>
       <c r="B291" t="str">
         <f t="shared" si="9"/>

--- a/Vite-Vercel開発.xlsx
+++ b/Vite-Vercel開発.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2c67ec30e06f060f/work/GitHub/work-time-tracker/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{1928CA11-C4AD-40E9-B1C5-143667E830EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{64C4BBF7-1515-4183-BBF0-04780074AFB2}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{1928CA11-C4AD-40E9-B1C5-143667E830EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{010239F8-1112-42A6-A678-DAF2809917FF}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1541" uniqueCount="919">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1542" uniqueCount="920">
   <si>
     <t>npm install -g vercel</t>
     <phoneticPr fontId="1"/>
@@ -5354,6 +5354,10 @@
   </si>
   <si>
     <t>Found 64 errors in 16 files.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Found 62 errors in 15 files.</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -6126,7 +6130,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{083174DA-A42C-4F9C-978E-61AEAAD9DDFF}">
-  <dimension ref="B2:D23"/>
+  <dimension ref="B2:D24"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
@@ -6249,6 +6253,11 @@
     <row r="23" spans="3:3">
       <c r="C23" t="s">
         <v>918</v>
+      </c>
+    </row>
+    <row r="24" spans="3:3">
+      <c r="C24" t="s">
+        <v>919</v>
       </c>
     </row>
   </sheetData>
@@ -6415,7 +6424,7 @@
       MOD(NOW(),1),
       TIME(0,5,0)
     ),"HH:mm")</f>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B2" s="19"/>
       <c r="D2" s="1">
@@ -6426,7 +6435,7 @@
     <row r="3" spans="1:65">
       <c r="A3" s="19" t="str">
         <f ca="1">TEXT(NOW(),"HH:mm")</f>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="17" t="s">
@@ -6625,7 +6634,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B4" t="str">
         <f t="shared" ref="B4:B67" si="1">TEXT($C4, "HH:mm")</f>
@@ -6704,7 +6713,7 @@
     <row r="5" spans="1:65">
       <c r="A5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B5" t="str">
         <f t="shared" si="1"/>
@@ -6783,7 +6792,7 @@
     <row r="6" spans="1:65">
       <c r="A6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B6" t="str">
         <f t="shared" si="1"/>
@@ -6862,7 +6871,7 @@
     <row r="7" spans="1:65">
       <c r="A7" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B7" t="str">
         <f t="shared" si="1"/>
@@ -6941,7 +6950,7 @@
     <row r="8" spans="1:65">
       <c r="A8" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B8" t="str">
         <f t="shared" si="1"/>
@@ -7020,7 +7029,7 @@
     <row r="9" spans="1:65">
       <c r="A9" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B9" t="str">
         <f t="shared" si="1"/>
@@ -7099,7 +7108,7 @@
     <row r="10" spans="1:65">
       <c r="A10" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B10" t="str">
         <f t="shared" si="1"/>
@@ -7178,7 +7187,7 @@
     <row r="11" spans="1:65">
       <c r="A11" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B11" t="str">
         <f t="shared" si="1"/>
@@ -7257,7 +7266,7 @@
     <row r="12" spans="1:65">
       <c r="A12" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B12" t="str">
         <f t="shared" si="1"/>
@@ -7336,7 +7345,7 @@
     <row r="13" spans="1:65">
       <c r="A13" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B13" t="str">
         <f t="shared" si="1"/>
@@ -7415,7 +7424,7 @@
     <row r="14" spans="1:65">
       <c r="A14" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B14" t="str">
         <f t="shared" si="1"/>
@@ -7494,7 +7503,7 @@
     <row r="15" spans="1:65">
       <c r="A15" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B15" t="str">
         <f t="shared" si="1"/>
@@ -7573,7 +7582,7 @@
     <row r="16" spans="1:65">
       <c r="A16" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B16" t="str">
         <f t="shared" si="1"/>
@@ -7652,7 +7661,7 @@
     <row r="17" spans="1:65">
       <c r="A17" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B17" t="str">
         <f t="shared" si="1"/>
@@ -7731,7 +7740,7 @@
     <row r="18" spans="1:65">
       <c r="A18" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B18" t="str">
         <f t="shared" si="1"/>
@@ -7810,7 +7819,7 @@
     <row r="19" spans="1:65">
       <c r="A19" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B19" t="str">
         <f t="shared" si="1"/>
@@ -7889,7 +7898,7 @@
     <row r="20" spans="1:65">
       <c r="A20" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B20" t="str">
         <f t="shared" si="1"/>
@@ -7968,7 +7977,7 @@
     <row r="21" spans="1:65">
       <c r="A21" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B21" t="str">
         <f t="shared" si="1"/>
@@ -8047,7 +8056,7 @@
     <row r="22" spans="1:65">
       <c r="A22" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B22" t="str">
         <f t="shared" si="1"/>
@@ -8126,7 +8135,7 @@
     <row r="23" spans="1:65">
       <c r="A23" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B23" t="str">
         <f t="shared" si="1"/>
@@ -8205,7 +8214,7 @@
     <row r="24" spans="1:65">
       <c r="A24" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B24" t="str">
         <f t="shared" si="1"/>
@@ -8284,7 +8293,7 @@
     <row r="25" spans="1:65">
       <c r="A25" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B25" t="str">
         <f t="shared" si="1"/>
@@ -8363,7 +8372,7 @@
     <row r="26" spans="1:65">
       <c r="A26" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B26" t="str">
         <f t="shared" si="1"/>
@@ -8442,7 +8451,7 @@
     <row r="27" spans="1:65">
       <c r="A27" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B27" t="str">
         <f t="shared" si="1"/>
@@ -8521,7 +8530,7 @@
     <row r="28" spans="1:65">
       <c r="A28" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B28" t="str">
         <f t="shared" si="1"/>
@@ -8602,7 +8611,7 @@
     <row r="29" spans="1:65">
       <c r="A29" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B29" t="str">
         <f t="shared" si="1"/>
@@ -8683,7 +8692,7 @@
     <row r="30" spans="1:65">
       <c r="A30" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B30" t="str">
         <f t="shared" si="1"/>
@@ -8764,7 +8773,7 @@
     <row r="31" spans="1:65">
       <c r="A31" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B31" t="str">
         <f t="shared" si="1"/>
@@ -8843,7 +8852,7 @@
     <row r="32" spans="1:65">
       <c r="A32" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B32" t="str">
         <f t="shared" si="1"/>
@@ -8922,7 +8931,7 @@
     <row r="33" spans="1:65">
       <c r="A33" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B33" t="str">
         <f t="shared" si="1"/>
@@ -9001,7 +9010,7 @@
     <row r="34" spans="1:65">
       <c r="A34" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B34" t="str">
         <f t="shared" si="1"/>
@@ -9082,7 +9091,7 @@
     <row r="35" spans="1:65">
       <c r="A35" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B35" t="str">
         <f t="shared" si="1"/>
@@ -9163,7 +9172,7 @@
     <row r="36" spans="1:65">
       <c r="A36" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B36" t="str">
         <f t="shared" si="1"/>
@@ -9244,7 +9253,7 @@
     <row r="37" spans="1:65">
       <c r="A37" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B37" t="str">
         <f t="shared" si="1"/>
@@ -9323,7 +9332,7 @@
     <row r="38" spans="1:65">
       <c r="A38" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B38" t="str">
         <f t="shared" si="1"/>
@@ -9402,7 +9411,7 @@
     <row r="39" spans="1:65">
       <c r="A39" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B39" t="str">
         <f t="shared" si="1"/>
@@ -9481,7 +9490,7 @@
     <row r="40" spans="1:65">
       <c r="A40" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B40" t="str">
         <f t="shared" si="1"/>
@@ -9560,7 +9569,7 @@
     <row r="41" spans="1:65">
       <c r="A41" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B41" t="str">
         <f t="shared" si="1"/>
@@ -9639,7 +9648,7 @@
     <row r="42" spans="1:65">
       <c r="A42" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B42" t="str">
         <f t="shared" si="1"/>
@@ -9720,7 +9729,7 @@
     <row r="43" spans="1:65">
       <c r="A43" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B43" t="str">
         <f t="shared" si="1"/>
@@ -9801,7 +9810,7 @@
     <row r="44" spans="1:65">
       <c r="A44" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B44" t="str">
         <f t="shared" si="1"/>
@@ -9880,7 +9889,7 @@
     <row r="45" spans="1:65">
       <c r="A45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B45" t="str">
         <f t="shared" si="1"/>
@@ -9959,7 +9968,7 @@
     <row r="46" spans="1:65">
       <c r="A46" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B46" t="str">
         <f t="shared" si="1"/>
@@ -10038,7 +10047,7 @@
     <row r="47" spans="1:65">
       <c r="A47" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B47" t="str">
         <f t="shared" si="1"/>
@@ -10117,7 +10126,7 @@
     <row r="48" spans="1:65">
       <c r="A48" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B48" t="str">
         <f t="shared" si="1"/>
@@ -10196,7 +10205,7 @@
     <row r="49" spans="1:65">
       <c r="A49" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B49" t="str">
         <f t="shared" si="1"/>
@@ -10277,7 +10286,7 @@
     <row r="50" spans="1:65">
       <c r="A50" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B50" t="str">
         <f t="shared" si="1"/>
@@ -10358,7 +10367,7 @@
     <row r="51" spans="1:65">
       <c r="A51" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B51" t="str">
         <f t="shared" si="1"/>
@@ -10437,7 +10446,7 @@
     <row r="52" spans="1:65">
       <c r="A52" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B52" t="str">
         <f t="shared" si="1"/>
@@ -10516,7 +10525,7 @@
     <row r="53" spans="1:65">
       <c r="A53" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B53" t="str">
         <f t="shared" si="1"/>
@@ -10595,7 +10604,7 @@
     <row r="54" spans="1:65">
       <c r="A54" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B54" t="str">
         <f t="shared" si="1"/>
@@ -10674,7 +10683,7 @@
     <row r="55" spans="1:65">
       <c r="A55" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B55" t="str">
         <f t="shared" si="1"/>
@@ -10753,7 +10762,7 @@
     <row r="56" spans="1:65">
       <c r="A56" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B56" t="str">
         <f t="shared" si="1"/>
@@ -10834,7 +10843,7 @@
     <row r="57" spans="1:65">
       <c r="A57" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B57" t="str">
         <f t="shared" si="1"/>
@@ -10913,7 +10922,7 @@
     <row r="58" spans="1:65">
       <c r="A58" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B58" t="str">
         <f t="shared" si="1"/>
@@ -10994,7 +11003,7 @@
     <row r="59" spans="1:65">
       <c r="A59" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B59" t="str">
         <f t="shared" si="1"/>
@@ -11073,7 +11082,7 @@
     <row r="60" spans="1:65">
       <c r="A60" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B60" t="str">
         <f t="shared" si="1"/>
@@ -11152,7 +11161,7 @@
     <row r="61" spans="1:65">
       <c r="A61" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B61" t="str">
         <f t="shared" si="1"/>
@@ -11231,7 +11240,7 @@
     <row r="62" spans="1:65">
       <c r="A62" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B62" t="str">
         <f t="shared" si="1"/>
@@ -11310,7 +11319,7 @@
     <row r="63" spans="1:65">
       <c r="A63" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B63" t="str">
         <f t="shared" si="1"/>
@@ -11389,7 +11398,7 @@
     <row r="64" spans="1:65">
       <c r="A64" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B64" t="str">
         <f t="shared" si="1"/>
@@ -11470,7 +11479,7 @@
     <row r="65" spans="1:65">
       <c r="A65" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B65" t="str">
         <f t="shared" si="1"/>
@@ -11549,7 +11558,7 @@
     <row r="66" spans="1:65">
       <c r="A66" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B66" t="str">
         <f t="shared" si="1"/>
@@ -11628,7 +11637,7 @@
     <row r="67" spans="1:65">
       <c r="A67" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B67" t="str">
         <f t="shared" si="1"/>
@@ -11710,7 +11719,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B68" t="str">
         <f t="shared" ref="B68:B131" si="3">TEXT($C68, "HH:mm")</f>
@@ -11789,7 +11798,7 @@
     <row r="69" spans="1:65">
       <c r="A69" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B69" t="str">
         <f t="shared" si="3"/>
@@ -11868,7 +11877,7 @@
     <row r="70" spans="1:65">
       <c r="A70" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B70" t="str">
         <f t="shared" si="3"/>
@@ -11947,7 +11956,7 @@
     <row r="71" spans="1:65">
       <c r="A71" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B71" t="str">
         <f t="shared" si="3"/>
@@ -12026,7 +12035,7 @@
     <row r="72" spans="1:65">
       <c r="A72" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B72" t="str">
         <f t="shared" si="3"/>
@@ -12105,7 +12114,7 @@
     <row r="73" spans="1:65">
       <c r="A73" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B73" t="str">
         <f t="shared" si="3"/>
@@ -12184,7 +12193,7 @@
     <row r="74" spans="1:65">
       <c r="A74" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B74" t="str">
         <f t="shared" si="3"/>
@@ -12263,7 +12272,7 @@
     <row r="75" spans="1:65">
       <c r="A75" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B75" t="str">
         <f t="shared" si="3"/>
@@ -12342,7 +12351,7 @@
     <row r="76" spans="1:65">
       <c r="A76" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B76" t="str">
         <f t="shared" si="3"/>
@@ -12421,7 +12430,7 @@
     <row r="77" spans="1:65">
       <c r="A77" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B77" t="str">
         <f t="shared" si="3"/>
@@ -12500,7 +12509,7 @@
     <row r="78" spans="1:65">
       <c r="A78" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B78" t="str">
         <f t="shared" si="3"/>
@@ -12579,7 +12588,7 @@
     <row r="79" spans="1:65">
       <c r="A79" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B79" t="str">
         <f t="shared" si="3"/>
@@ -12658,7 +12667,7 @@
     <row r="80" spans="1:65">
       <c r="A80" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B80" t="str">
         <f t="shared" si="3"/>
@@ -12737,7 +12746,7 @@
     <row r="81" spans="1:65">
       <c r="A81" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B81" t="str">
         <f t="shared" si="3"/>
@@ -12816,7 +12825,7 @@
     <row r="82" spans="1:65">
       <c r="A82" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B82" t="str">
         <f t="shared" si="3"/>
@@ -12895,7 +12904,7 @@
     <row r="83" spans="1:65">
       <c r="A83" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B83" t="str">
         <f t="shared" si="3"/>
@@ -12974,7 +12983,7 @@
     <row r="84" spans="1:65">
       <c r="A84" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B84" t="str">
         <f t="shared" si="3"/>
@@ -13053,7 +13062,7 @@
     <row r="85" spans="1:65">
       <c r="A85" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B85" t="str">
         <f t="shared" si="3"/>
@@ -13132,7 +13141,7 @@
     <row r="86" spans="1:65">
       <c r="A86" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B86" t="str">
         <f t="shared" si="3"/>
@@ -13211,7 +13220,7 @@
     <row r="87" spans="1:65">
       <c r="A87" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B87" t="str">
         <f t="shared" si="3"/>
@@ -13290,7 +13299,7 @@
     <row r="88" spans="1:65">
       <c r="A88" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B88" t="str">
         <f t="shared" si="3"/>
@@ -13369,7 +13378,7 @@
     <row r="89" spans="1:65">
       <c r="A89" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B89" t="str">
         <f t="shared" si="3"/>
@@ -13448,7 +13457,7 @@
     <row r="90" spans="1:65">
       <c r="A90" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B90" t="str">
         <f t="shared" si="3"/>
@@ -13527,7 +13536,7 @@
     <row r="91" spans="1:65">
       <c r="A91" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B91" t="str">
         <f t="shared" si="3"/>
@@ -13606,7 +13615,7 @@
     <row r="92" spans="1:65">
       <c r="A92" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B92" t="str">
         <f t="shared" si="3"/>
@@ -13685,7 +13694,7 @@
     <row r="93" spans="1:65">
       <c r="A93" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B93" t="str">
         <f t="shared" si="3"/>
@@ -13764,7 +13773,7 @@
     <row r="94" spans="1:65">
       <c r="A94" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B94" t="str">
         <f t="shared" si="3"/>
@@ -13843,7 +13852,7 @@
     <row r="95" spans="1:65">
       <c r="A95" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B95" t="str">
         <f t="shared" si="3"/>
@@ -13922,7 +13931,7 @@
     <row r="96" spans="1:65">
       <c r="A96" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B96" t="str">
         <f t="shared" si="3"/>
@@ -14001,7 +14010,7 @@
     <row r="97" spans="1:65">
       <c r="A97" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B97" t="str">
         <f t="shared" si="3"/>
@@ -14080,7 +14089,7 @@
     <row r="98" spans="1:65">
       <c r="A98" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B98" t="str">
         <f t="shared" si="3"/>
@@ -14159,7 +14168,7 @@
     <row r="99" spans="1:65">
       <c r="A99" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B99" t="str">
         <f t="shared" si="3"/>
@@ -14238,7 +14247,7 @@
     <row r="100" spans="1:65">
       <c r="A100" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B100" t="str">
         <f t="shared" si="3"/>
@@ -14319,7 +14328,7 @@
     <row r="101" spans="1:65">
       <c r="A101" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B101" t="str">
         <f t="shared" si="3"/>
@@ -14398,7 +14407,7 @@
     <row r="102" spans="1:65">
       <c r="A102" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B102" t="str">
         <f t="shared" si="3"/>
@@ -14477,7 +14486,7 @@
     <row r="103" spans="1:65">
       <c r="A103" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B103" t="str">
         <f t="shared" si="3"/>
@@ -14556,7 +14565,7 @@
     <row r="104" spans="1:65">
       <c r="A104" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B104" t="str">
         <f t="shared" si="3"/>
@@ -14635,7 +14644,7 @@
     <row r="105" spans="1:65">
       <c r="A105" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B105" t="str">
         <f t="shared" si="3"/>
@@ -14714,7 +14723,7 @@
     <row r="106" spans="1:65">
       <c r="A106" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B106" t="str">
         <f t="shared" si="3"/>
@@ -14795,7 +14804,7 @@
     <row r="107" spans="1:65">
       <c r="A107" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B107" t="str">
         <f t="shared" si="3"/>
@@ -14876,7 +14885,7 @@
     <row r="108" spans="1:65">
       <c r="A108" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B108" t="str">
         <f t="shared" si="3"/>
@@ -14955,7 +14964,7 @@
     <row r="109" spans="1:65">
       <c r="A109" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B109" t="str">
         <f t="shared" si="3"/>
@@ -15034,7 +15043,7 @@
     <row r="110" spans="1:65">
       <c r="A110" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B110" t="str">
         <f t="shared" si="3"/>
@@ -15113,7 +15122,7 @@
     <row r="111" spans="1:65">
       <c r="A111" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B111" t="str">
         <f t="shared" si="3"/>
@@ -15192,7 +15201,7 @@
     <row r="112" spans="1:65">
       <c r="A112" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B112" t="str">
         <f t="shared" si="3"/>
@@ -15273,7 +15282,7 @@
     <row r="113" spans="1:65">
       <c r="A113" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B113" t="str">
         <f t="shared" si="3"/>
@@ -15352,7 +15361,7 @@
     <row r="114" spans="1:65">
       <c r="A114" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B114" t="str">
         <f t="shared" si="3"/>
@@ -15431,7 +15440,7 @@
     <row r="115" spans="1:65">
       <c r="A115" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B115" t="str">
         <f t="shared" si="3"/>
@@ -15510,7 +15519,7 @@
     <row r="116" spans="1:65">
       <c r="A116" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B116" t="str">
         <f t="shared" si="3"/>
@@ -15589,7 +15598,7 @@
     <row r="117" spans="1:65">
       <c r="A117" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B117" t="str">
         <f t="shared" si="3"/>
@@ -15668,7 +15677,7 @@
     <row r="118" spans="1:65">
       <c r="A118" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B118" t="str">
         <f t="shared" si="3"/>
@@ -15747,7 +15756,7 @@
     <row r="119" spans="1:65">
       <c r="A119" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B119" t="str">
         <f t="shared" si="3"/>
@@ -15826,7 +15835,7 @@
     <row r="120" spans="1:65">
       <c r="A120" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B120" t="str">
         <f t="shared" si="3"/>
@@ -15905,7 +15914,7 @@
     <row r="121" spans="1:65">
       <c r="A121" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B121" t="str">
         <f t="shared" si="3"/>
@@ -15984,7 +15993,7 @@
     <row r="122" spans="1:65">
       <c r="A122" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B122" t="str">
         <f t="shared" si="3"/>
@@ -16063,7 +16072,7 @@
     <row r="123" spans="1:65">
       <c r="A123" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B123" t="str">
         <f t="shared" si="3"/>
@@ -16142,7 +16151,7 @@
     <row r="124" spans="1:65">
       <c r="A124" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B124" t="str">
         <f t="shared" si="3"/>
@@ -16223,7 +16232,7 @@
     <row r="125" spans="1:65">
       <c r="A125" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B125" t="str">
         <f t="shared" si="3"/>
@@ -16304,7 +16313,7 @@
     <row r="126" spans="1:65">
       <c r="A126" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B126" t="str">
         <f t="shared" si="3"/>
@@ -16383,7 +16392,7 @@
     <row r="127" spans="1:65">
       <c r="A127" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B127" t="str">
         <f t="shared" si="3"/>
@@ -16462,7 +16471,7 @@
     <row r="128" spans="1:65">
       <c r="A128" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B128" t="str">
         <f t="shared" si="3"/>
@@ -16541,7 +16550,7 @@
     <row r="129" spans="1:65">
       <c r="A129" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B129" t="str">
         <f t="shared" si="3"/>
@@ -16620,7 +16629,7 @@
     <row r="130" spans="1:65">
       <c r="A130" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B130" t="str">
         <f t="shared" si="3"/>
@@ -16699,7 +16708,7 @@
     <row r="131" spans="1:65">
       <c r="A131" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B131" t="str">
         <f t="shared" si="3"/>
@@ -16781,7 +16790,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B132" t="str">
         <f t="shared" ref="B132:B168" si="5">TEXT($C132, "HH:mm")</f>
@@ -16860,7 +16869,7 @@
     <row r="133" spans="1:65">
       <c r="A133" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B133" t="str">
         <f t="shared" si="5"/>
@@ -16939,7 +16948,7 @@
     <row r="134" spans="1:65">
       <c r="A134" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B134" t="str">
         <f t="shared" si="5"/>
@@ -17018,7 +17027,7 @@
     <row r="135" spans="1:65">
       <c r="A135" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B135" t="str">
         <f t="shared" si="5"/>
@@ -17097,7 +17106,7 @@
     <row r="136" spans="1:65">
       <c r="A136" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B136" t="str">
         <f t="shared" si="5"/>
@@ -17178,7 +17187,7 @@
     <row r="137" spans="1:65">
       <c r="A137" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B137" t="str">
         <f t="shared" si="5"/>
@@ -17259,7 +17268,7 @@
     <row r="138" spans="1:65">
       <c r="A138" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B138" t="str">
         <f t="shared" si="5"/>
@@ -17338,7 +17347,7 @@
     <row r="139" spans="1:65">
       <c r="A139" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B139" t="str">
         <f t="shared" si="5"/>
@@ -17417,7 +17426,7 @@
     <row r="140" spans="1:65">
       <c r="A140" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B140" t="str">
         <f t="shared" si="5"/>
@@ -17496,7 +17505,7 @@
     <row r="141" spans="1:65">
       <c r="A141" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B141" t="str">
         <f t="shared" si="5"/>
@@ -17575,7 +17584,7 @@
     <row r="142" spans="1:65">
       <c r="A142" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B142" t="str">
         <f t="shared" si="5"/>
@@ -17654,7 +17663,7 @@
     <row r="143" spans="1:65">
       <c r="A143" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B143" t="str">
         <f t="shared" si="5"/>
@@ -17733,7 +17742,7 @@
     <row r="144" spans="1:65">
       <c r="A144" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B144" t="str">
         <f t="shared" si="5"/>
@@ -17812,7 +17821,7 @@
     <row r="145" spans="1:65">
       <c r="A145" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B145" t="str">
         <f t="shared" si="5"/>
@@ -17891,7 +17900,7 @@
     <row r="146" spans="1:65">
       <c r="A146" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B146" t="str">
         <f t="shared" si="5"/>
@@ -17970,7 +17979,7 @@
     <row r="147" spans="1:65">
       <c r="A147" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B147" t="str">
         <f t="shared" si="5"/>
@@ -18049,7 +18058,7 @@
     <row r="148" spans="1:65">
       <c r="A148" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B148" t="str">
         <f t="shared" si="5"/>
@@ -18130,7 +18139,7 @@
     <row r="149" spans="1:65">
       <c r="A149" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B149" t="str">
         <f t="shared" si="5"/>
@@ -18209,7 +18218,7 @@
     <row r="150" spans="1:65">
       <c r="A150" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B150" t="str">
         <f t="shared" si="5"/>
@@ -18288,7 +18297,7 @@
     <row r="151" spans="1:65">
       <c r="A151" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B151" t="str">
         <f t="shared" si="5"/>
@@ -18367,7 +18376,7 @@
     <row r="152" spans="1:65">
       <c r="A152" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B152" t="str">
         <f t="shared" si="5"/>
@@ -18446,7 +18455,7 @@
     <row r="153" spans="1:65">
       <c r="A153" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B153" t="str">
         <f t="shared" si="5"/>
@@ -18525,7 +18534,7 @@
     <row r="154" spans="1:65">
       <c r="A154" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B154" t="str">
         <f t="shared" si="5"/>
@@ -18604,7 +18613,7 @@
     <row r="155" spans="1:65">
       <c r="A155" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B155" t="str">
         <f t="shared" si="5"/>
@@ -18683,7 +18692,7 @@
     <row r="156" spans="1:65">
       <c r="A156" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B156" t="str">
         <f t="shared" si="5"/>
@@ -18762,7 +18771,7 @@
     <row r="157" spans="1:65">
       <c r="A157" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B157" t="str">
         <f t="shared" si="5"/>
@@ -18841,7 +18850,7 @@
     <row r="158" spans="1:65">
       <c r="A158" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B158" t="str">
         <f t="shared" si="5"/>
@@ -18920,7 +18929,7 @@
     <row r="159" spans="1:65">
       <c r="A159" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B159" t="str">
         <f t="shared" si="5"/>
@@ -18999,7 +19008,7 @@
     <row r="160" spans="1:65">
       <c r="A160" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B160" t="str">
         <f t="shared" si="5"/>
@@ -19078,7 +19087,7 @@
     <row r="161" spans="1:65">
       <c r="A161" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B161" t="str">
         <f t="shared" si="5"/>
@@ -19157,7 +19166,7 @@
     <row r="162" spans="1:65">
       <c r="A162" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B162" t="str">
         <f t="shared" si="5"/>
@@ -19236,7 +19245,7 @@
     <row r="163" spans="1:65">
       <c r="A163" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B163" t="str">
         <f t="shared" si="5"/>
@@ -19315,7 +19324,7 @@
     <row r="164" spans="1:65">
       <c r="A164" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B164" t="str">
         <f t="shared" si="5"/>
@@ -19394,7 +19403,7 @@
     <row r="165" spans="1:65">
       <c r="A165" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B165" t="str">
         <f t="shared" si="5"/>
@@ -19473,7 +19482,7 @@
     <row r="166" spans="1:65">
       <c r="A166" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B166" t="str">
         <f t="shared" si="5"/>
@@ -19554,7 +19563,7 @@
     <row r="167" spans="1:65">
       <c r="A167" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B167" t="str">
         <f t="shared" si="5"/>
@@ -19633,7 +19642,7 @@
     <row r="168" spans="1:65">
       <c r="A168" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B168" t="str">
         <f t="shared" si="5"/>
@@ -19715,7 +19724,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B169" t="str">
         <f>TEXT($C169, "HH:mm")</f>
@@ -19797,7 +19806,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B170" t="str">
         <f t="shared" ref="B170:B233" si="7">TEXT($C170, "HH:mm")</f>
@@ -19876,7 +19885,7 @@
     <row r="171" spans="1:65">
       <c r="A171" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B171" t="str">
         <f t="shared" si="7"/>
@@ -19955,7 +19964,7 @@
     <row r="172" spans="1:65">
       <c r="A172" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B172" t="str">
         <f t="shared" si="7"/>
@@ -20036,7 +20045,7 @@
     <row r="173" spans="1:65">
       <c r="A173" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B173" t="str">
         <f t="shared" si="7"/>
@@ -20115,7 +20124,7 @@
     <row r="174" spans="1:65">
       <c r="A174" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B174" t="str">
         <f t="shared" si="7"/>
@@ -20194,7 +20203,7 @@
     <row r="175" spans="1:65">
       <c r="A175" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B175" t="str">
         <f t="shared" si="7"/>
@@ -20273,7 +20282,7 @@
     <row r="176" spans="1:65">
       <c r="A176" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B176" t="str">
         <f t="shared" si="7"/>
@@ -20352,7 +20361,7 @@
     <row r="177" spans="1:65">
       <c r="A177" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B177" t="str">
         <f t="shared" si="7"/>
@@ -20431,7 +20440,7 @@
     <row r="178" spans="1:65">
       <c r="A178" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B178" t="str">
         <f t="shared" si="7"/>
@@ -20512,7 +20521,7 @@
     <row r="179" spans="1:65">
       <c r="A179" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B179" t="str">
         <f t="shared" si="7"/>
@@ -20591,7 +20600,7 @@
     <row r="180" spans="1:65">
       <c r="A180" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B180" t="str">
         <f t="shared" si="7"/>
@@ -20670,7 +20679,7 @@
     <row r="181" spans="1:65">
       <c r="A181" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B181" t="str">
         <f t="shared" si="7"/>
@@ -20751,7 +20760,7 @@
     <row r="182" spans="1:65">
       <c r="A182" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B182" t="str">
         <f t="shared" si="7"/>
@@ -20832,7 +20841,7 @@
     <row r="183" spans="1:65">
       <c r="A183" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B183" t="str">
         <f t="shared" si="7"/>
@@ -20913,7 +20922,7 @@
     <row r="184" spans="1:65">
       <c r="A184" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B184" t="str">
         <f t="shared" si="7"/>
@@ -20996,7 +21005,7 @@
     <row r="185" spans="1:65">
       <c r="A185" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B185" t="str">
         <f t="shared" si="7"/>
@@ -21077,7 +21086,7 @@
     <row r="186" spans="1:65">
       <c r="A186" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B186" t="str">
         <f t="shared" si="7"/>
@@ -21158,7 +21167,7 @@
     <row r="187" spans="1:65">
       <c r="A187" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B187" t="str">
         <f t="shared" si="7"/>
@@ -21239,7 +21248,7 @@
     <row r="188" spans="1:65">
       <c r="A188" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B188" t="str">
         <f t="shared" si="7"/>
@@ -21320,7 +21329,7 @@
     <row r="189" spans="1:65">
       <c r="A189" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B189" t="str">
         <f t="shared" si="7"/>
@@ -21401,7 +21410,7 @@
     <row r="190" spans="1:65">
       <c r="A190" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B190" t="str">
         <f t="shared" si="7"/>
@@ -21484,7 +21493,7 @@
     <row r="191" spans="1:65">
       <c r="A191" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B191" t="str">
         <f t="shared" si="7"/>
@@ -21567,7 +21576,7 @@
     <row r="192" spans="1:65">
       <c r="A192" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B192" t="str">
         <f t="shared" si="7"/>
@@ -21650,7 +21659,7 @@
     <row r="193" spans="1:65">
       <c r="A193" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B193" t="str">
         <f t="shared" si="7"/>
@@ -21733,7 +21742,7 @@
     <row r="194" spans="1:65">
       <c r="A194" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B194" t="str">
         <f t="shared" si="7"/>
@@ -21814,7 +21823,7 @@
     <row r="195" spans="1:65">
       <c r="A195" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B195" t="str">
         <f t="shared" si="7"/>
@@ -21895,7 +21904,7 @@
     <row r="196" spans="1:65">
       <c r="A196" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B196" t="str">
         <f t="shared" si="7"/>
@@ -21978,7 +21987,7 @@
     <row r="197" spans="1:65">
       <c r="A197" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B197" t="str">
         <f t="shared" si="7"/>
@@ -22057,7 +22066,7 @@
     <row r="198" spans="1:65">
       <c r="A198" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B198" t="str">
         <f t="shared" si="7"/>
@@ -22136,7 +22145,7 @@
     <row r="199" spans="1:65">
       <c r="A199" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B199" t="str">
         <f t="shared" si="7"/>
@@ -22215,7 +22224,7 @@
     <row r="200" spans="1:65">
       <c r="A200" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B200" t="str">
         <f t="shared" si="7"/>
@@ -22294,7 +22303,7 @@
     <row r="201" spans="1:65">
       <c r="A201" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B201" t="str">
         <f t="shared" si="7"/>
@@ -22373,7 +22382,7 @@
     <row r="202" spans="1:65">
       <c r="A202" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B202" t="str">
         <f t="shared" si="7"/>
@@ -22454,7 +22463,7 @@
     <row r="203" spans="1:65">
       <c r="A203" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B203" t="str">
         <f t="shared" si="7"/>
@@ -22533,7 +22542,7 @@
     <row r="204" spans="1:65">
       <c r="A204" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B204" t="str">
         <f t="shared" si="7"/>
@@ -22612,7 +22621,7 @@
     <row r="205" spans="1:65">
       <c r="A205" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B205" t="str">
         <f t="shared" si="7"/>
@@ -22691,7 +22700,7 @@
     <row r="206" spans="1:65">
       <c r="A206" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B206" t="str">
         <f t="shared" si="7"/>
@@ -22770,7 +22779,7 @@
     <row r="207" spans="1:65">
       <c r="A207" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B207" t="str">
         <f t="shared" si="7"/>
@@ -22849,7 +22858,7 @@
     <row r="208" spans="1:65">
       <c r="A208" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B208" t="str">
         <f t="shared" si="7"/>
@@ -22930,7 +22939,7 @@
     <row r="209" spans="1:65">
       <c r="A209" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B209" t="str">
         <f t="shared" si="7"/>
@@ -23009,7 +23018,7 @@
     <row r="210" spans="1:65">
       <c r="A210" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B210" t="str">
         <f t="shared" si="7"/>
@@ -23088,7 +23097,7 @@
     <row r="211" spans="1:65">
       <c r="A211" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B211" t="str">
         <f t="shared" si="7"/>
@@ -23169,7 +23178,7 @@
     <row r="212" spans="1:65">
       <c r="A212" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B212" t="str">
         <f t="shared" si="7"/>
@@ -23248,7 +23257,7 @@
     <row r="213" spans="1:65">
       <c r="A213" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B213" t="str">
         <f t="shared" si="7"/>
@@ -23327,7 +23336,7 @@
     <row r="214" spans="1:65">
       <c r="A214" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B214" t="str">
         <f t="shared" si="7"/>
@@ -23406,7 +23415,7 @@
     <row r="215" spans="1:65">
       <c r="A215" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B215" t="str">
         <f t="shared" si="7"/>
@@ -23485,7 +23494,7 @@
     <row r="216" spans="1:65">
       <c r="A216" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B216" t="str">
         <f t="shared" si="7"/>
@@ -23564,7 +23573,7 @@
     <row r="217" spans="1:65">
       <c r="A217" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B217" t="str">
         <f t="shared" si="7"/>
@@ -23643,7 +23652,7 @@
     <row r="218" spans="1:65">
       <c r="A218" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B218" t="str">
         <f t="shared" si="7"/>
@@ -23722,7 +23731,7 @@
     <row r="219" spans="1:65">
       <c r="A219" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B219" t="str">
         <f t="shared" si="7"/>
@@ -23801,7 +23810,7 @@
     <row r="220" spans="1:65">
       <c r="A220" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B220" t="str">
         <f t="shared" si="7"/>
@@ -23882,7 +23891,7 @@
     <row r="221" spans="1:65">
       <c r="A221" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B221" t="str">
         <f t="shared" si="7"/>
@@ -23961,7 +23970,7 @@
     <row r="222" spans="1:65">
       <c r="A222" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B222" t="str">
         <f t="shared" si="7"/>
@@ -24040,7 +24049,7 @@
     <row r="223" spans="1:65">
       <c r="A223" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B223" t="str">
         <f t="shared" si="7"/>
@@ -24119,7 +24128,7 @@
     <row r="224" spans="1:65">
       <c r="A224" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B224" t="str">
         <f t="shared" si="7"/>
@@ -24198,7 +24207,7 @@
     <row r="225" spans="1:65">
       <c r="A225" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B225" t="str">
         <f t="shared" si="7"/>
@@ -24277,7 +24286,7 @@
     <row r="226" spans="1:65">
       <c r="A226" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B226" t="str">
         <f t="shared" si="7"/>
@@ -24356,7 +24365,7 @@
     <row r="227" spans="1:65">
       <c r="A227" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B227" t="str">
         <f t="shared" si="7"/>
@@ -24435,7 +24444,7 @@
     <row r="228" spans="1:65">
       <c r="A228" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B228" t="str">
         <f t="shared" si="7"/>
@@ -24514,7 +24523,7 @@
     <row r="229" spans="1:65">
       <c r="A229" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B229" t="str">
         <f t="shared" si="7"/>
@@ -24593,7 +24602,7 @@
     <row r="230" spans="1:65">
       <c r="A230" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B230" t="str">
         <f t="shared" si="7"/>
@@ -24672,7 +24681,7 @@
     <row r="231" spans="1:65">
       <c r="A231" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B231" t="str">
         <f t="shared" si="7"/>
@@ -24751,7 +24760,7 @@
     <row r="232" spans="1:65">
       <c r="A232" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B232" t="str">
         <f t="shared" si="7"/>
@@ -24830,7 +24839,7 @@
     <row r="233" spans="1:65">
       <c r="A233" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B233" t="str">
         <f t="shared" si="7"/>
@@ -24912,7 +24921,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B234" t="str">
         <f t="shared" ref="B234:B291" si="9">TEXT($C234, "HH:mm")</f>
@@ -24991,7 +25000,7 @@
     <row r="235" spans="1:65">
       <c r="A235" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B235" t="str">
         <f t="shared" si="9"/>
@@ -25070,7 +25079,7 @@
     <row r="236" spans="1:65">
       <c r="A236" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B236" t="str">
         <f t="shared" si="9"/>
@@ -25149,7 +25158,7 @@
     <row r="237" spans="1:65">
       <c r="A237" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B237" t="str">
         <f t="shared" si="9"/>
@@ -25228,7 +25237,7 @@
     <row r="238" spans="1:65">
       <c r="A238" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B238" t="str">
         <f t="shared" si="9"/>
@@ -25307,7 +25316,7 @@
     <row r="239" spans="1:65">
       <c r="A239" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B239" t="str">
         <f t="shared" si="9"/>
@@ -25386,7 +25395,7 @@
     <row r="240" spans="1:65">
       <c r="A240" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B240" t="str">
         <f t="shared" si="9"/>
@@ -25465,7 +25474,7 @@
     <row r="241" spans="1:65">
       <c r="A241" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B241" t="str">
         <f t="shared" si="9"/>
@@ -25544,7 +25553,7 @@
     <row r="242" spans="1:65">
       <c r="A242" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B242" t="str">
         <f t="shared" si="9"/>
@@ -25623,7 +25632,7 @@
     <row r="243" spans="1:65">
       <c r="A243" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B243" t="str">
         <f t="shared" si="9"/>
@@ -25702,7 +25711,7 @@
     <row r="244" spans="1:65">
       <c r="A244" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B244" t="str">
         <f t="shared" si="9"/>
@@ -25781,7 +25790,7 @@
     <row r="245" spans="1:65">
       <c r="A245" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B245" t="str">
         <f t="shared" si="9"/>
@@ -25860,7 +25869,7 @@
     <row r="246" spans="1:65">
       <c r="A246" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B246" t="str">
         <f t="shared" si="9"/>
@@ -25939,7 +25948,7 @@
     <row r="247" spans="1:65">
       <c r="A247" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B247" t="str">
         <f t="shared" si="9"/>
@@ -26018,7 +26027,7 @@
     <row r="248" spans="1:65">
       <c r="A248" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B248" t="str">
         <f t="shared" si="9"/>
@@ -26097,7 +26106,7 @@
     <row r="249" spans="1:65">
       <c r="A249" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B249" t="str">
         <f t="shared" si="9"/>
@@ -26176,7 +26185,7 @@
     <row r="250" spans="1:65">
       <c r="A250" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B250" t="str">
         <f t="shared" si="9"/>
@@ -26255,7 +26264,7 @@
     <row r="251" spans="1:65">
       <c r="A251" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B251" t="str">
         <f t="shared" si="9"/>
@@ -26334,7 +26343,7 @@
     <row r="252" spans="1:65">
       <c r="A252" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B252" t="str">
         <f t="shared" si="9"/>
@@ -26413,7 +26422,7 @@
     <row r="253" spans="1:65">
       <c r="A253" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B253" t="str">
         <f t="shared" si="9"/>
@@ -26492,7 +26501,7 @@
     <row r="254" spans="1:65">
       <c r="A254" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B254" t="str">
         <f t="shared" si="9"/>
@@ -26571,7 +26580,7 @@
     <row r="255" spans="1:65">
       <c r="A255" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B255" t="str">
         <f t="shared" si="9"/>
@@ -26650,7 +26659,7 @@
     <row r="256" spans="1:65">
       <c r="A256" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B256" t="str">
         <f t="shared" si="9"/>
@@ -26729,7 +26738,7 @@
     <row r="257" spans="1:65">
       <c r="A257" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B257" t="str">
         <f t="shared" si="9"/>
@@ -26808,7 +26817,7 @@
     <row r="258" spans="1:65">
       <c r="A258" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B258" t="str">
         <f t="shared" si="9"/>
@@ -26887,7 +26896,7 @@
     <row r="259" spans="1:65">
       <c r="A259" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B259" t="str">
         <f t="shared" si="9"/>
@@ -26966,7 +26975,7 @@
     <row r="260" spans="1:65">
       <c r="A260" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B260" t="str">
         <f t="shared" si="9"/>
@@ -27045,7 +27054,7 @@
     <row r="261" spans="1:65">
       <c r="A261" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B261" t="str">
         <f t="shared" si="9"/>
@@ -27124,7 +27133,7 @@
     <row r="262" spans="1:65">
       <c r="A262" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B262" t="str">
         <f t="shared" si="9"/>
@@ -27203,7 +27212,7 @@
     <row r="263" spans="1:65">
       <c r="A263" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B263" t="str">
         <f t="shared" si="9"/>
@@ -27282,7 +27291,7 @@
     <row r="264" spans="1:65">
       <c r="A264" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B264" t="str">
         <f t="shared" si="9"/>
@@ -27361,7 +27370,7 @@
     <row r="265" spans="1:65">
       <c r="A265" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B265" t="str">
         <f t="shared" si="9"/>
@@ -27440,7 +27449,7 @@
     <row r="266" spans="1:65">
       <c r="A266" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B266" t="str">
         <f t="shared" si="9"/>
@@ -27519,7 +27528,7 @@
     <row r="267" spans="1:65">
       <c r="A267" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B267" t="str">
         <f t="shared" si="9"/>
@@ -27598,7 +27607,7 @@
     <row r="268" spans="1:65">
       <c r="A268" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B268" t="str">
         <f t="shared" si="9"/>
@@ -27677,7 +27686,7 @@
     <row r="269" spans="1:65">
       <c r="A269" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B269" t="str">
         <f t="shared" si="9"/>
@@ -27756,7 +27765,7 @@
     <row r="270" spans="1:65">
       <c r="A270" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B270" t="str">
         <f t="shared" si="9"/>
@@ -27835,7 +27844,7 @@
     <row r="271" spans="1:65">
       <c r="A271" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B271" t="str">
         <f t="shared" si="9"/>
@@ -27914,7 +27923,7 @@
     <row r="272" spans="1:65">
       <c r="A272" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B272" t="str">
         <f t="shared" si="9"/>
@@ -27993,7 +28002,7 @@
     <row r="273" spans="1:65">
       <c r="A273" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B273" t="str">
         <f t="shared" si="9"/>
@@ -28072,7 +28081,7 @@
     <row r="274" spans="1:65">
       <c r="A274" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B274" t="str">
         <f t="shared" si="9"/>
@@ -28151,7 +28160,7 @@
     <row r="275" spans="1:65">
       <c r="A275" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B275" t="str">
         <f t="shared" si="9"/>
@@ -28230,7 +28239,7 @@
     <row r="276" spans="1:65">
       <c r="A276" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B276" t="str">
         <f t="shared" si="9"/>
@@ -28309,7 +28318,7 @@
     <row r="277" spans="1:65">
       <c r="A277" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B277" t="str">
         <f t="shared" si="9"/>
@@ -28388,7 +28397,7 @@
     <row r="278" spans="1:65">
       <c r="A278" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B278" t="str">
         <f t="shared" si="9"/>
@@ -28467,7 +28476,7 @@
     <row r="279" spans="1:65">
       <c r="A279" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B279" t="str">
         <f t="shared" si="9"/>
@@ -28546,7 +28555,7 @@
     <row r="280" spans="1:65">
       <c r="A280" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B280" t="str">
         <f t="shared" si="9"/>
@@ -28625,7 +28634,7 @@
     <row r="281" spans="1:65">
       <c r="A281" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B281" t="str">
         <f t="shared" si="9"/>
@@ -28704,7 +28713,7 @@
     <row r="282" spans="1:65">
       <c r="A282" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B282" t="str">
         <f t="shared" si="9"/>
@@ -28783,7 +28792,7 @@
     <row r="283" spans="1:65">
       <c r="A283" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B283" t="str">
         <f t="shared" si="9"/>
@@ -28862,7 +28871,7 @@
     <row r="284" spans="1:65">
       <c r="A284" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B284" t="str">
         <f t="shared" si="9"/>
@@ -28941,7 +28950,7 @@
     <row r="285" spans="1:65">
       <c r="A285" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B285" t="str">
         <f t="shared" si="9"/>
@@ -29020,7 +29029,7 @@
     <row r="286" spans="1:65">
       <c r="A286" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B286" t="str">
         <f t="shared" si="9"/>
@@ -29099,7 +29108,7 @@
     <row r="287" spans="1:65">
       <c r="A287" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B287" t="str">
         <f t="shared" si="9"/>
@@ -29178,7 +29187,7 @@
     <row r="288" spans="1:65">
       <c r="A288" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B288" t="str">
         <f t="shared" si="9"/>
@@ -29257,7 +29266,7 @@
     <row r="289" spans="1:65">
       <c r="A289" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B289" t="str">
         <f t="shared" si="9"/>
@@ -29336,7 +29345,7 @@
     <row r="290" spans="1:65">
       <c r="A290" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B290" t="str">
         <f t="shared" si="9"/>
@@ -29415,7 +29424,7 @@
     <row r="291" spans="1:65">
       <c r="A291" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:25</v>
+        <v>01:30</v>
       </c>
       <c r="B291" t="str">
         <f t="shared" si="9"/>

--- a/Vite-Vercel開発.xlsx
+++ b/Vite-Vercel開発.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2c67ec30e06f060f/work/GitHub/work-time-tracker/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{1928CA11-C4AD-40E9-B1C5-143667E830EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{010239F8-1112-42A6-A678-DAF2809917FF}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{1928CA11-C4AD-40E9-B1C5-143667E830EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E4A7048-251F-4F9A-A370-6ECC72A286D4}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1542" uniqueCount="920">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1543" uniqueCount="921">
   <si>
     <t>npm install -g vercel</t>
     <phoneticPr fontId="1"/>
@@ -5358,6 +5358,10 @@
   </si>
   <si>
     <t>Found 62 errors in 15 files.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Found 63 errors in 16 files.</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -6130,7 +6134,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{083174DA-A42C-4F9C-978E-61AEAAD9DDFF}">
-  <dimension ref="B2:D24"/>
+  <dimension ref="B2:D25"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
@@ -6258,6 +6262,11 @@
     <row r="24" spans="3:3">
       <c r="C24" t="s">
         <v>919</v>
+      </c>
+    </row>
+    <row r="25" spans="3:3">
+      <c r="C25" t="s">
+        <v>920</v>
       </c>
     </row>
   </sheetData>
@@ -6435,7 +6444,7 @@
     <row r="3" spans="1:65">
       <c r="A3" s="19" t="str">
         <f ca="1">TEXT(NOW(),"HH:mm")</f>
-        <v>01:30</v>
+        <v>01:33</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="17" t="s">

--- a/Vite-Vercel開発.xlsx
+++ b/Vite-Vercel開発.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2c67ec30e06f060f/work/GitHub/work-time-tracker/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{1928CA11-C4AD-40E9-B1C5-143667E830EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E4A7048-251F-4F9A-A370-6ECC72A286D4}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{1928CA11-C4AD-40E9-B1C5-143667E830EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C6CDF44-8573-4EE9-90B3-D9E1DBF55244}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1543" uniqueCount="921">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1544" uniqueCount="921">
   <si>
     <t>npm install -g vercel</t>
     <phoneticPr fontId="1"/>
@@ -6134,7 +6134,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{083174DA-A42C-4F9C-978E-61AEAAD9DDFF}">
-  <dimension ref="B2:D25"/>
+  <dimension ref="B2:D26"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
@@ -6267,6 +6267,11 @@
     <row r="25" spans="3:3">
       <c r="C25" t="s">
         <v>920</v>
+      </c>
+    </row>
+    <row r="26" spans="3:3">
+      <c r="C26" t="s">
+        <v>918</v>
       </c>
     </row>
   </sheetData>
@@ -6433,7 +6438,7 @@
       MOD(NOW(),1),
       TIME(0,5,0)
     ),"HH:mm")</f>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B2" s="19"/>
       <c r="D2" s="1">
@@ -6444,7 +6449,7 @@
     <row r="3" spans="1:65">
       <c r="A3" s="19" t="str">
         <f ca="1">TEXT(NOW(),"HH:mm")</f>
-        <v>01:33</v>
+        <v>01:39</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="17" t="s">
@@ -6643,7 +6648,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B4" t="str">
         <f t="shared" ref="B4:B67" si="1">TEXT($C4, "HH:mm")</f>
@@ -6722,7 +6727,7 @@
     <row r="5" spans="1:65">
       <c r="A5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B5" t="str">
         <f t="shared" si="1"/>
@@ -6801,7 +6806,7 @@
     <row r="6" spans="1:65">
       <c r="A6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B6" t="str">
         <f t="shared" si="1"/>
@@ -6880,7 +6885,7 @@
     <row r="7" spans="1:65">
       <c r="A7" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B7" t="str">
         <f t="shared" si="1"/>
@@ -6959,7 +6964,7 @@
     <row r="8" spans="1:65">
       <c r="A8" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B8" t="str">
         <f t="shared" si="1"/>
@@ -7038,7 +7043,7 @@
     <row r="9" spans="1:65">
       <c r="A9" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B9" t="str">
         <f t="shared" si="1"/>
@@ -7117,7 +7122,7 @@
     <row r="10" spans="1:65">
       <c r="A10" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B10" t="str">
         <f t="shared" si="1"/>
@@ -7196,7 +7201,7 @@
     <row r="11" spans="1:65">
       <c r="A11" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B11" t="str">
         <f t="shared" si="1"/>
@@ -7275,7 +7280,7 @@
     <row r="12" spans="1:65">
       <c r="A12" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B12" t="str">
         <f t="shared" si="1"/>
@@ -7354,7 +7359,7 @@
     <row r="13" spans="1:65">
       <c r="A13" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B13" t="str">
         <f t="shared" si="1"/>
@@ -7433,7 +7438,7 @@
     <row r="14" spans="1:65">
       <c r="A14" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B14" t="str">
         <f t="shared" si="1"/>
@@ -7512,7 +7517,7 @@
     <row r="15" spans="1:65">
       <c r="A15" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B15" t="str">
         <f t="shared" si="1"/>
@@ -7591,7 +7596,7 @@
     <row r="16" spans="1:65">
       <c r="A16" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B16" t="str">
         <f t="shared" si="1"/>
@@ -7670,7 +7675,7 @@
     <row r="17" spans="1:65">
       <c r="A17" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B17" t="str">
         <f t="shared" si="1"/>
@@ -7749,7 +7754,7 @@
     <row r="18" spans="1:65">
       <c r="A18" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B18" t="str">
         <f t="shared" si="1"/>
@@ -7828,7 +7833,7 @@
     <row r="19" spans="1:65">
       <c r="A19" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B19" t="str">
         <f t="shared" si="1"/>
@@ -7907,7 +7912,7 @@
     <row r="20" spans="1:65">
       <c r="A20" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B20" t="str">
         <f t="shared" si="1"/>
@@ -7986,7 +7991,7 @@
     <row r="21" spans="1:65">
       <c r="A21" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B21" t="str">
         <f t="shared" si="1"/>
@@ -8065,7 +8070,7 @@
     <row r="22" spans="1:65">
       <c r="A22" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B22" t="str">
         <f t="shared" si="1"/>
@@ -8144,7 +8149,7 @@
     <row r="23" spans="1:65">
       <c r="A23" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B23" t="str">
         <f t="shared" si="1"/>
@@ -8223,7 +8228,7 @@
     <row r="24" spans="1:65">
       <c r="A24" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B24" t="str">
         <f t="shared" si="1"/>
@@ -8302,7 +8307,7 @@
     <row r="25" spans="1:65">
       <c r="A25" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B25" t="str">
         <f t="shared" si="1"/>
@@ -8381,7 +8386,7 @@
     <row r="26" spans="1:65">
       <c r="A26" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B26" t="str">
         <f t="shared" si="1"/>
@@ -8460,7 +8465,7 @@
     <row r="27" spans="1:65">
       <c r="A27" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B27" t="str">
         <f t="shared" si="1"/>
@@ -8539,7 +8544,7 @@
     <row r="28" spans="1:65">
       <c r="A28" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B28" t="str">
         <f t="shared" si="1"/>
@@ -8620,7 +8625,7 @@
     <row r="29" spans="1:65">
       <c r="A29" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B29" t="str">
         <f t="shared" si="1"/>
@@ -8701,7 +8706,7 @@
     <row r="30" spans="1:65">
       <c r="A30" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B30" t="str">
         <f t="shared" si="1"/>
@@ -8782,7 +8787,7 @@
     <row r="31" spans="1:65">
       <c r="A31" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B31" t="str">
         <f t="shared" si="1"/>
@@ -8861,7 +8866,7 @@
     <row r="32" spans="1:65">
       <c r="A32" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B32" t="str">
         <f t="shared" si="1"/>
@@ -8940,7 +8945,7 @@
     <row r="33" spans="1:65">
       <c r="A33" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B33" t="str">
         <f t="shared" si="1"/>
@@ -9019,7 +9024,7 @@
     <row r="34" spans="1:65">
       <c r="A34" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B34" t="str">
         <f t="shared" si="1"/>
@@ -9100,7 +9105,7 @@
     <row r="35" spans="1:65">
       <c r="A35" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B35" t="str">
         <f t="shared" si="1"/>
@@ -9181,7 +9186,7 @@
     <row r="36" spans="1:65">
       <c r="A36" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B36" t="str">
         <f t="shared" si="1"/>
@@ -9262,7 +9267,7 @@
     <row r="37" spans="1:65">
       <c r="A37" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B37" t="str">
         <f t="shared" si="1"/>
@@ -9341,7 +9346,7 @@
     <row r="38" spans="1:65">
       <c r="A38" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B38" t="str">
         <f t="shared" si="1"/>
@@ -9420,7 +9425,7 @@
     <row r="39" spans="1:65">
       <c r="A39" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B39" t="str">
         <f t="shared" si="1"/>
@@ -9499,7 +9504,7 @@
     <row r="40" spans="1:65">
       <c r="A40" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B40" t="str">
         <f t="shared" si="1"/>
@@ -9578,7 +9583,7 @@
     <row r="41" spans="1:65">
       <c r="A41" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B41" t="str">
         <f t="shared" si="1"/>
@@ -9657,7 +9662,7 @@
     <row r="42" spans="1:65">
       <c r="A42" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B42" t="str">
         <f t="shared" si="1"/>
@@ -9738,7 +9743,7 @@
     <row r="43" spans="1:65">
       <c r="A43" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B43" t="str">
         <f t="shared" si="1"/>
@@ -9819,7 +9824,7 @@
     <row r="44" spans="1:65">
       <c r="A44" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B44" t="str">
         <f t="shared" si="1"/>
@@ -9898,7 +9903,7 @@
     <row r="45" spans="1:65">
       <c r="A45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B45" t="str">
         <f t="shared" si="1"/>
@@ -9977,7 +9982,7 @@
     <row r="46" spans="1:65">
       <c r="A46" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B46" t="str">
         <f t="shared" si="1"/>
@@ -10056,7 +10061,7 @@
     <row r="47" spans="1:65">
       <c r="A47" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B47" t="str">
         <f t="shared" si="1"/>
@@ -10135,7 +10140,7 @@
     <row r="48" spans="1:65">
       <c r="A48" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B48" t="str">
         <f t="shared" si="1"/>
@@ -10214,7 +10219,7 @@
     <row r="49" spans="1:65">
       <c r="A49" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B49" t="str">
         <f t="shared" si="1"/>
@@ -10295,7 +10300,7 @@
     <row r="50" spans="1:65">
       <c r="A50" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B50" t="str">
         <f t="shared" si="1"/>
@@ -10376,7 +10381,7 @@
     <row r="51" spans="1:65">
       <c r="A51" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B51" t="str">
         <f t="shared" si="1"/>
@@ -10455,7 +10460,7 @@
     <row r="52" spans="1:65">
       <c r="A52" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B52" t="str">
         <f t="shared" si="1"/>
@@ -10534,7 +10539,7 @@
     <row r="53" spans="1:65">
       <c r="A53" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B53" t="str">
         <f t="shared" si="1"/>
@@ -10613,7 +10618,7 @@
     <row r="54" spans="1:65">
       <c r="A54" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B54" t="str">
         <f t="shared" si="1"/>
@@ -10692,7 +10697,7 @@
     <row r="55" spans="1:65">
       <c r="A55" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B55" t="str">
         <f t="shared" si="1"/>
@@ -10771,7 +10776,7 @@
     <row r="56" spans="1:65">
       <c r="A56" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B56" t="str">
         <f t="shared" si="1"/>
@@ -10852,7 +10857,7 @@
     <row r="57" spans="1:65">
       <c r="A57" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B57" t="str">
         <f t="shared" si="1"/>
@@ -10931,7 +10936,7 @@
     <row r="58" spans="1:65">
       <c r="A58" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B58" t="str">
         <f t="shared" si="1"/>
@@ -11012,7 +11017,7 @@
     <row r="59" spans="1:65">
       <c r="A59" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B59" t="str">
         <f t="shared" si="1"/>
@@ -11091,7 +11096,7 @@
     <row r="60" spans="1:65">
       <c r="A60" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B60" t="str">
         <f t="shared" si="1"/>
@@ -11170,7 +11175,7 @@
     <row r="61" spans="1:65">
       <c r="A61" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B61" t="str">
         <f t="shared" si="1"/>
@@ -11249,7 +11254,7 @@
     <row r="62" spans="1:65">
       <c r="A62" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B62" t="str">
         <f t="shared" si="1"/>
@@ -11328,7 +11333,7 @@
     <row r="63" spans="1:65">
       <c r="A63" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B63" t="str">
         <f t="shared" si="1"/>
@@ -11407,7 +11412,7 @@
     <row r="64" spans="1:65">
       <c r="A64" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B64" t="str">
         <f t="shared" si="1"/>
@@ -11488,7 +11493,7 @@
     <row r="65" spans="1:65">
       <c r="A65" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B65" t="str">
         <f t="shared" si="1"/>
@@ -11567,7 +11572,7 @@
     <row r="66" spans="1:65">
       <c r="A66" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B66" t="str">
         <f t="shared" si="1"/>
@@ -11646,7 +11651,7 @@
     <row r="67" spans="1:65">
       <c r="A67" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B67" t="str">
         <f t="shared" si="1"/>
@@ -11728,7 +11733,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B68" t="str">
         <f t="shared" ref="B68:B131" si="3">TEXT($C68, "HH:mm")</f>
@@ -11807,7 +11812,7 @@
     <row r="69" spans="1:65">
       <c r="A69" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B69" t="str">
         <f t="shared" si="3"/>
@@ -11886,7 +11891,7 @@
     <row r="70" spans="1:65">
       <c r="A70" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B70" t="str">
         <f t="shared" si="3"/>
@@ -11965,7 +11970,7 @@
     <row r="71" spans="1:65">
       <c r="A71" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B71" t="str">
         <f t="shared" si="3"/>
@@ -12044,7 +12049,7 @@
     <row r="72" spans="1:65">
       <c r="A72" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B72" t="str">
         <f t="shared" si="3"/>
@@ -12123,7 +12128,7 @@
     <row r="73" spans="1:65">
       <c r="A73" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B73" t="str">
         <f t="shared" si="3"/>
@@ -12202,7 +12207,7 @@
     <row r="74" spans="1:65">
       <c r="A74" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B74" t="str">
         <f t="shared" si="3"/>
@@ -12281,7 +12286,7 @@
     <row r="75" spans="1:65">
       <c r="A75" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B75" t="str">
         <f t="shared" si="3"/>
@@ -12360,7 +12365,7 @@
     <row r="76" spans="1:65">
       <c r="A76" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B76" t="str">
         <f t="shared" si="3"/>
@@ -12439,7 +12444,7 @@
     <row r="77" spans="1:65">
       <c r="A77" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B77" t="str">
         <f t="shared" si="3"/>
@@ -12518,7 +12523,7 @@
     <row r="78" spans="1:65">
       <c r="A78" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B78" t="str">
         <f t="shared" si="3"/>
@@ -12597,7 +12602,7 @@
     <row r="79" spans="1:65">
       <c r="A79" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B79" t="str">
         <f t="shared" si="3"/>
@@ -12676,7 +12681,7 @@
     <row r="80" spans="1:65">
       <c r="A80" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B80" t="str">
         <f t="shared" si="3"/>
@@ -12755,7 +12760,7 @@
     <row r="81" spans="1:65">
       <c r="A81" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B81" t="str">
         <f t="shared" si="3"/>
@@ -12834,7 +12839,7 @@
     <row r="82" spans="1:65">
       <c r="A82" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B82" t="str">
         <f t="shared" si="3"/>
@@ -12913,7 +12918,7 @@
     <row r="83" spans="1:65">
       <c r="A83" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B83" t="str">
         <f t="shared" si="3"/>
@@ -12992,7 +12997,7 @@
     <row r="84" spans="1:65">
       <c r="A84" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B84" t="str">
         <f t="shared" si="3"/>
@@ -13071,7 +13076,7 @@
     <row r="85" spans="1:65">
       <c r="A85" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B85" t="str">
         <f t="shared" si="3"/>
@@ -13150,7 +13155,7 @@
     <row r="86" spans="1:65">
       <c r="A86" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B86" t="str">
         <f t="shared" si="3"/>
@@ -13229,7 +13234,7 @@
     <row r="87" spans="1:65">
       <c r="A87" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B87" t="str">
         <f t="shared" si="3"/>
@@ -13308,7 +13313,7 @@
     <row r="88" spans="1:65">
       <c r="A88" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B88" t="str">
         <f t="shared" si="3"/>
@@ -13387,7 +13392,7 @@
     <row r="89" spans="1:65">
       <c r="A89" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B89" t="str">
         <f t="shared" si="3"/>
@@ -13466,7 +13471,7 @@
     <row r="90" spans="1:65">
       <c r="A90" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B90" t="str">
         <f t="shared" si="3"/>
@@ -13545,7 +13550,7 @@
     <row r="91" spans="1:65">
       <c r="A91" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B91" t="str">
         <f t="shared" si="3"/>
@@ -13624,7 +13629,7 @@
     <row r="92" spans="1:65">
       <c r="A92" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B92" t="str">
         <f t="shared" si="3"/>
@@ -13703,7 +13708,7 @@
     <row r="93" spans="1:65">
       <c r="A93" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B93" t="str">
         <f t="shared" si="3"/>
@@ -13782,7 +13787,7 @@
     <row r="94" spans="1:65">
       <c r="A94" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B94" t="str">
         <f t="shared" si="3"/>
@@ -13861,7 +13866,7 @@
     <row r="95" spans="1:65">
       <c r="A95" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B95" t="str">
         <f t="shared" si="3"/>
@@ -13940,7 +13945,7 @@
     <row r="96" spans="1:65">
       <c r="A96" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B96" t="str">
         <f t="shared" si="3"/>
@@ -14019,7 +14024,7 @@
     <row r="97" spans="1:65">
       <c r="A97" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B97" t="str">
         <f t="shared" si="3"/>
@@ -14098,7 +14103,7 @@
     <row r="98" spans="1:65">
       <c r="A98" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B98" t="str">
         <f t="shared" si="3"/>
@@ -14177,7 +14182,7 @@
     <row r="99" spans="1:65">
       <c r="A99" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B99" t="str">
         <f t="shared" si="3"/>
@@ -14256,7 +14261,7 @@
     <row r="100" spans="1:65">
       <c r="A100" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B100" t="str">
         <f t="shared" si="3"/>
@@ -14337,7 +14342,7 @@
     <row r="101" spans="1:65">
       <c r="A101" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B101" t="str">
         <f t="shared" si="3"/>
@@ -14416,7 +14421,7 @@
     <row r="102" spans="1:65">
       <c r="A102" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B102" t="str">
         <f t="shared" si="3"/>
@@ -14495,7 +14500,7 @@
     <row r="103" spans="1:65">
       <c r="A103" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B103" t="str">
         <f t="shared" si="3"/>
@@ -14574,7 +14579,7 @@
     <row r="104" spans="1:65">
       <c r="A104" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B104" t="str">
         <f t="shared" si="3"/>
@@ -14653,7 +14658,7 @@
     <row r="105" spans="1:65">
       <c r="A105" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B105" t="str">
         <f t="shared" si="3"/>
@@ -14732,7 +14737,7 @@
     <row r="106" spans="1:65">
       <c r="A106" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B106" t="str">
         <f t="shared" si="3"/>
@@ -14813,7 +14818,7 @@
     <row r="107" spans="1:65">
       <c r="A107" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B107" t="str">
         <f t="shared" si="3"/>
@@ -14894,7 +14899,7 @@
     <row r="108" spans="1:65">
       <c r="A108" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B108" t="str">
         <f t="shared" si="3"/>
@@ -14973,7 +14978,7 @@
     <row r="109" spans="1:65">
       <c r="A109" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B109" t="str">
         <f t="shared" si="3"/>
@@ -15052,7 +15057,7 @@
     <row r="110" spans="1:65">
       <c r="A110" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B110" t="str">
         <f t="shared" si="3"/>
@@ -15131,7 +15136,7 @@
     <row r="111" spans="1:65">
       <c r="A111" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B111" t="str">
         <f t="shared" si="3"/>
@@ -15210,7 +15215,7 @@
     <row r="112" spans="1:65">
       <c r="A112" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B112" t="str">
         <f t="shared" si="3"/>
@@ -15291,7 +15296,7 @@
     <row r="113" spans="1:65">
       <c r="A113" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B113" t="str">
         <f t="shared" si="3"/>
@@ -15370,7 +15375,7 @@
     <row r="114" spans="1:65">
       <c r="A114" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B114" t="str">
         <f t="shared" si="3"/>
@@ -15449,7 +15454,7 @@
     <row r="115" spans="1:65">
       <c r="A115" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B115" t="str">
         <f t="shared" si="3"/>
@@ -15528,7 +15533,7 @@
     <row r="116" spans="1:65">
       <c r="A116" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B116" t="str">
         <f t="shared" si="3"/>
@@ -15607,7 +15612,7 @@
     <row r="117" spans="1:65">
       <c r="A117" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B117" t="str">
         <f t="shared" si="3"/>
@@ -15686,7 +15691,7 @@
     <row r="118" spans="1:65">
       <c r="A118" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B118" t="str">
         <f t="shared" si="3"/>
@@ -15765,7 +15770,7 @@
     <row r="119" spans="1:65">
       <c r="A119" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B119" t="str">
         <f t="shared" si="3"/>
@@ -15844,7 +15849,7 @@
     <row r="120" spans="1:65">
       <c r="A120" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B120" t="str">
         <f t="shared" si="3"/>
@@ -15923,7 +15928,7 @@
     <row r="121" spans="1:65">
       <c r="A121" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B121" t="str">
         <f t="shared" si="3"/>
@@ -16002,7 +16007,7 @@
     <row r="122" spans="1:65">
       <c r="A122" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B122" t="str">
         <f t="shared" si="3"/>
@@ -16081,7 +16086,7 @@
     <row r="123" spans="1:65">
       <c r="A123" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B123" t="str">
         <f t="shared" si="3"/>
@@ -16160,7 +16165,7 @@
     <row r="124" spans="1:65">
       <c r="A124" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B124" t="str">
         <f t="shared" si="3"/>
@@ -16241,7 +16246,7 @@
     <row r="125" spans="1:65">
       <c r="A125" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B125" t="str">
         <f t="shared" si="3"/>
@@ -16322,7 +16327,7 @@
     <row r="126" spans="1:65">
       <c r="A126" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B126" t="str">
         <f t="shared" si="3"/>
@@ -16401,7 +16406,7 @@
     <row r="127" spans="1:65">
       <c r="A127" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B127" t="str">
         <f t="shared" si="3"/>
@@ -16480,7 +16485,7 @@
     <row r="128" spans="1:65">
       <c r="A128" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B128" t="str">
         <f t="shared" si="3"/>
@@ -16559,7 +16564,7 @@
     <row r="129" spans="1:65">
       <c r="A129" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B129" t="str">
         <f t="shared" si="3"/>
@@ -16638,7 +16643,7 @@
     <row r="130" spans="1:65">
       <c r="A130" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B130" t="str">
         <f t="shared" si="3"/>
@@ -16717,7 +16722,7 @@
     <row r="131" spans="1:65">
       <c r="A131" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B131" t="str">
         <f t="shared" si="3"/>
@@ -16799,7 +16804,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B132" t="str">
         <f t="shared" ref="B132:B168" si="5">TEXT($C132, "HH:mm")</f>
@@ -16878,7 +16883,7 @@
     <row r="133" spans="1:65">
       <c r="A133" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B133" t="str">
         <f t="shared" si="5"/>
@@ -16957,7 +16962,7 @@
     <row r="134" spans="1:65">
       <c r="A134" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B134" t="str">
         <f t="shared" si="5"/>
@@ -17036,7 +17041,7 @@
     <row r="135" spans="1:65">
       <c r="A135" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B135" t="str">
         <f t="shared" si="5"/>
@@ -17115,7 +17120,7 @@
     <row r="136" spans="1:65">
       <c r="A136" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B136" t="str">
         <f t="shared" si="5"/>
@@ -17196,7 +17201,7 @@
     <row r="137" spans="1:65">
       <c r="A137" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B137" t="str">
         <f t="shared" si="5"/>
@@ -17277,7 +17282,7 @@
     <row r="138" spans="1:65">
       <c r="A138" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B138" t="str">
         <f t="shared" si="5"/>
@@ -17356,7 +17361,7 @@
     <row r="139" spans="1:65">
       <c r="A139" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B139" t="str">
         <f t="shared" si="5"/>
@@ -17435,7 +17440,7 @@
     <row r="140" spans="1:65">
       <c r="A140" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B140" t="str">
         <f t="shared" si="5"/>
@@ -17514,7 +17519,7 @@
     <row r="141" spans="1:65">
       <c r="A141" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B141" t="str">
         <f t="shared" si="5"/>
@@ -17593,7 +17598,7 @@
     <row r="142" spans="1:65">
       <c r="A142" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B142" t="str">
         <f t="shared" si="5"/>
@@ -17672,7 +17677,7 @@
     <row r="143" spans="1:65">
       <c r="A143" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B143" t="str">
         <f t="shared" si="5"/>
@@ -17751,7 +17756,7 @@
     <row r="144" spans="1:65">
       <c r="A144" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B144" t="str">
         <f t="shared" si="5"/>
@@ -17830,7 +17835,7 @@
     <row r="145" spans="1:65">
       <c r="A145" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B145" t="str">
         <f t="shared" si="5"/>
@@ -17909,7 +17914,7 @@
     <row r="146" spans="1:65">
       <c r="A146" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B146" t="str">
         <f t="shared" si="5"/>
@@ -17988,7 +17993,7 @@
     <row r="147" spans="1:65">
       <c r="A147" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B147" t="str">
         <f t="shared" si="5"/>
@@ -18067,7 +18072,7 @@
     <row r="148" spans="1:65">
       <c r="A148" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B148" t="str">
         <f t="shared" si="5"/>
@@ -18148,7 +18153,7 @@
     <row r="149" spans="1:65">
       <c r="A149" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B149" t="str">
         <f t="shared" si="5"/>
@@ -18227,7 +18232,7 @@
     <row r="150" spans="1:65">
       <c r="A150" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B150" t="str">
         <f t="shared" si="5"/>
@@ -18306,7 +18311,7 @@
     <row r="151" spans="1:65">
       <c r="A151" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B151" t="str">
         <f t="shared" si="5"/>
@@ -18385,7 +18390,7 @@
     <row r="152" spans="1:65">
       <c r="A152" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B152" t="str">
         <f t="shared" si="5"/>
@@ -18464,7 +18469,7 @@
     <row r="153" spans="1:65">
       <c r="A153" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B153" t="str">
         <f t="shared" si="5"/>
@@ -18543,7 +18548,7 @@
     <row r="154" spans="1:65">
       <c r="A154" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B154" t="str">
         <f t="shared" si="5"/>
@@ -18622,7 +18627,7 @@
     <row r="155" spans="1:65">
       <c r="A155" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B155" t="str">
         <f t="shared" si="5"/>
@@ -18701,7 +18706,7 @@
     <row r="156" spans="1:65">
       <c r="A156" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B156" t="str">
         <f t="shared" si="5"/>
@@ -18780,7 +18785,7 @@
     <row r="157" spans="1:65">
       <c r="A157" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B157" t="str">
         <f t="shared" si="5"/>
@@ -18859,7 +18864,7 @@
     <row r="158" spans="1:65">
       <c r="A158" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B158" t="str">
         <f t="shared" si="5"/>
@@ -18938,7 +18943,7 @@
     <row r="159" spans="1:65">
       <c r="A159" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B159" t="str">
         <f t="shared" si="5"/>
@@ -19017,7 +19022,7 @@
     <row r="160" spans="1:65">
       <c r="A160" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B160" t="str">
         <f t="shared" si="5"/>
@@ -19096,7 +19101,7 @@
     <row r="161" spans="1:65">
       <c r="A161" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B161" t="str">
         <f t="shared" si="5"/>
@@ -19175,7 +19180,7 @@
     <row r="162" spans="1:65">
       <c r="A162" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B162" t="str">
         <f t="shared" si="5"/>
@@ -19254,7 +19259,7 @@
     <row r="163" spans="1:65">
       <c r="A163" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B163" t="str">
         <f t="shared" si="5"/>
@@ -19333,7 +19338,7 @@
     <row r="164" spans="1:65">
       <c r="A164" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B164" t="str">
         <f t="shared" si="5"/>
@@ -19412,7 +19417,7 @@
     <row r="165" spans="1:65">
       <c r="A165" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B165" t="str">
         <f t="shared" si="5"/>
@@ -19491,7 +19496,7 @@
     <row r="166" spans="1:65">
       <c r="A166" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B166" t="str">
         <f t="shared" si="5"/>
@@ -19572,7 +19577,7 @@
     <row r="167" spans="1:65">
       <c r="A167" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B167" t="str">
         <f t="shared" si="5"/>
@@ -19651,7 +19656,7 @@
     <row r="168" spans="1:65">
       <c r="A168" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B168" t="str">
         <f t="shared" si="5"/>
@@ -19733,7 +19738,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B169" t="str">
         <f>TEXT($C169, "HH:mm")</f>
@@ -19815,7 +19820,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B170" t="str">
         <f t="shared" ref="B170:B233" si="7">TEXT($C170, "HH:mm")</f>
@@ -19894,7 +19899,7 @@
     <row r="171" spans="1:65">
       <c r="A171" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B171" t="str">
         <f t="shared" si="7"/>
@@ -19973,7 +19978,7 @@
     <row r="172" spans="1:65">
       <c r="A172" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B172" t="str">
         <f t="shared" si="7"/>
@@ -20054,7 +20059,7 @@
     <row r="173" spans="1:65">
       <c r="A173" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B173" t="str">
         <f t="shared" si="7"/>
@@ -20133,7 +20138,7 @@
     <row r="174" spans="1:65">
       <c r="A174" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B174" t="str">
         <f t="shared" si="7"/>
@@ -20212,7 +20217,7 @@
     <row r="175" spans="1:65">
       <c r="A175" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B175" t="str">
         <f t="shared" si="7"/>
@@ -20291,7 +20296,7 @@
     <row r="176" spans="1:65">
       <c r="A176" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B176" t="str">
         <f t="shared" si="7"/>
@@ -20370,7 +20375,7 @@
     <row r="177" spans="1:65">
       <c r="A177" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B177" t="str">
         <f t="shared" si="7"/>
@@ -20449,7 +20454,7 @@
     <row r="178" spans="1:65">
       <c r="A178" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B178" t="str">
         <f t="shared" si="7"/>
@@ -20530,7 +20535,7 @@
     <row r="179" spans="1:65">
       <c r="A179" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B179" t="str">
         <f t="shared" si="7"/>
@@ -20609,7 +20614,7 @@
     <row r="180" spans="1:65">
       <c r="A180" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B180" t="str">
         <f t="shared" si="7"/>
@@ -20688,7 +20693,7 @@
     <row r="181" spans="1:65">
       <c r="A181" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B181" t="str">
         <f t="shared" si="7"/>
@@ -20769,7 +20774,7 @@
     <row r="182" spans="1:65">
       <c r="A182" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B182" t="str">
         <f t="shared" si="7"/>
@@ -20850,7 +20855,7 @@
     <row r="183" spans="1:65">
       <c r="A183" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B183" t="str">
         <f t="shared" si="7"/>
@@ -20931,7 +20936,7 @@
     <row r="184" spans="1:65">
       <c r="A184" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B184" t="str">
         <f t="shared" si="7"/>
@@ -21014,7 +21019,7 @@
     <row r="185" spans="1:65">
       <c r="A185" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B185" t="str">
         <f t="shared" si="7"/>
@@ -21095,7 +21100,7 @@
     <row r="186" spans="1:65">
       <c r="A186" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B186" t="str">
         <f t="shared" si="7"/>
@@ -21176,7 +21181,7 @@
     <row r="187" spans="1:65">
       <c r="A187" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B187" t="str">
         <f t="shared" si="7"/>
@@ -21257,7 +21262,7 @@
     <row r="188" spans="1:65">
       <c r="A188" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B188" t="str">
         <f t="shared" si="7"/>
@@ -21338,7 +21343,7 @@
     <row r="189" spans="1:65">
       <c r="A189" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B189" t="str">
         <f t="shared" si="7"/>
@@ -21419,7 +21424,7 @@
     <row r="190" spans="1:65">
       <c r="A190" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B190" t="str">
         <f t="shared" si="7"/>
@@ -21502,7 +21507,7 @@
     <row r="191" spans="1:65">
       <c r="A191" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B191" t="str">
         <f t="shared" si="7"/>
@@ -21585,7 +21590,7 @@
     <row r="192" spans="1:65">
       <c r="A192" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B192" t="str">
         <f t="shared" si="7"/>
@@ -21668,7 +21673,7 @@
     <row r="193" spans="1:65">
       <c r="A193" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B193" t="str">
         <f t="shared" si="7"/>
@@ -21751,7 +21756,7 @@
     <row r="194" spans="1:65">
       <c r="A194" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B194" t="str">
         <f t="shared" si="7"/>
@@ -21832,7 +21837,7 @@
     <row r="195" spans="1:65">
       <c r="A195" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B195" t="str">
         <f t="shared" si="7"/>
@@ -21913,7 +21918,7 @@
     <row r="196" spans="1:65">
       <c r="A196" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B196" t="str">
         <f t="shared" si="7"/>
@@ -21996,7 +22001,7 @@
     <row r="197" spans="1:65">
       <c r="A197" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B197" t="str">
         <f t="shared" si="7"/>
@@ -22075,7 +22080,7 @@
     <row r="198" spans="1:65">
       <c r="A198" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B198" t="str">
         <f t="shared" si="7"/>
@@ -22154,7 +22159,7 @@
     <row r="199" spans="1:65">
       <c r="A199" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B199" t="str">
         <f t="shared" si="7"/>
@@ -22233,7 +22238,7 @@
     <row r="200" spans="1:65">
       <c r="A200" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B200" t="str">
         <f t="shared" si="7"/>
@@ -22312,7 +22317,7 @@
     <row r="201" spans="1:65">
       <c r="A201" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B201" t="str">
         <f t="shared" si="7"/>
@@ -22391,7 +22396,7 @@
     <row r="202" spans="1:65">
       <c r="A202" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B202" t="str">
         <f t="shared" si="7"/>
@@ -22472,7 +22477,7 @@
     <row r="203" spans="1:65">
       <c r="A203" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B203" t="str">
         <f t="shared" si="7"/>
@@ -22551,7 +22556,7 @@
     <row r="204" spans="1:65">
       <c r="A204" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B204" t="str">
         <f t="shared" si="7"/>
@@ -22630,7 +22635,7 @@
     <row r="205" spans="1:65">
       <c r="A205" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B205" t="str">
         <f t="shared" si="7"/>
@@ -22709,7 +22714,7 @@
     <row r="206" spans="1:65">
       <c r="A206" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B206" t="str">
         <f t="shared" si="7"/>
@@ -22788,7 +22793,7 @@
     <row r="207" spans="1:65">
       <c r="A207" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B207" t="str">
         <f t="shared" si="7"/>
@@ -22867,7 +22872,7 @@
     <row r="208" spans="1:65">
       <c r="A208" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B208" t="str">
         <f t="shared" si="7"/>
@@ -22948,7 +22953,7 @@
     <row r="209" spans="1:65">
       <c r="A209" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B209" t="str">
         <f t="shared" si="7"/>
@@ -23027,7 +23032,7 @@
     <row r="210" spans="1:65">
       <c r="A210" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B210" t="str">
         <f t="shared" si="7"/>
@@ -23106,7 +23111,7 @@
     <row r="211" spans="1:65">
       <c r="A211" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B211" t="str">
         <f t="shared" si="7"/>
@@ -23187,7 +23192,7 @@
     <row r="212" spans="1:65">
       <c r="A212" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B212" t="str">
         <f t="shared" si="7"/>
@@ -23266,7 +23271,7 @@
     <row r="213" spans="1:65">
       <c r="A213" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B213" t="str">
         <f t="shared" si="7"/>
@@ -23345,7 +23350,7 @@
     <row r="214" spans="1:65">
       <c r="A214" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B214" t="str">
         <f t="shared" si="7"/>
@@ -23424,7 +23429,7 @@
     <row r="215" spans="1:65">
       <c r="A215" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B215" t="str">
         <f t="shared" si="7"/>
@@ -23503,7 +23508,7 @@
     <row r="216" spans="1:65">
       <c r="A216" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B216" t="str">
         <f t="shared" si="7"/>
@@ -23582,7 +23587,7 @@
     <row r="217" spans="1:65">
       <c r="A217" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B217" t="str">
         <f t="shared" si="7"/>
@@ -23661,7 +23666,7 @@
     <row r="218" spans="1:65">
       <c r="A218" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B218" t="str">
         <f t="shared" si="7"/>
@@ -23740,7 +23745,7 @@
     <row r="219" spans="1:65">
       <c r="A219" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B219" t="str">
         <f t="shared" si="7"/>
@@ -23819,7 +23824,7 @@
     <row r="220" spans="1:65">
       <c r="A220" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B220" t="str">
         <f t="shared" si="7"/>
@@ -23900,7 +23905,7 @@
     <row r="221" spans="1:65">
       <c r="A221" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B221" t="str">
         <f t="shared" si="7"/>
@@ -23979,7 +23984,7 @@
     <row r="222" spans="1:65">
       <c r="A222" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B222" t="str">
         <f t="shared" si="7"/>
@@ -24058,7 +24063,7 @@
     <row r="223" spans="1:65">
       <c r="A223" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B223" t="str">
         <f t="shared" si="7"/>
@@ -24137,7 +24142,7 @@
     <row r="224" spans="1:65">
       <c r="A224" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B224" t="str">
         <f t="shared" si="7"/>
@@ -24216,7 +24221,7 @@
     <row r="225" spans="1:65">
       <c r="A225" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B225" t="str">
         <f t="shared" si="7"/>
@@ -24295,7 +24300,7 @@
     <row r="226" spans="1:65">
       <c r="A226" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B226" t="str">
         <f t="shared" si="7"/>
@@ -24374,7 +24379,7 @@
     <row r="227" spans="1:65">
       <c r="A227" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B227" t="str">
         <f t="shared" si="7"/>
@@ -24453,7 +24458,7 @@
     <row r="228" spans="1:65">
       <c r="A228" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B228" t="str">
         <f t="shared" si="7"/>
@@ -24532,7 +24537,7 @@
     <row r="229" spans="1:65">
       <c r="A229" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B229" t="str">
         <f t="shared" si="7"/>
@@ -24611,7 +24616,7 @@
     <row r="230" spans="1:65">
       <c r="A230" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B230" t="str">
         <f t="shared" si="7"/>
@@ -24690,7 +24695,7 @@
     <row r="231" spans="1:65">
       <c r="A231" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B231" t="str">
         <f t="shared" si="7"/>
@@ -24769,7 +24774,7 @@
     <row r="232" spans="1:65">
       <c r="A232" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B232" t="str">
         <f t="shared" si="7"/>
@@ -24848,7 +24853,7 @@
     <row r="233" spans="1:65">
       <c r="A233" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B233" t="str">
         <f t="shared" si="7"/>
@@ -24930,7 +24935,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B234" t="str">
         <f t="shared" ref="B234:B291" si="9">TEXT($C234, "HH:mm")</f>
@@ -25009,7 +25014,7 @@
     <row r="235" spans="1:65">
       <c r="A235" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B235" t="str">
         <f t="shared" si="9"/>
@@ -25088,7 +25093,7 @@
     <row r="236" spans="1:65">
       <c r="A236" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B236" t="str">
         <f t="shared" si="9"/>
@@ -25167,7 +25172,7 @@
     <row r="237" spans="1:65">
       <c r="A237" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B237" t="str">
         <f t="shared" si="9"/>
@@ -25246,7 +25251,7 @@
     <row r="238" spans="1:65">
       <c r="A238" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B238" t="str">
         <f t="shared" si="9"/>
@@ -25325,7 +25330,7 @@
     <row r="239" spans="1:65">
       <c r="A239" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B239" t="str">
         <f t="shared" si="9"/>
@@ -25404,7 +25409,7 @@
     <row r="240" spans="1:65">
       <c r="A240" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B240" t="str">
         <f t="shared" si="9"/>
@@ -25483,7 +25488,7 @@
     <row r="241" spans="1:65">
       <c r="A241" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B241" t="str">
         <f t="shared" si="9"/>
@@ -25562,7 +25567,7 @@
     <row r="242" spans="1:65">
       <c r="A242" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B242" t="str">
         <f t="shared" si="9"/>
@@ -25641,7 +25646,7 @@
     <row r="243" spans="1:65">
       <c r="A243" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B243" t="str">
         <f t="shared" si="9"/>
@@ -25720,7 +25725,7 @@
     <row r="244" spans="1:65">
       <c r="A244" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B244" t="str">
         <f t="shared" si="9"/>
@@ -25799,7 +25804,7 @@
     <row r="245" spans="1:65">
       <c r="A245" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B245" t="str">
         <f t="shared" si="9"/>
@@ -25878,7 +25883,7 @@
     <row r="246" spans="1:65">
       <c r="A246" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B246" t="str">
         <f t="shared" si="9"/>
@@ -25957,7 +25962,7 @@
     <row r="247" spans="1:65">
       <c r="A247" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B247" t="str">
         <f t="shared" si="9"/>
@@ -26036,7 +26041,7 @@
     <row r="248" spans="1:65">
       <c r="A248" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B248" t="str">
         <f t="shared" si="9"/>
@@ -26115,7 +26120,7 @@
     <row r="249" spans="1:65">
       <c r="A249" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B249" t="str">
         <f t="shared" si="9"/>
@@ -26194,7 +26199,7 @@
     <row r="250" spans="1:65">
       <c r="A250" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B250" t="str">
         <f t="shared" si="9"/>
@@ -26273,7 +26278,7 @@
     <row r="251" spans="1:65">
       <c r="A251" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B251" t="str">
         <f t="shared" si="9"/>
@@ -26352,7 +26357,7 @@
     <row r="252" spans="1:65">
       <c r="A252" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B252" t="str">
         <f t="shared" si="9"/>
@@ -26431,7 +26436,7 @@
     <row r="253" spans="1:65">
       <c r="A253" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B253" t="str">
         <f t="shared" si="9"/>
@@ -26510,7 +26515,7 @@
     <row r="254" spans="1:65">
       <c r="A254" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B254" t="str">
         <f t="shared" si="9"/>
@@ -26589,7 +26594,7 @@
     <row r="255" spans="1:65">
       <c r="A255" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B255" t="str">
         <f t="shared" si="9"/>
@@ -26668,7 +26673,7 @@
     <row r="256" spans="1:65">
       <c r="A256" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B256" t="str">
         <f t="shared" si="9"/>
@@ -26747,7 +26752,7 @@
     <row r="257" spans="1:65">
       <c r="A257" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B257" t="str">
         <f t="shared" si="9"/>
@@ -26826,7 +26831,7 @@
     <row r="258" spans="1:65">
       <c r="A258" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B258" t="str">
         <f t="shared" si="9"/>
@@ -26905,7 +26910,7 @@
     <row r="259" spans="1:65">
       <c r="A259" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B259" t="str">
         <f t="shared" si="9"/>
@@ -26984,7 +26989,7 @@
     <row r="260" spans="1:65">
       <c r="A260" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B260" t="str">
         <f t="shared" si="9"/>
@@ -27063,7 +27068,7 @@
     <row r="261" spans="1:65">
       <c r="A261" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B261" t="str">
         <f t="shared" si="9"/>
@@ -27142,7 +27147,7 @@
     <row r="262" spans="1:65">
       <c r="A262" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B262" t="str">
         <f t="shared" si="9"/>
@@ -27221,7 +27226,7 @@
     <row r="263" spans="1:65">
       <c r="A263" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B263" t="str">
         <f t="shared" si="9"/>
@@ -27300,7 +27305,7 @@
     <row r="264" spans="1:65">
       <c r="A264" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B264" t="str">
         <f t="shared" si="9"/>
@@ -27379,7 +27384,7 @@
     <row r="265" spans="1:65">
       <c r="A265" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B265" t="str">
         <f t="shared" si="9"/>
@@ -27458,7 +27463,7 @@
     <row r="266" spans="1:65">
       <c r="A266" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B266" t="str">
         <f t="shared" si="9"/>
@@ -27537,7 +27542,7 @@
     <row r="267" spans="1:65">
       <c r="A267" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B267" t="str">
         <f t="shared" si="9"/>
@@ -27616,7 +27621,7 @@
     <row r="268" spans="1:65">
       <c r="A268" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B268" t="str">
         <f t="shared" si="9"/>
@@ -27695,7 +27700,7 @@
     <row r="269" spans="1:65">
       <c r="A269" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B269" t="str">
         <f t="shared" si="9"/>
@@ -27774,7 +27779,7 @@
     <row r="270" spans="1:65">
       <c r="A270" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B270" t="str">
         <f t="shared" si="9"/>
@@ -27853,7 +27858,7 @@
     <row r="271" spans="1:65">
       <c r="A271" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B271" t="str">
         <f t="shared" si="9"/>
@@ -27932,7 +27937,7 @@
     <row r="272" spans="1:65">
       <c r="A272" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B272" t="str">
         <f t="shared" si="9"/>
@@ -28011,7 +28016,7 @@
     <row r="273" spans="1:65">
       <c r="A273" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B273" t="str">
         <f t="shared" si="9"/>
@@ -28090,7 +28095,7 @@
     <row r="274" spans="1:65">
       <c r="A274" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B274" t="str">
         <f t="shared" si="9"/>
@@ -28169,7 +28174,7 @@
     <row r="275" spans="1:65">
       <c r="A275" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B275" t="str">
         <f t="shared" si="9"/>
@@ -28248,7 +28253,7 @@
     <row r="276" spans="1:65">
       <c r="A276" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B276" t="str">
         <f t="shared" si="9"/>
@@ -28327,7 +28332,7 @@
     <row r="277" spans="1:65">
       <c r="A277" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B277" t="str">
         <f t="shared" si="9"/>
@@ -28406,7 +28411,7 @@
     <row r="278" spans="1:65">
       <c r="A278" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B278" t="str">
         <f t="shared" si="9"/>
@@ -28485,7 +28490,7 @@
     <row r="279" spans="1:65">
       <c r="A279" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B279" t="str">
         <f t="shared" si="9"/>
@@ -28564,7 +28569,7 @@
     <row r="280" spans="1:65">
       <c r="A280" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B280" t="str">
         <f t="shared" si="9"/>
@@ -28643,7 +28648,7 @@
     <row r="281" spans="1:65">
       <c r="A281" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B281" t="str">
         <f t="shared" si="9"/>
@@ -28722,7 +28727,7 @@
     <row r="282" spans="1:65">
       <c r="A282" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B282" t="str">
         <f t="shared" si="9"/>
@@ -28801,7 +28806,7 @@
     <row r="283" spans="1:65">
       <c r="A283" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B283" t="str">
         <f t="shared" si="9"/>
@@ -28880,7 +28885,7 @@
     <row r="284" spans="1:65">
       <c r="A284" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B284" t="str">
         <f t="shared" si="9"/>
@@ -28959,7 +28964,7 @@
     <row r="285" spans="1:65">
       <c r="A285" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B285" t="str">
         <f t="shared" si="9"/>
@@ -29038,7 +29043,7 @@
     <row r="286" spans="1:65">
       <c r="A286" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B286" t="str">
         <f t="shared" si="9"/>
@@ -29117,7 +29122,7 @@
     <row r="287" spans="1:65">
       <c r="A287" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B287" t="str">
         <f t="shared" si="9"/>
@@ -29196,7 +29201,7 @@
     <row r="288" spans="1:65">
       <c r="A288" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B288" t="str">
         <f t="shared" si="9"/>
@@ -29275,7 +29280,7 @@
     <row r="289" spans="1:65">
       <c r="A289" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B289" t="str">
         <f t="shared" si="9"/>
@@ -29354,7 +29359,7 @@
     <row r="290" spans="1:65">
       <c r="A290" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B290" t="str">
         <f t="shared" si="9"/>
@@ -29433,7 +29438,7 @@
     <row r="291" spans="1:65">
       <c r="A291" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:30</v>
+        <v>01:35</v>
       </c>
       <c r="B291" t="str">
         <f t="shared" si="9"/>

--- a/Vite-Vercel開発.xlsx
+++ b/Vite-Vercel開発.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2c67ec30e06f060f/work/GitHub/work-time-tracker/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{1928CA11-C4AD-40E9-B1C5-143667E830EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C6CDF44-8573-4EE9-90B3-D9E1DBF55244}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{1928CA11-C4AD-40E9-B1C5-143667E830EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5559AAB8-1CD9-4D76-BCA2-D303AE42D0F6}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1544" uniqueCount="921">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1545" uniqueCount="922">
   <si>
     <t>npm install -g vercel</t>
     <phoneticPr fontId="1"/>
@@ -5362,6 +5362,10 @@
   </si>
   <si>
     <t>Found 63 errors in 16 files.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Found 63 errors in 15 files.</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -6134,7 +6138,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{083174DA-A42C-4F9C-978E-61AEAAD9DDFF}">
-  <dimension ref="B2:D26"/>
+  <dimension ref="B2:D27"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
@@ -6272,6 +6276,11 @@
     <row r="26" spans="3:3">
       <c r="C26" t="s">
         <v>918</v>
+      </c>
+    </row>
+    <row r="27" spans="3:3">
+      <c r="C27" t="s">
+        <v>921</v>
       </c>
     </row>
   </sheetData>
@@ -6438,7 +6447,7 @@
       MOD(NOW(),1),
       TIME(0,5,0)
     ),"HH:mm")</f>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B2" s="19"/>
       <c r="D2" s="1">
@@ -6449,7 +6458,7 @@
     <row r="3" spans="1:65">
       <c r="A3" s="19" t="str">
         <f ca="1">TEXT(NOW(),"HH:mm")</f>
-        <v>01:39</v>
+        <v>01:46</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="17" t="s">
@@ -6648,7 +6657,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B4" t="str">
         <f t="shared" ref="B4:B67" si="1">TEXT($C4, "HH:mm")</f>
@@ -6727,7 +6736,7 @@
     <row r="5" spans="1:65">
       <c r="A5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B5" t="str">
         <f t="shared" si="1"/>
@@ -6806,7 +6815,7 @@
     <row r="6" spans="1:65">
       <c r="A6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B6" t="str">
         <f t="shared" si="1"/>
@@ -6885,7 +6894,7 @@
     <row r="7" spans="1:65">
       <c r="A7" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B7" t="str">
         <f t="shared" si="1"/>
@@ -6964,7 +6973,7 @@
     <row r="8" spans="1:65">
       <c r="A8" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B8" t="str">
         <f t="shared" si="1"/>
@@ -7043,7 +7052,7 @@
     <row r="9" spans="1:65">
       <c r="A9" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B9" t="str">
         <f t="shared" si="1"/>
@@ -7122,7 +7131,7 @@
     <row r="10" spans="1:65">
       <c r="A10" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B10" t="str">
         <f t="shared" si="1"/>
@@ -7201,7 +7210,7 @@
     <row r="11" spans="1:65">
       <c r="A11" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B11" t="str">
         <f t="shared" si="1"/>
@@ -7280,7 +7289,7 @@
     <row r="12" spans="1:65">
       <c r="A12" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B12" t="str">
         <f t="shared" si="1"/>
@@ -7359,7 +7368,7 @@
     <row r="13" spans="1:65">
       <c r="A13" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B13" t="str">
         <f t="shared" si="1"/>
@@ -7438,7 +7447,7 @@
     <row r="14" spans="1:65">
       <c r="A14" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B14" t="str">
         <f t="shared" si="1"/>
@@ -7517,7 +7526,7 @@
     <row r="15" spans="1:65">
       <c r="A15" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B15" t="str">
         <f t="shared" si="1"/>
@@ -7596,7 +7605,7 @@
     <row r="16" spans="1:65">
       <c r="A16" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B16" t="str">
         <f t="shared" si="1"/>
@@ -7675,7 +7684,7 @@
     <row r="17" spans="1:65">
       <c r="A17" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B17" t="str">
         <f t="shared" si="1"/>
@@ -7754,7 +7763,7 @@
     <row r="18" spans="1:65">
       <c r="A18" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B18" t="str">
         <f t="shared" si="1"/>
@@ -7833,7 +7842,7 @@
     <row r="19" spans="1:65">
       <c r="A19" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B19" t="str">
         <f t="shared" si="1"/>
@@ -7912,7 +7921,7 @@
     <row r="20" spans="1:65">
       <c r="A20" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B20" t="str">
         <f t="shared" si="1"/>
@@ -7991,7 +8000,7 @@
     <row r="21" spans="1:65">
       <c r="A21" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B21" t="str">
         <f t="shared" si="1"/>
@@ -8070,7 +8079,7 @@
     <row r="22" spans="1:65">
       <c r="A22" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B22" t="str">
         <f t="shared" si="1"/>
@@ -8149,7 +8158,7 @@
     <row r="23" spans="1:65">
       <c r="A23" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B23" t="str">
         <f t="shared" si="1"/>
@@ -8228,7 +8237,7 @@
     <row r="24" spans="1:65">
       <c r="A24" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B24" t="str">
         <f t="shared" si="1"/>
@@ -8307,7 +8316,7 @@
     <row r="25" spans="1:65">
       <c r="A25" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B25" t="str">
         <f t="shared" si="1"/>
@@ -8386,7 +8395,7 @@
     <row r="26" spans="1:65">
       <c r="A26" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B26" t="str">
         <f t="shared" si="1"/>
@@ -8465,7 +8474,7 @@
     <row r="27" spans="1:65">
       <c r="A27" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B27" t="str">
         <f t="shared" si="1"/>
@@ -8544,7 +8553,7 @@
     <row r="28" spans="1:65">
       <c r="A28" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B28" t="str">
         <f t="shared" si="1"/>
@@ -8625,7 +8634,7 @@
     <row r="29" spans="1:65">
       <c r="A29" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B29" t="str">
         <f t="shared" si="1"/>
@@ -8706,7 +8715,7 @@
     <row r="30" spans="1:65">
       <c r="A30" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B30" t="str">
         <f t="shared" si="1"/>
@@ -8787,7 +8796,7 @@
     <row r="31" spans="1:65">
       <c r="A31" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B31" t="str">
         <f t="shared" si="1"/>
@@ -8866,7 +8875,7 @@
     <row r="32" spans="1:65">
       <c r="A32" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B32" t="str">
         <f t="shared" si="1"/>
@@ -8945,7 +8954,7 @@
     <row r="33" spans="1:65">
       <c r="A33" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B33" t="str">
         <f t="shared" si="1"/>
@@ -9024,7 +9033,7 @@
     <row r="34" spans="1:65">
       <c r="A34" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B34" t="str">
         <f t="shared" si="1"/>
@@ -9105,7 +9114,7 @@
     <row r="35" spans="1:65">
       <c r="A35" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B35" t="str">
         <f t="shared" si="1"/>
@@ -9186,7 +9195,7 @@
     <row r="36" spans="1:65">
       <c r="A36" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B36" t="str">
         <f t="shared" si="1"/>
@@ -9267,7 +9276,7 @@
     <row r="37" spans="1:65">
       <c r="A37" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B37" t="str">
         <f t="shared" si="1"/>
@@ -9346,7 +9355,7 @@
     <row r="38" spans="1:65">
       <c r="A38" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B38" t="str">
         <f t="shared" si="1"/>
@@ -9425,7 +9434,7 @@
     <row r="39" spans="1:65">
       <c r="A39" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B39" t="str">
         <f t="shared" si="1"/>
@@ -9504,7 +9513,7 @@
     <row r="40" spans="1:65">
       <c r="A40" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B40" t="str">
         <f t="shared" si="1"/>
@@ -9583,7 +9592,7 @@
     <row r="41" spans="1:65">
       <c r="A41" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B41" t="str">
         <f t="shared" si="1"/>
@@ -9662,7 +9671,7 @@
     <row r="42" spans="1:65">
       <c r="A42" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B42" t="str">
         <f t="shared" si="1"/>
@@ -9743,7 +9752,7 @@
     <row r="43" spans="1:65">
       <c r="A43" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B43" t="str">
         <f t="shared" si="1"/>
@@ -9824,7 +9833,7 @@
     <row r="44" spans="1:65">
       <c r="A44" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B44" t="str">
         <f t="shared" si="1"/>
@@ -9903,7 +9912,7 @@
     <row r="45" spans="1:65">
       <c r="A45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B45" t="str">
         <f t="shared" si="1"/>
@@ -9982,7 +9991,7 @@
     <row r="46" spans="1:65">
       <c r="A46" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B46" t="str">
         <f t="shared" si="1"/>
@@ -10061,7 +10070,7 @@
     <row r="47" spans="1:65">
       <c r="A47" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B47" t="str">
         <f t="shared" si="1"/>
@@ -10140,7 +10149,7 @@
     <row r="48" spans="1:65">
       <c r="A48" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B48" t="str">
         <f t="shared" si="1"/>
@@ -10219,7 +10228,7 @@
     <row r="49" spans="1:65">
       <c r="A49" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B49" t="str">
         <f t="shared" si="1"/>
@@ -10300,7 +10309,7 @@
     <row r="50" spans="1:65">
       <c r="A50" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B50" t="str">
         <f t="shared" si="1"/>
@@ -10381,7 +10390,7 @@
     <row r="51" spans="1:65">
       <c r="A51" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B51" t="str">
         <f t="shared" si="1"/>
@@ -10460,7 +10469,7 @@
     <row r="52" spans="1:65">
       <c r="A52" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B52" t="str">
         <f t="shared" si="1"/>
@@ -10539,7 +10548,7 @@
     <row r="53" spans="1:65">
       <c r="A53" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B53" t="str">
         <f t="shared" si="1"/>
@@ -10618,7 +10627,7 @@
     <row r="54" spans="1:65">
       <c r="A54" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B54" t="str">
         <f t="shared" si="1"/>
@@ -10697,7 +10706,7 @@
     <row r="55" spans="1:65">
       <c r="A55" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B55" t="str">
         <f t="shared" si="1"/>
@@ -10776,7 +10785,7 @@
     <row r="56" spans="1:65">
       <c r="A56" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B56" t="str">
         <f t="shared" si="1"/>
@@ -10857,7 +10866,7 @@
     <row r="57" spans="1:65">
       <c r="A57" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B57" t="str">
         <f t="shared" si="1"/>
@@ -10936,7 +10945,7 @@
     <row r="58" spans="1:65">
       <c r="A58" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B58" t="str">
         <f t="shared" si="1"/>
@@ -11017,7 +11026,7 @@
     <row r="59" spans="1:65">
       <c r="A59" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B59" t="str">
         <f t="shared" si="1"/>
@@ -11096,7 +11105,7 @@
     <row r="60" spans="1:65">
       <c r="A60" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B60" t="str">
         <f t="shared" si="1"/>
@@ -11175,7 +11184,7 @@
     <row r="61" spans="1:65">
       <c r="A61" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B61" t="str">
         <f t="shared" si="1"/>
@@ -11254,7 +11263,7 @@
     <row r="62" spans="1:65">
       <c r="A62" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B62" t="str">
         <f t="shared" si="1"/>
@@ -11333,7 +11342,7 @@
     <row r="63" spans="1:65">
       <c r="A63" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B63" t="str">
         <f t="shared" si="1"/>
@@ -11412,7 +11421,7 @@
     <row r="64" spans="1:65">
       <c r="A64" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B64" t="str">
         <f t="shared" si="1"/>
@@ -11493,7 +11502,7 @@
     <row r="65" spans="1:65">
       <c r="A65" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B65" t="str">
         <f t="shared" si="1"/>
@@ -11572,7 +11581,7 @@
     <row r="66" spans="1:65">
       <c r="A66" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B66" t="str">
         <f t="shared" si="1"/>
@@ -11651,7 +11660,7 @@
     <row r="67" spans="1:65">
       <c r="A67" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B67" t="str">
         <f t="shared" si="1"/>
@@ -11733,7 +11742,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B68" t="str">
         <f t="shared" ref="B68:B131" si="3">TEXT($C68, "HH:mm")</f>
@@ -11812,7 +11821,7 @@
     <row r="69" spans="1:65">
       <c r="A69" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B69" t="str">
         <f t="shared" si="3"/>
@@ -11891,7 +11900,7 @@
     <row r="70" spans="1:65">
       <c r="A70" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B70" t="str">
         <f t="shared" si="3"/>
@@ -11970,7 +11979,7 @@
     <row r="71" spans="1:65">
       <c r="A71" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B71" t="str">
         <f t="shared" si="3"/>
@@ -12049,7 +12058,7 @@
     <row r="72" spans="1:65">
       <c r="A72" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B72" t="str">
         <f t="shared" si="3"/>
@@ -12128,7 +12137,7 @@
     <row r="73" spans="1:65">
       <c r="A73" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B73" t="str">
         <f t="shared" si="3"/>
@@ -12207,7 +12216,7 @@
     <row r="74" spans="1:65">
       <c r="A74" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B74" t="str">
         <f t="shared" si="3"/>
@@ -12286,7 +12295,7 @@
     <row r="75" spans="1:65">
       <c r="A75" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B75" t="str">
         <f t="shared" si="3"/>
@@ -12365,7 +12374,7 @@
     <row r="76" spans="1:65">
       <c r="A76" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B76" t="str">
         <f t="shared" si="3"/>
@@ -12444,7 +12453,7 @@
     <row r="77" spans="1:65">
       <c r="A77" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B77" t="str">
         <f t="shared" si="3"/>
@@ -12523,7 +12532,7 @@
     <row r="78" spans="1:65">
       <c r="A78" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B78" t="str">
         <f t="shared" si="3"/>
@@ -12602,7 +12611,7 @@
     <row r="79" spans="1:65">
       <c r="A79" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B79" t="str">
         <f t="shared" si="3"/>
@@ -12681,7 +12690,7 @@
     <row r="80" spans="1:65">
       <c r="A80" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B80" t="str">
         <f t="shared" si="3"/>
@@ -12760,7 +12769,7 @@
     <row r="81" spans="1:65">
       <c r="A81" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B81" t="str">
         <f t="shared" si="3"/>
@@ -12839,7 +12848,7 @@
     <row r="82" spans="1:65">
       <c r="A82" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B82" t="str">
         <f t="shared" si="3"/>
@@ -12918,7 +12927,7 @@
     <row r="83" spans="1:65">
       <c r="A83" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B83" t="str">
         <f t="shared" si="3"/>
@@ -12997,7 +13006,7 @@
     <row r="84" spans="1:65">
       <c r="A84" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B84" t="str">
         <f t="shared" si="3"/>
@@ -13076,7 +13085,7 @@
     <row r="85" spans="1:65">
       <c r="A85" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B85" t="str">
         <f t="shared" si="3"/>
@@ -13155,7 +13164,7 @@
     <row r="86" spans="1:65">
       <c r="A86" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B86" t="str">
         <f t="shared" si="3"/>
@@ -13234,7 +13243,7 @@
     <row r="87" spans="1:65">
       <c r="A87" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B87" t="str">
         <f t="shared" si="3"/>
@@ -13313,7 +13322,7 @@
     <row r="88" spans="1:65">
       <c r="A88" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B88" t="str">
         <f t="shared" si="3"/>
@@ -13392,7 +13401,7 @@
     <row r="89" spans="1:65">
       <c r="A89" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B89" t="str">
         <f t="shared" si="3"/>
@@ -13471,7 +13480,7 @@
     <row r="90" spans="1:65">
       <c r="A90" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B90" t="str">
         <f t="shared" si="3"/>
@@ -13550,7 +13559,7 @@
     <row r="91" spans="1:65">
       <c r="A91" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B91" t="str">
         <f t="shared" si="3"/>
@@ -13629,7 +13638,7 @@
     <row r="92" spans="1:65">
       <c r="A92" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B92" t="str">
         <f t="shared" si="3"/>
@@ -13708,7 +13717,7 @@
     <row r="93" spans="1:65">
       <c r="A93" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B93" t="str">
         <f t="shared" si="3"/>
@@ -13787,7 +13796,7 @@
     <row r="94" spans="1:65">
       <c r="A94" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B94" t="str">
         <f t="shared" si="3"/>
@@ -13866,7 +13875,7 @@
     <row r="95" spans="1:65">
       <c r="A95" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B95" t="str">
         <f t="shared" si="3"/>
@@ -13945,7 +13954,7 @@
     <row r="96" spans="1:65">
       <c r="A96" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B96" t="str">
         <f t="shared" si="3"/>
@@ -14024,7 +14033,7 @@
     <row r="97" spans="1:65">
       <c r="A97" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B97" t="str">
         <f t="shared" si="3"/>
@@ -14103,7 +14112,7 @@
     <row r="98" spans="1:65">
       <c r="A98" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B98" t="str">
         <f t="shared" si="3"/>
@@ -14182,7 +14191,7 @@
     <row r="99" spans="1:65">
       <c r="A99" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B99" t="str">
         <f t="shared" si="3"/>
@@ -14261,7 +14270,7 @@
     <row r="100" spans="1:65">
       <c r="A100" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B100" t="str">
         <f t="shared" si="3"/>
@@ -14342,7 +14351,7 @@
     <row r="101" spans="1:65">
       <c r="A101" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B101" t="str">
         <f t="shared" si="3"/>
@@ -14421,7 +14430,7 @@
     <row r="102" spans="1:65">
       <c r="A102" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B102" t="str">
         <f t="shared" si="3"/>
@@ -14500,7 +14509,7 @@
     <row r="103" spans="1:65">
       <c r="A103" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B103" t="str">
         <f t="shared" si="3"/>
@@ -14579,7 +14588,7 @@
     <row r="104" spans="1:65">
       <c r="A104" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B104" t="str">
         <f t="shared" si="3"/>
@@ -14658,7 +14667,7 @@
     <row r="105" spans="1:65">
       <c r="A105" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B105" t="str">
         <f t="shared" si="3"/>
@@ -14737,7 +14746,7 @@
     <row r="106" spans="1:65">
       <c r="A106" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B106" t="str">
         <f t="shared" si="3"/>
@@ -14818,7 +14827,7 @@
     <row r="107" spans="1:65">
       <c r="A107" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B107" t="str">
         <f t="shared" si="3"/>
@@ -14899,7 +14908,7 @@
     <row r="108" spans="1:65">
       <c r="A108" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B108" t="str">
         <f t="shared" si="3"/>
@@ -14978,7 +14987,7 @@
     <row r="109" spans="1:65">
       <c r="A109" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B109" t="str">
         <f t="shared" si="3"/>
@@ -15057,7 +15066,7 @@
     <row r="110" spans="1:65">
       <c r="A110" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B110" t="str">
         <f t="shared" si="3"/>
@@ -15136,7 +15145,7 @@
     <row r="111" spans="1:65">
       <c r="A111" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B111" t="str">
         <f t="shared" si="3"/>
@@ -15215,7 +15224,7 @@
     <row r="112" spans="1:65">
       <c r="A112" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B112" t="str">
         <f t="shared" si="3"/>
@@ -15296,7 +15305,7 @@
     <row r="113" spans="1:65">
       <c r="A113" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B113" t="str">
         <f t="shared" si="3"/>
@@ -15375,7 +15384,7 @@
     <row r="114" spans="1:65">
       <c r="A114" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B114" t="str">
         <f t="shared" si="3"/>
@@ -15454,7 +15463,7 @@
     <row r="115" spans="1:65">
       <c r="A115" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B115" t="str">
         <f t="shared" si="3"/>
@@ -15533,7 +15542,7 @@
     <row r="116" spans="1:65">
       <c r="A116" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B116" t="str">
         <f t="shared" si="3"/>
@@ -15612,7 +15621,7 @@
     <row r="117" spans="1:65">
       <c r="A117" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B117" t="str">
         <f t="shared" si="3"/>
@@ -15691,7 +15700,7 @@
     <row r="118" spans="1:65">
       <c r="A118" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B118" t="str">
         <f t="shared" si="3"/>
@@ -15770,7 +15779,7 @@
     <row r="119" spans="1:65">
       <c r="A119" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B119" t="str">
         <f t="shared" si="3"/>
@@ -15849,7 +15858,7 @@
     <row r="120" spans="1:65">
       <c r="A120" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B120" t="str">
         <f t="shared" si="3"/>
@@ -15928,7 +15937,7 @@
     <row r="121" spans="1:65">
       <c r="A121" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B121" t="str">
         <f t="shared" si="3"/>
@@ -16007,7 +16016,7 @@
     <row r="122" spans="1:65">
       <c r="A122" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B122" t="str">
         <f t="shared" si="3"/>
@@ -16086,7 +16095,7 @@
     <row r="123" spans="1:65">
       <c r="A123" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B123" t="str">
         <f t="shared" si="3"/>
@@ -16165,7 +16174,7 @@
     <row r="124" spans="1:65">
       <c r="A124" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B124" t="str">
         <f t="shared" si="3"/>
@@ -16246,7 +16255,7 @@
     <row r="125" spans="1:65">
       <c r="A125" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B125" t="str">
         <f t="shared" si="3"/>
@@ -16327,7 +16336,7 @@
     <row r="126" spans="1:65">
       <c r="A126" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B126" t="str">
         <f t="shared" si="3"/>
@@ -16406,7 +16415,7 @@
     <row r="127" spans="1:65">
       <c r="A127" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B127" t="str">
         <f t="shared" si="3"/>
@@ -16485,7 +16494,7 @@
     <row r="128" spans="1:65">
       <c r="A128" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B128" t="str">
         <f t="shared" si="3"/>
@@ -16564,7 +16573,7 @@
     <row r="129" spans="1:65">
       <c r="A129" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B129" t="str">
         <f t="shared" si="3"/>
@@ -16643,7 +16652,7 @@
     <row r="130" spans="1:65">
       <c r="A130" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B130" t="str">
         <f t="shared" si="3"/>
@@ -16722,7 +16731,7 @@
     <row r="131" spans="1:65">
       <c r="A131" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B131" t="str">
         <f t="shared" si="3"/>
@@ -16804,7 +16813,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B132" t="str">
         <f t="shared" ref="B132:B168" si="5">TEXT($C132, "HH:mm")</f>
@@ -16883,7 +16892,7 @@
     <row r="133" spans="1:65">
       <c r="A133" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B133" t="str">
         <f t="shared" si="5"/>
@@ -16962,7 +16971,7 @@
     <row r="134" spans="1:65">
       <c r="A134" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B134" t="str">
         <f t="shared" si="5"/>
@@ -17041,7 +17050,7 @@
     <row r="135" spans="1:65">
       <c r="A135" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B135" t="str">
         <f t="shared" si="5"/>
@@ -17120,7 +17129,7 @@
     <row r="136" spans="1:65">
       <c r="A136" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B136" t="str">
         <f t="shared" si="5"/>
@@ -17201,7 +17210,7 @@
     <row r="137" spans="1:65">
       <c r="A137" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B137" t="str">
         <f t="shared" si="5"/>
@@ -17282,7 +17291,7 @@
     <row r="138" spans="1:65">
       <c r="A138" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B138" t="str">
         <f t="shared" si="5"/>
@@ -17361,7 +17370,7 @@
     <row r="139" spans="1:65">
       <c r="A139" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B139" t="str">
         <f t="shared" si="5"/>
@@ -17440,7 +17449,7 @@
     <row r="140" spans="1:65">
       <c r="A140" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B140" t="str">
         <f t="shared" si="5"/>
@@ -17519,7 +17528,7 @@
     <row r="141" spans="1:65">
       <c r="A141" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B141" t="str">
         <f t="shared" si="5"/>
@@ -17598,7 +17607,7 @@
     <row r="142" spans="1:65">
       <c r="A142" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B142" t="str">
         <f t="shared" si="5"/>
@@ -17677,7 +17686,7 @@
     <row r="143" spans="1:65">
       <c r="A143" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B143" t="str">
         <f t="shared" si="5"/>
@@ -17756,7 +17765,7 @@
     <row r="144" spans="1:65">
       <c r="A144" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B144" t="str">
         <f t="shared" si="5"/>
@@ -17835,7 +17844,7 @@
     <row r="145" spans="1:65">
       <c r="A145" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B145" t="str">
         <f t="shared" si="5"/>
@@ -17914,7 +17923,7 @@
     <row r="146" spans="1:65">
       <c r="A146" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B146" t="str">
         <f t="shared" si="5"/>
@@ -17993,7 +18002,7 @@
     <row r="147" spans="1:65">
       <c r="A147" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B147" t="str">
         <f t="shared" si="5"/>
@@ -18072,7 +18081,7 @@
     <row r="148" spans="1:65">
       <c r="A148" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B148" t="str">
         <f t="shared" si="5"/>
@@ -18153,7 +18162,7 @@
     <row r="149" spans="1:65">
       <c r="A149" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B149" t="str">
         <f t="shared" si="5"/>
@@ -18232,7 +18241,7 @@
     <row r="150" spans="1:65">
       <c r="A150" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B150" t="str">
         <f t="shared" si="5"/>
@@ -18311,7 +18320,7 @@
     <row r="151" spans="1:65">
       <c r="A151" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B151" t="str">
         <f t="shared" si="5"/>
@@ -18390,7 +18399,7 @@
     <row r="152" spans="1:65">
       <c r="A152" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B152" t="str">
         <f t="shared" si="5"/>
@@ -18469,7 +18478,7 @@
     <row r="153" spans="1:65">
       <c r="A153" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B153" t="str">
         <f t="shared" si="5"/>
@@ -18548,7 +18557,7 @@
     <row r="154" spans="1:65">
       <c r="A154" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B154" t="str">
         <f t="shared" si="5"/>
@@ -18627,7 +18636,7 @@
     <row r="155" spans="1:65">
       <c r="A155" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B155" t="str">
         <f t="shared" si="5"/>
@@ -18706,7 +18715,7 @@
     <row r="156" spans="1:65">
       <c r="A156" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B156" t="str">
         <f t="shared" si="5"/>
@@ -18785,7 +18794,7 @@
     <row r="157" spans="1:65">
       <c r="A157" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B157" t="str">
         <f t="shared" si="5"/>
@@ -18864,7 +18873,7 @@
     <row r="158" spans="1:65">
       <c r="A158" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B158" t="str">
         <f t="shared" si="5"/>
@@ -18943,7 +18952,7 @@
     <row r="159" spans="1:65">
       <c r="A159" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B159" t="str">
         <f t="shared" si="5"/>
@@ -19022,7 +19031,7 @@
     <row r="160" spans="1:65">
       <c r="A160" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B160" t="str">
         <f t="shared" si="5"/>
@@ -19101,7 +19110,7 @@
     <row r="161" spans="1:65">
       <c r="A161" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B161" t="str">
         <f t="shared" si="5"/>
@@ -19180,7 +19189,7 @@
     <row r="162" spans="1:65">
       <c r="A162" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B162" t="str">
         <f t="shared" si="5"/>
@@ -19259,7 +19268,7 @@
     <row r="163" spans="1:65">
       <c r="A163" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B163" t="str">
         <f t="shared" si="5"/>
@@ -19338,7 +19347,7 @@
     <row r="164" spans="1:65">
       <c r="A164" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B164" t="str">
         <f t="shared" si="5"/>
@@ -19417,7 +19426,7 @@
     <row r="165" spans="1:65">
       <c r="A165" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B165" t="str">
         <f t="shared" si="5"/>
@@ -19496,7 +19505,7 @@
     <row r="166" spans="1:65">
       <c r="A166" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B166" t="str">
         <f t="shared" si="5"/>
@@ -19577,7 +19586,7 @@
     <row r="167" spans="1:65">
       <c r="A167" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B167" t="str">
         <f t="shared" si="5"/>
@@ -19656,7 +19665,7 @@
     <row r="168" spans="1:65">
       <c r="A168" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B168" t="str">
         <f t="shared" si="5"/>
@@ -19738,7 +19747,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B169" t="str">
         <f>TEXT($C169, "HH:mm")</f>
@@ -19820,7 +19829,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B170" t="str">
         <f t="shared" ref="B170:B233" si="7">TEXT($C170, "HH:mm")</f>
@@ -19899,7 +19908,7 @@
     <row r="171" spans="1:65">
       <c r="A171" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B171" t="str">
         <f t="shared" si="7"/>
@@ -19978,7 +19987,7 @@
     <row r="172" spans="1:65">
       <c r="A172" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B172" t="str">
         <f t="shared" si="7"/>
@@ -20059,7 +20068,7 @@
     <row r="173" spans="1:65">
       <c r="A173" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B173" t="str">
         <f t="shared" si="7"/>
@@ -20138,7 +20147,7 @@
     <row r="174" spans="1:65">
       <c r="A174" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B174" t="str">
         <f t="shared" si="7"/>
@@ -20217,7 +20226,7 @@
     <row r="175" spans="1:65">
       <c r="A175" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B175" t="str">
         <f t="shared" si="7"/>
@@ -20296,7 +20305,7 @@
     <row r="176" spans="1:65">
       <c r="A176" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B176" t="str">
         <f t="shared" si="7"/>
@@ -20375,7 +20384,7 @@
     <row r="177" spans="1:65">
       <c r="A177" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B177" t="str">
         <f t="shared" si="7"/>
@@ -20454,7 +20463,7 @@
     <row r="178" spans="1:65">
       <c r="A178" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B178" t="str">
         <f t="shared" si="7"/>
@@ -20535,7 +20544,7 @@
     <row r="179" spans="1:65">
       <c r="A179" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B179" t="str">
         <f t="shared" si="7"/>
@@ -20614,7 +20623,7 @@
     <row r="180" spans="1:65">
       <c r="A180" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B180" t="str">
         <f t="shared" si="7"/>
@@ -20693,7 +20702,7 @@
     <row r="181" spans="1:65">
       <c r="A181" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B181" t="str">
         <f t="shared" si="7"/>
@@ -20774,7 +20783,7 @@
     <row r="182" spans="1:65">
       <c r="A182" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B182" t="str">
         <f t="shared" si="7"/>
@@ -20855,7 +20864,7 @@
     <row r="183" spans="1:65">
       <c r="A183" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B183" t="str">
         <f t="shared" si="7"/>
@@ -20936,7 +20945,7 @@
     <row r="184" spans="1:65">
       <c r="A184" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B184" t="str">
         <f t="shared" si="7"/>
@@ -21019,7 +21028,7 @@
     <row r="185" spans="1:65">
       <c r="A185" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B185" t="str">
         <f t="shared" si="7"/>
@@ -21100,7 +21109,7 @@
     <row r="186" spans="1:65">
       <c r="A186" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B186" t="str">
         <f t="shared" si="7"/>
@@ -21181,7 +21190,7 @@
     <row r="187" spans="1:65">
       <c r="A187" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B187" t="str">
         <f t="shared" si="7"/>
@@ -21262,7 +21271,7 @@
     <row r="188" spans="1:65">
       <c r="A188" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B188" t="str">
         <f t="shared" si="7"/>
@@ -21343,7 +21352,7 @@
     <row r="189" spans="1:65">
       <c r="A189" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B189" t="str">
         <f t="shared" si="7"/>
@@ -21424,7 +21433,7 @@
     <row r="190" spans="1:65">
       <c r="A190" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B190" t="str">
         <f t="shared" si="7"/>
@@ -21507,7 +21516,7 @@
     <row r="191" spans="1:65">
       <c r="A191" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B191" t="str">
         <f t="shared" si="7"/>
@@ -21590,7 +21599,7 @@
     <row r="192" spans="1:65">
       <c r="A192" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B192" t="str">
         <f t="shared" si="7"/>
@@ -21673,7 +21682,7 @@
     <row r="193" spans="1:65">
       <c r="A193" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B193" t="str">
         <f t="shared" si="7"/>
@@ -21756,7 +21765,7 @@
     <row r="194" spans="1:65">
       <c r="A194" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B194" t="str">
         <f t="shared" si="7"/>
@@ -21837,7 +21846,7 @@
     <row r="195" spans="1:65">
       <c r="A195" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B195" t="str">
         <f t="shared" si="7"/>
@@ -21918,7 +21927,7 @@
     <row r="196" spans="1:65">
       <c r="A196" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B196" t="str">
         <f t="shared" si="7"/>
@@ -22001,7 +22010,7 @@
     <row r="197" spans="1:65">
       <c r="A197" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B197" t="str">
         <f t="shared" si="7"/>
@@ -22080,7 +22089,7 @@
     <row r="198" spans="1:65">
       <c r="A198" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B198" t="str">
         <f t="shared" si="7"/>
@@ -22159,7 +22168,7 @@
     <row r="199" spans="1:65">
       <c r="A199" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B199" t="str">
         <f t="shared" si="7"/>
@@ -22238,7 +22247,7 @@
     <row r="200" spans="1:65">
       <c r="A200" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B200" t="str">
         <f t="shared" si="7"/>
@@ -22317,7 +22326,7 @@
     <row r="201" spans="1:65">
       <c r="A201" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B201" t="str">
         <f t="shared" si="7"/>
@@ -22396,7 +22405,7 @@
     <row r="202" spans="1:65">
       <c r="A202" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B202" t="str">
         <f t="shared" si="7"/>
@@ -22477,7 +22486,7 @@
     <row r="203" spans="1:65">
       <c r="A203" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B203" t="str">
         <f t="shared" si="7"/>
@@ -22556,7 +22565,7 @@
     <row r="204" spans="1:65">
       <c r="A204" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B204" t="str">
         <f t="shared" si="7"/>
@@ -22635,7 +22644,7 @@
     <row r="205" spans="1:65">
       <c r="A205" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B205" t="str">
         <f t="shared" si="7"/>
@@ -22714,7 +22723,7 @@
     <row r="206" spans="1:65">
       <c r="A206" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B206" t="str">
         <f t="shared" si="7"/>
@@ -22793,7 +22802,7 @@
     <row r="207" spans="1:65">
       <c r="A207" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B207" t="str">
         <f t="shared" si="7"/>
@@ -22872,7 +22881,7 @@
     <row r="208" spans="1:65">
       <c r="A208" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B208" t="str">
         <f t="shared" si="7"/>
@@ -22953,7 +22962,7 @@
     <row r="209" spans="1:65">
       <c r="A209" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B209" t="str">
         <f t="shared" si="7"/>
@@ -23032,7 +23041,7 @@
     <row r="210" spans="1:65">
       <c r="A210" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B210" t="str">
         <f t="shared" si="7"/>
@@ -23111,7 +23120,7 @@
     <row r="211" spans="1:65">
       <c r="A211" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B211" t="str">
         <f t="shared" si="7"/>
@@ -23192,7 +23201,7 @@
     <row r="212" spans="1:65">
       <c r="A212" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B212" t="str">
         <f t="shared" si="7"/>
@@ -23271,7 +23280,7 @@
     <row r="213" spans="1:65">
       <c r="A213" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B213" t="str">
         <f t="shared" si="7"/>
@@ -23350,7 +23359,7 @@
     <row r="214" spans="1:65">
       <c r="A214" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B214" t="str">
         <f t="shared" si="7"/>
@@ -23429,7 +23438,7 @@
     <row r="215" spans="1:65">
       <c r="A215" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B215" t="str">
         <f t="shared" si="7"/>
@@ -23508,7 +23517,7 @@
     <row r="216" spans="1:65">
       <c r="A216" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B216" t="str">
         <f t="shared" si="7"/>
@@ -23587,7 +23596,7 @@
     <row r="217" spans="1:65">
       <c r="A217" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B217" t="str">
         <f t="shared" si="7"/>
@@ -23666,7 +23675,7 @@
     <row r="218" spans="1:65">
       <c r="A218" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B218" t="str">
         <f t="shared" si="7"/>
@@ -23745,7 +23754,7 @@
     <row r="219" spans="1:65">
       <c r="A219" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B219" t="str">
         <f t="shared" si="7"/>
@@ -23824,7 +23833,7 @@
     <row r="220" spans="1:65">
       <c r="A220" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B220" t="str">
         <f t="shared" si="7"/>
@@ -23905,7 +23914,7 @@
     <row r="221" spans="1:65">
       <c r="A221" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B221" t="str">
         <f t="shared" si="7"/>
@@ -23984,7 +23993,7 @@
     <row r="222" spans="1:65">
       <c r="A222" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B222" t="str">
         <f t="shared" si="7"/>
@@ -24063,7 +24072,7 @@
     <row r="223" spans="1:65">
       <c r="A223" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B223" t="str">
         <f t="shared" si="7"/>
@@ -24142,7 +24151,7 @@
     <row r="224" spans="1:65">
       <c r="A224" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B224" t="str">
         <f t="shared" si="7"/>
@@ -24221,7 +24230,7 @@
     <row r="225" spans="1:65">
       <c r="A225" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B225" t="str">
         <f t="shared" si="7"/>
@@ -24300,7 +24309,7 @@
     <row r="226" spans="1:65">
       <c r="A226" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B226" t="str">
         <f t="shared" si="7"/>
@@ -24379,7 +24388,7 @@
     <row r="227" spans="1:65">
       <c r="A227" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B227" t="str">
         <f t="shared" si="7"/>
@@ -24458,7 +24467,7 @@
     <row r="228" spans="1:65">
       <c r="A228" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B228" t="str">
         <f t="shared" si="7"/>
@@ -24537,7 +24546,7 @@
     <row r="229" spans="1:65">
       <c r="A229" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B229" t="str">
         <f t="shared" si="7"/>
@@ -24616,7 +24625,7 @@
     <row r="230" spans="1:65">
       <c r="A230" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B230" t="str">
         <f t="shared" si="7"/>
@@ -24695,7 +24704,7 @@
     <row r="231" spans="1:65">
       <c r="A231" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B231" t="str">
         <f t="shared" si="7"/>
@@ -24774,7 +24783,7 @@
     <row r="232" spans="1:65">
       <c r="A232" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B232" t="str">
         <f t="shared" si="7"/>
@@ -24853,7 +24862,7 @@
     <row r="233" spans="1:65">
       <c r="A233" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B233" t="str">
         <f t="shared" si="7"/>
@@ -24935,7 +24944,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B234" t="str">
         <f t="shared" ref="B234:B291" si="9">TEXT($C234, "HH:mm")</f>
@@ -25014,7 +25023,7 @@
     <row r="235" spans="1:65">
       <c r="A235" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B235" t="str">
         <f t="shared" si="9"/>
@@ -25093,7 +25102,7 @@
     <row r="236" spans="1:65">
       <c r="A236" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B236" t="str">
         <f t="shared" si="9"/>
@@ -25172,7 +25181,7 @@
     <row r="237" spans="1:65">
       <c r="A237" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B237" t="str">
         <f t="shared" si="9"/>
@@ -25251,7 +25260,7 @@
     <row r="238" spans="1:65">
       <c r="A238" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B238" t="str">
         <f t="shared" si="9"/>
@@ -25330,7 +25339,7 @@
     <row r="239" spans="1:65">
       <c r="A239" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B239" t="str">
         <f t="shared" si="9"/>
@@ -25409,7 +25418,7 @@
     <row r="240" spans="1:65">
       <c r="A240" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B240" t="str">
         <f t="shared" si="9"/>
@@ -25488,7 +25497,7 @@
     <row r="241" spans="1:65">
       <c r="A241" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B241" t="str">
         <f t="shared" si="9"/>
@@ -25567,7 +25576,7 @@
     <row r="242" spans="1:65">
       <c r="A242" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B242" t="str">
         <f t="shared" si="9"/>
@@ -25646,7 +25655,7 @@
     <row r="243" spans="1:65">
       <c r="A243" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B243" t="str">
         <f t="shared" si="9"/>
@@ -25725,7 +25734,7 @@
     <row r="244" spans="1:65">
       <c r="A244" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B244" t="str">
         <f t="shared" si="9"/>
@@ -25804,7 +25813,7 @@
     <row r="245" spans="1:65">
       <c r="A245" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B245" t="str">
         <f t="shared" si="9"/>
@@ -25883,7 +25892,7 @@
     <row r="246" spans="1:65">
       <c r="A246" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B246" t="str">
         <f t="shared" si="9"/>
@@ -25962,7 +25971,7 @@
     <row r="247" spans="1:65">
       <c r="A247" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B247" t="str">
         <f t="shared" si="9"/>
@@ -26041,7 +26050,7 @@
     <row r="248" spans="1:65">
       <c r="A248" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B248" t="str">
         <f t="shared" si="9"/>
@@ -26120,7 +26129,7 @@
     <row r="249" spans="1:65">
       <c r="A249" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B249" t="str">
         <f t="shared" si="9"/>
@@ -26199,7 +26208,7 @@
     <row r="250" spans="1:65">
       <c r="A250" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B250" t="str">
         <f t="shared" si="9"/>
@@ -26278,7 +26287,7 @@
     <row r="251" spans="1:65">
       <c r="A251" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B251" t="str">
         <f t="shared" si="9"/>
@@ -26357,7 +26366,7 @@
     <row r="252" spans="1:65">
       <c r="A252" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B252" t="str">
         <f t="shared" si="9"/>
@@ -26436,7 +26445,7 @@
     <row r="253" spans="1:65">
       <c r="A253" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B253" t="str">
         <f t="shared" si="9"/>
@@ -26515,7 +26524,7 @@
     <row r="254" spans="1:65">
       <c r="A254" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B254" t="str">
         <f t="shared" si="9"/>
@@ -26594,7 +26603,7 @@
     <row r="255" spans="1:65">
       <c r="A255" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B255" t="str">
         <f t="shared" si="9"/>
@@ -26673,7 +26682,7 @@
     <row r="256" spans="1:65">
       <c r="A256" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B256" t="str">
         <f t="shared" si="9"/>
@@ -26752,7 +26761,7 @@
     <row r="257" spans="1:65">
       <c r="A257" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B257" t="str">
         <f t="shared" si="9"/>
@@ -26831,7 +26840,7 @@
     <row r="258" spans="1:65">
       <c r="A258" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B258" t="str">
         <f t="shared" si="9"/>
@@ -26910,7 +26919,7 @@
     <row r="259" spans="1:65">
       <c r="A259" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B259" t="str">
         <f t="shared" si="9"/>
@@ -26989,7 +26998,7 @@
     <row r="260" spans="1:65">
       <c r="A260" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B260" t="str">
         <f t="shared" si="9"/>
@@ -27068,7 +27077,7 @@
     <row r="261" spans="1:65">
       <c r="A261" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B261" t="str">
         <f t="shared" si="9"/>
@@ -27147,7 +27156,7 @@
     <row r="262" spans="1:65">
       <c r="A262" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B262" t="str">
         <f t="shared" si="9"/>
@@ -27226,7 +27235,7 @@
     <row r="263" spans="1:65">
       <c r="A263" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B263" t="str">
         <f t="shared" si="9"/>
@@ -27305,7 +27314,7 @@
     <row r="264" spans="1:65">
       <c r="A264" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B264" t="str">
         <f t="shared" si="9"/>
@@ -27384,7 +27393,7 @@
     <row r="265" spans="1:65">
       <c r="A265" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B265" t="str">
         <f t="shared" si="9"/>
@@ -27463,7 +27472,7 @@
     <row r="266" spans="1:65">
       <c r="A266" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B266" t="str">
         <f t="shared" si="9"/>
@@ -27542,7 +27551,7 @@
     <row r="267" spans="1:65">
       <c r="A267" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B267" t="str">
         <f t="shared" si="9"/>
@@ -27621,7 +27630,7 @@
     <row r="268" spans="1:65">
       <c r="A268" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B268" t="str">
         <f t="shared" si="9"/>
@@ -27700,7 +27709,7 @@
     <row r="269" spans="1:65">
       <c r="A269" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B269" t="str">
         <f t="shared" si="9"/>
@@ -27779,7 +27788,7 @@
     <row r="270" spans="1:65">
       <c r="A270" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B270" t="str">
         <f t="shared" si="9"/>
@@ -27858,7 +27867,7 @@
     <row r="271" spans="1:65">
       <c r="A271" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B271" t="str">
         <f t="shared" si="9"/>
@@ -27937,7 +27946,7 @@
     <row r="272" spans="1:65">
       <c r="A272" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B272" t="str">
         <f t="shared" si="9"/>
@@ -28016,7 +28025,7 @@
     <row r="273" spans="1:65">
       <c r="A273" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B273" t="str">
         <f t="shared" si="9"/>
@@ -28095,7 +28104,7 @@
     <row r="274" spans="1:65">
       <c r="A274" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B274" t="str">
         <f t="shared" si="9"/>
@@ -28174,7 +28183,7 @@
     <row r="275" spans="1:65">
       <c r="A275" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B275" t="str">
         <f t="shared" si="9"/>
@@ -28253,7 +28262,7 @@
     <row r="276" spans="1:65">
       <c r="A276" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B276" t="str">
         <f t="shared" si="9"/>
@@ -28332,7 +28341,7 @@
     <row r="277" spans="1:65">
       <c r="A277" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B277" t="str">
         <f t="shared" si="9"/>
@@ -28411,7 +28420,7 @@
     <row r="278" spans="1:65">
       <c r="A278" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B278" t="str">
         <f t="shared" si="9"/>
@@ -28490,7 +28499,7 @@
     <row r="279" spans="1:65">
       <c r="A279" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B279" t="str">
         <f t="shared" si="9"/>
@@ -28569,7 +28578,7 @@
     <row r="280" spans="1:65">
       <c r="A280" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B280" t="str">
         <f t="shared" si="9"/>
@@ -28648,7 +28657,7 @@
     <row r="281" spans="1:65">
       <c r="A281" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B281" t="str">
         <f t="shared" si="9"/>
@@ -28727,7 +28736,7 @@
     <row r="282" spans="1:65">
       <c r="A282" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B282" t="str">
         <f t="shared" si="9"/>
@@ -28806,7 +28815,7 @@
     <row r="283" spans="1:65">
       <c r="A283" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B283" t="str">
         <f t="shared" si="9"/>
@@ -28885,7 +28894,7 @@
     <row r="284" spans="1:65">
       <c r="A284" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B284" t="str">
         <f t="shared" si="9"/>
@@ -28964,7 +28973,7 @@
     <row r="285" spans="1:65">
       <c r="A285" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B285" t="str">
         <f t="shared" si="9"/>
@@ -29043,7 +29052,7 @@
     <row r="286" spans="1:65">
       <c r="A286" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B286" t="str">
         <f t="shared" si="9"/>
@@ -29122,7 +29131,7 @@
     <row r="287" spans="1:65">
       <c r="A287" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B287" t="str">
         <f t="shared" si="9"/>
@@ -29201,7 +29210,7 @@
     <row r="288" spans="1:65">
       <c r="A288" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B288" t="str">
         <f t="shared" si="9"/>
@@ -29280,7 +29289,7 @@
     <row r="289" spans="1:65">
       <c r="A289" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B289" t="str">
         <f t="shared" si="9"/>
@@ -29359,7 +29368,7 @@
     <row r="290" spans="1:65">
       <c r="A290" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B290" t="str">
         <f t="shared" si="9"/>
@@ -29438,7 +29447,7 @@
     <row r="291" spans="1:65">
       <c r="A291" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:35</v>
+        <v>01:45</v>
       </c>
       <c r="B291" t="str">
         <f t="shared" si="9"/>

--- a/Vite-Vercel開発.xlsx
+++ b/Vite-Vercel開発.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2c67ec30e06f060f/work/GitHub/work-time-tracker/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{1928CA11-C4AD-40E9-B1C5-143667E830EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5559AAB8-1CD9-4D76-BCA2-D303AE42D0F6}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{1928CA11-C4AD-40E9-B1C5-143667E830EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0E3CF06-DBF0-490C-A784-0DAEBE68D2D7}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1545" uniqueCount="922">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1546" uniqueCount="923">
   <si>
     <t>npm install -g vercel</t>
     <phoneticPr fontId="1"/>
@@ -5366,6 +5366,10 @@
   </si>
   <si>
     <t>Found 63 errors in 15 files.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Found 54 errors in 14 files.</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -6138,7 +6142,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{083174DA-A42C-4F9C-978E-61AEAAD9DDFF}">
-  <dimension ref="B2:D27"/>
+  <dimension ref="B2:D28"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
@@ -6281,6 +6285,11 @@
     <row r="27" spans="3:3">
       <c r="C27" t="s">
         <v>921</v>
+      </c>
+    </row>
+    <row r="28" spans="3:3">
+      <c r="C28" t="s">
+        <v>922</v>
       </c>
     </row>
   </sheetData>
@@ -6447,7 +6456,7 @@
       MOD(NOW(),1),
       TIME(0,5,0)
     ),"HH:mm")</f>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B2" s="19"/>
       <c r="D2" s="1">
@@ -6458,7 +6467,7 @@
     <row r="3" spans="1:65">
       <c r="A3" s="19" t="str">
         <f ca="1">TEXT(NOW(),"HH:mm")</f>
-        <v>01:46</v>
+        <v>01:52</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="17" t="s">
@@ -6657,7 +6666,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B4" t="str">
         <f t="shared" ref="B4:B67" si="1">TEXT($C4, "HH:mm")</f>
@@ -6736,7 +6745,7 @@
     <row r="5" spans="1:65">
       <c r="A5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B5" t="str">
         <f t="shared" si="1"/>
@@ -6815,7 +6824,7 @@
     <row r="6" spans="1:65">
       <c r="A6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B6" t="str">
         <f t="shared" si="1"/>
@@ -6894,7 +6903,7 @@
     <row r="7" spans="1:65">
       <c r="A7" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B7" t="str">
         <f t="shared" si="1"/>
@@ -6973,7 +6982,7 @@
     <row r="8" spans="1:65">
       <c r="A8" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B8" t="str">
         <f t="shared" si="1"/>
@@ -7052,7 +7061,7 @@
     <row r="9" spans="1:65">
       <c r="A9" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B9" t="str">
         <f t="shared" si="1"/>
@@ -7131,7 +7140,7 @@
     <row r="10" spans="1:65">
       <c r="A10" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B10" t="str">
         <f t="shared" si="1"/>
@@ -7210,7 +7219,7 @@
     <row r="11" spans="1:65">
       <c r="A11" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B11" t="str">
         <f t="shared" si="1"/>
@@ -7289,7 +7298,7 @@
     <row r="12" spans="1:65">
       <c r="A12" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B12" t="str">
         <f t="shared" si="1"/>
@@ -7368,7 +7377,7 @@
     <row r="13" spans="1:65">
       <c r="A13" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B13" t="str">
         <f t="shared" si="1"/>
@@ -7447,7 +7456,7 @@
     <row r="14" spans="1:65">
       <c r="A14" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B14" t="str">
         <f t="shared" si="1"/>
@@ -7526,7 +7535,7 @@
     <row r="15" spans="1:65">
       <c r="A15" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B15" t="str">
         <f t="shared" si="1"/>
@@ -7605,7 +7614,7 @@
     <row r="16" spans="1:65">
       <c r="A16" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B16" t="str">
         <f t="shared" si="1"/>
@@ -7684,7 +7693,7 @@
     <row r="17" spans="1:65">
       <c r="A17" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B17" t="str">
         <f t="shared" si="1"/>
@@ -7763,7 +7772,7 @@
     <row r="18" spans="1:65">
       <c r="A18" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B18" t="str">
         <f t="shared" si="1"/>
@@ -7842,7 +7851,7 @@
     <row r="19" spans="1:65">
       <c r="A19" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B19" t="str">
         <f t="shared" si="1"/>
@@ -7921,7 +7930,7 @@
     <row r="20" spans="1:65">
       <c r="A20" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B20" t="str">
         <f t="shared" si="1"/>
@@ -8000,7 +8009,7 @@
     <row r="21" spans="1:65">
       <c r="A21" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B21" t="str">
         <f t="shared" si="1"/>
@@ -8079,7 +8088,7 @@
     <row r="22" spans="1:65">
       <c r="A22" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B22" t="str">
         <f t="shared" si="1"/>
@@ -8158,7 +8167,7 @@
     <row r="23" spans="1:65">
       <c r="A23" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B23" t="str">
         <f t="shared" si="1"/>
@@ -8237,7 +8246,7 @@
     <row r="24" spans="1:65">
       <c r="A24" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B24" t="str">
         <f t="shared" si="1"/>
@@ -8316,7 +8325,7 @@
     <row r="25" spans="1:65">
       <c r="A25" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B25" t="str">
         <f t="shared" si="1"/>
@@ -8395,7 +8404,7 @@
     <row r="26" spans="1:65">
       <c r="A26" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B26" t="str">
         <f t="shared" si="1"/>
@@ -8474,7 +8483,7 @@
     <row r="27" spans="1:65">
       <c r="A27" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B27" t="str">
         <f t="shared" si="1"/>
@@ -8553,7 +8562,7 @@
     <row r="28" spans="1:65">
       <c r="A28" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B28" t="str">
         <f t="shared" si="1"/>
@@ -8634,7 +8643,7 @@
     <row r="29" spans="1:65">
       <c r="A29" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B29" t="str">
         <f t="shared" si="1"/>
@@ -8715,7 +8724,7 @@
     <row r="30" spans="1:65">
       <c r="A30" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B30" t="str">
         <f t="shared" si="1"/>
@@ -8796,7 +8805,7 @@
     <row r="31" spans="1:65">
       <c r="A31" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B31" t="str">
         <f t="shared" si="1"/>
@@ -8875,7 +8884,7 @@
     <row r="32" spans="1:65">
       <c r="A32" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B32" t="str">
         <f t="shared" si="1"/>
@@ -8954,7 +8963,7 @@
     <row r="33" spans="1:65">
       <c r="A33" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B33" t="str">
         <f t="shared" si="1"/>
@@ -9033,7 +9042,7 @@
     <row r="34" spans="1:65">
       <c r="A34" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B34" t="str">
         <f t="shared" si="1"/>
@@ -9114,7 +9123,7 @@
     <row r="35" spans="1:65">
       <c r="A35" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B35" t="str">
         <f t="shared" si="1"/>
@@ -9195,7 +9204,7 @@
     <row r="36" spans="1:65">
       <c r="A36" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B36" t="str">
         <f t="shared" si="1"/>
@@ -9276,7 +9285,7 @@
     <row r="37" spans="1:65">
       <c r="A37" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B37" t="str">
         <f t="shared" si="1"/>
@@ -9355,7 +9364,7 @@
     <row r="38" spans="1:65">
       <c r="A38" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B38" t="str">
         <f t="shared" si="1"/>
@@ -9434,7 +9443,7 @@
     <row r="39" spans="1:65">
       <c r="A39" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B39" t="str">
         <f t="shared" si="1"/>
@@ -9513,7 +9522,7 @@
     <row r="40" spans="1:65">
       <c r="A40" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B40" t="str">
         <f t="shared" si="1"/>
@@ -9592,7 +9601,7 @@
     <row r="41" spans="1:65">
       <c r="A41" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B41" t="str">
         <f t="shared" si="1"/>
@@ -9671,7 +9680,7 @@
     <row r="42" spans="1:65">
       <c r="A42" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B42" t="str">
         <f t="shared" si="1"/>
@@ -9752,7 +9761,7 @@
     <row r="43" spans="1:65">
       <c r="A43" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B43" t="str">
         <f t="shared" si="1"/>
@@ -9833,7 +9842,7 @@
     <row r="44" spans="1:65">
       <c r="A44" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B44" t="str">
         <f t="shared" si="1"/>
@@ -9912,7 +9921,7 @@
     <row r="45" spans="1:65">
       <c r="A45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B45" t="str">
         <f t="shared" si="1"/>
@@ -9991,7 +10000,7 @@
     <row r="46" spans="1:65">
       <c r="A46" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B46" t="str">
         <f t="shared" si="1"/>
@@ -10070,7 +10079,7 @@
     <row r="47" spans="1:65">
       <c r="A47" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B47" t="str">
         <f t="shared" si="1"/>
@@ -10149,7 +10158,7 @@
     <row r="48" spans="1:65">
       <c r="A48" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B48" t="str">
         <f t="shared" si="1"/>
@@ -10228,7 +10237,7 @@
     <row r="49" spans="1:65">
       <c r="A49" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B49" t="str">
         <f t="shared" si="1"/>
@@ -10309,7 +10318,7 @@
     <row r="50" spans="1:65">
       <c r="A50" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B50" t="str">
         <f t="shared" si="1"/>
@@ -10390,7 +10399,7 @@
     <row r="51" spans="1:65">
       <c r="A51" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B51" t="str">
         <f t="shared" si="1"/>
@@ -10469,7 +10478,7 @@
     <row r="52" spans="1:65">
       <c r="A52" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B52" t="str">
         <f t="shared" si="1"/>
@@ -10548,7 +10557,7 @@
     <row r="53" spans="1:65">
       <c r="A53" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B53" t="str">
         <f t="shared" si="1"/>
@@ -10627,7 +10636,7 @@
     <row r="54" spans="1:65">
       <c r="A54" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B54" t="str">
         <f t="shared" si="1"/>
@@ -10706,7 +10715,7 @@
     <row r="55" spans="1:65">
       <c r="A55" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B55" t="str">
         <f t="shared" si="1"/>
@@ -10785,7 +10794,7 @@
     <row r="56" spans="1:65">
       <c r="A56" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B56" t="str">
         <f t="shared" si="1"/>
@@ -10866,7 +10875,7 @@
     <row r="57" spans="1:65">
       <c r="A57" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B57" t="str">
         <f t="shared" si="1"/>
@@ -10945,7 +10954,7 @@
     <row r="58" spans="1:65">
       <c r="A58" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B58" t="str">
         <f t="shared" si="1"/>
@@ -11026,7 +11035,7 @@
     <row r="59" spans="1:65">
       <c r="A59" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B59" t="str">
         <f t="shared" si="1"/>
@@ -11105,7 +11114,7 @@
     <row r="60" spans="1:65">
       <c r="A60" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B60" t="str">
         <f t="shared" si="1"/>
@@ -11184,7 +11193,7 @@
     <row r="61" spans="1:65">
       <c r="A61" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B61" t="str">
         <f t="shared" si="1"/>
@@ -11263,7 +11272,7 @@
     <row r="62" spans="1:65">
       <c r="A62" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B62" t="str">
         <f t="shared" si="1"/>
@@ -11342,7 +11351,7 @@
     <row r="63" spans="1:65">
       <c r="A63" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B63" t="str">
         <f t="shared" si="1"/>
@@ -11421,7 +11430,7 @@
     <row r="64" spans="1:65">
       <c r="A64" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B64" t="str">
         <f t="shared" si="1"/>
@@ -11502,7 +11511,7 @@
     <row r="65" spans="1:65">
       <c r="A65" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B65" t="str">
         <f t="shared" si="1"/>
@@ -11581,7 +11590,7 @@
     <row r="66" spans="1:65">
       <c r="A66" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B66" t="str">
         <f t="shared" si="1"/>
@@ -11660,7 +11669,7 @@
     <row r="67" spans="1:65">
       <c r="A67" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B67" t="str">
         <f t="shared" si="1"/>
@@ -11742,7 +11751,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B68" t="str">
         <f t="shared" ref="B68:B131" si="3">TEXT($C68, "HH:mm")</f>
@@ -11821,7 +11830,7 @@
     <row r="69" spans="1:65">
       <c r="A69" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B69" t="str">
         <f t="shared" si="3"/>
@@ -11900,7 +11909,7 @@
     <row r="70" spans="1:65">
       <c r="A70" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B70" t="str">
         <f t="shared" si="3"/>
@@ -11979,7 +11988,7 @@
     <row r="71" spans="1:65">
       <c r="A71" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B71" t="str">
         <f t="shared" si="3"/>
@@ -12058,7 +12067,7 @@
     <row r="72" spans="1:65">
       <c r="A72" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B72" t="str">
         <f t="shared" si="3"/>
@@ -12137,7 +12146,7 @@
     <row r="73" spans="1:65">
       <c r="A73" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B73" t="str">
         <f t="shared" si="3"/>
@@ -12216,7 +12225,7 @@
     <row r="74" spans="1:65">
       <c r="A74" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B74" t="str">
         <f t="shared" si="3"/>
@@ -12295,7 +12304,7 @@
     <row r="75" spans="1:65">
       <c r="A75" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B75" t="str">
         <f t="shared" si="3"/>
@@ -12374,7 +12383,7 @@
     <row r="76" spans="1:65">
       <c r="A76" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B76" t="str">
         <f t="shared" si="3"/>
@@ -12453,7 +12462,7 @@
     <row r="77" spans="1:65">
       <c r="A77" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B77" t="str">
         <f t="shared" si="3"/>
@@ -12532,7 +12541,7 @@
     <row r="78" spans="1:65">
       <c r="A78" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B78" t="str">
         <f t="shared" si="3"/>
@@ -12611,7 +12620,7 @@
     <row r="79" spans="1:65">
       <c r="A79" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B79" t="str">
         <f t="shared" si="3"/>
@@ -12690,7 +12699,7 @@
     <row r="80" spans="1:65">
       <c r="A80" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B80" t="str">
         <f t="shared" si="3"/>
@@ -12769,7 +12778,7 @@
     <row r="81" spans="1:65">
       <c r="A81" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B81" t="str">
         <f t="shared" si="3"/>
@@ -12848,7 +12857,7 @@
     <row r="82" spans="1:65">
       <c r="A82" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B82" t="str">
         <f t="shared" si="3"/>
@@ -12927,7 +12936,7 @@
     <row r="83" spans="1:65">
       <c r="A83" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B83" t="str">
         <f t="shared" si="3"/>
@@ -13006,7 +13015,7 @@
     <row r="84" spans="1:65">
       <c r="A84" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B84" t="str">
         <f t="shared" si="3"/>
@@ -13085,7 +13094,7 @@
     <row r="85" spans="1:65">
       <c r="A85" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B85" t="str">
         <f t="shared" si="3"/>
@@ -13164,7 +13173,7 @@
     <row r="86" spans="1:65">
       <c r="A86" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B86" t="str">
         <f t="shared" si="3"/>
@@ -13243,7 +13252,7 @@
     <row r="87" spans="1:65">
       <c r="A87" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B87" t="str">
         <f t="shared" si="3"/>
@@ -13322,7 +13331,7 @@
     <row r="88" spans="1:65">
       <c r="A88" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B88" t="str">
         <f t="shared" si="3"/>
@@ -13401,7 +13410,7 @@
     <row r="89" spans="1:65">
       <c r="A89" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B89" t="str">
         <f t="shared" si="3"/>
@@ -13480,7 +13489,7 @@
     <row r="90" spans="1:65">
       <c r="A90" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B90" t="str">
         <f t="shared" si="3"/>
@@ -13559,7 +13568,7 @@
     <row r="91" spans="1:65">
       <c r="A91" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B91" t="str">
         <f t="shared" si="3"/>
@@ -13638,7 +13647,7 @@
     <row r="92" spans="1:65">
       <c r="A92" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B92" t="str">
         <f t="shared" si="3"/>
@@ -13717,7 +13726,7 @@
     <row r="93" spans="1:65">
       <c r="A93" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B93" t="str">
         <f t="shared" si="3"/>
@@ -13796,7 +13805,7 @@
     <row r="94" spans="1:65">
       <c r="A94" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B94" t="str">
         <f t="shared" si="3"/>
@@ -13875,7 +13884,7 @@
     <row r="95" spans="1:65">
       <c r="A95" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B95" t="str">
         <f t="shared" si="3"/>
@@ -13954,7 +13963,7 @@
     <row r="96" spans="1:65">
       <c r="A96" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B96" t="str">
         <f t="shared" si="3"/>
@@ -14033,7 +14042,7 @@
     <row r="97" spans="1:65">
       <c r="A97" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B97" t="str">
         <f t="shared" si="3"/>
@@ -14112,7 +14121,7 @@
     <row r="98" spans="1:65">
       <c r="A98" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B98" t="str">
         <f t="shared" si="3"/>
@@ -14191,7 +14200,7 @@
     <row r="99" spans="1:65">
       <c r="A99" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B99" t="str">
         <f t="shared" si="3"/>
@@ -14270,7 +14279,7 @@
     <row r="100" spans="1:65">
       <c r="A100" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B100" t="str">
         <f t="shared" si="3"/>
@@ -14351,7 +14360,7 @@
     <row r="101" spans="1:65">
       <c r="A101" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B101" t="str">
         <f t="shared" si="3"/>
@@ -14430,7 +14439,7 @@
     <row r="102" spans="1:65">
       <c r="A102" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B102" t="str">
         <f t="shared" si="3"/>
@@ -14509,7 +14518,7 @@
     <row r="103" spans="1:65">
       <c r="A103" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B103" t="str">
         <f t="shared" si="3"/>
@@ -14588,7 +14597,7 @@
     <row r="104" spans="1:65">
       <c r="A104" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B104" t="str">
         <f t="shared" si="3"/>
@@ -14667,7 +14676,7 @@
     <row r="105" spans="1:65">
       <c r="A105" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B105" t="str">
         <f t="shared" si="3"/>
@@ -14746,7 +14755,7 @@
     <row r="106" spans="1:65">
       <c r="A106" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B106" t="str">
         <f t="shared" si="3"/>
@@ -14827,7 +14836,7 @@
     <row r="107" spans="1:65">
       <c r="A107" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B107" t="str">
         <f t="shared" si="3"/>
@@ -14908,7 +14917,7 @@
     <row r="108" spans="1:65">
       <c r="A108" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B108" t="str">
         <f t="shared" si="3"/>
@@ -14987,7 +14996,7 @@
     <row r="109" spans="1:65">
       <c r="A109" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B109" t="str">
         <f t="shared" si="3"/>
@@ -15066,7 +15075,7 @@
     <row r="110" spans="1:65">
       <c r="A110" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B110" t="str">
         <f t="shared" si="3"/>
@@ -15145,7 +15154,7 @@
     <row r="111" spans="1:65">
       <c r="A111" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B111" t="str">
         <f t="shared" si="3"/>
@@ -15224,7 +15233,7 @@
     <row r="112" spans="1:65">
       <c r="A112" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B112" t="str">
         <f t="shared" si="3"/>
@@ -15305,7 +15314,7 @@
     <row r="113" spans="1:65">
       <c r="A113" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B113" t="str">
         <f t="shared" si="3"/>
@@ -15384,7 +15393,7 @@
     <row r="114" spans="1:65">
       <c r="A114" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B114" t="str">
         <f t="shared" si="3"/>
@@ -15463,7 +15472,7 @@
     <row r="115" spans="1:65">
       <c r="A115" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B115" t="str">
         <f t="shared" si="3"/>
@@ -15542,7 +15551,7 @@
     <row r="116" spans="1:65">
       <c r="A116" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B116" t="str">
         <f t="shared" si="3"/>
@@ -15621,7 +15630,7 @@
     <row r="117" spans="1:65">
       <c r="A117" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B117" t="str">
         <f t="shared" si="3"/>
@@ -15700,7 +15709,7 @@
     <row r="118" spans="1:65">
       <c r="A118" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B118" t="str">
         <f t="shared" si="3"/>
@@ -15779,7 +15788,7 @@
     <row r="119" spans="1:65">
       <c r="A119" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B119" t="str">
         <f t="shared" si="3"/>
@@ -15858,7 +15867,7 @@
     <row r="120" spans="1:65">
       <c r="A120" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B120" t="str">
         <f t="shared" si="3"/>
@@ -15937,7 +15946,7 @@
     <row r="121" spans="1:65">
       <c r="A121" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B121" t="str">
         <f t="shared" si="3"/>
@@ -16016,7 +16025,7 @@
     <row r="122" spans="1:65">
       <c r="A122" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B122" t="str">
         <f t="shared" si="3"/>
@@ -16095,7 +16104,7 @@
     <row r="123" spans="1:65">
       <c r="A123" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B123" t="str">
         <f t="shared" si="3"/>
@@ -16174,7 +16183,7 @@
     <row r="124" spans="1:65">
       <c r="A124" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B124" t="str">
         <f t="shared" si="3"/>
@@ -16255,7 +16264,7 @@
     <row r="125" spans="1:65">
       <c r="A125" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B125" t="str">
         <f t="shared" si="3"/>
@@ -16336,7 +16345,7 @@
     <row r="126" spans="1:65">
       <c r="A126" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B126" t="str">
         <f t="shared" si="3"/>
@@ -16415,7 +16424,7 @@
     <row r="127" spans="1:65">
       <c r="A127" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B127" t="str">
         <f t="shared" si="3"/>
@@ -16494,7 +16503,7 @@
     <row r="128" spans="1:65">
       <c r="A128" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B128" t="str">
         <f t="shared" si="3"/>
@@ -16573,7 +16582,7 @@
     <row r="129" spans="1:65">
       <c r="A129" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B129" t="str">
         <f t="shared" si="3"/>
@@ -16652,7 +16661,7 @@
     <row r="130" spans="1:65">
       <c r="A130" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B130" t="str">
         <f t="shared" si="3"/>
@@ -16731,7 +16740,7 @@
     <row r="131" spans="1:65">
       <c r="A131" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B131" t="str">
         <f t="shared" si="3"/>
@@ -16813,7 +16822,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B132" t="str">
         <f t="shared" ref="B132:B168" si="5">TEXT($C132, "HH:mm")</f>
@@ -16892,7 +16901,7 @@
     <row r="133" spans="1:65">
       <c r="A133" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B133" t="str">
         <f t="shared" si="5"/>
@@ -16971,7 +16980,7 @@
     <row r="134" spans="1:65">
       <c r="A134" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B134" t="str">
         <f t="shared" si="5"/>
@@ -17050,7 +17059,7 @@
     <row r="135" spans="1:65">
       <c r="A135" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B135" t="str">
         <f t="shared" si="5"/>
@@ -17129,7 +17138,7 @@
     <row r="136" spans="1:65">
       <c r="A136" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B136" t="str">
         <f t="shared" si="5"/>
@@ -17210,7 +17219,7 @@
     <row r="137" spans="1:65">
       <c r="A137" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B137" t="str">
         <f t="shared" si="5"/>
@@ -17291,7 +17300,7 @@
     <row r="138" spans="1:65">
       <c r="A138" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B138" t="str">
         <f t="shared" si="5"/>
@@ -17370,7 +17379,7 @@
     <row r="139" spans="1:65">
       <c r="A139" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B139" t="str">
         <f t="shared" si="5"/>
@@ -17449,7 +17458,7 @@
     <row r="140" spans="1:65">
       <c r="A140" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B140" t="str">
         <f t="shared" si="5"/>
@@ -17528,7 +17537,7 @@
     <row r="141" spans="1:65">
       <c r="A141" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B141" t="str">
         <f t="shared" si="5"/>
@@ -17607,7 +17616,7 @@
     <row r="142" spans="1:65">
       <c r="A142" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B142" t="str">
         <f t="shared" si="5"/>
@@ -17686,7 +17695,7 @@
     <row r="143" spans="1:65">
       <c r="A143" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B143" t="str">
         <f t="shared" si="5"/>
@@ -17765,7 +17774,7 @@
     <row r="144" spans="1:65">
       <c r="A144" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B144" t="str">
         <f t="shared" si="5"/>
@@ -17844,7 +17853,7 @@
     <row r="145" spans="1:65">
       <c r="A145" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B145" t="str">
         <f t="shared" si="5"/>
@@ -17923,7 +17932,7 @@
     <row r="146" spans="1:65">
       <c r="A146" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B146" t="str">
         <f t="shared" si="5"/>
@@ -18002,7 +18011,7 @@
     <row r="147" spans="1:65">
       <c r="A147" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B147" t="str">
         <f t="shared" si="5"/>
@@ -18081,7 +18090,7 @@
     <row r="148" spans="1:65">
       <c r="A148" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B148" t="str">
         <f t="shared" si="5"/>
@@ -18162,7 +18171,7 @@
     <row r="149" spans="1:65">
       <c r="A149" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B149" t="str">
         <f t="shared" si="5"/>
@@ -18241,7 +18250,7 @@
     <row r="150" spans="1:65">
       <c r="A150" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B150" t="str">
         <f t="shared" si="5"/>
@@ -18320,7 +18329,7 @@
     <row r="151" spans="1:65">
       <c r="A151" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B151" t="str">
         <f t="shared" si="5"/>
@@ -18399,7 +18408,7 @@
     <row r="152" spans="1:65">
       <c r="A152" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B152" t="str">
         <f t="shared" si="5"/>
@@ -18478,7 +18487,7 @@
     <row r="153" spans="1:65">
       <c r="A153" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B153" t="str">
         <f t="shared" si="5"/>
@@ -18557,7 +18566,7 @@
     <row r="154" spans="1:65">
       <c r="A154" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B154" t="str">
         <f t="shared" si="5"/>
@@ -18636,7 +18645,7 @@
     <row r="155" spans="1:65">
       <c r="A155" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B155" t="str">
         <f t="shared" si="5"/>
@@ -18715,7 +18724,7 @@
     <row r="156" spans="1:65">
       <c r="A156" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B156" t="str">
         <f t="shared" si="5"/>
@@ -18794,7 +18803,7 @@
     <row r="157" spans="1:65">
       <c r="A157" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B157" t="str">
         <f t="shared" si="5"/>
@@ -18873,7 +18882,7 @@
     <row r="158" spans="1:65">
       <c r="A158" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B158" t="str">
         <f t="shared" si="5"/>
@@ -18952,7 +18961,7 @@
     <row r="159" spans="1:65">
       <c r="A159" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B159" t="str">
         <f t="shared" si="5"/>
@@ -19031,7 +19040,7 @@
     <row r="160" spans="1:65">
       <c r="A160" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B160" t="str">
         <f t="shared" si="5"/>
@@ -19110,7 +19119,7 @@
     <row r="161" spans="1:65">
       <c r="A161" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B161" t="str">
         <f t="shared" si="5"/>
@@ -19189,7 +19198,7 @@
     <row r="162" spans="1:65">
       <c r="A162" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B162" t="str">
         <f t="shared" si="5"/>
@@ -19268,7 +19277,7 @@
     <row r="163" spans="1:65">
       <c r="A163" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B163" t="str">
         <f t="shared" si="5"/>
@@ -19347,7 +19356,7 @@
     <row r="164" spans="1:65">
       <c r="A164" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B164" t="str">
         <f t="shared" si="5"/>
@@ -19426,7 +19435,7 @@
     <row r="165" spans="1:65">
       <c r="A165" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B165" t="str">
         <f t="shared" si="5"/>
@@ -19505,7 +19514,7 @@
     <row r="166" spans="1:65">
       <c r="A166" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B166" t="str">
         <f t="shared" si="5"/>
@@ -19586,7 +19595,7 @@
     <row r="167" spans="1:65">
       <c r="A167" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B167" t="str">
         <f t="shared" si="5"/>
@@ -19665,7 +19674,7 @@
     <row r="168" spans="1:65">
       <c r="A168" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B168" t="str">
         <f t="shared" si="5"/>
@@ -19747,7 +19756,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B169" t="str">
         <f>TEXT($C169, "HH:mm")</f>
@@ -19829,7 +19838,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B170" t="str">
         <f t="shared" ref="B170:B233" si="7">TEXT($C170, "HH:mm")</f>
@@ -19908,7 +19917,7 @@
     <row r="171" spans="1:65">
       <c r="A171" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B171" t="str">
         <f t="shared" si="7"/>
@@ -19987,7 +19996,7 @@
     <row r="172" spans="1:65">
       <c r="A172" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B172" t="str">
         <f t="shared" si="7"/>
@@ -20068,7 +20077,7 @@
     <row r="173" spans="1:65">
       <c r="A173" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B173" t="str">
         <f t="shared" si="7"/>
@@ -20147,7 +20156,7 @@
     <row r="174" spans="1:65">
       <c r="A174" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B174" t="str">
         <f t="shared" si="7"/>
@@ -20226,7 +20235,7 @@
     <row r="175" spans="1:65">
       <c r="A175" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B175" t="str">
         <f t="shared" si="7"/>
@@ -20305,7 +20314,7 @@
     <row r="176" spans="1:65">
       <c r="A176" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B176" t="str">
         <f t="shared" si="7"/>
@@ -20384,7 +20393,7 @@
     <row r="177" spans="1:65">
       <c r="A177" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B177" t="str">
         <f t="shared" si="7"/>
@@ -20463,7 +20472,7 @@
     <row r="178" spans="1:65">
       <c r="A178" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B178" t="str">
         <f t="shared" si="7"/>
@@ -20544,7 +20553,7 @@
     <row r="179" spans="1:65">
       <c r="A179" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B179" t="str">
         <f t="shared" si="7"/>
@@ -20623,7 +20632,7 @@
     <row r="180" spans="1:65">
       <c r="A180" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B180" t="str">
         <f t="shared" si="7"/>
@@ -20702,7 +20711,7 @@
     <row r="181" spans="1:65">
       <c r="A181" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B181" t="str">
         <f t="shared" si="7"/>
@@ -20783,7 +20792,7 @@
     <row r="182" spans="1:65">
       <c r="A182" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B182" t="str">
         <f t="shared" si="7"/>
@@ -20864,7 +20873,7 @@
     <row r="183" spans="1:65">
       <c r="A183" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B183" t="str">
         <f t="shared" si="7"/>
@@ -20945,7 +20954,7 @@
     <row r="184" spans="1:65">
       <c r="A184" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B184" t="str">
         <f t="shared" si="7"/>
@@ -21028,7 +21037,7 @@
     <row r="185" spans="1:65">
       <c r="A185" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B185" t="str">
         <f t="shared" si="7"/>
@@ -21109,7 +21118,7 @@
     <row r="186" spans="1:65">
       <c r="A186" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B186" t="str">
         <f t="shared" si="7"/>
@@ -21190,7 +21199,7 @@
     <row r="187" spans="1:65">
       <c r="A187" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B187" t="str">
         <f t="shared" si="7"/>
@@ -21271,7 +21280,7 @@
     <row r="188" spans="1:65">
       <c r="A188" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B188" t="str">
         <f t="shared" si="7"/>
@@ -21352,7 +21361,7 @@
     <row r="189" spans="1:65">
       <c r="A189" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B189" t="str">
         <f t="shared" si="7"/>
@@ -21433,7 +21442,7 @@
     <row r="190" spans="1:65">
       <c r="A190" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B190" t="str">
         <f t="shared" si="7"/>
@@ -21516,7 +21525,7 @@
     <row r="191" spans="1:65">
       <c r="A191" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B191" t="str">
         <f t="shared" si="7"/>
@@ -21599,7 +21608,7 @@
     <row r="192" spans="1:65">
       <c r="A192" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B192" t="str">
         <f t="shared" si="7"/>
@@ -21682,7 +21691,7 @@
     <row r="193" spans="1:65">
       <c r="A193" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B193" t="str">
         <f t="shared" si="7"/>
@@ -21765,7 +21774,7 @@
     <row r="194" spans="1:65">
       <c r="A194" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B194" t="str">
         <f t="shared" si="7"/>
@@ -21846,7 +21855,7 @@
     <row r="195" spans="1:65">
       <c r="A195" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B195" t="str">
         <f t="shared" si="7"/>
@@ -21927,7 +21936,7 @@
     <row r="196" spans="1:65">
       <c r="A196" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B196" t="str">
         <f t="shared" si="7"/>
@@ -22010,7 +22019,7 @@
     <row r="197" spans="1:65">
       <c r="A197" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B197" t="str">
         <f t="shared" si="7"/>
@@ -22089,7 +22098,7 @@
     <row r="198" spans="1:65">
       <c r="A198" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B198" t="str">
         <f t="shared" si="7"/>
@@ -22168,7 +22177,7 @@
     <row r="199" spans="1:65">
       <c r="A199" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B199" t="str">
         <f t="shared" si="7"/>
@@ -22247,7 +22256,7 @@
     <row r="200" spans="1:65">
       <c r="A200" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B200" t="str">
         <f t="shared" si="7"/>
@@ -22326,7 +22335,7 @@
     <row r="201" spans="1:65">
       <c r="A201" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B201" t="str">
         <f t="shared" si="7"/>
@@ -22405,7 +22414,7 @@
     <row r="202" spans="1:65">
       <c r="A202" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B202" t="str">
         <f t="shared" si="7"/>
@@ -22486,7 +22495,7 @@
     <row r="203" spans="1:65">
       <c r="A203" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B203" t="str">
         <f t="shared" si="7"/>
@@ -22565,7 +22574,7 @@
     <row r="204" spans="1:65">
       <c r="A204" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B204" t="str">
         <f t="shared" si="7"/>
@@ -22644,7 +22653,7 @@
     <row r="205" spans="1:65">
       <c r="A205" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B205" t="str">
         <f t="shared" si="7"/>
@@ -22723,7 +22732,7 @@
     <row r="206" spans="1:65">
       <c r="A206" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B206" t="str">
         <f t="shared" si="7"/>
@@ -22802,7 +22811,7 @@
     <row r="207" spans="1:65">
       <c r="A207" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B207" t="str">
         <f t="shared" si="7"/>
@@ -22881,7 +22890,7 @@
     <row r="208" spans="1:65">
       <c r="A208" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B208" t="str">
         <f t="shared" si="7"/>
@@ -22962,7 +22971,7 @@
     <row r="209" spans="1:65">
       <c r="A209" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B209" t="str">
         <f t="shared" si="7"/>
@@ -23041,7 +23050,7 @@
     <row r="210" spans="1:65">
       <c r="A210" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B210" t="str">
         <f t="shared" si="7"/>
@@ -23120,7 +23129,7 @@
     <row r="211" spans="1:65">
       <c r="A211" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B211" t="str">
         <f t="shared" si="7"/>
@@ -23201,7 +23210,7 @@
     <row r="212" spans="1:65">
       <c r="A212" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B212" t="str">
         <f t="shared" si="7"/>
@@ -23280,7 +23289,7 @@
     <row r="213" spans="1:65">
       <c r="A213" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B213" t="str">
         <f t="shared" si="7"/>
@@ -23359,7 +23368,7 @@
     <row r="214" spans="1:65">
       <c r="A214" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B214" t="str">
         <f t="shared" si="7"/>
@@ -23438,7 +23447,7 @@
     <row r="215" spans="1:65">
       <c r="A215" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B215" t="str">
         <f t="shared" si="7"/>
@@ -23517,7 +23526,7 @@
     <row r="216" spans="1:65">
       <c r="A216" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B216" t="str">
         <f t="shared" si="7"/>
@@ -23596,7 +23605,7 @@
     <row r="217" spans="1:65">
       <c r="A217" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B217" t="str">
         <f t="shared" si="7"/>
@@ -23675,7 +23684,7 @@
     <row r="218" spans="1:65">
       <c r="A218" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B218" t="str">
         <f t="shared" si="7"/>
@@ -23754,7 +23763,7 @@
     <row r="219" spans="1:65">
       <c r="A219" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B219" t="str">
         <f t="shared" si="7"/>
@@ -23833,7 +23842,7 @@
     <row r="220" spans="1:65">
       <c r="A220" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B220" t="str">
         <f t="shared" si="7"/>
@@ -23914,7 +23923,7 @@
     <row r="221" spans="1:65">
       <c r="A221" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B221" t="str">
         <f t="shared" si="7"/>
@@ -23993,7 +24002,7 @@
     <row r="222" spans="1:65">
       <c r="A222" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B222" t="str">
         <f t="shared" si="7"/>
@@ -24072,7 +24081,7 @@
     <row r="223" spans="1:65">
       <c r="A223" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B223" t="str">
         <f t="shared" si="7"/>
@@ -24151,7 +24160,7 @@
     <row r="224" spans="1:65">
       <c r="A224" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B224" t="str">
         <f t="shared" si="7"/>
@@ -24230,7 +24239,7 @@
     <row r="225" spans="1:65">
       <c r="A225" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B225" t="str">
         <f t="shared" si="7"/>
@@ -24309,7 +24318,7 @@
     <row r="226" spans="1:65">
       <c r="A226" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B226" t="str">
         <f t="shared" si="7"/>
@@ -24388,7 +24397,7 @@
     <row r="227" spans="1:65">
       <c r="A227" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B227" t="str">
         <f t="shared" si="7"/>
@@ -24467,7 +24476,7 @@
     <row r="228" spans="1:65">
       <c r="A228" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B228" t="str">
         <f t="shared" si="7"/>
@@ -24546,7 +24555,7 @@
     <row r="229" spans="1:65">
       <c r="A229" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B229" t="str">
         <f t="shared" si="7"/>
@@ -24625,7 +24634,7 @@
     <row r="230" spans="1:65">
       <c r="A230" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B230" t="str">
         <f t="shared" si="7"/>
@@ -24704,7 +24713,7 @@
     <row r="231" spans="1:65">
       <c r="A231" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B231" t="str">
         <f t="shared" si="7"/>
@@ -24783,7 +24792,7 @@
     <row r="232" spans="1:65">
       <c r="A232" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B232" t="str">
         <f t="shared" si="7"/>
@@ -24862,7 +24871,7 @@
     <row r="233" spans="1:65">
       <c r="A233" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B233" t="str">
         <f t="shared" si="7"/>
@@ -24944,7 +24953,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B234" t="str">
         <f t="shared" ref="B234:B291" si="9">TEXT($C234, "HH:mm")</f>
@@ -25023,7 +25032,7 @@
     <row r="235" spans="1:65">
       <c r="A235" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B235" t="str">
         <f t="shared" si="9"/>
@@ -25102,7 +25111,7 @@
     <row r="236" spans="1:65">
       <c r="A236" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B236" t="str">
         <f t="shared" si="9"/>
@@ -25181,7 +25190,7 @@
     <row r="237" spans="1:65">
       <c r="A237" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B237" t="str">
         <f t="shared" si="9"/>
@@ -25260,7 +25269,7 @@
     <row r="238" spans="1:65">
       <c r="A238" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B238" t="str">
         <f t="shared" si="9"/>
@@ -25339,7 +25348,7 @@
     <row r="239" spans="1:65">
       <c r="A239" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B239" t="str">
         <f t="shared" si="9"/>
@@ -25418,7 +25427,7 @@
     <row r="240" spans="1:65">
       <c r="A240" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B240" t="str">
         <f t="shared" si="9"/>
@@ -25497,7 +25506,7 @@
     <row r="241" spans="1:65">
       <c r="A241" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B241" t="str">
         <f t="shared" si="9"/>
@@ -25576,7 +25585,7 @@
     <row r="242" spans="1:65">
       <c r="A242" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B242" t="str">
         <f t="shared" si="9"/>
@@ -25655,7 +25664,7 @@
     <row r="243" spans="1:65">
       <c r="A243" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B243" t="str">
         <f t="shared" si="9"/>
@@ -25734,7 +25743,7 @@
     <row r="244" spans="1:65">
       <c r="A244" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B244" t="str">
         <f t="shared" si="9"/>
@@ -25813,7 +25822,7 @@
     <row r="245" spans="1:65">
       <c r="A245" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B245" t="str">
         <f t="shared" si="9"/>
@@ -25892,7 +25901,7 @@
     <row r="246" spans="1:65">
       <c r="A246" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B246" t="str">
         <f t="shared" si="9"/>
@@ -25971,7 +25980,7 @@
     <row r="247" spans="1:65">
       <c r="A247" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B247" t="str">
         <f t="shared" si="9"/>
@@ -26050,7 +26059,7 @@
     <row r="248" spans="1:65">
       <c r="A248" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B248" t="str">
         <f t="shared" si="9"/>
@@ -26129,7 +26138,7 @@
     <row r="249" spans="1:65">
       <c r="A249" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B249" t="str">
         <f t="shared" si="9"/>
@@ -26208,7 +26217,7 @@
     <row r="250" spans="1:65">
       <c r="A250" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B250" t="str">
         <f t="shared" si="9"/>
@@ -26287,7 +26296,7 @@
     <row r="251" spans="1:65">
       <c r="A251" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B251" t="str">
         <f t="shared" si="9"/>
@@ -26366,7 +26375,7 @@
     <row r="252" spans="1:65">
       <c r="A252" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B252" t="str">
         <f t="shared" si="9"/>
@@ -26445,7 +26454,7 @@
     <row r="253" spans="1:65">
       <c r="A253" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B253" t="str">
         <f t="shared" si="9"/>
@@ -26524,7 +26533,7 @@
     <row r="254" spans="1:65">
       <c r="A254" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B254" t="str">
         <f t="shared" si="9"/>
@@ -26603,7 +26612,7 @@
     <row r="255" spans="1:65">
       <c r="A255" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B255" t="str">
         <f t="shared" si="9"/>
@@ -26682,7 +26691,7 @@
     <row r="256" spans="1:65">
       <c r="A256" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B256" t="str">
         <f t="shared" si="9"/>
@@ -26761,7 +26770,7 @@
     <row r="257" spans="1:65">
       <c r="A257" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B257" t="str">
         <f t="shared" si="9"/>
@@ -26840,7 +26849,7 @@
     <row r="258" spans="1:65">
       <c r="A258" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B258" t="str">
         <f t="shared" si="9"/>
@@ -26919,7 +26928,7 @@
     <row r="259" spans="1:65">
       <c r="A259" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B259" t="str">
         <f t="shared" si="9"/>
@@ -26998,7 +27007,7 @@
     <row r="260" spans="1:65">
       <c r="A260" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B260" t="str">
         <f t="shared" si="9"/>
@@ -27077,7 +27086,7 @@
     <row r="261" spans="1:65">
       <c r="A261" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B261" t="str">
         <f t="shared" si="9"/>
@@ -27156,7 +27165,7 @@
     <row r="262" spans="1:65">
       <c r="A262" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B262" t="str">
         <f t="shared" si="9"/>
@@ -27235,7 +27244,7 @@
     <row r="263" spans="1:65">
       <c r="A263" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B263" t="str">
         <f t="shared" si="9"/>
@@ -27314,7 +27323,7 @@
     <row r="264" spans="1:65">
       <c r="A264" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B264" t="str">
         <f t="shared" si="9"/>
@@ -27393,7 +27402,7 @@
     <row r="265" spans="1:65">
       <c r="A265" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B265" t="str">
         <f t="shared" si="9"/>
@@ -27472,7 +27481,7 @@
     <row r="266" spans="1:65">
       <c r="A266" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B266" t="str">
         <f t="shared" si="9"/>
@@ -27551,7 +27560,7 @@
     <row r="267" spans="1:65">
       <c r="A267" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B267" t="str">
         <f t="shared" si="9"/>
@@ -27630,7 +27639,7 @@
     <row r="268" spans="1:65">
       <c r="A268" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B268" t="str">
         <f t="shared" si="9"/>
@@ -27709,7 +27718,7 @@
     <row r="269" spans="1:65">
       <c r="A269" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B269" t="str">
         <f t="shared" si="9"/>
@@ -27788,7 +27797,7 @@
     <row r="270" spans="1:65">
       <c r="A270" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B270" t="str">
         <f t="shared" si="9"/>
@@ -27867,7 +27876,7 @@
     <row r="271" spans="1:65">
       <c r="A271" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B271" t="str">
         <f t="shared" si="9"/>
@@ -27946,7 +27955,7 @@
     <row r="272" spans="1:65">
       <c r="A272" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B272" t="str">
         <f t="shared" si="9"/>
@@ -28025,7 +28034,7 @@
     <row r="273" spans="1:65">
       <c r="A273" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B273" t="str">
         <f t="shared" si="9"/>
@@ -28104,7 +28113,7 @@
     <row r="274" spans="1:65">
       <c r="A274" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B274" t="str">
         <f t="shared" si="9"/>
@@ -28183,7 +28192,7 @@
     <row r="275" spans="1:65">
       <c r="A275" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B275" t="str">
         <f t="shared" si="9"/>
@@ -28262,7 +28271,7 @@
     <row r="276" spans="1:65">
       <c r="A276" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B276" t="str">
         <f t="shared" si="9"/>
@@ -28341,7 +28350,7 @@
     <row r="277" spans="1:65">
       <c r="A277" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B277" t="str">
         <f t="shared" si="9"/>
@@ -28420,7 +28429,7 @@
     <row r="278" spans="1:65">
       <c r="A278" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B278" t="str">
         <f t="shared" si="9"/>
@@ -28499,7 +28508,7 @@
     <row r="279" spans="1:65">
       <c r="A279" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B279" t="str">
         <f t="shared" si="9"/>
@@ -28578,7 +28587,7 @@
     <row r="280" spans="1:65">
       <c r="A280" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B280" t="str">
         <f t="shared" si="9"/>
@@ -28657,7 +28666,7 @@
     <row r="281" spans="1:65">
       <c r="A281" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B281" t="str">
         <f t="shared" si="9"/>
@@ -28736,7 +28745,7 @@
     <row r="282" spans="1:65">
       <c r="A282" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B282" t="str">
         <f t="shared" si="9"/>
@@ -28815,7 +28824,7 @@
     <row r="283" spans="1:65">
       <c r="A283" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B283" t="str">
         <f t="shared" si="9"/>
@@ -28894,7 +28903,7 @@
     <row r="284" spans="1:65">
       <c r="A284" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B284" t="str">
         <f t="shared" si="9"/>
@@ -28973,7 +28982,7 @@
     <row r="285" spans="1:65">
       <c r="A285" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B285" t="str">
         <f t="shared" si="9"/>
@@ -29052,7 +29061,7 @@
     <row r="286" spans="1:65">
       <c r="A286" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B286" t="str">
         <f t="shared" si="9"/>
@@ -29131,7 +29140,7 @@
     <row r="287" spans="1:65">
       <c r="A287" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B287" t="str">
         <f t="shared" si="9"/>
@@ -29210,7 +29219,7 @@
     <row r="288" spans="1:65">
       <c r="A288" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B288" t="str">
         <f t="shared" si="9"/>
@@ -29289,7 +29298,7 @@
     <row r="289" spans="1:65">
       <c r="A289" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B289" t="str">
         <f t="shared" si="9"/>
@@ -29368,7 +29377,7 @@
     <row r="290" spans="1:65">
       <c r="A290" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B290" t="str">
         <f t="shared" si="9"/>
@@ -29447,7 +29456,7 @@
     <row r="291" spans="1:65">
       <c r="A291" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:45</v>
+        <v>01:50</v>
       </c>
       <c r="B291" t="str">
         <f t="shared" si="9"/>

--- a/Vite-Vercel開発.xlsx
+++ b/Vite-Vercel開発.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2c67ec30e06f060f/work/GitHub/work-time-tracker/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{1928CA11-C4AD-40E9-B1C5-143667E830EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0E3CF06-DBF0-490C-A784-0DAEBE68D2D7}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{1928CA11-C4AD-40E9-B1C5-143667E830EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0A94D47-EB38-414E-9E37-725EAC88550C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1546" uniqueCount="923">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1547" uniqueCount="924">
   <si>
     <t>npm install -g vercel</t>
     <phoneticPr fontId="1"/>
@@ -5370,6 +5370,10 @@
   </si>
   <si>
     <t>Found 54 errors in 14 files.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Found 56 errors in 14 files.</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -6142,7 +6146,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{083174DA-A42C-4F9C-978E-61AEAAD9DDFF}">
-  <dimension ref="B2:D28"/>
+  <dimension ref="B2:D29"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
@@ -6290,6 +6294,11 @@
     <row r="28" spans="3:3">
       <c r="C28" t="s">
         <v>922</v>
+      </c>
+    </row>
+    <row r="29" spans="3:3">
+      <c r="C29" t="s">
+        <v>923</v>
       </c>
     </row>
   </sheetData>
@@ -6456,7 +6465,7 @@
       MOD(NOW(),1),
       TIME(0,5,0)
     ),"HH:mm")</f>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B2" s="19"/>
       <c r="D2" s="1">
@@ -6467,7 +6476,7 @@
     <row r="3" spans="1:65">
       <c r="A3" s="19" t="str">
         <f ca="1">TEXT(NOW(),"HH:mm")</f>
-        <v>01:52</v>
+        <v>01:57</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="17" t="s">
@@ -6666,7 +6675,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B4" t="str">
         <f t="shared" ref="B4:B67" si="1">TEXT($C4, "HH:mm")</f>
@@ -6745,7 +6754,7 @@
     <row r="5" spans="1:65">
       <c r="A5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B5" t="str">
         <f t="shared" si="1"/>
@@ -6824,7 +6833,7 @@
     <row r="6" spans="1:65">
       <c r="A6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B6" t="str">
         <f t="shared" si="1"/>
@@ -6903,7 +6912,7 @@
     <row r="7" spans="1:65">
       <c r="A7" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B7" t="str">
         <f t="shared" si="1"/>
@@ -6982,7 +6991,7 @@
     <row r="8" spans="1:65">
       <c r="A8" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B8" t="str">
         <f t="shared" si="1"/>
@@ -7061,7 +7070,7 @@
     <row r="9" spans="1:65">
       <c r="A9" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B9" t="str">
         <f t="shared" si="1"/>
@@ -7140,7 +7149,7 @@
     <row r="10" spans="1:65">
       <c r="A10" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B10" t="str">
         <f t="shared" si="1"/>
@@ -7219,7 +7228,7 @@
     <row r="11" spans="1:65">
       <c r="A11" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B11" t="str">
         <f t="shared" si="1"/>
@@ -7298,7 +7307,7 @@
     <row r="12" spans="1:65">
       <c r="A12" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B12" t="str">
         <f t="shared" si="1"/>
@@ -7377,7 +7386,7 @@
     <row r="13" spans="1:65">
       <c r="A13" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B13" t="str">
         <f t="shared" si="1"/>
@@ -7456,7 +7465,7 @@
     <row r="14" spans="1:65">
       <c r="A14" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B14" t="str">
         <f t="shared" si="1"/>
@@ -7535,7 +7544,7 @@
     <row r="15" spans="1:65">
       <c r="A15" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B15" t="str">
         <f t="shared" si="1"/>
@@ -7614,7 +7623,7 @@
     <row r="16" spans="1:65">
       <c r="A16" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B16" t="str">
         <f t="shared" si="1"/>
@@ -7693,7 +7702,7 @@
     <row r="17" spans="1:65">
       <c r="A17" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B17" t="str">
         <f t="shared" si="1"/>
@@ -7772,7 +7781,7 @@
     <row r="18" spans="1:65">
       <c r="A18" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B18" t="str">
         <f t="shared" si="1"/>
@@ -7851,7 +7860,7 @@
     <row r="19" spans="1:65">
       <c r="A19" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B19" t="str">
         <f t="shared" si="1"/>
@@ -7930,7 +7939,7 @@
     <row r="20" spans="1:65">
       <c r="A20" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B20" t="str">
         <f t="shared" si="1"/>
@@ -8009,7 +8018,7 @@
     <row r="21" spans="1:65">
       <c r="A21" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B21" t="str">
         <f t="shared" si="1"/>
@@ -8088,7 +8097,7 @@
     <row r="22" spans="1:65">
       <c r="A22" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B22" t="str">
         <f t="shared" si="1"/>
@@ -8167,7 +8176,7 @@
     <row r="23" spans="1:65">
       <c r="A23" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B23" t="str">
         <f t="shared" si="1"/>
@@ -8246,7 +8255,7 @@
     <row r="24" spans="1:65">
       <c r="A24" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B24" t="str">
         <f t="shared" si="1"/>
@@ -8325,7 +8334,7 @@
     <row r="25" spans="1:65">
       <c r="A25" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B25" t="str">
         <f t="shared" si="1"/>
@@ -8404,7 +8413,7 @@
     <row r="26" spans="1:65">
       <c r="A26" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B26" t="str">
         <f t="shared" si="1"/>
@@ -8483,7 +8492,7 @@
     <row r="27" spans="1:65">
       <c r="A27" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B27" t="str">
         <f t="shared" si="1"/>
@@ -8562,7 +8571,7 @@
     <row r="28" spans="1:65">
       <c r="A28" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B28" t="str">
         <f t="shared" si="1"/>
@@ -8643,7 +8652,7 @@
     <row r="29" spans="1:65">
       <c r="A29" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B29" t="str">
         <f t="shared" si="1"/>
@@ -8724,7 +8733,7 @@
     <row r="30" spans="1:65">
       <c r="A30" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B30" t="str">
         <f t="shared" si="1"/>
@@ -8805,7 +8814,7 @@
     <row r="31" spans="1:65">
       <c r="A31" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B31" t="str">
         <f t="shared" si="1"/>
@@ -8884,7 +8893,7 @@
     <row r="32" spans="1:65">
       <c r="A32" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B32" t="str">
         <f t="shared" si="1"/>
@@ -8963,7 +8972,7 @@
     <row r="33" spans="1:65">
       <c r="A33" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B33" t="str">
         <f t="shared" si="1"/>
@@ -9042,7 +9051,7 @@
     <row r="34" spans="1:65">
       <c r="A34" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B34" t="str">
         <f t="shared" si="1"/>
@@ -9123,7 +9132,7 @@
     <row r="35" spans="1:65">
       <c r="A35" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B35" t="str">
         <f t="shared" si="1"/>
@@ -9204,7 +9213,7 @@
     <row r="36" spans="1:65">
       <c r="A36" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B36" t="str">
         <f t="shared" si="1"/>
@@ -9285,7 +9294,7 @@
     <row r="37" spans="1:65">
       <c r="A37" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B37" t="str">
         <f t="shared" si="1"/>
@@ -9364,7 +9373,7 @@
     <row r="38" spans="1:65">
       <c r="A38" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B38" t="str">
         <f t="shared" si="1"/>
@@ -9443,7 +9452,7 @@
     <row r="39" spans="1:65">
       <c r="A39" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B39" t="str">
         <f t="shared" si="1"/>
@@ -9522,7 +9531,7 @@
     <row r="40" spans="1:65">
       <c r="A40" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B40" t="str">
         <f t="shared" si="1"/>
@@ -9601,7 +9610,7 @@
     <row r="41" spans="1:65">
       <c r="A41" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B41" t="str">
         <f t="shared" si="1"/>
@@ -9680,7 +9689,7 @@
     <row r="42" spans="1:65">
       <c r="A42" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B42" t="str">
         <f t="shared" si="1"/>
@@ -9761,7 +9770,7 @@
     <row r="43" spans="1:65">
       <c r="A43" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B43" t="str">
         <f t="shared" si="1"/>
@@ -9842,7 +9851,7 @@
     <row r="44" spans="1:65">
       <c r="A44" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B44" t="str">
         <f t="shared" si="1"/>
@@ -9921,7 +9930,7 @@
     <row r="45" spans="1:65">
       <c r="A45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B45" t="str">
         <f t="shared" si="1"/>
@@ -10000,7 +10009,7 @@
     <row r="46" spans="1:65">
       <c r="A46" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B46" t="str">
         <f t="shared" si="1"/>
@@ -10079,7 +10088,7 @@
     <row r="47" spans="1:65">
       <c r="A47" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B47" t="str">
         <f t="shared" si="1"/>
@@ -10158,7 +10167,7 @@
     <row r="48" spans="1:65">
       <c r="A48" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B48" t="str">
         <f t="shared" si="1"/>
@@ -10237,7 +10246,7 @@
     <row r="49" spans="1:65">
       <c r="A49" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B49" t="str">
         <f t="shared" si="1"/>
@@ -10318,7 +10327,7 @@
     <row r="50" spans="1:65">
       <c r="A50" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B50" t="str">
         <f t="shared" si="1"/>
@@ -10399,7 +10408,7 @@
     <row r="51" spans="1:65">
       <c r="A51" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B51" t="str">
         <f t="shared" si="1"/>
@@ -10478,7 +10487,7 @@
     <row r="52" spans="1:65">
       <c r="A52" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B52" t="str">
         <f t="shared" si="1"/>
@@ -10557,7 +10566,7 @@
     <row r="53" spans="1:65">
       <c r="A53" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B53" t="str">
         <f t="shared" si="1"/>
@@ -10636,7 +10645,7 @@
     <row r="54" spans="1:65">
       <c r="A54" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B54" t="str">
         <f t="shared" si="1"/>
@@ -10715,7 +10724,7 @@
     <row r="55" spans="1:65">
       <c r="A55" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B55" t="str">
         <f t="shared" si="1"/>
@@ -10794,7 +10803,7 @@
     <row r="56" spans="1:65">
       <c r="A56" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B56" t="str">
         <f t="shared" si="1"/>
@@ -10875,7 +10884,7 @@
     <row r="57" spans="1:65">
       <c r="A57" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B57" t="str">
         <f t="shared" si="1"/>
@@ -10954,7 +10963,7 @@
     <row r="58" spans="1:65">
       <c r="A58" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B58" t="str">
         <f t="shared" si="1"/>
@@ -11035,7 +11044,7 @@
     <row r="59" spans="1:65">
       <c r="A59" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B59" t="str">
         <f t="shared" si="1"/>
@@ -11114,7 +11123,7 @@
     <row r="60" spans="1:65">
       <c r="A60" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B60" t="str">
         <f t="shared" si="1"/>
@@ -11193,7 +11202,7 @@
     <row r="61" spans="1:65">
       <c r="A61" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B61" t="str">
         <f t="shared" si="1"/>
@@ -11272,7 +11281,7 @@
     <row r="62" spans="1:65">
       <c r="A62" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B62" t="str">
         <f t="shared" si="1"/>
@@ -11351,7 +11360,7 @@
     <row r="63" spans="1:65">
       <c r="A63" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B63" t="str">
         <f t="shared" si="1"/>
@@ -11430,7 +11439,7 @@
     <row r="64" spans="1:65">
       <c r="A64" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B64" t="str">
         <f t="shared" si="1"/>
@@ -11511,7 +11520,7 @@
     <row r="65" spans="1:65">
       <c r="A65" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B65" t="str">
         <f t="shared" si="1"/>
@@ -11590,7 +11599,7 @@
     <row r="66" spans="1:65">
       <c r="A66" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B66" t="str">
         <f t="shared" si="1"/>
@@ -11669,7 +11678,7 @@
     <row r="67" spans="1:65">
       <c r="A67" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B67" t="str">
         <f t="shared" si="1"/>
@@ -11751,7 +11760,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B68" t="str">
         <f t="shared" ref="B68:B131" si="3">TEXT($C68, "HH:mm")</f>
@@ -11830,7 +11839,7 @@
     <row r="69" spans="1:65">
       <c r="A69" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B69" t="str">
         <f t="shared" si="3"/>
@@ -11909,7 +11918,7 @@
     <row r="70" spans="1:65">
       <c r="A70" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B70" t="str">
         <f t="shared" si="3"/>
@@ -11988,7 +11997,7 @@
     <row r="71" spans="1:65">
       <c r="A71" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B71" t="str">
         <f t="shared" si="3"/>
@@ -12067,7 +12076,7 @@
     <row r="72" spans="1:65">
       <c r="A72" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B72" t="str">
         <f t="shared" si="3"/>
@@ -12146,7 +12155,7 @@
     <row r="73" spans="1:65">
       <c r="A73" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B73" t="str">
         <f t="shared" si="3"/>
@@ -12225,7 +12234,7 @@
     <row r="74" spans="1:65">
       <c r="A74" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B74" t="str">
         <f t="shared" si="3"/>
@@ -12304,7 +12313,7 @@
     <row r="75" spans="1:65">
       <c r="A75" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B75" t="str">
         <f t="shared" si="3"/>
@@ -12383,7 +12392,7 @@
     <row r="76" spans="1:65">
       <c r="A76" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B76" t="str">
         <f t="shared" si="3"/>
@@ -12462,7 +12471,7 @@
     <row r="77" spans="1:65">
       <c r="A77" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B77" t="str">
         <f t="shared" si="3"/>
@@ -12541,7 +12550,7 @@
     <row r="78" spans="1:65">
       <c r="A78" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B78" t="str">
         <f t="shared" si="3"/>
@@ -12620,7 +12629,7 @@
     <row r="79" spans="1:65">
       <c r="A79" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B79" t="str">
         <f t="shared" si="3"/>
@@ -12699,7 +12708,7 @@
     <row r="80" spans="1:65">
       <c r="A80" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B80" t="str">
         <f t="shared" si="3"/>
@@ -12778,7 +12787,7 @@
     <row r="81" spans="1:65">
       <c r="A81" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B81" t="str">
         <f t="shared" si="3"/>
@@ -12857,7 +12866,7 @@
     <row r="82" spans="1:65">
       <c r="A82" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B82" t="str">
         <f t="shared" si="3"/>
@@ -12936,7 +12945,7 @@
     <row r="83" spans="1:65">
       <c r="A83" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B83" t="str">
         <f t="shared" si="3"/>
@@ -13015,7 +13024,7 @@
     <row r="84" spans="1:65">
       <c r="A84" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B84" t="str">
         <f t="shared" si="3"/>
@@ -13094,7 +13103,7 @@
     <row r="85" spans="1:65">
       <c r="A85" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B85" t="str">
         <f t="shared" si="3"/>
@@ -13173,7 +13182,7 @@
     <row r="86" spans="1:65">
       <c r="A86" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B86" t="str">
         <f t="shared" si="3"/>
@@ -13252,7 +13261,7 @@
     <row r="87" spans="1:65">
       <c r="A87" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B87" t="str">
         <f t="shared" si="3"/>
@@ -13331,7 +13340,7 @@
     <row r="88" spans="1:65">
       <c r="A88" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B88" t="str">
         <f t="shared" si="3"/>
@@ -13410,7 +13419,7 @@
     <row r="89" spans="1:65">
       <c r="A89" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B89" t="str">
         <f t="shared" si="3"/>
@@ -13489,7 +13498,7 @@
     <row r="90" spans="1:65">
       <c r="A90" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B90" t="str">
         <f t="shared" si="3"/>
@@ -13568,7 +13577,7 @@
     <row r="91" spans="1:65">
       <c r="A91" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B91" t="str">
         <f t="shared" si="3"/>
@@ -13647,7 +13656,7 @@
     <row r="92" spans="1:65">
       <c r="A92" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B92" t="str">
         <f t="shared" si="3"/>
@@ -13726,7 +13735,7 @@
     <row r="93" spans="1:65">
       <c r="A93" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B93" t="str">
         <f t="shared" si="3"/>
@@ -13805,7 +13814,7 @@
     <row r="94" spans="1:65">
       <c r="A94" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B94" t="str">
         <f t="shared" si="3"/>
@@ -13884,7 +13893,7 @@
     <row r="95" spans="1:65">
       <c r="A95" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B95" t="str">
         <f t="shared" si="3"/>
@@ -13963,7 +13972,7 @@
     <row r="96" spans="1:65">
       <c r="A96" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B96" t="str">
         <f t="shared" si="3"/>
@@ -14042,7 +14051,7 @@
     <row r="97" spans="1:65">
       <c r="A97" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B97" t="str">
         <f t="shared" si="3"/>
@@ -14121,7 +14130,7 @@
     <row r="98" spans="1:65">
       <c r="A98" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B98" t="str">
         <f t="shared" si="3"/>
@@ -14200,7 +14209,7 @@
     <row r="99" spans="1:65">
       <c r="A99" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B99" t="str">
         <f t="shared" si="3"/>
@@ -14279,7 +14288,7 @@
     <row r="100" spans="1:65">
       <c r="A100" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B100" t="str">
         <f t="shared" si="3"/>
@@ -14360,7 +14369,7 @@
     <row r="101" spans="1:65">
       <c r="A101" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B101" t="str">
         <f t="shared" si="3"/>
@@ -14439,7 +14448,7 @@
     <row r="102" spans="1:65">
       <c r="A102" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B102" t="str">
         <f t="shared" si="3"/>
@@ -14518,7 +14527,7 @@
     <row r="103" spans="1:65">
       <c r="A103" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B103" t="str">
         <f t="shared" si="3"/>
@@ -14597,7 +14606,7 @@
     <row r="104" spans="1:65">
       <c r="A104" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B104" t="str">
         <f t="shared" si="3"/>
@@ -14676,7 +14685,7 @@
     <row r="105" spans="1:65">
       <c r="A105" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B105" t="str">
         <f t="shared" si="3"/>
@@ -14755,7 +14764,7 @@
     <row r="106" spans="1:65">
       <c r="A106" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B106" t="str">
         <f t="shared" si="3"/>
@@ -14836,7 +14845,7 @@
     <row r="107" spans="1:65">
       <c r="A107" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B107" t="str">
         <f t="shared" si="3"/>
@@ -14917,7 +14926,7 @@
     <row r="108" spans="1:65">
       <c r="A108" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B108" t="str">
         <f t="shared" si="3"/>
@@ -14996,7 +15005,7 @@
     <row r="109" spans="1:65">
       <c r="A109" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B109" t="str">
         <f t="shared" si="3"/>
@@ -15075,7 +15084,7 @@
     <row r="110" spans="1:65">
       <c r="A110" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B110" t="str">
         <f t="shared" si="3"/>
@@ -15154,7 +15163,7 @@
     <row r="111" spans="1:65">
       <c r="A111" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B111" t="str">
         <f t="shared" si="3"/>
@@ -15233,7 +15242,7 @@
     <row r="112" spans="1:65">
       <c r="A112" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B112" t="str">
         <f t="shared" si="3"/>
@@ -15314,7 +15323,7 @@
     <row r="113" spans="1:65">
       <c r="A113" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B113" t="str">
         <f t="shared" si="3"/>
@@ -15393,7 +15402,7 @@
     <row r="114" spans="1:65">
       <c r="A114" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B114" t="str">
         <f t="shared" si="3"/>
@@ -15472,7 +15481,7 @@
     <row r="115" spans="1:65">
       <c r="A115" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B115" t="str">
         <f t="shared" si="3"/>
@@ -15551,7 +15560,7 @@
     <row r="116" spans="1:65">
       <c r="A116" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B116" t="str">
         <f t="shared" si="3"/>
@@ -15630,7 +15639,7 @@
     <row r="117" spans="1:65">
       <c r="A117" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B117" t="str">
         <f t="shared" si="3"/>
@@ -15709,7 +15718,7 @@
     <row r="118" spans="1:65">
       <c r="A118" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B118" t="str">
         <f t="shared" si="3"/>
@@ -15788,7 +15797,7 @@
     <row r="119" spans="1:65">
       <c r="A119" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B119" t="str">
         <f t="shared" si="3"/>
@@ -15867,7 +15876,7 @@
     <row r="120" spans="1:65">
       <c r="A120" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B120" t="str">
         <f t="shared" si="3"/>
@@ -15946,7 +15955,7 @@
     <row r="121" spans="1:65">
       <c r="A121" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B121" t="str">
         <f t="shared" si="3"/>
@@ -16025,7 +16034,7 @@
     <row r="122" spans="1:65">
       <c r="A122" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B122" t="str">
         <f t="shared" si="3"/>
@@ -16104,7 +16113,7 @@
     <row r="123" spans="1:65">
       <c r="A123" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B123" t="str">
         <f t="shared" si="3"/>
@@ -16183,7 +16192,7 @@
     <row r="124" spans="1:65">
       <c r="A124" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B124" t="str">
         <f t="shared" si="3"/>
@@ -16264,7 +16273,7 @@
     <row r="125" spans="1:65">
       <c r="A125" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B125" t="str">
         <f t="shared" si="3"/>
@@ -16345,7 +16354,7 @@
     <row r="126" spans="1:65">
       <c r="A126" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B126" t="str">
         <f t="shared" si="3"/>
@@ -16424,7 +16433,7 @@
     <row r="127" spans="1:65">
       <c r="A127" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B127" t="str">
         <f t="shared" si="3"/>
@@ -16503,7 +16512,7 @@
     <row r="128" spans="1:65">
       <c r="A128" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B128" t="str">
         <f t="shared" si="3"/>
@@ -16582,7 +16591,7 @@
     <row r="129" spans="1:65">
       <c r="A129" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B129" t="str">
         <f t="shared" si="3"/>
@@ -16661,7 +16670,7 @@
     <row r="130" spans="1:65">
       <c r="A130" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B130" t="str">
         <f t="shared" si="3"/>
@@ -16740,7 +16749,7 @@
     <row r="131" spans="1:65">
       <c r="A131" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B131" t="str">
         <f t="shared" si="3"/>
@@ -16822,7 +16831,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B132" t="str">
         <f t="shared" ref="B132:B168" si="5">TEXT($C132, "HH:mm")</f>
@@ -16901,7 +16910,7 @@
     <row r="133" spans="1:65">
       <c r="A133" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B133" t="str">
         <f t="shared" si="5"/>
@@ -16980,7 +16989,7 @@
     <row r="134" spans="1:65">
       <c r="A134" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B134" t="str">
         <f t="shared" si="5"/>
@@ -17059,7 +17068,7 @@
     <row r="135" spans="1:65">
       <c r="A135" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B135" t="str">
         <f t="shared" si="5"/>
@@ -17138,7 +17147,7 @@
     <row r="136" spans="1:65">
       <c r="A136" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B136" t="str">
         <f t="shared" si="5"/>
@@ -17219,7 +17228,7 @@
     <row r="137" spans="1:65">
       <c r="A137" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B137" t="str">
         <f t="shared" si="5"/>
@@ -17300,7 +17309,7 @@
     <row r="138" spans="1:65">
       <c r="A138" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B138" t="str">
         <f t="shared" si="5"/>
@@ -17379,7 +17388,7 @@
     <row r="139" spans="1:65">
       <c r="A139" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B139" t="str">
         <f t="shared" si="5"/>
@@ -17458,7 +17467,7 @@
     <row r="140" spans="1:65">
       <c r="A140" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B140" t="str">
         <f t="shared" si="5"/>
@@ -17537,7 +17546,7 @@
     <row r="141" spans="1:65">
       <c r="A141" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B141" t="str">
         <f t="shared" si="5"/>
@@ -17616,7 +17625,7 @@
     <row r="142" spans="1:65">
       <c r="A142" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B142" t="str">
         <f t="shared" si="5"/>
@@ -17695,7 +17704,7 @@
     <row r="143" spans="1:65">
       <c r="A143" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B143" t="str">
         <f t="shared" si="5"/>
@@ -17774,7 +17783,7 @@
     <row r="144" spans="1:65">
       <c r="A144" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B144" t="str">
         <f t="shared" si="5"/>
@@ -17853,7 +17862,7 @@
     <row r="145" spans="1:65">
       <c r="A145" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B145" t="str">
         <f t="shared" si="5"/>
@@ -17932,7 +17941,7 @@
     <row r="146" spans="1:65">
       <c r="A146" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B146" t="str">
         <f t="shared" si="5"/>
@@ -18011,7 +18020,7 @@
     <row r="147" spans="1:65">
       <c r="A147" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B147" t="str">
         <f t="shared" si="5"/>
@@ -18090,7 +18099,7 @@
     <row r="148" spans="1:65">
       <c r="A148" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B148" t="str">
         <f t="shared" si="5"/>
@@ -18171,7 +18180,7 @@
     <row r="149" spans="1:65">
       <c r="A149" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B149" t="str">
         <f t="shared" si="5"/>
@@ -18250,7 +18259,7 @@
     <row r="150" spans="1:65">
       <c r="A150" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B150" t="str">
         <f t="shared" si="5"/>
@@ -18329,7 +18338,7 @@
     <row r="151" spans="1:65">
       <c r="A151" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B151" t="str">
         <f t="shared" si="5"/>
@@ -18408,7 +18417,7 @@
     <row r="152" spans="1:65">
       <c r="A152" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B152" t="str">
         <f t="shared" si="5"/>
@@ -18487,7 +18496,7 @@
     <row r="153" spans="1:65">
       <c r="A153" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B153" t="str">
         <f t="shared" si="5"/>
@@ -18566,7 +18575,7 @@
     <row r="154" spans="1:65">
       <c r="A154" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B154" t="str">
         <f t="shared" si="5"/>
@@ -18645,7 +18654,7 @@
     <row r="155" spans="1:65">
       <c r="A155" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B155" t="str">
         <f t="shared" si="5"/>
@@ -18724,7 +18733,7 @@
     <row r="156" spans="1:65">
       <c r="A156" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B156" t="str">
         <f t="shared" si="5"/>
@@ -18803,7 +18812,7 @@
     <row r="157" spans="1:65">
       <c r="A157" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B157" t="str">
         <f t="shared" si="5"/>
@@ -18882,7 +18891,7 @@
     <row r="158" spans="1:65">
       <c r="A158" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B158" t="str">
         <f t="shared" si="5"/>
@@ -18961,7 +18970,7 @@
     <row r="159" spans="1:65">
       <c r="A159" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B159" t="str">
         <f t="shared" si="5"/>
@@ -19040,7 +19049,7 @@
     <row r="160" spans="1:65">
       <c r="A160" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B160" t="str">
         <f t="shared" si="5"/>
@@ -19119,7 +19128,7 @@
     <row r="161" spans="1:65">
       <c r="A161" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B161" t="str">
         <f t="shared" si="5"/>
@@ -19198,7 +19207,7 @@
     <row r="162" spans="1:65">
       <c r="A162" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B162" t="str">
         <f t="shared" si="5"/>
@@ -19277,7 +19286,7 @@
     <row r="163" spans="1:65">
       <c r="A163" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B163" t="str">
         <f t="shared" si="5"/>
@@ -19356,7 +19365,7 @@
     <row r="164" spans="1:65">
       <c r="A164" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B164" t="str">
         <f t="shared" si="5"/>
@@ -19435,7 +19444,7 @@
     <row r="165" spans="1:65">
       <c r="A165" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B165" t="str">
         <f t="shared" si="5"/>
@@ -19514,7 +19523,7 @@
     <row r="166" spans="1:65">
       <c r="A166" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B166" t="str">
         <f t="shared" si="5"/>
@@ -19595,7 +19604,7 @@
     <row r="167" spans="1:65">
       <c r="A167" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B167" t="str">
         <f t="shared" si="5"/>
@@ -19674,7 +19683,7 @@
     <row r="168" spans="1:65">
       <c r="A168" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B168" t="str">
         <f t="shared" si="5"/>
@@ -19756,7 +19765,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B169" t="str">
         <f>TEXT($C169, "HH:mm")</f>
@@ -19838,7 +19847,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B170" t="str">
         <f t="shared" ref="B170:B233" si="7">TEXT($C170, "HH:mm")</f>
@@ -19917,7 +19926,7 @@
     <row r="171" spans="1:65">
       <c r="A171" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B171" t="str">
         <f t="shared" si="7"/>
@@ -19996,7 +20005,7 @@
     <row r="172" spans="1:65">
       <c r="A172" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B172" t="str">
         <f t="shared" si="7"/>
@@ -20077,7 +20086,7 @@
     <row r="173" spans="1:65">
       <c r="A173" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B173" t="str">
         <f t="shared" si="7"/>
@@ -20156,7 +20165,7 @@
     <row r="174" spans="1:65">
       <c r="A174" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B174" t="str">
         <f t="shared" si="7"/>
@@ -20235,7 +20244,7 @@
     <row r="175" spans="1:65">
       <c r="A175" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B175" t="str">
         <f t="shared" si="7"/>
@@ -20314,7 +20323,7 @@
     <row r="176" spans="1:65">
       <c r="A176" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B176" t="str">
         <f t="shared" si="7"/>
@@ -20393,7 +20402,7 @@
     <row r="177" spans="1:65">
       <c r="A177" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B177" t="str">
         <f t="shared" si="7"/>
@@ -20472,7 +20481,7 @@
     <row r="178" spans="1:65">
       <c r="A178" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B178" t="str">
         <f t="shared" si="7"/>
@@ -20553,7 +20562,7 @@
     <row r="179" spans="1:65">
       <c r="A179" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B179" t="str">
         <f t="shared" si="7"/>
@@ -20632,7 +20641,7 @@
     <row r="180" spans="1:65">
       <c r="A180" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B180" t="str">
         <f t="shared" si="7"/>
@@ -20711,7 +20720,7 @@
     <row r="181" spans="1:65">
       <c r="A181" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B181" t="str">
         <f t="shared" si="7"/>
@@ -20792,7 +20801,7 @@
     <row r="182" spans="1:65">
       <c r="A182" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B182" t="str">
         <f t="shared" si="7"/>
@@ -20873,7 +20882,7 @@
     <row r="183" spans="1:65">
       <c r="A183" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B183" t="str">
         <f t="shared" si="7"/>
@@ -20954,7 +20963,7 @@
     <row r="184" spans="1:65">
       <c r="A184" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B184" t="str">
         <f t="shared" si="7"/>
@@ -21037,7 +21046,7 @@
     <row r="185" spans="1:65">
       <c r="A185" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B185" t="str">
         <f t="shared" si="7"/>
@@ -21118,7 +21127,7 @@
     <row r="186" spans="1:65">
       <c r="A186" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B186" t="str">
         <f t="shared" si="7"/>
@@ -21199,7 +21208,7 @@
     <row r="187" spans="1:65">
       <c r="A187" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B187" t="str">
         <f t="shared" si="7"/>
@@ -21280,7 +21289,7 @@
     <row r="188" spans="1:65">
       <c r="A188" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B188" t="str">
         <f t="shared" si="7"/>
@@ -21361,7 +21370,7 @@
     <row r="189" spans="1:65">
       <c r="A189" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B189" t="str">
         <f t="shared" si="7"/>
@@ -21442,7 +21451,7 @@
     <row r="190" spans="1:65">
       <c r="A190" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B190" t="str">
         <f t="shared" si="7"/>
@@ -21525,7 +21534,7 @@
     <row r="191" spans="1:65">
       <c r="A191" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B191" t="str">
         <f t="shared" si="7"/>
@@ -21608,7 +21617,7 @@
     <row r="192" spans="1:65">
       <c r="A192" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B192" t="str">
         <f t="shared" si="7"/>
@@ -21691,7 +21700,7 @@
     <row r="193" spans="1:65">
       <c r="A193" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B193" t="str">
         <f t="shared" si="7"/>
@@ -21774,7 +21783,7 @@
     <row r="194" spans="1:65">
       <c r="A194" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B194" t="str">
         <f t="shared" si="7"/>
@@ -21855,7 +21864,7 @@
     <row r="195" spans="1:65">
       <c r="A195" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B195" t="str">
         <f t="shared" si="7"/>
@@ -21936,7 +21945,7 @@
     <row r="196" spans="1:65">
       <c r="A196" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B196" t="str">
         <f t="shared" si="7"/>
@@ -22019,7 +22028,7 @@
     <row r="197" spans="1:65">
       <c r="A197" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B197" t="str">
         <f t="shared" si="7"/>
@@ -22098,7 +22107,7 @@
     <row r="198" spans="1:65">
       <c r="A198" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B198" t="str">
         <f t="shared" si="7"/>
@@ -22177,7 +22186,7 @@
     <row r="199" spans="1:65">
       <c r="A199" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B199" t="str">
         <f t="shared" si="7"/>
@@ -22256,7 +22265,7 @@
     <row r="200" spans="1:65">
       <c r="A200" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B200" t="str">
         <f t="shared" si="7"/>
@@ -22335,7 +22344,7 @@
     <row r="201" spans="1:65">
       <c r="A201" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B201" t="str">
         <f t="shared" si="7"/>
@@ -22414,7 +22423,7 @@
     <row r="202" spans="1:65">
       <c r="A202" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B202" t="str">
         <f t="shared" si="7"/>
@@ -22495,7 +22504,7 @@
     <row r="203" spans="1:65">
       <c r="A203" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B203" t="str">
         <f t="shared" si="7"/>
@@ -22574,7 +22583,7 @@
     <row r="204" spans="1:65">
       <c r="A204" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B204" t="str">
         <f t="shared" si="7"/>
@@ -22653,7 +22662,7 @@
     <row r="205" spans="1:65">
       <c r="A205" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B205" t="str">
         <f t="shared" si="7"/>
@@ -22732,7 +22741,7 @@
     <row r="206" spans="1:65">
       <c r="A206" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B206" t="str">
         <f t="shared" si="7"/>
@@ -22811,7 +22820,7 @@
     <row r="207" spans="1:65">
       <c r="A207" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B207" t="str">
         <f t="shared" si="7"/>
@@ -22890,7 +22899,7 @@
     <row r="208" spans="1:65">
       <c r="A208" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B208" t="str">
         <f t="shared" si="7"/>
@@ -22971,7 +22980,7 @@
     <row r="209" spans="1:65">
       <c r="A209" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B209" t="str">
         <f t="shared" si="7"/>
@@ -23050,7 +23059,7 @@
     <row r="210" spans="1:65">
       <c r="A210" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B210" t="str">
         <f t="shared" si="7"/>
@@ -23129,7 +23138,7 @@
     <row r="211" spans="1:65">
       <c r="A211" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B211" t="str">
         <f t="shared" si="7"/>
@@ -23210,7 +23219,7 @@
     <row r="212" spans="1:65">
       <c r="A212" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B212" t="str">
         <f t="shared" si="7"/>
@@ -23289,7 +23298,7 @@
     <row r="213" spans="1:65">
       <c r="A213" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B213" t="str">
         <f t="shared" si="7"/>
@@ -23368,7 +23377,7 @@
     <row r="214" spans="1:65">
       <c r="A214" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B214" t="str">
         <f t="shared" si="7"/>
@@ -23447,7 +23456,7 @@
     <row r="215" spans="1:65">
       <c r="A215" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B215" t="str">
         <f t="shared" si="7"/>
@@ -23526,7 +23535,7 @@
     <row r="216" spans="1:65">
       <c r="A216" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B216" t="str">
         <f t="shared" si="7"/>
@@ -23605,7 +23614,7 @@
     <row r="217" spans="1:65">
       <c r="A217" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B217" t="str">
         <f t="shared" si="7"/>
@@ -23684,7 +23693,7 @@
     <row r="218" spans="1:65">
       <c r="A218" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B218" t="str">
         <f t="shared" si="7"/>
@@ -23763,7 +23772,7 @@
     <row r="219" spans="1:65">
       <c r="A219" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B219" t="str">
         <f t="shared" si="7"/>
@@ -23842,7 +23851,7 @@
     <row r="220" spans="1:65">
       <c r="A220" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B220" t="str">
         <f t="shared" si="7"/>
@@ -23923,7 +23932,7 @@
     <row r="221" spans="1:65">
       <c r="A221" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B221" t="str">
         <f t="shared" si="7"/>
@@ -24002,7 +24011,7 @@
     <row r="222" spans="1:65">
       <c r="A222" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B222" t="str">
         <f t="shared" si="7"/>
@@ -24081,7 +24090,7 @@
     <row r="223" spans="1:65">
       <c r="A223" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B223" t="str">
         <f t="shared" si="7"/>
@@ -24160,7 +24169,7 @@
     <row r="224" spans="1:65">
       <c r="A224" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B224" t="str">
         <f t="shared" si="7"/>
@@ -24239,7 +24248,7 @@
     <row r="225" spans="1:65">
       <c r="A225" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B225" t="str">
         <f t="shared" si="7"/>
@@ -24318,7 +24327,7 @@
     <row r="226" spans="1:65">
       <c r="A226" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B226" t="str">
         <f t="shared" si="7"/>
@@ -24397,7 +24406,7 @@
     <row r="227" spans="1:65">
       <c r="A227" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B227" t="str">
         <f t="shared" si="7"/>
@@ -24476,7 +24485,7 @@
     <row r="228" spans="1:65">
       <c r="A228" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B228" t="str">
         <f t="shared" si="7"/>
@@ -24555,7 +24564,7 @@
     <row r="229" spans="1:65">
       <c r="A229" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B229" t="str">
         <f t="shared" si="7"/>
@@ -24634,7 +24643,7 @@
     <row r="230" spans="1:65">
       <c r="A230" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B230" t="str">
         <f t="shared" si="7"/>
@@ -24713,7 +24722,7 @@
     <row r="231" spans="1:65">
       <c r="A231" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B231" t="str">
         <f t="shared" si="7"/>
@@ -24792,7 +24801,7 @@
     <row r="232" spans="1:65">
       <c r="A232" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B232" t="str">
         <f t="shared" si="7"/>
@@ -24871,7 +24880,7 @@
     <row r="233" spans="1:65">
       <c r="A233" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B233" t="str">
         <f t="shared" si="7"/>
@@ -24953,7 +24962,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B234" t="str">
         <f t="shared" ref="B234:B291" si="9">TEXT($C234, "HH:mm")</f>
@@ -25032,7 +25041,7 @@
     <row r="235" spans="1:65">
       <c r="A235" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B235" t="str">
         <f t="shared" si="9"/>
@@ -25111,7 +25120,7 @@
     <row r="236" spans="1:65">
       <c r="A236" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B236" t="str">
         <f t="shared" si="9"/>
@@ -25190,7 +25199,7 @@
     <row r="237" spans="1:65">
       <c r="A237" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B237" t="str">
         <f t="shared" si="9"/>
@@ -25269,7 +25278,7 @@
     <row r="238" spans="1:65">
       <c r="A238" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B238" t="str">
         <f t="shared" si="9"/>
@@ -25348,7 +25357,7 @@
     <row r="239" spans="1:65">
       <c r="A239" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B239" t="str">
         <f t="shared" si="9"/>
@@ -25427,7 +25436,7 @@
     <row r="240" spans="1:65">
       <c r="A240" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B240" t="str">
         <f t="shared" si="9"/>
@@ -25506,7 +25515,7 @@
     <row r="241" spans="1:65">
       <c r="A241" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B241" t="str">
         <f t="shared" si="9"/>
@@ -25585,7 +25594,7 @@
     <row r="242" spans="1:65">
       <c r="A242" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B242" t="str">
         <f t="shared" si="9"/>
@@ -25664,7 +25673,7 @@
     <row r="243" spans="1:65">
       <c r="A243" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B243" t="str">
         <f t="shared" si="9"/>
@@ -25743,7 +25752,7 @@
     <row r="244" spans="1:65">
       <c r="A244" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B244" t="str">
         <f t="shared" si="9"/>
@@ -25822,7 +25831,7 @@
     <row r="245" spans="1:65">
       <c r="A245" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B245" t="str">
         <f t="shared" si="9"/>
@@ -25901,7 +25910,7 @@
     <row r="246" spans="1:65">
       <c r="A246" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B246" t="str">
         <f t="shared" si="9"/>
@@ -25980,7 +25989,7 @@
     <row r="247" spans="1:65">
       <c r="A247" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B247" t="str">
         <f t="shared" si="9"/>
@@ -26059,7 +26068,7 @@
     <row r="248" spans="1:65">
       <c r="A248" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B248" t="str">
         <f t="shared" si="9"/>
@@ -26138,7 +26147,7 @@
     <row r="249" spans="1:65">
       <c r="A249" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B249" t="str">
         <f t="shared" si="9"/>
@@ -26217,7 +26226,7 @@
     <row r="250" spans="1:65">
       <c r="A250" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B250" t="str">
         <f t="shared" si="9"/>
@@ -26296,7 +26305,7 @@
     <row r="251" spans="1:65">
       <c r="A251" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B251" t="str">
         <f t="shared" si="9"/>
@@ -26375,7 +26384,7 @@
     <row r="252" spans="1:65">
       <c r="A252" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B252" t="str">
         <f t="shared" si="9"/>
@@ -26454,7 +26463,7 @@
     <row r="253" spans="1:65">
       <c r="A253" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B253" t="str">
         <f t="shared" si="9"/>
@@ -26533,7 +26542,7 @@
     <row r="254" spans="1:65">
       <c r="A254" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B254" t="str">
         <f t="shared" si="9"/>
@@ -26612,7 +26621,7 @@
     <row r="255" spans="1:65">
       <c r="A255" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B255" t="str">
         <f t="shared" si="9"/>
@@ -26691,7 +26700,7 @@
     <row r="256" spans="1:65">
       <c r="A256" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B256" t="str">
         <f t="shared" si="9"/>
@@ -26770,7 +26779,7 @@
     <row r="257" spans="1:65">
       <c r="A257" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B257" t="str">
         <f t="shared" si="9"/>
@@ -26849,7 +26858,7 @@
     <row r="258" spans="1:65">
       <c r="A258" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B258" t="str">
         <f t="shared" si="9"/>
@@ -26928,7 +26937,7 @@
     <row r="259" spans="1:65">
       <c r="A259" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B259" t="str">
         <f t="shared" si="9"/>
@@ -27007,7 +27016,7 @@
     <row r="260" spans="1:65">
       <c r="A260" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B260" t="str">
         <f t="shared" si="9"/>
@@ -27086,7 +27095,7 @@
     <row r="261" spans="1:65">
       <c r="A261" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B261" t="str">
         <f t="shared" si="9"/>
@@ -27165,7 +27174,7 @@
     <row r="262" spans="1:65">
       <c r="A262" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B262" t="str">
         <f t="shared" si="9"/>
@@ -27244,7 +27253,7 @@
     <row r="263" spans="1:65">
       <c r="A263" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B263" t="str">
         <f t="shared" si="9"/>
@@ -27323,7 +27332,7 @@
     <row r="264" spans="1:65">
       <c r="A264" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B264" t="str">
         <f t="shared" si="9"/>
@@ -27402,7 +27411,7 @@
     <row r="265" spans="1:65">
       <c r="A265" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B265" t="str">
         <f t="shared" si="9"/>
@@ -27481,7 +27490,7 @@
     <row r="266" spans="1:65">
       <c r="A266" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B266" t="str">
         <f t="shared" si="9"/>
@@ -27560,7 +27569,7 @@
     <row r="267" spans="1:65">
       <c r="A267" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B267" t="str">
         <f t="shared" si="9"/>
@@ -27639,7 +27648,7 @@
     <row r="268" spans="1:65">
       <c r="A268" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B268" t="str">
         <f t="shared" si="9"/>
@@ -27718,7 +27727,7 @@
     <row r="269" spans="1:65">
       <c r="A269" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B269" t="str">
         <f t="shared" si="9"/>
@@ -27797,7 +27806,7 @@
     <row r="270" spans="1:65">
       <c r="A270" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B270" t="str">
         <f t="shared" si="9"/>
@@ -27876,7 +27885,7 @@
     <row r="271" spans="1:65">
       <c r="A271" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B271" t="str">
         <f t="shared" si="9"/>
@@ -27955,7 +27964,7 @@
     <row r="272" spans="1:65">
       <c r="A272" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B272" t="str">
         <f t="shared" si="9"/>
@@ -28034,7 +28043,7 @@
     <row r="273" spans="1:65">
       <c r="A273" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B273" t="str">
         <f t="shared" si="9"/>
@@ -28113,7 +28122,7 @@
     <row r="274" spans="1:65">
       <c r="A274" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B274" t="str">
         <f t="shared" si="9"/>
@@ -28192,7 +28201,7 @@
     <row r="275" spans="1:65">
       <c r="A275" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B275" t="str">
         <f t="shared" si="9"/>
@@ -28271,7 +28280,7 @@
     <row r="276" spans="1:65">
       <c r="A276" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B276" t="str">
         <f t="shared" si="9"/>
@@ -28350,7 +28359,7 @@
     <row r="277" spans="1:65">
       <c r="A277" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B277" t="str">
         <f t="shared" si="9"/>
@@ -28429,7 +28438,7 @@
     <row r="278" spans="1:65">
       <c r="A278" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B278" t="str">
         <f t="shared" si="9"/>
@@ -28508,7 +28517,7 @@
     <row r="279" spans="1:65">
       <c r="A279" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B279" t="str">
         <f t="shared" si="9"/>
@@ -28587,7 +28596,7 @@
     <row r="280" spans="1:65">
       <c r="A280" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B280" t="str">
         <f t="shared" si="9"/>
@@ -28666,7 +28675,7 @@
     <row r="281" spans="1:65">
       <c r="A281" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B281" t="str">
         <f t="shared" si="9"/>
@@ -28745,7 +28754,7 @@
     <row r="282" spans="1:65">
       <c r="A282" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B282" t="str">
         <f t="shared" si="9"/>
@@ -28824,7 +28833,7 @@
     <row r="283" spans="1:65">
       <c r="A283" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B283" t="str">
         <f t="shared" si="9"/>
@@ -28903,7 +28912,7 @@
     <row r="284" spans="1:65">
       <c r="A284" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B284" t="str">
         <f t="shared" si="9"/>
@@ -28982,7 +28991,7 @@
     <row r="285" spans="1:65">
       <c r="A285" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B285" t="str">
         <f t="shared" si="9"/>
@@ -29061,7 +29070,7 @@
     <row r="286" spans="1:65">
       <c r="A286" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B286" t="str">
         <f t="shared" si="9"/>
@@ -29140,7 +29149,7 @@
     <row r="287" spans="1:65">
       <c r="A287" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B287" t="str">
         <f t="shared" si="9"/>
@@ -29219,7 +29228,7 @@
     <row r="288" spans="1:65">
       <c r="A288" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B288" t="str">
         <f t="shared" si="9"/>
@@ -29298,7 +29307,7 @@
     <row r="289" spans="1:65">
       <c r="A289" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B289" t="str">
         <f t="shared" si="9"/>
@@ -29377,7 +29386,7 @@
     <row r="290" spans="1:65">
       <c r="A290" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B290" t="str">
         <f t="shared" si="9"/>
@@ -29456,7 +29465,7 @@
     <row r="291" spans="1:65">
       <c r="A291" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:50</v>
+        <v>01:55</v>
       </c>
       <c r="B291" t="str">
         <f t="shared" si="9"/>

--- a/Vite-Vercel開発.xlsx
+++ b/Vite-Vercel開発.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2c67ec30e06f060f/work/GitHub/work-time-tracker/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{1928CA11-C4AD-40E9-B1C5-143667E830EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0A94D47-EB38-414E-9E37-725EAC88550C}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{1928CA11-C4AD-40E9-B1C5-143667E830EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43CEE80F-D70D-4CBE-81AD-2823A128AD66}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1547" uniqueCount="924">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1548" uniqueCount="925">
   <si>
     <t>npm install -g vercel</t>
     <phoneticPr fontId="1"/>
@@ -5374,6 +5374,10 @@
   </si>
   <si>
     <t>Found 56 errors in 14 files.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Found 47 errors in 11 files.</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -6146,7 +6150,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{083174DA-A42C-4F9C-978E-61AEAAD9DDFF}">
-  <dimension ref="B2:D29"/>
+  <dimension ref="B2:D30"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
@@ -6299,6 +6303,11 @@
     <row r="29" spans="3:3">
       <c r="C29" t="s">
         <v>923</v>
+      </c>
+    </row>
+    <row r="30" spans="3:3">
+      <c r="C30" t="s">
+        <v>924</v>
       </c>
     </row>
   </sheetData>
@@ -6465,7 +6474,7 @@
       MOD(NOW(),1),
       TIME(0,5,0)
     ),"HH:mm")</f>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B2" s="19"/>
       <c r="D2" s="1">
@@ -6476,7 +6485,7 @@
     <row r="3" spans="1:65">
       <c r="A3" s="19" t="str">
         <f ca="1">TEXT(NOW(),"HH:mm")</f>
-        <v>01:57</v>
+        <v>02:05</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="17" t="s">
@@ -6675,7 +6684,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B4" t="str">
         <f t="shared" ref="B4:B67" si="1">TEXT($C4, "HH:mm")</f>
@@ -6754,7 +6763,7 @@
     <row r="5" spans="1:65">
       <c r="A5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B5" t="str">
         <f t="shared" si="1"/>
@@ -6833,7 +6842,7 @@
     <row r="6" spans="1:65">
       <c r="A6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B6" t="str">
         <f t="shared" si="1"/>
@@ -6912,7 +6921,7 @@
     <row r="7" spans="1:65">
       <c r="A7" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B7" t="str">
         <f t="shared" si="1"/>
@@ -6991,7 +7000,7 @@
     <row r="8" spans="1:65">
       <c r="A8" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B8" t="str">
         <f t="shared" si="1"/>
@@ -7070,7 +7079,7 @@
     <row r="9" spans="1:65">
       <c r="A9" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B9" t="str">
         <f t="shared" si="1"/>
@@ -7149,7 +7158,7 @@
     <row r="10" spans="1:65">
       <c r="A10" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B10" t="str">
         <f t="shared" si="1"/>
@@ -7228,7 +7237,7 @@
     <row r="11" spans="1:65">
       <c r="A11" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B11" t="str">
         <f t="shared" si="1"/>
@@ -7307,7 +7316,7 @@
     <row r="12" spans="1:65">
       <c r="A12" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B12" t="str">
         <f t="shared" si="1"/>
@@ -7386,7 +7395,7 @@
     <row r="13" spans="1:65">
       <c r="A13" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B13" t="str">
         <f t="shared" si="1"/>
@@ -7465,7 +7474,7 @@
     <row r="14" spans="1:65">
       <c r="A14" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B14" t="str">
         <f t="shared" si="1"/>
@@ -7544,7 +7553,7 @@
     <row r="15" spans="1:65">
       <c r="A15" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B15" t="str">
         <f t="shared" si="1"/>
@@ -7623,7 +7632,7 @@
     <row r="16" spans="1:65">
       <c r="A16" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B16" t="str">
         <f t="shared" si="1"/>
@@ -7702,7 +7711,7 @@
     <row r="17" spans="1:65">
       <c r="A17" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B17" t="str">
         <f t="shared" si="1"/>
@@ -7781,7 +7790,7 @@
     <row r="18" spans="1:65">
       <c r="A18" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B18" t="str">
         <f t="shared" si="1"/>
@@ -7860,7 +7869,7 @@
     <row r="19" spans="1:65">
       <c r="A19" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B19" t="str">
         <f t="shared" si="1"/>
@@ -7939,7 +7948,7 @@
     <row r="20" spans="1:65">
       <c r="A20" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B20" t="str">
         <f t="shared" si="1"/>
@@ -8018,7 +8027,7 @@
     <row r="21" spans="1:65">
       <c r="A21" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B21" t="str">
         <f t="shared" si="1"/>
@@ -8097,7 +8106,7 @@
     <row r="22" spans="1:65">
       <c r="A22" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B22" t="str">
         <f t="shared" si="1"/>
@@ -8176,7 +8185,7 @@
     <row r="23" spans="1:65">
       <c r="A23" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B23" t="str">
         <f t="shared" si="1"/>
@@ -8255,7 +8264,7 @@
     <row r="24" spans="1:65">
       <c r="A24" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B24" t="str">
         <f t="shared" si="1"/>
@@ -8334,7 +8343,7 @@
     <row r="25" spans="1:65">
       <c r="A25" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B25" t="str">
         <f t="shared" si="1"/>
@@ -8413,7 +8422,7 @@
     <row r="26" spans="1:65">
       <c r="A26" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B26" t="str">
         <f t="shared" si="1"/>
@@ -8492,7 +8501,7 @@
     <row r="27" spans="1:65">
       <c r="A27" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B27" t="str">
         <f t="shared" si="1"/>
@@ -8571,7 +8580,7 @@
     <row r="28" spans="1:65">
       <c r="A28" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B28" t="str">
         <f t="shared" si="1"/>
@@ -8652,7 +8661,7 @@
     <row r="29" spans="1:65">
       <c r="A29" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B29" t="str">
         <f t="shared" si="1"/>
@@ -8733,7 +8742,7 @@
     <row r="30" spans="1:65">
       <c r="A30" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B30" t="str">
         <f t="shared" si="1"/>
@@ -8814,7 +8823,7 @@
     <row r="31" spans="1:65">
       <c r="A31" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B31" t="str">
         <f t="shared" si="1"/>
@@ -8893,7 +8902,7 @@
     <row r="32" spans="1:65">
       <c r="A32" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B32" t="str">
         <f t="shared" si="1"/>
@@ -8972,7 +8981,7 @@
     <row r="33" spans="1:65">
       <c r="A33" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B33" t="str">
         <f t="shared" si="1"/>
@@ -9051,7 +9060,7 @@
     <row r="34" spans="1:65">
       <c r="A34" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B34" t="str">
         <f t="shared" si="1"/>
@@ -9132,7 +9141,7 @@
     <row r="35" spans="1:65">
       <c r="A35" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B35" t="str">
         <f t="shared" si="1"/>
@@ -9213,7 +9222,7 @@
     <row r="36" spans="1:65">
       <c r="A36" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B36" t="str">
         <f t="shared" si="1"/>
@@ -9294,7 +9303,7 @@
     <row r="37" spans="1:65">
       <c r="A37" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B37" t="str">
         <f t="shared" si="1"/>
@@ -9373,7 +9382,7 @@
     <row r="38" spans="1:65">
       <c r="A38" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B38" t="str">
         <f t="shared" si="1"/>
@@ -9452,7 +9461,7 @@
     <row r="39" spans="1:65">
       <c r="A39" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B39" t="str">
         <f t="shared" si="1"/>
@@ -9531,7 +9540,7 @@
     <row r="40" spans="1:65">
       <c r="A40" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B40" t="str">
         <f t="shared" si="1"/>
@@ -9610,7 +9619,7 @@
     <row r="41" spans="1:65">
       <c r="A41" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B41" t="str">
         <f t="shared" si="1"/>
@@ -9689,7 +9698,7 @@
     <row r="42" spans="1:65">
       <c r="A42" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B42" t="str">
         <f t="shared" si="1"/>
@@ -9770,7 +9779,7 @@
     <row r="43" spans="1:65">
       <c r="A43" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B43" t="str">
         <f t="shared" si="1"/>
@@ -9851,7 +9860,7 @@
     <row r="44" spans="1:65">
       <c r="A44" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B44" t="str">
         <f t="shared" si="1"/>
@@ -9930,7 +9939,7 @@
     <row r="45" spans="1:65">
       <c r="A45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B45" t="str">
         <f t="shared" si="1"/>
@@ -10009,7 +10018,7 @@
     <row r="46" spans="1:65">
       <c r="A46" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B46" t="str">
         <f t="shared" si="1"/>
@@ -10088,7 +10097,7 @@
     <row r="47" spans="1:65">
       <c r="A47" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B47" t="str">
         <f t="shared" si="1"/>
@@ -10167,7 +10176,7 @@
     <row r="48" spans="1:65">
       <c r="A48" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B48" t="str">
         <f t="shared" si="1"/>
@@ -10246,7 +10255,7 @@
     <row r="49" spans="1:65">
       <c r="A49" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B49" t="str">
         <f t="shared" si="1"/>
@@ -10327,7 +10336,7 @@
     <row r="50" spans="1:65">
       <c r="A50" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B50" t="str">
         <f t="shared" si="1"/>
@@ -10408,7 +10417,7 @@
     <row r="51" spans="1:65">
       <c r="A51" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B51" t="str">
         <f t="shared" si="1"/>
@@ -10487,7 +10496,7 @@
     <row r="52" spans="1:65">
       <c r="A52" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B52" t="str">
         <f t="shared" si="1"/>
@@ -10566,7 +10575,7 @@
     <row r="53" spans="1:65">
       <c r="A53" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B53" t="str">
         <f t="shared" si="1"/>
@@ -10645,7 +10654,7 @@
     <row r="54" spans="1:65">
       <c r="A54" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B54" t="str">
         <f t="shared" si="1"/>
@@ -10724,7 +10733,7 @@
     <row r="55" spans="1:65">
       <c r="A55" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B55" t="str">
         <f t="shared" si="1"/>
@@ -10803,7 +10812,7 @@
     <row r="56" spans="1:65">
       <c r="A56" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B56" t="str">
         <f t="shared" si="1"/>
@@ -10884,7 +10893,7 @@
     <row r="57" spans="1:65">
       <c r="A57" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B57" t="str">
         <f t="shared" si="1"/>
@@ -10963,7 +10972,7 @@
     <row r="58" spans="1:65">
       <c r="A58" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B58" t="str">
         <f t="shared" si="1"/>
@@ -11044,7 +11053,7 @@
     <row r="59" spans="1:65">
       <c r="A59" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B59" t="str">
         <f t="shared" si="1"/>
@@ -11123,7 +11132,7 @@
     <row r="60" spans="1:65">
       <c r="A60" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B60" t="str">
         <f t="shared" si="1"/>
@@ -11202,7 +11211,7 @@
     <row r="61" spans="1:65">
       <c r="A61" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B61" t="str">
         <f t="shared" si="1"/>
@@ -11281,7 +11290,7 @@
     <row r="62" spans="1:65">
       <c r="A62" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B62" t="str">
         <f t="shared" si="1"/>
@@ -11360,7 +11369,7 @@
     <row r="63" spans="1:65">
       <c r="A63" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B63" t="str">
         <f t="shared" si="1"/>
@@ -11439,7 +11448,7 @@
     <row r="64" spans="1:65">
       <c r="A64" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B64" t="str">
         <f t="shared" si="1"/>
@@ -11520,7 +11529,7 @@
     <row r="65" spans="1:65">
       <c r="A65" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B65" t="str">
         <f t="shared" si="1"/>
@@ -11599,7 +11608,7 @@
     <row r="66" spans="1:65">
       <c r="A66" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B66" t="str">
         <f t="shared" si="1"/>
@@ -11678,7 +11687,7 @@
     <row r="67" spans="1:65">
       <c r="A67" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B67" t="str">
         <f t="shared" si="1"/>
@@ -11760,7 +11769,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B68" t="str">
         <f t="shared" ref="B68:B131" si="3">TEXT($C68, "HH:mm")</f>
@@ -11839,7 +11848,7 @@
     <row r="69" spans="1:65">
       <c r="A69" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B69" t="str">
         <f t="shared" si="3"/>
@@ -11918,7 +11927,7 @@
     <row r="70" spans="1:65">
       <c r="A70" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B70" t="str">
         <f t="shared" si="3"/>
@@ -11997,7 +12006,7 @@
     <row r="71" spans="1:65">
       <c r="A71" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B71" t="str">
         <f t="shared" si="3"/>
@@ -12076,7 +12085,7 @@
     <row r="72" spans="1:65">
       <c r="A72" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B72" t="str">
         <f t="shared" si="3"/>
@@ -12155,7 +12164,7 @@
     <row r="73" spans="1:65">
       <c r="A73" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B73" t="str">
         <f t="shared" si="3"/>
@@ -12234,7 +12243,7 @@
     <row r="74" spans="1:65">
       <c r="A74" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B74" t="str">
         <f t="shared" si="3"/>
@@ -12313,7 +12322,7 @@
     <row r="75" spans="1:65">
       <c r="A75" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B75" t="str">
         <f t="shared" si="3"/>
@@ -12392,7 +12401,7 @@
     <row r="76" spans="1:65">
       <c r="A76" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B76" t="str">
         <f t="shared" si="3"/>
@@ -12471,7 +12480,7 @@
     <row r="77" spans="1:65">
       <c r="A77" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B77" t="str">
         <f t="shared" si="3"/>
@@ -12550,7 +12559,7 @@
     <row r="78" spans="1:65">
       <c r="A78" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B78" t="str">
         <f t="shared" si="3"/>
@@ -12629,7 +12638,7 @@
     <row r="79" spans="1:65">
       <c r="A79" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B79" t="str">
         <f t="shared" si="3"/>
@@ -12708,7 +12717,7 @@
     <row r="80" spans="1:65">
       <c r="A80" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B80" t="str">
         <f t="shared" si="3"/>
@@ -12787,7 +12796,7 @@
     <row r="81" spans="1:65">
       <c r="A81" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B81" t="str">
         <f t="shared" si="3"/>
@@ -12866,7 +12875,7 @@
     <row r="82" spans="1:65">
       <c r="A82" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B82" t="str">
         <f t="shared" si="3"/>
@@ -12945,7 +12954,7 @@
     <row r="83" spans="1:65">
       <c r="A83" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B83" t="str">
         <f t="shared" si="3"/>
@@ -13024,7 +13033,7 @@
     <row r="84" spans="1:65">
       <c r="A84" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B84" t="str">
         <f t="shared" si="3"/>
@@ -13103,7 +13112,7 @@
     <row r="85" spans="1:65">
       <c r="A85" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B85" t="str">
         <f t="shared" si="3"/>
@@ -13182,7 +13191,7 @@
     <row r="86" spans="1:65">
       <c r="A86" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B86" t="str">
         <f t="shared" si="3"/>
@@ -13261,7 +13270,7 @@
     <row r="87" spans="1:65">
       <c r="A87" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B87" t="str">
         <f t="shared" si="3"/>
@@ -13340,7 +13349,7 @@
     <row r="88" spans="1:65">
       <c r="A88" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B88" t="str">
         <f t="shared" si="3"/>
@@ -13419,7 +13428,7 @@
     <row r="89" spans="1:65">
       <c r="A89" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B89" t="str">
         <f t="shared" si="3"/>
@@ -13498,7 +13507,7 @@
     <row r="90" spans="1:65">
       <c r="A90" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B90" t="str">
         <f t="shared" si="3"/>
@@ -13577,7 +13586,7 @@
     <row r="91" spans="1:65">
       <c r="A91" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B91" t="str">
         <f t="shared" si="3"/>
@@ -13656,7 +13665,7 @@
     <row r="92" spans="1:65">
       <c r="A92" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B92" t="str">
         <f t="shared" si="3"/>
@@ -13735,7 +13744,7 @@
     <row r="93" spans="1:65">
       <c r="A93" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B93" t="str">
         <f t="shared" si="3"/>
@@ -13814,7 +13823,7 @@
     <row r="94" spans="1:65">
       <c r="A94" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B94" t="str">
         <f t="shared" si="3"/>
@@ -13893,7 +13902,7 @@
     <row r="95" spans="1:65">
       <c r="A95" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B95" t="str">
         <f t="shared" si="3"/>
@@ -13972,7 +13981,7 @@
     <row r="96" spans="1:65">
       <c r="A96" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B96" t="str">
         <f t="shared" si="3"/>
@@ -14051,7 +14060,7 @@
     <row r="97" spans="1:65">
       <c r="A97" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B97" t="str">
         <f t="shared" si="3"/>
@@ -14130,7 +14139,7 @@
     <row r="98" spans="1:65">
       <c r="A98" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B98" t="str">
         <f t="shared" si="3"/>
@@ -14209,7 +14218,7 @@
     <row r="99" spans="1:65">
       <c r="A99" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B99" t="str">
         <f t="shared" si="3"/>
@@ -14288,7 +14297,7 @@
     <row r="100" spans="1:65">
       <c r="A100" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B100" t="str">
         <f t="shared" si="3"/>
@@ -14369,7 +14378,7 @@
     <row r="101" spans="1:65">
       <c r="A101" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B101" t="str">
         <f t="shared" si="3"/>
@@ -14448,7 +14457,7 @@
     <row r="102" spans="1:65">
       <c r="A102" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B102" t="str">
         <f t="shared" si="3"/>
@@ -14527,7 +14536,7 @@
     <row r="103" spans="1:65">
       <c r="A103" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B103" t="str">
         <f t="shared" si="3"/>
@@ -14606,7 +14615,7 @@
     <row r="104" spans="1:65">
       <c r="A104" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B104" t="str">
         <f t="shared" si="3"/>
@@ -14685,7 +14694,7 @@
     <row r="105" spans="1:65">
       <c r="A105" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B105" t="str">
         <f t="shared" si="3"/>
@@ -14764,7 +14773,7 @@
     <row r="106" spans="1:65">
       <c r="A106" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B106" t="str">
         <f t="shared" si="3"/>
@@ -14845,7 +14854,7 @@
     <row r="107" spans="1:65">
       <c r="A107" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B107" t="str">
         <f t="shared" si="3"/>
@@ -14926,7 +14935,7 @@
     <row r="108" spans="1:65">
       <c r="A108" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B108" t="str">
         <f t="shared" si="3"/>
@@ -15005,7 +15014,7 @@
     <row r="109" spans="1:65">
       <c r="A109" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B109" t="str">
         <f t="shared" si="3"/>
@@ -15084,7 +15093,7 @@
     <row r="110" spans="1:65">
       <c r="A110" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B110" t="str">
         <f t="shared" si="3"/>
@@ -15163,7 +15172,7 @@
     <row r="111" spans="1:65">
       <c r="A111" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B111" t="str">
         <f t="shared" si="3"/>
@@ -15242,7 +15251,7 @@
     <row r="112" spans="1:65">
       <c r="A112" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B112" t="str">
         <f t="shared" si="3"/>
@@ -15323,7 +15332,7 @@
     <row r="113" spans="1:65">
       <c r="A113" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B113" t="str">
         <f t="shared" si="3"/>
@@ -15402,7 +15411,7 @@
     <row r="114" spans="1:65">
       <c r="A114" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B114" t="str">
         <f t="shared" si="3"/>
@@ -15481,7 +15490,7 @@
     <row r="115" spans="1:65">
       <c r="A115" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B115" t="str">
         <f t="shared" si="3"/>
@@ -15560,7 +15569,7 @@
     <row r="116" spans="1:65">
       <c r="A116" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B116" t="str">
         <f t="shared" si="3"/>
@@ -15639,7 +15648,7 @@
     <row r="117" spans="1:65">
       <c r="A117" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B117" t="str">
         <f t="shared" si="3"/>
@@ -15718,7 +15727,7 @@
     <row r="118" spans="1:65">
       <c r="A118" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B118" t="str">
         <f t="shared" si="3"/>
@@ -15797,7 +15806,7 @@
     <row r="119" spans="1:65">
       <c r="A119" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B119" t="str">
         <f t="shared" si="3"/>
@@ -15876,7 +15885,7 @@
     <row r="120" spans="1:65">
       <c r="A120" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B120" t="str">
         <f t="shared" si="3"/>
@@ -15955,7 +15964,7 @@
     <row r="121" spans="1:65">
       <c r="A121" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B121" t="str">
         <f t="shared" si="3"/>
@@ -16034,7 +16043,7 @@
     <row r="122" spans="1:65">
       <c r="A122" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B122" t="str">
         <f t="shared" si="3"/>
@@ -16113,7 +16122,7 @@
     <row r="123" spans="1:65">
       <c r="A123" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B123" t="str">
         <f t="shared" si="3"/>
@@ -16192,7 +16201,7 @@
     <row r="124" spans="1:65">
       <c r="A124" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B124" t="str">
         <f t="shared" si="3"/>
@@ -16273,7 +16282,7 @@
     <row r="125" spans="1:65">
       <c r="A125" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B125" t="str">
         <f t="shared" si="3"/>
@@ -16354,7 +16363,7 @@
     <row r="126" spans="1:65">
       <c r="A126" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B126" t="str">
         <f t="shared" si="3"/>
@@ -16433,7 +16442,7 @@
     <row r="127" spans="1:65">
       <c r="A127" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B127" t="str">
         <f t="shared" si="3"/>
@@ -16512,7 +16521,7 @@
     <row r="128" spans="1:65">
       <c r="A128" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B128" t="str">
         <f t="shared" si="3"/>
@@ -16591,7 +16600,7 @@
     <row r="129" spans="1:65">
       <c r="A129" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B129" t="str">
         <f t="shared" si="3"/>
@@ -16670,7 +16679,7 @@
     <row r="130" spans="1:65">
       <c r="A130" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B130" t="str">
         <f t="shared" si="3"/>
@@ -16749,7 +16758,7 @@
     <row r="131" spans="1:65">
       <c r="A131" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B131" t="str">
         <f t="shared" si="3"/>
@@ -16831,7 +16840,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B132" t="str">
         <f t="shared" ref="B132:B168" si="5">TEXT($C132, "HH:mm")</f>
@@ -16910,7 +16919,7 @@
     <row r="133" spans="1:65">
       <c r="A133" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B133" t="str">
         <f t="shared" si="5"/>
@@ -16989,7 +16998,7 @@
     <row r="134" spans="1:65">
       <c r="A134" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B134" t="str">
         <f t="shared" si="5"/>
@@ -17068,7 +17077,7 @@
     <row r="135" spans="1:65">
       <c r="A135" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B135" t="str">
         <f t="shared" si="5"/>
@@ -17147,7 +17156,7 @@
     <row r="136" spans="1:65">
       <c r="A136" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B136" t="str">
         <f t="shared" si="5"/>
@@ -17228,7 +17237,7 @@
     <row r="137" spans="1:65">
       <c r="A137" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B137" t="str">
         <f t="shared" si="5"/>
@@ -17309,7 +17318,7 @@
     <row r="138" spans="1:65">
       <c r="A138" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B138" t="str">
         <f t="shared" si="5"/>
@@ -17388,7 +17397,7 @@
     <row r="139" spans="1:65">
       <c r="A139" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B139" t="str">
         <f t="shared" si="5"/>
@@ -17467,7 +17476,7 @@
     <row r="140" spans="1:65">
       <c r="A140" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B140" t="str">
         <f t="shared" si="5"/>
@@ -17546,7 +17555,7 @@
     <row r="141" spans="1:65">
       <c r="A141" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B141" t="str">
         <f t="shared" si="5"/>
@@ -17625,7 +17634,7 @@
     <row r="142" spans="1:65">
       <c r="A142" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B142" t="str">
         <f t="shared" si="5"/>
@@ -17704,7 +17713,7 @@
     <row r="143" spans="1:65">
       <c r="A143" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B143" t="str">
         <f t="shared" si="5"/>
@@ -17783,7 +17792,7 @@
     <row r="144" spans="1:65">
       <c r="A144" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B144" t="str">
         <f t="shared" si="5"/>
@@ -17862,7 +17871,7 @@
     <row r="145" spans="1:65">
       <c r="A145" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B145" t="str">
         <f t="shared" si="5"/>
@@ -17941,7 +17950,7 @@
     <row r="146" spans="1:65">
       <c r="A146" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B146" t="str">
         <f t="shared" si="5"/>
@@ -18020,7 +18029,7 @@
     <row r="147" spans="1:65">
       <c r="A147" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B147" t="str">
         <f t="shared" si="5"/>
@@ -18099,7 +18108,7 @@
     <row r="148" spans="1:65">
       <c r="A148" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B148" t="str">
         <f t="shared" si="5"/>
@@ -18180,7 +18189,7 @@
     <row r="149" spans="1:65">
       <c r="A149" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B149" t="str">
         <f t="shared" si="5"/>
@@ -18259,7 +18268,7 @@
     <row r="150" spans="1:65">
       <c r="A150" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B150" t="str">
         <f t="shared" si="5"/>
@@ -18338,7 +18347,7 @@
     <row r="151" spans="1:65">
       <c r="A151" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B151" t="str">
         <f t="shared" si="5"/>
@@ -18417,7 +18426,7 @@
     <row r="152" spans="1:65">
       <c r="A152" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B152" t="str">
         <f t="shared" si="5"/>
@@ -18496,7 +18505,7 @@
     <row r="153" spans="1:65">
       <c r="A153" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B153" t="str">
         <f t="shared" si="5"/>
@@ -18575,7 +18584,7 @@
     <row r="154" spans="1:65">
       <c r="A154" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B154" t="str">
         <f t="shared" si="5"/>
@@ -18654,7 +18663,7 @@
     <row r="155" spans="1:65">
       <c r="A155" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B155" t="str">
         <f t="shared" si="5"/>
@@ -18733,7 +18742,7 @@
     <row r="156" spans="1:65">
       <c r="A156" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B156" t="str">
         <f t="shared" si="5"/>
@@ -18812,7 +18821,7 @@
     <row r="157" spans="1:65">
       <c r="A157" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B157" t="str">
         <f t="shared" si="5"/>
@@ -18891,7 +18900,7 @@
     <row r="158" spans="1:65">
       <c r="A158" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B158" t="str">
         <f t="shared" si="5"/>
@@ -18970,7 +18979,7 @@
     <row r="159" spans="1:65">
       <c r="A159" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B159" t="str">
         <f t="shared" si="5"/>
@@ -19049,7 +19058,7 @@
     <row r="160" spans="1:65">
       <c r="A160" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B160" t="str">
         <f t="shared" si="5"/>
@@ -19128,7 +19137,7 @@
     <row r="161" spans="1:65">
       <c r="A161" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B161" t="str">
         <f t="shared" si="5"/>
@@ -19207,7 +19216,7 @@
     <row r="162" spans="1:65">
       <c r="A162" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B162" t="str">
         <f t="shared" si="5"/>
@@ -19286,7 +19295,7 @@
     <row r="163" spans="1:65">
       <c r="A163" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B163" t="str">
         <f t="shared" si="5"/>
@@ -19365,7 +19374,7 @@
     <row r="164" spans="1:65">
       <c r="A164" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B164" t="str">
         <f t="shared" si="5"/>
@@ -19444,7 +19453,7 @@
     <row r="165" spans="1:65">
       <c r="A165" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B165" t="str">
         <f t="shared" si="5"/>
@@ -19523,7 +19532,7 @@
     <row r="166" spans="1:65">
       <c r="A166" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B166" t="str">
         <f t="shared" si="5"/>
@@ -19604,7 +19613,7 @@
     <row r="167" spans="1:65">
       <c r="A167" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B167" t="str">
         <f t="shared" si="5"/>
@@ -19683,7 +19692,7 @@
     <row r="168" spans="1:65">
       <c r="A168" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B168" t="str">
         <f t="shared" si="5"/>
@@ -19765,7 +19774,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B169" t="str">
         <f>TEXT($C169, "HH:mm")</f>
@@ -19847,7 +19856,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B170" t="str">
         <f t="shared" ref="B170:B233" si="7">TEXT($C170, "HH:mm")</f>
@@ -19926,7 +19935,7 @@
     <row r="171" spans="1:65">
       <c r="A171" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B171" t="str">
         <f t="shared" si="7"/>
@@ -20005,7 +20014,7 @@
     <row r="172" spans="1:65">
       <c r="A172" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B172" t="str">
         <f t="shared" si="7"/>
@@ -20086,7 +20095,7 @@
     <row r="173" spans="1:65">
       <c r="A173" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B173" t="str">
         <f t="shared" si="7"/>
@@ -20165,7 +20174,7 @@
     <row r="174" spans="1:65">
       <c r="A174" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B174" t="str">
         <f t="shared" si="7"/>
@@ -20244,7 +20253,7 @@
     <row r="175" spans="1:65">
       <c r="A175" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B175" t="str">
         <f t="shared" si="7"/>
@@ -20323,7 +20332,7 @@
     <row r="176" spans="1:65">
       <c r="A176" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B176" t="str">
         <f t="shared" si="7"/>
@@ -20402,7 +20411,7 @@
     <row r="177" spans="1:65">
       <c r="A177" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B177" t="str">
         <f t="shared" si="7"/>
@@ -20481,7 +20490,7 @@
     <row r="178" spans="1:65">
       <c r="A178" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B178" t="str">
         <f t="shared" si="7"/>
@@ -20562,7 +20571,7 @@
     <row r="179" spans="1:65">
       <c r="A179" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B179" t="str">
         <f t="shared" si="7"/>
@@ -20641,7 +20650,7 @@
     <row r="180" spans="1:65">
       <c r="A180" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B180" t="str">
         <f t="shared" si="7"/>
@@ -20720,7 +20729,7 @@
     <row r="181" spans="1:65">
       <c r="A181" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B181" t="str">
         <f t="shared" si="7"/>
@@ -20801,7 +20810,7 @@
     <row r="182" spans="1:65">
       <c r="A182" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B182" t="str">
         <f t="shared" si="7"/>
@@ -20882,7 +20891,7 @@
     <row r="183" spans="1:65">
       <c r="A183" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B183" t="str">
         <f t="shared" si="7"/>
@@ -20963,7 +20972,7 @@
     <row r="184" spans="1:65">
       <c r="A184" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B184" t="str">
         <f t="shared" si="7"/>
@@ -21046,7 +21055,7 @@
     <row r="185" spans="1:65">
       <c r="A185" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B185" t="str">
         <f t="shared" si="7"/>
@@ -21127,7 +21136,7 @@
     <row r="186" spans="1:65">
       <c r="A186" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B186" t="str">
         <f t="shared" si="7"/>
@@ -21208,7 +21217,7 @@
     <row r="187" spans="1:65">
       <c r="A187" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B187" t="str">
         <f t="shared" si="7"/>
@@ -21289,7 +21298,7 @@
     <row r="188" spans="1:65">
       <c r="A188" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B188" t="str">
         <f t="shared" si="7"/>
@@ -21370,7 +21379,7 @@
     <row r="189" spans="1:65">
       <c r="A189" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B189" t="str">
         <f t="shared" si="7"/>
@@ -21451,7 +21460,7 @@
     <row r="190" spans="1:65">
       <c r="A190" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B190" t="str">
         <f t="shared" si="7"/>
@@ -21534,7 +21543,7 @@
     <row r="191" spans="1:65">
       <c r="A191" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B191" t="str">
         <f t="shared" si="7"/>
@@ -21617,7 +21626,7 @@
     <row r="192" spans="1:65">
       <c r="A192" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B192" t="str">
         <f t="shared" si="7"/>
@@ -21700,7 +21709,7 @@
     <row r="193" spans="1:65">
       <c r="A193" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B193" t="str">
         <f t="shared" si="7"/>
@@ -21783,7 +21792,7 @@
     <row r="194" spans="1:65">
       <c r="A194" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B194" t="str">
         <f t="shared" si="7"/>
@@ -21864,7 +21873,7 @@
     <row r="195" spans="1:65">
       <c r="A195" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B195" t="str">
         <f t="shared" si="7"/>
@@ -21945,7 +21954,7 @@
     <row r="196" spans="1:65">
       <c r="A196" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B196" t="str">
         <f t="shared" si="7"/>
@@ -22028,7 +22037,7 @@
     <row r="197" spans="1:65">
       <c r="A197" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B197" t="str">
         <f t="shared" si="7"/>
@@ -22107,7 +22116,7 @@
     <row r="198" spans="1:65">
       <c r="A198" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B198" t="str">
         <f t="shared" si="7"/>
@@ -22186,7 +22195,7 @@
     <row r="199" spans="1:65">
       <c r="A199" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B199" t="str">
         <f t="shared" si="7"/>
@@ -22265,7 +22274,7 @@
     <row r="200" spans="1:65">
       <c r="A200" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B200" t="str">
         <f t="shared" si="7"/>
@@ -22344,7 +22353,7 @@
     <row r="201" spans="1:65">
       <c r="A201" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B201" t="str">
         <f t="shared" si="7"/>
@@ -22423,7 +22432,7 @@
     <row r="202" spans="1:65">
       <c r="A202" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B202" t="str">
         <f t="shared" si="7"/>
@@ -22504,7 +22513,7 @@
     <row r="203" spans="1:65">
       <c r="A203" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B203" t="str">
         <f t="shared" si="7"/>
@@ -22583,7 +22592,7 @@
     <row r="204" spans="1:65">
       <c r="A204" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B204" t="str">
         <f t="shared" si="7"/>
@@ -22662,7 +22671,7 @@
     <row r="205" spans="1:65">
       <c r="A205" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B205" t="str">
         <f t="shared" si="7"/>
@@ -22741,7 +22750,7 @@
     <row r="206" spans="1:65">
       <c r="A206" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B206" t="str">
         <f t="shared" si="7"/>
@@ -22820,7 +22829,7 @@
     <row r="207" spans="1:65">
       <c r="A207" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B207" t="str">
         <f t="shared" si="7"/>
@@ -22899,7 +22908,7 @@
     <row r="208" spans="1:65">
       <c r="A208" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B208" t="str">
         <f t="shared" si="7"/>
@@ -22980,7 +22989,7 @@
     <row r="209" spans="1:65">
       <c r="A209" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B209" t="str">
         <f t="shared" si="7"/>
@@ -23059,7 +23068,7 @@
     <row r="210" spans="1:65">
       <c r="A210" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B210" t="str">
         <f t="shared" si="7"/>
@@ -23138,7 +23147,7 @@
     <row r="211" spans="1:65">
       <c r="A211" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B211" t="str">
         <f t="shared" si="7"/>
@@ -23219,7 +23228,7 @@
     <row r="212" spans="1:65">
       <c r="A212" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B212" t="str">
         <f t="shared" si="7"/>
@@ -23298,7 +23307,7 @@
     <row r="213" spans="1:65">
       <c r="A213" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B213" t="str">
         <f t="shared" si="7"/>
@@ -23377,7 +23386,7 @@
     <row r="214" spans="1:65">
       <c r="A214" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B214" t="str">
         <f t="shared" si="7"/>
@@ -23456,7 +23465,7 @@
     <row r="215" spans="1:65">
       <c r="A215" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B215" t="str">
         <f t="shared" si="7"/>
@@ -23535,7 +23544,7 @@
     <row r="216" spans="1:65">
       <c r="A216" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B216" t="str">
         <f t="shared" si="7"/>
@@ -23614,7 +23623,7 @@
     <row r="217" spans="1:65">
       <c r="A217" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B217" t="str">
         <f t="shared" si="7"/>
@@ -23693,7 +23702,7 @@
     <row r="218" spans="1:65">
       <c r="A218" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B218" t="str">
         <f t="shared" si="7"/>
@@ -23772,7 +23781,7 @@
     <row r="219" spans="1:65">
       <c r="A219" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B219" t="str">
         <f t="shared" si="7"/>
@@ -23851,7 +23860,7 @@
     <row r="220" spans="1:65">
       <c r="A220" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B220" t="str">
         <f t="shared" si="7"/>
@@ -23932,7 +23941,7 @@
     <row r="221" spans="1:65">
       <c r="A221" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B221" t="str">
         <f t="shared" si="7"/>
@@ -24011,7 +24020,7 @@
     <row r="222" spans="1:65">
       <c r="A222" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B222" t="str">
         <f t="shared" si="7"/>
@@ -24090,7 +24099,7 @@
     <row r="223" spans="1:65">
       <c r="A223" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B223" t="str">
         <f t="shared" si="7"/>
@@ -24169,7 +24178,7 @@
     <row r="224" spans="1:65">
       <c r="A224" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B224" t="str">
         <f t="shared" si="7"/>
@@ -24248,7 +24257,7 @@
     <row r="225" spans="1:65">
       <c r="A225" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B225" t="str">
         <f t="shared" si="7"/>
@@ -24327,7 +24336,7 @@
     <row r="226" spans="1:65">
       <c r="A226" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B226" t="str">
         <f t="shared" si="7"/>
@@ -24406,7 +24415,7 @@
     <row r="227" spans="1:65">
       <c r="A227" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B227" t="str">
         <f t="shared" si="7"/>
@@ -24485,7 +24494,7 @@
     <row r="228" spans="1:65">
       <c r="A228" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B228" t="str">
         <f t="shared" si="7"/>
@@ -24564,7 +24573,7 @@
     <row r="229" spans="1:65">
       <c r="A229" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B229" t="str">
         <f t="shared" si="7"/>
@@ -24643,7 +24652,7 @@
     <row r="230" spans="1:65">
       <c r="A230" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B230" t="str">
         <f t="shared" si="7"/>
@@ -24722,7 +24731,7 @@
     <row r="231" spans="1:65">
       <c r="A231" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B231" t="str">
         <f t="shared" si="7"/>
@@ -24801,7 +24810,7 @@
     <row r="232" spans="1:65">
       <c r="A232" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B232" t="str">
         <f t="shared" si="7"/>
@@ -24880,7 +24889,7 @@
     <row r="233" spans="1:65">
       <c r="A233" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B233" t="str">
         <f t="shared" si="7"/>
@@ -24962,7 +24971,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B234" t="str">
         <f t="shared" ref="B234:B291" si="9">TEXT($C234, "HH:mm")</f>
@@ -25041,7 +25050,7 @@
     <row r="235" spans="1:65">
       <c r="A235" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B235" t="str">
         <f t="shared" si="9"/>
@@ -25120,7 +25129,7 @@
     <row r="236" spans="1:65">
       <c r="A236" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B236" t="str">
         <f t="shared" si="9"/>
@@ -25199,7 +25208,7 @@
     <row r="237" spans="1:65">
       <c r="A237" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B237" t="str">
         <f t="shared" si="9"/>
@@ -25278,7 +25287,7 @@
     <row r="238" spans="1:65">
       <c r="A238" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B238" t="str">
         <f t="shared" si="9"/>
@@ -25357,7 +25366,7 @@
     <row r="239" spans="1:65">
       <c r="A239" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B239" t="str">
         <f t="shared" si="9"/>
@@ -25436,7 +25445,7 @@
     <row r="240" spans="1:65">
       <c r="A240" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B240" t="str">
         <f t="shared" si="9"/>
@@ -25515,7 +25524,7 @@
     <row r="241" spans="1:65">
       <c r="A241" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B241" t="str">
         <f t="shared" si="9"/>
@@ -25594,7 +25603,7 @@
     <row r="242" spans="1:65">
       <c r="A242" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B242" t="str">
         <f t="shared" si="9"/>
@@ -25673,7 +25682,7 @@
     <row r="243" spans="1:65">
       <c r="A243" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B243" t="str">
         <f t="shared" si="9"/>
@@ -25752,7 +25761,7 @@
     <row r="244" spans="1:65">
       <c r="A244" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B244" t="str">
         <f t="shared" si="9"/>
@@ -25831,7 +25840,7 @@
     <row r="245" spans="1:65">
       <c r="A245" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B245" t="str">
         <f t="shared" si="9"/>
@@ -25910,7 +25919,7 @@
     <row r="246" spans="1:65">
       <c r="A246" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B246" t="str">
         <f t="shared" si="9"/>
@@ -25989,7 +25998,7 @@
     <row r="247" spans="1:65">
       <c r="A247" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B247" t="str">
         <f t="shared" si="9"/>
@@ -26068,7 +26077,7 @@
     <row r="248" spans="1:65">
       <c r="A248" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B248" t="str">
         <f t="shared" si="9"/>
@@ -26147,7 +26156,7 @@
     <row r="249" spans="1:65">
       <c r="A249" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B249" t="str">
         <f t="shared" si="9"/>
@@ -26226,7 +26235,7 @@
     <row r="250" spans="1:65">
       <c r="A250" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B250" t="str">
         <f t="shared" si="9"/>
@@ -26305,7 +26314,7 @@
     <row r="251" spans="1:65">
       <c r="A251" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B251" t="str">
         <f t="shared" si="9"/>
@@ -26384,7 +26393,7 @@
     <row r="252" spans="1:65">
       <c r="A252" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B252" t="str">
         <f t="shared" si="9"/>
@@ -26463,7 +26472,7 @@
     <row r="253" spans="1:65">
       <c r="A253" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B253" t="str">
         <f t="shared" si="9"/>
@@ -26542,7 +26551,7 @@
     <row r="254" spans="1:65">
       <c r="A254" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B254" t="str">
         <f t="shared" si="9"/>
@@ -26621,7 +26630,7 @@
     <row r="255" spans="1:65">
       <c r="A255" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B255" t="str">
         <f t="shared" si="9"/>
@@ -26700,7 +26709,7 @@
     <row r="256" spans="1:65">
       <c r="A256" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B256" t="str">
         <f t="shared" si="9"/>
@@ -26779,7 +26788,7 @@
     <row r="257" spans="1:65">
       <c r="A257" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B257" t="str">
         <f t="shared" si="9"/>
@@ -26858,7 +26867,7 @@
     <row r="258" spans="1:65">
       <c r="A258" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B258" t="str">
         <f t="shared" si="9"/>
@@ -26937,7 +26946,7 @@
     <row r="259" spans="1:65">
       <c r="A259" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B259" t="str">
         <f t="shared" si="9"/>
@@ -27016,7 +27025,7 @@
     <row r="260" spans="1:65">
       <c r="A260" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B260" t="str">
         <f t="shared" si="9"/>
@@ -27095,7 +27104,7 @@
     <row r="261" spans="1:65">
       <c r="A261" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B261" t="str">
         <f t="shared" si="9"/>
@@ -27174,7 +27183,7 @@
     <row r="262" spans="1:65">
       <c r="A262" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B262" t="str">
         <f t="shared" si="9"/>
@@ -27253,7 +27262,7 @@
     <row r="263" spans="1:65">
       <c r="A263" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B263" t="str">
         <f t="shared" si="9"/>
@@ -27332,7 +27341,7 @@
     <row r="264" spans="1:65">
       <c r="A264" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B264" t="str">
         <f t="shared" si="9"/>
@@ -27411,7 +27420,7 @@
     <row r="265" spans="1:65">
       <c r="A265" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B265" t="str">
         <f t="shared" si="9"/>
@@ -27490,7 +27499,7 @@
     <row r="266" spans="1:65">
       <c r="A266" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B266" t="str">
         <f t="shared" si="9"/>
@@ -27569,7 +27578,7 @@
     <row r="267" spans="1:65">
       <c r="A267" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B267" t="str">
         <f t="shared" si="9"/>
@@ -27648,7 +27657,7 @@
     <row r="268" spans="1:65">
       <c r="A268" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B268" t="str">
         <f t="shared" si="9"/>
@@ -27727,7 +27736,7 @@
     <row r="269" spans="1:65">
       <c r="A269" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B269" t="str">
         <f t="shared" si="9"/>
@@ -27806,7 +27815,7 @@
     <row r="270" spans="1:65">
       <c r="A270" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B270" t="str">
         <f t="shared" si="9"/>
@@ -27885,7 +27894,7 @@
     <row r="271" spans="1:65">
       <c r="A271" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B271" t="str">
         <f t="shared" si="9"/>
@@ -27964,7 +27973,7 @@
     <row r="272" spans="1:65">
       <c r="A272" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B272" t="str">
         <f t="shared" si="9"/>
@@ -28043,7 +28052,7 @@
     <row r="273" spans="1:65">
       <c r="A273" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B273" t="str">
         <f t="shared" si="9"/>
@@ -28122,7 +28131,7 @@
     <row r="274" spans="1:65">
       <c r="A274" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B274" t="str">
         <f t="shared" si="9"/>
@@ -28201,7 +28210,7 @@
     <row r="275" spans="1:65">
       <c r="A275" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B275" t="str">
         <f t="shared" si="9"/>
@@ -28280,7 +28289,7 @@
     <row r="276" spans="1:65">
       <c r="A276" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B276" t="str">
         <f t="shared" si="9"/>
@@ -28359,7 +28368,7 @@
     <row r="277" spans="1:65">
       <c r="A277" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B277" t="str">
         <f t="shared" si="9"/>
@@ -28438,7 +28447,7 @@
     <row r="278" spans="1:65">
       <c r="A278" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B278" t="str">
         <f t="shared" si="9"/>
@@ -28517,7 +28526,7 @@
     <row r="279" spans="1:65">
       <c r="A279" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B279" t="str">
         <f t="shared" si="9"/>
@@ -28596,7 +28605,7 @@
     <row r="280" spans="1:65">
       <c r="A280" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B280" t="str">
         <f t="shared" si="9"/>
@@ -28675,7 +28684,7 @@
     <row r="281" spans="1:65">
       <c r="A281" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B281" t="str">
         <f t="shared" si="9"/>
@@ -28754,7 +28763,7 @@
     <row r="282" spans="1:65">
       <c r="A282" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B282" t="str">
         <f t="shared" si="9"/>
@@ -28833,7 +28842,7 @@
     <row r="283" spans="1:65">
       <c r="A283" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B283" t="str">
         <f t="shared" si="9"/>
@@ -28912,7 +28921,7 @@
     <row r="284" spans="1:65">
       <c r="A284" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B284" t="str">
         <f t="shared" si="9"/>
@@ -28991,7 +29000,7 @@
     <row r="285" spans="1:65">
       <c r="A285" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B285" t="str">
         <f t="shared" si="9"/>
@@ -29070,7 +29079,7 @@
     <row r="286" spans="1:65">
       <c r="A286" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B286" t="str">
         <f t="shared" si="9"/>
@@ -29149,7 +29158,7 @@
     <row r="287" spans="1:65">
       <c r="A287" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B287" t="str">
         <f t="shared" si="9"/>
@@ -29228,7 +29237,7 @@
     <row r="288" spans="1:65">
       <c r="A288" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B288" t="str">
         <f t="shared" si="9"/>
@@ -29307,7 +29316,7 @@
     <row r="289" spans="1:65">
       <c r="A289" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B289" t="str">
         <f t="shared" si="9"/>
@@ -29386,7 +29395,7 @@
     <row r="290" spans="1:65">
       <c r="A290" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B290" t="str">
         <f t="shared" si="9"/>
@@ -29465,7 +29474,7 @@
     <row r="291" spans="1:65">
       <c r="A291" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>01:55</v>
+        <v>02:05</v>
       </c>
       <c r="B291" t="str">
         <f t="shared" si="9"/>

--- a/Vite-Vercel開発.xlsx
+++ b/Vite-Vercel開発.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2c67ec30e06f060f/work/GitHub/work-time-tracker/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{1928CA11-C4AD-40E9-B1C5-143667E830EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43CEE80F-D70D-4CBE-81AD-2823A128AD66}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{1928CA11-C4AD-40E9-B1C5-143667E830EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD0F5074-14FB-40EA-8A06-30C32E352E83}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1548" uniqueCount="925">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1549" uniqueCount="926">
   <si>
     <t>npm install -g vercel</t>
     <phoneticPr fontId="1"/>
@@ -5378,6 +5378,10 @@
   </si>
   <si>
     <t>Found 47 errors in 11 files.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Found 36 errors in 8 files.</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -6150,7 +6154,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{083174DA-A42C-4F9C-978E-61AEAAD9DDFF}">
-  <dimension ref="B2:D30"/>
+  <dimension ref="B2:D31"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
@@ -6308,6 +6312,11 @@
     <row r="30" spans="3:3">
       <c r="C30" t="s">
         <v>924</v>
+      </c>
+    </row>
+    <row r="31" spans="3:3">
+      <c r="C31" t="s">
+        <v>925</v>
       </c>
     </row>
   </sheetData>
@@ -6474,7 +6483,7 @@
       MOD(NOW(),1),
       TIME(0,5,0)
     ),"HH:mm")</f>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B2" s="19"/>
       <c r="D2" s="1">
@@ -6485,7 +6494,7 @@
     <row r="3" spans="1:65">
       <c r="A3" s="19" t="str">
         <f ca="1">TEXT(NOW(),"HH:mm")</f>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="17" t="s">
@@ -6684,7 +6693,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B4" t="str">
         <f t="shared" ref="B4:B67" si="1">TEXT($C4, "HH:mm")</f>
@@ -6763,7 +6772,7 @@
     <row r="5" spans="1:65">
       <c r="A5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B5" t="str">
         <f t="shared" si="1"/>
@@ -6842,7 +6851,7 @@
     <row r="6" spans="1:65">
       <c r="A6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B6" t="str">
         <f t="shared" si="1"/>
@@ -6921,7 +6930,7 @@
     <row r="7" spans="1:65">
       <c r="A7" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B7" t="str">
         <f t="shared" si="1"/>
@@ -7000,7 +7009,7 @@
     <row r="8" spans="1:65">
       <c r="A8" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B8" t="str">
         <f t="shared" si="1"/>
@@ -7079,7 +7088,7 @@
     <row r="9" spans="1:65">
       <c r="A9" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B9" t="str">
         <f t="shared" si="1"/>
@@ -7158,7 +7167,7 @@
     <row r="10" spans="1:65">
       <c r="A10" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B10" t="str">
         <f t="shared" si="1"/>
@@ -7237,7 +7246,7 @@
     <row r="11" spans="1:65">
       <c r="A11" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B11" t="str">
         <f t="shared" si="1"/>
@@ -7316,7 +7325,7 @@
     <row r="12" spans="1:65">
       <c r="A12" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B12" t="str">
         <f t="shared" si="1"/>
@@ -7395,7 +7404,7 @@
     <row r="13" spans="1:65">
       <c r="A13" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B13" t="str">
         <f t="shared" si="1"/>
@@ -7474,7 +7483,7 @@
     <row r="14" spans="1:65">
       <c r="A14" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B14" t="str">
         <f t="shared" si="1"/>
@@ -7553,7 +7562,7 @@
     <row r="15" spans="1:65">
       <c r="A15" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B15" t="str">
         <f t="shared" si="1"/>
@@ -7632,7 +7641,7 @@
     <row r="16" spans="1:65">
       <c r="A16" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B16" t="str">
         <f t="shared" si="1"/>
@@ -7711,7 +7720,7 @@
     <row r="17" spans="1:65">
       <c r="A17" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B17" t="str">
         <f t="shared" si="1"/>
@@ -7790,7 +7799,7 @@
     <row r="18" spans="1:65">
       <c r="A18" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B18" t="str">
         <f t="shared" si="1"/>
@@ -7869,7 +7878,7 @@
     <row r="19" spans="1:65">
       <c r="A19" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B19" t="str">
         <f t="shared" si="1"/>
@@ -7948,7 +7957,7 @@
     <row r="20" spans="1:65">
       <c r="A20" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B20" t="str">
         <f t="shared" si="1"/>
@@ -8027,7 +8036,7 @@
     <row r="21" spans="1:65">
       <c r="A21" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B21" t="str">
         <f t="shared" si="1"/>
@@ -8106,7 +8115,7 @@
     <row r="22" spans="1:65">
       <c r="A22" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B22" t="str">
         <f t="shared" si="1"/>
@@ -8185,7 +8194,7 @@
     <row r="23" spans="1:65">
       <c r="A23" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B23" t="str">
         <f t="shared" si="1"/>
@@ -8264,7 +8273,7 @@
     <row r="24" spans="1:65">
       <c r="A24" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B24" t="str">
         <f t="shared" si="1"/>
@@ -8343,7 +8352,7 @@
     <row r="25" spans="1:65">
       <c r="A25" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B25" t="str">
         <f t="shared" si="1"/>
@@ -8422,7 +8431,7 @@
     <row r="26" spans="1:65">
       <c r="A26" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B26" t="str">
         <f t="shared" si="1"/>
@@ -8501,7 +8510,7 @@
     <row r="27" spans="1:65">
       <c r="A27" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B27" t="str">
         <f t="shared" si="1"/>
@@ -8580,7 +8589,7 @@
     <row r="28" spans="1:65">
       <c r="A28" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B28" t="str">
         <f t="shared" si="1"/>
@@ -8661,7 +8670,7 @@
     <row r="29" spans="1:65">
       <c r="A29" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B29" t="str">
         <f t="shared" si="1"/>
@@ -8742,7 +8751,7 @@
     <row r="30" spans="1:65">
       <c r="A30" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B30" t="str">
         <f t="shared" si="1"/>
@@ -8823,7 +8832,7 @@
     <row r="31" spans="1:65">
       <c r="A31" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B31" t="str">
         <f t="shared" si="1"/>
@@ -8902,7 +8911,7 @@
     <row r="32" spans="1:65">
       <c r="A32" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B32" t="str">
         <f t="shared" si="1"/>
@@ -8981,7 +8990,7 @@
     <row r="33" spans="1:65">
       <c r="A33" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B33" t="str">
         <f t="shared" si="1"/>
@@ -9060,7 +9069,7 @@
     <row r="34" spans="1:65">
       <c r="A34" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B34" t="str">
         <f t="shared" si="1"/>
@@ -9141,7 +9150,7 @@
     <row r="35" spans="1:65">
       <c r="A35" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B35" t="str">
         <f t="shared" si="1"/>
@@ -9222,7 +9231,7 @@
     <row r="36" spans="1:65">
       <c r="A36" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B36" t="str">
         <f t="shared" si="1"/>
@@ -9303,7 +9312,7 @@
     <row r="37" spans="1:65">
       <c r="A37" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B37" t="str">
         <f t="shared" si="1"/>
@@ -9382,7 +9391,7 @@
     <row r="38" spans="1:65">
       <c r="A38" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B38" t="str">
         <f t="shared" si="1"/>
@@ -9461,7 +9470,7 @@
     <row r="39" spans="1:65">
       <c r="A39" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B39" t="str">
         <f t="shared" si="1"/>
@@ -9540,7 +9549,7 @@
     <row r="40" spans="1:65">
       <c r="A40" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B40" t="str">
         <f t="shared" si="1"/>
@@ -9619,7 +9628,7 @@
     <row r="41" spans="1:65">
       <c r="A41" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B41" t="str">
         <f t="shared" si="1"/>
@@ -9698,7 +9707,7 @@
     <row r="42" spans="1:65">
       <c r="A42" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B42" t="str">
         <f t="shared" si="1"/>
@@ -9779,7 +9788,7 @@
     <row r="43" spans="1:65">
       <c r="A43" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B43" t="str">
         <f t="shared" si="1"/>
@@ -9860,7 +9869,7 @@
     <row r="44" spans="1:65">
       <c r="A44" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B44" t="str">
         <f t="shared" si="1"/>
@@ -9939,7 +9948,7 @@
     <row r="45" spans="1:65">
       <c r="A45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B45" t="str">
         <f t="shared" si="1"/>
@@ -10018,7 +10027,7 @@
     <row r="46" spans="1:65">
       <c r="A46" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B46" t="str">
         <f t="shared" si="1"/>
@@ -10097,7 +10106,7 @@
     <row r="47" spans="1:65">
       <c r="A47" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B47" t="str">
         <f t="shared" si="1"/>
@@ -10176,7 +10185,7 @@
     <row r="48" spans="1:65">
       <c r="A48" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B48" t="str">
         <f t="shared" si="1"/>
@@ -10255,7 +10264,7 @@
     <row r="49" spans="1:65">
       <c r="A49" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B49" t="str">
         <f t="shared" si="1"/>
@@ -10336,7 +10345,7 @@
     <row r="50" spans="1:65">
       <c r="A50" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B50" t="str">
         <f t="shared" si="1"/>
@@ -10417,7 +10426,7 @@
     <row r="51" spans="1:65">
       <c r="A51" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B51" t="str">
         <f t="shared" si="1"/>
@@ -10496,7 +10505,7 @@
     <row r="52" spans="1:65">
       <c r="A52" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B52" t="str">
         <f t="shared" si="1"/>
@@ -10575,7 +10584,7 @@
     <row r="53" spans="1:65">
       <c r="A53" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B53" t="str">
         <f t="shared" si="1"/>
@@ -10654,7 +10663,7 @@
     <row r="54" spans="1:65">
       <c r="A54" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B54" t="str">
         <f t="shared" si="1"/>
@@ -10733,7 +10742,7 @@
     <row r="55" spans="1:65">
       <c r="A55" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B55" t="str">
         <f t="shared" si="1"/>
@@ -10812,7 +10821,7 @@
     <row r="56" spans="1:65">
       <c r="A56" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B56" t="str">
         <f t="shared" si="1"/>
@@ -10893,7 +10902,7 @@
     <row r="57" spans="1:65">
       <c r="A57" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B57" t="str">
         <f t="shared" si="1"/>
@@ -10972,7 +10981,7 @@
     <row r="58" spans="1:65">
       <c r="A58" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B58" t="str">
         <f t="shared" si="1"/>
@@ -11053,7 +11062,7 @@
     <row r="59" spans="1:65">
       <c r="A59" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B59" t="str">
         <f t="shared" si="1"/>
@@ -11132,7 +11141,7 @@
     <row r="60" spans="1:65">
       <c r="A60" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B60" t="str">
         <f t="shared" si="1"/>
@@ -11211,7 +11220,7 @@
     <row r="61" spans="1:65">
       <c r="A61" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B61" t="str">
         <f t="shared" si="1"/>
@@ -11290,7 +11299,7 @@
     <row r="62" spans="1:65">
       <c r="A62" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B62" t="str">
         <f t="shared" si="1"/>
@@ -11369,7 +11378,7 @@
     <row r="63" spans="1:65">
       <c r="A63" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B63" t="str">
         <f t="shared" si="1"/>
@@ -11448,7 +11457,7 @@
     <row r="64" spans="1:65">
       <c r="A64" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B64" t="str">
         <f t="shared" si="1"/>
@@ -11529,7 +11538,7 @@
     <row r="65" spans="1:65">
       <c r="A65" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B65" t="str">
         <f t="shared" si="1"/>
@@ -11608,7 +11617,7 @@
     <row r="66" spans="1:65">
       <c r="A66" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B66" t="str">
         <f t="shared" si="1"/>
@@ -11687,7 +11696,7 @@
     <row r="67" spans="1:65">
       <c r="A67" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B67" t="str">
         <f t="shared" si="1"/>
@@ -11769,7 +11778,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B68" t="str">
         <f t="shared" ref="B68:B131" si="3">TEXT($C68, "HH:mm")</f>
@@ -11848,7 +11857,7 @@
     <row r="69" spans="1:65">
       <c r="A69" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B69" t="str">
         <f t="shared" si="3"/>
@@ -11927,7 +11936,7 @@
     <row r="70" spans="1:65">
       <c r="A70" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B70" t="str">
         <f t="shared" si="3"/>
@@ -12006,7 +12015,7 @@
     <row r="71" spans="1:65">
       <c r="A71" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B71" t="str">
         <f t="shared" si="3"/>
@@ -12085,7 +12094,7 @@
     <row r="72" spans="1:65">
       <c r="A72" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B72" t="str">
         <f t="shared" si="3"/>
@@ -12164,7 +12173,7 @@
     <row r="73" spans="1:65">
       <c r="A73" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B73" t="str">
         <f t="shared" si="3"/>
@@ -12243,7 +12252,7 @@
     <row r="74" spans="1:65">
       <c r="A74" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B74" t="str">
         <f t="shared" si="3"/>
@@ -12322,7 +12331,7 @@
     <row r="75" spans="1:65">
       <c r="A75" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B75" t="str">
         <f t="shared" si="3"/>
@@ -12401,7 +12410,7 @@
     <row r="76" spans="1:65">
       <c r="A76" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B76" t="str">
         <f t="shared" si="3"/>
@@ -12480,7 +12489,7 @@
     <row r="77" spans="1:65">
       <c r="A77" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B77" t="str">
         <f t="shared" si="3"/>
@@ -12559,7 +12568,7 @@
     <row r="78" spans="1:65">
       <c r="A78" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B78" t="str">
         <f t="shared" si="3"/>
@@ -12638,7 +12647,7 @@
     <row r="79" spans="1:65">
       <c r="A79" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B79" t="str">
         <f t="shared" si="3"/>
@@ -12717,7 +12726,7 @@
     <row r="80" spans="1:65">
       <c r="A80" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B80" t="str">
         <f t="shared" si="3"/>
@@ -12796,7 +12805,7 @@
     <row r="81" spans="1:65">
       <c r="A81" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B81" t="str">
         <f t="shared" si="3"/>
@@ -12875,7 +12884,7 @@
     <row r="82" spans="1:65">
       <c r="A82" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B82" t="str">
         <f t="shared" si="3"/>
@@ -12954,7 +12963,7 @@
     <row r="83" spans="1:65">
       <c r="A83" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B83" t="str">
         <f t="shared" si="3"/>
@@ -13033,7 +13042,7 @@
     <row r="84" spans="1:65">
       <c r="A84" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B84" t="str">
         <f t="shared" si="3"/>
@@ -13112,7 +13121,7 @@
     <row r="85" spans="1:65">
       <c r="A85" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B85" t="str">
         <f t="shared" si="3"/>
@@ -13191,7 +13200,7 @@
     <row r="86" spans="1:65">
       <c r="A86" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B86" t="str">
         <f t="shared" si="3"/>
@@ -13270,7 +13279,7 @@
     <row r="87" spans="1:65">
       <c r="A87" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B87" t="str">
         <f t="shared" si="3"/>
@@ -13349,7 +13358,7 @@
     <row r="88" spans="1:65">
       <c r="A88" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B88" t="str">
         <f t="shared" si="3"/>
@@ -13428,7 +13437,7 @@
     <row r="89" spans="1:65">
       <c r="A89" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B89" t="str">
         <f t="shared" si="3"/>
@@ -13507,7 +13516,7 @@
     <row r="90" spans="1:65">
       <c r="A90" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B90" t="str">
         <f t="shared" si="3"/>
@@ -13586,7 +13595,7 @@
     <row r="91" spans="1:65">
       <c r="A91" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B91" t="str">
         <f t="shared" si="3"/>
@@ -13665,7 +13674,7 @@
     <row r="92" spans="1:65">
       <c r="A92" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B92" t="str">
         <f t="shared" si="3"/>
@@ -13744,7 +13753,7 @@
     <row r="93" spans="1:65">
       <c r="A93" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B93" t="str">
         <f t="shared" si="3"/>
@@ -13823,7 +13832,7 @@
     <row r="94" spans="1:65">
       <c r="A94" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B94" t="str">
         <f t="shared" si="3"/>
@@ -13902,7 +13911,7 @@
     <row r="95" spans="1:65">
       <c r="A95" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B95" t="str">
         <f t="shared" si="3"/>
@@ -13981,7 +13990,7 @@
     <row r="96" spans="1:65">
       <c r="A96" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B96" t="str">
         <f t="shared" si="3"/>
@@ -14060,7 +14069,7 @@
     <row r="97" spans="1:65">
       <c r="A97" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B97" t="str">
         <f t="shared" si="3"/>
@@ -14139,7 +14148,7 @@
     <row r="98" spans="1:65">
       <c r="A98" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B98" t="str">
         <f t="shared" si="3"/>
@@ -14218,7 +14227,7 @@
     <row r="99" spans="1:65">
       <c r="A99" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B99" t="str">
         <f t="shared" si="3"/>
@@ -14297,7 +14306,7 @@
     <row r="100" spans="1:65">
       <c r="A100" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B100" t="str">
         <f t="shared" si="3"/>
@@ -14378,7 +14387,7 @@
     <row r="101" spans="1:65">
       <c r="A101" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B101" t="str">
         <f t="shared" si="3"/>
@@ -14457,7 +14466,7 @@
     <row r="102" spans="1:65">
       <c r="A102" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B102" t="str">
         <f t="shared" si="3"/>
@@ -14536,7 +14545,7 @@
     <row r="103" spans="1:65">
       <c r="A103" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B103" t="str">
         <f t="shared" si="3"/>
@@ -14615,7 +14624,7 @@
     <row r="104" spans="1:65">
       <c r="A104" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B104" t="str">
         <f t="shared" si="3"/>
@@ -14694,7 +14703,7 @@
     <row r="105" spans="1:65">
       <c r="A105" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B105" t="str">
         <f t="shared" si="3"/>
@@ -14773,7 +14782,7 @@
     <row r="106" spans="1:65">
       <c r="A106" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B106" t="str">
         <f t="shared" si="3"/>
@@ -14854,7 +14863,7 @@
     <row r="107" spans="1:65">
       <c r="A107" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B107" t="str">
         <f t="shared" si="3"/>
@@ -14935,7 +14944,7 @@
     <row r="108" spans="1:65">
       <c r="A108" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B108" t="str">
         <f t="shared" si="3"/>
@@ -15014,7 +15023,7 @@
     <row r="109" spans="1:65">
       <c r="A109" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B109" t="str">
         <f t="shared" si="3"/>
@@ -15093,7 +15102,7 @@
     <row r="110" spans="1:65">
       <c r="A110" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B110" t="str">
         <f t="shared" si="3"/>
@@ -15172,7 +15181,7 @@
     <row r="111" spans="1:65">
       <c r="A111" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B111" t="str">
         <f t="shared" si="3"/>
@@ -15251,7 +15260,7 @@
     <row r="112" spans="1:65">
       <c r="A112" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B112" t="str">
         <f t="shared" si="3"/>
@@ -15332,7 +15341,7 @@
     <row r="113" spans="1:65">
       <c r="A113" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B113" t="str">
         <f t="shared" si="3"/>
@@ -15411,7 +15420,7 @@
     <row r="114" spans="1:65">
       <c r="A114" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B114" t="str">
         <f t="shared" si="3"/>
@@ -15490,7 +15499,7 @@
     <row r="115" spans="1:65">
       <c r="A115" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B115" t="str">
         <f t="shared" si="3"/>
@@ -15569,7 +15578,7 @@
     <row r="116" spans="1:65">
       <c r="A116" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B116" t="str">
         <f t="shared" si="3"/>
@@ -15648,7 +15657,7 @@
     <row r="117" spans="1:65">
       <c r="A117" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B117" t="str">
         <f t="shared" si="3"/>
@@ -15727,7 +15736,7 @@
     <row r="118" spans="1:65">
       <c r="A118" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B118" t="str">
         <f t="shared" si="3"/>
@@ -15806,7 +15815,7 @@
     <row r="119" spans="1:65">
       <c r="A119" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B119" t="str">
         <f t="shared" si="3"/>
@@ -15885,7 +15894,7 @@
     <row r="120" spans="1:65">
       <c r="A120" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B120" t="str">
         <f t="shared" si="3"/>
@@ -15964,7 +15973,7 @@
     <row r="121" spans="1:65">
       <c r="A121" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B121" t="str">
         <f t="shared" si="3"/>
@@ -16043,7 +16052,7 @@
     <row r="122" spans="1:65">
       <c r="A122" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B122" t="str">
         <f t="shared" si="3"/>
@@ -16122,7 +16131,7 @@
     <row r="123" spans="1:65">
       <c r="A123" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B123" t="str">
         <f t="shared" si="3"/>
@@ -16201,7 +16210,7 @@
     <row r="124" spans="1:65">
       <c r="A124" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B124" t="str">
         <f t="shared" si="3"/>
@@ -16282,7 +16291,7 @@
     <row r="125" spans="1:65">
       <c r="A125" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B125" t="str">
         <f t="shared" si="3"/>
@@ -16363,7 +16372,7 @@
     <row r="126" spans="1:65">
       <c r="A126" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B126" t="str">
         <f t="shared" si="3"/>
@@ -16442,7 +16451,7 @@
     <row r="127" spans="1:65">
       <c r="A127" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B127" t="str">
         <f t="shared" si="3"/>
@@ -16521,7 +16530,7 @@
     <row r="128" spans="1:65">
       <c r="A128" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B128" t="str">
         <f t="shared" si="3"/>
@@ -16600,7 +16609,7 @@
     <row r="129" spans="1:65">
       <c r="A129" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B129" t="str">
         <f t="shared" si="3"/>
@@ -16679,7 +16688,7 @@
     <row r="130" spans="1:65">
       <c r="A130" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B130" t="str">
         <f t="shared" si="3"/>
@@ -16758,7 +16767,7 @@
     <row r="131" spans="1:65">
       <c r="A131" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B131" t="str">
         <f t="shared" si="3"/>
@@ -16840,7 +16849,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B132" t="str">
         <f t="shared" ref="B132:B168" si="5">TEXT($C132, "HH:mm")</f>
@@ -16919,7 +16928,7 @@
     <row r="133" spans="1:65">
       <c r="A133" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B133" t="str">
         <f t="shared" si="5"/>
@@ -16998,7 +17007,7 @@
     <row r="134" spans="1:65">
       <c r="A134" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B134" t="str">
         <f t="shared" si="5"/>
@@ -17077,7 +17086,7 @@
     <row r="135" spans="1:65">
       <c r="A135" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B135" t="str">
         <f t="shared" si="5"/>
@@ -17156,7 +17165,7 @@
     <row r="136" spans="1:65">
       <c r="A136" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B136" t="str">
         <f t="shared" si="5"/>
@@ -17237,7 +17246,7 @@
     <row r="137" spans="1:65">
       <c r="A137" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B137" t="str">
         <f t="shared" si="5"/>
@@ -17318,7 +17327,7 @@
     <row r="138" spans="1:65">
       <c r="A138" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B138" t="str">
         <f t="shared" si="5"/>
@@ -17397,7 +17406,7 @@
     <row r="139" spans="1:65">
       <c r="A139" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B139" t="str">
         <f t="shared" si="5"/>
@@ -17476,7 +17485,7 @@
     <row r="140" spans="1:65">
       <c r="A140" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B140" t="str">
         <f t="shared" si="5"/>
@@ -17555,7 +17564,7 @@
     <row r="141" spans="1:65">
       <c r="A141" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B141" t="str">
         <f t="shared" si="5"/>
@@ -17634,7 +17643,7 @@
     <row r="142" spans="1:65">
       <c r="A142" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B142" t="str">
         <f t="shared" si="5"/>
@@ -17713,7 +17722,7 @@
     <row r="143" spans="1:65">
       <c r="A143" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B143" t="str">
         <f t="shared" si="5"/>
@@ -17792,7 +17801,7 @@
     <row r="144" spans="1:65">
       <c r="A144" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B144" t="str">
         <f t="shared" si="5"/>
@@ -17871,7 +17880,7 @@
     <row r="145" spans="1:65">
       <c r="A145" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B145" t="str">
         <f t="shared" si="5"/>
@@ -17950,7 +17959,7 @@
     <row r="146" spans="1:65">
       <c r="A146" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B146" t="str">
         <f t="shared" si="5"/>
@@ -18029,7 +18038,7 @@
     <row r="147" spans="1:65">
       <c r="A147" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B147" t="str">
         <f t="shared" si="5"/>
@@ -18108,7 +18117,7 @@
     <row r="148" spans="1:65">
       <c r="A148" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B148" t="str">
         <f t="shared" si="5"/>
@@ -18189,7 +18198,7 @@
     <row r="149" spans="1:65">
       <c r="A149" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B149" t="str">
         <f t="shared" si="5"/>
@@ -18268,7 +18277,7 @@
     <row r="150" spans="1:65">
       <c r="A150" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B150" t="str">
         <f t="shared" si="5"/>
@@ -18347,7 +18356,7 @@
     <row r="151" spans="1:65">
       <c r="A151" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B151" t="str">
         <f t="shared" si="5"/>
@@ -18426,7 +18435,7 @@
     <row r="152" spans="1:65">
       <c r="A152" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B152" t="str">
         <f t="shared" si="5"/>
@@ -18505,7 +18514,7 @@
     <row r="153" spans="1:65">
       <c r="A153" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B153" t="str">
         <f t="shared" si="5"/>
@@ -18584,7 +18593,7 @@
     <row r="154" spans="1:65">
       <c r="A154" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B154" t="str">
         <f t="shared" si="5"/>
@@ -18663,7 +18672,7 @@
     <row r="155" spans="1:65">
       <c r="A155" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B155" t="str">
         <f t="shared" si="5"/>
@@ -18742,7 +18751,7 @@
     <row r="156" spans="1:65">
       <c r="A156" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B156" t="str">
         <f t="shared" si="5"/>
@@ -18821,7 +18830,7 @@
     <row r="157" spans="1:65">
       <c r="A157" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B157" t="str">
         <f t="shared" si="5"/>
@@ -18900,7 +18909,7 @@
     <row r="158" spans="1:65">
       <c r="A158" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B158" t="str">
         <f t="shared" si="5"/>
@@ -18979,7 +18988,7 @@
     <row r="159" spans="1:65">
       <c r="A159" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B159" t="str">
         <f t="shared" si="5"/>
@@ -19058,7 +19067,7 @@
     <row r="160" spans="1:65">
       <c r="A160" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B160" t="str">
         <f t="shared" si="5"/>
@@ -19137,7 +19146,7 @@
     <row r="161" spans="1:65">
       <c r="A161" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B161" t="str">
         <f t="shared" si="5"/>
@@ -19216,7 +19225,7 @@
     <row r="162" spans="1:65">
       <c r="A162" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B162" t="str">
         <f t="shared" si="5"/>
@@ -19295,7 +19304,7 @@
     <row r="163" spans="1:65">
       <c r="A163" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B163" t="str">
         <f t="shared" si="5"/>
@@ -19374,7 +19383,7 @@
     <row r="164" spans="1:65">
       <c r="A164" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B164" t="str">
         <f t="shared" si="5"/>
@@ -19453,7 +19462,7 @@
     <row r="165" spans="1:65">
       <c r="A165" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B165" t="str">
         <f t="shared" si="5"/>
@@ -19532,7 +19541,7 @@
     <row r="166" spans="1:65">
       <c r="A166" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B166" t="str">
         <f t="shared" si="5"/>
@@ -19613,7 +19622,7 @@
     <row r="167" spans="1:65">
       <c r="A167" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B167" t="str">
         <f t="shared" si="5"/>
@@ -19692,7 +19701,7 @@
     <row r="168" spans="1:65">
       <c r="A168" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B168" t="str">
         <f t="shared" si="5"/>
@@ -19774,7 +19783,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B169" t="str">
         <f>TEXT($C169, "HH:mm")</f>
@@ -19856,7 +19865,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B170" t="str">
         <f t="shared" ref="B170:B233" si="7">TEXT($C170, "HH:mm")</f>
@@ -19935,7 +19944,7 @@
     <row r="171" spans="1:65">
       <c r="A171" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B171" t="str">
         <f t="shared" si="7"/>
@@ -20014,7 +20023,7 @@
     <row r="172" spans="1:65">
       <c r="A172" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B172" t="str">
         <f t="shared" si="7"/>
@@ -20095,7 +20104,7 @@
     <row r="173" spans="1:65">
       <c r="A173" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B173" t="str">
         <f t="shared" si="7"/>
@@ -20174,7 +20183,7 @@
     <row r="174" spans="1:65">
       <c r="A174" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B174" t="str">
         <f t="shared" si="7"/>
@@ -20253,7 +20262,7 @@
     <row r="175" spans="1:65">
       <c r="A175" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B175" t="str">
         <f t="shared" si="7"/>
@@ -20332,7 +20341,7 @@
     <row r="176" spans="1:65">
       <c r="A176" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B176" t="str">
         <f t="shared" si="7"/>
@@ -20411,7 +20420,7 @@
     <row r="177" spans="1:65">
       <c r="A177" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B177" t="str">
         <f t="shared" si="7"/>
@@ -20490,7 +20499,7 @@
     <row r="178" spans="1:65">
       <c r="A178" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B178" t="str">
         <f t="shared" si="7"/>
@@ -20571,7 +20580,7 @@
     <row r="179" spans="1:65">
       <c r="A179" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B179" t="str">
         <f t="shared" si="7"/>
@@ -20650,7 +20659,7 @@
     <row r="180" spans="1:65">
       <c r="A180" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B180" t="str">
         <f t="shared" si="7"/>
@@ -20729,7 +20738,7 @@
     <row r="181" spans="1:65">
       <c r="A181" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B181" t="str">
         <f t="shared" si="7"/>
@@ -20810,7 +20819,7 @@
     <row r="182" spans="1:65">
       <c r="A182" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B182" t="str">
         <f t="shared" si="7"/>
@@ -20891,7 +20900,7 @@
     <row r="183" spans="1:65">
       <c r="A183" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B183" t="str">
         <f t="shared" si="7"/>
@@ -20972,7 +20981,7 @@
     <row r="184" spans="1:65">
       <c r="A184" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B184" t="str">
         <f t="shared" si="7"/>
@@ -21055,7 +21064,7 @@
     <row r="185" spans="1:65">
       <c r="A185" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B185" t="str">
         <f t="shared" si="7"/>
@@ -21136,7 +21145,7 @@
     <row r="186" spans="1:65">
       <c r="A186" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B186" t="str">
         <f t="shared" si="7"/>
@@ -21217,7 +21226,7 @@
     <row r="187" spans="1:65">
       <c r="A187" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B187" t="str">
         <f t="shared" si="7"/>
@@ -21298,7 +21307,7 @@
     <row r="188" spans="1:65">
       <c r="A188" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B188" t="str">
         <f t="shared" si="7"/>
@@ -21379,7 +21388,7 @@
     <row r="189" spans="1:65">
       <c r="A189" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B189" t="str">
         <f t="shared" si="7"/>
@@ -21460,7 +21469,7 @@
     <row r="190" spans="1:65">
       <c r="A190" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B190" t="str">
         <f t="shared" si="7"/>
@@ -21543,7 +21552,7 @@
     <row r="191" spans="1:65">
       <c r="A191" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B191" t="str">
         <f t="shared" si="7"/>
@@ -21626,7 +21635,7 @@
     <row r="192" spans="1:65">
       <c r="A192" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B192" t="str">
         <f t="shared" si="7"/>
@@ -21709,7 +21718,7 @@
     <row r="193" spans="1:65">
       <c r="A193" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B193" t="str">
         <f t="shared" si="7"/>
@@ -21792,7 +21801,7 @@
     <row r="194" spans="1:65">
       <c r="A194" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B194" t="str">
         <f t="shared" si="7"/>
@@ -21873,7 +21882,7 @@
     <row r="195" spans="1:65">
       <c r="A195" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B195" t="str">
         <f t="shared" si="7"/>
@@ -21954,7 +21963,7 @@
     <row r="196" spans="1:65">
       <c r="A196" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B196" t="str">
         <f t="shared" si="7"/>
@@ -22037,7 +22046,7 @@
     <row r="197" spans="1:65">
       <c r="A197" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B197" t="str">
         <f t="shared" si="7"/>
@@ -22116,7 +22125,7 @@
     <row r="198" spans="1:65">
       <c r="A198" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B198" t="str">
         <f t="shared" si="7"/>
@@ -22195,7 +22204,7 @@
     <row r="199" spans="1:65">
       <c r="A199" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B199" t="str">
         <f t="shared" si="7"/>
@@ -22274,7 +22283,7 @@
     <row r="200" spans="1:65">
       <c r="A200" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B200" t="str">
         <f t="shared" si="7"/>
@@ -22353,7 +22362,7 @@
     <row r="201" spans="1:65">
       <c r="A201" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B201" t="str">
         <f t="shared" si="7"/>
@@ -22432,7 +22441,7 @@
     <row r="202" spans="1:65">
       <c r="A202" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B202" t="str">
         <f t="shared" si="7"/>
@@ -22513,7 +22522,7 @@
     <row r="203" spans="1:65">
       <c r="A203" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B203" t="str">
         <f t="shared" si="7"/>
@@ -22592,7 +22601,7 @@
     <row r="204" spans="1:65">
       <c r="A204" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B204" t="str">
         <f t="shared" si="7"/>
@@ -22671,7 +22680,7 @@
     <row r="205" spans="1:65">
       <c r="A205" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B205" t="str">
         <f t="shared" si="7"/>
@@ -22750,7 +22759,7 @@
     <row r="206" spans="1:65">
       <c r="A206" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B206" t="str">
         <f t="shared" si="7"/>
@@ -22829,7 +22838,7 @@
     <row r="207" spans="1:65">
       <c r="A207" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B207" t="str">
         <f t="shared" si="7"/>
@@ -22908,7 +22917,7 @@
     <row r="208" spans="1:65">
       <c r="A208" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B208" t="str">
         <f t="shared" si="7"/>
@@ -22989,7 +22998,7 @@
     <row r="209" spans="1:65">
       <c r="A209" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B209" t="str">
         <f t="shared" si="7"/>
@@ -23068,7 +23077,7 @@
     <row r="210" spans="1:65">
       <c r="A210" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B210" t="str">
         <f t="shared" si="7"/>
@@ -23147,7 +23156,7 @@
     <row r="211" spans="1:65">
       <c r="A211" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B211" t="str">
         <f t="shared" si="7"/>
@@ -23228,7 +23237,7 @@
     <row r="212" spans="1:65">
       <c r="A212" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B212" t="str">
         <f t="shared" si="7"/>
@@ -23307,7 +23316,7 @@
     <row r="213" spans="1:65">
       <c r="A213" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B213" t="str">
         <f t="shared" si="7"/>
@@ -23386,7 +23395,7 @@
     <row r="214" spans="1:65">
       <c r="A214" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B214" t="str">
         <f t="shared" si="7"/>
@@ -23465,7 +23474,7 @@
     <row r="215" spans="1:65">
       <c r="A215" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B215" t="str">
         <f t="shared" si="7"/>
@@ -23544,7 +23553,7 @@
     <row r="216" spans="1:65">
       <c r="A216" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B216" t="str">
         <f t="shared" si="7"/>
@@ -23623,7 +23632,7 @@
     <row r="217" spans="1:65">
       <c r="A217" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B217" t="str">
         <f t="shared" si="7"/>
@@ -23702,7 +23711,7 @@
     <row r="218" spans="1:65">
       <c r="A218" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B218" t="str">
         <f t="shared" si="7"/>
@@ -23781,7 +23790,7 @@
     <row r="219" spans="1:65">
       <c r="A219" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B219" t="str">
         <f t="shared" si="7"/>
@@ -23860,7 +23869,7 @@
     <row r="220" spans="1:65">
       <c r="A220" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B220" t="str">
         <f t="shared" si="7"/>
@@ -23941,7 +23950,7 @@
     <row r="221" spans="1:65">
       <c r="A221" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B221" t="str">
         <f t="shared" si="7"/>
@@ -24020,7 +24029,7 @@
     <row r="222" spans="1:65">
       <c r="A222" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B222" t="str">
         <f t="shared" si="7"/>
@@ -24099,7 +24108,7 @@
     <row r="223" spans="1:65">
       <c r="A223" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B223" t="str">
         <f t="shared" si="7"/>
@@ -24178,7 +24187,7 @@
     <row r="224" spans="1:65">
       <c r="A224" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B224" t="str">
         <f t="shared" si="7"/>
@@ -24257,7 +24266,7 @@
     <row r="225" spans="1:65">
       <c r="A225" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B225" t="str">
         <f t="shared" si="7"/>
@@ -24336,7 +24345,7 @@
     <row r="226" spans="1:65">
       <c r="A226" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B226" t="str">
         <f t="shared" si="7"/>
@@ -24415,7 +24424,7 @@
     <row r="227" spans="1:65">
       <c r="A227" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B227" t="str">
         <f t="shared" si="7"/>
@@ -24494,7 +24503,7 @@
     <row r="228" spans="1:65">
       <c r="A228" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B228" t="str">
         <f t="shared" si="7"/>
@@ -24573,7 +24582,7 @@
     <row r="229" spans="1:65">
       <c r="A229" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B229" t="str">
         <f t="shared" si="7"/>
@@ -24652,7 +24661,7 @@
     <row r="230" spans="1:65">
       <c r="A230" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B230" t="str">
         <f t="shared" si="7"/>
@@ -24731,7 +24740,7 @@
     <row r="231" spans="1:65">
       <c r="A231" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B231" t="str">
         <f t="shared" si="7"/>
@@ -24810,7 +24819,7 @@
     <row r="232" spans="1:65">
       <c r="A232" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B232" t="str">
         <f t="shared" si="7"/>
@@ -24889,7 +24898,7 @@
     <row r="233" spans="1:65">
       <c r="A233" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B233" t="str">
         <f t="shared" si="7"/>
@@ -24971,7 +24980,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B234" t="str">
         <f t="shared" ref="B234:B291" si="9">TEXT($C234, "HH:mm")</f>
@@ -25050,7 +25059,7 @@
     <row r="235" spans="1:65">
       <c r="A235" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B235" t="str">
         <f t="shared" si="9"/>
@@ -25129,7 +25138,7 @@
     <row r="236" spans="1:65">
       <c r="A236" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B236" t="str">
         <f t="shared" si="9"/>
@@ -25208,7 +25217,7 @@
     <row r="237" spans="1:65">
       <c r="A237" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B237" t="str">
         <f t="shared" si="9"/>
@@ -25287,7 +25296,7 @@
     <row r="238" spans="1:65">
       <c r="A238" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B238" t="str">
         <f t="shared" si="9"/>
@@ -25366,7 +25375,7 @@
     <row r="239" spans="1:65">
       <c r="A239" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B239" t="str">
         <f t="shared" si="9"/>
@@ -25445,7 +25454,7 @@
     <row r="240" spans="1:65">
       <c r="A240" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B240" t="str">
         <f t="shared" si="9"/>
@@ -25524,7 +25533,7 @@
     <row r="241" spans="1:65">
       <c r="A241" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B241" t="str">
         <f t="shared" si="9"/>
@@ -25603,7 +25612,7 @@
     <row r="242" spans="1:65">
       <c r="A242" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B242" t="str">
         <f t="shared" si="9"/>
@@ -25682,7 +25691,7 @@
     <row r="243" spans="1:65">
       <c r="A243" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B243" t="str">
         <f t="shared" si="9"/>
@@ -25761,7 +25770,7 @@
     <row r="244" spans="1:65">
       <c r="A244" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B244" t="str">
         <f t="shared" si="9"/>
@@ -25840,7 +25849,7 @@
     <row r="245" spans="1:65">
       <c r="A245" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B245" t="str">
         <f t="shared" si="9"/>
@@ -25919,7 +25928,7 @@
     <row r="246" spans="1:65">
       <c r="A246" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B246" t="str">
         <f t="shared" si="9"/>
@@ -25998,7 +26007,7 @@
     <row r="247" spans="1:65">
       <c r="A247" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B247" t="str">
         <f t="shared" si="9"/>
@@ -26077,7 +26086,7 @@
     <row r="248" spans="1:65">
       <c r="A248" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B248" t="str">
         <f t="shared" si="9"/>
@@ -26156,7 +26165,7 @@
     <row r="249" spans="1:65">
       <c r="A249" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B249" t="str">
         <f t="shared" si="9"/>
@@ -26235,7 +26244,7 @@
     <row r="250" spans="1:65">
       <c r="A250" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B250" t="str">
         <f t="shared" si="9"/>
@@ -26314,7 +26323,7 @@
     <row r="251" spans="1:65">
       <c r="A251" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B251" t="str">
         <f t="shared" si="9"/>
@@ -26393,7 +26402,7 @@
     <row r="252" spans="1:65">
       <c r="A252" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B252" t="str">
         <f t="shared" si="9"/>
@@ -26472,7 +26481,7 @@
     <row r="253" spans="1:65">
       <c r="A253" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B253" t="str">
         <f t="shared" si="9"/>
@@ -26551,7 +26560,7 @@
     <row r="254" spans="1:65">
       <c r="A254" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B254" t="str">
         <f t="shared" si="9"/>
@@ -26630,7 +26639,7 @@
     <row r="255" spans="1:65">
       <c r="A255" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B255" t="str">
         <f t="shared" si="9"/>
@@ -26709,7 +26718,7 @@
     <row r="256" spans="1:65">
       <c r="A256" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B256" t="str">
         <f t="shared" si="9"/>
@@ -26788,7 +26797,7 @@
     <row r="257" spans="1:65">
       <c r="A257" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B257" t="str">
         <f t="shared" si="9"/>
@@ -26867,7 +26876,7 @@
     <row r="258" spans="1:65">
       <c r="A258" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B258" t="str">
         <f t="shared" si="9"/>
@@ -26946,7 +26955,7 @@
     <row r="259" spans="1:65">
       <c r="A259" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B259" t="str">
         <f t="shared" si="9"/>
@@ -27025,7 +27034,7 @@
     <row r="260" spans="1:65">
       <c r="A260" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B260" t="str">
         <f t="shared" si="9"/>
@@ -27104,7 +27113,7 @@
     <row r="261" spans="1:65">
       <c r="A261" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B261" t="str">
         <f t="shared" si="9"/>
@@ -27183,7 +27192,7 @@
     <row r="262" spans="1:65">
       <c r="A262" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B262" t="str">
         <f t="shared" si="9"/>
@@ -27262,7 +27271,7 @@
     <row r="263" spans="1:65">
       <c r="A263" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B263" t="str">
         <f t="shared" si="9"/>
@@ -27341,7 +27350,7 @@
     <row r="264" spans="1:65">
       <c r="A264" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B264" t="str">
         <f t="shared" si="9"/>
@@ -27420,7 +27429,7 @@
     <row r="265" spans="1:65">
       <c r="A265" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B265" t="str">
         <f t="shared" si="9"/>
@@ -27499,7 +27508,7 @@
     <row r="266" spans="1:65">
       <c r="A266" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B266" t="str">
         <f t="shared" si="9"/>
@@ -27578,7 +27587,7 @@
     <row r="267" spans="1:65">
       <c r="A267" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B267" t="str">
         <f t="shared" si="9"/>
@@ -27657,7 +27666,7 @@
     <row r="268" spans="1:65">
       <c r="A268" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B268" t="str">
         <f t="shared" si="9"/>
@@ -27736,7 +27745,7 @@
     <row r="269" spans="1:65">
       <c r="A269" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B269" t="str">
         <f t="shared" si="9"/>
@@ -27815,7 +27824,7 @@
     <row r="270" spans="1:65">
       <c r="A270" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B270" t="str">
         <f t="shared" si="9"/>
@@ -27894,7 +27903,7 @@
     <row r="271" spans="1:65">
       <c r="A271" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B271" t="str">
         <f t="shared" si="9"/>
@@ -27973,7 +27982,7 @@
     <row r="272" spans="1:65">
       <c r="A272" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B272" t="str">
         <f t="shared" si="9"/>
@@ -28052,7 +28061,7 @@
     <row r="273" spans="1:65">
       <c r="A273" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B273" t="str">
         <f t="shared" si="9"/>
@@ -28131,7 +28140,7 @@
     <row r="274" spans="1:65">
       <c r="A274" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B274" t="str">
         <f t="shared" si="9"/>
@@ -28210,7 +28219,7 @@
     <row r="275" spans="1:65">
       <c r="A275" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B275" t="str">
         <f t="shared" si="9"/>
@@ -28289,7 +28298,7 @@
     <row r="276" spans="1:65">
       <c r="A276" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B276" t="str">
         <f t="shared" si="9"/>
@@ -28368,7 +28377,7 @@
     <row r="277" spans="1:65">
       <c r="A277" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B277" t="str">
         <f t="shared" si="9"/>
@@ -28447,7 +28456,7 @@
     <row r="278" spans="1:65">
       <c r="A278" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B278" t="str">
         <f t="shared" si="9"/>
@@ -28526,7 +28535,7 @@
     <row r="279" spans="1:65">
       <c r="A279" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B279" t="str">
         <f t="shared" si="9"/>
@@ -28605,7 +28614,7 @@
     <row r="280" spans="1:65">
       <c r="A280" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B280" t="str">
         <f t="shared" si="9"/>
@@ -28684,7 +28693,7 @@
     <row r="281" spans="1:65">
       <c r="A281" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B281" t="str">
         <f t="shared" si="9"/>
@@ -28763,7 +28772,7 @@
     <row r="282" spans="1:65">
       <c r="A282" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B282" t="str">
         <f t="shared" si="9"/>
@@ -28842,7 +28851,7 @@
     <row r="283" spans="1:65">
       <c r="A283" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B283" t="str">
         <f t="shared" si="9"/>
@@ -28921,7 +28930,7 @@
     <row r="284" spans="1:65">
       <c r="A284" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B284" t="str">
         <f t="shared" si="9"/>
@@ -29000,7 +29009,7 @@
     <row r="285" spans="1:65">
       <c r="A285" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B285" t="str">
         <f t="shared" si="9"/>
@@ -29079,7 +29088,7 @@
     <row r="286" spans="1:65">
       <c r="A286" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B286" t="str">
         <f t="shared" si="9"/>
@@ -29158,7 +29167,7 @@
     <row r="287" spans="1:65">
       <c r="A287" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B287" t="str">
         <f t="shared" si="9"/>
@@ -29237,7 +29246,7 @@
     <row r="288" spans="1:65">
       <c r="A288" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B288" t="str">
         <f t="shared" si="9"/>
@@ -29316,7 +29325,7 @@
     <row r="289" spans="1:65">
       <c r="A289" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B289" t="str">
         <f t="shared" si="9"/>
@@ -29395,7 +29404,7 @@
     <row r="290" spans="1:65">
       <c r="A290" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B290" t="str">
         <f t="shared" si="9"/>
@@ -29474,7 +29483,7 @@
     <row r="291" spans="1:65">
       <c r="A291" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:05</v>
+        <v>02:10</v>
       </c>
       <c r="B291" t="str">
         <f t="shared" si="9"/>

--- a/Vite-Vercel開発.xlsx
+++ b/Vite-Vercel開発.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2c67ec30e06f060f/work/GitHub/work-time-tracker/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{1928CA11-C4AD-40E9-B1C5-143667E830EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD0F5074-14FB-40EA-8A06-30C32E352E83}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{1928CA11-C4AD-40E9-B1C5-143667E830EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09F1C063-48DE-46FA-82A3-7B9297622148}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1549" uniqueCount="926">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1550" uniqueCount="927">
   <si>
     <t>npm install -g vercel</t>
     <phoneticPr fontId="1"/>
@@ -5382,6 +5382,10 @@
   </si>
   <si>
     <t>Found 36 errors in 8 files.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Found 34 errors in 9 files.</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -6154,7 +6158,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{083174DA-A42C-4F9C-978E-61AEAAD9DDFF}">
-  <dimension ref="B2:D31"/>
+  <dimension ref="B2:D32"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
@@ -6317,6 +6321,11 @@
     <row r="31" spans="3:3">
       <c r="C31" t="s">
         <v>925</v>
+      </c>
+    </row>
+    <row r="32" spans="3:3">
+      <c r="C32" t="s">
+        <v>926</v>
       </c>
     </row>
   </sheetData>
@@ -6483,7 +6492,7 @@
       MOD(NOW(),1),
       TIME(0,5,0)
     ),"HH:mm")</f>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B2" s="19"/>
       <c r="D2" s="1">
@@ -6494,7 +6503,7 @@
     <row r="3" spans="1:65">
       <c r="A3" s="19" t="str">
         <f ca="1">TEXT(NOW(),"HH:mm")</f>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="17" t="s">
@@ -6693,7 +6702,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B4" t="str">
         <f t="shared" ref="B4:B67" si="1">TEXT($C4, "HH:mm")</f>
@@ -6772,7 +6781,7 @@
     <row r="5" spans="1:65">
       <c r="A5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B5" t="str">
         <f t="shared" si="1"/>
@@ -6851,7 +6860,7 @@
     <row r="6" spans="1:65">
       <c r="A6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B6" t="str">
         <f t="shared" si="1"/>
@@ -6930,7 +6939,7 @@
     <row r="7" spans="1:65">
       <c r="A7" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B7" t="str">
         <f t="shared" si="1"/>
@@ -7009,7 +7018,7 @@
     <row r="8" spans="1:65">
       <c r="A8" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B8" t="str">
         <f t="shared" si="1"/>
@@ -7088,7 +7097,7 @@
     <row r="9" spans="1:65">
       <c r="A9" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B9" t="str">
         <f t="shared" si="1"/>
@@ -7167,7 +7176,7 @@
     <row r="10" spans="1:65">
       <c r="A10" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B10" t="str">
         <f t="shared" si="1"/>
@@ -7246,7 +7255,7 @@
     <row r="11" spans="1:65">
       <c r="A11" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B11" t="str">
         <f t="shared" si="1"/>
@@ -7325,7 +7334,7 @@
     <row r="12" spans="1:65">
       <c r="A12" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B12" t="str">
         <f t="shared" si="1"/>
@@ -7404,7 +7413,7 @@
     <row r="13" spans="1:65">
       <c r="A13" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B13" t="str">
         <f t="shared" si="1"/>
@@ -7483,7 +7492,7 @@
     <row r="14" spans="1:65">
       <c r="A14" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B14" t="str">
         <f t="shared" si="1"/>
@@ -7562,7 +7571,7 @@
     <row r="15" spans="1:65">
       <c r="A15" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B15" t="str">
         <f t="shared" si="1"/>
@@ -7641,7 +7650,7 @@
     <row r="16" spans="1:65">
       <c r="A16" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B16" t="str">
         <f t="shared" si="1"/>
@@ -7720,7 +7729,7 @@
     <row r="17" spans="1:65">
       <c r="A17" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B17" t="str">
         <f t="shared" si="1"/>
@@ -7799,7 +7808,7 @@
     <row r="18" spans="1:65">
       <c r="A18" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B18" t="str">
         <f t="shared" si="1"/>
@@ -7878,7 +7887,7 @@
     <row r="19" spans="1:65">
       <c r="A19" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B19" t="str">
         <f t="shared" si="1"/>
@@ -7957,7 +7966,7 @@
     <row r="20" spans="1:65">
       <c r="A20" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B20" t="str">
         <f t="shared" si="1"/>
@@ -8036,7 +8045,7 @@
     <row r="21" spans="1:65">
       <c r="A21" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B21" t="str">
         <f t="shared" si="1"/>
@@ -8115,7 +8124,7 @@
     <row r="22" spans="1:65">
       <c r="A22" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B22" t="str">
         <f t="shared" si="1"/>
@@ -8194,7 +8203,7 @@
     <row r="23" spans="1:65">
       <c r="A23" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B23" t="str">
         <f t="shared" si="1"/>
@@ -8273,7 +8282,7 @@
     <row r="24" spans="1:65">
       <c r="A24" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B24" t="str">
         <f t="shared" si="1"/>
@@ -8352,7 +8361,7 @@
     <row r="25" spans="1:65">
       <c r="A25" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B25" t="str">
         <f t="shared" si="1"/>
@@ -8431,7 +8440,7 @@
     <row r="26" spans="1:65">
       <c r="A26" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B26" t="str">
         <f t="shared" si="1"/>
@@ -8510,7 +8519,7 @@
     <row r="27" spans="1:65">
       <c r="A27" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B27" t="str">
         <f t="shared" si="1"/>
@@ -8589,7 +8598,7 @@
     <row r="28" spans="1:65">
       <c r="A28" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B28" t="str">
         <f t="shared" si="1"/>
@@ -8670,7 +8679,7 @@
     <row r="29" spans="1:65">
       <c r="A29" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B29" t="str">
         <f t="shared" si="1"/>
@@ -8751,7 +8760,7 @@
     <row r="30" spans="1:65">
       <c r="A30" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B30" t="str">
         <f t="shared" si="1"/>
@@ -8832,7 +8841,7 @@
     <row r="31" spans="1:65">
       <c r="A31" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B31" t="str">
         <f t="shared" si="1"/>
@@ -8911,7 +8920,7 @@
     <row r="32" spans="1:65">
       <c r="A32" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B32" t="str">
         <f t="shared" si="1"/>
@@ -8990,7 +8999,7 @@
     <row r="33" spans="1:65">
       <c r="A33" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B33" t="str">
         <f t="shared" si="1"/>
@@ -9069,7 +9078,7 @@
     <row r="34" spans="1:65">
       <c r="A34" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B34" t="str">
         <f t="shared" si="1"/>
@@ -9150,7 +9159,7 @@
     <row r="35" spans="1:65">
       <c r="A35" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B35" t="str">
         <f t="shared" si="1"/>
@@ -9231,7 +9240,7 @@
     <row r="36" spans="1:65">
       <c r="A36" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B36" t="str">
         <f t="shared" si="1"/>
@@ -9312,7 +9321,7 @@
     <row r="37" spans="1:65">
       <c r="A37" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B37" t="str">
         <f t="shared" si="1"/>
@@ -9391,7 +9400,7 @@
     <row r="38" spans="1:65">
       <c r="A38" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B38" t="str">
         <f t="shared" si="1"/>
@@ -9470,7 +9479,7 @@
     <row r="39" spans="1:65">
       <c r="A39" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B39" t="str">
         <f t="shared" si="1"/>
@@ -9549,7 +9558,7 @@
     <row r="40" spans="1:65">
       <c r="A40" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B40" t="str">
         <f t="shared" si="1"/>
@@ -9628,7 +9637,7 @@
     <row r="41" spans="1:65">
       <c r="A41" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B41" t="str">
         <f t="shared" si="1"/>
@@ -9707,7 +9716,7 @@
     <row r="42" spans="1:65">
       <c r="A42" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B42" t="str">
         <f t="shared" si="1"/>
@@ -9788,7 +9797,7 @@
     <row r="43" spans="1:65">
       <c r="A43" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B43" t="str">
         <f t="shared" si="1"/>
@@ -9869,7 +9878,7 @@
     <row r="44" spans="1:65">
       <c r="A44" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B44" t="str">
         <f t="shared" si="1"/>
@@ -9948,7 +9957,7 @@
     <row r="45" spans="1:65">
       <c r="A45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B45" t="str">
         <f t="shared" si="1"/>
@@ -10027,7 +10036,7 @@
     <row r="46" spans="1:65">
       <c r="A46" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B46" t="str">
         <f t="shared" si="1"/>
@@ -10106,7 +10115,7 @@
     <row r="47" spans="1:65">
       <c r="A47" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B47" t="str">
         <f t="shared" si="1"/>
@@ -10185,7 +10194,7 @@
     <row r="48" spans="1:65">
       <c r="A48" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B48" t="str">
         <f t="shared" si="1"/>
@@ -10264,7 +10273,7 @@
     <row r="49" spans="1:65">
       <c r="A49" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B49" t="str">
         <f t="shared" si="1"/>
@@ -10345,7 +10354,7 @@
     <row r="50" spans="1:65">
       <c r="A50" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B50" t="str">
         <f t="shared" si="1"/>
@@ -10426,7 +10435,7 @@
     <row r="51" spans="1:65">
       <c r="A51" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B51" t="str">
         <f t="shared" si="1"/>
@@ -10505,7 +10514,7 @@
     <row r="52" spans="1:65">
       <c r="A52" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B52" t="str">
         <f t="shared" si="1"/>
@@ -10584,7 +10593,7 @@
     <row r="53" spans="1:65">
       <c r="A53" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B53" t="str">
         <f t="shared" si="1"/>
@@ -10663,7 +10672,7 @@
     <row r="54" spans="1:65">
       <c r="A54" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B54" t="str">
         <f t="shared" si="1"/>
@@ -10742,7 +10751,7 @@
     <row r="55" spans="1:65">
       <c r="A55" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B55" t="str">
         <f t="shared" si="1"/>
@@ -10821,7 +10830,7 @@
     <row r="56" spans="1:65">
       <c r="A56" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B56" t="str">
         <f t="shared" si="1"/>
@@ -10902,7 +10911,7 @@
     <row r="57" spans="1:65">
       <c r="A57" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B57" t="str">
         <f t="shared" si="1"/>
@@ -10981,7 +10990,7 @@
     <row r="58" spans="1:65">
       <c r="A58" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B58" t="str">
         <f t="shared" si="1"/>
@@ -11062,7 +11071,7 @@
     <row r="59" spans="1:65">
       <c r="A59" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B59" t="str">
         <f t="shared" si="1"/>
@@ -11141,7 +11150,7 @@
     <row r="60" spans="1:65">
       <c r="A60" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B60" t="str">
         <f t="shared" si="1"/>
@@ -11220,7 +11229,7 @@
     <row r="61" spans="1:65">
       <c r="A61" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B61" t="str">
         <f t="shared" si="1"/>
@@ -11299,7 +11308,7 @@
     <row r="62" spans="1:65">
       <c r="A62" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B62" t="str">
         <f t="shared" si="1"/>
@@ -11378,7 +11387,7 @@
     <row r="63" spans="1:65">
       <c r="A63" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B63" t="str">
         <f t="shared" si="1"/>
@@ -11457,7 +11466,7 @@
     <row r="64" spans="1:65">
       <c r="A64" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B64" t="str">
         <f t="shared" si="1"/>
@@ -11538,7 +11547,7 @@
     <row r="65" spans="1:65">
       <c r="A65" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B65" t="str">
         <f t="shared" si="1"/>
@@ -11617,7 +11626,7 @@
     <row r="66" spans="1:65">
       <c r="A66" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B66" t="str">
         <f t="shared" si="1"/>
@@ -11696,7 +11705,7 @@
     <row r="67" spans="1:65">
       <c r="A67" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B67" t="str">
         <f t="shared" si="1"/>
@@ -11778,7 +11787,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B68" t="str">
         <f t="shared" ref="B68:B131" si="3">TEXT($C68, "HH:mm")</f>
@@ -11857,7 +11866,7 @@
     <row r="69" spans="1:65">
       <c r="A69" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B69" t="str">
         <f t="shared" si="3"/>
@@ -11936,7 +11945,7 @@
     <row r="70" spans="1:65">
       <c r="A70" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B70" t="str">
         <f t="shared" si="3"/>
@@ -12015,7 +12024,7 @@
     <row r="71" spans="1:65">
       <c r="A71" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B71" t="str">
         <f t="shared" si="3"/>
@@ -12094,7 +12103,7 @@
     <row r="72" spans="1:65">
       <c r="A72" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B72" t="str">
         <f t="shared" si="3"/>
@@ -12173,7 +12182,7 @@
     <row r="73" spans="1:65">
       <c r="A73" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B73" t="str">
         <f t="shared" si="3"/>
@@ -12252,7 +12261,7 @@
     <row r="74" spans="1:65">
       <c r="A74" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B74" t="str">
         <f t="shared" si="3"/>
@@ -12331,7 +12340,7 @@
     <row r="75" spans="1:65">
       <c r="A75" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B75" t="str">
         <f t="shared" si="3"/>
@@ -12410,7 +12419,7 @@
     <row r="76" spans="1:65">
       <c r="A76" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B76" t="str">
         <f t="shared" si="3"/>
@@ -12489,7 +12498,7 @@
     <row r="77" spans="1:65">
       <c r="A77" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B77" t="str">
         <f t="shared" si="3"/>
@@ -12568,7 +12577,7 @@
     <row r="78" spans="1:65">
       <c r="A78" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B78" t="str">
         <f t="shared" si="3"/>
@@ -12647,7 +12656,7 @@
     <row r="79" spans="1:65">
       <c r="A79" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B79" t="str">
         <f t="shared" si="3"/>
@@ -12726,7 +12735,7 @@
     <row r="80" spans="1:65">
       <c r="A80" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B80" t="str">
         <f t="shared" si="3"/>
@@ -12805,7 +12814,7 @@
     <row r="81" spans="1:65">
       <c r="A81" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B81" t="str">
         <f t="shared" si="3"/>
@@ -12884,7 +12893,7 @@
     <row r="82" spans="1:65">
       <c r="A82" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B82" t="str">
         <f t="shared" si="3"/>
@@ -12963,7 +12972,7 @@
     <row r="83" spans="1:65">
       <c r="A83" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B83" t="str">
         <f t="shared" si="3"/>
@@ -13042,7 +13051,7 @@
     <row r="84" spans="1:65">
       <c r="A84" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B84" t="str">
         <f t="shared" si="3"/>
@@ -13121,7 +13130,7 @@
     <row r="85" spans="1:65">
       <c r="A85" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B85" t="str">
         <f t="shared" si="3"/>
@@ -13200,7 +13209,7 @@
     <row r="86" spans="1:65">
       <c r="A86" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B86" t="str">
         <f t="shared" si="3"/>
@@ -13279,7 +13288,7 @@
     <row r="87" spans="1:65">
       <c r="A87" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B87" t="str">
         <f t="shared" si="3"/>
@@ -13358,7 +13367,7 @@
     <row r="88" spans="1:65">
       <c r="A88" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B88" t="str">
         <f t="shared" si="3"/>
@@ -13437,7 +13446,7 @@
     <row r="89" spans="1:65">
       <c r="A89" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B89" t="str">
         <f t="shared" si="3"/>
@@ -13516,7 +13525,7 @@
     <row r="90" spans="1:65">
       <c r="A90" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B90" t="str">
         <f t="shared" si="3"/>
@@ -13595,7 +13604,7 @@
     <row r="91" spans="1:65">
       <c r="A91" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B91" t="str">
         <f t="shared" si="3"/>
@@ -13674,7 +13683,7 @@
     <row r="92" spans="1:65">
       <c r="A92" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B92" t="str">
         <f t="shared" si="3"/>
@@ -13753,7 +13762,7 @@
     <row r="93" spans="1:65">
       <c r="A93" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B93" t="str">
         <f t="shared" si="3"/>
@@ -13832,7 +13841,7 @@
     <row r="94" spans="1:65">
       <c r="A94" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B94" t="str">
         <f t="shared" si="3"/>
@@ -13911,7 +13920,7 @@
     <row r="95" spans="1:65">
       <c r="A95" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B95" t="str">
         <f t="shared" si="3"/>
@@ -13990,7 +13999,7 @@
     <row r="96" spans="1:65">
       <c r="A96" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B96" t="str">
         <f t="shared" si="3"/>
@@ -14069,7 +14078,7 @@
     <row r="97" spans="1:65">
       <c r="A97" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B97" t="str">
         <f t="shared" si="3"/>
@@ -14148,7 +14157,7 @@
     <row r="98" spans="1:65">
       <c r="A98" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B98" t="str">
         <f t="shared" si="3"/>
@@ -14227,7 +14236,7 @@
     <row r="99" spans="1:65">
       <c r="A99" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B99" t="str">
         <f t="shared" si="3"/>
@@ -14306,7 +14315,7 @@
     <row r="100" spans="1:65">
       <c r="A100" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B100" t="str">
         <f t="shared" si="3"/>
@@ -14387,7 +14396,7 @@
     <row r="101" spans="1:65">
       <c r="A101" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B101" t="str">
         <f t="shared" si="3"/>
@@ -14466,7 +14475,7 @@
     <row r="102" spans="1:65">
       <c r="A102" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B102" t="str">
         <f t="shared" si="3"/>
@@ -14545,7 +14554,7 @@
     <row r="103" spans="1:65">
       <c r="A103" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B103" t="str">
         <f t="shared" si="3"/>
@@ -14624,7 +14633,7 @@
     <row r="104" spans="1:65">
       <c r="A104" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B104" t="str">
         <f t="shared" si="3"/>
@@ -14703,7 +14712,7 @@
     <row r="105" spans="1:65">
       <c r="A105" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B105" t="str">
         <f t="shared" si="3"/>
@@ -14782,7 +14791,7 @@
     <row r="106" spans="1:65">
       <c r="A106" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B106" t="str">
         <f t="shared" si="3"/>
@@ -14863,7 +14872,7 @@
     <row r="107" spans="1:65">
       <c r="A107" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B107" t="str">
         <f t="shared" si="3"/>
@@ -14944,7 +14953,7 @@
     <row r="108" spans="1:65">
       <c r="A108" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B108" t="str">
         <f t="shared" si="3"/>
@@ -15023,7 +15032,7 @@
     <row r="109" spans="1:65">
       <c r="A109" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B109" t="str">
         <f t="shared" si="3"/>
@@ -15102,7 +15111,7 @@
     <row r="110" spans="1:65">
       <c r="A110" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B110" t="str">
         <f t="shared" si="3"/>
@@ -15181,7 +15190,7 @@
     <row r="111" spans="1:65">
       <c r="A111" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B111" t="str">
         <f t="shared" si="3"/>
@@ -15260,7 +15269,7 @@
     <row r="112" spans="1:65">
       <c r="A112" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B112" t="str">
         <f t="shared" si="3"/>
@@ -15341,7 +15350,7 @@
     <row r="113" spans="1:65">
       <c r="A113" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B113" t="str">
         <f t="shared" si="3"/>
@@ -15420,7 +15429,7 @@
     <row r="114" spans="1:65">
       <c r="A114" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B114" t="str">
         <f t="shared" si="3"/>
@@ -15499,7 +15508,7 @@
     <row r="115" spans="1:65">
       <c r="A115" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B115" t="str">
         <f t="shared" si="3"/>
@@ -15578,7 +15587,7 @@
     <row r="116" spans="1:65">
       <c r="A116" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B116" t="str">
         <f t="shared" si="3"/>
@@ -15657,7 +15666,7 @@
     <row r="117" spans="1:65">
       <c r="A117" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B117" t="str">
         <f t="shared" si="3"/>
@@ -15736,7 +15745,7 @@
     <row r="118" spans="1:65">
       <c r="A118" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B118" t="str">
         <f t="shared" si="3"/>
@@ -15815,7 +15824,7 @@
     <row r="119" spans="1:65">
       <c r="A119" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B119" t="str">
         <f t="shared" si="3"/>
@@ -15894,7 +15903,7 @@
     <row r="120" spans="1:65">
       <c r="A120" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B120" t="str">
         <f t="shared" si="3"/>
@@ -15973,7 +15982,7 @@
     <row r="121" spans="1:65">
       <c r="A121" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B121" t="str">
         <f t="shared" si="3"/>
@@ -16052,7 +16061,7 @@
     <row r="122" spans="1:65">
       <c r="A122" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B122" t="str">
         <f t="shared" si="3"/>
@@ -16131,7 +16140,7 @@
     <row r="123" spans="1:65">
       <c r="A123" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B123" t="str">
         <f t="shared" si="3"/>
@@ -16210,7 +16219,7 @@
     <row r="124" spans="1:65">
       <c r="A124" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B124" t="str">
         <f t="shared" si="3"/>
@@ -16291,7 +16300,7 @@
     <row r="125" spans="1:65">
       <c r="A125" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B125" t="str">
         <f t="shared" si="3"/>
@@ -16372,7 +16381,7 @@
     <row r="126" spans="1:65">
       <c r="A126" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B126" t="str">
         <f t="shared" si="3"/>
@@ -16451,7 +16460,7 @@
     <row r="127" spans="1:65">
       <c r="A127" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B127" t="str">
         <f t="shared" si="3"/>
@@ -16530,7 +16539,7 @@
     <row r="128" spans="1:65">
       <c r="A128" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B128" t="str">
         <f t="shared" si="3"/>
@@ -16609,7 +16618,7 @@
     <row r="129" spans="1:65">
       <c r="A129" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B129" t="str">
         <f t="shared" si="3"/>
@@ -16688,7 +16697,7 @@
     <row r="130" spans="1:65">
       <c r="A130" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B130" t="str">
         <f t="shared" si="3"/>
@@ -16767,7 +16776,7 @@
     <row r="131" spans="1:65">
       <c r="A131" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B131" t="str">
         <f t="shared" si="3"/>
@@ -16849,7 +16858,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B132" t="str">
         <f t="shared" ref="B132:B168" si="5">TEXT($C132, "HH:mm")</f>
@@ -16928,7 +16937,7 @@
     <row r="133" spans="1:65">
       <c r="A133" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B133" t="str">
         <f t="shared" si="5"/>
@@ -17007,7 +17016,7 @@
     <row r="134" spans="1:65">
       <c r="A134" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B134" t="str">
         <f t="shared" si="5"/>
@@ -17086,7 +17095,7 @@
     <row r="135" spans="1:65">
       <c r="A135" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B135" t="str">
         <f t="shared" si="5"/>
@@ -17165,7 +17174,7 @@
     <row r="136" spans="1:65">
       <c r="A136" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B136" t="str">
         <f t="shared" si="5"/>
@@ -17246,7 +17255,7 @@
     <row r="137" spans="1:65">
       <c r="A137" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B137" t="str">
         <f t="shared" si="5"/>
@@ -17327,7 +17336,7 @@
     <row r="138" spans="1:65">
       <c r="A138" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B138" t="str">
         <f t="shared" si="5"/>
@@ -17406,7 +17415,7 @@
     <row r="139" spans="1:65">
       <c r="A139" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B139" t="str">
         <f t="shared" si="5"/>
@@ -17485,7 +17494,7 @@
     <row r="140" spans="1:65">
       <c r="A140" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B140" t="str">
         <f t="shared" si="5"/>
@@ -17564,7 +17573,7 @@
     <row r="141" spans="1:65">
       <c r="A141" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B141" t="str">
         <f t="shared" si="5"/>
@@ -17643,7 +17652,7 @@
     <row r="142" spans="1:65">
       <c r="A142" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B142" t="str">
         <f t="shared" si="5"/>
@@ -17722,7 +17731,7 @@
     <row r="143" spans="1:65">
       <c r="A143" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B143" t="str">
         <f t="shared" si="5"/>
@@ -17801,7 +17810,7 @@
     <row r="144" spans="1:65">
       <c r="A144" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B144" t="str">
         <f t="shared" si="5"/>
@@ -17880,7 +17889,7 @@
     <row r="145" spans="1:65">
       <c r="A145" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B145" t="str">
         <f t="shared" si="5"/>
@@ -17959,7 +17968,7 @@
     <row r="146" spans="1:65">
       <c r="A146" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B146" t="str">
         <f t="shared" si="5"/>
@@ -18038,7 +18047,7 @@
     <row r="147" spans="1:65">
       <c r="A147" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B147" t="str">
         <f t="shared" si="5"/>
@@ -18117,7 +18126,7 @@
     <row r="148" spans="1:65">
       <c r="A148" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B148" t="str">
         <f t="shared" si="5"/>
@@ -18198,7 +18207,7 @@
     <row r="149" spans="1:65">
       <c r="A149" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B149" t="str">
         <f t="shared" si="5"/>
@@ -18277,7 +18286,7 @@
     <row r="150" spans="1:65">
       <c r="A150" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B150" t="str">
         <f t="shared" si="5"/>
@@ -18356,7 +18365,7 @@
     <row r="151" spans="1:65">
       <c r="A151" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B151" t="str">
         <f t="shared" si="5"/>
@@ -18435,7 +18444,7 @@
     <row r="152" spans="1:65">
       <c r="A152" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B152" t="str">
         <f t="shared" si="5"/>
@@ -18514,7 +18523,7 @@
     <row r="153" spans="1:65">
       <c r="A153" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B153" t="str">
         <f t="shared" si="5"/>
@@ -18593,7 +18602,7 @@
     <row r="154" spans="1:65">
       <c r="A154" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B154" t="str">
         <f t="shared" si="5"/>
@@ -18672,7 +18681,7 @@
     <row r="155" spans="1:65">
       <c r="A155" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B155" t="str">
         <f t="shared" si="5"/>
@@ -18751,7 +18760,7 @@
     <row r="156" spans="1:65">
       <c r="A156" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B156" t="str">
         <f t="shared" si="5"/>
@@ -18830,7 +18839,7 @@
     <row r="157" spans="1:65">
       <c r="A157" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B157" t="str">
         <f t="shared" si="5"/>
@@ -18909,7 +18918,7 @@
     <row r="158" spans="1:65">
       <c r="A158" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B158" t="str">
         <f t="shared" si="5"/>
@@ -18988,7 +18997,7 @@
     <row r="159" spans="1:65">
       <c r="A159" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B159" t="str">
         <f t="shared" si="5"/>
@@ -19067,7 +19076,7 @@
     <row r="160" spans="1:65">
       <c r="A160" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B160" t="str">
         <f t="shared" si="5"/>
@@ -19146,7 +19155,7 @@
     <row r="161" spans="1:65">
       <c r="A161" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B161" t="str">
         <f t="shared" si="5"/>
@@ -19225,7 +19234,7 @@
     <row r="162" spans="1:65">
       <c r="A162" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B162" t="str">
         <f t="shared" si="5"/>
@@ -19304,7 +19313,7 @@
     <row r="163" spans="1:65">
       <c r="A163" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B163" t="str">
         <f t="shared" si="5"/>
@@ -19383,7 +19392,7 @@
     <row r="164" spans="1:65">
       <c r="A164" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B164" t="str">
         <f t="shared" si="5"/>
@@ -19462,7 +19471,7 @@
     <row r="165" spans="1:65">
       <c r="A165" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B165" t="str">
         <f t="shared" si="5"/>
@@ -19541,7 +19550,7 @@
     <row r="166" spans="1:65">
       <c r="A166" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B166" t="str">
         <f t="shared" si="5"/>
@@ -19622,7 +19631,7 @@
     <row r="167" spans="1:65">
       <c r="A167" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B167" t="str">
         <f t="shared" si="5"/>
@@ -19701,7 +19710,7 @@
     <row r="168" spans="1:65">
       <c r="A168" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B168" t="str">
         <f t="shared" si="5"/>
@@ -19783,7 +19792,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B169" t="str">
         <f>TEXT($C169, "HH:mm")</f>
@@ -19865,7 +19874,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B170" t="str">
         <f t="shared" ref="B170:B233" si="7">TEXT($C170, "HH:mm")</f>
@@ -19944,7 +19953,7 @@
     <row r="171" spans="1:65">
       <c r="A171" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B171" t="str">
         <f t="shared" si="7"/>
@@ -20023,7 +20032,7 @@
     <row r="172" spans="1:65">
       <c r="A172" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B172" t="str">
         <f t="shared" si="7"/>
@@ -20104,7 +20113,7 @@
     <row r="173" spans="1:65">
       <c r="A173" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B173" t="str">
         <f t="shared" si="7"/>
@@ -20183,7 +20192,7 @@
     <row r="174" spans="1:65">
       <c r="A174" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B174" t="str">
         <f t="shared" si="7"/>
@@ -20262,7 +20271,7 @@
     <row r="175" spans="1:65">
       <c r="A175" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B175" t="str">
         <f t="shared" si="7"/>
@@ -20341,7 +20350,7 @@
     <row r="176" spans="1:65">
       <c r="A176" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B176" t="str">
         <f t="shared" si="7"/>
@@ -20420,7 +20429,7 @@
     <row r="177" spans="1:65">
       <c r="A177" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B177" t="str">
         <f t="shared" si="7"/>
@@ -20499,7 +20508,7 @@
     <row r="178" spans="1:65">
       <c r="A178" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B178" t="str">
         <f t="shared" si="7"/>
@@ -20580,7 +20589,7 @@
     <row r="179" spans="1:65">
       <c r="A179" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B179" t="str">
         <f t="shared" si="7"/>
@@ -20659,7 +20668,7 @@
     <row r="180" spans="1:65">
       <c r="A180" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B180" t="str">
         <f t="shared" si="7"/>
@@ -20738,7 +20747,7 @@
     <row r="181" spans="1:65">
       <c r="A181" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B181" t="str">
         <f t="shared" si="7"/>
@@ -20819,7 +20828,7 @@
     <row r="182" spans="1:65">
       <c r="A182" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B182" t="str">
         <f t="shared" si="7"/>
@@ -20900,7 +20909,7 @@
     <row r="183" spans="1:65">
       <c r="A183" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B183" t="str">
         <f t="shared" si="7"/>
@@ -20981,7 +20990,7 @@
     <row r="184" spans="1:65">
       <c r="A184" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B184" t="str">
         <f t="shared" si="7"/>
@@ -21064,7 +21073,7 @@
     <row r="185" spans="1:65">
       <c r="A185" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B185" t="str">
         <f t="shared" si="7"/>
@@ -21145,7 +21154,7 @@
     <row r="186" spans="1:65">
       <c r="A186" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B186" t="str">
         <f t="shared" si="7"/>
@@ -21226,7 +21235,7 @@
     <row r="187" spans="1:65">
       <c r="A187" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B187" t="str">
         <f t="shared" si="7"/>
@@ -21307,7 +21316,7 @@
     <row r="188" spans="1:65">
       <c r="A188" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B188" t="str">
         <f t="shared" si="7"/>
@@ -21388,7 +21397,7 @@
     <row r="189" spans="1:65">
       <c r="A189" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B189" t="str">
         <f t="shared" si="7"/>
@@ -21469,7 +21478,7 @@
     <row r="190" spans="1:65">
       <c r="A190" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B190" t="str">
         <f t="shared" si="7"/>
@@ -21552,7 +21561,7 @@
     <row r="191" spans="1:65">
       <c r="A191" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B191" t="str">
         <f t="shared" si="7"/>
@@ -21635,7 +21644,7 @@
     <row r="192" spans="1:65">
       <c r="A192" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B192" t="str">
         <f t="shared" si="7"/>
@@ -21718,7 +21727,7 @@
     <row r="193" spans="1:65">
       <c r="A193" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B193" t="str">
         <f t="shared" si="7"/>
@@ -21801,7 +21810,7 @@
     <row r="194" spans="1:65">
       <c r="A194" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B194" t="str">
         <f t="shared" si="7"/>
@@ -21882,7 +21891,7 @@
     <row r="195" spans="1:65">
       <c r="A195" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B195" t="str">
         <f t="shared" si="7"/>
@@ -21963,7 +21972,7 @@
     <row r="196" spans="1:65">
       <c r="A196" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B196" t="str">
         <f t="shared" si="7"/>
@@ -22046,7 +22055,7 @@
     <row r="197" spans="1:65">
       <c r="A197" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B197" t="str">
         <f t="shared" si="7"/>
@@ -22125,7 +22134,7 @@
     <row r="198" spans="1:65">
       <c r="A198" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B198" t="str">
         <f t="shared" si="7"/>
@@ -22204,7 +22213,7 @@
     <row r="199" spans="1:65">
       <c r="A199" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B199" t="str">
         <f t="shared" si="7"/>
@@ -22283,7 +22292,7 @@
     <row r="200" spans="1:65">
       <c r="A200" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B200" t="str">
         <f t="shared" si="7"/>
@@ -22362,7 +22371,7 @@
     <row r="201" spans="1:65">
       <c r="A201" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B201" t="str">
         <f t="shared" si="7"/>
@@ -22441,7 +22450,7 @@
     <row r="202" spans="1:65">
       <c r="A202" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B202" t="str">
         <f t="shared" si="7"/>
@@ -22522,7 +22531,7 @@
     <row r="203" spans="1:65">
       <c r="A203" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B203" t="str">
         <f t="shared" si="7"/>
@@ -22601,7 +22610,7 @@
     <row r="204" spans="1:65">
       <c r="A204" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B204" t="str">
         <f t="shared" si="7"/>
@@ -22680,7 +22689,7 @@
     <row r="205" spans="1:65">
       <c r="A205" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B205" t="str">
         <f t="shared" si="7"/>
@@ -22759,7 +22768,7 @@
     <row r="206" spans="1:65">
       <c r="A206" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B206" t="str">
         <f t="shared" si="7"/>
@@ -22838,7 +22847,7 @@
     <row r="207" spans="1:65">
       <c r="A207" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B207" t="str">
         <f t="shared" si="7"/>
@@ -22917,7 +22926,7 @@
     <row r="208" spans="1:65">
       <c r="A208" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B208" t="str">
         <f t="shared" si="7"/>
@@ -22998,7 +23007,7 @@
     <row r="209" spans="1:65">
       <c r="A209" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B209" t="str">
         <f t="shared" si="7"/>
@@ -23077,7 +23086,7 @@
     <row r="210" spans="1:65">
       <c r="A210" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B210" t="str">
         <f t="shared" si="7"/>
@@ -23156,7 +23165,7 @@
     <row r="211" spans="1:65">
       <c r="A211" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B211" t="str">
         <f t="shared" si="7"/>
@@ -23237,7 +23246,7 @@
     <row r="212" spans="1:65">
       <c r="A212" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B212" t="str">
         <f t="shared" si="7"/>
@@ -23316,7 +23325,7 @@
     <row r="213" spans="1:65">
       <c r="A213" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B213" t="str">
         <f t="shared" si="7"/>
@@ -23395,7 +23404,7 @@
     <row r="214" spans="1:65">
       <c r="A214" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B214" t="str">
         <f t="shared" si="7"/>
@@ -23474,7 +23483,7 @@
     <row r="215" spans="1:65">
       <c r="A215" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B215" t="str">
         <f t="shared" si="7"/>
@@ -23553,7 +23562,7 @@
     <row r="216" spans="1:65">
       <c r="A216" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B216" t="str">
         <f t="shared" si="7"/>
@@ -23632,7 +23641,7 @@
     <row r="217" spans="1:65">
       <c r="A217" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B217" t="str">
         <f t="shared" si="7"/>
@@ -23711,7 +23720,7 @@
     <row r="218" spans="1:65">
       <c r="A218" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B218" t="str">
         <f t="shared" si="7"/>
@@ -23790,7 +23799,7 @@
     <row r="219" spans="1:65">
       <c r="A219" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B219" t="str">
         <f t="shared" si="7"/>
@@ -23869,7 +23878,7 @@
     <row r="220" spans="1:65">
       <c r="A220" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B220" t="str">
         <f t="shared" si="7"/>
@@ -23950,7 +23959,7 @@
     <row r="221" spans="1:65">
       <c r="A221" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B221" t="str">
         <f t="shared" si="7"/>
@@ -24029,7 +24038,7 @@
     <row r="222" spans="1:65">
       <c r="A222" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B222" t="str">
         <f t="shared" si="7"/>
@@ -24108,7 +24117,7 @@
     <row r="223" spans="1:65">
       <c r="A223" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B223" t="str">
         <f t="shared" si="7"/>
@@ -24187,7 +24196,7 @@
     <row r="224" spans="1:65">
       <c r="A224" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B224" t="str">
         <f t="shared" si="7"/>
@@ -24266,7 +24275,7 @@
     <row r="225" spans="1:65">
       <c r="A225" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B225" t="str">
         <f t="shared" si="7"/>
@@ -24345,7 +24354,7 @@
     <row r="226" spans="1:65">
       <c r="A226" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B226" t="str">
         <f t="shared" si="7"/>
@@ -24424,7 +24433,7 @@
     <row r="227" spans="1:65">
       <c r="A227" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B227" t="str">
         <f t="shared" si="7"/>
@@ -24503,7 +24512,7 @@
     <row r="228" spans="1:65">
       <c r="A228" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B228" t="str">
         <f t="shared" si="7"/>
@@ -24582,7 +24591,7 @@
     <row r="229" spans="1:65">
       <c r="A229" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B229" t="str">
         <f t="shared" si="7"/>
@@ -24661,7 +24670,7 @@
     <row r="230" spans="1:65">
       <c r="A230" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B230" t="str">
         <f t="shared" si="7"/>
@@ -24740,7 +24749,7 @@
     <row r="231" spans="1:65">
       <c r="A231" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B231" t="str">
         <f t="shared" si="7"/>
@@ -24819,7 +24828,7 @@
     <row r="232" spans="1:65">
       <c r="A232" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B232" t="str">
         <f t="shared" si="7"/>
@@ -24898,7 +24907,7 @@
     <row r="233" spans="1:65">
       <c r="A233" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B233" t="str">
         <f t="shared" si="7"/>
@@ -24980,7 +24989,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B234" t="str">
         <f t="shared" ref="B234:B291" si="9">TEXT($C234, "HH:mm")</f>
@@ -25059,7 +25068,7 @@
     <row r="235" spans="1:65">
       <c r="A235" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B235" t="str">
         <f t="shared" si="9"/>
@@ -25138,7 +25147,7 @@
     <row r="236" spans="1:65">
       <c r="A236" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B236" t="str">
         <f t="shared" si="9"/>
@@ -25217,7 +25226,7 @@
     <row r="237" spans="1:65">
       <c r="A237" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B237" t="str">
         <f t="shared" si="9"/>
@@ -25296,7 +25305,7 @@
     <row r="238" spans="1:65">
       <c r="A238" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B238" t="str">
         <f t="shared" si="9"/>
@@ -25375,7 +25384,7 @@
     <row r="239" spans="1:65">
       <c r="A239" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B239" t="str">
         <f t="shared" si="9"/>
@@ -25454,7 +25463,7 @@
     <row r="240" spans="1:65">
       <c r="A240" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B240" t="str">
         <f t="shared" si="9"/>
@@ -25533,7 +25542,7 @@
     <row r="241" spans="1:65">
       <c r="A241" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B241" t="str">
         <f t="shared" si="9"/>
@@ -25612,7 +25621,7 @@
     <row r="242" spans="1:65">
       <c r="A242" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B242" t="str">
         <f t="shared" si="9"/>
@@ -25691,7 +25700,7 @@
     <row r="243" spans="1:65">
       <c r="A243" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B243" t="str">
         <f t="shared" si="9"/>
@@ -25770,7 +25779,7 @@
     <row r="244" spans="1:65">
       <c r="A244" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B244" t="str">
         <f t="shared" si="9"/>
@@ -25849,7 +25858,7 @@
     <row r="245" spans="1:65">
       <c r="A245" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B245" t="str">
         <f t="shared" si="9"/>
@@ -25928,7 +25937,7 @@
     <row r="246" spans="1:65">
       <c r="A246" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B246" t="str">
         <f t="shared" si="9"/>
@@ -26007,7 +26016,7 @@
     <row r="247" spans="1:65">
       <c r="A247" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B247" t="str">
         <f t="shared" si="9"/>
@@ -26086,7 +26095,7 @@
     <row r="248" spans="1:65">
       <c r="A248" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B248" t="str">
         <f t="shared" si="9"/>
@@ -26165,7 +26174,7 @@
     <row r="249" spans="1:65">
       <c r="A249" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B249" t="str">
         <f t="shared" si="9"/>
@@ -26244,7 +26253,7 @@
     <row r="250" spans="1:65">
       <c r="A250" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B250" t="str">
         <f t="shared" si="9"/>
@@ -26323,7 +26332,7 @@
     <row r="251" spans="1:65">
       <c r="A251" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B251" t="str">
         <f t="shared" si="9"/>
@@ -26402,7 +26411,7 @@
     <row r="252" spans="1:65">
       <c r="A252" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B252" t="str">
         <f t="shared" si="9"/>
@@ -26481,7 +26490,7 @@
     <row r="253" spans="1:65">
       <c r="A253" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B253" t="str">
         <f t="shared" si="9"/>
@@ -26560,7 +26569,7 @@
     <row r="254" spans="1:65">
       <c r="A254" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B254" t="str">
         <f t="shared" si="9"/>
@@ -26639,7 +26648,7 @@
     <row r="255" spans="1:65">
       <c r="A255" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B255" t="str">
         <f t="shared" si="9"/>
@@ -26718,7 +26727,7 @@
     <row r="256" spans="1:65">
       <c r="A256" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B256" t="str">
         <f t="shared" si="9"/>
@@ -26797,7 +26806,7 @@
     <row r="257" spans="1:65">
       <c r="A257" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B257" t="str">
         <f t="shared" si="9"/>
@@ -26876,7 +26885,7 @@
     <row r="258" spans="1:65">
       <c r="A258" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B258" t="str">
         <f t="shared" si="9"/>
@@ -26955,7 +26964,7 @@
     <row r="259" spans="1:65">
       <c r="A259" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B259" t="str">
         <f t="shared" si="9"/>
@@ -27034,7 +27043,7 @@
     <row r="260" spans="1:65">
       <c r="A260" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B260" t="str">
         <f t="shared" si="9"/>
@@ -27113,7 +27122,7 @@
     <row r="261" spans="1:65">
       <c r="A261" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B261" t="str">
         <f t="shared" si="9"/>
@@ -27192,7 +27201,7 @@
     <row r="262" spans="1:65">
       <c r="A262" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B262" t="str">
         <f t="shared" si="9"/>
@@ -27271,7 +27280,7 @@
     <row r="263" spans="1:65">
       <c r="A263" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B263" t="str">
         <f t="shared" si="9"/>
@@ -27350,7 +27359,7 @@
     <row r="264" spans="1:65">
       <c r="A264" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B264" t="str">
         <f t="shared" si="9"/>
@@ -27429,7 +27438,7 @@
     <row r="265" spans="1:65">
       <c r="A265" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B265" t="str">
         <f t="shared" si="9"/>
@@ -27508,7 +27517,7 @@
     <row r="266" spans="1:65">
       <c r="A266" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B266" t="str">
         <f t="shared" si="9"/>
@@ -27587,7 +27596,7 @@
     <row r="267" spans="1:65">
       <c r="A267" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B267" t="str">
         <f t="shared" si="9"/>
@@ -27666,7 +27675,7 @@
     <row r="268" spans="1:65">
       <c r="A268" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B268" t="str">
         <f t="shared" si="9"/>
@@ -27745,7 +27754,7 @@
     <row r="269" spans="1:65">
       <c r="A269" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B269" t="str">
         <f t="shared" si="9"/>
@@ -27824,7 +27833,7 @@
     <row r="270" spans="1:65">
       <c r="A270" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B270" t="str">
         <f t="shared" si="9"/>
@@ -27903,7 +27912,7 @@
     <row r="271" spans="1:65">
       <c r="A271" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B271" t="str">
         <f t="shared" si="9"/>
@@ -27982,7 +27991,7 @@
     <row r="272" spans="1:65">
       <c r="A272" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B272" t="str">
         <f t="shared" si="9"/>
@@ -28061,7 +28070,7 @@
     <row r="273" spans="1:65">
       <c r="A273" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B273" t="str">
         <f t="shared" si="9"/>
@@ -28140,7 +28149,7 @@
     <row r="274" spans="1:65">
       <c r="A274" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B274" t="str">
         <f t="shared" si="9"/>
@@ -28219,7 +28228,7 @@
     <row r="275" spans="1:65">
       <c r="A275" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B275" t="str">
         <f t="shared" si="9"/>
@@ -28298,7 +28307,7 @@
     <row r="276" spans="1:65">
       <c r="A276" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B276" t="str">
         <f t="shared" si="9"/>
@@ -28377,7 +28386,7 @@
     <row r="277" spans="1:65">
       <c r="A277" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B277" t="str">
         <f t="shared" si="9"/>
@@ -28456,7 +28465,7 @@
     <row r="278" spans="1:65">
       <c r="A278" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B278" t="str">
         <f t="shared" si="9"/>
@@ -28535,7 +28544,7 @@
     <row r="279" spans="1:65">
       <c r="A279" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B279" t="str">
         <f t="shared" si="9"/>
@@ -28614,7 +28623,7 @@
     <row r="280" spans="1:65">
       <c r="A280" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B280" t="str">
         <f t="shared" si="9"/>
@@ -28693,7 +28702,7 @@
     <row r="281" spans="1:65">
       <c r="A281" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B281" t="str">
         <f t="shared" si="9"/>
@@ -28772,7 +28781,7 @@
     <row r="282" spans="1:65">
       <c r="A282" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B282" t="str">
         <f t="shared" si="9"/>
@@ -28851,7 +28860,7 @@
     <row r="283" spans="1:65">
       <c r="A283" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B283" t="str">
         <f t="shared" si="9"/>
@@ -28930,7 +28939,7 @@
     <row r="284" spans="1:65">
       <c r="A284" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B284" t="str">
         <f t="shared" si="9"/>
@@ -29009,7 +29018,7 @@
     <row r="285" spans="1:65">
       <c r="A285" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B285" t="str">
         <f t="shared" si="9"/>
@@ -29088,7 +29097,7 @@
     <row r="286" spans="1:65">
       <c r="A286" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B286" t="str">
         <f t="shared" si="9"/>
@@ -29167,7 +29176,7 @@
     <row r="287" spans="1:65">
       <c r="A287" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B287" t="str">
         <f t="shared" si="9"/>
@@ -29246,7 +29255,7 @@
     <row r="288" spans="1:65">
       <c r="A288" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B288" t="str">
         <f t="shared" si="9"/>
@@ -29325,7 +29334,7 @@
     <row r="289" spans="1:65">
       <c r="A289" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B289" t="str">
         <f t="shared" si="9"/>
@@ -29404,7 +29413,7 @@
     <row r="290" spans="1:65">
       <c r="A290" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B290" t="str">
         <f t="shared" si="9"/>
@@ -29483,7 +29492,7 @@
     <row r="291" spans="1:65">
       <c r="A291" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:10</v>
+        <v>02:15</v>
       </c>
       <c r="B291" t="str">
         <f t="shared" si="9"/>

--- a/Vite-Vercel開発.xlsx
+++ b/Vite-Vercel開発.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2c67ec30e06f060f/work/GitHub/work-time-tracker/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{1928CA11-C4AD-40E9-B1C5-143667E830EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09F1C063-48DE-46FA-82A3-7B9297622148}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="13_ncr:1_{1928CA11-C4AD-40E9-B1C5-143667E830EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA1CAEA5-E758-4272-A02F-8C2CC5F0D64B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1550" uniqueCount="927">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1551" uniqueCount="928">
   <si>
     <t>npm install -g vercel</t>
     <phoneticPr fontId="1"/>
@@ -5386,6 +5386,10 @@
   </si>
   <si>
     <t>Found 34 errors in 9 files.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Found 24 errors in 8 files.</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -6158,7 +6162,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{083174DA-A42C-4F9C-978E-61AEAAD9DDFF}">
-  <dimension ref="B2:D32"/>
+  <dimension ref="B2:D33"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
@@ -6326,6 +6330,11 @@
     <row r="32" spans="3:3">
       <c r="C32" t="s">
         <v>926</v>
+      </c>
+    </row>
+    <row r="33" spans="3:3">
+      <c r="C33" t="s">
+        <v>927</v>
       </c>
     </row>
   </sheetData>
@@ -6503,7 +6512,7 @@
     <row r="3" spans="1:65">
       <c r="A3" s="19" t="str">
         <f ca="1">TEXT(NOW(),"HH:mm")</f>
-        <v>02:15</v>
+        <v>02:19</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="17" t="s">

--- a/Vite-Vercel開発.xlsx
+++ b/Vite-Vercel開発.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2c67ec30e06f060f/work/GitHub/work-time-tracker/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="13_ncr:1_{1928CA11-C4AD-40E9-B1C5-143667E830EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA1CAEA5-E758-4272-A02F-8C2CC5F0D64B}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{1928CA11-C4AD-40E9-B1C5-143667E830EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89CC501B-06AB-4281-BEA1-7A52FD14E733}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1551" uniqueCount="928">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1552" uniqueCount="929">
   <si>
     <t>npm install -g vercel</t>
     <phoneticPr fontId="1"/>
@@ -5390,6 +5390,10 @@
   </si>
   <si>
     <t>Found 24 errors in 8 files.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Found 7 errors in 3 files.</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -6162,7 +6166,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{083174DA-A42C-4F9C-978E-61AEAAD9DDFF}">
-  <dimension ref="B2:D33"/>
+  <dimension ref="B2:D34"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
@@ -6335,6 +6339,11 @@
     <row r="33" spans="3:3">
       <c r="C33" t="s">
         <v>927</v>
+      </c>
+    </row>
+    <row r="34" spans="3:3">
+      <c r="C34" t="s">
+        <v>928</v>
       </c>
     </row>
   </sheetData>
@@ -6501,7 +6510,7 @@
       MOD(NOW(),1),
       TIME(0,5,0)
     ),"HH:mm")</f>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B2" s="19"/>
       <c r="D2" s="1">
@@ -6512,7 +6521,7 @@
     <row r="3" spans="1:65">
       <c r="A3" s="19" t="str">
         <f ca="1">TEXT(NOW(),"HH:mm")</f>
-        <v>02:19</v>
+        <v>02:22</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="17" t="s">
@@ -6711,7 +6720,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B4" t="str">
         <f t="shared" ref="B4:B67" si="1">TEXT($C4, "HH:mm")</f>
@@ -6790,7 +6799,7 @@
     <row r="5" spans="1:65">
       <c r="A5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B5" t="str">
         <f t="shared" si="1"/>
@@ -6869,7 +6878,7 @@
     <row r="6" spans="1:65">
       <c r="A6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B6" t="str">
         <f t="shared" si="1"/>
@@ -6948,7 +6957,7 @@
     <row r="7" spans="1:65">
       <c r="A7" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B7" t="str">
         <f t="shared" si="1"/>
@@ -7027,7 +7036,7 @@
     <row r="8" spans="1:65">
       <c r="A8" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B8" t="str">
         <f t="shared" si="1"/>
@@ -7106,7 +7115,7 @@
     <row r="9" spans="1:65">
       <c r="A9" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B9" t="str">
         <f t="shared" si="1"/>
@@ -7185,7 +7194,7 @@
     <row r="10" spans="1:65">
       <c r="A10" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B10" t="str">
         <f t="shared" si="1"/>
@@ -7264,7 +7273,7 @@
     <row r="11" spans="1:65">
       <c r="A11" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B11" t="str">
         <f t="shared" si="1"/>
@@ -7343,7 +7352,7 @@
     <row r="12" spans="1:65">
       <c r="A12" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B12" t="str">
         <f t="shared" si="1"/>
@@ -7422,7 +7431,7 @@
     <row r="13" spans="1:65">
       <c r="A13" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B13" t="str">
         <f t="shared" si="1"/>
@@ -7501,7 +7510,7 @@
     <row r="14" spans="1:65">
       <c r="A14" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B14" t="str">
         <f t="shared" si="1"/>
@@ -7580,7 +7589,7 @@
     <row r="15" spans="1:65">
       <c r="A15" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B15" t="str">
         <f t="shared" si="1"/>
@@ -7659,7 +7668,7 @@
     <row r="16" spans="1:65">
       <c r="A16" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B16" t="str">
         <f t="shared" si="1"/>
@@ -7738,7 +7747,7 @@
     <row r="17" spans="1:65">
       <c r="A17" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B17" t="str">
         <f t="shared" si="1"/>
@@ -7817,7 +7826,7 @@
     <row r="18" spans="1:65">
       <c r="A18" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B18" t="str">
         <f t="shared" si="1"/>
@@ -7896,7 +7905,7 @@
     <row r="19" spans="1:65">
       <c r="A19" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B19" t="str">
         <f t="shared" si="1"/>
@@ -7975,7 +7984,7 @@
     <row r="20" spans="1:65">
       <c r="A20" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B20" t="str">
         <f t="shared" si="1"/>
@@ -8054,7 +8063,7 @@
     <row r="21" spans="1:65">
       <c r="A21" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B21" t="str">
         <f t="shared" si="1"/>
@@ -8133,7 +8142,7 @@
     <row r="22" spans="1:65">
       <c r="A22" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B22" t="str">
         <f t="shared" si="1"/>
@@ -8212,7 +8221,7 @@
     <row r="23" spans="1:65">
       <c r="A23" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B23" t="str">
         <f t="shared" si="1"/>
@@ -8291,7 +8300,7 @@
     <row r="24" spans="1:65">
       <c r="A24" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B24" t="str">
         <f t="shared" si="1"/>
@@ -8370,7 +8379,7 @@
     <row r="25" spans="1:65">
       <c r="A25" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B25" t="str">
         <f t="shared" si="1"/>
@@ -8449,7 +8458,7 @@
     <row r="26" spans="1:65">
       <c r="A26" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B26" t="str">
         <f t="shared" si="1"/>
@@ -8528,7 +8537,7 @@
     <row r="27" spans="1:65">
       <c r="A27" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B27" t="str">
         <f t="shared" si="1"/>
@@ -8607,7 +8616,7 @@
     <row r="28" spans="1:65">
       <c r="A28" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B28" t="str">
         <f t="shared" si="1"/>
@@ -8688,7 +8697,7 @@
     <row r="29" spans="1:65">
       <c r="A29" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B29" t="str">
         <f t="shared" si="1"/>
@@ -8769,7 +8778,7 @@
     <row r="30" spans="1:65">
       <c r="A30" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B30" t="str">
         <f t="shared" si="1"/>
@@ -8850,7 +8859,7 @@
     <row r="31" spans="1:65">
       <c r="A31" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B31" t="str">
         <f t="shared" si="1"/>
@@ -8929,7 +8938,7 @@
     <row r="32" spans="1:65">
       <c r="A32" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B32" t="str">
         <f t="shared" si="1"/>
@@ -9008,7 +9017,7 @@
     <row r="33" spans="1:65">
       <c r="A33" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B33" t="str">
         <f t="shared" si="1"/>
@@ -9087,7 +9096,7 @@
     <row r="34" spans="1:65">
       <c r="A34" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B34" t="str">
         <f t="shared" si="1"/>
@@ -9168,7 +9177,7 @@
     <row r="35" spans="1:65">
       <c r="A35" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B35" t="str">
         <f t="shared" si="1"/>
@@ -9249,7 +9258,7 @@
     <row r="36" spans="1:65">
       <c r="A36" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B36" t="str">
         <f t="shared" si="1"/>
@@ -9330,7 +9339,7 @@
     <row r="37" spans="1:65">
       <c r="A37" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B37" t="str">
         <f t="shared" si="1"/>
@@ -9409,7 +9418,7 @@
     <row r="38" spans="1:65">
       <c r="A38" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B38" t="str">
         <f t="shared" si="1"/>
@@ -9488,7 +9497,7 @@
     <row r="39" spans="1:65">
       <c r="A39" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B39" t="str">
         <f t="shared" si="1"/>
@@ -9567,7 +9576,7 @@
     <row r="40" spans="1:65">
       <c r="A40" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B40" t="str">
         <f t="shared" si="1"/>
@@ -9646,7 +9655,7 @@
     <row r="41" spans="1:65">
       <c r="A41" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B41" t="str">
         <f t="shared" si="1"/>
@@ -9725,7 +9734,7 @@
     <row r="42" spans="1:65">
       <c r="A42" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B42" t="str">
         <f t="shared" si="1"/>
@@ -9806,7 +9815,7 @@
     <row r="43" spans="1:65">
       <c r="A43" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B43" t="str">
         <f t="shared" si="1"/>
@@ -9887,7 +9896,7 @@
     <row r="44" spans="1:65">
       <c r="A44" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B44" t="str">
         <f t="shared" si="1"/>
@@ -9966,7 +9975,7 @@
     <row r="45" spans="1:65">
       <c r="A45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B45" t="str">
         <f t="shared" si="1"/>
@@ -10045,7 +10054,7 @@
     <row r="46" spans="1:65">
       <c r="A46" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B46" t="str">
         <f t="shared" si="1"/>
@@ -10124,7 +10133,7 @@
     <row r="47" spans="1:65">
       <c r="A47" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B47" t="str">
         <f t="shared" si="1"/>
@@ -10203,7 +10212,7 @@
     <row r="48" spans="1:65">
       <c r="A48" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B48" t="str">
         <f t="shared" si="1"/>
@@ -10282,7 +10291,7 @@
     <row r="49" spans="1:65">
       <c r="A49" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B49" t="str">
         <f t="shared" si="1"/>
@@ -10363,7 +10372,7 @@
     <row r="50" spans="1:65">
       <c r="A50" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B50" t="str">
         <f t="shared" si="1"/>
@@ -10444,7 +10453,7 @@
     <row r="51" spans="1:65">
       <c r="A51" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B51" t="str">
         <f t="shared" si="1"/>
@@ -10523,7 +10532,7 @@
     <row r="52" spans="1:65">
       <c r="A52" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B52" t="str">
         <f t="shared" si="1"/>
@@ -10602,7 +10611,7 @@
     <row r="53" spans="1:65">
       <c r="A53" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B53" t="str">
         <f t="shared" si="1"/>
@@ -10681,7 +10690,7 @@
     <row r="54" spans="1:65">
       <c r="A54" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B54" t="str">
         <f t="shared" si="1"/>
@@ -10760,7 +10769,7 @@
     <row r="55" spans="1:65">
       <c r="A55" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B55" t="str">
         <f t="shared" si="1"/>
@@ -10839,7 +10848,7 @@
     <row r="56" spans="1:65">
       <c r="A56" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B56" t="str">
         <f t="shared" si="1"/>
@@ -10920,7 +10929,7 @@
     <row r="57" spans="1:65">
       <c r="A57" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B57" t="str">
         <f t="shared" si="1"/>
@@ -10999,7 +11008,7 @@
     <row r="58" spans="1:65">
       <c r="A58" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B58" t="str">
         <f t="shared" si="1"/>
@@ -11080,7 +11089,7 @@
     <row r="59" spans="1:65">
       <c r="A59" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B59" t="str">
         <f t="shared" si="1"/>
@@ -11159,7 +11168,7 @@
     <row r="60" spans="1:65">
       <c r="A60" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B60" t="str">
         <f t="shared" si="1"/>
@@ -11238,7 +11247,7 @@
     <row r="61" spans="1:65">
       <c r="A61" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B61" t="str">
         <f t="shared" si="1"/>
@@ -11317,7 +11326,7 @@
     <row r="62" spans="1:65">
       <c r="A62" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B62" t="str">
         <f t="shared" si="1"/>
@@ -11396,7 +11405,7 @@
     <row r="63" spans="1:65">
       <c r="A63" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B63" t="str">
         <f t="shared" si="1"/>
@@ -11475,7 +11484,7 @@
     <row r="64" spans="1:65">
       <c r="A64" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B64" t="str">
         <f t="shared" si="1"/>
@@ -11556,7 +11565,7 @@
     <row r="65" spans="1:65">
       <c r="A65" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B65" t="str">
         <f t="shared" si="1"/>
@@ -11635,7 +11644,7 @@
     <row r="66" spans="1:65">
       <c r="A66" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B66" t="str">
         <f t="shared" si="1"/>
@@ -11714,7 +11723,7 @@
     <row r="67" spans="1:65">
       <c r="A67" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B67" t="str">
         <f t="shared" si="1"/>
@@ -11796,7 +11805,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B68" t="str">
         <f t="shared" ref="B68:B131" si="3">TEXT($C68, "HH:mm")</f>
@@ -11875,7 +11884,7 @@
     <row r="69" spans="1:65">
       <c r="A69" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B69" t="str">
         <f t="shared" si="3"/>
@@ -11954,7 +11963,7 @@
     <row r="70" spans="1:65">
       <c r="A70" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B70" t="str">
         <f t="shared" si="3"/>
@@ -12033,7 +12042,7 @@
     <row r="71" spans="1:65">
       <c r="A71" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B71" t="str">
         <f t="shared" si="3"/>
@@ -12112,7 +12121,7 @@
     <row r="72" spans="1:65">
       <c r="A72" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B72" t="str">
         <f t="shared" si="3"/>
@@ -12191,7 +12200,7 @@
     <row r="73" spans="1:65">
       <c r="A73" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B73" t="str">
         <f t="shared" si="3"/>
@@ -12270,7 +12279,7 @@
     <row r="74" spans="1:65">
       <c r="A74" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B74" t="str">
         <f t="shared" si="3"/>
@@ -12349,7 +12358,7 @@
     <row r="75" spans="1:65">
       <c r="A75" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B75" t="str">
         <f t="shared" si="3"/>
@@ -12428,7 +12437,7 @@
     <row r="76" spans="1:65">
       <c r="A76" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B76" t="str">
         <f t="shared" si="3"/>
@@ -12507,7 +12516,7 @@
     <row r="77" spans="1:65">
       <c r="A77" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B77" t="str">
         <f t="shared" si="3"/>
@@ -12586,7 +12595,7 @@
     <row r="78" spans="1:65">
       <c r="A78" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B78" t="str">
         <f t="shared" si="3"/>
@@ -12665,7 +12674,7 @@
     <row r="79" spans="1:65">
       <c r="A79" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B79" t="str">
         <f t="shared" si="3"/>
@@ -12744,7 +12753,7 @@
     <row r="80" spans="1:65">
       <c r="A80" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B80" t="str">
         <f t="shared" si="3"/>
@@ -12823,7 +12832,7 @@
     <row r="81" spans="1:65">
       <c r="A81" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B81" t="str">
         <f t="shared" si="3"/>
@@ -12902,7 +12911,7 @@
     <row r="82" spans="1:65">
       <c r="A82" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B82" t="str">
         <f t="shared" si="3"/>
@@ -12981,7 +12990,7 @@
     <row r="83" spans="1:65">
       <c r="A83" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B83" t="str">
         <f t="shared" si="3"/>
@@ -13060,7 +13069,7 @@
     <row r="84" spans="1:65">
       <c r="A84" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B84" t="str">
         <f t="shared" si="3"/>
@@ -13139,7 +13148,7 @@
     <row r="85" spans="1:65">
       <c r="A85" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B85" t="str">
         <f t="shared" si="3"/>
@@ -13218,7 +13227,7 @@
     <row r="86" spans="1:65">
       <c r="A86" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B86" t="str">
         <f t="shared" si="3"/>
@@ -13297,7 +13306,7 @@
     <row r="87" spans="1:65">
       <c r="A87" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B87" t="str">
         <f t="shared" si="3"/>
@@ -13376,7 +13385,7 @@
     <row r="88" spans="1:65">
       <c r="A88" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B88" t="str">
         <f t="shared" si="3"/>
@@ -13455,7 +13464,7 @@
     <row r="89" spans="1:65">
       <c r="A89" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B89" t="str">
         <f t="shared" si="3"/>
@@ -13534,7 +13543,7 @@
     <row r="90" spans="1:65">
       <c r="A90" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B90" t="str">
         <f t="shared" si="3"/>
@@ -13613,7 +13622,7 @@
     <row r="91" spans="1:65">
       <c r="A91" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B91" t="str">
         <f t="shared" si="3"/>
@@ -13692,7 +13701,7 @@
     <row r="92" spans="1:65">
       <c r="A92" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B92" t="str">
         <f t="shared" si="3"/>
@@ -13771,7 +13780,7 @@
     <row r="93" spans="1:65">
       <c r="A93" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B93" t="str">
         <f t="shared" si="3"/>
@@ -13850,7 +13859,7 @@
     <row r="94" spans="1:65">
       <c r="A94" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B94" t="str">
         <f t="shared" si="3"/>
@@ -13929,7 +13938,7 @@
     <row r="95" spans="1:65">
       <c r="A95" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B95" t="str">
         <f t="shared" si="3"/>
@@ -14008,7 +14017,7 @@
     <row r="96" spans="1:65">
       <c r="A96" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B96" t="str">
         <f t="shared" si="3"/>
@@ -14087,7 +14096,7 @@
     <row r="97" spans="1:65">
       <c r="A97" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B97" t="str">
         <f t="shared" si="3"/>
@@ -14166,7 +14175,7 @@
     <row r="98" spans="1:65">
       <c r="A98" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B98" t="str">
         <f t="shared" si="3"/>
@@ -14245,7 +14254,7 @@
     <row r="99" spans="1:65">
       <c r="A99" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B99" t="str">
         <f t="shared" si="3"/>
@@ -14324,7 +14333,7 @@
     <row r="100" spans="1:65">
       <c r="A100" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B100" t="str">
         <f t="shared" si="3"/>
@@ -14405,7 +14414,7 @@
     <row r="101" spans="1:65">
       <c r="A101" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B101" t="str">
         <f t="shared" si="3"/>
@@ -14484,7 +14493,7 @@
     <row r="102" spans="1:65">
       <c r="A102" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B102" t="str">
         <f t="shared" si="3"/>
@@ -14563,7 +14572,7 @@
     <row r="103" spans="1:65">
       <c r="A103" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B103" t="str">
         <f t="shared" si="3"/>
@@ -14642,7 +14651,7 @@
     <row r="104" spans="1:65">
       <c r="A104" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B104" t="str">
         <f t="shared" si="3"/>
@@ -14721,7 +14730,7 @@
     <row r="105" spans="1:65">
       <c r="A105" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B105" t="str">
         <f t="shared" si="3"/>
@@ -14800,7 +14809,7 @@
     <row r="106" spans="1:65">
       <c r="A106" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B106" t="str">
         <f t="shared" si="3"/>
@@ -14881,7 +14890,7 @@
     <row r="107" spans="1:65">
       <c r="A107" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B107" t="str">
         <f t="shared" si="3"/>
@@ -14962,7 +14971,7 @@
     <row r="108" spans="1:65">
       <c r="A108" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B108" t="str">
         <f t="shared" si="3"/>
@@ -15041,7 +15050,7 @@
     <row r="109" spans="1:65">
       <c r="A109" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B109" t="str">
         <f t="shared" si="3"/>
@@ -15120,7 +15129,7 @@
     <row r="110" spans="1:65">
       <c r="A110" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B110" t="str">
         <f t="shared" si="3"/>
@@ -15199,7 +15208,7 @@
     <row r="111" spans="1:65">
       <c r="A111" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B111" t="str">
         <f t="shared" si="3"/>
@@ -15278,7 +15287,7 @@
     <row r="112" spans="1:65">
       <c r="A112" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B112" t="str">
         <f t="shared" si="3"/>
@@ -15359,7 +15368,7 @@
     <row r="113" spans="1:65">
       <c r="A113" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B113" t="str">
         <f t="shared" si="3"/>
@@ -15438,7 +15447,7 @@
     <row r="114" spans="1:65">
       <c r="A114" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B114" t="str">
         <f t="shared" si="3"/>
@@ -15517,7 +15526,7 @@
     <row r="115" spans="1:65">
       <c r="A115" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B115" t="str">
         <f t="shared" si="3"/>
@@ -15596,7 +15605,7 @@
     <row r="116" spans="1:65">
       <c r="A116" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B116" t="str">
         <f t="shared" si="3"/>
@@ -15675,7 +15684,7 @@
     <row r="117" spans="1:65">
       <c r="A117" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B117" t="str">
         <f t="shared" si="3"/>
@@ -15754,7 +15763,7 @@
     <row r="118" spans="1:65">
       <c r="A118" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B118" t="str">
         <f t="shared" si="3"/>
@@ -15833,7 +15842,7 @@
     <row r="119" spans="1:65">
       <c r="A119" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B119" t="str">
         <f t="shared" si="3"/>
@@ -15912,7 +15921,7 @@
     <row r="120" spans="1:65">
       <c r="A120" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B120" t="str">
         <f t="shared" si="3"/>
@@ -15991,7 +16000,7 @@
     <row r="121" spans="1:65">
       <c r="A121" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B121" t="str">
         <f t="shared" si="3"/>
@@ -16070,7 +16079,7 @@
     <row r="122" spans="1:65">
       <c r="A122" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B122" t="str">
         <f t="shared" si="3"/>
@@ -16149,7 +16158,7 @@
     <row r="123" spans="1:65">
       <c r="A123" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B123" t="str">
         <f t="shared" si="3"/>
@@ -16228,7 +16237,7 @@
     <row r="124" spans="1:65">
       <c r="A124" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B124" t="str">
         <f t="shared" si="3"/>
@@ -16309,7 +16318,7 @@
     <row r="125" spans="1:65">
       <c r="A125" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B125" t="str">
         <f t="shared" si="3"/>
@@ -16390,7 +16399,7 @@
     <row r="126" spans="1:65">
       <c r="A126" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B126" t="str">
         <f t="shared" si="3"/>
@@ -16469,7 +16478,7 @@
     <row r="127" spans="1:65">
       <c r="A127" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B127" t="str">
         <f t="shared" si="3"/>
@@ -16548,7 +16557,7 @@
     <row r="128" spans="1:65">
       <c r="A128" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B128" t="str">
         <f t="shared" si="3"/>
@@ -16627,7 +16636,7 @@
     <row r="129" spans="1:65">
       <c r="A129" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B129" t="str">
         <f t="shared" si="3"/>
@@ -16706,7 +16715,7 @@
     <row r="130" spans="1:65">
       <c r="A130" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B130" t="str">
         <f t="shared" si="3"/>
@@ -16785,7 +16794,7 @@
     <row r="131" spans="1:65">
       <c r="A131" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B131" t="str">
         <f t="shared" si="3"/>
@@ -16867,7 +16876,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B132" t="str">
         <f t="shared" ref="B132:B168" si="5">TEXT($C132, "HH:mm")</f>
@@ -16946,7 +16955,7 @@
     <row r="133" spans="1:65">
       <c r="A133" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B133" t="str">
         <f t="shared" si="5"/>
@@ -17025,7 +17034,7 @@
     <row r="134" spans="1:65">
       <c r="A134" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B134" t="str">
         <f t="shared" si="5"/>
@@ -17104,7 +17113,7 @@
     <row r="135" spans="1:65">
       <c r="A135" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B135" t="str">
         <f t="shared" si="5"/>
@@ -17183,7 +17192,7 @@
     <row r="136" spans="1:65">
       <c r="A136" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B136" t="str">
         <f t="shared" si="5"/>
@@ -17264,7 +17273,7 @@
     <row r="137" spans="1:65">
       <c r="A137" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B137" t="str">
         <f t="shared" si="5"/>
@@ -17345,7 +17354,7 @@
     <row r="138" spans="1:65">
       <c r="A138" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B138" t="str">
         <f t="shared" si="5"/>
@@ -17424,7 +17433,7 @@
     <row r="139" spans="1:65">
       <c r="A139" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B139" t="str">
         <f t="shared" si="5"/>
@@ -17503,7 +17512,7 @@
     <row r="140" spans="1:65">
       <c r="A140" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B140" t="str">
         <f t="shared" si="5"/>
@@ -17582,7 +17591,7 @@
     <row r="141" spans="1:65">
       <c r="A141" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B141" t="str">
         <f t="shared" si="5"/>
@@ -17661,7 +17670,7 @@
     <row r="142" spans="1:65">
       <c r="A142" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B142" t="str">
         <f t="shared" si="5"/>
@@ -17740,7 +17749,7 @@
     <row r="143" spans="1:65">
       <c r="A143" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B143" t="str">
         <f t="shared" si="5"/>
@@ -17819,7 +17828,7 @@
     <row r="144" spans="1:65">
       <c r="A144" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B144" t="str">
         <f t="shared" si="5"/>
@@ -17898,7 +17907,7 @@
     <row r="145" spans="1:65">
       <c r="A145" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B145" t="str">
         <f t="shared" si="5"/>
@@ -17977,7 +17986,7 @@
     <row r="146" spans="1:65">
       <c r="A146" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B146" t="str">
         <f t="shared" si="5"/>
@@ -18056,7 +18065,7 @@
     <row r="147" spans="1:65">
       <c r="A147" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B147" t="str">
         <f t="shared" si="5"/>
@@ -18135,7 +18144,7 @@
     <row r="148" spans="1:65">
       <c r="A148" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B148" t="str">
         <f t="shared" si="5"/>
@@ -18216,7 +18225,7 @@
     <row r="149" spans="1:65">
       <c r="A149" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B149" t="str">
         <f t="shared" si="5"/>
@@ -18295,7 +18304,7 @@
     <row r="150" spans="1:65">
       <c r="A150" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B150" t="str">
         <f t="shared" si="5"/>
@@ -18374,7 +18383,7 @@
     <row r="151" spans="1:65">
       <c r="A151" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B151" t="str">
         <f t="shared" si="5"/>
@@ -18453,7 +18462,7 @@
     <row r="152" spans="1:65">
       <c r="A152" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B152" t="str">
         <f t="shared" si="5"/>
@@ -18532,7 +18541,7 @@
     <row r="153" spans="1:65">
       <c r="A153" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B153" t="str">
         <f t="shared" si="5"/>
@@ -18611,7 +18620,7 @@
     <row r="154" spans="1:65">
       <c r="A154" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B154" t="str">
         <f t="shared" si="5"/>
@@ -18690,7 +18699,7 @@
     <row r="155" spans="1:65">
       <c r="A155" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B155" t="str">
         <f t="shared" si="5"/>
@@ -18769,7 +18778,7 @@
     <row r="156" spans="1:65">
       <c r="A156" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B156" t="str">
         <f t="shared" si="5"/>
@@ -18848,7 +18857,7 @@
     <row r="157" spans="1:65">
       <c r="A157" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B157" t="str">
         <f t="shared" si="5"/>
@@ -18927,7 +18936,7 @@
     <row r="158" spans="1:65">
       <c r="A158" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B158" t="str">
         <f t="shared" si="5"/>
@@ -19006,7 +19015,7 @@
     <row r="159" spans="1:65">
       <c r="A159" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B159" t="str">
         <f t="shared" si="5"/>
@@ -19085,7 +19094,7 @@
     <row r="160" spans="1:65">
       <c r="A160" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B160" t="str">
         <f t="shared" si="5"/>
@@ -19164,7 +19173,7 @@
     <row r="161" spans="1:65">
       <c r="A161" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B161" t="str">
         <f t="shared" si="5"/>
@@ -19243,7 +19252,7 @@
     <row r="162" spans="1:65">
       <c r="A162" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B162" t="str">
         <f t="shared" si="5"/>
@@ -19322,7 +19331,7 @@
     <row r="163" spans="1:65">
       <c r="A163" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B163" t="str">
         <f t="shared" si="5"/>
@@ -19401,7 +19410,7 @@
     <row r="164" spans="1:65">
       <c r="A164" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B164" t="str">
         <f t="shared" si="5"/>
@@ -19480,7 +19489,7 @@
     <row r="165" spans="1:65">
       <c r="A165" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B165" t="str">
         <f t="shared" si="5"/>
@@ -19559,7 +19568,7 @@
     <row r="166" spans="1:65">
       <c r="A166" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B166" t="str">
         <f t="shared" si="5"/>
@@ -19640,7 +19649,7 @@
     <row r="167" spans="1:65">
       <c r="A167" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B167" t="str">
         <f t="shared" si="5"/>
@@ -19719,7 +19728,7 @@
     <row r="168" spans="1:65">
       <c r="A168" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B168" t="str">
         <f t="shared" si="5"/>
@@ -19801,7 +19810,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B169" t="str">
         <f>TEXT($C169, "HH:mm")</f>
@@ -19883,7 +19892,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B170" t="str">
         <f t="shared" ref="B170:B233" si="7">TEXT($C170, "HH:mm")</f>
@@ -19962,7 +19971,7 @@
     <row r="171" spans="1:65">
       <c r="A171" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B171" t="str">
         <f t="shared" si="7"/>
@@ -20041,7 +20050,7 @@
     <row r="172" spans="1:65">
       <c r="A172" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B172" t="str">
         <f t="shared" si="7"/>
@@ -20122,7 +20131,7 @@
     <row r="173" spans="1:65">
       <c r="A173" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B173" t="str">
         <f t="shared" si="7"/>
@@ -20201,7 +20210,7 @@
     <row r="174" spans="1:65">
       <c r="A174" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B174" t="str">
         <f t="shared" si="7"/>
@@ -20280,7 +20289,7 @@
     <row r="175" spans="1:65">
       <c r="A175" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B175" t="str">
         <f t="shared" si="7"/>
@@ -20359,7 +20368,7 @@
     <row r="176" spans="1:65">
       <c r="A176" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B176" t="str">
         <f t="shared" si="7"/>
@@ -20438,7 +20447,7 @@
     <row r="177" spans="1:65">
       <c r="A177" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B177" t="str">
         <f t="shared" si="7"/>
@@ -20517,7 +20526,7 @@
     <row r="178" spans="1:65">
       <c r="A178" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B178" t="str">
         <f t="shared" si="7"/>
@@ -20598,7 +20607,7 @@
     <row r="179" spans="1:65">
       <c r="A179" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B179" t="str">
         <f t="shared" si="7"/>
@@ -20677,7 +20686,7 @@
     <row r="180" spans="1:65">
       <c r="A180" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B180" t="str">
         <f t="shared" si="7"/>
@@ -20756,7 +20765,7 @@
     <row r="181" spans="1:65">
       <c r="A181" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B181" t="str">
         <f t="shared" si="7"/>
@@ -20837,7 +20846,7 @@
     <row r="182" spans="1:65">
       <c r="A182" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B182" t="str">
         <f t="shared" si="7"/>
@@ -20918,7 +20927,7 @@
     <row r="183" spans="1:65">
       <c r="A183" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B183" t="str">
         <f t="shared" si="7"/>
@@ -20999,7 +21008,7 @@
     <row r="184" spans="1:65">
       <c r="A184" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B184" t="str">
         <f t="shared" si="7"/>
@@ -21082,7 +21091,7 @@
     <row r="185" spans="1:65">
       <c r="A185" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B185" t="str">
         <f t="shared" si="7"/>
@@ -21163,7 +21172,7 @@
     <row r="186" spans="1:65">
       <c r="A186" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B186" t="str">
         <f t="shared" si="7"/>
@@ -21244,7 +21253,7 @@
     <row r="187" spans="1:65">
       <c r="A187" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B187" t="str">
         <f t="shared" si="7"/>
@@ -21325,7 +21334,7 @@
     <row r="188" spans="1:65">
       <c r="A188" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B188" t="str">
         <f t="shared" si="7"/>
@@ -21406,7 +21415,7 @@
     <row r="189" spans="1:65">
       <c r="A189" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B189" t="str">
         <f t="shared" si="7"/>
@@ -21487,7 +21496,7 @@
     <row r="190" spans="1:65">
       <c r="A190" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B190" t="str">
         <f t="shared" si="7"/>
@@ -21570,7 +21579,7 @@
     <row r="191" spans="1:65">
       <c r="A191" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B191" t="str">
         <f t="shared" si="7"/>
@@ -21653,7 +21662,7 @@
     <row r="192" spans="1:65">
       <c r="A192" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B192" t="str">
         <f t="shared" si="7"/>
@@ -21736,7 +21745,7 @@
     <row r="193" spans="1:65">
       <c r="A193" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B193" t="str">
         <f t="shared" si="7"/>
@@ -21819,7 +21828,7 @@
     <row r="194" spans="1:65">
       <c r="A194" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B194" t="str">
         <f t="shared" si="7"/>
@@ -21900,7 +21909,7 @@
     <row r="195" spans="1:65">
       <c r="A195" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B195" t="str">
         <f t="shared" si="7"/>
@@ -21981,7 +21990,7 @@
     <row r="196" spans="1:65">
       <c r="A196" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B196" t="str">
         <f t="shared" si="7"/>
@@ -22064,7 +22073,7 @@
     <row r="197" spans="1:65">
       <c r="A197" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B197" t="str">
         <f t="shared" si="7"/>
@@ -22143,7 +22152,7 @@
     <row r="198" spans="1:65">
       <c r="A198" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B198" t="str">
         <f t="shared" si="7"/>
@@ -22222,7 +22231,7 @@
     <row r="199" spans="1:65">
       <c r="A199" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B199" t="str">
         <f t="shared" si="7"/>
@@ -22301,7 +22310,7 @@
     <row r="200" spans="1:65">
       <c r="A200" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B200" t="str">
         <f t="shared" si="7"/>
@@ -22380,7 +22389,7 @@
     <row r="201" spans="1:65">
       <c r="A201" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B201" t="str">
         <f t="shared" si="7"/>
@@ -22459,7 +22468,7 @@
     <row r="202" spans="1:65">
       <c r="A202" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B202" t="str">
         <f t="shared" si="7"/>
@@ -22540,7 +22549,7 @@
     <row r="203" spans="1:65">
       <c r="A203" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B203" t="str">
         <f t="shared" si="7"/>
@@ -22619,7 +22628,7 @@
     <row r="204" spans="1:65">
       <c r="A204" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B204" t="str">
         <f t="shared" si="7"/>
@@ -22698,7 +22707,7 @@
     <row r="205" spans="1:65">
       <c r="A205" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B205" t="str">
         <f t="shared" si="7"/>
@@ -22777,7 +22786,7 @@
     <row r="206" spans="1:65">
       <c r="A206" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B206" t="str">
         <f t="shared" si="7"/>
@@ -22856,7 +22865,7 @@
     <row r="207" spans="1:65">
       <c r="A207" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B207" t="str">
         <f t="shared" si="7"/>
@@ -22935,7 +22944,7 @@
     <row r="208" spans="1:65">
       <c r="A208" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B208" t="str">
         <f t="shared" si="7"/>
@@ -23016,7 +23025,7 @@
     <row r="209" spans="1:65">
       <c r="A209" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B209" t="str">
         <f t="shared" si="7"/>
@@ -23095,7 +23104,7 @@
     <row r="210" spans="1:65">
       <c r="A210" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B210" t="str">
         <f t="shared" si="7"/>
@@ -23174,7 +23183,7 @@
     <row r="211" spans="1:65">
       <c r="A211" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B211" t="str">
         <f t="shared" si="7"/>
@@ -23255,7 +23264,7 @@
     <row r="212" spans="1:65">
       <c r="A212" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B212" t="str">
         <f t="shared" si="7"/>
@@ -23334,7 +23343,7 @@
     <row r="213" spans="1:65">
       <c r="A213" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B213" t="str">
         <f t="shared" si="7"/>
@@ -23413,7 +23422,7 @@
     <row r="214" spans="1:65">
       <c r="A214" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B214" t="str">
         <f t="shared" si="7"/>
@@ -23492,7 +23501,7 @@
     <row r="215" spans="1:65">
       <c r="A215" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B215" t="str">
         <f t="shared" si="7"/>
@@ -23571,7 +23580,7 @@
     <row r="216" spans="1:65">
       <c r="A216" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B216" t="str">
         <f t="shared" si="7"/>
@@ -23650,7 +23659,7 @@
     <row r="217" spans="1:65">
       <c r="A217" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B217" t="str">
         <f t="shared" si="7"/>
@@ -23729,7 +23738,7 @@
     <row r="218" spans="1:65">
       <c r="A218" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B218" t="str">
         <f t="shared" si="7"/>
@@ -23808,7 +23817,7 @@
     <row r="219" spans="1:65">
       <c r="A219" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B219" t="str">
         <f t="shared" si="7"/>
@@ -23887,7 +23896,7 @@
     <row r="220" spans="1:65">
       <c r="A220" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B220" t="str">
         <f t="shared" si="7"/>
@@ -23968,7 +23977,7 @@
     <row r="221" spans="1:65">
       <c r="A221" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B221" t="str">
         <f t="shared" si="7"/>
@@ -24047,7 +24056,7 @@
     <row r="222" spans="1:65">
       <c r="A222" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B222" t="str">
         <f t="shared" si="7"/>
@@ -24126,7 +24135,7 @@
     <row r="223" spans="1:65">
       <c r="A223" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B223" t="str">
         <f t="shared" si="7"/>
@@ -24205,7 +24214,7 @@
     <row r="224" spans="1:65">
       <c r="A224" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B224" t="str">
         <f t="shared" si="7"/>
@@ -24284,7 +24293,7 @@
     <row r="225" spans="1:65">
       <c r="A225" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B225" t="str">
         <f t="shared" si="7"/>
@@ -24363,7 +24372,7 @@
     <row r="226" spans="1:65">
       <c r="A226" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B226" t="str">
         <f t="shared" si="7"/>
@@ -24442,7 +24451,7 @@
     <row r="227" spans="1:65">
       <c r="A227" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B227" t="str">
         <f t="shared" si="7"/>
@@ -24521,7 +24530,7 @@
     <row r="228" spans="1:65">
       <c r="A228" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B228" t="str">
         <f t="shared" si="7"/>
@@ -24600,7 +24609,7 @@
     <row r="229" spans="1:65">
       <c r="A229" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B229" t="str">
         <f t="shared" si="7"/>
@@ -24679,7 +24688,7 @@
     <row r="230" spans="1:65">
       <c r="A230" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B230" t="str">
         <f t="shared" si="7"/>
@@ -24758,7 +24767,7 @@
     <row r="231" spans="1:65">
       <c r="A231" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B231" t="str">
         <f t="shared" si="7"/>
@@ -24837,7 +24846,7 @@
     <row r="232" spans="1:65">
       <c r="A232" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B232" t="str">
         <f t="shared" si="7"/>
@@ -24916,7 +24925,7 @@
     <row r="233" spans="1:65">
       <c r="A233" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B233" t="str">
         <f t="shared" si="7"/>
@@ -24998,7 +25007,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B234" t="str">
         <f t="shared" ref="B234:B291" si="9">TEXT($C234, "HH:mm")</f>
@@ -25077,7 +25086,7 @@
     <row r="235" spans="1:65">
       <c r="A235" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B235" t="str">
         <f t="shared" si="9"/>
@@ -25156,7 +25165,7 @@
     <row r="236" spans="1:65">
       <c r="A236" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B236" t="str">
         <f t="shared" si="9"/>
@@ -25235,7 +25244,7 @@
     <row r="237" spans="1:65">
       <c r="A237" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B237" t="str">
         <f t="shared" si="9"/>
@@ -25314,7 +25323,7 @@
     <row r="238" spans="1:65">
       <c r="A238" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B238" t="str">
         <f t="shared" si="9"/>
@@ -25393,7 +25402,7 @@
     <row r="239" spans="1:65">
       <c r="A239" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B239" t="str">
         <f t="shared" si="9"/>
@@ -25472,7 +25481,7 @@
     <row r="240" spans="1:65">
       <c r="A240" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B240" t="str">
         <f t="shared" si="9"/>
@@ -25551,7 +25560,7 @@
     <row r="241" spans="1:65">
       <c r="A241" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B241" t="str">
         <f t="shared" si="9"/>
@@ -25630,7 +25639,7 @@
     <row r="242" spans="1:65">
       <c r="A242" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B242" t="str">
         <f t="shared" si="9"/>
@@ -25709,7 +25718,7 @@
     <row r="243" spans="1:65">
       <c r="A243" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B243" t="str">
         <f t="shared" si="9"/>
@@ -25788,7 +25797,7 @@
     <row r="244" spans="1:65">
       <c r="A244" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B244" t="str">
         <f t="shared" si="9"/>
@@ -25867,7 +25876,7 @@
     <row r="245" spans="1:65">
       <c r="A245" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B245" t="str">
         <f t="shared" si="9"/>
@@ -25946,7 +25955,7 @@
     <row r="246" spans="1:65">
       <c r="A246" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B246" t="str">
         <f t="shared" si="9"/>
@@ -26025,7 +26034,7 @@
     <row r="247" spans="1:65">
       <c r="A247" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B247" t="str">
         <f t="shared" si="9"/>
@@ -26104,7 +26113,7 @@
     <row r="248" spans="1:65">
       <c r="A248" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B248" t="str">
         <f t="shared" si="9"/>
@@ -26183,7 +26192,7 @@
     <row r="249" spans="1:65">
       <c r="A249" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B249" t="str">
         <f t="shared" si="9"/>
@@ -26262,7 +26271,7 @@
     <row r="250" spans="1:65">
       <c r="A250" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B250" t="str">
         <f t="shared" si="9"/>
@@ -26341,7 +26350,7 @@
     <row r="251" spans="1:65">
       <c r="A251" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B251" t="str">
         <f t="shared" si="9"/>
@@ -26420,7 +26429,7 @@
     <row r="252" spans="1:65">
       <c r="A252" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B252" t="str">
         <f t="shared" si="9"/>
@@ -26499,7 +26508,7 @@
     <row r="253" spans="1:65">
       <c r="A253" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B253" t="str">
         <f t="shared" si="9"/>
@@ -26578,7 +26587,7 @@
     <row r="254" spans="1:65">
       <c r="A254" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B254" t="str">
         <f t="shared" si="9"/>
@@ -26657,7 +26666,7 @@
     <row r="255" spans="1:65">
       <c r="A255" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B255" t="str">
         <f t="shared" si="9"/>
@@ -26736,7 +26745,7 @@
     <row r="256" spans="1:65">
       <c r="A256" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B256" t="str">
         <f t="shared" si="9"/>
@@ -26815,7 +26824,7 @@
     <row r="257" spans="1:65">
       <c r="A257" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B257" t="str">
         <f t="shared" si="9"/>
@@ -26894,7 +26903,7 @@
     <row r="258" spans="1:65">
       <c r="A258" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B258" t="str">
         <f t="shared" si="9"/>
@@ -26973,7 +26982,7 @@
     <row r="259" spans="1:65">
       <c r="A259" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B259" t="str">
         <f t="shared" si="9"/>
@@ -27052,7 +27061,7 @@
     <row r="260" spans="1:65">
       <c r="A260" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B260" t="str">
         <f t="shared" si="9"/>
@@ -27131,7 +27140,7 @@
     <row r="261" spans="1:65">
       <c r="A261" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B261" t="str">
         <f t="shared" si="9"/>
@@ -27210,7 +27219,7 @@
     <row r="262" spans="1:65">
       <c r="A262" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B262" t="str">
         <f t="shared" si="9"/>
@@ -27289,7 +27298,7 @@
     <row r="263" spans="1:65">
       <c r="A263" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B263" t="str">
         <f t="shared" si="9"/>
@@ -27368,7 +27377,7 @@
     <row r="264" spans="1:65">
       <c r="A264" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B264" t="str">
         <f t="shared" si="9"/>
@@ -27447,7 +27456,7 @@
     <row r="265" spans="1:65">
       <c r="A265" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B265" t="str">
         <f t="shared" si="9"/>
@@ -27526,7 +27535,7 @@
     <row r="266" spans="1:65">
       <c r="A266" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B266" t="str">
         <f t="shared" si="9"/>
@@ -27605,7 +27614,7 @@
     <row r="267" spans="1:65">
       <c r="A267" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B267" t="str">
         <f t="shared" si="9"/>
@@ -27684,7 +27693,7 @@
     <row r="268" spans="1:65">
       <c r="A268" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B268" t="str">
         <f t="shared" si="9"/>
@@ -27763,7 +27772,7 @@
     <row r="269" spans="1:65">
       <c r="A269" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B269" t="str">
         <f t="shared" si="9"/>
@@ -27842,7 +27851,7 @@
     <row r="270" spans="1:65">
       <c r="A270" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B270" t="str">
         <f t="shared" si="9"/>
@@ -27921,7 +27930,7 @@
     <row r="271" spans="1:65">
       <c r="A271" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B271" t="str">
         <f t="shared" si="9"/>
@@ -28000,7 +28009,7 @@
     <row r="272" spans="1:65">
       <c r="A272" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B272" t="str">
         <f t="shared" si="9"/>
@@ -28079,7 +28088,7 @@
     <row r="273" spans="1:65">
       <c r="A273" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B273" t="str">
         <f t="shared" si="9"/>
@@ -28158,7 +28167,7 @@
     <row r="274" spans="1:65">
       <c r="A274" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B274" t="str">
         <f t="shared" si="9"/>
@@ -28237,7 +28246,7 @@
     <row r="275" spans="1:65">
       <c r="A275" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B275" t="str">
         <f t="shared" si="9"/>
@@ -28316,7 +28325,7 @@
     <row r="276" spans="1:65">
       <c r="A276" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B276" t="str">
         <f t="shared" si="9"/>
@@ -28395,7 +28404,7 @@
     <row r="277" spans="1:65">
       <c r="A277" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B277" t="str">
         <f t="shared" si="9"/>
@@ -28474,7 +28483,7 @@
     <row r="278" spans="1:65">
       <c r="A278" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B278" t="str">
         <f t="shared" si="9"/>
@@ -28553,7 +28562,7 @@
     <row r="279" spans="1:65">
       <c r="A279" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B279" t="str">
         <f t="shared" si="9"/>
@@ -28632,7 +28641,7 @@
     <row r="280" spans="1:65">
       <c r="A280" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B280" t="str">
         <f t="shared" si="9"/>
@@ -28711,7 +28720,7 @@
     <row r="281" spans="1:65">
       <c r="A281" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B281" t="str">
         <f t="shared" si="9"/>
@@ -28790,7 +28799,7 @@
     <row r="282" spans="1:65">
       <c r="A282" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B282" t="str">
         <f t="shared" si="9"/>
@@ -28869,7 +28878,7 @@
     <row r="283" spans="1:65">
       <c r="A283" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B283" t="str">
         <f t="shared" si="9"/>
@@ -28948,7 +28957,7 @@
     <row r="284" spans="1:65">
       <c r="A284" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B284" t="str">
         <f t="shared" si="9"/>
@@ -29027,7 +29036,7 @@
     <row r="285" spans="1:65">
       <c r="A285" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B285" t="str">
         <f t="shared" si="9"/>
@@ -29106,7 +29115,7 @@
     <row r="286" spans="1:65">
       <c r="A286" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B286" t="str">
         <f t="shared" si="9"/>
@@ -29185,7 +29194,7 @@
     <row r="287" spans="1:65">
       <c r="A287" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B287" t="str">
         <f t="shared" si="9"/>
@@ -29264,7 +29273,7 @@
     <row r="288" spans="1:65">
       <c r="A288" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B288" t="str">
         <f t="shared" si="9"/>
@@ -29343,7 +29352,7 @@
     <row r="289" spans="1:65">
       <c r="A289" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B289" t="str">
         <f t="shared" si="9"/>
@@ -29422,7 +29431,7 @@
     <row r="290" spans="1:65">
       <c r="A290" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B290" t="str">
         <f t="shared" si="9"/>
@@ -29501,7 +29510,7 @@
     <row r="291" spans="1:65">
       <c r="A291" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:15</v>
+        <v>02:20</v>
       </c>
       <c r="B291" t="str">
         <f t="shared" si="9"/>

--- a/Vite-Vercel開発.xlsx
+++ b/Vite-Vercel開発.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2c67ec30e06f060f/work/GitHub/work-time-tracker/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{1928CA11-C4AD-40E9-B1C5-143667E830EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89CC501B-06AB-4281-BEA1-7A52FD14E733}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{1928CA11-C4AD-40E9-B1C5-143667E830EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F3E0FBC-1262-4039-B607-4C53D5B1F725}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1552" uniqueCount="929">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1553" uniqueCount="929">
   <si>
     <t>npm install -g vercel</t>
     <phoneticPr fontId="1"/>
@@ -6166,7 +6166,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{083174DA-A42C-4F9C-978E-61AEAAD9DDFF}">
-  <dimension ref="B2:D34"/>
+  <dimension ref="B2:D35"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
@@ -6343,6 +6343,11 @@
     </row>
     <row r="34" spans="3:3">
       <c r="C34" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="35" spans="3:3">
+      <c r="C35" t="s">
         <v>928</v>
       </c>
     </row>
@@ -6510,7 +6515,7 @@
       MOD(NOW(),1),
       TIME(0,5,0)
     ),"HH:mm")</f>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B2" s="19"/>
       <c r="D2" s="1">
@@ -6521,7 +6526,7 @@
     <row r="3" spans="1:65">
       <c r="A3" s="19" t="str">
         <f ca="1">TEXT(NOW(),"HH:mm")</f>
-        <v>02:22</v>
+        <v>02:25</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="17" t="s">
@@ -6720,7 +6725,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B4" t="str">
         <f t="shared" ref="B4:B67" si="1">TEXT($C4, "HH:mm")</f>
@@ -6799,7 +6804,7 @@
     <row r="5" spans="1:65">
       <c r="A5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B5" t="str">
         <f t="shared" si="1"/>
@@ -6878,7 +6883,7 @@
     <row r="6" spans="1:65">
       <c r="A6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B6" t="str">
         <f t="shared" si="1"/>
@@ -6957,7 +6962,7 @@
     <row r="7" spans="1:65">
       <c r="A7" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B7" t="str">
         <f t="shared" si="1"/>
@@ -7036,7 +7041,7 @@
     <row r="8" spans="1:65">
       <c r="A8" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B8" t="str">
         <f t="shared" si="1"/>
@@ -7115,7 +7120,7 @@
     <row r="9" spans="1:65">
       <c r="A9" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B9" t="str">
         <f t="shared" si="1"/>
@@ -7194,7 +7199,7 @@
     <row r="10" spans="1:65">
       <c r="A10" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B10" t="str">
         <f t="shared" si="1"/>
@@ -7273,7 +7278,7 @@
     <row r="11" spans="1:65">
       <c r="A11" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B11" t="str">
         <f t="shared" si="1"/>
@@ -7352,7 +7357,7 @@
     <row r="12" spans="1:65">
       <c r="A12" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B12" t="str">
         <f t="shared" si="1"/>
@@ -7431,7 +7436,7 @@
     <row r="13" spans="1:65">
       <c r="A13" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B13" t="str">
         <f t="shared" si="1"/>
@@ -7510,7 +7515,7 @@
     <row r="14" spans="1:65">
       <c r="A14" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B14" t="str">
         <f t="shared" si="1"/>
@@ -7589,7 +7594,7 @@
     <row r="15" spans="1:65">
       <c r="A15" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B15" t="str">
         <f t="shared" si="1"/>
@@ -7668,7 +7673,7 @@
     <row r="16" spans="1:65">
       <c r="A16" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B16" t="str">
         <f t="shared" si="1"/>
@@ -7747,7 +7752,7 @@
     <row r="17" spans="1:65">
       <c r="A17" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B17" t="str">
         <f t="shared" si="1"/>
@@ -7826,7 +7831,7 @@
     <row r="18" spans="1:65">
       <c r="A18" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B18" t="str">
         <f t="shared" si="1"/>
@@ -7905,7 +7910,7 @@
     <row r="19" spans="1:65">
       <c r="A19" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B19" t="str">
         <f t="shared" si="1"/>
@@ -7984,7 +7989,7 @@
     <row r="20" spans="1:65">
       <c r="A20" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B20" t="str">
         <f t="shared" si="1"/>
@@ -8063,7 +8068,7 @@
     <row r="21" spans="1:65">
       <c r="A21" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B21" t="str">
         <f t="shared" si="1"/>
@@ -8142,7 +8147,7 @@
     <row r="22" spans="1:65">
       <c r="A22" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B22" t="str">
         <f t="shared" si="1"/>
@@ -8221,7 +8226,7 @@
     <row r="23" spans="1:65">
       <c r="A23" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B23" t="str">
         <f t="shared" si="1"/>
@@ -8300,7 +8305,7 @@
     <row r="24" spans="1:65">
       <c r="A24" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B24" t="str">
         <f t="shared" si="1"/>
@@ -8379,7 +8384,7 @@
     <row r="25" spans="1:65">
       <c r="A25" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B25" t="str">
         <f t="shared" si="1"/>
@@ -8458,7 +8463,7 @@
     <row r="26" spans="1:65">
       <c r="A26" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B26" t="str">
         <f t="shared" si="1"/>
@@ -8537,7 +8542,7 @@
     <row r="27" spans="1:65">
       <c r="A27" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B27" t="str">
         <f t="shared" si="1"/>
@@ -8616,7 +8621,7 @@
     <row r="28" spans="1:65">
       <c r="A28" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B28" t="str">
         <f t="shared" si="1"/>
@@ -8697,7 +8702,7 @@
     <row r="29" spans="1:65">
       <c r="A29" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B29" t="str">
         <f t="shared" si="1"/>
@@ -8778,7 +8783,7 @@
     <row r="30" spans="1:65">
       <c r="A30" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B30" t="str">
         <f t="shared" si="1"/>
@@ -8859,7 +8864,7 @@
     <row r="31" spans="1:65">
       <c r="A31" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B31" t="str">
         <f t="shared" si="1"/>
@@ -8938,7 +8943,7 @@
     <row r="32" spans="1:65">
       <c r="A32" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B32" t="str">
         <f t="shared" si="1"/>
@@ -9017,7 +9022,7 @@
     <row r="33" spans="1:65">
       <c r="A33" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B33" t="str">
         <f t="shared" si="1"/>
@@ -9096,7 +9101,7 @@
     <row r="34" spans="1:65">
       <c r="A34" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B34" t="str">
         <f t="shared" si="1"/>
@@ -9177,7 +9182,7 @@
     <row r="35" spans="1:65">
       <c r="A35" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B35" t="str">
         <f t="shared" si="1"/>
@@ -9258,7 +9263,7 @@
     <row r="36" spans="1:65">
       <c r="A36" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B36" t="str">
         <f t="shared" si="1"/>
@@ -9339,7 +9344,7 @@
     <row r="37" spans="1:65">
       <c r="A37" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B37" t="str">
         <f t="shared" si="1"/>
@@ -9418,7 +9423,7 @@
     <row r="38" spans="1:65">
       <c r="A38" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B38" t="str">
         <f t="shared" si="1"/>
@@ -9497,7 +9502,7 @@
     <row r="39" spans="1:65">
       <c r="A39" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B39" t="str">
         <f t="shared" si="1"/>
@@ -9576,7 +9581,7 @@
     <row r="40" spans="1:65">
       <c r="A40" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B40" t="str">
         <f t="shared" si="1"/>
@@ -9655,7 +9660,7 @@
     <row r="41" spans="1:65">
       <c r="A41" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B41" t="str">
         <f t="shared" si="1"/>
@@ -9734,7 +9739,7 @@
     <row r="42" spans="1:65">
       <c r="A42" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B42" t="str">
         <f t="shared" si="1"/>
@@ -9815,7 +9820,7 @@
     <row r="43" spans="1:65">
       <c r="A43" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B43" t="str">
         <f t="shared" si="1"/>
@@ -9896,7 +9901,7 @@
     <row r="44" spans="1:65">
       <c r="A44" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B44" t="str">
         <f t="shared" si="1"/>
@@ -9975,7 +9980,7 @@
     <row r="45" spans="1:65">
       <c r="A45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B45" t="str">
         <f t="shared" si="1"/>
@@ -10054,7 +10059,7 @@
     <row r="46" spans="1:65">
       <c r="A46" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B46" t="str">
         <f t="shared" si="1"/>
@@ -10133,7 +10138,7 @@
     <row r="47" spans="1:65">
       <c r="A47" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B47" t="str">
         <f t="shared" si="1"/>
@@ -10212,7 +10217,7 @@
     <row r="48" spans="1:65">
       <c r="A48" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B48" t="str">
         <f t="shared" si="1"/>
@@ -10291,7 +10296,7 @@
     <row r="49" spans="1:65">
       <c r="A49" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B49" t="str">
         <f t="shared" si="1"/>
@@ -10372,7 +10377,7 @@
     <row r="50" spans="1:65">
       <c r="A50" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B50" t="str">
         <f t="shared" si="1"/>
@@ -10453,7 +10458,7 @@
     <row r="51" spans="1:65">
       <c r="A51" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B51" t="str">
         <f t="shared" si="1"/>
@@ -10532,7 +10537,7 @@
     <row r="52" spans="1:65">
       <c r="A52" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B52" t="str">
         <f t="shared" si="1"/>
@@ -10611,7 +10616,7 @@
     <row r="53" spans="1:65">
       <c r="A53" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B53" t="str">
         <f t="shared" si="1"/>
@@ -10690,7 +10695,7 @@
     <row r="54" spans="1:65">
       <c r="A54" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B54" t="str">
         <f t="shared" si="1"/>
@@ -10769,7 +10774,7 @@
     <row r="55" spans="1:65">
       <c r="A55" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B55" t="str">
         <f t="shared" si="1"/>
@@ -10848,7 +10853,7 @@
     <row r="56" spans="1:65">
       <c r="A56" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B56" t="str">
         <f t="shared" si="1"/>
@@ -10929,7 +10934,7 @@
     <row r="57" spans="1:65">
       <c r="A57" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B57" t="str">
         <f t="shared" si="1"/>
@@ -11008,7 +11013,7 @@
     <row r="58" spans="1:65">
       <c r="A58" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B58" t="str">
         <f t="shared" si="1"/>
@@ -11089,7 +11094,7 @@
     <row r="59" spans="1:65">
       <c r="A59" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B59" t="str">
         <f t="shared" si="1"/>
@@ -11168,7 +11173,7 @@
     <row r="60" spans="1:65">
       <c r="A60" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B60" t="str">
         <f t="shared" si="1"/>
@@ -11247,7 +11252,7 @@
     <row r="61" spans="1:65">
       <c r="A61" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B61" t="str">
         <f t="shared" si="1"/>
@@ -11326,7 +11331,7 @@
     <row r="62" spans="1:65">
       <c r="A62" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B62" t="str">
         <f t="shared" si="1"/>
@@ -11405,7 +11410,7 @@
     <row r="63" spans="1:65">
       <c r="A63" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B63" t="str">
         <f t="shared" si="1"/>
@@ -11484,7 +11489,7 @@
     <row r="64" spans="1:65">
       <c r="A64" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B64" t="str">
         <f t="shared" si="1"/>
@@ -11565,7 +11570,7 @@
     <row r="65" spans="1:65">
       <c r="A65" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B65" t="str">
         <f t="shared" si="1"/>
@@ -11644,7 +11649,7 @@
     <row r="66" spans="1:65">
       <c r="A66" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B66" t="str">
         <f t="shared" si="1"/>
@@ -11723,7 +11728,7 @@
     <row r="67" spans="1:65">
       <c r="A67" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B67" t="str">
         <f t="shared" si="1"/>
@@ -11805,7 +11810,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B68" t="str">
         <f t="shared" ref="B68:B131" si="3">TEXT($C68, "HH:mm")</f>
@@ -11884,7 +11889,7 @@
     <row r="69" spans="1:65">
       <c r="A69" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B69" t="str">
         <f t="shared" si="3"/>
@@ -11963,7 +11968,7 @@
     <row r="70" spans="1:65">
       <c r="A70" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B70" t="str">
         <f t="shared" si="3"/>
@@ -12042,7 +12047,7 @@
     <row r="71" spans="1:65">
       <c r="A71" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B71" t="str">
         <f t="shared" si="3"/>
@@ -12121,7 +12126,7 @@
     <row r="72" spans="1:65">
       <c r="A72" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B72" t="str">
         <f t="shared" si="3"/>
@@ -12200,7 +12205,7 @@
     <row r="73" spans="1:65">
       <c r="A73" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B73" t="str">
         <f t="shared" si="3"/>
@@ -12279,7 +12284,7 @@
     <row r="74" spans="1:65">
       <c r="A74" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B74" t="str">
         <f t="shared" si="3"/>
@@ -12358,7 +12363,7 @@
     <row r="75" spans="1:65">
       <c r="A75" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B75" t="str">
         <f t="shared" si="3"/>
@@ -12437,7 +12442,7 @@
     <row r="76" spans="1:65">
       <c r="A76" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B76" t="str">
         <f t="shared" si="3"/>
@@ -12516,7 +12521,7 @@
     <row r="77" spans="1:65">
       <c r="A77" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B77" t="str">
         <f t="shared" si="3"/>
@@ -12595,7 +12600,7 @@
     <row r="78" spans="1:65">
       <c r="A78" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B78" t="str">
         <f t="shared" si="3"/>
@@ -12674,7 +12679,7 @@
     <row r="79" spans="1:65">
       <c r="A79" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B79" t="str">
         <f t="shared" si="3"/>
@@ -12753,7 +12758,7 @@
     <row r="80" spans="1:65">
       <c r="A80" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B80" t="str">
         <f t="shared" si="3"/>
@@ -12832,7 +12837,7 @@
     <row r="81" spans="1:65">
       <c r="A81" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B81" t="str">
         <f t="shared" si="3"/>
@@ -12911,7 +12916,7 @@
     <row r="82" spans="1:65">
       <c r="A82" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B82" t="str">
         <f t="shared" si="3"/>
@@ -12990,7 +12995,7 @@
     <row r="83" spans="1:65">
       <c r="A83" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B83" t="str">
         <f t="shared" si="3"/>
@@ -13069,7 +13074,7 @@
     <row r="84" spans="1:65">
       <c r="A84" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B84" t="str">
         <f t="shared" si="3"/>
@@ -13148,7 +13153,7 @@
     <row r="85" spans="1:65">
       <c r="A85" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B85" t="str">
         <f t="shared" si="3"/>
@@ -13227,7 +13232,7 @@
     <row r="86" spans="1:65">
       <c r="A86" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B86" t="str">
         <f t="shared" si="3"/>
@@ -13306,7 +13311,7 @@
     <row r="87" spans="1:65">
       <c r="A87" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B87" t="str">
         <f t="shared" si="3"/>
@@ -13385,7 +13390,7 @@
     <row r="88" spans="1:65">
       <c r="A88" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B88" t="str">
         <f t="shared" si="3"/>
@@ -13464,7 +13469,7 @@
     <row r="89" spans="1:65">
       <c r="A89" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B89" t="str">
         <f t="shared" si="3"/>
@@ -13543,7 +13548,7 @@
     <row r="90" spans="1:65">
       <c r="A90" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B90" t="str">
         <f t="shared" si="3"/>
@@ -13622,7 +13627,7 @@
     <row r="91" spans="1:65">
       <c r="A91" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B91" t="str">
         <f t="shared" si="3"/>
@@ -13701,7 +13706,7 @@
     <row r="92" spans="1:65">
       <c r="A92" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B92" t="str">
         <f t="shared" si="3"/>
@@ -13780,7 +13785,7 @@
     <row r="93" spans="1:65">
       <c r="A93" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B93" t="str">
         <f t="shared" si="3"/>
@@ -13859,7 +13864,7 @@
     <row r="94" spans="1:65">
       <c r="A94" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B94" t="str">
         <f t="shared" si="3"/>
@@ -13938,7 +13943,7 @@
     <row r="95" spans="1:65">
       <c r="A95" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B95" t="str">
         <f t="shared" si="3"/>
@@ -14017,7 +14022,7 @@
     <row r="96" spans="1:65">
       <c r="A96" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B96" t="str">
         <f t="shared" si="3"/>
@@ -14096,7 +14101,7 @@
     <row r="97" spans="1:65">
       <c r="A97" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B97" t="str">
         <f t="shared" si="3"/>
@@ -14175,7 +14180,7 @@
     <row r="98" spans="1:65">
       <c r="A98" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B98" t="str">
         <f t="shared" si="3"/>
@@ -14254,7 +14259,7 @@
     <row r="99" spans="1:65">
       <c r="A99" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B99" t="str">
         <f t="shared" si="3"/>
@@ -14333,7 +14338,7 @@
     <row r="100" spans="1:65">
       <c r="A100" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B100" t="str">
         <f t="shared" si="3"/>
@@ -14414,7 +14419,7 @@
     <row r="101" spans="1:65">
       <c r="A101" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B101" t="str">
         <f t="shared" si="3"/>
@@ -14493,7 +14498,7 @@
     <row r="102" spans="1:65">
       <c r="A102" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B102" t="str">
         <f t="shared" si="3"/>
@@ -14572,7 +14577,7 @@
     <row r="103" spans="1:65">
       <c r="A103" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B103" t="str">
         <f t="shared" si="3"/>
@@ -14651,7 +14656,7 @@
     <row r="104" spans="1:65">
       <c r="A104" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B104" t="str">
         <f t="shared" si="3"/>
@@ -14730,7 +14735,7 @@
     <row r="105" spans="1:65">
       <c r="A105" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B105" t="str">
         <f t="shared" si="3"/>
@@ -14809,7 +14814,7 @@
     <row r="106" spans="1:65">
       <c r="A106" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B106" t="str">
         <f t="shared" si="3"/>
@@ -14890,7 +14895,7 @@
     <row r="107" spans="1:65">
       <c r="A107" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B107" t="str">
         <f t="shared" si="3"/>
@@ -14971,7 +14976,7 @@
     <row r="108" spans="1:65">
       <c r="A108" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B108" t="str">
         <f t="shared" si="3"/>
@@ -15050,7 +15055,7 @@
     <row r="109" spans="1:65">
       <c r="A109" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B109" t="str">
         <f t="shared" si="3"/>
@@ -15129,7 +15134,7 @@
     <row r="110" spans="1:65">
       <c r="A110" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B110" t="str">
         <f t="shared" si="3"/>
@@ -15208,7 +15213,7 @@
     <row r="111" spans="1:65">
       <c r="A111" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B111" t="str">
         <f t="shared" si="3"/>
@@ -15287,7 +15292,7 @@
     <row r="112" spans="1:65">
       <c r="A112" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B112" t="str">
         <f t="shared" si="3"/>
@@ -15368,7 +15373,7 @@
     <row r="113" spans="1:65">
       <c r="A113" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B113" t="str">
         <f t="shared" si="3"/>
@@ -15447,7 +15452,7 @@
     <row r="114" spans="1:65">
       <c r="A114" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B114" t="str">
         <f t="shared" si="3"/>
@@ -15526,7 +15531,7 @@
     <row r="115" spans="1:65">
       <c r="A115" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B115" t="str">
         <f t="shared" si="3"/>
@@ -15605,7 +15610,7 @@
     <row r="116" spans="1:65">
       <c r="A116" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B116" t="str">
         <f t="shared" si="3"/>
@@ -15684,7 +15689,7 @@
     <row r="117" spans="1:65">
       <c r="A117" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B117" t="str">
         <f t="shared" si="3"/>
@@ -15763,7 +15768,7 @@
     <row r="118" spans="1:65">
       <c r="A118" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B118" t="str">
         <f t="shared" si="3"/>
@@ -15842,7 +15847,7 @@
     <row r="119" spans="1:65">
       <c r="A119" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B119" t="str">
         <f t="shared" si="3"/>
@@ -15921,7 +15926,7 @@
     <row r="120" spans="1:65">
       <c r="A120" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B120" t="str">
         <f t="shared" si="3"/>
@@ -16000,7 +16005,7 @@
     <row r="121" spans="1:65">
       <c r="A121" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B121" t="str">
         <f t="shared" si="3"/>
@@ -16079,7 +16084,7 @@
     <row r="122" spans="1:65">
       <c r="A122" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B122" t="str">
         <f t="shared" si="3"/>
@@ -16158,7 +16163,7 @@
     <row r="123" spans="1:65">
       <c r="A123" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B123" t="str">
         <f t="shared" si="3"/>
@@ -16237,7 +16242,7 @@
     <row r="124" spans="1:65">
       <c r="A124" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B124" t="str">
         <f t="shared" si="3"/>
@@ -16318,7 +16323,7 @@
     <row r="125" spans="1:65">
       <c r="A125" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B125" t="str">
         <f t="shared" si="3"/>
@@ -16399,7 +16404,7 @@
     <row r="126" spans="1:65">
       <c r="A126" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B126" t="str">
         <f t="shared" si="3"/>
@@ -16478,7 +16483,7 @@
     <row r="127" spans="1:65">
       <c r="A127" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B127" t="str">
         <f t="shared" si="3"/>
@@ -16557,7 +16562,7 @@
     <row r="128" spans="1:65">
       <c r="A128" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B128" t="str">
         <f t="shared" si="3"/>
@@ -16636,7 +16641,7 @@
     <row r="129" spans="1:65">
       <c r="A129" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B129" t="str">
         <f t="shared" si="3"/>
@@ -16715,7 +16720,7 @@
     <row r="130" spans="1:65">
       <c r="A130" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B130" t="str">
         <f t="shared" si="3"/>
@@ -16794,7 +16799,7 @@
     <row r="131" spans="1:65">
       <c r="A131" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B131" t="str">
         <f t="shared" si="3"/>
@@ -16876,7 +16881,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B132" t="str">
         <f t="shared" ref="B132:B168" si="5">TEXT($C132, "HH:mm")</f>
@@ -16955,7 +16960,7 @@
     <row r="133" spans="1:65">
       <c r="A133" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B133" t="str">
         <f t="shared" si="5"/>
@@ -17034,7 +17039,7 @@
     <row r="134" spans="1:65">
       <c r="A134" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B134" t="str">
         <f t="shared" si="5"/>
@@ -17113,7 +17118,7 @@
     <row r="135" spans="1:65">
       <c r="A135" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B135" t="str">
         <f t="shared" si="5"/>
@@ -17192,7 +17197,7 @@
     <row r="136" spans="1:65">
       <c r="A136" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B136" t="str">
         <f t="shared" si="5"/>
@@ -17273,7 +17278,7 @@
     <row r="137" spans="1:65">
       <c r="A137" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B137" t="str">
         <f t="shared" si="5"/>
@@ -17354,7 +17359,7 @@
     <row r="138" spans="1:65">
       <c r="A138" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B138" t="str">
         <f t="shared" si="5"/>
@@ -17433,7 +17438,7 @@
     <row r="139" spans="1:65">
       <c r="A139" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B139" t="str">
         <f t="shared" si="5"/>
@@ -17512,7 +17517,7 @@
     <row r="140" spans="1:65">
       <c r="A140" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B140" t="str">
         <f t="shared" si="5"/>
@@ -17591,7 +17596,7 @@
     <row r="141" spans="1:65">
       <c r="A141" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B141" t="str">
         <f t="shared" si="5"/>
@@ -17670,7 +17675,7 @@
     <row r="142" spans="1:65">
       <c r="A142" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B142" t="str">
         <f t="shared" si="5"/>
@@ -17749,7 +17754,7 @@
     <row r="143" spans="1:65">
       <c r="A143" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B143" t="str">
         <f t="shared" si="5"/>
@@ -17828,7 +17833,7 @@
     <row r="144" spans="1:65">
       <c r="A144" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B144" t="str">
         <f t="shared" si="5"/>
@@ -17907,7 +17912,7 @@
     <row r="145" spans="1:65">
       <c r="A145" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B145" t="str">
         <f t="shared" si="5"/>
@@ -17986,7 +17991,7 @@
     <row r="146" spans="1:65">
       <c r="A146" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B146" t="str">
         <f t="shared" si="5"/>
@@ -18065,7 +18070,7 @@
     <row r="147" spans="1:65">
       <c r="A147" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B147" t="str">
         <f t="shared" si="5"/>
@@ -18144,7 +18149,7 @@
     <row r="148" spans="1:65">
       <c r="A148" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B148" t="str">
         <f t="shared" si="5"/>
@@ -18225,7 +18230,7 @@
     <row r="149" spans="1:65">
       <c r="A149" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B149" t="str">
         <f t="shared" si="5"/>
@@ -18304,7 +18309,7 @@
     <row r="150" spans="1:65">
       <c r="A150" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B150" t="str">
         <f t="shared" si="5"/>
@@ -18383,7 +18388,7 @@
     <row r="151" spans="1:65">
       <c r="A151" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B151" t="str">
         <f t="shared" si="5"/>
@@ -18462,7 +18467,7 @@
     <row r="152" spans="1:65">
       <c r="A152" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B152" t="str">
         <f t="shared" si="5"/>
@@ -18541,7 +18546,7 @@
     <row r="153" spans="1:65">
       <c r="A153" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B153" t="str">
         <f t="shared" si="5"/>
@@ -18620,7 +18625,7 @@
     <row r="154" spans="1:65">
       <c r="A154" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B154" t="str">
         <f t="shared" si="5"/>
@@ -18699,7 +18704,7 @@
     <row r="155" spans="1:65">
       <c r="A155" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B155" t="str">
         <f t="shared" si="5"/>
@@ -18778,7 +18783,7 @@
     <row r="156" spans="1:65">
       <c r="A156" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B156" t="str">
         <f t="shared" si="5"/>
@@ -18857,7 +18862,7 @@
     <row r="157" spans="1:65">
       <c r="A157" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B157" t="str">
         <f t="shared" si="5"/>
@@ -18936,7 +18941,7 @@
     <row r="158" spans="1:65">
       <c r="A158" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B158" t="str">
         <f t="shared" si="5"/>
@@ -19015,7 +19020,7 @@
     <row r="159" spans="1:65">
       <c r="A159" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B159" t="str">
         <f t="shared" si="5"/>
@@ -19094,7 +19099,7 @@
     <row r="160" spans="1:65">
       <c r="A160" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B160" t="str">
         <f t="shared" si="5"/>
@@ -19173,7 +19178,7 @@
     <row r="161" spans="1:65">
       <c r="A161" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B161" t="str">
         <f t="shared" si="5"/>
@@ -19252,7 +19257,7 @@
     <row r="162" spans="1:65">
       <c r="A162" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B162" t="str">
         <f t="shared" si="5"/>
@@ -19331,7 +19336,7 @@
     <row r="163" spans="1:65">
       <c r="A163" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B163" t="str">
         <f t="shared" si="5"/>
@@ -19410,7 +19415,7 @@
     <row r="164" spans="1:65">
       <c r="A164" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B164" t="str">
         <f t="shared" si="5"/>
@@ -19489,7 +19494,7 @@
     <row r="165" spans="1:65">
       <c r="A165" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B165" t="str">
         <f t="shared" si="5"/>
@@ -19568,7 +19573,7 @@
     <row r="166" spans="1:65">
       <c r="A166" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B166" t="str">
         <f t="shared" si="5"/>
@@ -19649,7 +19654,7 @@
     <row r="167" spans="1:65">
       <c r="A167" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B167" t="str">
         <f t="shared" si="5"/>
@@ -19728,7 +19733,7 @@
     <row r="168" spans="1:65">
       <c r="A168" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B168" t="str">
         <f t="shared" si="5"/>
@@ -19810,7 +19815,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B169" t="str">
         <f>TEXT($C169, "HH:mm")</f>
@@ -19892,7 +19897,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B170" t="str">
         <f t="shared" ref="B170:B233" si="7">TEXT($C170, "HH:mm")</f>
@@ -19971,7 +19976,7 @@
     <row r="171" spans="1:65">
       <c r="A171" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B171" t="str">
         <f t="shared" si="7"/>
@@ -20050,7 +20055,7 @@
     <row r="172" spans="1:65">
       <c r="A172" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B172" t="str">
         <f t="shared" si="7"/>
@@ -20131,7 +20136,7 @@
     <row r="173" spans="1:65">
       <c r="A173" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B173" t="str">
         <f t="shared" si="7"/>
@@ -20210,7 +20215,7 @@
     <row r="174" spans="1:65">
       <c r="A174" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B174" t="str">
         <f t="shared" si="7"/>
@@ -20289,7 +20294,7 @@
     <row r="175" spans="1:65">
       <c r="A175" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B175" t="str">
         <f t="shared" si="7"/>
@@ -20368,7 +20373,7 @@
     <row r="176" spans="1:65">
       <c r="A176" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B176" t="str">
         <f t="shared" si="7"/>
@@ -20447,7 +20452,7 @@
     <row r="177" spans="1:65">
       <c r="A177" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B177" t="str">
         <f t="shared" si="7"/>
@@ -20526,7 +20531,7 @@
     <row r="178" spans="1:65">
       <c r="A178" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B178" t="str">
         <f t="shared" si="7"/>
@@ -20607,7 +20612,7 @@
     <row r="179" spans="1:65">
       <c r="A179" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B179" t="str">
         <f t="shared" si="7"/>
@@ -20686,7 +20691,7 @@
     <row r="180" spans="1:65">
       <c r="A180" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B180" t="str">
         <f t="shared" si="7"/>
@@ -20765,7 +20770,7 @@
     <row r="181" spans="1:65">
       <c r="A181" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B181" t="str">
         <f t="shared" si="7"/>
@@ -20846,7 +20851,7 @@
     <row r="182" spans="1:65">
       <c r="A182" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B182" t="str">
         <f t="shared" si="7"/>
@@ -20927,7 +20932,7 @@
     <row r="183" spans="1:65">
       <c r="A183" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B183" t="str">
         <f t="shared" si="7"/>
@@ -21008,7 +21013,7 @@
     <row r="184" spans="1:65">
       <c r="A184" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B184" t="str">
         <f t="shared" si="7"/>
@@ -21091,7 +21096,7 @@
     <row r="185" spans="1:65">
       <c r="A185" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B185" t="str">
         <f t="shared" si="7"/>
@@ -21172,7 +21177,7 @@
     <row r="186" spans="1:65">
       <c r="A186" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B186" t="str">
         <f t="shared" si="7"/>
@@ -21253,7 +21258,7 @@
     <row r="187" spans="1:65">
       <c r="A187" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B187" t="str">
         <f t="shared" si="7"/>
@@ -21334,7 +21339,7 @@
     <row r="188" spans="1:65">
       <c r="A188" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B188" t="str">
         <f t="shared" si="7"/>
@@ -21415,7 +21420,7 @@
     <row r="189" spans="1:65">
       <c r="A189" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B189" t="str">
         <f t="shared" si="7"/>
@@ -21496,7 +21501,7 @@
     <row r="190" spans="1:65">
       <c r="A190" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B190" t="str">
         <f t="shared" si="7"/>
@@ -21579,7 +21584,7 @@
     <row r="191" spans="1:65">
       <c r="A191" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B191" t="str">
         <f t="shared" si="7"/>
@@ -21662,7 +21667,7 @@
     <row r="192" spans="1:65">
       <c r="A192" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B192" t="str">
         <f t="shared" si="7"/>
@@ -21745,7 +21750,7 @@
     <row r="193" spans="1:65">
       <c r="A193" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B193" t="str">
         <f t="shared" si="7"/>
@@ -21828,7 +21833,7 @@
     <row r="194" spans="1:65">
       <c r="A194" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B194" t="str">
         <f t="shared" si="7"/>
@@ -21909,7 +21914,7 @@
     <row r="195" spans="1:65">
       <c r="A195" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B195" t="str">
         <f t="shared" si="7"/>
@@ -21990,7 +21995,7 @@
     <row r="196" spans="1:65">
       <c r="A196" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B196" t="str">
         <f t="shared" si="7"/>
@@ -22073,7 +22078,7 @@
     <row r="197" spans="1:65">
       <c r="A197" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B197" t="str">
         <f t="shared" si="7"/>
@@ -22152,7 +22157,7 @@
     <row r="198" spans="1:65">
       <c r="A198" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B198" t="str">
         <f t="shared" si="7"/>
@@ -22231,7 +22236,7 @@
     <row r="199" spans="1:65">
       <c r="A199" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B199" t="str">
         <f t="shared" si="7"/>
@@ -22310,7 +22315,7 @@
     <row r="200" spans="1:65">
       <c r="A200" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B200" t="str">
         <f t="shared" si="7"/>
@@ -22389,7 +22394,7 @@
     <row r="201" spans="1:65">
       <c r="A201" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B201" t="str">
         <f t="shared" si="7"/>
@@ -22468,7 +22473,7 @@
     <row r="202" spans="1:65">
       <c r="A202" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B202" t="str">
         <f t="shared" si="7"/>
@@ -22549,7 +22554,7 @@
     <row r="203" spans="1:65">
       <c r="A203" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B203" t="str">
         <f t="shared" si="7"/>
@@ -22628,7 +22633,7 @@
     <row r="204" spans="1:65">
       <c r="A204" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B204" t="str">
         <f t="shared" si="7"/>
@@ -22707,7 +22712,7 @@
     <row r="205" spans="1:65">
       <c r="A205" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B205" t="str">
         <f t="shared" si="7"/>
@@ -22786,7 +22791,7 @@
     <row r="206" spans="1:65">
       <c r="A206" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B206" t="str">
         <f t="shared" si="7"/>
@@ -22865,7 +22870,7 @@
     <row r="207" spans="1:65">
       <c r="A207" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B207" t="str">
         <f t="shared" si="7"/>
@@ -22944,7 +22949,7 @@
     <row r="208" spans="1:65">
       <c r="A208" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B208" t="str">
         <f t="shared" si="7"/>
@@ -23025,7 +23030,7 @@
     <row r="209" spans="1:65">
       <c r="A209" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B209" t="str">
         <f t="shared" si="7"/>
@@ -23104,7 +23109,7 @@
     <row r="210" spans="1:65">
       <c r="A210" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B210" t="str">
         <f t="shared" si="7"/>
@@ -23183,7 +23188,7 @@
     <row r="211" spans="1:65">
       <c r="A211" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B211" t="str">
         <f t="shared" si="7"/>
@@ -23264,7 +23269,7 @@
     <row r="212" spans="1:65">
       <c r="A212" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B212" t="str">
         <f t="shared" si="7"/>
@@ -23343,7 +23348,7 @@
     <row r="213" spans="1:65">
       <c r="A213" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B213" t="str">
         <f t="shared" si="7"/>
@@ -23422,7 +23427,7 @@
     <row r="214" spans="1:65">
       <c r="A214" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B214" t="str">
         <f t="shared" si="7"/>
@@ -23501,7 +23506,7 @@
     <row r="215" spans="1:65">
       <c r="A215" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B215" t="str">
         <f t="shared" si="7"/>
@@ -23580,7 +23585,7 @@
     <row r="216" spans="1:65">
       <c r="A216" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B216" t="str">
         <f t="shared" si="7"/>
@@ -23659,7 +23664,7 @@
     <row r="217" spans="1:65">
       <c r="A217" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B217" t="str">
         <f t="shared" si="7"/>
@@ -23738,7 +23743,7 @@
     <row r="218" spans="1:65">
       <c r="A218" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B218" t="str">
         <f t="shared" si="7"/>
@@ -23817,7 +23822,7 @@
     <row r="219" spans="1:65">
       <c r="A219" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B219" t="str">
         <f t="shared" si="7"/>
@@ -23896,7 +23901,7 @@
     <row r="220" spans="1:65">
       <c r="A220" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B220" t="str">
         <f t="shared" si="7"/>
@@ -23977,7 +23982,7 @@
     <row r="221" spans="1:65">
       <c r="A221" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B221" t="str">
         <f t="shared" si="7"/>
@@ -24056,7 +24061,7 @@
     <row r="222" spans="1:65">
       <c r="A222" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B222" t="str">
         <f t="shared" si="7"/>
@@ -24135,7 +24140,7 @@
     <row r="223" spans="1:65">
       <c r="A223" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B223" t="str">
         <f t="shared" si="7"/>
@@ -24214,7 +24219,7 @@
     <row r="224" spans="1:65">
       <c r="A224" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B224" t="str">
         <f t="shared" si="7"/>
@@ -24293,7 +24298,7 @@
     <row r="225" spans="1:65">
       <c r="A225" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B225" t="str">
         <f t="shared" si="7"/>
@@ -24372,7 +24377,7 @@
     <row r="226" spans="1:65">
       <c r="A226" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B226" t="str">
         <f t="shared" si="7"/>
@@ -24451,7 +24456,7 @@
     <row r="227" spans="1:65">
       <c r="A227" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B227" t="str">
         <f t="shared" si="7"/>
@@ -24530,7 +24535,7 @@
     <row r="228" spans="1:65">
       <c r="A228" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B228" t="str">
         <f t="shared" si="7"/>
@@ -24609,7 +24614,7 @@
     <row r="229" spans="1:65">
       <c r="A229" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B229" t="str">
         <f t="shared" si="7"/>
@@ -24688,7 +24693,7 @@
     <row r="230" spans="1:65">
       <c r="A230" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B230" t="str">
         <f t="shared" si="7"/>
@@ -24767,7 +24772,7 @@
     <row r="231" spans="1:65">
       <c r="A231" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B231" t="str">
         <f t="shared" si="7"/>
@@ -24846,7 +24851,7 @@
     <row r="232" spans="1:65">
       <c r="A232" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B232" t="str">
         <f t="shared" si="7"/>
@@ -24925,7 +24930,7 @@
     <row r="233" spans="1:65">
       <c r="A233" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B233" t="str">
         <f t="shared" si="7"/>
@@ -25007,7 +25012,7 @@
   FLOOR( MOD(NOW(),1), TIME(0,5,0) ),
   "HH:mm"
 )</f>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B234" t="str">
         <f t="shared" ref="B234:B291" si="9">TEXT($C234, "HH:mm")</f>
@@ -25086,7 +25091,7 @@
     <row r="235" spans="1:65">
       <c r="A235" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B235" t="str">
         <f t="shared" si="9"/>
@@ -25165,7 +25170,7 @@
     <row r="236" spans="1:65">
       <c r="A236" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B236" t="str">
         <f t="shared" si="9"/>
@@ -25244,7 +25249,7 @@
     <row r="237" spans="1:65">
       <c r="A237" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B237" t="str">
         <f t="shared" si="9"/>
@@ -25323,7 +25328,7 @@
     <row r="238" spans="1:65">
       <c r="A238" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B238" t="str">
         <f t="shared" si="9"/>
@@ -25402,7 +25407,7 @@
     <row r="239" spans="1:65">
       <c r="A239" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B239" t="str">
         <f t="shared" si="9"/>
@@ -25481,7 +25486,7 @@
     <row r="240" spans="1:65">
       <c r="A240" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B240" t="str">
         <f t="shared" si="9"/>
@@ -25560,7 +25565,7 @@
     <row r="241" spans="1:65">
       <c r="A241" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B241" t="str">
         <f t="shared" si="9"/>
@@ -25639,7 +25644,7 @@
     <row r="242" spans="1:65">
       <c r="A242" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B242" t="str">
         <f t="shared" si="9"/>
@@ -25718,7 +25723,7 @@
     <row r="243" spans="1:65">
       <c r="A243" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B243" t="str">
         <f t="shared" si="9"/>
@@ -25797,7 +25802,7 @@
     <row r="244" spans="1:65">
       <c r="A244" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B244" t="str">
         <f t="shared" si="9"/>
@@ -25876,7 +25881,7 @@
     <row r="245" spans="1:65">
       <c r="A245" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B245" t="str">
         <f t="shared" si="9"/>
@@ -25955,7 +25960,7 @@
     <row r="246" spans="1:65">
       <c r="A246" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B246" t="str">
         <f t="shared" si="9"/>
@@ -26034,7 +26039,7 @@
     <row r="247" spans="1:65">
       <c r="A247" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B247" t="str">
         <f t="shared" si="9"/>
@@ -26113,7 +26118,7 @@
     <row r="248" spans="1:65">
       <c r="A248" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B248" t="str">
         <f t="shared" si="9"/>
@@ -26192,7 +26197,7 @@
     <row r="249" spans="1:65">
       <c r="A249" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B249" t="str">
         <f t="shared" si="9"/>
@@ -26271,7 +26276,7 @@
     <row r="250" spans="1:65">
       <c r="A250" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B250" t="str">
         <f t="shared" si="9"/>
@@ -26350,7 +26355,7 @@
     <row r="251" spans="1:65">
       <c r="A251" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B251" t="str">
         <f t="shared" si="9"/>
@@ -26429,7 +26434,7 @@
     <row r="252" spans="1:65">
       <c r="A252" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B252" t="str">
         <f t="shared" si="9"/>
@@ -26508,7 +26513,7 @@
     <row r="253" spans="1:65">
       <c r="A253" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B253" t="str">
         <f t="shared" si="9"/>
@@ -26587,7 +26592,7 @@
     <row r="254" spans="1:65">
       <c r="A254" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B254" t="str">
         <f t="shared" si="9"/>
@@ -26666,7 +26671,7 @@
     <row r="255" spans="1:65">
       <c r="A255" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B255" t="str">
         <f t="shared" si="9"/>
@@ -26745,7 +26750,7 @@
     <row r="256" spans="1:65">
       <c r="A256" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B256" t="str">
         <f t="shared" si="9"/>
@@ -26824,7 +26829,7 @@
     <row r="257" spans="1:65">
       <c r="A257" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B257" t="str">
         <f t="shared" si="9"/>
@@ -26903,7 +26908,7 @@
     <row r="258" spans="1:65">
       <c r="A258" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B258" t="str">
         <f t="shared" si="9"/>
@@ -26982,7 +26987,7 @@
     <row r="259" spans="1:65">
       <c r="A259" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B259" t="str">
         <f t="shared" si="9"/>
@@ -27061,7 +27066,7 @@
     <row r="260" spans="1:65">
       <c r="A260" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>02:20</v>
+        <v>02:25</v>
       </c>
       <c r="B